--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B625301-F6F2-4413-8C13-0B4C7EBA3F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F679A5B8-B187-495D-BB0A-7ADF3FD61CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
@@ -365,7 +365,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="162">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -839,6 +839,18 @@
   </si>
   <si>
     <t>INFIMOTION</t>
+  </si>
+  <si>
+    <t>O001</t>
+  </si>
+  <si>
+    <t>MAERSK</t>
+  </si>
+  <si>
+    <t>DSV</t>
+  </si>
+  <si>
+    <t>WUHAN JINRUI TECH</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1025,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1059,10 +1071,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1076,7 +1084,7 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1137,7 +1145,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1453,11 +1461,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4" filterMode="1">
+  <sheetPr codeName="Feuil4">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:BD51"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BD52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="5" width="10.42578125" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" style="14" customWidth="1"/>
@@ -1481,180 +1489,180 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:56" ht="75" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="16" t="s">
+      <c r="E1" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="O1" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="P1" s="17" t="s">
+      <c r="P1" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="Q1" s="21" t="s">
+      <c r="Q1" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="R1" s="21" t="s">
+      <c r="R1" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="S1" s="21" t="s">
+      <c r="S1" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="T1" s="21" t="s">
+      <c r="T1" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="U1" s="17" t="s">
+      <c r="U1" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="V1" s="17" t="s">
+      <c r="V1" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="W1" s="17" t="s">
+      <c r="W1" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="X1" s="22" t="s">
+      <c r="X1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Y1" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="Z1" s="17" t="s">
+      <c r="Z1" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="AA1" s="17" t="s">
+      <c r="AA1" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="17" t="s">
+      <c r="AB1" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="AC1" s="34" t="s">
+      <c r="AC1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" s="34" t="s">
+      <c r="AD1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="AE1" s="17" t="s">
+      <c r="AE1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="AF1" s="17" t="s">
+      <c r="AF1" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="AG1" s="17" t="s">
+      <c r="AG1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="AH1" s="17" t="s">
+      <c r="AH1" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="AI1" s="17" t="s">
+      <c r="AI1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="AJ1" s="17" t="s">
+      <c r="AJ1" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="AK1" s="17" t="s">
+      <c r="AK1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="AL1" s="17" t="s">
+      <c r="AL1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="AM1" s="17" t="s">
+      <c r="AM1" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="AN1" s="17" t="s">
+      <c r="AN1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="AO1" s="17" t="s">
+      <c r="AO1" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="AP1" s="17" t="s">
+      <c r="AP1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="AQ1" s="17" t="s">
+      <c r="AQ1" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="AR1" s="17" t="s">
+      <c r="AR1" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="AS1" s="17" t="s">
+      <c r="AS1" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="AT1" s="23" t="s">
+      <c r="AT1" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="AU1" s="23" t="s">
+      <c r="AU1" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="AV1" s="34" t="s">
+      <c r="AV1" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="AW1" s="24" t="s">
+      <c r="AW1" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="AX1" s="17" t="s">
+      <c r="AX1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="23" t="s">
+      <c r="AY1" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="AZ1" s="23" t="s">
+      <c r="AZ1" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="BA1" s="17" t="s">
+      <c r="BA1" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="BB1" s="17" t="s">
+      <c r="BB1" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="BC1" s="17" t="s">
+      <c r="BC1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="BD1" s="25" t="s">
+      <c r="BD1" s="24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>416</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="25" t="s">
         <v>77</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -1666,7 +1674,7 @@
       <c r="E2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="26">
         <v>90014400</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -1833,18 +1841,18 @@
       <c r="BB2" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC2" s="28" t="s">
+      <c r="BC2" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="BD2" s="29">
+      <c r="BD2" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="3" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>901</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>92</v>
       </c>
       <c r="C3" s="7" t="s">
@@ -1856,7 +1864,7 @@
       <c r="E3" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="26">
         <v>90012500</v>
       </c>
       <c r="G3" s="8" t="s">
@@ -2023,18 +2031,18 @@
       <c r="BB3" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC3" s="28" t="s">
+      <c r="BC3" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD3" s="29">
+      <c r="BD3" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="4" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>916</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>96</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -2046,7 +2054,7 @@
       <c r="E4" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="26">
         <v>91017700</v>
       </c>
       <c r="G4" s="8" t="s">
@@ -2213,18 +2221,18 @@
       <c r="BB4" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC4" s="28" t="s">
+      <c r="BC4" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD4" s="29">
+      <c r="BD4" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="5" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+    <row r="5" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
         <v>752</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>83</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -2236,7 +2244,7 @@
       <c r="E5" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="26">
         <v>90018000</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -2403,18 +2411,18 @@
       <c r="BB5" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC5" s="28" t="s">
+      <c r="BC5" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="BD5" s="29">
+      <c r="BD5" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="6" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>761</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="29" t="s">
         <v>86</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -2426,7 +2434,7 @@
       <c r="E6" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="26">
         <v>90016900</v>
       </c>
       <c r="G6" s="8" t="s">
@@ -2593,18 +2601,18 @@
       <c r="BB6" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC6" s="28" t="s">
+      <c r="BC6" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="BD6" s="29">
+      <c r="BD6" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="7" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+    <row r="7" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>927</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="29" t="s">
         <v>77</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -2616,7 +2624,7 @@
       <c r="E7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="26">
         <v>90014400</v>
       </c>
       <c r="G7" s="8" t="s">
@@ -2783,18 +2791,18 @@
       <c r="BB7" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC7" s="28" t="s">
+      <c r="BC7" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD7" s="29">
+      <c r="BD7" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="8" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>930</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="30" t="s">
         <v>96</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -2806,7 +2814,7 @@
       <c r="E8" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="26">
         <v>91017700</v>
       </c>
       <c r="G8" s="9" t="s">
@@ -2973,18 +2981,18 @@
       <c r="BB8" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC8" s="28" t="s">
+      <c r="BC8" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD8" s="29">
+      <c r="BD8" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="9" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>931</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="29" t="s">
         <v>83</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -2996,7 +3004,7 @@
       <c r="E9" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="26">
         <v>90018600</v>
       </c>
       <c r="G9" s="11" t="s">
@@ -3005,7 +3013,7 @@
       <c r="H9" s="3">
         <v>26037000</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="I9" s="31" t="s">
         <v>48</v>
       </c>
       <c r="J9" s="3">
@@ -3163,18 +3171,18 @@
       <c r="BB9" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC9" s="28" t="s">
+      <c r="BC9" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD9" s="29">
+      <c r="BD9" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="10" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>932</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="25" t="s">
         <v>92</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -3186,7 +3194,7 @@
       <c r="E10" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="26">
         <v>90012500</v>
       </c>
       <c r="G10" s="8" t="s">
@@ -3353,18 +3361,18 @@
       <c r="BB10" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC10" s="28" t="s">
+      <c r="BC10" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD10" s="29">
+      <c r="BD10" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="11" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+    <row r="11" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>1027</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="29" t="s">
         <v>96</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -3376,7 +3384,7 @@
       <c r="E11" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="26">
         <v>91017700</v>
       </c>
       <c r="G11" s="8" t="s">
@@ -3543,18 +3551,18 @@
       <c r="BB11" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC11" s="28" t="s">
+      <c r="BC11" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD11" s="29">
+      <c r="BD11" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="12" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>1045</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="29" t="s">
         <v>77</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -3566,7 +3574,7 @@
       <c r="E12" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="26">
         <v>90014400</v>
       </c>
       <c r="G12" s="8" t="s">
@@ -3733,18 +3741,18 @@
       <c r="BB12" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC12" s="28" t="s">
+      <c r="BC12" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="BD12" s="29">
+      <c r="BD12" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="13" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>1060</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="29" t="s">
         <v>89</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -3756,7 +3764,7 @@
       <c r="E13" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="26">
         <v>26549502</v>
       </c>
       <c r="G13" s="8" t="s">
@@ -3923,18 +3931,18 @@
       <c r="BB13" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC13" s="28" t="s">
+      <c r="BC13" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD13" s="29">
+      <c r="BD13" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="14" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>233</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="25" t="s">
         <v>67</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -3946,7 +3954,7 @@
       <c r="E14" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="26">
         <v>90009500</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -4114,18 +4122,18 @@
       <c r="BB14" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC14" s="28" t="s">
+      <c r="BC14" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD14" s="29">
+      <c r="BD14" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="15" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>928</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="30" t="s">
         <v>83</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -4137,7 +4145,7 @@
       <c r="E15" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="26">
         <v>90018600</v>
       </c>
       <c r="G15" s="9" t="s">
@@ -4304,18 +4312,18 @@
       <c r="BB15" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC15" s="28" t="s">
+      <c r="BC15" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD15" s="29">
+      <c r="BD15" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="16" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>926</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="25" t="s">
         <v>100</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -4327,7 +4335,7 @@
       <c r="E16" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="26">
         <v>90016000</v>
       </c>
       <c r="G16" s="2" t="s">
@@ -4494,18 +4502,18 @@
       <c r="BB16" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC16" s="28" t="s">
+      <c r="BC16" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="BD16" s="29">
+      <c r="BD16" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="17" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>981</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>100</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -4517,7 +4525,7 @@
       <c r="E17" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="26">
         <v>90016000</v>
       </c>
       <c r="G17" s="8" t="s">
@@ -4684,18 +4692,18 @@
       <c r="BB17" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="BC17" s="28" t="s">
+      <c r="BC17" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD17" s="29">
+      <c r="BD17" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="18" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>120</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="25" t="s">
         <v>67</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -4707,7 +4715,7 @@
       <c r="E18" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="26">
         <v>90009500</v>
       </c>
       <c r="G18" s="2" t="s">
@@ -4874,18 +4882,18 @@
       <c r="BB18" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC18" s="28" t="s">
+      <c r="BC18" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD18" s="29">
+      <c r="BD18" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="19" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>915</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="25" t="s">
         <v>92</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -4897,7 +4905,7 @@
       <c r="E19" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="26">
         <v>90012500</v>
       </c>
       <c r="G19" s="8" t="s">
@@ -5064,18 +5072,18 @@
       <c r="BB19" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC19" s="28" t="s">
+      <c r="BC19" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD19" s="29">
+      <c r="BD19" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="20" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>917</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="25" t="s">
         <v>77</v>
       </c>
       <c r="C20" s="7" t="s">
@@ -5087,7 +5095,7 @@
       <c r="E20" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="26">
         <v>90014400</v>
       </c>
       <c r="G20" s="2" t="s">
@@ -5254,18 +5262,18 @@
       <c r="BB20" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC20" s="28" t="s">
+      <c r="BC20" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD20" s="29">
+      <c r="BD20" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="21" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>918</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="29" t="s">
         <v>96</v>
       </c>
       <c r="C21" s="7" t="s">
@@ -5277,7 +5285,7 @@
       <c r="E21" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="26">
         <v>91017700</v>
       </c>
       <c r="G21" s="10" t="s">
@@ -5444,18 +5452,18 @@
       <c r="BB21" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC21" s="28" t="s">
+      <c r="BC21" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD21" s="29">
+      <c r="BD21" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="22" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>925</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="29" t="s">
         <v>83</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -5467,7 +5475,7 @@
       <c r="E22" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="26">
         <v>90018600</v>
       </c>
       <c r="G22" s="8" t="s">
@@ -5634,18 +5642,18 @@
       <c r="BB22" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC22" s="28" t="s">
+      <c r="BC22" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD22" s="29">
+      <c r="BD22" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="23" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>121</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="25" t="s">
         <v>67</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -5657,7 +5665,7 @@
       <c r="E23" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="26">
         <v>90009500</v>
       </c>
       <c r="G23" s="2" t="s">
@@ -5824,18 +5832,18 @@
       <c r="BB23" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC23" s="28" t="s">
+      <c r="BC23" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD23" s="29">
+      <c r="BD23" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="24" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>912</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="25" t="s">
         <v>83</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -5847,7 +5855,7 @@
       <c r="E24" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="26">
         <v>90018600</v>
       </c>
       <c r="G24" s="2" t="s">
@@ -6014,18 +6022,18 @@
       <c r="BB24" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC24" s="28" t="s">
+      <c r="BC24" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD24" s="29">
+      <c r="BD24" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="25" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>920</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="29" t="s">
         <v>96</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -6037,7 +6045,7 @@
       <c r="E25" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="26">
         <v>91017500</v>
       </c>
       <c r="G25" s="10" t="s">
@@ -6204,18 +6212,18 @@
       <c r="BB25" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC25" s="28" t="s">
+      <c r="BC25" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD25" s="29">
+      <c r="BD25" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="26" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>921</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="29" t="s">
         <v>77</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -6227,7 +6235,7 @@
       <c r="E26" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="26">
         <v>90014400</v>
       </c>
       <c r="G26" s="8" t="s">
@@ -6394,18 +6402,18 @@
       <c r="BB26" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC26" s="28" t="s">
+      <c r="BC26" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD26" s="29">
+      <c r="BD26" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="27" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>1001</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="29" t="s">
         <v>83</v>
       </c>
       <c r="C27" s="7" t="s">
@@ -6417,7 +6425,7 @@
       <c r="E27" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F27" s="27">
+      <c r="F27" s="26">
         <v>90018600</v>
       </c>
       <c r="G27" s="8" t="s">
@@ -6584,18 +6592,18 @@
       <c r="BB27" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC27" s="28" t="s">
+      <c r="BC27" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="BD27" s="29">
+      <c r="BD27" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="28" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>1063</v>
       </c>
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="29" t="s">
         <v>77</v>
       </c>
       <c r="C28" s="7" t="s">
@@ -6607,7 +6615,7 @@
       <c r="E28" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="26">
         <v>90014400</v>
       </c>
       <c r="G28" s="8" t="s">
@@ -6774,18 +6782,18 @@
       <c r="BB28" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC28" s="28" t="s">
+      <c r="BC28" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="BD28" s="29">
+      <c r="BD28" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="29" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>1005</v>
       </c>
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="29" t="s">
         <v>107</v>
       </c>
       <c r="C29" s="7" t="s">
@@ -6797,7 +6805,7 @@
       <c r="E29" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="26">
         <v>9510600</v>
       </c>
       <c r="G29" s="8" t="s">
@@ -6964,18 +6972,18 @@
       <c r="BB29" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC29" s="28" t="s">
+      <c r="BC29" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD29" s="29">
+      <c r="BD29" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="30" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>1006</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="29" t="s">
         <v>110</v>
       </c>
       <c r="C30" s="7" t="s">
@@ -6987,7 +6995,7 @@
       <c r="E30" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="27">
+      <c r="F30" s="26">
         <v>90038200</v>
       </c>
       <c r="G30" s="8" t="s">
@@ -7154,18 +7162,18 @@
       <c r="BB30" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC30" s="28" t="s">
+      <c r="BC30" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD30" s="29">
+      <c r="BD30" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="31" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>1007</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="29" t="s">
         <v>110</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -7177,7 +7185,7 @@
       <c r="E31" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="26">
         <v>900383</v>
       </c>
       <c r="G31" s="8" t="s">
@@ -7344,18 +7352,18 @@
       <c r="BB31" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC31" s="28" t="s">
+      <c r="BC31" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD31" s="29">
+      <c r="BD31" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="32" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>1008</v>
       </c>
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="29" t="s">
         <v>92</v>
       </c>
       <c r="C32" s="7" t="s">
@@ -7367,7 +7375,7 @@
       <c r="E32" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F32" s="27">
+      <c r="F32" s="26">
         <v>90016800</v>
       </c>
       <c r="G32" s="8" t="s">
@@ -7534,18 +7542,18 @@
       <c r="BB32" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC32" s="28" t="s">
+      <c r="BC32" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD32" s="29">
+      <c r="BD32" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="33" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>1009</v>
       </c>
-      <c r="B33" s="30" t="s">
+      <c r="B33" s="29" t="s">
         <v>112</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -7557,7 +7565,7 @@
       <c r="E33" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F33" s="27">
+      <c r="F33" s="26">
         <v>90016700</v>
       </c>
       <c r="G33" s="8" t="s">
@@ -7724,18 +7732,18 @@
       <c r="BB33" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC33" s="28" t="s">
+      <c r="BC33" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD33" s="29">
+      <c r="BD33" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="34" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>1010</v>
       </c>
-      <c r="B34" s="30" t="s">
+      <c r="B34" s="29" t="s">
         <v>77</v>
       </c>
       <c r="C34" s="7" t="s">
@@ -7747,7 +7755,7 @@
       <c r="E34" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F34" s="27">
+      <c r="F34" s="26">
         <v>90017000</v>
       </c>
       <c r="G34" s="8" t="s">
@@ -7776,7 +7784,7 @@
         <v>14</v>
       </c>
       <c r="O34" s="4">
-        <f t="shared" ref="O34:O51" si="21">IF(I34="SFK Freight Forwarder",0,M34+N34-1)</f>
+        <f t="shared" ref="O34:O52" si="21">IF(I34="SFK Freight Forwarder",0,M34+N34-1)</f>
         <v>0</v>
       </c>
       <c r="P34" s="4">
@@ -7875,7 +7883,7 @@
         <v>3</v>
       </c>
       <c r="AQ34" s="4">
-        <f t="shared" ref="AQ34:AQ51" si="35">+AO34+AP34</f>
+        <f t="shared" ref="AQ34:AQ52" si="35">+AO34+AP34</f>
         <v>107</v>
       </c>
       <c r="AR34" s="4">
@@ -7914,18 +7922,18 @@
       <c r="BB34" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC34" s="28" t="s">
+      <c r="BC34" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD34" s="29">
+      <c r="BD34" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="35" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>1012</v>
       </c>
-      <c r="B35" s="30" t="s">
+      <c r="B35" s="29" t="s">
         <v>83</v>
       </c>
       <c r="C35" s="7" t="s">
@@ -7937,7 +7945,7 @@
       <c r="E35" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F35" s="27">
+      <c r="F35" s="26">
         <v>90018000</v>
       </c>
       <c r="G35" s="8" t="s">
@@ -8104,18 +8112,18 @@
       <c r="BB35" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC35" s="28" t="s">
+      <c r="BC35" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD35" s="29">
+      <c r="BD35" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="36" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>1034</v>
       </c>
-      <c r="B36" s="30" t="s">
+      <c r="B36" s="29" t="s">
         <v>96</v>
       </c>
       <c r="C36" s="7" t="s">
@@ -8127,7 +8135,7 @@
       <c r="E36" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F36" s="27">
+      <c r="F36" s="26">
         <v>91017300</v>
       </c>
       <c r="G36" s="8" t="s">
@@ -8294,18 +8302,18 @@
       <c r="BB36" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC36" s="28" t="s">
+      <c r="BC36" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD36" s="29">
+      <c r="BD36" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="37" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>1037</v>
       </c>
-      <c r="B37" s="30" t="s">
+      <c r="B37" s="29" t="s">
         <v>100</v>
       </c>
       <c r="C37" s="7" t="s">
@@ -8317,7 +8325,7 @@
       <c r="E37" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F37" s="27">
+      <c r="F37" s="26">
         <v>90016000</v>
       </c>
       <c r="G37" s="8" t="s">
@@ -8484,18 +8492,18 @@
       <c r="BB37" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC37" s="28" t="s">
+      <c r="BC37" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD37" s="29">
+      <c r="BD37" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="38" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>1040</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="29" t="s">
         <v>89</v>
       </c>
       <c r="C38" s="7" t="s">
@@ -8507,7 +8515,7 @@
       <c r="E38" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F38" s="27">
+      <c r="F38" s="26">
         <v>26549502</v>
       </c>
       <c r="G38" s="8" t="s">
@@ -8674,18 +8682,18 @@
       <c r="BB38" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC38" s="28" t="s">
+      <c r="BC38" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD38" s="29">
+      <c r="BD38" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="39" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>1029</v>
       </c>
-      <c r="B39" s="30" t="s">
+      <c r="B39" s="29" t="s">
         <v>92</v>
       </c>
       <c r="C39" s="7" t="s">
@@ -8697,7 +8705,7 @@
       <c r="E39" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F39" s="27">
+      <c r="F39" s="26">
         <v>90012500</v>
       </c>
       <c r="G39" s="8" t="s">
@@ -8864,18 +8872,18 @@
       <c r="BB39" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC39" s="28" t="s">
+      <c r="BC39" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="BD39" s="29">
+      <c r="BD39" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="40" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>1032</v>
       </c>
-      <c r="B40" s="30" t="s">
+      <c r="B40" s="29" t="s">
         <v>96</v>
       </c>
       <c r="C40" s="7" t="s">
@@ -8887,7 +8895,7 @@
       <c r="E40" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F40" s="27">
+      <c r="F40" s="26">
         <v>91017500</v>
       </c>
       <c r="G40" s="8" t="s">
@@ -9054,18 +9062,18 @@
       <c r="BB40" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC40" s="28" t="s">
+      <c r="BC40" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="BD40" s="29">
+      <c r="BD40" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="41" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>1033</v>
       </c>
-      <c r="B41" s="30" t="s">
+      <c r="B41" s="29" t="s">
         <v>86</v>
       </c>
       <c r="C41" s="7" t="s">
@@ -9077,7 +9085,7 @@
       <c r="E41" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F41" s="27">
+      <c r="F41" s="26">
         <v>92000100</v>
       </c>
       <c r="G41" s="8" t="s">
@@ -9244,18 +9252,18 @@
       <c r="BB41" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC41" s="28" t="s">
+      <c r="BC41" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD41" s="29">
+      <c r="BD41" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="42" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>904</v>
       </c>
-      <c r="B42" s="30" t="s">
+      <c r="B42" s="29" t="s">
         <v>77</v>
       </c>
       <c r="C42" s="7" t="s">
@@ -9267,7 +9275,7 @@
       <c r="E42" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F42" s="27">
+      <c r="F42" s="26">
         <v>90014400</v>
       </c>
       <c r="G42" s="10" t="s">
@@ -9434,18 +9442,18 @@
       <c r="BB42" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC42" s="28" t="s">
+      <c r="BC42" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD42" s="29">
+      <c r="BD42" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="43" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>906</v>
       </c>
-      <c r="B43" s="30" t="s">
+      <c r="B43" s="29" t="s">
         <v>83</v>
       </c>
       <c r="C43" s="7" t="s">
@@ -9457,7 +9465,7 @@
       <c r="E43" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F43" s="27">
+      <c r="F43" s="26">
         <v>90018600</v>
       </c>
       <c r="G43" s="9" t="s">
@@ -9624,18 +9632,18 @@
       <c r="BB43" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC43" s="28" t="s">
+      <c r="BC43" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD43" s="29">
+      <c r="BD43" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="44" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>924</v>
       </c>
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="25" t="s">
         <v>92</v>
       </c>
       <c r="C44" s="7" t="s">
@@ -9647,7 +9655,7 @@
       <c r="E44" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F44" s="27">
+      <c r="F44" s="26">
         <v>90012500</v>
       </c>
       <c r="G44" s="8" t="s">
@@ -9814,18 +9822,18 @@
       <c r="BB44" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC44" s="28" t="s">
+      <c r="BC44" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="BD44" s="29">
+      <c r="BD44" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="45" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>1014</v>
       </c>
-      <c r="B45" s="30" t="s">
+      <c r="B45" s="29" t="s">
         <v>107</v>
       </c>
       <c r="C45" s="7" t="s">
@@ -9837,7 +9845,7 @@
       <c r="E45" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F45" s="27">
+      <c r="F45" s="26">
         <v>9510600</v>
       </c>
       <c r="G45" s="8" t="s">
@@ -10004,18 +10012,18 @@
       <c r="BB45" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC45" s="28" t="s">
+      <c r="BC45" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD45" s="29">
+      <c r="BD45" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="46" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>1015</v>
       </c>
-      <c r="B46" s="30" t="s">
+      <c r="B46" s="29" t="s">
         <v>83</v>
       </c>
       <c r="C46" s="7" t="s">
@@ -10027,7 +10035,7 @@
       <c r="E46" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F46" s="27">
+      <c r="F46" s="26">
         <v>90018000</v>
       </c>
       <c r="G46" s="8" t="s">
@@ -10194,18 +10202,18 @@
       <c r="BB46" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC46" s="28" t="s">
+      <c r="BC46" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD46" s="29">
+      <c r="BD46" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="47" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>1036</v>
       </c>
-      <c r="B47" s="30" t="s">
+      <c r="B47" s="29" t="s">
         <v>96</v>
       </c>
       <c r="C47" s="7" t="s">
@@ -10217,7 +10225,7 @@
       <c r="E47" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F47" s="27">
+      <c r="F47" s="26">
         <v>91017200</v>
       </c>
       <c r="G47" s="8" t="s">
@@ -10384,10 +10392,10 @@
       <c r="BB47" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC47" s="28" t="s">
+      <c r="BC47" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="BD47" s="29">
+      <c r="BD47" s="28">
         <v>46142</v>
       </c>
     </row>
@@ -10395,7 +10403,7 @@
       <c r="A48" s="6">
         <v>1084</v>
       </c>
-      <c r="B48" s="30" t="s">
+      <c r="B48" s="29" t="s">
         <v>83</v>
       </c>
       <c r="C48" s="7" t="s">
@@ -10407,7 +10415,7 @@
       <c r="E48" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F48" s="27">
+      <c r="F48" s="26">
         <v>90018600</v>
       </c>
       <c r="G48" s="8" t="s">
@@ -10574,18 +10582,18 @@
       <c r="BB48" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="BC48" s="28" t="s">
+      <c r="BC48" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="BD48" s="29">
+      <c r="BD48" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="49" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>908</v>
       </c>
-      <c r="B49" s="31" t="s">
+      <c r="B49" s="30" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="7" t="s">
@@ -10597,7 +10605,7 @@
       <c r="E49" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F49" s="27">
+      <c r="F49" s="26">
         <v>90018600</v>
       </c>
       <c r="G49" s="9" t="s">
@@ -10764,18 +10772,18 @@
       <c r="BB49" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC49" s="28" t="s">
+      <c r="BC49" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD49" s="29">
+      <c r="BD49" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="50" spans="1:56" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>907</v>
       </c>
-      <c r="B50" s="31" t="s">
+      <c r="B50" s="30" t="s">
         <v>83</v>
       </c>
       <c r="C50" s="7" t="s">
@@ -10787,7 +10795,7 @@
       <c r="E50" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F50" s="27">
+      <c r="F50" s="26">
         <v>90018600</v>
       </c>
       <c r="G50" s="9" t="s">
@@ -10936,7 +10944,7 @@
       <c r="AV50" s="4">
         <v>17</v>
       </c>
-      <c r="AW50" s="33">
+      <c r="AW50" s="32">
         <f>+AE50+AG50+AI50</f>
         <v>37</v>
       </c>
@@ -10955,33 +10963,33 @@
       <c r="BB50" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="BC50" s="28" t="s">
+      <c r="BC50" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD50" s="29">
+      <c r="BD50" s="28">
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:56" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="15">
+    <row r="51" spans="1:56" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
         <v>1085</v>
       </c>
-      <c r="B51" s="31" t="s">
+      <c r="B51" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="C51" s="33" t="s">
+      <c r="C51" s="32" t="s">
         <v>84</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E51" s="33" t="s">
+      <c r="E51" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="F51" s="27">
+      <c r="F51" s="26">
         <v>90016500</v>
       </c>
-      <c r="G51" s="33" t="s">
+      <c r="G51" s="32" t="s">
         <v>156</v>
       </c>
       <c r="H51" s="3">
@@ -10993,7 +11001,7 @@
       <c r="J51" s="3">
         <v>29159</v>
       </c>
-      <c r="K51" s="33" t="s">
+      <c r="K51" s="32" t="s">
         <v>157</v>
       </c>
       <c r="L51" s="4">
@@ -11003,7 +11011,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="N51" s="33">
+      <c r="N51" s="32">
         <v>4</v>
       </c>
       <c r="O51" s="4">
@@ -11018,147 +11026,310 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="R51" s="33">
+      <c r="R51" s="32">
         <f t="shared" si="24"/>
         <v>13</v>
       </c>
-      <c r="S51" s="33">
+      <c r="S51" s="32">
         <v>4</v>
       </c>
-      <c r="T51" s="33">
+      <c r="T51" s="32">
         <f t="shared" si="25"/>
         <v>16</v>
       </c>
-      <c r="U51" s="33">
+      <c r="U51" s="32">
         <f t="shared" si="26"/>
         <v>17</v>
       </c>
-      <c r="V51" s="33">
-        <v>7</v>
-      </c>
-      <c r="W51" s="33">
+      <c r="V51" s="32">
+        <v>7</v>
+      </c>
+      <c r="W51" s="32">
         <f t="shared" si="27"/>
         <v>23</v>
       </c>
-      <c r="X51" s="33">
+      <c r="X51" s="32">
         <v>5</v>
       </c>
       <c r="Y51" s="4">
         <f t="shared" si="28"/>
         <v>26</v>
       </c>
-      <c r="Z51" s="33">
+      <c r="Z51" s="32">
         <v>29</v>
       </c>
       <c r="AA51" s="7">
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="AB51" s="33">
+      <c r="AB51" s="32">
         <v>4</v>
       </c>
-      <c r="AC51" s="33"/>
-      <c r="AD51" s="33"/>
-      <c r="AE51" s="33">
+      <c r="AC51" s="32"/>
+      <c r="AD51" s="32"/>
+      <c r="AE51" s="32">
         <v>57</v>
       </c>
-      <c r="AF51" s="33">
+      <c r="AF51" s="32">
         <f t="shared" si="30"/>
         <v>88</v>
       </c>
-      <c r="AG51" s="33">
+      <c r="AG51" s="32">
         <v>3</v>
       </c>
-      <c r="AH51" s="33">
+      <c r="AH51" s="32">
         <f t="shared" si="31"/>
         <v>91</v>
       </c>
-      <c r="AI51" s="33">
-        <v>7</v>
-      </c>
-      <c r="AJ51" s="33">
+      <c r="AI51" s="32">
+        <v>7</v>
+      </c>
+      <c r="AJ51" s="32">
         <f t="shared" si="32"/>
         <v>98</v>
       </c>
-      <c r="AK51" s="33"/>
-      <c r="AL51" s="33">
+      <c r="AK51" s="32"/>
+      <c r="AL51" s="32">
         <v>3</v>
       </c>
-      <c r="AM51" s="33">
+      <c r="AM51" s="32">
         <f t="shared" si="33"/>
         <v>101</v>
       </c>
-      <c r="AN51" s="33">
+      <c r="AN51" s="32">
         <v>2</v>
       </c>
-      <c r="AO51" s="33">
+      <c r="AO51" s="32">
         <f t="shared" si="34"/>
         <v>103</v>
       </c>
-      <c r="AP51" s="33">
+      <c r="AP51" s="32">
         <v>2</v>
       </c>
-      <c r="AQ51" s="33">
+      <c r="AQ51" s="32">
         <f t="shared" si="35"/>
         <v>105</v>
       </c>
-      <c r="AR51" s="33">
+      <c r="AR51" s="32">
         <f t="shared" si="36"/>
         <v>112</v>
       </c>
-      <c r="AS51" s="33">
+      <c r="AS51" s="32">
         <f t="shared" si="37"/>
         <v>133</v>
       </c>
-      <c r="AT51" s="33">
+      <c r="AT51" s="32">
         <v>14</v>
       </c>
       <c r="AU51" s="4">
         <f t="shared" si="38"/>
         <v>19</v>
       </c>
-      <c r="AV51" s="33"/>
-      <c r="AW51" s="33">
+      <c r="AV51" s="32"/>
+      <c r="AW51" s="32">
         <f>+AE51+AG51+AI51</f>
         <v>67</v>
       </c>
-      <c r="AX51" s="33">
+      <c r="AX51" s="32">
         <f>+AQ51-R51+1</f>
         <v>93</v>
       </c>
-      <c r="AY51" s="33">
+      <c r="AY51" s="32">
         <f>+AQ51-L51+1</f>
         <v>101</v>
       </c>
-      <c r="AZ51" s="33"/>
-      <c r="BA51" s="33" t="s">
+      <c r="AZ51" s="32"/>
+      <c r="BA51" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="BB51" s="33" t="s">
+      <c r="BB51" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="BC51" s="28" t="s">
+      <c r="BC51" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="BD51" s="29">
+      <c r="BD51" s="28">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="52" spans="1:56" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B52" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C52" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E52" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="F52" s="26">
+        <v>91017700</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="J52" s="3">
+        <v>29159</v>
+      </c>
+      <c r="K52" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="L52" s="4">
+        <v>7</v>
+      </c>
+      <c r="M52" s="4">
+        <v>0</v>
+      </c>
+      <c r="N52" s="32">
+        <v>0</v>
+      </c>
+      <c r="O52" s="4">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="4">
+        <v>0</v>
+      </c>
+      <c r="R52" s="32">
+        <v>0</v>
+      </c>
+      <c r="S52" s="32">
+        <v>0</v>
+      </c>
+      <c r="T52" s="32">
+        <v>0</v>
+      </c>
+      <c r="U52" s="32">
+        <v>7</v>
+      </c>
+      <c r="V52" s="32">
+        <v>7</v>
+      </c>
+      <c r="W52" s="32">
+        <v>14</v>
+      </c>
+      <c r="X52" s="32">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="4">
+        <v>15</v>
+      </c>
+      <c r="Z52" s="32">
+        <v>18</v>
+      </c>
+      <c r="AA52" s="7">
+        <v>19</v>
+      </c>
+      <c r="AB52" s="32">
+        <v>4</v>
+      </c>
+      <c r="AC52" s="32"/>
+      <c r="AD52" s="32"/>
+      <c r="AE52" s="32">
+        <v>41</v>
+      </c>
+      <c r="AF52" s="32">
+        <f t="shared" ref="AF52" si="39">+AE52+AA52-1</f>
+        <v>59</v>
+      </c>
+      <c r="AG52" s="32">
+        <v>3</v>
+      </c>
+      <c r="AH52" s="32">
+        <f t="shared" ref="AH52" si="40">+AF52+AG52</f>
+        <v>62</v>
+      </c>
+      <c r="AI52" s="32">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="32">
+        <f t="shared" ref="AJ52" si="41">+AI52+AH52</f>
+        <v>62</v>
+      </c>
+      <c r="AK52" s="32"/>
+      <c r="AL52" s="32">
+        <v>3</v>
+      </c>
+      <c r="AM52" s="32">
+        <f t="shared" ref="AM52" si="42">+AJ52+AL52</f>
+        <v>65</v>
+      </c>
+      <c r="AN52" s="32">
+        <v>2</v>
+      </c>
+      <c r="AO52" s="32">
+        <f t="shared" ref="AO52" si="43">+AM52+AN52</f>
+        <v>67</v>
+      </c>
+      <c r="AP52" s="32">
+        <v>2</v>
+      </c>
+      <c r="AQ52" s="32">
+        <v>0</v>
+      </c>
+      <c r="AR52" s="32">
+        <v>0</v>
+      </c>
+      <c r="AS52" s="32">
+        <f t="shared" ref="AS52" si="44">+AR52+7+AT52</f>
+        <v>21</v>
+      </c>
+      <c r="AT52" s="32">
+        <v>14</v>
+      </c>
+      <c r="AU52" s="4">
+        <f t="shared" ref="AU52" si="45">+AA52-R52</f>
+        <v>19</v>
+      </c>
+      <c r="AV52" s="32"/>
+      <c r="AW52" s="32">
+        <f>+AE52+AG52+AI52</f>
+        <v>44</v>
+      </c>
+      <c r="AX52" s="32">
+        <f>+AQ52-R52+1</f>
+        <v>1</v>
+      </c>
+      <c r="AY52" s="32">
+        <f>+AU52+AW52+4</f>
+        <v>67</v>
+      </c>
+      <c r="AZ52" s="32"/>
+      <c r="BA52" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="BB52" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="BC52" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="BD52" s="28">
         <v>46143</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:BD51" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="MXVER"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E10 K2:K10 C14:E1048195 K14:K1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E10 K2:K10 K14:K1048195 C14:E1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
       <formula1>shippername</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K51 H52:K1048195 C2:E1048195" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K52 C2:E1048195 H53:K1048195" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
       <formula1>AILNname</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048195" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">
@@ -11167,6 +11338,15 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;K0000FF Internal Use</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9999a5d2-caa4-4f63-bace-dd6824b086db}" enabled="1" method="Standard" siteId="{de415ce7-227e-480f-88c9-c7dab50e161a}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>
--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F679A5B8-B187-495D-BB0A-7ADF3FD61CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F412D0FA-01A6-4C61-83D3-2296F9AED2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -365,7 +365,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="163">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -844,13 +844,16 @@
     <t>O001</t>
   </si>
   <si>
-    <t>MAERSK</t>
-  </si>
-  <si>
     <t>DSV</t>
   </si>
   <si>
     <t>WUHAN JINRUI TECH</t>
+  </si>
+  <si>
+    <t>O002</t>
+  </si>
+  <si>
+    <t>EXPEDITORS</t>
   </si>
 </sst>
 </file>
@@ -861,7 +864,7 @@
     <numFmt numFmtId="164" formatCode="0000000000"/>
     <numFmt numFmtId="165" formatCode="00########"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -924,6 +927,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFF00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1025,7 +1036,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1125,6 +1136,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1467,7 +1481,8 @@
   <dimension ref="A1:BD52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="5" width="10.42578125" customWidth="1"/>
+    <col min="2" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" style="14" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" customWidth="1"/>
     <col min="8" max="8" width="16" style="13" customWidth="1"/>
@@ -1934,7 +1949,7 @@
         <v>26</v>
       </c>
       <c r="Z3" s="7">
-        <f t="shared" ref="Z3:Z50" si="19">+Y3+X3-1</f>
+        <f t="shared" ref="Z3:Z51" si="19">+Y3+X3-1</f>
         <v>30</v>
       </c>
       <c r="AA3" s="7">
@@ -7792,18 +7807,18 @@
         <v>0</v>
       </c>
       <c r="Q34" s="4">
-        <f t="shared" ref="Q34:Q51" si="23">+IF(I34="SFK Freight Forwarder",0,O34+P34-1)</f>
+        <f t="shared" ref="Q34:Q52" si="23">+IF(I34="SFK Freight Forwarder",0,O34+P34-1)</f>
         <v>0</v>
       </c>
       <c r="R34" s="4">
-        <f t="shared" ref="R34:R51" si="24">9+N34</f>
+        <f t="shared" ref="R34:R52" si="24">9+N34</f>
         <v>23</v>
       </c>
       <c r="S34" s="4">
         <v>7</v>
       </c>
       <c r="T34" s="4">
-        <f t="shared" ref="T34:T51" si="25">+R34+S34-1</f>
+        <f t="shared" ref="T34:T52" si="25">+R34+S34-1</f>
         <v>29</v>
       </c>
       <c r="U34" s="4">
@@ -7814,7 +7829,7 @@
         <v>1</v>
       </c>
       <c r="W34" s="4">
-        <f t="shared" ref="W34:W51" si="27">+U34+V34-1</f>
+        <f t="shared" ref="W34:W52" si="27">+U34+V34-1</f>
         <v>30</v>
       </c>
       <c r="X34" s="4">
@@ -7829,7 +7844,7 @@
         <v>33</v>
       </c>
       <c r="AA34" s="7">
-        <f t="shared" ref="AA34:AA51" si="29">+Z34+AB34-1</f>
+        <f t="shared" ref="AA34:AA52" si="29">+Z34+AB34-1</f>
         <v>34</v>
       </c>
       <c r="AB34" s="4">
@@ -7887,7 +7902,7 @@
         <v>107</v>
       </c>
       <c r="AR34" s="4">
-        <f t="shared" ref="AR34:AR51" si="36">+AQ34+7</f>
+        <f t="shared" ref="AR34:AR52" si="36">+AQ34+7</f>
         <v>114</v>
       </c>
       <c r="AS34" s="4">
@@ -10971,8 +10986,8 @@
       </c>
     </row>
     <row r="51" spans="1:56" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
-        <v>1085</v>
+      <c r="A51" s="6" t="s">
+        <v>158</v>
       </c>
       <c r="B51" s="30" t="s">
         <v>154</v>
@@ -10983,8 +10998,8 @@
       <c r="D51" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E51" s="32" t="s">
-        <v>103</v>
+      <c r="E51" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="F51" s="26">
         <v>90016500</v>
@@ -10996,7 +11011,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>32</v>
+        <v>162</v>
       </c>
       <c r="J51" s="3">
         <v>29159</v>
@@ -11008,54 +11023,51 @@
         <v>5</v>
       </c>
       <c r="M51" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N51" s="32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O51" s="4">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P51" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q51" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R51" s="32">
-        <f t="shared" si="24"/>
+        <v>9</v>
+      </c>
+      <c r="S51" s="32">
         <v>13</v>
-      </c>
-      <c r="S51" s="32">
-        <v>4</v>
       </c>
       <c r="T51" s="32">
         <f t="shared" si="25"/>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="U51" s="32">
         <f t="shared" si="26"/>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="V51" s="32">
         <v>7</v>
       </c>
       <c r="W51" s="32">
         <f t="shared" si="27"/>
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="X51" s="32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y51" s="4">
         <f t="shared" si="28"/>
-        <v>26</v>
-      </c>
-      <c r="Z51" s="32">
+        <v>29</v>
+      </c>
+      <c r="Z51" s="7">
+        <f t="shared" si="19"/>
         <v>29</v>
       </c>
       <c r="AA51" s="7">
@@ -11123,7 +11135,7 @@
       </c>
       <c r="AU51" s="4">
         <f t="shared" si="38"/>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AV51" s="32"/>
       <c r="AW51" s="32">
@@ -11132,7 +11144,7 @@
       </c>
       <c r="AX51" s="32">
         <f>+AQ51-R51+1</f>
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AY51" s="32">
         <f>+AQ51-L51+1</f>
@@ -11154,7 +11166,7 @@
     </row>
     <row r="52" spans="1:56" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B52" s="30" t="s">
         <v>96</v>
@@ -11166,7 +11178,7 @@
         <v>74</v>
       </c>
       <c r="E52" s="32" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="F52" s="26">
         <v>91017700</v>
@@ -11178,61 +11190,67 @@
         <v>0</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J52" s="3">
         <v>29159</v>
       </c>
       <c r="K52" s="32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L52" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M52" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N52" s="32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O52" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P52" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q52" s="4">
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>12</v>
       </c>
       <c r="R52" s="32">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S52" s="32">
-        <v>0</v>
-      </c>
-      <c r="T52" s="32">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="T52" s="34">
+        <f t="shared" si="25"/>
+        <v>21</v>
       </c>
       <c r="U52" s="32">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="V52" s="32">
         <v>7</v>
       </c>
       <c r="W52" s="32">
-        <v>14</v>
+        <f t="shared" si="27"/>
+        <v>22</v>
       </c>
       <c r="X52" s="32">
         <v>1</v>
       </c>
       <c r="Y52" s="4">
-        <v>15</v>
-      </c>
-      <c r="Z52" s="32">
-        <v>18</v>
+        <f t="shared" ref="Y52" si="39">+ROUNDDOWN(W52/7,0)*7+X52</f>
+        <v>22</v>
+      </c>
+      <c r="Z52" s="7">
+        <f t="shared" ref="Z52" si="40">+Y52+X52-1</f>
+        <v>22</v>
       </c>
       <c r="AA52" s="7">
-        <v>19</v>
+        <f t="shared" si="29"/>
+        <v>25</v>
       </c>
       <c r="AB52" s="32">
         <v>4</v>
@@ -11243,70 +11261,72 @@
         <v>41</v>
       </c>
       <c r="AF52" s="32">
-        <f t="shared" ref="AF52" si="39">+AE52+AA52-1</f>
-        <v>59</v>
+        <f t="shared" ref="AF52" si="41">+AE52+AA52-1</f>
+        <v>65</v>
       </c>
       <c r="AG52" s="32">
         <v>3</v>
       </c>
       <c r="AH52" s="32">
-        <f t="shared" ref="AH52" si="40">+AF52+AG52</f>
-        <v>62</v>
+        <f t="shared" ref="AH52" si="42">+AF52+AG52</f>
+        <v>68</v>
       </c>
       <c r="AI52" s="32">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ52" s="32">
-        <f t="shared" ref="AJ52" si="41">+AI52+AH52</f>
-        <v>62</v>
+        <f t="shared" ref="AJ52" si="43">+AI52+AH52</f>
+        <v>75</v>
       </c>
       <c r="AK52" s="32"/>
       <c r="AL52" s="32">
         <v>3</v>
       </c>
       <c r="AM52" s="32">
-        <f t="shared" ref="AM52" si="42">+AJ52+AL52</f>
-        <v>65</v>
+        <f t="shared" ref="AM52" si="44">+AJ52+AL52</f>
+        <v>78</v>
       </c>
       <c r="AN52" s="32">
         <v>2</v>
       </c>
       <c r="AO52" s="32">
-        <f t="shared" ref="AO52" si="43">+AM52+AN52</f>
-        <v>67</v>
+        <f t="shared" ref="AO52" si="45">+AM52+AN52</f>
+        <v>80</v>
       </c>
       <c r="AP52" s="32">
         <v>2</v>
       </c>
       <c r="AQ52" s="32">
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>82</v>
       </c>
       <c r="AR52" s="32">
-        <v>0</v>
+        <f t="shared" si="36"/>
+        <v>89</v>
       </c>
       <c r="AS52" s="32">
-        <f t="shared" ref="AS52" si="44">+AR52+7+AT52</f>
-        <v>21</v>
+        <f t="shared" ref="AS52" si="46">+AR52+7+AT52</f>
+        <v>110</v>
       </c>
       <c r="AT52" s="32">
         <v>14</v>
       </c>
       <c r="AU52" s="4">
-        <f t="shared" ref="AU52" si="45">+AA52-R52</f>
-        <v>19</v>
+        <f t="shared" ref="AU52" si="47">+AA52-R52</f>
+        <v>16</v>
       </c>
       <c r="AV52" s="32"/>
       <c r="AW52" s="32">
         <f>+AE52+AG52+AI52</f>
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AX52" s="32">
         <f>+AQ52-R52+1</f>
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="AY52" s="32">
         <f>+AU52+AW52+4</f>
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AZ52" s="32"/>
       <c r="BA52" s="32" t="s">
@@ -11329,7 +11349,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E10 K2:K10 K14:K1048195 C14:E1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
       <formula1>shippername</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K52 C2:E1048195 H53:K1048195" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K52 H53:K1048195 C2:E1048195" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
       <formula1>AILNname</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048195" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F412D0FA-01A6-4C61-83D3-2296F9AED2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40930431-0DC3-44B2-9B50-B6E54B481E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40930431-0DC3-44B2-9B50-B6E54B481E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE5EACD-C571-4E8A-9C6E-9380F8C04152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -43,6 +43,7 @@
   <authors>
     <author>ZHAO Tengda</author>
     <author>KERHOAS Delphine</author>
+    <author>OLMEDO Jorge</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{76836CDF-0CCC-4954-9A5F-D98726354FA2}">
@@ -360,6 +361,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="AE51" authorId="2" shapeId="0" xr:uid="{03B2F475-038D-443C-85E7-A56E14FE222A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>OLMEDO Jorge:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+from 57 to 37 with new LSP</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -864,7 +889,7 @@
     <numFmt numFmtId="164" formatCode="0000000000"/>
     <numFmt numFmtId="165" formatCode="00########"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -939,8 +964,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1007,6 +1045,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1036,7 +1080,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1138,6 +1182,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7792,18 +7839,18 @@
         <v>7</v>
       </c>
       <c r="M34" s="4">
-        <f t="shared" ref="M34:M51" si="20">+IF(I34="SFK Freight Forwarder",0,9)</f>
+        <f t="shared" ref="M34:M50" si="20">+IF(I34="SFK Freight Forwarder",0,9)</f>
         <v>0</v>
       </c>
       <c r="N34" s="4">
         <v>14</v>
       </c>
       <c r="O34" s="4">
-        <f t="shared" ref="O34:O52" si="21">IF(I34="SFK Freight Forwarder",0,M34+N34-1)</f>
+        <f t="shared" ref="O34:O50" si="21">IF(I34="SFK Freight Forwarder",0,M34+N34-1)</f>
         <v>0</v>
       </c>
       <c r="P34" s="4">
-        <f t="shared" ref="P34:P51" si="22">+IF(I34="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P34:P50" si="22">+IF(I34="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q34" s="4">
@@ -7811,7 +7858,7 @@
         <v>0</v>
       </c>
       <c r="R34" s="4">
-        <f t="shared" ref="R34:R52" si="24">9+N34</f>
+        <f t="shared" ref="R34:R50" si="24">9+N34</f>
         <v>23</v>
       </c>
       <c r="S34" s="4">
@@ -11079,26 +11126,26 @@
       </c>
       <c r="AC51" s="32"/>
       <c r="AD51" s="32"/>
-      <c r="AE51" s="32">
-        <v>57</v>
+      <c r="AE51" s="35">
+        <v>39</v>
       </c>
       <c r="AF51" s="32">
         <f t="shared" si="30"/>
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="AG51" s="32">
         <v>3</v>
       </c>
       <c r="AH51" s="32">
         <f t="shared" si="31"/>
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="AI51" s="32">
         <v>7</v>
       </c>
       <c r="AJ51" s="32">
         <f t="shared" si="32"/>
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="AK51" s="32"/>
       <c r="AL51" s="32">
@@ -11106,29 +11153,29 @@
       </c>
       <c r="AM51" s="32">
         <f t="shared" si="33"/>
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="AN51" s="32">
         <v>2</v>
       </c>
       <c r="AO51" s="32">
         <f t="shared" si="34"/>
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="AP51" s="32">
         <v>2</v>
       </c>
       <c r="AQ51" s="32">
         <f t="shared" si="35"/>
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="AR51" s="32">
         <f t="shared" si="36"/>
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AS51" s="32">
         <f t="shared" si="37"/>
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="AT51" s="32">
         <v>14</v>
@@ -11140,15 +11187,15 @@
       <c r="AV51" s="32"/>
       <c r="AW51" s="32">
         <f>+AE51+AG51+AI51</f>
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="AX51" s="32">
         <f>+AQ51-R51+1</f>
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="AY51" s="32">
         <f>+AQ51-L51+1</f>
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="AZ51" s="32"/>
       <c r="BA51" s="32" t="s">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BDF8F0B-200B-4692-8694-4BF1F9C4070E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B08D69B-2D8F-4C24-BA34-C6EEA0952E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -1541,7 +1541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4" filterMode="1">
+  <sheetPr codeName="Feuil4">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF53"/>
@@ -1740,7 +1740,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>60</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>120</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>121</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>233</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>416</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>752</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>761</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>888</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>901</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>904</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>906</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>907</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>908</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>910</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>912</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>916</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>917</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>918</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>920</v>
       </c>
@@ -5229,7 +5229,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>924</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>925</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>928</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>930</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>931</v>
       </c>
@@ -6447,7 +6447,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>932</v>
       </c>
@@ -6621,7 +6621,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>1005</v>
       </c>
@@ -6796,7 +6796,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>1006</v>
       </c>
@@ -6971,7 +6971,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>1007</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>1008</v>
       </c>
@@ -7321,7 +7321,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>1009</v>
       </c>
@@ -7496,7 +7496,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>1010</v>
       </c>
@@ -7671,7 +7671,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>1012</v>
       </c>
@@ -7846,7 +7846,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>1014</v>
       </c>
@@ -8021,7 +8021,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>1015</v>
       </c>
@@ -8196,7 +8196,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1034</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>1036</v>
       </c>
@@ -8546,7 +8546,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>1037</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>1039</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>1040</v>
       </c>
@@ -9070,7 +9070,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>1045</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>1084</v>
       </c>
@@ -10803,16 +10803,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="47">
-      <filters>
-        <filter val="Direct"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AY43">
-      <sortCondition ref="A1:A53"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K16:K1048196 C16:E1048196 K2:K12 C2:E12" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B08D69B-2D8F-4C24-BA34-C6EEA0952E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D8FA55-00D3-49FB-BC7F-CC936D077B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
@@ -1541,7 +1541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4">
+  <sheetPr codeName="Feuil4" filterMode="1">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF53"/>
@@ -1551,13 +1551,13 @@
     <col min="2" max="2" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="15.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="15.5703125" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="28" width="10.42578125" customWidth="1"/>
@@ -1740,7 +1740,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>60</v>
       </c>
@@ -1778,44 +1778,44 @@
         <v>7</v>
       </c>
       <c r="M2" s="3">
-        <f>+IF(I2="SFK Freight Forwarder",L2,9)</f>
+        <f t="shared" ref="M2:M33" si="0">+IF(I2="SFK Freight Forwarder",L2,9)</f>
         <v>9</v>
       </c>
       <c r="N2" s="3">
         <v>7</v>
       </c>
       <c r="O2" s="3">
-        <f>IF(I2="SFK Freight Forwarder",M2,M2+N2-1)</f>
+        <f t="shared" ref="O2:O33" si="1">IF(I2="SFK Freight Forwarder",M2,M2+N2-1)</f>
         <v>15</v>
       </c>
       <c r="P2" s="3">
-        <f>+IF(I2="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P2:P26" si="2">+IF(I2="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q2" s="3">
-        <f>+IF(I2="SFK Freight Forwarder",O2,O2+P2-1)</f>
+        <f t="shared" ref="Q2:Q33" si="3">+IF(I2="SFK Freight Forwarder",O2,O2+P2-1)</f>
         <v>19</v>
       </c>
       <c r="R2" s="3">
-        <f>9+N2</f>
+        <f t="shared" ref="R2:R45" si="4">9+N2</f>
         <v>16</v>
       </c>
       <c r="S2" s="3">
         <v>7</v>
       </c>
       <c r="T2" s="3">
-        <f>+R2+S2-1</f>
+        <f t="shared" ref="T2:T33" si="5">+R2+S2-1</f>
         <v>22</v>
       </c>
       <c r="U2" s="3">
-        <f>+T2+1</f>
+        <f t="shared" ref="U2:U46" si="6">+T2+1</f>
         <v>23</v>
       </c>
       <c r="V2" s="3">
         <v>1</v>
       </c>
       <c r="W2" s="3">
-        <f>+U2+V2-1</f>
+        <f t="shared" ref="W2:W33" si="7">+U2+V2-1</f>
         <v>23</v>
       </c>
       <c r="X2" s="3">
@@ -1829,7 +1829,7 @@
         <v>25</v>
       </c>
       <c r="AA2" s="6">
-        <f>+Z2+AB2-1</f>
+        <f t="shared" ref="AA2:AA16" si="8">+Z2+AB2-1</f>
         <v>27</v>
       </c>
       <c r="AB2" s="3">
@@ -1845,21 +1845,21 @@
         <v>46</v>
       </c>
       <c r="AF2" s="3">
-        <f>+AE2+AA2-1</f>
+        <f t="shared" ref="AF2:AF33" si="9">+AE2+AA2-1</f>
         <v>72</v>
       </c>
       <c r="AG2" s="6">
         <v>3</v>
       </c>
       <c r="AH2" s="6">
-        <f>+AF2+AG2</f>
+        <f t="shared" ref="AH2:AH33" si="10">+AF2+AG2</f>
         <v>75</v>
       </c>
       <c r="AI2" s="3">
         <v>7</v>
       </c>
       <c r="AJ2" s="3">
-        <f>+AI2+AH2</f>
+        <f t="shared" ref="AJ2:AJ33" si="11">+AI2+AH2</f>
         <v>82</v>
       </c>
       <c r="AK2" s="3" t="s">
@@ -1869,36 +1869,36 @@
         <v>2</v>
       </c>
       <c r="AM2" s="3">
-        <f>+AJ2+AL2</f>
+        <f t="shared" ref="AM2:AM33" si="12">+AJ2+AL2</f>
         <v>84</v>
       </c>
       <c r="AN2" s="3">
         <v>2</v>
       </c>
       <c r="AO2" s="3">
-        <f>+AM2+AN2</f>
+        <f t="shared" ref="AO2:AO33" si="13">+AM2+AN2</f>
         <v>86</v>
       </c>
       <c r="AP2" s="3">
         <v>5</v>
       </c>
       <c r="AQ2" s="3">
-        <f>+AO2+AP2</f>
+        <f t="shared" ref="AQ2:AQ33" si="14">+AO2+AP2</f>
         <v>91</v>
       </c>
       <c r="AR2" s="3">
-        <f>+AQ2+7</f>
+        <f t="shared" ref="AR2:AR33" si="15">+AQ2+7</f>
         <v>98</v>
       </c>
       <c r="AS2" s="3">
-        <f>+AR2+7+AT2</f>
+        <f t="shared" ref="AS2:AS33" si="16">+AR2+7+AT2</f>
         <v>115</v>
       </c>
       <c r="AT2" s="3">
         <v>10</v>
       </c>
       <c r="AU2" s="3">
-        <f>+AA2-R2</f>
+        <f t="shared" ref="AU2:AU33" si="17">+AA2-R2</f>
         <v>11</v>
       </c>
       <c r="AV2" s="3" t="s">
@@ -1914,7 +1914,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>120</v>
       </c>
@@ -1952,44 +1952,44 @@
         <v>7</v>
       </c>
       <c r="M3" s="3">
-        <f>+IF(I3="SFK Freight Forwarder",L3,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N3" s="3">
         <v>14</v>
       </c>
       <c r="O3" s="3">
-        <f>IF(I3="SFK Freight Forwarder",M3,M3+N3-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P3" s="3">
-        <f>+IF(I3="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q3" s="3">
-        <f>+IF(I3="SFK Freight Forwarder",O3,O3+P3-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R3" s="3">
-        <f>9+N3</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S3" s="3">
         <v>7</v>
       </c>
       <c r="T3" s="3">
-        <f>+R3+S3-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U3" s="3">
-        <f>+T3+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V3" s="3">
         <v>2</v>
       </c>
       <c r="W3" s="3">
-        <f>+U3+V3-1</f>
+        <f t="shared" si="7"/>
         <v>31</v>
       </c>
       <c r="X3" s="3">
@@ -2003,7 +2003,7 @@
         <v>33</v>
       </c>
       <c r="AA3" s="6">
-        <f>+Z3+AB3-1</f>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
       <c r="AB3" s="3">
@@ -2019,21 +2019,21 @@
         <v>68</v>
       </c>
       <c r="AF3" s="3">
-        <f>+AE3+AA3-1</f>
+        <f t="shared" si="9"/>
         <v>102</v>
       </c>
       <c r="AG3" s="6">
         <v>3</v>
       </c>
       <c r="AH3" s="6">
-        <f>+AF3+AG3</f>
+        <f t="shared" si="10"/>
         <v>105</v>
       </c>
       <c r="AI3" s="3">
         <v>7</v>
       </c>
       <c r="AJ3" s="3">
-        <f>+AI3+AH3</f>
+        <f t="shared" si="11"/>
         <v>112</v>
       </c>
       <c r="AK3" s="3" t="s">
@@ -2043,36 +2043,36 @@
         <v>2</v>
       </c>
       <c r="AM3" s="3">
-        <f>+AJ3+AL3</f>
+        <f t="shared" si="12"/>
         <v>114</v>
       </c>
       <c r="AN3" s="3">
         <v>2</v>
       </c>
       <c r="AO3" s="3">
-        <f>+AM3+AN3</f>
+        <f t="shared" si="13"/>
         <v>116</v>
       </c>
       <c r="AP3" s="3">
         <v>3</v>
       </c>
       <c r="AQ3" s="3">
-        <f>+AO3+AP3</f>
+        <f t="shared" si="14"/>
         <v>119</v>
       </c>
       <c r="AR3" s="3">
-        <f>+AQ3+7</f>
+        <f t="shared" si="15"/>
         <v>126</v>
       </c>
       <c r="AS3" s="3">
-        <f>+AR3+7+AT3</f>
+        <f t="shared" si="16"/>
         <v>143</v>
       </c>
       <c r="AT3" s="3">
         <v>10</v>
       </c>
       <c r="AU3" s="3">
-        <f>+AA3-R3</f>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="AV3" s="3" t="s">
@@ -2088,7 +2088,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>121</v>
       </c>
@@ -2126,44 +2126,44 @@
         <v>7</v>
       </c>
       <c r="M4" s="3">
-        <f>+IF(I4="SFK Freight Forwarder",L4,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N4" s="3">
         <v>14</v>
       </c>
       <c r="O4" s="3">
-        <f>IF(I4="SFK Freight Forwarder",M4,M4+N4-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P4" s="3">
-        <f>+IF(I4="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q4" s="3">
-        <f>+IF(I4="SFK Freight Forwarder",O4,O4+P4-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R4" s="3">
-        <f>9+N4</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S4" s="3">
         <v>7</v>
       </c>
       <c r="T4" s="3">
-        <f>+R4+S4-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U4" s="3">
-        <f>+T4+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V4" s="3">
         <v>3</v>
       </c>
       <c r="W4" s="3">
-        <f>+U4+V4-1</f>
+        <f t="shared" si="7"/>
         <v>32</v>
       </c>
       <c r="X4" s="3">
@@ -2177,7 +2177,7 @@
         <v>33</v>
       </c>
       <c r="AA4" s="6">
-        <f>+Z4+AB4-1</f>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
       <c r="AB4" s="3">
@@ -2193,21 +2193,21 @@
         <v>75</v>
       </c>
       <c r="AF4" s="3">
-        <f>+AE4+AA4-1</f>
+        <f t="shared" si="9"/>
         <v>109</v>
       </c>
       <c r="AG4" s="6">
         <v>3</v>
       </c>
       <c r="AH4" s="6">
-        <f>+AF4+AG4</f>
+        <f t="shared" si="10"/>
         <v>112</v>
       </c>
       <c r="AI4" s="3">
         <v>7</v>
       </c>
       <c r="AJ4" s="3">
-        <f>+AI4+AH4</f>
+        <f t="shared" si="11"/>
         <v>119</v>
       </c>
       <c r="AK4" s="3" t="s">
@@ -2217,36 +2217,36 @@
         <v>2</v>
       </c>
       <c r="AM4" s="3">
-        <f>+AJ4+AL4</f>
+        <f t="shared" si="12"/>
         <v>121</v>
       </c>
       <c r="AN4" s="3">
         <v>2</v>
       </c>
       <c r="AO4" s="3">
-        <f>+AM4+AN4</f>
+        <f t="shared" si="13"/>
         <v>123</v>
       </c>
       <c r="AP4" s="3">
         <v>3</v>
       </c>
       <c r="AQ4" s="3">
-        <f>+AO4+AP4</f>
+        <f t="shared" si="14"/>
         <v>126</v>
       </c>
       <c r="AR4" s="3">
-        <f>+AQ4+7</f>
+        <f t="shared" si="15"/>
         <v>133</v>
       </c>
       <c r="AS4" s="3">
-        <f>+AR4+7+AT4</f>
+        <f t="shared" si="16"/>
         <v>150</v>
       </c>
       <c r="AT4" s="3">
         <v>10</v>
       </c>
       <c r="AU4" s="3">
-        <f>+AA4-R4</f>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="AV4" s="3" t="s">
@@ -2262,7 +2262,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>233</v>
       </c>
@@ -2300,44 +2300,44 @@
         <v>7</v>
       </c>
       <c r="M5" s="3">
-        <f>+IF(I5="SFK Freight Forwarder",L5,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N5" s="3">
         <v>7</v>
       </c>
       <c r="O5" s="3">
-        <f>IF(I5="SFK Freight Forwarder",M5,M5+N5-1)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="P5" s="3">
-        <f>+IF(I5="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q5" s="3">
-        <f>+IF(I5="SFK Freight Forwarder",O5,O5+P5-1)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="R5" s="3">
-        <f>9+N5</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S5" s="3">
         <v>7</v>
       </c>
       <c r="T5" s="3">
-        <f>+R5+S5-1</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="U5" s="3">
-        <f>+T5+1</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="V5" s="3">
         <v>2</v>
       </c>
       <c r="W5" s="3">
-        <f>+U5+V5-1</f>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="X5" s="3">
@@ -2352,7 +2352,7 @@
         <v>31</v>
       </c>
       <c r="AA5" s="6">
-        <f>+Z5+AB5-1</f>
+        <f t="shared" si="8"/>
         <v>33</v>
       </c>
       <c r="AB5" s="3">
@@ -2368,21 +2368,21 @@
         <v>41</v>
       </c>
       <c r="AF5" s="3">
-        <f>+AE5+AA5-1</f>
+        <f t="shared" si="9"/>
         <v>73</v>
       </c>
       <c r="AG5" s="6">
         <v>3</v>
       </c>
       <c r="AH5" s="6">
-        <f>+AF5+AG5</f>
+        <f t="shared" si="10"/>
         <v>76</v>
       </c>
       <c r="AI5" s="3">
         <v>0</v>
       </c>
       <c r="AJ5" s="3">
-        <f>+AI5+AH5</f>
+        <f t="shared" si="11"/>
         <v>76</v>
       </c>
       <c r="AK5" s="3" t="s">
@@ -2392,36 +2392,36 @@
         <v>2</v>
       </c>
       <c r="AM5" s="3">
-        <f>+AJ5+AL5</f>
+        <f t="shared" si="12"/>
         <v>78</v>
       </c>
       <c r="AN5" s="3">
         <v>2</v>
       </c>
       <c r="AO5" s="3">
-        <f>+AM5+AN5</f>
+        <f t="shared" si="13"/>
         <v>80</v>
       </c>
       <c r="AP5" s="3">
         <v>4</v>
       </c>
       <c r="AQ5" s="3">
-        <f>+AO5+AP5</f>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="AR5" s="3">
-        <f>+AQ5+7</f>
+        <f t="shared" si="15"/>
         <v>91</v>
       </c>
       <c r="AS5" s="3">
-        <f>+AR5+7+AT5</f>
+        <f t="shared" si="16"/>
         <v>104</v>
       </c>
       <c r="AT5" s="3">
         <v>6</v>
       </c>
       <c r="AU5" s="3">
-        <f>+AA5-R5</f>
+        <f t="shared" si="17"/>
         <v>17</v>
       </c>
       <c r="AV5" s="3" t="s">
@@ -2437,7 +2437,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>416</v>
       </c>
@@ -2475,44 +2475,44 @@
         <v>7</v>
       </c>
       <c r="M6" s="3">
-        <f>+IF(I6="SFK Freight Forwarder",L6,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N6" s="3">
         <v>7</v>
       </c>
       <c r="O6" s="3">
-        <f>IF(I6="SFK Freight Forwarder",M6,M6+N6-1)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="P6" s="3">
-        <f>+IF(I6="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q6" s="3">
-        <f>+IF(I6="SFK Freight Forwarder",O6,O6+P6-1)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="R6" s="3">
-        <f>9+N6</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S6" s="3">
         <v>7</v>
       </c>
       <c r="T6" s="3">
-        <f>+R6+S6-1</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="U6" s="3">
-        <f>+T6+1</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="V6" s="3">
         <v>4</v>
       </c>
       <c r="W6" s="3">
-        <f>+U6+V6-1</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="X6" s="3">
@@ -2527,7 +2527,7 @@
         <v>30</v>
       </c>
       <c r="AA6" s="6">
-        <f>+Z6+AB6-1</f>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="AB6" s="3">
@@ -2543,21 +2543,21 @@
         <v>46</v>
       </c>
       <c r="AF6" s="3">
-        <f>+AE6+AA6-1</f>
+        <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="AG6" s="6">
         <v>3</v>
       </c>
       <c r="AH6" s="6">
-        <f>+AF6+AG6</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="AI6" s="3">
         <v>0</v>
       </c>
       <c r="AJ6" s="3">
-        <f>+AI6+AH6</f>
+        <f t="shared" si="11"/>
         <v>80</v>
       </c>
       <c r="AK6" s="3" t="s">
@@ -2567,36 +2567,36 @@
         <v>4</v>
       </c>
       <c r="AM6" s="3">
-        <f>+AJ6+AL6</f>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="AN6" s="3">
         <v>3</v>
       </c>
       <c r="AO6" s="3">
-        <f>+AM6+AN6</f>
+        <f t="shared" si="13"/>
         <v>87</v>
       </c>
       <c r="AP6" s="3">
         <v>4</v>
       </c>
       <c r="AQ6" s="3">
-        <f>+AO6+AP6</f>
+        <f t="shared" si="14"/>
         <v>91</v>
       </c>
       <c r="AR6" s="3">
-        <f>+AQ6+7</f>
+        <f t="shared" si="15"/>
         <v>98</v>
       </c>
       <c r="AS6" s="3">
-        <f>+AR6+7+AT6</f>
+        <f t="shared" si="16"/>
         <v>112</v>
       </c>
       <c r="AT6" s="3">
         <v>7</v>
       </c>
       <c r="AU6" s="3">
-        <f>+AA6-R6</f>
+        <f t="shared" si="17"/>
         <v>16</v>
       </c>
       <c r="AV6" s="3" t="s">
@@ -2612,7 +2612,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>752</v>
       </c>
@@ -2650,44 +2650,44 @@
         <v>7</v>
       </c>
       <c r="M7" s="3">
-        <f>+IF(I7="SFK Freight Forwarder",L7,9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N7" s="3">
         <v>7</v>
       </c>
       <c r="O7" s="3">
-        <f>IF(I7="SFK Freight Forwarder",M7,M7+N7-1)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="P7" s="3">
-        <f>+IF(I7="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q7" s="3">
-        <f>+IF(I7="SFK Freight Forwarder",O7,O7+P7-1)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="R7" s="3">
-        <f>9+N7</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S7" s="3">
         <v>7</v>
       </c>
       <c r="T7" s="3">
-        <f>+R7+S7-1</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="U7" s="3">
-        <f>+T7+1</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="V7" s="3">
         <v>8</v>
       </c>
       <c r="W7" s="3">
-        <f>+U7+V7-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X7" s="3">
@@ -2702,7 +2702,7 @@
         <v>33</v>
       </c>
       <c r="AA7" s="6">
-        <f>+Z7+AB7-1</f>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
       <c r="AB7" s="3">
@@ -2718,21 +2718,21 @@
         <v>39</v>
       </c>
       <c r="AF7" s="3">
-        <f>+AE7+AA7-1</f>
+        <f t="shared" si="9"/>
         <v>73</v>
       </c>
       <c r="AG7" s="6">
         <v>3</v>
       </c>
       <c r="AH7" s="6">
-        <f>+AF7+AG7</f>
+        <f t="shared" si="10"/>
         <v>76</v>
       </c>
       <c r="AI7" s="3">
         <v>0</v>
       </c>
       <c r="AJ7" s="3">
-        <f>+AI7+AH7</f>
+        <f t="shared" si="11"/>
         <v>76</v>
       </c>
       <c r="AK7" s="3" t="s">
@@ -2742,36 +2742,36 @@
         <v>2</v>
       </c>
       <c r="AM7" s="3">
-        <f>+AJ7+AL7</f>
+        <f t="shared" si="12"/>
         <v>78</v>
       </c>
       <c r="AN7" s="3">
         <v>2</v>
       </c>
       <c r="AO7" s="3">
-        <f>+AM7+AN7</f>
+        <f t="shared" si="13"/>
         <v>80</v>
       </c>
       <c r="AP7" s="3">
         <v>6</v>
       </c>
       <c r="AQ7" s="3">
-        <f>+AO7+AP7</f>
+        <f t="shared" si="14"/>
         <v>86</v>
       </c>
       <c r="AR7" s="3">
-        <f>+AQ7+7</f>
+        <f t="shared" si="15"/>
         <v>93</v>
       </c>
       <c r="AS7" s="3">
-        <f>+AR7+7+AT7</f>
+        <f t="shared" si="16"/>
         <v>114</v>
       </c>
       <c r="AT7" s="3">
         <v>14</v>
       </c>
       <c r="AU7" s="3">
-        <f>+AA7-R7</f>
+        <f t="shared" si="17"/>
         <v>19</v>
       </c>
       <c r="AV7" s="3" t="s">
@@ -2787,7 +2787,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>761</v>
       </c>
@@ -2825,44 +2825,44 @@
         <v>7</v>
       </c>
       <c r="M8" s="3">
-        <f>+IF(I8="SFK Freight Forwarder",L8,9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N8" s="3">
         <v>7</v>
       </c>
       <c r="O8" s="3">
-        <f>IF(I8="SFK Freight Forwarder",M8,M8+N8-1)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="P8" s="3">
-        <f>+IF(I8="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q8" s="3">
-        <f>+IF(I8="SFK Freight Forwarder",O8,O8+P8-1)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="R8" s="3">
-        <f>9+N8</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S8" s="3">
         <v>7</v>
       </c>
       <c r="T8" s="3">
-        <f>+R8+S8-1</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="U8" s="3">
-        <f>+T8+1</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="V8" s="3">
         <v>8</v>
       </c>
       <c r="W8" s="3">
-        <f>+U8+V8-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X8" s="3">
@@ -2877,7 +2877,7 @@
         <v>33</v>
       </c>
       <c r="AA8" s="6">
-        <f>+Z8+AB8-1</f>
+        <f t="shared" si="8"/>
         <v>36</v>
       </c>
       <c r="AB8" s="3">
@@ -2893,21 +2893,21 @@
         <v>37</v>
       </c>
       <c r="AF8" s="3">
-        <f>+AE8+AA8-1</f>
+        <f t="shared" si="9"/>
         <v>72</v>
       </c>
       <c r="AG8" s="6">
         <v>3</v>
       </c>
       <c r="AH8" s="6">
-        <f>+AF8+AG8</f>
+        <f t="shared" si="10"/>
         <v>75</v>
       </c>
       <c r="AI8" s="3">
         <v>7</v>
       </c>
       <c r="AJ8" s="3">
-        <f>+AI8+AH8</f>
+        <f t="shared" si="11"/>
         <v>82</v>
       </c>
       <c r="AK8" s="3" t="s">
@@ -2917,36 +2917,36 @@
         <v>3</v>
       </c>
       <c r="AM8" s="3">
-        <f>+AJ8+AL8</f>
+        <f t="shared" si="12"/>
         <v>85</v>
       </c>
       <c r="AN8" s="3">
         <v>4</v>
       </c>
       <c r="AO8" s="3">
-        <f>+AM8+AN8</f>
+        <f t="shared" si="13"/>
         <v>89</v>
       </c>
       <c r="AP8" s="3">
         <v>2</v>
       </c>
       <c r="AQ8" s="3">
-        <f>+AO8+AP8</f>
+        <f t="shared" si="14"/>
         <v>91</v>
       </c>
       <c r="AR8" s="3">
-        <f>+AQ8+7</f>
+        <f t="shared" si="15"/>
         <v>98</v>
       </c>
       <c r="AS8" s="3">
-        <f>+AR8+7+AT8</f>
+        <f t="shared" si="16"/>
         <v>119</v>
       </c>
       <c r="AT8" s="3">
         <v>14</v>
       </c>
       <c r="AU8" s="3">
-        <f>+AA8-R8</f>
+        <f t="shared" si="17"/>
         <v>20</v>
       </c>
       <c r="AV8" s="3" t="s">
@@ -2962,7 +2962,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>888</v>
       </c>
@@ -3000,44 +3000,44 @@
         <v>5</v>
       </c>
       <c r="M9" s="3">
-        <f>+IF(I9="SFK Freight Forwarder",L9,9)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N9" s="3">
         <v>7</v>
       </c>
       <c r="O9" s="3">
-        <f>IF(I9="SFK Freight Forwarder",M9,M9+N9-1)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="P9" s="3">
-        <f>+IF(I9="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <f>+IF(I9="SFK Freight Forwarder",O9,O9+P9-1)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="R9" s="3">
-        <f>9+N9</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S9" s="3">
         <v>7</v>
       </c>
       <c r="T9" s="3">
-        <f>+R9+S9-1</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="U9" s="3">
-        <f>+T9+1</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="V9" s="3">
         <v>8</v>
       </c>
       <c r="W9" s="3">
-        <f>+U9+V9-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X9" s="3">
@@ -3052,7 +3052,7 @@
         <v>36</v>
       </c>
       <c r="AA9" s="6">
-        <f>+Z9+AB9-1</f>
+        <f t="shared" si="8"/>
         <v>38</v>
       </c>
       <c r="AB9" s="3">
@@ -3068,21 +3068,21 @@
         <v>16</v>
       </c>
       <c r="AF9" s="3">
-        <f>+AE9+AA9-1</f>
+        <f t="shared" si="9"/>
         <v>53</v>
       </c>
       <c r="AG9" s="6">
         <v>3</v>
       </c>
       <c r="AH9" s="6">
-        <f>+AF9+AG9</f>
+        <f t="shared" si="10"/>
         <v>56</v>
       </c>
       <c r="AI9" s="3">
         <v>7</v>
       </c>
       <c r="AJ9" s="3">
-        <f>+AI9+AH9</f>
+        <f t="shared" si="11"/>
         <v>63</v>
       </c>
       <c r="AK9" s="3" t="s">
@@ -3092,36 +3092,36 @@
         <v>4</v>
       </c>
       <c r="AM9" s="3">
-        <f>+AJ9+AL9</f>
+        <f t="shared" si="12"/>
         <v>67</v>
       </c>
       <c r="AN9" s="3">
         <v>3</v>
       </c>
       <c r="AO9" s="3">
-        <f>+AM9+AN9</f>
+        <f t="shared" si="13"/>
         <v>70</v>
       </c>
       <c r="AP9" s="3">
         <v>0</v>
       </c>
       <c r="AQ9" s="3">
-        <f>+AO9+AP9</f>
+        <f t="shared" si="14"/>
         <v>70</v>
       </c>
       <c r="AR9" s="3">
-        <f>+AQ9+7</f>
+        <f t="shared" si="15"/>
         <v>77</v>
       </c>
       <c r="AS9" s="3">
-        <f>+AR9+7+AT9</f>
+        <f t="shared" si="16"/>
         <v>84</v>
       </c>
       <c r="AT9" s="3">
         <v>0</v>
       </c>
       <c r="AU9" s="3">
-        <f>+AA9-R9</f>
+        <f t="shared" si="17"/>
         <v>22</v>
       </c>
       <c r="AV9" s="3" t="s">
@@ -3137,7 +3137,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>901</v>
       </c>
@@ -3175,51 +3175,51 @@
         <v>7</v>
       </c>
       <c r="M10" s="3">
-        <f>+IF(I10="SFK Freight Forwarder",L10,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N10" s="3">
         <v>7</v>
       </c>
       <c r="O10" s="3">
-        <f>IF(I10="SFK Freight Forwarder",M10,M10+N10-1)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="P10" s="3">
-        <f>+IF(I10="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q10" s="3">
-        <f>+IF(I10="SFK Freight Forwarder",O10,O10+P10-1)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="R10" s="3">
-        <f>9+N10</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S10" s="3">
         <v>7</v>
       </c>
       <c r="T10" s="3">
-        <f>+R10+S10-1</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="U10" s="3">
-        <f>+T10+1</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="V10" s="3">
         <v>4</v>
       </c>
       <c r="W10" s="3">
-        <f>+U10+V10-1</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="X10" s="3">
         <v>5</v>
       </c>
       <c r="Y10" s="3">
-        <f>+ROUNDDOWN(W10/7,0)*7+X10</f>
+        <f t="shared" ref="Y10:Y53" si="18">+ROUNDDOWN(W10/7,0)*7+X10</f>
         <v>26</v>
       </c>
       <c r="Z10" s="6">
@@ -3227,7 +3227,7 @@
         <v>30</v>
       </c>
       <c r="AA10" s="6">
-        <f>+Z10+AB10-1</f>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="AB10" s="3">
@@ -3243,21 +3243,21 @@
         <v>49</v>
       </c>
       <c r="AF10" s="3">
-        <f>+AE10+AA10-1</f>
+        <f t="shared" si="9"/>
         <v>80</v>
       </c>
       <c r="AG10" s="6">
         <v>3</v>
       </c>
       <c r="AH10" s="6">
-        <f>+AF10+AG10</f>
+        <f t="shared" si="10"/>
         <v>83</v>
       </c>
       <c r="AI10" s="3">
         <v>0</v>
       </c>
       <c r="AJ10" s="3">
-        <f>+AI10+AH10</f>
+        <f t="shared" si="11"/>
         <v>83</v>
       </c>
       <c r="AK10" s="3" t="s">
@@ -3267,36 +3267,36 @@
         <v>1</v>
       </c>
       <c r="AM10" s="3">
-        <f>+AJ10+AL10</f>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="AN10" s="3">
         <v>8</v>
       </c>
       <c r="AO10" s="3">
-        <f>+AM10+AN10</f>
+        <f t="shared" si="13"/>
         <v>92</v>
       </c>
       <c r="AP10" s="3">
         <v>6</v>
       </c>
       <c r="AQ10" s="3">
-        <f>+AO10+AP10</f>
+        <f t="shared" si="14"/>
         <v>98</v>
       </c>
       <c r="AR10" s="3">
-        <f>+AQ10+7</f>
+        <f t="shared" si="15"/>
         <v>105</v>
       </c>
       <c r="AS10" s="3">
-        <f>+AR10+7+AT10</f>
+        <f t="shared" si="16"/>
         <v>119</v>
       </c>
       <c r="AT10" s="3">
         <v>7</v>
       </c>
       <c r="AU10" s="3">
-        <f>+AA10-R10</f>
+        <f t="shared" si="17"/>
         <v>16</v>
       </c>
       <c r="AV10" s="3" t="s">
@@ -3312,7 +3312,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>904</v>
       </c>
@@ -3350,58 +3350,58 @@
         <v>2</v>
       </c>
       <c r="M11" s="3">
-        <f>+IF(I11="SFK Freight Forwarder",L11,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N11" s="3">
         <v>14</v>
       </c>
       <c r="O11" s="3">
-        <f>IF(I11="SFK Freight Forwarder",M11,M11+N11-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P11" s="3">
-        <f>+IF(I11="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q11" s="3">
-        <f>+IF(I11="SFK Freight Forwarder",O11,O11+P11-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R11" s="3">
-        <f>9+N11</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S11" s="3">
         <v>7</v>
       </c>
       <c r="T11" s="3">
-        <f>+R11+S11-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U11" s="3">
-        <f>+T11+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V11" s="3">
         <v>1</v>
       </c>
       <c r="W11" s="3">
-        <f>+U11+V11-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X11" s="3">
         <v>3</v>
       </c>
       <c r="Y11" s="3">
-        <f>+ROUNDDOWN(W11/7,0)*7+X11</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z11" s="6">
         <v>37</v>
       </c>
       <c r="AA11" s="6">
-        <f>+Z11+AB11-1</f>
+        <f t="shared" si="8"/>
         <v>39</v>
       </c>
       <c r="AB11" s="3">
@@ -3417,21 +3417,21 @@
         <v>57</v>
       </c>
       <c r="AF11" s="3">
-        <f>+AE11+AA11-1</f>
+        <f t="shared" si="9"/>
         <v>95</v>
       </c>
       <c r="AG11" s="6">
         <v>3</v>
       </c>
       <c r="AH11" s="6">
-        <f>+AF11+AG11</f>
+        <f t="shared" si="10"/>
         <v>98</v>
       </c>
       <c r="AI11" s="3">
         <v>14</v>
       </c>
       <c r="AJ11" s="3">
-        <f>+AI11+AH11</f>
+        <f t="shared" si="11"/>
         <v>112</v>
       </c>
       <c r="AK11" s="3" t="s">
@@ -3441,36 +3441,36 @@
         <v>4</v>
       </c>
       <c r="AM11" s="3">
-        <f>+AJ11+AL11</f>
+        <f t="shared" si="12"/>
         <v>116</v>
       </c>
       <c r="AN11" s="3">
         <v>3</v>
       </c>
       <c r="AO11" s="3">
-        <f>+AM11+AN11</f>
+        <f t="shared" si="13"/>
         <v>119</v>
       </c>
       <c r="AP11" s="3">
         <v>0</v>
       </c>
       <c r="AQ11" s="3">
-        <f>+AO11+AP11</f>
+        <f t="shared" si="14"/>
         <v>119</v>
       </c>
       <c r="AR11" s="3">
-        <f>+AQ11+7</f>
+        <f t="shared" si="15"/>
         <v>126</v>
       </c>
       <c r="AS11" s="3">
-        <f>+AR11+7+AT11</f>
+        <f t="shared" si="16"/>
         <v>147</v>
       </c>
       <c r="AT11" s="3">
         <v>14</v>
       </c>
       <c r="AU11" s="3">
-        <f>+AA11-R11</f>
+        <f t="shared" si="17"/>
         <v>16</v>
       </c>
       <c r="AV11" s="3" t="s">
@@ -3486,7 +3486,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>906</v>
       </c>
@@ -3524,51 +3524,51 @@
         <v>7</v>
       </c>
       <c r="M12" s="3">
-        <f>+IF(I12="SFK Freight Forwarder",L12,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N12" s="3">
         <v>14</v>
       </c>
       <c r="O12" s="3">
-        <f>IF(I12="SFK Freight Forwarder",M12,M12+N12-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P12" s="3">
-        <f>+IF(I12="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q12" s="3">
-        <f>+IF(I12="SFK Freight Forwarder",O12,O12+P12-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R12" s="3">
-        <f>9+N12</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S12" s="3">
         <v>7</v>
       </c>
       <c r="T12" s="3">
-        <f>+R12+S12-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U12" s="3">
-        <f>+T12+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V12" s="3">
         <v>1</v>
       </c>
       <c r="W12" s="3">
-        <f>+U12+V12-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X12" s="3">
         <v>5</v>
       </c>
       <c r="Y12" s="3">
-        <f>+ROUNDDOWN(W12/7,0)*7+X12</f>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z12" s="6">
@@ -3576,7 +3576,7 @@
         <v>37</v>
       </c>
       <c r="AA12" s="6">
-        <f>+Z12+AB12-1</f>
+        <f t="shared" si="8"/>
         <v>38</v>
       </c>
       <c r="AB12" s="3">
@@ -3592,21 +3592,21 @@
         <v>47</v>
       </c>
       <c r="AF12" s="3">
-        <f>+AE12+AA12-1</f>
+        <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="AG12" s="6">
         <v>3</v>
       </c>
       <c r="AH12" s="6">
-        <f>+AF12+AG12</f>
+        <f t="shared" si="10"/>
         <v>87</v>
       </c>
       <c r="AI12" s="3">
         <v>14</v>
       </c>
       <c r="AJ12" s="3">
-        <f>+AI12+AH12</f>
+        <f t="shared" si="11"/>
         <v>101</v>
       </c>
       <c r="AK12" s="3" t="s">
@@ -3616,36 +3616,36 @@
         <v>2</v>
       </c>
       <c r="AM12" s="3">
-        <f>+AJ12+AL12</f>
+        <f t="shared" si="12"/>
         <v>103</v>
       </c>
       <c r="AN12" s="3">
         <v>2</v>
       </c>
       <c r="AO12" s="3">
-        <f>+AM12+AN12</f>
+        <f t="shared" si="13"/>
         <v>105</v>
       </c>
       <c r="AP12" s="3">
         <v>0</v>
       </c>
       <c r="AQ12" s="3">
-        <f>+AO12+AP12</f>
+        <f t="shared" si="14"/>
         <v>105</v>
       </c>
       <c r="AR12" s="3">
-        <f>+AQ12+7</f>
+        <f t="shared" si="15"/>
         <v>112</v>
       </c>
       <c r="AS12" s="3">
-        <f>+AR12+7+AT12</f>
+        <f t="shared" si="16"/>
         <v>134</v>
       </c>
       <c r="AT12" s="3">
         <v>15</v>
       </c>
       <c r="AU12" s="3">
-        <f>+AA12-R12</f>
+        <f t="shared" si="17"/>
         <v>15</v>
       </c>
       <c r="AV12" s="3" t="s">
@@ -3661,7 +3661,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>907</v>
       </c>
@@ -3699,58 +3699,58 @@
         <v>7</v>
       </c>
       <c r="M13" s="3">
-        <f>+IF(I13="SFK Freight Forwarder",L13,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N13" s="3">
         <v>7</v>
       </c>
       <c r="O13" s="3">
-        <f>IF(I13="SFK Freight Forwarder",M13,M13+N13-1)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="P13" s="3">
-        <f>+IF(I13="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q13" s="3">
-        <f>+IF(I13="SFK Freight Forwarder",O13,O13+P13-1)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="R13" s="3">
-        <f>9+N13</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S13" s="3">
         <v>7</v>
       </c>
       <c r="T13" s="3">
-        <f>+R13+S13-1</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="U13" s="3">
-        <f>+T13+1</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="V13" s="3">
         <v>1</v>
       </c>
       <c r="W13" s="3">
-        <f>+U13+V13-1</f>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="X13" s="3">
         <v>5</v>
       </c>
       <c r="Y13" s="3">
-        <f>+ROUNDDOWN(W13/7,0)*7+X13</f>
+        <f t="shared" si="18"/>
         <v>26</v>
       </c>
       <c r="Z13" s="6">
         <v>31</v>
       </c>
       <c r="AA13" s="6">
-        <f>+Z13+AB13-1</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="AB13" s="3">
@@ -3766,21 +3766,21 @@
         <v>40</v>
       </c>
       <c r="AF13" s="3">
-        <f>+AE13+AA13-1</f>
+        <f t="shared" si="9"/>
         <v>73</v>
       </c>
       <c r="AG13" s="6">
         <v>3</v>
       </c>
       <c r="AH13" s="6">
-        <f>+AF13+AG13</f>
+        <f t="shared" si="10"/>
         <v>76</v>
       </c>
       <c r="AI13" s="3">
         <v>0</v>
       </c>
       <c r="AJ13" s="3">
-        <f>+AI13+AH13</f>
+        <f t="shared" si="11"/>
         <v>76</v>
       </c>
       <c r="AK13" s="3" t="s">
@@ -3790,36 +3790,36 @@
         <v>2</v>
       </c>
       <c r="AM13" s="3">
-        <f>+AJ13+AL13</f>
+        <f t="shared" si="12"/>
         <v>78</v>
       </c>
       <c r="AN13" s="3">
         <v>2</v>
       </c>
       <c r="AO13" s="3">
-        <f>+AM13+AN13</f>
+        <f t="shared" si="13"/>
         <v>80</v>
       </c>
       <c r="AP13" s="3">
         <v>4</v>
       </c>
       <c r="AQ13" s="3">
-        <f>+AO13+AP13</f>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="AR13" s="3">
-        <f>+AQ13+7</f>
+        <f t="shared" si="15"/>
         <v>91</v>
       </c>
       <c r="AS13" s="3">
-        <f>+AR13+7+AT13</f>
+        <f t="shared" si="16"/>
         <v>112</v>
       </c>
       <c r="AT13" s="3">
         <v>14</v>
       </c>
       <c r="AU13" s="3">
-        <f>+AA13-R13</f>
+        <f t="shared" si="17"/>
         <v>18</v>
       </c>
       <c r="AV13" s="3" t="s">
@@ -3835,7 +3835,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>908</v>
       </c>
@@ -3873,58 +3873,58 @@
         <v>7</v>
       </c>
       <c r="M14" s="3">
-        <f>+IF(I14="SFK Freight Forwarder",L14,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N14" s="3">
         <v>14</v>
       </c>
       <c r="O14" s="3">
-        <f>IF(I14="SFK Freight Forwarder",M14,M14+N14-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P14" s="3">
-        <f>+IF(I14="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q14" s="3">
-        <f>+IF(I14="SFK Freight Forwarder",O14,O14+P14-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R14" s="3">
-        <f>9+N14</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S14" s="3">
         <v>7</v>
       </c>
       <c r="T14" s="3">
-        <f>+R14+S14-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U14" s="3">
-        <f>+T14+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V14" s="3">
         <v>4</v>
       </c>
       <c r="W14" s="3">
-        <f>+U14+V14-1</f>
+        <f t="shared" si="7"/>
         <v>33</v>
       </c>
       <c r="X14" s="3">
         <v>5</v>
       </c>
       <c r="Y14" s="3">
-        <f>+ROUNDDOWN(W14/7,0)*7+X14</f>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z14" s="6">
         <v>36</v>
       </c>
       <c r="AA14" s="6">
-        <f>+Z14+AB14-1</f>
+        <f t="shared" si="8"/>
         <v>37</v>
       </c>
       <c r="AB14" s="3">
@@ -3940,21 +3940,21 @@
         <v>37</v>
       </c>
       <c r="AF14" s="3">
-        <f>+AE14+AA14-1</f>
+        <f t="shared" si="9"/>
         <v>73</v>
       </c>
       <c r="AG14" s="6">
         <v>3</v>
       </c>
       <c r="AH14" s="6">
-        <f>+AF14+AG14</f>
+        <f t="shared" si="10"/>
         <v>76</v>
       </c>
       <c r="AI14" s="3">
         <v>7</v>
       </c>
       <c r="AJ14" s="3">
-        <f>+AI14+AH14</f>
+        <f t="shared" si="11"/>
         <v>83</v>
       </c>
       <c r="AK14" s="28" t="s">
@@ -3964,36 +3964,36 @@
         <v>2</v>
       </c>
       <c r="AM14" s="3">
-        <f>+AJ14+AL14</f>
+        <f t="shared" si="12"/>
         <v>85</v>
       </c>
       <c r="AN14" s="3">
         <v>2</v>
       </c>
       <c r="AO14" s="3">
-        <f>+AM14+AN14</f>
+        <f t="shared" si="13"/>
         <v>87</v>
       </c>
       <c r="AP14" s="3">
         <v>4</v>
       </c>
       <c r="AQ14" s="3">
-        <f>+AO14+AP14</f>
+        <f t="shared" si="14"/>
         <v>91</v>
       </c>
       <c r="AR14" s="3">
-        <f>+AQ14+7</f>
+        <f t="shared" si="15"/>
         <v>98</v>
       </c>
       <c r="AS14" s="3">
-        <f>+AR14+7+AT14</f>
+        <f t="shared" si="16"/>
         <v>121</v>
       </c>
       <c r="AT14" s="3">
         <v>16</v>
       </c>
       <c r="AU14" s="3">
-        <f>+AA14-R14</f>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="AV14" s="3" t="s">
@@ -4009,7 +4009,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>910</v>
       </c>
@@ -4047,51 +4047,51 @@
         <v>7</v>
       </c>
       <c r="M15" s="3">
-        <f>+IF(I15="SFK Freight Forwarder",L15,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N15" s="3">
         <v>14</v>
       </c>
       <c r="O15" s="3">
-        <f>IF(I15="SFK Freight Forwarder",M15,M15+N15-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P15" s="3">
-        <f>+IF(I15="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q15" s="3">
-        <f>+IF(I15="SFK Freight Forwarder",O15,O15+P15-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R15" s="3">
-        <f>9+N15</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S15" s="3">
         <v>7</v>
       </c>
       <c r="T15" s="3">
-        <f>+R15+S15-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U15" s="3">
-        <f>+T15+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V15" s="3">
         <v>1</v>
       </c>
       <c r="W15" s="3">
-        <f>+U15+V15-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X15" s="3">
         <v>8</v>
       </c>
       <c r="Y15" s="3">
-        <f>+ROUNDDOWN(W15/7,0)*7+X15</f>
+        <f t="shared" si="18"/>
         <v>36</v>
       </c>
       <c r="Z15" s="6">
@@ -4099,7 +4099,7 @@
         <v>37</v>
       </c>
       <c r="AA15" s="6">
-        <f>+Z15+AB15-1</f>
+        <f t="shared" si="8"/>
         <v>39</v>
       </c>
       <c r="AB15" s="3">
@@ -4115,21 +4115,21 @@
         <v>26</v>
       </c>
       <c r="AF15" s="3">
-        <f>+AE15+AA15-1</f>
+        <f t="shared" si="9"/>
         <v>64</v>
       </c>
       <c r="AG15" s="6">
         <v>3</v>
       </c>
       <c r="AH15" s="6">
-        <f>+AF15+AG15</f>
+        <f t="shared" si="10"/>
         <v>67</v>
       </c>
       <c r="AI15" s="3">
         <v>14</v>
       </c>
       <c r="AJ15" s="3">
-        <f>+AI15+AH15</f>
+        <f t="shared" si="11"/>
         <v>81</v>
       </c>
       <c r="AK15" s="3" t="s">
@@ -4139,36 +4139,36 @@
         <v>2</v>
       </c>
       <c r="AM15" s="3">
-        <f>+AJ15+AL15</f>
+        <f t="shared" si="12"/>
         <v>83</v>
       </c>
       <c r="AN15" s="3">
         <v>2</v>
       </c>
       <c r="AO15" s="3">
-        <f>+AM15+AN15</f>
+        <f t="shared" si="13"/>
         <v>85</v>
       </c>
       <c r="AP15" s="3">
         <v>6</v>
       </c>
       <c r="AQ15" s="3">
-        <f>+AO15+AP15</f>
+        <f t="shared" si="14"/>
         <v>91</v>
       </c>
       <c r="AR15" s="3">
-        <f>+AQ15+7</f>
+        <f t="shared" si="15"/>
         <v>98</v>
       </c>
       <c r="AS15" s="3">
-        <f>+AR15+7+AT15</f>
+        <f t="shared" si="16"/>
         <v>119</v>
       </c>
       <c r="AT15" s="3">
         <v>14</v>
       </c>
       <c r="AU15" s="3">
-        <f>+AA15-R15</f>
+        <f t="shared" si="17"/>
         <v>16</v>
       </c>
       <c r="AV15" s="3" t="s">
@@ -4184,7 +4184,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>912</v>
       </c>
@@ -4222,58 +4222,58 @@
         <v>7</v>
       </c>
       <c r="M16" s="3">
-        <f>+IF(I16="SFK Freight Forwarder",L16,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N16" s="3">
         <v>14</v>
       </c>
       <c r="O16" s="3">
-        <f>IF(I16="SFK Freight Forwarder",M16,M16+N16-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P16" s="3">
-        <f>+IF(I16="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q16" s="3">
-        <f>+IF(I16="SFK Freight Forwarder",O16,O16+P16-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R16" s="3">
-        <f>9+N16</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S16" s="3">
         <v>7</v>
       </c>
       <c r="T16" s="3">
-        <f>+R16+S16-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U16" s="3">
-        <f>+T16+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V16" s="3">
         <v>4</v>
       </c>
       <c r="W16" s="3">
-        <f>+U16+V16-1</f>
+        <f t="shared" si="7"/>
         <v>33</v>
       </c>
       <c r="X16" s="3">
         <v>5</v>
       </c>
       <c r="Y16" s="3">
-        <f>+ROUNDDOWN(W16/7,0)*7+X16</f>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z16" s="6">
         <v>33</v>
       </c>
       <c r="AA16" s="6">
-        <f>+Z16+AB16-1</f>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
       <c r="AB16" s="3">
@@ -4289,21 +4289,21 @@
         <v>44</v>
       </c>
       <c r="AF16" s="3">
-        <f>+AE16+AA16-1</f>
+        <f t="shared" si="9"/>
         <v>78</v>
       </c>
       <c r="AG16" s="6">
         <v>3</v>
       </c>
       <c r="AH16" s="6">
-        <f>+AF16+AG16</f>
+        <f t="shared" si="10"/>
         <v>81</v>
       </c>
       <c r="AI16" s="3">
         <v>7</v>
       </c>
       <c r="AJ16" s="3">
-        <f>+AI16+AH16</f>
+        <f t="shared" si="11"/>
         <v>88</v>
       </c>
       <c r="AK16" s="3" t="s">
@@ -4313,36 +4313,36 @@
         <v>2</v>
       </c>
       <c r="AM16" s="3">
-        <f>+AJ16+AL16</f>
+        <f t="shared" si="12"/>
         <v>90</v>
       </c>
       <c r="AN16" s="3">
         <v>2</v>
       </c>
       <c r="AO16" s="3">
-        <f>+AM16+AN16</f>
+        <f t="shared" si="13"/>
         <v>92</v>
       </c>
       <c r="AP16" s="3">
         <v>6</v>
       </c>
       <c r="AQ16" s="3">
-        <f>+AO16+AP16</f>
+        <f t="shared" si="14"/>
         <v>98</v>
       </c>
       <c r="AR16" s="3">
-        <f>+AQ16+7</f>
+        <f t="shared" si="15"/>
         <v>105</v>
       </c>
       <c r="AS16" s="3">
-        <f>+AR16+7+AT16</f>
+        <f t="shared" si="16"/>
         <v>121</v>
       </c>
       <c r="AT16" s="3">
         <v>9</v>
       </c>
       <c r="AU16" s="3">
-        <f>+AA16-R16</f>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="AV16" s="3" t="s">
@@ -4358,7 +4358,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -4396,51 +4396,51 @@
         <v>7</v>
       </c>
       <c r="M17" s="3">
-        <f>+IF(I17="SFK Freight Forwarder",L17,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N17" s="3">
         <v>14</v>
       </c>
       <c r="O17" s="3">
-        <f>IF(I17="SFK Freight Forwarder",M17,M17+N17-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P17" s="3">
-        <f>+IF(I17="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q17" s="3">
-        <f>+IF(I17="SFK Freight Forwarder",O17,O17+P17-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R17" s="3">
-        <f>9+N17</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S17" s="3">
         <v>7</v>
       </c>
       <c r="T17" s="3">
-        <f>+R17+S17-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U17" s="3">
-        <f>+T17+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V17" s="3">
         <v>2</v>
       </c>
       <c r="W17" s="3">
-        <f>+U17+V17-1</f>
+        <f t="shared" si="7"/>
         <v>31</v>
       </c>
       <c r="X17" s="3">
         <v>4</v>
       </c>
       <c r="Y17" s="3">
-        <f>+ROUNDDOWN(W17/7,0)*7+X17</f>
+        <f t="shared" si="18"/>
         <v>32</v>
       </c>
       <c r="Z17" s="6">
@@ -4463,21 +4463,21 @@
         <v>43</v>
       </c>
       <c r="AF17" s="3">
-        <f>+AE17+AA17-1</f>
+        <f t="shared" si="9"/>
         <v>80</v>
       </c>
       <c r="AG17" s="6">
         <v>3</v>
       </c>
       <c r="AH17" s="6">
-        <f>+AF17+AG17</f>
+        <f t="shared" si="10"/>
         <v>83</v>
       </c>
       <c r="AI17" s="3">
         <v>14</v>
       </c>
       <c r="AJ17" s="3">
-        <f>+AI17+AH17</f>
+        <f t="shared" si="11"/>
         <v>97</v>
       </c>
       <c r="AK17" s="3" t="s">
@@ -4487,36 +4487,36 @@
         <v>1</v>
       </c>
       <c r="AM17" s="3">
-        <f>+AJ17+AL17</f>
+        <f t="shared" si="12"/>
         <v>98</v>
       </c>
       <c r="AN17" s="3">
         <v>8</v>
       </c>
       <c r="AO17" s="3">
-        <f>+AM17+AN17</f>
+        <f t="shared" si="13"/>
         <v>106</v>
       </c>
       <c r="AP17" s="3">
         <v>6</v>
       </c>
       <c r="AQ17" s="3">
-        <f>+AO17+AP17</f>
+        <f t="shared" si="14"/>
         <v>112</v>
       </c>
       <c r="AR17" s="3">
-        <f>+AQ17+7</f>
+        <f t="shared" si="15"/>
         <v>119</v>
       </c>
       <c r="AS17" s="3">
-        <f>+AR17+7+AT17</f>
+        <f t="shared" si="16"/>
         <v>139</v>
       </c>
       <c r="AT17" s="3">
         <v>13</v>
       </c>
       <c r="AU17" s="3">
-        <f>+AA17-R17</f>
+        <f t="shared" si="17"/>
         <v>15</v>
       </c>
       <c r="AV17" s="3" t="s">
@@ -4532,7 +4532,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>916</v>
       </c>
@@ -4570,58 +4570,58 @@
         <v>7</v>
       </c>
       <c r="M18" s="3">
-        <f>+IF(I18="SFK Freight Forwarder",L18,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N18" s="3">
         <v>7</v>
       </c>
       <c r="O18" s="3">
-        <f>IF(I18="SFK Freight Forwarder",M18,M18+N18-1)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="P18" s="3">
-        <f>+IF(I18="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q18" s="3">
-        <f>+IF(I18="SFK Freight Forwarder",O18,O18+P18-1)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="R18" s="3">
-        <f>9+N18</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S18" s="3">
         <v>7</v>
       </c>
       <c r="T18" s="3">
-        <f>+R18+S18-1</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="U18" s="3">
-        <f>+T18+1</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="V18" s="3">
         <v>4</v>
       </c>
       <c r="W18" s="3">
-        <f>+U18+V18-1</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="X18" s="3">
         <v>5</v>
       </c>
       <c r="Y18" s="3">
-        <f>+ROUNDDOWN(W18/7,0)*7+X18</f>
+        <f t="shared" si="18"/>
         <v>26</v>
       </c>
       <c r="Z18" s="6">
         <v>31</v>
       </c>
       <c r="AA18" s="6">
-        <f>+Z18+AB18-1</f>
+        <f t="shared" ref="AA18:AA53" si="19">+Z18+AB18-1</f>
         <v>33</v>
       </c>
       <c r="AB18" s="3">
@@ -4637,21 +4637,21 @@
         <v>27</v>
       </c>
       <c r="AF18" s="3">
-        <f>+AE18+AA18-1</f>
+        <f t="shared" si="9"/>
         <v>59</v>
       </c>
       <c r="AG18" s="6">
         <v>3</v>
       </c>
       <c r="AH18" s="6">
-        <f>+AF18+AG18</f>
+        <f t="shared" si="10"/>
         <v>62</v>
       </c>
       <c r="AI18" s="3">
         <v>7</v>
       </c>
       <c r="AJ18" s="3">
-        <f>+AI18+AH18</f>
+        <f t="shared" si="11"/>
         <v>69</v>
       </c>
       <c r="AK18" s="3" t="s">
@@ -4661,36 +4661,36 @@
         <v>2</v>
       </c>
       <c r="AM18" s="3">
-        <f>+AJ18+AL18</f>
+        <f t="shared" si="12"/>
         <v>71</v>
       </c>
       <c r="AN18" s="3">
         <v>9</v>
       </c>
       <c r="AO18" s="3">
-        <f>+AM18+AN18</f>
+        <f t="shared" si="13"/>
         <v>80</v>
       </c>
       <c r="AP18" s="3">
         <v>4</v>
       </c>
       <c r="AQ18" s="3">
-        <f>+AO18+AP18</f>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="AR18" s="3">
-        <f>+AQ18+7</f>
+        <f t="shared" si="15"/>
         <v>91</v>
       </c>
       <c r="AS18" s="3">
-        <f>+AR18+7+AT18</f>
+        <f t="shared" si="16"/>
         <v>111</v>
       </c>
       <c r="AT18" s="3">
         <v>13</v>
       </c>
       <c r="AU18" s="3">
-        <f>+AA18-R18</f>
+        <f t="shared" si="17"/>
         <v>17</v>
       </c>
       <c r="AV18" s="3" t="s">
@@ -4706,7 +4706,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>917</v>
       </c>
@@ -4744,58 +4744,58 @@
         <v>2</v>
       </c>
       <c r="M19" s="3">
-        <f>+IF(I19="SFK Freight Forwarder",L19,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N19" s="3">
         <v>14</v>
       </c>
       <c r="O19" s="3">
-        <f>IF(I19="SFK Freight Forwarder",M19,M19+N19-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P19" s="3">
-        <f>+IF(I19="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q19" s="3">
-        <f>+IF(I19="SFK Freight Forwarder",O19,O19+P19-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R19" s="3">
-        <f>9+N19</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S19" s="3">
         <v>7</v>
       </c>
       <c r="T19" s="3">
-        <f>+R19+S19-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U19" s="3">
-        <f>+T19+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V19" s="3">
         <v>2</v>
       </c>
       <c r="W19" s="3">
-        <f>+U19+V19-1</f>
+        <f t="shared" si="7"/>
         <v>31</v>
       </c>
       <c r="X19" s="3">
         <v>5</v>
       </c>
       <c r="Y19" s="3">
-        <f>+ROUNDDOWN(W19/7,0)*7+X19</f>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z19" s="6">
         <v>36</v>
       </c>
       <c r="AA19" s="6">
-        <f>+Z19+AB19-1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="AB19" s="3">
@@ -4811,21 +4811,21 @@
         <v>37</v>
       </c>
       <c r="AF19" s="3">
-        <f>+AE19+AA19-1</f>
+        <f t="shared" si="9"/>
         <v>73</v>
       </c>
       <c r="AG19" s="6">
         <v>3</v>
       </c>
       <c r="AH19" s="6">
-        <f>+AF19+AG19</f>
+        <f t="shared" si="10"/>
         <v>76</v>
       </c>
       <c r="AI19" s="3">
         <v>14</v>
       </c>
       <c r="AJ19" s="3">
-        <f>+AI19+AH19</f>
+        <f t="shared" si="11"/>
         <v>90</v>
       </c>
       <c r="AK19" s="3" t="s">
@@ -4835,36 +4835,36 @@
         <v>2</v>
       </c>
       <c r="AM19" s="3">
-        <f>+AJ19+AL19</f>
+        <f t="shared" si="12"/>
         <v>92</v>
       </c>
       <c r="AN19" s="3">
         <v>2</v>
       </c>
       <c r="AO19" s="3">
-        <f>+AM19+AN19</f>
+        <f t="shared" si="13"/>
         <v>94</v>
       </c>
       <c r="AP19" s="3">
         <v>4</v>
       </c>
       <c r="AQ19" s="3">
-        <f>+AO19+AP19</f>
+        <f t="shared" si="14"/>
         <v>98</v>
       </c>
       <c r="AR19" s="3">
-        <f>+AQ19+7</f>
+        <f t="shared" si="15"/>
         <v>105</v>
       </c>
       <c r="AS19" s="3">
-        <f>+AR19+7+AT19</f>
+        <f t="shared" si="16"/>
         <v>126</v>
       </c>
       <c r="AT19" s="3">
         <v>14</v>
       </c>
       <c r="AU19" s="3">
-        <f>+AA19-R19</f>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="AV19" s="3" t="s">
@@ -4880,7 +4880,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>918</v>
       </c>
@@ -4918,58 +4918,58 @@
         <v>7</v>
       </c>
       <c r="M20" s="3">
-        <f>+IF(I20="SFK Freight Forwarder",L20,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N20" s="3">
         <v>14</v>
       </c>
       <c r="O20" s="3">
-        <f>IF(I20="SFK Freight Forwarder",M20,M20+N20-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P20" s="3">
-        <f>+IF(I20="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q20" s="3">
-        <f>+IF(I20="SFK Freight Forwarder",O20,O20+P20-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R20" s="3">
-        <f>9+N20</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S20" s="3">
         <v>7</v>
       </c>
       <c r="T20" s="3">
-        <f>+R20+S20-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U20" s="3">
-        <f>+T20+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V20" s="3">
         <v>2</v>
       </c>
       <c r="W20" s="3">
-        <f>+U20+V20-1</f>
+        <f t="shared" si="7"/>
         <v>31</v>
       </c>
       <c r="X20" s="3">
         <v>3</v>
       </c>
       <c r="Y20" s="3">
-        <f>+ROUNDDOWN(W20/7,0)*7+X20</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z20" s="6">
         <v>35</v>
       </c>
       <c r="AA20" s="6">
-        <f>+Z20+AB20-1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="AB20" s="3">
@@ -4985,21 +4985,21 @@
         <v>36</v>
       </c>
       <c r="AF20" s="3">
-        <f>+AE20+AA20-1</f>
+        <f t="shared" si="9"/>
         <v>72</v>
       </c>
       <c r="AG20" s="6">
         <v>3</v>
       </c>
       <c r="AH20" s="6">
-        <f>+AF20+AG20</f>
+        <f t="shared" si="10"/>
         <v>75</v>
       </c>
       <c r="AI20" s="3">
         <v>14</v>
       </c>
       <c r="AJ20" s="3">
-        <f>+AI20+AH20</f>
+        <f t="shared" si="11"/>
         <v>89</v>
       </c>
       <c r="AK20" s="3" t="s">
@@ -5009,36 +5009,36 @@
         <v>2</v>
       </c>
       <c r="AM20" s="3">
-        <f>+AJ20+AL20</f>
+        <f t="shared" si="12"/>
         <v>91</v>
       </c>
       <c r="AN20" s="3">
         <v>7</v>
       </c>
       <c r="AO20" s="3">
-        <f>+AM20+AN20</f>
+        <f t="shared" si="13"/>
         <v>98</v>
       </c>
       <c r="AP20" s="3">
         <v>0</v>
       </c>
       <c r="AQ20" s="3">
-        <f>+AO20+AP20</f>
+        <f t="shared" si="14"/>
         <v>98</v>
       </c>
       <c r="AR20" s="3">
-        <f>+AQ20+7</f>
+        <f t="shared" si="15"/>
         <v>105</v>
       </c>
       <c r="AS20" s="3">
-        <f>+AR20+7+AT20</f>
+        <f t="shared" si="16"/>
         <v>126</v>
       </c>
       <c r="AT20" s="3">
         <v>14</v>
       </c>
       <c r="AU20" s="3">
-        <f>+AA20-R20</f>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="AV20" s="3" t="s">
@@ -5054,7 +5054,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>920</v>
       </c>
@@ -5092,51 +5092,51 @@
         <v>7</v>
       </c>
       <c r="M21" s="3">
-        <f>+IF(I21="SFK Freight Forwarder",L21,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N21" s="3">
         <v>14</v>
       </c>
       <c r="O21" s="3">
-        <f>IF(I21="SFK Freight Forwarder",M21,M21+N21-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P21" s="3">
-        <f>+IF(I21="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q21" s="3">
-        <f>+IF(I21="SFK Freight Forwarder",O21,O21+P21-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R21" s="3">
-        <f>9+N21</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S21" s="3">
         <v>7</v>
       </c>
       <c r="T21" s="3">
-        <f>+R21+S21-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U21" s="3">
-        <f>+T21+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V21" s="3">
         <v>3</v>
       </c>
       <c r="W21" s="3">
-        <f>+U21+V21-1</f>
+        <f t="shared" si="7"/>
         <v>32</v>
       </c>
       <c r="X21" s="3">
         <v>5</v>
       </c>
       <c r="Y21" s="3">
-        <f>+ROUNDDOWN(W21/7,0)*7+X21</f>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z21" s="6">
@@ -5144,7 +5144,7 @@
         <v>37</v>
       </c>
       <c r="AA21" s="6">
-        <f>+Z21+AB21-1</f>
+        <f t="shared" si="19"/>
         <v>39</v>
       </c>
       <c r="AB21" s="3">
@@ -5160,21 +5160,21 @@
         <v>39</v>
       </c>
       <c r="AF21" s="3">
-        <f>+AE21+AA21-1</f>
+        <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="AG21" s="6">
         <v>3</v>
       </c>
       <c r="AH21" s="6">
-        <f>+AF21+AG21</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="AI21" s="3">
         <v>0</v>
       </c>
       <c r="AJ21" s="3">
-        <f>+AI21+AH21</f>
+        <f t="shared" si="11"/>
         <v>80</v>
       </c>
       <c r="AK21" s="3" t="s">
@@ -5184,36 +5184,36 @@
         <v>3</v>
       </c>
       <c r="AM21" s="3">
-        <f>+AJ21+AL21</f>
+        <f t="shared" si="12"/>
         <v>83</v>
       </c>
       <c r="AN21" s="3">
         <v>9</v>
       </c>
       <c r="AO21" s="3">
-        <f>+AM21+AN21</f>
+        <f t="shared" si="13"/>
         <v>92</v>
       </c>
       <c r="AP21" s="3">
         <v>6</v>
       </c>
       <c r="AQ21" s="3">
-        <f>+AO21+AP21</f>
+        <f t="shared" si="14"/>
         <v>98</v>
       </c>
       <c r="AR21" s="3">
-        <f>+AQ21+7</f>
+        <f t="shared" si="15"/>
         <v>105</v>
       </c>
       <c r="AS21" s="3">
-        <f>+AR21+7+AT21</f>
+        <f t="shared" si="16"/>
         <v>126</v>
       </c>
       <c r="AT21" s="3">
         <v>14</v>
       </c>
       <c r="AU21" s="3">
-        <f>+AA21-R21</f>
+        <f t="shared" si="17"/>
         <v>16</v>
       </c>
       <c r="AV21" s="3" t="s">
@@ -5229,7 +5229,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5267,51 +5267,51 @@
         <v>2</v>
       </c>
       <c r="M22" s="3">
-        <f>+IF(I22="SFK Freight Forwarder",L22,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N22" s="3">
         <v>14</v>
       </c>
       <c r="O22" s="3">
-        <f>IF(I22="SFK Freight Forwarder",M22,M22+N22-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P22" s="3">
-        <f>+IF(I22="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q22" s="3">
-        <f>+IF(I22="SFK Freight Forwarder",O22,O22+P22-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R22" s="3">
-        <f>9+N22</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S22" s="3">
         <v>7</v>
       </c>
       <c r="T22" s="3">
-        <f>+R22+S22-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U22" s="3">
-        <f>+T22+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V22" s="3">
         <v>3</v>
       </c>
       <c r="W22" s="3">
-        <f>+U22+V22-1</f>
+        <f t="shared" si="7"/>
         <v>32</v>
       </c>
       <c r="X22" s="3">
         <v>5</v>
       </c>
       <c r="Y22" s="3">
-        <f>+ROUNDDOWN(W22/7,0)*7+X22</f>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z22" s="6">
@@ -5319,7 +5319,7 @@
         <v>37</v>
       </c>
       <c r="AA22" s="6">
-        <f>+Z22+AB22-1</f>
+        <f t="shared" si="19"/>
         <v>39</v>
       </c>
       <c r="AB22" s="3">
@@ -5335,21 +5335,21 @@
         <v>46</v>
       </c>
       <c r="AF22" s="3">
-        <f>+AE22+AA22-1</f>
+        <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="AG22" s="6">
         <v>3</v>
       </c>
       <c r="AH22" s="6">
-        <f>+AF22+AG22</f>
+        <f t="shared" si="10"/>
         <v>87</v>
       </c>
       <c r="AI22" s="3">
         <v>7</v>
       </c>
       <c r="AJ22" s="3">
-        <f>+AI22+AH22</f>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="AK22" s="3" t="s">
@@ -5359,36 +5359,36 @@
         <v>2</v>
       </c>
       <c r="AM22" s="3">
-        <f>+AJ22+AL22</f>
+        <f t="shared" si="12"/>
         <v>96</v>
       </c>
       <c r="AN22" s="3">
         <v>2</v>
       </c>
       <c r="AO22" s="3">
-        <f>+AM22+AN22</f>
+        <f t="shared" si="13"/>
         <v>98</v>
       </c>
       <c r="AP22" s="3">
         <v>0</v>
       </c>
       <c r="AQ22" s="3">
-        <f>+AO22+AP22</f>
+        <f t="shared" si="14"/>
         <v>98</v>
       </c>
       <c r="AR22" s="3">
-        <f>+AQ22+7</f>
+        <f t="shared" si="15"/>
         <v>105</v>
       </c>
       <c r="AS22" s="3">
-        <f>+AR22+7+AT22</f>
+        <f t="shared" si="16"/>
         <v>126</v>
       </c>
       <c r="AT22" s="3">
         <v>14</v>
       </c>
       <c r="AU22" s="3">
-        <f>+AA22-R22</f>
+        <f t="shared" si="17"/>
         <v>16</v>
       </c>
       <c r="AV22" s="3" t="s">
@@ -5404,7 +5404,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>924</v>
       </c>
@@ -5442,58 +5442,58 @@
         <v>7</v>
       </c>
       <c r="M23" s="3">
-        <f>+IF(I23="SFK Freight Forwarder",L23,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N23" s="3">
         <v>7</v>
       </c>
       <c r="O23" s="3">
-        <f>IF(I23="SFK Freight Forwarder",M23,M23+N23-1)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="P23" s="3">
-        <f>+IF(I23="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q23" s="3">
-        <f>+IF(I23="SFK Freight Forwarder",O23,O23+P23-1)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="R23" s="3">
-        <f>9+N23</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S23" s="3">
         <v>7</v>
       </c>
       <c r="T23" s="3">
-        <f>+R23+S23-1</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="U23" s="3">
-        <f>+T23+1</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="V23" s="3">
         <v>3</v>
       </c>
       <c r="W23" s="3">
-        <f>+U23+V23-1</f>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="X23" s="3">
         <v>4</v>
       </c>
       <c r="Y23" s="3">
-        <f>+ROUNDDOWN(W23/7,0)*7+X23</f>
+        <f t="shared" si="18"/>
         <v>25</v>
       </c>
       <c r="Z23" s="6">
         <v>30</v>
       </c>
       <c r="AA23" s="6">
-        <f>+Z23+AB23-1</f>
+        <f t="shared" si="19"/>
         <v>32</v>
       </c>
       <c r="AB23" s="3">
@@ -5509,21 +5509,21 @@
         <v>21</v>
       </c>
       <c r="AF23" s="3">
-        <f>+AE23+AA23-1</f>
+        <f t="shared" si="9"/>
         <v>52</v>
       </c>
       <c r="AG23" s="6">
         <v>3</v>
       </c>
       <c r="AH23" s="6">
-        <f>+AF23+AG23</f>
+        <f t="shared" si="10"/>
         <v>55</v>
       </c>
       <c r="AI23" s="3">
         <v>0</v>
       </c>
       <c r="AJ23" s="3">
-        <f>+AI23+AH23</f>
+        <f t="shared" si="11"/>
         <v>55</v>
       </c>
       <c r="AK23" s="3" t="s">
@@ -5533,36 +5533,36 @@
         <v>1</v>
       </c>
       <c r="AM23" s="3">
-        <f>+AJ23+AL23</f>
+        <f t="shared" si="12"/>
         <v>56</v>
       </c>
       <c r="AN23" s="3">
         <v>8</v>
       </c>
       <c r="AO23" s="3">
-        <f>+AM23+AN23</f>
+        <f t="shared" si="13"/>
         <v>64</v>
       </c>
       <c r="AP23" s="3">
         <v>6</v>
       </c>
       <c r="AQ23" s="3">
-        <f>+AO23+AP23</f>
+        <f t="shared" si="14"/>
         <v>70</v>
       </c>
       <c r="AR23" s="3">
-        <f>+AQ23+7</f>
+        <f t="shared" si="15"/>
         <v>77</v>
       </c>
       <c r="AS23" s="3">
-        <f>+AR23+7+AT23</f>
+        <f t="shared" si="16"/>
         <v>84</v>
       </c>
       <c r="AT23" s="3">
         <v>0</v>
       </c>
       <c r="AU23" s="3">
-        <f>+AA23-R23</f>
+        <f t="shared" si="17"/>
         <v>16</v>
       </c>
       <c r="AV23" s="3" t="s">
@@ -5578,7 +5578,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>925</v>
       </c>
@@ -5616,58 +5616,58 @@
         <v>7</v>
       </c>
       <c r="M24" s="3">
-        <f>+IF(I24="SFK Freight Forwarder",L24,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N24" s="3">
         <v>14</v>
       </c>
       <c r="O24" s="3">
-        <f>IF(I24="SFK Freight Forwarder",M24,M24+N24-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P24" s="3">
-        <f>+IF(I24="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q24" s="3">
-        <f>+IF(I24="SFK Freight Forwarder",O24,O24+P24-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R24" s="3">
-        <f>9+N24</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S24" s="3">
         <v>7</v>
       </c>
       <c r="T24" s="3">
-        <f>+R24+S24-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U24" s="3">
-        <f>+T24+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V24" s="3">
         <v>2</v>
       </c>
       <c r="W24" s="3">
-        <f>+U24+V24-1</f>
+        <f t="shared" si="7"/>
         <v>31</v>
       </c>
       <c r="X24" s="3">
         <v>4</v>
       </c>
       <c r="Y24" s="3">
-        <f>+ROUNDDOWN(W24/7,0)*7+X24</f>
+        <f t="shared" si="18"/>
         <v>32</v>
       </c>
       <c r="Z24" s="6">
         <v>33</v>
       </c>
       <c r="AA24" s="6">
-        <f>+Z24+AB24-1</f>
+        <f t="shared" si="19"/>
         <v>35</v>
       </c>
       <c r="AB24" s="3">
@@ -5683,21 +5683,21 @@
         <v>40</v>
       </c>
       <c r="AF24" s="3">
-        <f>+AE24+AA24-1</f>
+        <f t="shared" si="9"/>
         <v>74</v>
       </c>
       <c r="AG24" s="6">
         <v>3</v>
       </c>
       <c r="AH24" s="6">
-        <f>+AF24+AG24</f>
+        <f t="shared" si="10"/>
         <v>77</v>
       </c>
       <c r="AI24" s="3">
         <v>14</v>
       </c>
       <c r="AJ24" s="3">
-        <f>+AI24+AH24</f>
+        <f t="shared" si="11"/>
         <v>91</v>
       </c>
       <c r="AK24" s="3" t="s">
@@ -5707,36 +5707,36 @@
         <v>2</v>
       </c>
       <c r="AM24" s="3">
-        <f>+AJ24+AL24</f>
+        <f t="shared" si="12"/>
         <v>93</v>
       </c>
       <c r="AN24" s="3">
         <v>2</v>
       </c>
       <c r="AO24" s="3">
-        <f>+AM24+AN24</f>
+        <f t="shared" si="13"/>
         <v>95</v>
       </c>
       <c r="AP24" s="3">
         <v>3</v>
       </c>
       <c r="AQ24" s="3">
-        <f>+AO24+AP24</f>
+        <f t="shared" si="14"/>
         <v>98</v>
       </c>
       <c r="AR24" s="3">
-        <f>+AQ24+7</f>
+        <f t="shared" si="15"/>
         <v>105</v>
       </c>
       <c r="AS24" s="3">
-        <f>+AR24+7+AT24</f>
+        <f t="shared" si="16"/>
         <v>126</v>
       </c>
       <c r="AT24" s="3">
         <v>14</v>
       </c>
       <c r="AU24" s="3">
-        <f>+AA24-R24</f>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="AV24" s="3" t="s">
@@ -5752,7 +5752,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -5790,58 +5790,58 @@
         <v>2</v>
       </c>
       <c r="M25" s="3">
-        <f>+IF(I25="SFK Freight Forwarder",L25,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N25" s="3">
         <v>14</v>
       </c>
       <c r="O25" s="3">
-        <f>IF(I25="SFK Freight Forwarder",M25,M25+N25-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P25" s="3">
-        <f>+IF(I25="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q25" s="3">
-        <f>+IF(I25="SFK Freight Forwarder",O25,O25+P25-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R25" s="3">
-        <f>9+N25</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S25" s="3">
         <v>7</v>
       </c>
       <c r="T25" s="3">
-        <f>+R25+S25-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U25" s="3">
-        <f>+T25+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V25" s="3">
         <v>1</v>
       </c>
       <c r="W25" s="3">
-        <f>+U25+V25-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X25" s="3">
         <v>2</v>
       </c>
       <c r="Y25" s="3">
-        <f>+ROUNDDOWN(W25/7,0)*7+X25</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="Z25" s="6">
         <v>30</v>
       </c>
       <c r="AA25" s="6">
-        <f>+Z25+AB25-1</f>
+        <f t="shared" si="19"/>
         <v>32</v>
       </c>
       <c r="AB25" s="3">
@@ -5857,21 +5857,21 @@
         <v>46</v>
       </c>
       <c r="AF25" s="3">
-        <f>+AE25+AA25-1</f>
+        <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="AG25" s="6">
         <v>3</v>
       </c>
       <c r="AH25" s="6">
-        <f>+AF25+AG25</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="AI25" s="3">
         <v>14</v>
       </c>
       <c r="AJ25" s="3">
-        <f>+AI25+AH25</f>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="AK25" s="3" t="s">
@@ -5881,36 +5881,36 @@
         <v>4</v>
       </c>
       <c r="AM25" s="3">
-        <f>+AJ25+AL25</f>
+        <f t="shared" si="12"/>
         <v>98</v>
       </c>
       <c r="AN25" s="3">
         <v>3</v>
       </c>
       <c r="AO25" s="3">
-        <f>+AM25+AN25</f>
+        <f t="shared" si="13"/>
         <v>101</v>
       </c>
       <c r="AP25" s="3">
         <v>4</v>
       </c>
       <c r="AQ25" s="3">
-        <f>+AO25+AP25</f>
+        <f t="shared" si="14"/>
         <v>105</v>
       </c>
       <c r="AR25" s="3">
-        <f>+AQ25+7</f>
+        <f t="shared" si="15"/>
         <v>112</v>
       </c>
       <c r="AS25" s="3">
-        <f>+AR25+7+AT25</f>
+        <f t="shared" si="16"/>
         <v>133</v>
       </c>
       <c r="AT25" s="3">
         <v>14</v>
       </c>
       <c r="AU25" s="3">
-        <f>+AA25-R25</f>
+        <f t="shared" si="17"/>
         <v>9</v>
       </c>
       <c r="AV25" s="3" t="s">
@@ -5926,7 +5926,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>928</v>
       </c>
@@ -5964,58 +5964,58 @@
         <v>7</v>
       </c>
       <c r="M26" s="3">
-        <f>+IF(I26="SFK Freight Forwarder",L26,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N26" s="3">
         <v>7</v>
       </c>
       <c r="O26" s="3">
-        <f>IF(I26="SFK Freight Forwarder",M26,M26+N26-1)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="P26" s="3">
-        <f>+IF(I26="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Q26" s="3">
-        <f>+IF(I26="SFK Freight Forwarder",O26,O26+P26-1)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="R26" s="3">
-        <f>9+N26</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S26" s="3">
         <v>7</v>
       </c>
       <c r="T26" s="3">
-        <f>+R26+S26-1</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="U26" s="3">
-        <f>+T26+1</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="V26" s="3">
         <v>2</v>
       </c>
       <c r="W26" s="3">
-        <f>+U26+V26-1</f>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="X26" s="3">
         <v>5</v>
       </c>
       <c r="Y26" s="3">
-        <f>+ROUNDDOWN(W26/7,0)*7+X26</f>
+        <f t="shared" si="18"/>
         <v>26</v>
       </c>
       <c r="Z26" s="6">
         <v>31</v>
       </c>
       <c r="AA26" s="6">
-        <f>+Z26+AB26-1</f>
+        <f t="shared" si="19"/>
         <v>33</v>
       </c>
       <c r="AB26" s="3">
@@ -6031,21 +6031,21 @@
         <v>21</v>
       </c>
       <c r="AF26" s="3">
-        <f>+AE26+AA26-1</f>
+        <f t="shared" si="9"/>
         <v>53</v>
       </c>
       <c r="AG26" s="6">
         <v>3</v>
       </c>
       <c r="AH26" s="6">
-        <f>+AF26+AG26</f>
+        <f t="shared" si="10"/>
         <v>56</v>
       </c>
       <c r="AI26" s="3">
         <v>7</v>
       </c>
       <c r="AJ26" s="3">
-        <f>+AI26+AH26</f>
+        <f t="shared" si="11"/>
         <v>63</v>
       </c>
       <c r="AK26" s="3" t="s">
@@ -6055,36 +6055,36 @@
         <v>2</v>
       </c>
       <c r="AM26" s="3">
-        <f>+AJ26+AL26</f>
+        <f t="shared" si="12"/>
         <v>65</v>
       </c>
       <c r="AN26" s="3">
         <v>2</v>
       </c>
       <c r="AO26" s="3">
-        <f>+AM26+AN26</f>
+        <f t="shared" si="13"/>
         <v>67</v>
       </c>
       <c r="AP26" s="3">
         <v>3</v>
       </c>
       <c r="AQ26" s="3">
-        <f>+AO26+AP26</f>
+        <f t="shared" si="14"/>
         <v>70</v>
       </c>
       <c r="AR26" s="3">
-        <f>+AQ26+7</f>
+        <f t="shared" si="15"/>
         <v>77</v>
       </c>
       <c r="AS26" s="3">
-        <f>+AR26+7+AT26</f>
+        <f t="shared" si="16"/>
         <v>98</v>
       </c>
       <c r="AT26" s="3">
         <v>14</v>
       </c>
       <c r="AU26" s="3">
-        <f>+AA26-R26</f>
+        <f t="shared" si="17"/>
         <v>17</v>
       </c>
       <c r="AV26" s="3" t="s">
@@ -6100,7 +6100,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>930</v>
       </c>
@@ -6138,57 +6138,57 @@
         <v>2</v>
       </c>
       <c r="M27" s="3">
-        <f>+IF(I27="SFK Freight Forwarder",L27,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N27" s="3">
         <v>14</v>
       </c>
       <c r="O27" s="3">
-        <f>IF(I27="SFK Freight Forwarder",M27,M27+N27-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P27" s="3">
         <v>5</v>
       </c>
       <c r="Q27" s="3">
-        <f>+IF(I27="SFK Freight Forwarder",O27,O27+P27-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R27" s="3">
-        <f>9+N27</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S27" s="3">
         <v>7</v>
       </c>
       <c r="T27" s="3">
-        <f>+R27+S27-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U27" s="3">
-        <f>+T27+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V27" s="3">
         <v>1</v>
       </c>
       <c r="W27" s="3">
-        <f>+U27+V27-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X27" s="3">
         <v>2</v>
       </c>
       <c r="Y27" s="3">
-        <f>+ROUNDDOWN(W27/7,0)*7+X27</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="Z27" s="6">
         <v>35</v>
       </c>
       <c r="AA27" s="6">
-        <f>+Z27+AB27-1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="AB27" s="3">
@@ -6204,21 +6204,21 @@
         <v>40</v>
       </c>
       <c r="AF27" s="3">
-        <f>+AE27+AA27-1</f>
+        <f t="shared" si="9"/>
         <v>76</v>
       </c>
       <c r="AG27" s="6">
         <v>3</v>
       </c>
       <c r="AH27" s="6">
-        <f>+AF27+AG27</f>
+        <f t="shared" si="10"/>
         <v>79</v>
       </c>
       <c r="AI27" s="3">
         <v>7</v>
       </c>
       <c r="AJ27" s="3">
-        <f>+AI27+AH27</f>
+        <f t="shared" si="11"/>
         <v>86</v>
       </c>
       <c r="AK27" s="3" t="s">
@@ -6228,36 +6228,36 @@
         <v>3</v>
       </c>
       <c r="AM27" s="3">
-        <f>+AJ27+AL27</f>
+        <f t="shared" si="12"/>
         <v>89</v>
       </c>
       <c r="AN27" s="3">
         <v>11</v>
       </c>
       <c r="AO27" s="3">
-        <f>+AM27+AN27</f>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="AP27" s="3">
         <v>5</v>
       </c>
       <c r="AQ27" s="3">
-        <f>+AO27+AP27</f>
+        <f t="shared" si="14"/>
         <v>105</v>
       </c>
       <c r="AR27" s="3">
-        <f>+AQ27+7</f>
+        <f t="shared" si="15"/>
         <v>112</v>
       </c>
       <c r="AS27" s="3">
-        <f>+AR27+7+AT27</f>
+        <f t="shared" si="16"/>
         <v>136</v>
       </c>
       <c r="AT27" s="3">
         <v>17</v>
       </c>
       <c r="AU27" s="3">
-        <f>+AA27-R27</f>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="AV27" s="3" t="s">
@@ -6273,7 +6273,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>931</v>
       </c>
@@ -6311,58 +6311,58 @@
         <v>7</v>
       </c>
       <c r="M28" s="3">
-        <f>+IF(I28="SFK Freight Forwarder",L28,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N28" s="3">
         <v>14</v>
       </c>
       <c r="O28" s="3">
-        <f>IF(I28="SFK Freight Forwarder",M28,M28+N28-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P28" s="3">
-        <f>+IF(I28="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P28:P45" si="20">+IF(I28="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q28" s="3">
-        <f>+IF(I28="SFK Freight Forwarder",O28,O28+P28-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R28" s="3">
-        <f>9+N28</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S28" s="3">
         <v>7</v>
       </c>
       <c r="T28" s="3">
-        <f>+R28+S28-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U28" s="3">
-        <f>+T28+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V28" s="3">
         <v>1</v>
       </c>
       <c r="W28" s="3">
-        <f>+U28+V28-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X28" s="3">
         <v>2</v>
       </c>
       <c r="Y28" s="3">
-        <f>+ROUNDDOWN(W28/7,0)*7+X28</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="Z28" s="6">
         <v>33</v>
       </c>
       <c r="AA28" s="6">
-        <f>+Z28+AB28-1</f>
+        <f t="shared" si="19"/>
         <v>35</v>
       </c>
       <c r="AB28" s="3">
@@ -6378,21 +6378,21 @@
         <v>43</v>
       </c>
       <c r="AF28" s="3">
-        <f>+AE28+AA28-1</f>
+        <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="AG28" s="6">
         <v>3</v>
       </c>
       <c r="AH28" s="6">
-        <f>+AF28+AG28</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="AI28" s="3">
         <v>7</v>
       </c>
       <c r="AJ28" s="3">
-        <f>+AI28+AH28</f>
+        <f t="shared" si="11"/>
         <v>87</v>
       </c>
       <c r="AK28" s="3" t="s">
@@ -6402,36 +6402,36 @@
         <v>2</v>
       </c>
       <c r="AM28" s="3">
-        <f>+AJ28+AL28</f>
+        <f t="shared" si="12"/>
         <v>89</v>
       </c>
       <c r="AN28" s="3">
         <v>2</v>
       </c>
       <c r="AO28" s="3">
-        <f>+AM28+AN28</f>
+        <f t="shared" si="13"/>
         <v>91</v>
       </c>
       <c r="AP28" s="3">
         <v>0</v>
       </c>
       <c r="AQ28" s="3">
-        <f>+AO28+AP28</f>
+        <f t="shared" si="14"/>
         <v>91</v>
       </c>
       <c r="AR28" s="3">
-        <f>+AQ28+7</f>
+        <f t="shared" si="15"/>
         <v>98</v>
       </c>
       <c r="AS28" s="3">
-        <f>+AR28+7+AT28</f>
+        <f t="shared" si="16"/>
         <v>122</v>
       </c>
       <c r="AT28" s="3">
         <v>17</v>
       </c>
       <c r="AU28" s="3">
-        <f>+AA28-R28</f>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="AV28" s="3" t="s">
@@ -6447,7 +6447,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>932</v>
       </c>
@@ -6485,58 +6485,58 @@
         <v>7</v>
       </c>
       <c r="M29" s="3">
-        <f>+IF(I29="SFK Freight Forwarder",L29,9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N29" s="3">
         <v>14</v>
       </c>
       <c r="O29" s="3">
-        <f>IF(I29="SFK Freight Forwarder",M29,M29+N29-1)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="P29" s="3">
-        <f>+IF(I29="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="Q29" s="3">
-        <f>+IF(I29="SFK Freight Forwarder",O29,O29+P29-1)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="R29" s="3">
-        <f>9+N29</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S29" s="3">
         <v>7</v>
       </c>
       <c r="T29" s="3">
-        <f>+R29+S29-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U29" s="3">
-        <f>+T29+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V29" s="3">
         <v>1</v>
       </c>
       <c r="W29" s="3">
-        <f>+U29+V29-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X29" s="3">
         <v>2</v>
       </c>
       <c r="Y29" s="3">
-        <f>+ROUNDDOWN(W29/7,0)*7+X29</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="Z29" s="6">
         <v>35</v>
       </c>
       <c r="AA29" s="6">
-        <f>+Z29+AB29-1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="AB29" s="3">
@@ -6552,21 +6552,21 @@
         <v>58</v>
       </c>
       <c r="AF29" s="3">
-        <f>+AE29+AA29-1</f>
+        <f t="shared" si="9"/>
         <v>94</v>
       </c>
       <c r="AG29" s="6">
         <v>3</v>
       </c>
       <c r="AH29" s="6">
-        <f>+AF29+AG29</f>
+        <f t="shared" si="10"/>
         <v>97</v>
       </c>
       <c r="AI29" s="3">
         <v>7</v>
       </c>
       <c r="AJ29" s="3">
-        <f>+AI29+AH29</f>
+        <f t="shared" si="11"/>
         <v>104</v>
       </c>
       <c r="AK29" s="3" t="s">
@@ -6576,36 +6576,36 @@
         <v>1</v>
       </c>
       <c r="AM29" s="3">
-        <f>+AJ29+AL29</f>
+        <f t="shared" si="12"/>
         <v>105</v>
       </c>
       <c r="AN29" s="3">
         <v>8</v>
       </c>
       <c r="AO29" s="3">
-        <f>+AM29+AN29</f>
+        <f t="shared" si="13"/>
         <v>113</v>
       </c>
       <c r="AP29" s="3">
         <v>6</v>
       </c>
       <c r="AQ29" s="3">
-        <f>+AO29+AP29</f>
+        <f t="shared" si="14"/>
         <v>119</v>
       </c>
       <c r="AR29" s="3">
-        <f>+AQ29+7</f>
+        <f t="shared" si="15"/>
         <v>126</v>
       </c>
       <c r="AS29" s="3">
-        <f>+AR29+7+AT29</f>
+        <f t="shared" si="16"/>
         <v>147</v>
       </c>
       <c r="AT29" s="3">
         <v>14</v>
       </c>
       <c r="AU29" s="3">
-        <f>+AA29-R29</f>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="AV29" s="3" t="s">
@@ -6621,7 +6621,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>1005</v>
       </c>
@@ -6659,59 +6659,59 @@
         <v>7</v>
       </c>
       <c r="M30" s="3">
-        <f>+IF(I30="SFK Freight Forwarder",L30,9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N30" s="3">
         <v>14</v>
       </c>
       <c r="O30" s="3">
-        <f>IF(I30="SFK Freight Forwarder",M30,M30+N30-1)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="P30" s="3">
-        <f>+IF(I30="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q30" s="3">
-        <f>+IF(I30="SFK Freight Forwarder",O30,O30+P30-1)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="R30" s="3">
-        <f>9+N30</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S30" s="3">
         <v>7</v>
       </c>
       <c r="T30" s="3">
-        <f>+R30+S30-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U30" s="3">
-        <f>+T30+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V30" s="3">
         <v>1</v>
       </c>
       <c r="W30" s="3">
-        <f>+U30+V30-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X30" s="3">
         <v>3</v>
       </c>
       <c r="Y30" s="3">
-        <f>+ROUNDDOWN(W30/7,0)*7+X30</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z30" s="6">
-        <f>+Y30+X30-1</f>
+        <f t="shared" ref="Z30:Z41" si="21">+Y30+X30-1</f>
         <v>33</v>
       </c>
       <c r="AA30" s="6">
-        <f>+Z30+AB30-1</f>
+        <f t="shared" si="19"/>
         <v>34</v>
       </c>
       <c r="AB30" s="3">
@@ -6727,21 +6727,21 @@
         <v>35</v>
       </c>
       <c r="AF30" s="3">
-        <f>+AE30+AA30-1</f>
+        <f t="shared" si="9"/>
         <v>68</v>
       </c>
       <c r="AG30" s="6">
         <v>3</v>
       </c>
       <c r="AH30" s="6">
-        <f>+AF30+AG30</f>
+        <f t="shared" si="10"/>
         <v>71</v>
       </c>
       <c r="AI30" s="3">
         <v>7</v>
       </c>
       <c r="AJ30" s="3">
-        <f>+AI30+AH30</f>
+        <f t="shared" si="11"/>
         <v>78</v>
       </c>
       <c r="AK30" s="3" t="s">
@@ -6751,36 +6751,36 @@
         <v>0</v>
       </c>
       <c r="AM30" s="3">
-        <f>+AJ30+AL30</f>
+        <f t="shared" si="12"/>
         <v>78</v>
       </c>
       <c r="AN30" s="3">
         <v>0</v>
       </c>
       <c r="AO30" s="3">
-        <f>+AM30+AN30</f>
+        <f t="shared" si="13"/>
         <v>78</v>
       </c>
       <c r="AP30" s="3">
         <v>1</v>
       </c>
       <c r="AQ30" s="3">
-        <f>+AO30+AP30</f>
+        <f t="shared" si="14"/>
         <v>79</v>
       </c>
       <c r="AR30" s="3">
-        <f>+AQ30+7</f>
+        <f t="shared" si="15"/>
         <v>86</v>
       </c>
       <c r="AS30" s="3">
-        <f>+AR30+7+AT30</f>
+        <f t="shared" si="16"/>
         <v>93</v>
       </c>
       <c r="AT30" s="3">
         <v>0</v>
       </c>
       <c r="AU30" s="3">
-        <f>+AA30-R30</f>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="AV30" s="3" t="s">
@@ -6796,7 +6796,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>1006</v>
       </c>
@@ -6834,59 +6834,59 @@
         <v>7</v>
       </c>
       <c r="M31" s="3">
-        <f>+IF(I31="SFK Freight Forwarder",L31,9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N31" s="3">
         <v>14</v>
       </c>
       <c r="O31" s="3">
-        <f>IF(I31="SFK Freight Forwarder",M31,M31+N31-1)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="P31" s="3">
-        <f>+IF(I31="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q31" s="3">
-        <f>+IF(I31="SFK Freight Forwarder",O31,O31+P31-1)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="R31" s="3">
-        <f>9+N31</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S31" s="3">
         <v>7</v>
       </c>
       <c r="T31" s="3">
-        <f>+R31+S31-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U31" s="3">
-        <f>+T31+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V31" s="3">
         <v>1</v>
       </c>
       <c r="W31" s="3">
-        <f>+U31+V31-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X31" s="3">
         <v>3</v>
       </c>
       <c r="Y31" s="3">
-        <f>+ROUNDDOWN(W31/7,0)*7+X31</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z31" s="6">
-        <f>+Y31+X31-1</f>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="AA31" s="6">
-        <f>+Z31+AB31-1</f>
+        <f t="shared" si="19"/>
         <v>34</v>
       </c>
       <c r="AB31" s="3">
@@ -6902,21 +6902,21 @@
         <v>57</v>
       </c>
       <c r="AF31" s="3">
-        <f>+AE31+AA31-1</f>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="AG31" s="6">
         <v>3</v>
       </c>
       <c r="AH31" s="6">
-        <f>+AF31+AG31</f>
+        <f t="shared" si="10"/>
         <v>93</v>
       </c>
       <c r="AI31" s="3">
         <v>0</v>
       </c>
       <c r="AJ31" s="3">
-        <f>+AI31+AH31</f>
+        <f t="shared" si="11"/>
         <v>93</v>
       </c>
       <c r="AK31" s="3" t="s">
@@ -6926,36 +6926,36 @@
         <v>1</v>
       </c>
       <c r="AM31" s="3">
-        <f>+AJ31+AL31</f>
+        <f t="shared" si="12"/>
         <v>94</v>
       </c>
       <c r="AN31" s="3">
         <v>4</v>
       </c>
       <c r="AO31" s="3">
-        <f>+AM31+AN31</f>
+        <f t="shared" si="13"/>
         <v>98</v>
       </c>
       <c r="AP31" s="3">
         <v>2</v>
       </c>
       <c r="AQ31" s="3">
-        <f>+AO31+AP31</f>
+        <f t="shared" si="14"/>
         <v>100</v>
       </c>
       <c r="AR31" s="3">
-        <f>+AQ31+7</f>
+        <f t="shared" si="15"/>
         <v>107</v>
       </c>
       <c r="AS31" s="3">
-        <f>+AR31+7+AT31</f>
+        <f t="shared" si="16"/>
         <v>130</v>
       </c>
       <c r="AT31" s="3">
         <v>16</v>
       </c>
       <c r="AU31" s="3">
-        <f>+AA31-R31</f>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="AV31" s="3" t="s">
@@ -6971,7 +6971,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>1007</v>
       </c>
@@ -7009,59 +7009,59 @@
         <v>7</v>
       </c>
       <c r="M32" s="3">
-        <f>+IF(I32="SFK Freight Forwarder",L32,9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N32" s="3">
         <v>14</v>
       </c>
       <c r="O32" s="3">
-        <f>IF(I32="SFK Freight Forwarder",M32,M32+N32-1)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="P32" s="3">
-        <f>+IF(I32="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <f>+IF(I32="SFK Freight Forwarder",O32,O32+P32-1)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="R32" s="3">
-        <f>9+N32</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S32" s="3">
         <v>7</v>
       </c>
       <c r="T32" s="3">
-        <f>+R32+S32-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U32" s="3">
-        <f>+T32+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V32" s="3">
         <v>1</v>
       </c>
       <c r="W32" s="3">
-        <f>+U32+V32-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X32" s="3">
         <v>3</v>
       </c>
       <c r="Y32" s="3">
-        <f>+ROUNDDOWN(W32/7,0)*7+X32</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z32" s="6">
-        <f>+Y32+X32-1</f>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="AA32" s="6">
-        <f>+Z32+AB32-1</f>
+        <f t="shared" si="19"/>
         <v>38</v>
       </c>
       <c r="AB32" s="3">
@@ -7077,21 +7077,21 @@
         <v>44</v>
       </c>
       <c r="AF32" s="3">
-        <f>+AE32+AA32-1</f>
+        <f t="shared" si="9"/>
         <v>81</v>
       </c>
       <c r="AG32" s="6">
         <v>3</v>
       </c>
       <c r="AH32" s="6">
-        <f>+AF32+AG32</f>
+        <f t="shared" si="10"/>
         <v>84</v>
       </c>
       <c r="AI32" s="3">
         <v>7</v>
       </c>
       <c r="AJ32" s="3">
-        <f>+AI32+AH32</f>
+        <f t="shared" si="11"/>
         <v>91</v>
       </c>
       <c r="AK32" s="3" t="s">
@@ -7101,36 +7101,36 @@
         <v>3</v>
       </c>
       <c r="AM32" s="3">
-        <f>+AJ32+AL32</f>
+        <f t="shared" si="12"/>
         <v>94</v>
       </c>
       <c r="AN32" s="3">
         <v>1</v>
       </c>
       <c r="AO32" s="3">
-        <f>+AM32+AN32</f>
+        <f t="shared" si="13"/>
         <v>95</v>
       </c>
       <c r="AP32" s="3">
         <v>6</v>
       </c>
       <c r="AQ32" s="3">
-        <f>+AO32+AP32</f>
+        <f t="shared" si="14"/>
         <v>101</v>
       </c>
       <c r="AR32" s="3">
-        <f>+AQ32+7</f>
+        <f t="shared" si="15"/>
         <v>108</v>
       </c>
       <c r="AS32" s="3">
-        <f>+AR32+7+AT32</f>
+        <f t="shared" si="16"/>
         <v>132</v>
       </c>
       <c r="AT32" s="3">
         <v>17</v>
       </c>
       <c r="AU32" s="3">
-        <f>+AA32-R32</f>
+        <f t="shared" si="17"/>
         <v>15</v>
       </c>
       <c r="AV32" s="3" t="s">
@@ -7146,7 +7146,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>1008</v>
       </c>
@@ -7184,59 +7184,59 @@
         <v>7</v>
       </c>
       <c r="M33" s="3">
-        <f>+IF(I33="SFK Freight Forwarder",L33,9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N33" s="3">
         <v>14</v>
       </c>
       <c r="O33" s="3">
-        <f>IF(I33="SFK Freight Forwarder",M33,M33+N33-1)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="P33" s="3">
-        <f>+IF(I33="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <f>+IF(I33="SFK Freight Forwarder",O33,O33+P33-1)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="R33" s="3">
-        <f>9+N33</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S33" s="3">
         <v>7</v>
       </c>
       <c r="T33" s="3">
-        <f>+R33+S33-1</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="U33" s="3">
-        <f>+T33+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V33" s="3">
         <v>1</v>
       </c>
       <c r="W33" s="3">
-        <f>+U33+V33-1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="X33" s="3">
         <v>3</v>
       </c>
       <c r="Y33" s="3">
-        <f>+ROUNDDOWN(W33/7,0)*7+X33</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z33" s="6">
-        <f>+Y33+X33-1</f>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="AA33" s="6">
-        <f>+Z33+AB33-1</f>
+        <f t="shared" si="19"/>
         <v>35</v>
       </c>
       <c r="AB33" s="3">
@@ -7252,21 +7252,21 @@
         <v>78</v>
       </c>
       <c r="AF33" s="3">
-        <f>+AE33+AA33-1</f>
+        <f t="shared" si="9"/>
         <v>112</v>
       </c>
       <c r="AG33" s="6">
         <v>3</v>
       </c>
       <c r="AH33" s="6">
-        <f>+AF33+AG33</f>
+        <f t="shared" si="10"/>
         <v>115</v>
       </c>
       <c r="AI33" s="3">
         <v>0</v>
       </c>
       <c r="AJ33" s="3">
-        <f>+AI33+AH33</f>
+        <f t="shared" si="11"/>
         <v>115</v>
       </c>
       <c r="AK33" s="3" t="s">
@@ -7276,36 +7276,36 @@
         <v>1</v>
       </c>
       <c r="AM33" s="3">
-        <f>+AJ33+AL33</f>
+        <f t="shared" si="12"/>
         <v>116</v>
       </c>
       <c r="AN33" s="3">
         <v>1</v>
       </c>
       <c r="AO33" s="3">
-        <f>+AM33+AN33</f>
+        <f t="shared" si="13"/>
         <v>117</v>
       </c>
       <c r="AP33" s="3">
         <v>4</v>
       </c>
       <c r="AQ33" s="3">
-        <f>+AO33+AP33</f>
+        <f t="shared" si="14"/>
         <v>121</v>
       </c>
       <c r="AR33" s="3">
-        <f>+AQ33+7</f>
+        <f t="shared" si="15"/>
         <v>128</v>
       </c>
       <c r="AS33" s="3">
-        <f>+AR33+7+AT33</f>
+        <f t="shared" si="16"/>
         <v>147</v>
       </c>
       <c r="AT33" s="3">
         <v>12</v>
       </c>
       <c r="AU33" s="3">
-        <f>+AA33-R33</f>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="AV33" s="3" t="s">
@@ -7321,7 +7321,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>1009</v>
       </c>
@@ -7359,59 +7359,59 @@
         <v>7</v>
       </c>
       <c r="M34" s="3">
-        <f>+IF(I34="SFK Freight Forwarder",L34,9)</f>
+        <f t="shared" ref="M34:M65" si="22">+IF(I34="SFK Freight Forwarder",L34,9)</f>
         <v>7</v>
       </c>
       <c r="N34" s="3">
         <v>14</v>
       </c>
       <c r="O34" s="3">
-        <f>IF(I34="SFK Freight Forwarder",M34,M34+N34-1)</f>
+        <f t="shared" ref="O34:O65" si="23">IF(I34="SFK Freight Forwarder",M34,M34+N34-1)</f>
         <v>7</v>
       </c>
       <c r="P34" s="3">
-        <f>+IF(I34="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q34" s="3">
-        <f>+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
+        <f t="shared" ref="Q34:Q65" si="24">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
         <v>7</v>
       </c>
       <c r="R34" s="3">
-        <f>9+N34</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S34" s="3">
         <v>7</v>
       </c>
       <c r="T34" s="3">
-        <f>+R34+S34-1</f>
+        <f t="shared" ref="T34:T65" si="25">+R34+S34-1</f>
         <v>29</v>
       </c>
       <c r="U34" s="3">
-        <f>+T34+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V34" s="3">
         <v>1</v>
       </c>
       <c r="W34" s="3">
-        <f>+U34+V34-1</f>
+        <f t="shared" ref="W34:W65" si="26">+U34+V34-1</f>
         <v>30</v>
       </c>
       <c r="X34" s="3">
         <v>3</v>
       </c>
       <c r="Y34" s="3">
-        <f>+ROUNDDOWN(W34/7,0)*7+X34</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z34" s="6">
-        <f>+Y34+X34-1</f>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="AA34" s="6">
-        <f>+Z34+AB34-1</f>
+        <f t="shared" si="19"/>
         <v>34</v>
       </c>
       <c r="AB34" s="3">
@@ -7427,21 +7427,21 @@
         <v>60</v>
       </c>
       <c r="AF34" s="3">
-        <f>+AE34+AA34-1</f>
+        <f t="shared" ref="AF34:AF65" si="27">+AE34+AA34-1</f>
         <v>93</v>
       </c>
       <c r="AG34" s="6">
         <v>3</v>
       </c>
       <c r="AH34" s="6">
-        <f>+AF34+AG34</f>
+        <f t="shared" ref="AH34:AH65" si="28">+AF34+AG34</f>
         <v>96</v>
       </c>
       <c r="AI34" s="3">
         <v>0</v>
       </c>
       <c r="AJ34" s="3">
-        <f>+AI34+AH34</f>
+        <f t="shared" ref="AJ34:AJ65" si="29">+AI34+AH34</f>
         <v>96</v>
       </c>
       <c r="AK34" s="3" t="s">
@@ -7451,36 +7451,36 @@
         <v>2</v>
       </c>
       <c r="AM34" s="3">
-        <f>+AJ34+AL34</f>
+        <f t="shared" ref="AM34:AM65" si="30">+AJ34+AL34</f>
         <v>98</v>
       </c>
       <c r="AN34" s="3">
         <v>2</v>
       </c>
       <c r="AO34" s="3">
-        <f>+AM34+AN34</f>
+        <f t="shared" ref="AO34:AO65" si="31">+AM34+AN34</f>
         <v>100</v>
       </c>
       <c r="AP34" s="3">
         <v>0</v>
       </c>
       <c r="AQ34" s="3">
-        <f>+AO34+AP34</f>
+        <f t="shared" ref="AQ34:AQ65" si="32">+AO34+AP34</f>
         <v>100</v>
       </c>
       <c r="AR34" s="3">
-        <f>+AQ34+7</f>
+        <f t="shared" ref="AR34:AR65" si="33">+AQ34+7</f>
         <v>107</v>
       </c>
       <c r="AS34" s="3">
-        <f>+AR34+7+AT34</f>
+        <f t="shared" ref="AS34:AS65" si="34">+AR34+7+AT34</f>
         <v>127</v>
       </c>
       <c r="AT34" s="3">
         <v>13</v>
       </c>
       <c r="AU34" s="3">
-        <f>+AA34-R34</f>
+        <f t="shared" ref="AU34:AU53" si="35">+AA34-R34</f>
         <v>11</v>
       </c>
       <c r="AV34" s="3" t="s">
@@ -7496,7 +7496,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>1010</v>
       </c>
@@ -7534,59 +7534,59 @@
         <v>7</v>
       </c>
       <c r="M35" s="3">
-        <f>+IF(I35="SFK Freight Forwarder",L35,9)</f>
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
       <c r="N35" s="3">
         <v>14</v>
       </c>
       <c r="O35" s="3">
-        <f>IF(I35="SFK Freight Forwarder",M35,M35+N35-1)</f>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
       <c r="P35" s="3">
-        <f>+IF(I35="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <f>+IF(I35="SFK Freight Forwarder",O35,O35+P35-1)</f>
+        <f t="shared" si="24"/>
         <v>7</v>
       </c>
       <c r="R35" s="3">
-        <f>9+N35</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S35" s="3">
         <v>7</v>
       </c>
       <c r="T35" s="3">
-        <f>+R35+S35-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U35" s="3">
-        <f>+T35+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V35" s="3">
         <v>1</v>
       </c>
       <c r="W35" s="3">
-        <f>+U35+V35-1</f>
+        <f t="shared" si="26"/>
         <v>30</v>
       </c>
       <c r="X35" s="3">
         <v>3</v>
       </c>
       <c r="Y35" s="3">
-        <f>+ROUNDDOWN(W35/7,0)*7+X35</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z35" s="6">
-        <f>+Y35+X35-1</f>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="AA35" s="6">
-        <f>+Z35+AB35-1</f>
+        <f t="shared" si="19"/>
         <v>34</v>
       </c>
       <c r="AB35" s="3">
@@ -7602,21 +7602,21 @@
         <v>62</v>
       </c>
       <c r="AF35" s="3">
-        <f>+AE35+AA35-1</f>
+        <f t="shared" si="27"/>
         <v>95</v>
       </c>
       <c r="AG35" s="6">
         <v>3</v>
       </c>
       <c r="AH35" s="6">
-        <f>+AF35+AG35</f>
+        <f t="shared" si="28"/>
         <v>98</v>
       </c>
       <c r="AI35" s="3">
         <v>0</v>
       </c>
       <c r="AJ35" s="3">
-        <f>+AI35+AH35</f>
+        <f t="shared" si="29"/>
         <v>98</v>
       </c>
       <c r="AK35" s="3" t="s">
@@ -7626,36 +7626,36 @@
         <v>4</v>
       </c>
       <c r="AM35" s="3">
-        <f>+AJ35+AL35</f>
+        <f t="shared" si="30"/>
         <v>102</v>
       </c>
       <c r="AN35" s="3">
         <v>2</v>
       </c>
       <c r="AO35" s="3">
-        <f>+AM35+AN35</f>
+        <f t="shared" si="31"/>
         <v>104</v>
       </c>
       <c r="AP35" s="3">
         <v>3</v>
       </c>
       <c r="AQ35" s="3">
-        <f>+AO35+AP35</f>
+        <f t="shared" si="32"/>
         <v>107</v>
       </c>
       <c r="AR35" s="3">
-        <f>+AQ35+7</f>
+        <f t="shared" si="33"/>
         <v>114</v>
       </c>
       <c r="AS35" s="3">
-        <f>+AR35+7+AT35</f>
+        <f t="shared" si="34"/>
         <v>135</v>
       </c>
       <c r="AT35" s="3">
         <v>14</v>
       </c>
       <c r="AU35" s="3">
-        <f>+AA35-R35</f>
+        <f t="shared" si="35"/>
         <v>11</v>
       </c>
       <c r="AV35" s="3" t="s">
@@ -7671,7 +7671,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>1012</v>
       </c>
@@ -7709,59 +7709,59 @@
         <v>7</v>
       </c>
       <c r="M36" s="3">
-        <f>+IF(I36="SFK Freight Forwarder",L36,9)</f>
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
       <c r="N36" s="3">
         <v>14</v>
       </c>
       <c r="O36" s="3">
-        <f>IF(I36="SFK Freight Forwarder",M36,M36+N36-1)</f>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
       <c r="P36" s="3">
-        <f>+IF(I36="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q36" s="3">
-        <f>+IF(I36="SFK Freight Forwarder",O36,O36+P36-1)</f>
+        <f t="shared" si="24"/>
         <v>7</v>
       </c>
       <c r="R36" s="3">
-        <f>9+N36</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S36" s="3">
         <v>7</v>
       </c>
       <c r="T36" s="3">
-        <f>+R36+S36-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U36" s="3">
-        <f>+T36+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V36" s="3">
         <v>1</v>
       </c>
       <c r="W36" s="3">
-        <f>+U36+V36-1</f>
+        <f t="shared" si="26"/>
         <v>30</v>
       </c>
       <c r="X36" s="3">
         <v>3</v>
       </c>
       <c r="Y36" s="3">
-        <f>+ROUNDDOWN(W36/7,0)*7+X36</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z36" s="6">
-        <f>+Y36+X36-1</f>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="AA36" s="6">
-        <f>+Z36+AB36-1</f>
+        <f t="shared" si="19"/>
         <v>34</v>
       </c>
       <c r="AB36" s="3">
@@ -7777,21 +7777,21 @@
         <v>57</v>
       </c>
       <c r="AF36" s="3">
-        <f>+AE36+AA36-1</f>
+        <f t="shared" si="27"/>
         <v>90</v>
       </c>
       <c r="AG36" s="6">
         <v>3</v>
       </c>
       <c r="AH36" s="6">
-        <f>+AF36+AG36</f>
+        <f t="shared" si="28"/>
         <v>93</v>
       </c>
       <c r="AI36" s="3">
         <v>0</v>
       </c>
       <c r="AJ36" s="3">
-        <f>+AI36+AH36</f>
+        <f t="shared" si="29"/>
         <v>93</v>
       </c>
       <c r="AK36" s="3" t="s">
@@ -7801,36 +7801,36 @@
         <v>2</v>
       </c>
       <c r="AM36" s="3">
-        <f>+AJ36+AL36</f>
+        <f t="shared" si="30"/>
         <v>95</v>
       </c>
       <c r="AN36" s="3">
         <v>2</v>
       </c>
       <c r="AO36" s="3">
-        <f>+AM36+AN36</f>
+        <f t="shared" si="31"/>
         <v>97</v>
       </c>
       <c r="AP36" s="3">
         <v>3</v>
       </c>
       <c r="AQ36" s="3">
-        <f>+AO36+AP36</f>
+        <f t="shared" si="32"/>
         <v>100</v>
       </c>
       <c r="AR36" s="3">
-        <f>+AQ36+7</f>
+        <f t="shared" si="33"/>
         <v>107</v>
       </c>
       <c r="AS36" s="3">
-        <f>+AR36+7+AT36</f>
+        <f t="shared" si="34"/>
         <v>124</v>
       </c>
       <c r="AT36" s="3">
         <v>10</v>
       </c>
       <c r="AU36" s="3">
-        <f>+AA36-R36</f>
+        <f t="shared" si="35"/>
         <v>11</v>
       </c>
       <c r="AV36" s="3" t="s">
@@ -7846,7 +7846,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>1014</v>
       </c>
@@ -7884,59 +7884,59 @@
         <v>7</v>
       </c>
       <c r="M37" s="3">
-        <f>+IF(I37="SFK Freight Forwarder",L37,9)</f>
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
       <c r="N37" s="3">
         <v>14</v>
       </c>
       <c r="O37" s="3">
-        <f>IF(I37="SFK Freight Forwarder",M37,M37+N37-1)</f>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
       <c r="P37" s="3">
-        <f>+IF(I37="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q37" s="3">
-        <f>+IF(I37="SFK Freight Forwarder",O37,O37+P37-1)</f>
+        <f t="shared" si="24"/>
         <v>7</v>
       </c>
       <c r="R37" s="3">
-        <f>9+N37</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S37" s="3">
         <v>7</v>
       </c>
       <c r="T37" s="3">
-        <f>+R37+S37-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U37" s="3">
-        <f>+T37+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V37" s="3">
         <v>2</v>
       </c>
       <c r="W37" s="3">
-        <f>+U37+V37-1</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="X37" s="3">
         <v>5</v>
       </c>
       <c r="Y37" s="3">
-        <f>+ROUNDDOWN(W37/7,0)*7+X37</f>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z37" s="6">
-        <f>+Y37+X37-1</f>
+        <f t="shared" si="21"/>
         <v>37</v>
       </c>
       <c r="AA37" s="6">
-        <f>+Z37+AB37-1</f>
+        <f t="shared" si="19"/>
         <v>42</v>
       </c>
       <c r="AB37" s="3">
@@ -7952,21 +7952,21 @@
         <v>13</v>
       </c>
       <c r="AF37" s="3">
-        <f>+AE37+AA37-1</f>
+        <f t="shared" si="27"/>
         <v>54</v>
       </c>
       <c r="AG37" s="6">
         <v>3</v>
       </c>
       <c r="AH37" s="6">
-        <f>+AF37+AG37</f>
+        <f t="shared" si="28"/>
         <v>57</v>
       </c>
       <c r="AI37" s="3">
         <v>7</v>
       </c>
       <c r="AJ37" s="3">
-        <f>+AI37+AH37</f>
+        <f t="shared" si="29"/>
         <v>64</v>
       </c>
       <c r="AK37" s="3" t="s">
@@ -7976,36 +7976,36 @@
         <v>0</v>
       </c>
       <c r="AM37" s="3">
-        <f>+AJ37+AL37</f>
+        <f t="shared" si="30"/>
         <v>64</v>
       </c>
       <c r="AN37" s="3">
         <v>0</v>
       </c>
       <c r="AO37" s="3">
-        <f>+AM37+AN37</f>
+        <f t="shared" si="31"/>
         <v>64</v>
       </c>
       <c r="AP37" s="3">
         <v>5</v>
       </c>
       <c r="AQ37" s="3">
-        <f>+AO37+AP37</f>
+        <f t="shared" si="32"/>
         <v>69</v>
       </c>
       <c r="AR37" s="3">
-        <f>+AQ37+7</f>
+        <f t="shared" si="33"/>
         <v>76</v>
       </c>
       <c r="AS37" s="3">
-        <f>+AR37+7+AT37</f>
+        <f t="shared" si="34"/>
         <v>83</v>
       </c>
       <c r="AT37" s="3">
         <v>0</v>
       </c>
       <c r="AU37" s="3">
-        <f>+AA37-R37</f>
+        <f t="shared" si="35"/>
         <v>19</v>
       </c>
       <c r="AV37" s="3" t="s">
@@ -8021,7 +8021,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>1015</v>
       </c>
@@ -8059,59 +8059,59 @@
         <v>7</v>
       </c>
       <c r="M38" s="3">
-        <f>+IF(I38="SFK Freight Forwarder",L38,9)</f>
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
       <c r="N38" s="3">
         <v>14</v>
       </c>
       <c r="O38" s="3">
-        <f>IF(I38="SFK Freight Forwarder",M38,M38+N38-1)</f>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
       <c r="P38" s="3">
-        <f>+IF(I38="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q38" s="3">
-        <f>+IF(I38="SFK Freight Forwarder",O38,O38+P38-1)</f>
+        <f t="shared" si="24"/>
         <v>7</v>
       </c>
       <c r="R38" s="3">
-        <f>9+N38</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S38" s="3">
         <v>7</v>
       </c>
       <c r="T38" s="3">
-        <f>+R38+S38-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U38" s="3">
-        <f>+T38+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V38" s="3">
         <v>2</v>
       </c>
       <c r="W38" s="3">
-        <f>+U38+V38-1</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="X38" s="3">
         <v>5</v>
       </c>
       <c r="Y38" s="3">
-        <f>+ROUNDDOWN(W38/7,0)*7+X38</f>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z38" s="6">
-        <f>+Y38+X38-1</f>
+        <f t="shared" si="21"/>
         <v>37</v>
       </c>
       <c r="AA38" s="6">
-        <f>+Z38+AB38-1</f>
+        <f t="shared" si="19"/>
         <v>42</v>
       </c>
       <c r="AB38" s="3">
@@ -8127,21 +8127,21 @@
         <v>32</v>
       </c>
       <c r="AF38" s="3">
-        <f>+AE38+AA38-1</f>
+        <f t="shared" si="27"/>
         <v>73</v>
       </c>
       <c r="AG38" s="6">
         <v>3</v>
       </c>
       <c r="AH38" s="6">
-        <f>+AF38+AG38</f>
+        <f t="shared" si="28"/>
         <v>76</v>
       </c>
       <c r="AI38" s="3">
         <v>7</v>
       </c>
       <c r="AJ38" s="3">
-        <f>+AI38+AH38</f>
+        <f t="shared" si="29"/>
         <v>83</v>
       </c>
       <c r="AK38" s="3" t="s">
@@ -8151,36 +8151,36 @@
         <v>2</v>
       </c>
       <c r="AM38" s="3">
-        <f>+AJ38+AL38</f>
+        <f t="shared" si="30"/>
         <v>85</v>
       </c>
       <c r="AN38" s="3">
         <v>2</v>
       </c>
       <c r="AO38" s="3">
-        <f>+AM38+AN38</f>
+        <f t="shared" si="31"/>
         <v>87</v>
       </c>
       <c r="AP38" s="3">
         <v>3</v>
       </c>
       <c r="AQ38" s="3">
-        <f>+AO38+AP38</f>
+        <f t="shared" si="32"/>
         <v>90</v>
       </c>
       <c r="AR38" s="3">
-        <f>+AQ38+7</f>
+        <f t="shared" si="33"/>
         <v>97</v>
       </c>
       <c r="AS38" s="3">
-        <f>+AR38+7+AT38</f>
+        <f t="shared" si="34"/>
         <v>104</v>
       </c>
       <c r="AT38" s="3">
         <v>0</v>
       </c>
       <c r="AU38" s="3">
-        <f>+AA38-R38</f>
+        <f t="shared" si="35"/>
         <v>19</v>
       </c>
       <c r="AV38" s="3" t="s">
@@ -8196,7 +8196,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1034</v>
       </c>
@@ -8234,59 +8234,59 @@
         <v>7</v>
       </c>
       <c r="M39" s="3">
-        <f>+IF(I39="SFK Freight Forwarder",L39,9)</f>
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
       <c r="N39" s="3">
         <v>14</v>
       </c>
       <c r="O39" s="3">
-        <f>IF(I39="SFK Freight Forwarder",M39,M39+N39-1)</f>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
       <c r="P39" s="3">
-        <f>+IF(I39="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q39" s="3">
-        <f>+IF(I39="SFK Freight Forwarder",O39,O39+P39-1)</f>
+        <f t="shared" si="24"/>
         <v>7</v>
       </c>
       <c r="R39" s="3">
-        <f>9+N39</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S39" s="3">
         <v>7</v>
       </c>
       <c r="T39" s="3">
-        <f>+R39+S39-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U39" s="3">
-        <f>+T39+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V39" s="3">
         <v>1</v>
       </c>
       <c r="W39" s="3">
-        <f>+U39+V39-1</f>
+        <f t="shared" si="26"/>
         <v>30</v>
       </c>
       <c r="X39" s="3">
         <v>3</v>
       </c>
       <c r="Y39" s="3">
-        <f>+ROUNDDOWN(W39/7,0)*7+X39</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z39" s="6">
-        <f>+Y39+X39-1</f>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="AA39" s="6">
-        <f>+Z39+AB39-1</f>
+        <f t="shared" si="19"/>
         <v>34</v>
       </c>
       <c r="AB39" s="3">
@@ -8302,21 +8302,21 @@
         <v>52</v>
       </c>
       <c r="AF39" s="3">
-        <f>+AE39+AA39-1</f>
+        <f t="shared" si="27"/>
         <v>85</v>
       </c>
       <c r="AG39" s="6">
         <v>3</v>
       </c>
       <c r="AH39" s="6">
-        <f>+AF39+AG39</f>
+        <f t="shared" si="28"/>
         <v>88</v>
       </c>
       <c r="AI39" s="3">
         <v>0</v>
       </c>
       <c r="AJ39" s="3">
-        <f>+AI39+AH39</f>
+        <f t="shared" si="29"/>
         <v>88</v>
       </c>
       <c r="AK39" s="3" t="s">
@@ -8326,36 +8326,36 @@
         <v>2</v>
       </c>
       <c r="AM39" s="3">
-        <f>+AJ39+AL39</f>
+        <f t="shared" si="30"/>
         <v>90</v>
       </c>
       <c r="AN39" s="3">
         <v>3</v>
       </c>
       <c r="AO39" s="3">
-        <f>+AM39+AN39</f>
+        <f t="shared" si="31"/>
         <v>93</v>
       </c>
       <c r="AP39" s="3">
         <v>0</v>
       </c>
       <c r="AQ39" s="3">
-        <f>+AO39+AP39</f>
+        <f t="shared" si="32"/>
         <v>93</v>
       </c>
       <c r="AR39" s="3">
-        <f>+AQ39+7</f>
+        <f t="shared" si="33"/>
         <v>100</v>
       </c>
       <c r="AS39" s="3">
-        <f>+AR39+7+AT39</f>
+        <f t="shared" si="34"/>
         <v>107</v>
       </c>
       <c r="AT39" s="3">
         <v>0</v>
       </c>
       <c r="AU39" s="3">
-        <f>+AA39-R39</f>
+        <f t="shared" si="35"/>
         <v>11</v>
       </c>
       <c r="AV39" s="3" t="s">
@@ -8371,7 +8371,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>1036</v>
       </c>
@@ -8409,59 +8409,59 @@
         <v>7</v>
       </c>
       <c r="M40" s="3">
-        <f>+IF(I40="SFK Freight Forwarder",L40,9)</f>
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
       <c r="N40" s="3">
         <v>14</v>
       </c>
       <c r="O40" s="3">
-        <f>IF(I40="SFK Freight Forwarder",M40,M40+N40-1)</f>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
       <c r="P40" s="3">
-        <f>+IF(I40="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q40" s="3">
-        <f>+IF(I40="SFK Freight Forwarder",O40,O40+P40-1)</f>
+        <f t="shared" si="24"/>
         <v>7</v>
       </c>
       <c r="R40" s="3">
-        <f>9+N40</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S40" s="3">
         <v>7</v>
       </c>
       <c r="T40" s="3">
-        <f>+R40+S40-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U40" s="3">
-        <f>+T40+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V40" s="3">
         <v>2</v>
       </c>
       <c r="W40" s="3">
-        <f>+U40+V40-1</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="X40" s="3">
         <v>5</v>
       </c>
       <c r="Y40" s="3">
-        <f>+ROUNDDOWN(W40/7,0)*7+X40</f>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z40" s="6">
-        <f>+Y40+X40-1</f>
+        <f t="shared" si="21"/>
         <v>37</v>
       </c>
       <c r="AA40" s="6">
-        <f>+Z40+AB40-1</f>
+        <f t="shared" si="19"/>
         <v>39</v>
       </c>
       <c r="AB40" s="3">
@@ -8477,21 +8477,21 @@
         <v>28</v>
       </c>
       <c r="AF40" s="3">
-        <f>+AE40+AA40-1</f>
+        <f t="shared" si="27"/>
         <v>66</v>
       </c>
       <c r="AG40" s="6">
         <v>3</v>
       </c>
       <c r="AH40" s="6">
-        <f>+AF40+AG40</f>
+        <f t="shared" si="28"/>
         <v>69</v>
       </c>
       <c r="AI40" s="3">
         <v>0</v>
       </c>
       <c r="AJ40" s="3">
-        <f>+AI40+AH40</f>
+        <f t="shared" si="29"/>
         <v>69</v>
       </c>
       <c r="AK40" s="3" t="s">
@@ -8501,36 +8501,36 @@
         <v>2</v>
       </c>
       <c r="AM40" s="3">
-        <f>+AJ40+AL40</f>
+        <f t="shared" si="30"/>
         <v>71</v>
       </c>
       <c r="AN40" s="3">
         <v>2</v>
       </c>
       <c r="AO40" s="3">
-        <f>+AM40+AN40</f>
+        <f t="shared" si="31"/>
         <v>73</v>
       </c>
       <c r="AP40" s="3">
         <v>1</v>
       </c>
       <c r="AQ40" s="3">
-        <f>+AO40+AP40</f>
+        <f t="shared" si="32"/>
         <v>74</v>
       </c>
       <c r="AR40" s="3">
-        <f>+AQ40+7</f>
+        <f t="shared" si="33"/>
         <v>81</v>
       </c>
       <c r="AS40" s="3">
-        <f>+AR40+7+AT40</f>
+        <f t="shared" si="34"/>
         <v>88</v>
       </c>
       <c r="AT40" s="3">
         <v>0</v>
       </c>
       <c r="AU40" s="3">
-        <f>+AA40-R40</f>
+        <f t="shared" si="35"/>
         <v>16</v>
       </c>
       <c r="AV40" s="3" t="s">
@@ -8546,7 +8546,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>1037</v>
       </c>
@@ -8584,59 +8584,59 @@
         <v>7</v>
       </c>
       <c r="M41" s="3">
-        <f>+IF(I41="SFK Freight Forwarder",L41,9)</f>
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
       <c r="N41" s="3">
         <v>14</v>
       </c>
       <c r="O41" s="3">
-        <f>IF(I41="SFK Freight Forwarder",M41,M41+N41-1)</f>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
       <c r="P41" s="3">
-        <f>+IF(I41="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q41" s="3">
-        <f>+IF(I41="SFK Freight Forwarder",O41,O41+P41-1)</f>
+        <f t="shared" si="24"/>
         <v>7</v>
       </c>
       <c r="R41" s="3">
-        <f>9+N41</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S41" s="3">
         <v>7</v>
       </c>
       <c r="T41" s="3">
-        <f>+R41+S41-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U41" s="3">
-        <f>+T41+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V41" s="3">
         <v>1</v>
       </c>
       <c r="W41" s="3">
-        <f>+U41+V41-1</f>
+        <f t="shared" si="26"/>
         <v>30</v>
       </c>
       <c r="X41" s="3">
         <v>3</v>
       </c>
       <c r="Y41" s="3">
-        <f>+ROUNDDOWN(W41/7,0)*7+X41</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z41" s="6">
-        <f>+Y41+X41-1</f>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="AA41" s="6">
-        <f>+Z41+AB41-1</f>
+        <f t="shared" si="19"/>
         <v>34</v>
       </c>
       <c r="AB41" s="3">
@@ -8652,21 +8652,21 @@
         <v>62</v>
       </c>
       <c r="AF41" s="3">
-        <f>+AE41+AA41-1</f>
+        <f t="shared" si="27"/>
         <v>95</v>
       </c>
       <c r="AG41" s="6">
         <v>3</v>
       </c>
       <c r="AH41" s="6">
-        <f>+AF41+AG41</f>
+        <f t="shared" si="28"/>
         <v>98</v>
       </c>
       <c r="AI41" s="3">
         <v>7</v>
       </c>
       <c r="AJ41" s="3">
-        <f>+AI41+AH41</f>
+        <f t="shared" si="29"/>
         <v>105</v>
       </c>
       <c r="AK41" s="3" t="s">
@@ -8676,36 +8676,36 @@
         <v>3</v>
       </c>
       <c r="AM41" s="3">
-        <f>+AJ41+AL41</f>
+        <f t="shared" si="30"/>
         <v>108</v>
       </c>
       <c r="AN41" s="3">
         <v>3</v>
       </c>
       <c r="AO41" s="3">
-        <f>+AM41+AN41</f>
+        <f t="shared" si="31"/>
         <v>111</v>
       </c>
       <c r="AP41" s="3">
         <v>3</v>
       </c>
       <c r="AQ41" s="3">
-        <f>+AO41+AP41</f>
+        <f t="shared" si="32"/>
         <v>114</v>
       </c>
       <c r="AR41" s="3">
-        <f>+AQ41+7</f>
+        <f t="shared" si="33"/>
         <v>121</v>
       </c>
       <c r="AS41" s="3">
-        <f>+AR41+7+AT41</f>
+        <f t="shared" si="34"/>
         <v>136</v>
       </c>
       <c r="AT41" s="3">
         <v>8</v>
       </c>
       <c r="AU41" s="3">
-        <f>+AA41-R41</f>
+        <f t="shared" si="35"/>
         <v>11</v>
       </c>
       <c r="AV41" s="3" t="s">
@@ -8721,7 +8721,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>1039</v>
       </c>
@@ -8759,58 +8759,58 @@
         <v>7</v>
       </c>
       <c r="M42" s="3">
-        <f>+IF(I42="SFK Freight Forwarder",L42,9)</f>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="N42" s="3">
         <v>21</v>
       </c>
       <c r="O42" s="3">
-        <f>IF(I42="SFK Freight Forwarder",M42,M42+N42-1)</f>
+        <f t="shared" si="23"/>
         <v>29</v>
       </c>
       <c r="P42" s="3">
-        <f>+IF(I42="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="Q42" s="3">
-        <f>+IF(I42="SFK Freight Forwarder",O42,O42+P42-1)</f>
+        <f t="shared" si="24"/>
         <v>33</v>
       </c>
       <c r="R42" s="3">
-        <f>9+N42</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="S42" s="3">
         <v>7</v>
       </c>
       <c r="T42" s="3">
-        <f>+R42+S42-1</f>
+        <f t="shared" si="25"/>
         <v>36</v>
       </c>
       <c r="U42" s="3">
-        <f>+T42+1</f>
+        <f t="shared" si="6"/>
         <v>37</v>
       </c>
       <c r="V42" s="3">
         <v>1</v>
       </c>
       <c r="W42" s="3">
-        <f>+U42+V42-1</f>
+        <f t="shared" si="26"/>
         <v>37</v>
       </c>
       <c r="X42" s="3">
         <v>2</v>
       </c>
       <c r="Y42" s="3">
-        <f>+ROUNDDOWN(W42/7,0)*7+X42</f>
+        <f t="shared" si="18"/>
         <v>37</v>
       </c>
       <c r="Z42" s="6">
         <v>42</v>
       </c>
       <c r="AA42" s="6">
-        <f>+Z42+AB42-1</f>
+        <f t="shared" si="19"/>
         <v>44</v>
       </c>
       <c r="AB42" s="3">
@@ -8826,21 +8826,21 @@
         <v>40</v>
       </c>
       <c r="AF42" s="3">
-        <f>+AE42+AA42-1</f>
+        <f t="shared" si="27"/>
         <v>83</v>
       </c>
       <c r="AG42" s="6">
         <v>3</v>
       </c>
       <c r="AH42" s="6">
-        <f>+AF42+AG42</f>
+        <f t="shared" si="28"/>
         <v>86</v>
       </c>
       <c r="AI42" s="3">
         <v>0</v>
       </c>
       <c r="AJ42" s="3">
-        <f>+AI42+AH42</f>
+        <f t="shared" si="29"/>
         <v>86</v>
       </c>
       <c r="AK42" s="3" t="s">
@@ -8850,36 +8850,36 @@
         <v>2</v>
       </c>
       <c r="AM42" s="3">
-        <f>+AJ42+AL42</f>
+        <f t="shared" si="30"/>
         <v>88</v>
       </c>
       <c r="AN42" s="3">
         <v>3</v>
       </c>
       <c r="AO42" s="3">
-        <f>+AM42+AN42</f>
+        <f t="shared" si="31"/>
         <v>91</v>
       </c>
       <c r="AP42" s="3">
         <v>0</v>
       </c>
       <c r="AQ42" s="3">
-        <f>+AO42+AP42</f>
+        <f t="shared" si="32"/>
         <v>91</v>
       </c>
       <c r="AR42" s="3">
-        <f>+AQ42+7</f>
+        <f t="shared" si="33"/>
         <v>98</v>
       </c>
       <c r="AS42" s="3">
-        <f>+AR42+7+AT42</f>
+        <f t="shared" si="34"/>
         <v>105</v>
       </c>
       <c r="AT42" s="3">
         <v>0</v>
       </c>
       <c r="AU42" s="3">
-        <f>+AA42-R42</f>
+        <f t="shared" si="35"/>
         <v>14</v>
       </c>
       <c r="AV42" s="3" t="s">
@@ -8895,7 +8895,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>1040</v>
       </c>
@@ -8933,51 +8933,51 @@
         <v>7</v>
       </c>
       <c r="M43" s="3">
-        <f>+IF(I43="SFK Freight Forwarder",L43,9)</f>
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
       <c r="N43" s="3">
         <v>14</v>
       </c>
       <c r="O43" s="3">
-        <f>IF(I43="SFK Freight Forwarder",M43,M43+N43-1)</f>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
       <c r="P43" s="3">
-        <f>+IF(I43="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q43" s="3">
-        <f>+IF(I43="SFK Freight Forwarder",O43,O43+P43-1)</f>
+        <f t="shared" si="24"/>
         <v>7</v>
       </c>
       <c r="R43" s="3">
-        <f>9+N43</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S43" s="3">
         <v>7</v>
       </c>
       <c r="T43" s="3">
-        <f>+R43+S43-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U43" s="3">
-        <f>+T43+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V43" s="3">
         <v>1</v>
       </c>
       <c r="W43" s="3">
-        <f>+U43+V43-1</f>
+        <f t="shared" si="26"/>
         <v>30</v>
       </c>
       <c r="X43" s="3">
         <v>3</v>
       </c>
       <c r="Y43" s="3">
-        <f>+ROUNDDOWN(W43/7,0)*7+X43</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z43" s="6">
@@ -8985,7 +8985,7 @@
         <v>33</v>
       </c>
       <c r="AA43" s="6">
-        <f>+Z43+AB43-1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="AB43" s="3">
@@ -9001,21 +9001,21 @@
         <v>32</v>
       </c>
       <c r="AF43" s="3">
-        <f>+AE43+AA43-1</f>
+        <f t="shared" si="27"/>
         <v>68</v>
       </c>
       <c r="AG43" s="6">
         <v>3</v>
       </c>
       <c r="AH43" s="6">
-        <f>+AF43+AG43</f>
+        <f t="shared" si="28"/>
         <v>71</v>
       </c>
       <c r="AI43" s="3">
         <v>0</v>
       </c>
       <c r="AJ43" s="3">
-        <f>+AI43+AH43</f>
+        <f t="shared" si="29"/>
         <v>71</v>
       </c>
       <c r="AK43" s="3" t="s">
@@ -9025,36 +9025,36 @@
         <v>6</v>
       </c>
       <c r="AM43" s="3">
-        <f>+AJ43+AL43</f>
+        <f t="shared" si="30"/>
         <v>77</v>
       </c>
       <c r="AN43" s="3">
         <v>3</v>
       </c>
       <c r="AO43" s="3">
-        <f>+AM43+AN43</f>
+        <f t="shared" si="31"/>
         <v>80</v>
       </c>
       <c r="AP43" s="3">
         <v>2</v>
       </c>
       <c r="AQ43" s="3">
-        <f>+AO43+AP43</f>
+        <f t="shared" si="32"/>
         <v>82</v>
       </c>
       <c r="AR43" s="3">
-        <f>+AQ43+7</f>
+        <f t="shared" si="33"/>
         <v>89</v>
       </c>
       <c r="AS43" s="3">
-        <f>+AR43+7+AT43</f>
+        <f t="shared" si="34"/>
         <v>96</v>
       </c>
       <c r="AT43" s="3">
         <v>0</v>
       </c>
       <c r="AU43" s="3">
-        <f>+AA43-R43</f>
+        <f t="shared" si="35"/>
         <v>14</v>
       </c>
       <c r="AV43" s="3" t="s">
@@ -9070,7 +9070,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>1045</v>
       </c>
@@ -9108,58 +9108,58 @@
         <v>2</v>
       </c>
       <c r="M44" s="3">
-        <f>+IF(I44="SFK Freight Forwarder",L44,9)</f>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="N44" s="3">
         <v>21</v>
       </c>
       <c r="O44" s="3">
-        <f>IF(I44="SFK Freight Forwarder",M44,M44+N44-1)</f>
+        <f t="shared" si="23"/>
         <v>29</v>
       </c>
       <c r="P44" s="3">
-        <f>+IF(I44="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="Q44" s="3">
-        <f>+IF(I44="SFK Freight Forwarder",O44,O44+P44-1)</f>
+        <f t="shared" si="24"/>
         <v>33</v>
       </c>
       <c r="R44" s="3">
-        <f>9+N44</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="S44" s="3">
         <v>7</v>
       </c>
       <c r="T44" s="3">
-        <f>+R44+S44-1</f>
+        <f t="shared" si="25"/>
         <v>36</v>
       </c>
       <c r="U44" s="3">
-        <f>+T44+1</f>
+        <f t="shared" si="6"/>
         <v>37</v>
       </c>
       <c r="V44" s="3">
         <v>1</v>
       </c>
       <c r="W44" s="3">
-        <f>+U44+V44-1</f>
+        <f t="shared" si="26"/>
         <v>37</v>
       </c>
       <c r="X44" s="3">
         <v>2</v>
       </c>
       <c r="Y44" s="3">
-        <f>+ROUNDDOWN(W44/7,0)*7+X44</f>
+        <f t="shared" si="18"/>
         <v>37</v>
       </c>
       <c r="Z44" s="6">
         <v>37</v>
       </c>
       <c r="AA44" s="6">
-        <f>+Z44+AB44-1</f>
+        <f t="shared" si="19"/>
         <v>39</v>
       </c>
       <c r="AB44" s="3">
@@ -9175,21 +9175,21 @@
         <v>46</v>
       </c>
       <c r="AF44" s="3">
-        <f>+AE44+AA44-1</f>
+        <f t="shared" si="27"/>
         <v>84</v>
       </c>
       <c r="AG44" s="6">
         <v>3</v>
       </c>
       <c r="AH44" s="6">
-        <f>+AF44+AG44</f>
+        <f t="shared" si="28"/>
         <v>87</v>
       </c>
       <c r="AI44" s="3">
         <v>7</v>
       </c>
       <c r="AJ44" s="3">
-        <f>+AI44+AH44</f>
+        <f t="shared" si="29"/>
         <v>94</v>
       </c>
       <c r="AK44" s="3" t="s">
@@ -9199,36 +9199,36 @@
         <v>4</v>
       </c>
       <c r="AM44" s="3">
-        <f>+AJ44+AL44</f>
+        <f t="shared" si="30"/>
         <v>98</v>
       </c>
       <c r="AN44" s="3">
         <v>3</v>
       </c>
       <c r="AO44" s="3">
-        <f>+AM44+AN44</f>
+        <f t="shared" si="31"/>
         <v>101</v>
       </c>
       <c r="AP44" s="3">
         <v>4</v>
       </c>
       <c r="AQ44" s="3">
-        <f>+AO44+AP44</f>
+        <f t="shared" si="32"/>
         <v>105</v>
       </c>
       <c r="AR44" s="3">
-        <f>+AQ44+7</f>
+        <f t="shared" si="33"/>
         <v>112</v>
       </c>
       <c r="AS44" s="3">
-        <f>+AR44+7+AT44</f>
+        <f t="shared" si="34"/>
         <v>119</v>
       </c>
       <c r="AT44" s="3">
         <v>0</v>
       </c>
       <c r="AU44" s="3">
-        <f>+AA44-R44</f>
+        <f t="shared" si="35"/>
         <v>9</v>
       </c>
       <c r="AV44" s="3" t="s">
@@ -9244,7 +9244,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>1084</v>
       </c>
@@ -9282,58 +9282,58 @@
         <v>7</v>
       </c>
       <c r="M45" s="3">
-        <f>+IF(I45="SFK Freight Forwarder",L45,9)</f>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="N45" s="3">
         <v>14</v>
       </c>
       <c r="O45" s="3">
-        <f>IF(I45="SFK Freight Forwarder",M45,M45+N45-1)</f>
+        <f t="shared" si="23"/>
         <v>22</v>
       </c>
       <c r="P45" s="3">
-        <f>+IF(I45="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="Q45" s="3">
-        <f>+IF(I45="SFK Freight Forwarder",O45,O45+P45-1)</f>
+        <f t="shared" si="24"/>
         <v>26</v>
       </c>
       <c r="R45" s="3">
-        <f>9+N45</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S45" s="3">
         <v>7</v>
       </c>
       <c r="T45" s="3">
-        <f>+R45+S45-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U45" s="3">
-        <f>+T45+1</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V45" s="3">
         <v>2</v>
       </c>
       <c r="W45" s="3">
-        <f>+U45+V45-1</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="X45" s="3">
         <v>8</v>
       </c>
       <c r="Y45" s="3">
-        <f>+ROUNDDOWN(W45/7,0)*7+X45</f>
+        <f t="shared" si="18"/>
         <v>36</v>
       </c>
       <c r="Z45" s="6">
         <v>39</v>
       </c>
       <c r="AA45" s="6">
-        <f>+Z45+AB45-1</f>
+        <f t="shared" si="19"/>
         <v>41</v>
       </c>
       <c r="AB45" s="3">
@@ -9349,21 +9349,21 @@
         <v>35</v>
       </c>
       <c r="AF45" s="3">
-        <f>+AE45+AA45-1</f>
+        <f t="shared" si="27"/>
         <v>75</v>
       </c>
       <c r="AG45" s="6">
         <v>3</v>
       </c>
       <c r="AH45" s="6">
-        <f>+AF45+AG45</f>
+        <f t="shared" si="28"/>
         <v>78</v>
       </c>
       <c r="AI45" s="3">
         <v>0</v>
       </c>
       <c r="AJ45" s="3">
-        <f>+AI45+AH45</f>
+        <f t="shared" si="29"/>
         <v>78</v>
       </c>
       <c r="AK45" s="3" t="s">
@@ -9373,36 +9373,36 @@
         <v>2</v>
       </c>
       <c r="AM45" s="3">
-        <f>+AJ45+AL45</f>
+        <f t="shared" si="30"/>
         <v>80</v>
       </c>
       <c r="AN45" s="3">
         <v>2</v>
       </c>
       <c r="AO45" s="3">
-        <f>+AM45+AN45</f>
+        <f t="shared" si="31"/>
         <v>82</v>
       </c>
       <c r="AP45" s="3">
         <v>2</v>
       </c>
       <c r="AQ45" s="3">
-        <f>+AO45+AP45</f>
+        <f t="shared" si="32"/>
         <v>84</v>
       </c>
       <c r="AR45" s="3">
-        <f>+AQ45+7</f>
+        <f t="shared" si="33"/>
         <v>91</v>
       </c>
       <c r="AS45" s="3">
-        <f>+AR45+7+AT45</f>
+        <f t="shared" si="34"/>
         <v>98</v>
       </c>
       <c r="AT45" s="3">
         <v>0</v>
       </c>
       <c r="AU45" s="3">
-        <f>+AA45-R45</f>
+        <f t="shared" si="35"/>
         <v>18</v>
       </c>
       <c r="AV45" s="3" t="s">
@@ -9456,21 +9456,21 @@
         <v>5</v>
       </c>
       <c r="M46" s="3">
-        <f>+IF(I46="SFK Freight Forwarder",L46,9)</f>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="N46" s="23">
         <v>2</v>
       </c>
       <c r="O46" s="3">
-        <f>IF(I46="SFK Freight Forwarder",M46,M46+N46-1)</f>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="P46" s="3">
         <v>5</v>
       </c>
       <c r="Q46" s="3">
-        <f>+IF(I46="SFK Freight Forwarder",O46,O46+P46-1)</f>
+        <f t="shared" si="24"/>
         <v>14</v>
       </c>
       <c r="R46" s="23">
@@ -9480,34 +9480,33 @@
         <v>13</v>
       </c>
       <c r="T46" s="23">
-        <f>+R46+S46-1</f>
+        <f t="shared" si="25"/>
         <v>21</v>
       </c>
       <c r="U46" s="23">
-        <f>+T46+1</f>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="V46" s="23">
         <v>7</v>
       </c>
       <c r="W46" s="23">
-        <f>+U46+V46-1</f>
+        <f t="shared" si="26"/>
         <v>28</v>
       </c>
       <c r="X46" s="23">
         <v>1</v>
       </c>
       <c r="Y46" s="3">
-        <f>+ROUNDDOWN(W46/7,0)*7+X46</f>
+        <f t="shared" si="18"/>
         <v>29</v>
       </c>
       <c r="Z46" s="6">
-        <f>+Y46+X46-1</f>
+        <f t="shared" ref="Z46:Z53" si="36">+Y46+X46-1</f>
         <v>29</v>
       </c>
       <c r="AA46" s="6">
-        <f>+Z46+AB46-1</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AB46" s="23">
         <v>4</v>
@@ -9518,59 +9517,59 @@
         <v>40</v>
       </c>
       <c r="AF46" s="23">
-        <f>+AE46+AA46-1</f>
-        <v>71</v>
+        <f t="shared" si="27"/>
+        <v>70</v>
       </c>
       <c r="AG46" s="23">
         <v>3</v>
       </c>
       <c r="AH46" s="23">
-        <f>+AF46+AG46</f>
-        <v>74</v>
+        <f t="shared" si="28"/>
+        <v>73</v>
       </c>
       <c r="AI46" s="23">
         <v>7</v>
       </c>
       <c r="AJ46" s="23">
-        <f>+AI46+AH46</f>
-        <v>81</v>
+        <f t="shared" si="29"/>
+        <v>80</v>
       </c>
       <c r="AK46" s="23"/>
       <c r="AL46" s="23">
         <v>3</v>
       </c>
       <c r="AM46" s="23">
-        <f>+AJ46+AL46</f>
-        <v>84</v>
+        <f t="shared" si="30"/>
+        <v>83</v>
       </c>
       <c r="AN46" s="23">
         <v>2</v>
       </c>
       <c r="AO46" s="23">
-        <f>+AM46+AN46</f>
-        <v>86</v>
+        <f t="shared" si="31"/>
+        <v>85</v>
       </c>
       <c r="AP46" s="23">
         <v>2</v>
       </c>
       <c r="AQ46" s="23">
-        <f>+AO46+AP46</f>
-        <v>88</v>
+        <f t="shared" si="32"/>
+        <v>87</v>
       </c>
       <c r="AR46" s="23">
-        <f>+AQ46+7</f>
-        <v>95</v>
+        <f t="shared" si="33"/>
+        <v>94</v>
       </c>
       <c r="AS46" s="23">
-        <f>+AR46+7+AT46</f>
-        <v>116</v>
+        <f t="shared" si="34"/>
+        <v>115</v>
       </c>
       <c r="AT46" s="23">
         <v>14</v>
       </c>
       <c r="AU46" s="3">
-        <f>+AA46-R46</f>
-        <v>23</v>
+        <f t="shared" si="35"/>
+        <v>22</v>
       </c>
       <c r="AV46" s="23" t="s">
         <v>134</v>
@@ -9585,7 +9584,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>142</v>
       </c>
@@ -9623,21 +9622,21 @@
         <v>5</v>
       </c>
       <c r="M47" s="3">
-        <f>+IF(I47="SFK Freight Forwarder",L47,9)</f>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="N47" s="23">
         <v>2</v>
       </c>
       <c r="O47" s="3">
-        <f>IF(I47="SFK Freight Forwarder",M47,M47+N47-1)</f>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="P47" s="3">
         <v>5</v>
       </c>
       <c r="Q47" s="3">
-        <f>+IF(I47="SFK Freight Forwarder",O47,O47+P47-1)</f>
+        <f t="shared" si="24"/>
         <v>14</v>
       </c>
       <c r="R47" s="23">
@@ -9647,7 +9646,7 @@
         <v>13</v>
       </c>
       <c r="T47" s="25">
-        <f>+R47+S47-1</f>
+        <f t="shared" si="25"/>
         <v>21</v>
       </c>
       <c r="U47" s="23">
@@ -9657,22 +9656,22 @@
         <v>7</v>
       </c>
       <c r="W47" s="23">
-        <f>+U47+V47-1</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="X47" s="23">
         <v>1</v>
       </c>
       <c r="Y47" s="3">
-        <f>+ROUNDDOWN(W47/7,0)*7+X47</f>
+        <f t="shared" si="18"/>
         <v>22</v>
       </c>
       <c r="Z47" s="6">
-        <f>+Y47+X47-1</f>
+        <f t="shared" si="36"/>
         <v>22</v>
       </c>
       <c r="AA47" s="6">
-        <f>+Z47+AB47-1</f>
+        <f t="shared" si="19"/>
         <v>25</v>
       </c>
       <c r="AB47" s="23">
@@ -9684,21 +9683,21 @@
         <v>39</v>
       </c>
       <c r="AF47" s="23">
-        <f>+AE47+AA47-1</f>
+        <f t="shared" si="27"/>
         <v>63</v>
       </c>
       <c r="AG47" s="23">
         <v>3</v>
       </c>
       <c r="AH47" s="23">
-        <f>+AF47+AG47</f>
+        <f t="shared" si="28"/>
         <v>66</v>
       </c>
       <c r="AI47" s="23">
         <v>7</v>
       </c>
       <c r="AJ47" s="23">
-        <f>+AI47+AH47</f>
+        <f t="shared" si="29"/>
         <v>73</v>
       </c>
       <c r="AK47" s="23"/>
@@ -9706,36 +9705,36 @@
         <v>3</v>
       </c>
       <c r="AM47" s="23">
-        <f>+AJ47+AL47</f>
+        <f t="shared" si="30"/>
         <v>76</v>
       </c>
       <c r="AN47" s="23">
         <v>2</v>
       </c>
       <c r="AO47" s="23">
-        <f>+AM47+AN47</f>
+        <f t="shared" si="31"/>
         <v>78</v>
       </c>
       <c r="AP47" s="23">
         <v>2</v>
       </c>
       <c r="AQ47" s="23">
-        <f>+AO47+AP47</f>
+        <f t="shared" si="32"/>
         <v>80</v>
       </c>
       <c r="AR47" s="23">
-        <f>+AQ47+7</f>
+        <f t="shared" si="33"/>
         <v>87</v>
       </c>
       <c r="AS47" s="23">
-        <f>+AR47+7+AT47</f>
+        <f t="shared" si="34"/>
         <v>108</v>
       </c>
       <c r="AT47" s="23">
         <v>14</v>
       </c>
       <c r="AU47" s="3">
-        <f>+AA47-R47</f>
+        <f t="shared" si="35"/>
         <v>16</v>
       </c>
       <c r="AV47" s="23" t="s">
@@ -9751,7 +9750,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>145</v>
       </c>
@@ -9789,59 +9788,59 @@
         <v>7</v>
       </c>
       <c r="M48" s="3">
-        <f>+IF(I48="SFK Freight Forwarder",L48,9)</f>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="N48" s="3">
         <v>14</v>
       </c>
       <c r="O48" s="3">
-        <f>IF(I48="SFK Freight Forwarder",M48,M48+N48-1)</f>
+        <f t="shared" si="23"/>
         <v>22</v>
       </c>
       <c r="P48" s="3">
-        <f>+IF(I48="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P48:P53" si="37">+IF(I48="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q48" s="3">
-        <f>+IF(I48="SFK Freight Forwarder",O48,O48+P48-1)</f>
+        <f t="shared" si="24"/>
         <v>26</v>
       </c>
       <c r="R48" s="3">
-        <f>9+N48</f>
+        <f t="shared" ref="R48:R53" si="38">9+N48</f>
         <v>23</v>
       </c>
       <c r="S48" s="3">
         <v>7</v>
       </c>
       <c r="T48" s="3">
-        <f>+R48+S48-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U48" s="3">
-        <f>+T48+1</f>
+        <f t="shared" ref="U48:U53" si="39">+T48+1</f>
         <v>30</v>
       </c>
       <c r="V48" s="3">
         <v>2</v>
       </c>
       <c r="W48" s="3">
-        <f>+U48+V48-1</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="X48" s="3">
         <v>3</v>
       </c>
       <c r="Y48" s="3">
-        <f>+ROUNDDOWN(W48/7,0)*7+X48</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z48" s="6">
-        <f>+Y48+X48-1</f>
+        <f t="shared" si="36"/>
         <v>33</v>
       </c>
       <c r="AA48" s="6">
-        <f>+Z48+AB48-1</f>
+        <f t="shared" si="19"/>
         <v>34</v>
       </c>
       <c r="AB48" s="3">
@@ -9857,21 +9856,21 @@
         <v>40</v>
       </c>
       <c r="AF48" s="3">
-        <f>+AE48+AA48-1</f>
+        <f t="shared" si="27"/>
         <v>73</v>
       </c>
       <c r="AG48" s="6">
         <v>3</v>
       </c>
       <c r="AH48" s="6">
-        <f>+AF48+AG48</f>
+        <f t="shared" si="28"/>
         <v>76</v>
       </c>
       <c r="AI48" s="3">
         <v>0</v>
       </c>
       <c r="AJ48" s="3">
-        <f>+AI48+AH48</f>
+        <f t="shared" si="29"/>
         <v>76</v>
       </c>
       <c r="AK48" s="3" t="s">
@@ -9881,36 +9880,36 @@
         <v>2</v>
       </c>
       <c r="AM48" s="3">
-        <f>+AJ48+AL48</f>
+        <f t="shared" si="30"/>
         <v>78</v>
       </c>
       <c r="AN48" s="3">
         <v>2</v>
       </c>
       <c r="AO48" s="3">
-        <f>+AM48+AN48</f>
+        <f t="shared" si="31"/>
         <v>80</v>
       </c>
       <c r="AP48" s="3">
         <v>6</v>
       </c>
       <c r="AQ48" s="3">
-        <f>+AO48+AP48</f>
+        <f t="shared" si="32"/>
         <v>86</v>
       </c>
       <c r="AR48" s="3">
-        <f>+AQ48+7</f>
+        <f t="shared" si="33"/>
         <v>93</v>
       </c>
       <c r="AS48" s="3">
-        <f>+AR48+7+AT48</f>
+        <f t="shared" si="34"/>
         <v>100</v>
       </c>
       <c r="AT48" s="3">
         <v>0</v>
       </c>
       <c r="AU48" s="3">
-        <f>+AA48-R48</f>
+        <f t="shared" si="35"/>
         <v>11</v>
       </c>
       <c r="AV48" s="3" t="s">
@@ -9926,7 +9925,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>146</v>
       </c>
@@ -9964,59 +9963,59 @@
         <v>7</v>
       </c>
       <c r="M49" s="3">
-        <f>+IF(I49="SFK Freight Forwarder",L49,9)</f>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="N49" s="3">
         <v>14</v>
       </c>
       <c r="O49" s="3">
-        <f>IF(I49="SFK Freight Forwarder",M49,M49+N49-1)</f>
+        <f t="shared" si="23"/>
         <v>22</v>
       </c>
       <c r="P49" s="3">
-        <f>+IF(I49="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="37"/>
         <v>5</v>
       </c>
       <c r="Q49" s="3">
-        <f>+IF(I49="SFK Freight Forwarder",O49,O49+P49-1)</f>
+        <f t="shared" si="24"/>
         <v>26</v>
       </c>
       <c r="R49" s="3">
-        <f>9+N49</f>
+        <f t="shared" si="38"/>
         <v>23</v>
       </c>
       <c r="S49" s="3">
         <v>7</v>
       </c>
       <c r="T49" s="3">
-        <f>+R49+S49-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U49" s="3">
-        <f>+T49+1</f>
+        <f t="shared" si="39"/>
         <v>30</v>
       </c>
       <c r="V49" s="3">
         <v>2</v>
       </c>
       <c r="W49" s="3">
-        <f>+U49+V49-1</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="X49" s="3">
         <v>2</v>
       </c>
       <c r="Y49" s="3">
-        <f>+ROUNDDOWN(W49/7,0)*7+X49</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="Z49" s="6">
-        <f>+Y49+X49-1</f>
+        <f t="shared" si="36"/>
         <v>31</v>
       </c>
       <c r="AA49" s="6">
-        <f>+Z49+AB49-1</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AB49" s="3">
@@ -10032,21 +10031,21 @@
         <v>58</v>
       </c>
       <c r="AF49" s="3">
-        <f>+AE49+AA49-1</f>
+        <f t="shared" si="27"/>
         <v>88</v>
       </c>
       <c r="AG49" s="6">
         <v>3</v>
       </c>
       <c r="AH49" s="6">
-        <f>+AF49+AG49</f>
+        <f t="shared" si="28"/>
         <v>91</v>
       </c>
       <c r="AI49" s="3">
         <v>0</v>
       </c>
       <c r="AJ49" s="3">
-        <f>+AI49+AH49</f>
+        <f t="shared" si="29"/>
         <v>91</v>
       </c>
       <c r="AK49" s="3" t="s">
@@ -10056,36 +10055,36 @@
         <v>2</v>
       </c>
       <c r="AM49" s="3">
-        <f>+AJ49+AL49</f>
+        <f t="shared" si="30"/>
         <v>93</v>
       </c>
       <c r="AN49" s="3">
         <v>7</v>
       </c>
       <c r="AO49" s="3">
-        <f>+AM49+AN49</f>
+        <f t="shared" si="31"/>
         <v>100</v>
       </c>
       <c r="AP49" s="3">
         <v>5</v>
       </c>
       <c r="AQ49" s="3">
-        <f>+AO49+AP49</f>
+        <f t="shared" si="32"/>
         <v>105</v>
       </c>
       <c r="AR49" s="3">
-        <f>+AQ49+7</f>
+        <f t="shared" si="33"/>
         <v>112</v>
       </c>
       <c r="AS49" s="3">
-        <f>+AR49+7+AT49</f>
+        <f t="shared" si="34"/>
         <v>119</v>
       </c>
       <c r="AT49" s="3">
         <v>0</v>
       </c>
       <c r="AU49" s="3">
-        <f>+AA49-R49</f>
+        <f t="shared" si="35"/>
         <v>8</v>
       </c>
       <c r="AV49" s="3" t="s">
@@ -10101,7 +10100,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>147</v>
       </c>
@@ -10139,59 +10138,59 @@
         <v>7</v>
       </c>
       <c r="M50" s="3">
-        <f>+IF(I50="SFK Freight Forwarder",L50,9)</f>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="N50" s="3">
         <v>14</v>
       </c>
       <c r="O50" s="3">
-        <f>IF(I50="SFK Freight Forwarder",M50,M50+N50-1)</f>
+        <f t="shared" si="23"/>
         <v>22</v>
       </c>
       <c r="P50" s="3">
-        <f>+IF(I50="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="37"/>
         <v>5</v>
       </c>
       <c r="Q50" s="3">
-        <f>+IF(I50="SFK Freight Forwarder",O50,O50+P50-1)</f>
+        <f t="shared" si="24"/>
         <v>26</v>
       </c>
       <c r="R50" s="3">
-        <f>9+N50</f>
+        <f t="shared" si="38"/>
         <v>23</v>
       </c>
       <c r="S50" s="3">
         <v>7</v>
       </c>
       <c r="T50" s="3">
-        <f>+R50+S50-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U50" s="3">
-        <f>+T50+1</f>
+        <f t="shared" si="39"/>
         <v>30</v>
       </c>
       <c r="V50" s="3">
         <v>2</v>
       </c>
       <c r="W50" s="3">
-        <f>+U50+V50-1</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="X50" s="3">
         <v>2</v>
       </c>
       <c r="Y50" s="3">
-        <f>+ROUNDDOWN(W50/7,0)*7+X50</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="Z50" s="6">
-        <f>+Y50+X50-1</f>
+        <f t="shared" si="36"/>
         <v>31</v>
       </c>
       <c r="AA50" s="6">
-        <f>+Z50+AB50-1</f>
+        <f t="shared" si="19"/>
         <v>36</v>
       </c>
       <c r="AB50" s="3">
@@ -10207,21 +10206,21 @@
         <v>42</v>
       </c>
       <c r="AF50" s="3">
-        <f>+AE50+AA50-1</f>
+        <f t="shared" si="27"/>
         <v>77</v>
       </c>
       <c r="AG50" s="6">
         <v>3</v>
       </c>
       <c r="AH50" s="6">
-        <f>+AF50+AG50</f>
+        <f t="shared" si="28"/>
         <v>80</v>
       </c>
       <c r="AI50" s="3">
         <v>0</v>
       </c>
       <c r="AJ50" s="3">
-        <f>+AI50+AH50</f>
+        <f t="shared" si="29"/>
         <v>80</v>
       </c>
       <c r="AK50" s="3" t="s">
@@ -10231,36 +10230,36 @@
         <v>1</v>
       </c>
       <c r="AM50" s="3">
-        <f>+AJ50+AL50</f>
+        <f t="shared" si="30"/>
         <v>81</v>
       </c>
       <c r="AN50" s="3">
         <v>1</v>
       </c>
       <c r="AO50" s="3">
-        <f>+AM50+AN50</f>
+        <f t="shared" si="31"/>
         <v>82</v>
       </c>
       <c r="AP50" s="3">
         <v>3</v>
       </c>
       <c r="AQ50" s="3">
-        <f>+AO50+AP50</f>
+        <f t="shared" si="32"/>
         <v>85</v>
       </c>
       <c r="AR50" s="3">
-        <f>+AQ50+7</f>
+        <f t="shared" si="33"/>
         <v>92</v>
       </c>
       <c r="AS50" s="3">
-        <f>+AR50+7+AT50</f>
+        <f t="shared" si="34"/>
         <v>99</v>
       </c>
       <c r="AT50" s="3">
         <v>0</v>
       </c>
       <c r="AU50" s="3">
-        <f>+AA50-R50</f>
+        <f t="shared" si="35"/>
         <v>13</v>
       </c>
       <c r="AV50" s="3" t="s">
@@ -10276,7 +10275,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>148</v>
       </c>
@@ -10314,59 +10313,59 @@
         <v>7</v>
       </c>
       <c r="M51" s="3">
-        <f>+IF(I51="SFK Freight Forwarder",L51,9)</f>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="N51" s="3">
         <v>14</v>
       </c>
       <c r="O51" s="3">
-        <f>IF(I51="SFK Freight Forwarder",M51,M51+N51-1)</f>
+        <f t="shared" si="23"/>
         <v>22</v>
       </c>
       <c r="P51" s="3">
-        <f>+IF(I51="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="37"/>
         <v>5</v>
       </c>
       <c r="Q51" s="3">
-        <f>+IF(I51="SFK Freight Forwarder",O51,O51+P51-1)</f>
+        <f t="shared" si="24"/>
         <v>26</v>
       </c>
       <c r="R51" s="3">
-        <f>9+N51</f>
+        <f t="shared" si="38"/>
         <v>23</v>
       </c>
       <c r="S51" s="3">
         <v>7</v>
       </c>
       <c r="T51" s="3">
-        <f>+R51+S51-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U51" s="3">
-        <f>+T51+1</f>
+        <f t="shared" si="39"/>
         <v>30</v>
       </c>
       <c r="V51" s="3">
         <v>2</v>
       </c>
       <c r="W51" s="3">
-        <f>+U51+V51-1</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="X51" s="3">
         <v>2</v>
       </c>
       <c r="Y51" s="3">
-        <f>+ROUNDDOWN(W51/7,0)*7+X51</f>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="Z51" s="6">
-        <f>+Y51+X51-1</f>
+        <f t="shared" si="36"/>
         <v>31</v>
       </c>
       <c r="AA51" s="6">
-        <f>+Z51+AB51-1</f>
+        <f t="shared" si="19"/>
         <v>34</v>
       </c>
       <c r="AB51" s="3">
@@ -10382,21 +10381,21 @@
         <v>48</v>
       </c>
       <c r="AF51" s="3">
-        <f>+AE51+AA51-1</f>
+        <f t="shared" si="27"/>
         <v>81</v>
       </c>
       <c r="AG51" s="6">
         <v>0</v>
       </c>
       <c r="AH51" s="6">
-        <f>+AF51+AG51</f>
+        <f t="shared" si="28"/>
         <v>81</v>
       </c>
       <c r="AI51" s="3">
         <v>0</v>
       </c>
       <c r="AJ51" s="3">
-        <f>+AI51+AH51</f>
+        <f t="shared" si="29"/>
         <v>81</v>
       </c>
       <c r="AK51" s="3" t="s">
@@ -10406,36 +10405,36 @@
         <v>3</v>
       </c>
       <c r="AM51" s="3">
-        <f>+AJ51+AL51</f>
+        <f t="shared" si="30"/>
         <v>84</v>
       </c>
       <c r="AN51" s="3">
         <v>8</v>
       </c>
       <c r="AO51" s="3">
-        <f>+AM51+AN51</f>
+        <f t="shared" si="31"/>
         <v>92</v>
       </c>
       <c r="AP51" s="3">
         <v>0</v>
       </c>
       <c r="AQ51" s="3">
-        <f>+AO51+AP51</f>
+        <f t="shared" si="32"/>
         <v>92</v>
       </c>
       <c r="AR51" s="3">
-        <f>+AQ51+7</f>
+        <f t="shared" si="33"/>
         <v>99</v>
       </c>
       <c r="AS51" s="3">
-        <f>+AR51+7+AT51</f>
+        <f t="shared" si="34"/>
         <v>106</v>
       </c>
       <c r="AT51" s="3">
         <v>0</v>
       </c>
       <c r="AU51" s="3">
-        <f>+AA51-R51</f>
+        <f t="shared" si="35"/>
         <v>11</v>
       </c>
       <c r="AV51" s="3" t="s">
@@ -10451,7 +10450,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="52" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>149</v>
       </c>
@@ -10489,59 +10488,59 @@
         <v>2</v>
       </c>
       <c r="M52" s="3">
-        <f>+IF(I52="SFK Freight Forwarder",L52,9)</f>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="N52" s="3">
         <v>14</v>
       </c>
       <c r="O52" s="3">
-        <f>IF(I52="SFK Freight Forwarder",M52,M52+N52-1)</f>
+        <f t="shared" si="23"/>
         <v>22</v>
       </c>
       <c r="P52" s="3">
-        <f>+IF(I52="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="37"/>
         <v>5</v>
       </c>
       <c r="Q52" s="3">
-        <f>+IF(I52="SFK Freight Forwarder",O52,O52+P52-1)</f>
+        <f t="shared" si="24"/>
         <v>26</v>
       </c>
       <c r="R52" s="3">
-        <f>9+N52</f>
+        <f t="shared" si="38"/>
         <v>23</v>
       </c>
       <c r="S52" s="3">
         <v>7</v>
       </c>
       <c r="T52" s="3">
-        <f>+R52+S52-1</f>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U52" s="3">
-        <f>+T52+1</f>
+        <f t="shared" si="39"/>
         <v>30</v>
       </c>
       <c r="V52" s="3">
         <v>2</v>
       </c>
       <c r="W52" s="3">
-        <f>+U52+V52-1</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="X52" s="3">
         <v>3</v>
       </c>
       <c r="Y52" s="3">
-        <f>+ROUNDDOWN(W52/7,0)*7+X52</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z52" s="6">
-        <f>+Y52+X52-1</f>
+        <f t="shared" si="36"/>
         <v>33</v>
       </c>
       <c r="AA52" s="6">
-        <f>+Z52+AB52-1</f>
+        <f t="shared" si="19"/>
         <v>34</v>
       </c>
       <c r="AB52" s="3">
@@ -10557,21 +10556,21 @@
         <v>50</v>
       </c>
       <c r="AF52" s="3">
-        <f>+AE52+AA52-1</f>
+        <f t="shared" si="27"/>
         <v>83</v>
       </c>
       <c r="AG52" s="6">
         <v>3</v>
       </c>
       <c r="AH52" s="6">
-        <f>+AF52+AG52</f>
+        <f t="shared" si="28"/>
         <v>86</v>
       </c>
       <c r="AI52" s="3">
         <v>0</v>
       </c>
       <c r="AJ52" s="3">
-        <f>+AI52+AH52</f>
+        <f t="shared" si="29"/>
         <v>86</v>
       </c>
       <c r="AK52" s="3" t="s">
@@ -10581,36 +10580,36 @@
         <v>4</v>
       </c>
       <c r="AM52" s="3">
-        <f>+AJ52+AL52</f>
+        <f t="shared" si="30"/>
         <v>90</v>
       </c>
       <c r="AN52" s="3">
         <v>2</v>
       </c>
       <c r="AO52" s="3">
-        <f>+AM52+AN52</f>
+        <f t="shared" si="31"/>
         <v>92</v>
       </c>
       <c r="AP52" s="3">
         <v>1</v>
       </c>
       <c r="AQ52" s="3">
-        <f>+AO52+AP52</f>
+        <f t="shared" si="32"/>
         <v>93</v>
       </c>
       <c r="AR52" s="3">
-        <f>+AQ52+7</f>
+        <f t="shared" si="33"/>
         <v>100</v>
       </c>
       <c r="AS52" s="3">
-        <f>+AR52+7+AT52</f>
+        <f t="shared" si="34"/>
         <v>107</v>
       </c>
       <c r="AT52" s="3">
         <v>0</v>
       </c>
       <c r="AU52" s="3">
-        <f>+AA52-R52</f>
+        <f t="shared" si="35"/>
         <v>11</v>
       </c>
       <c r="AV52" s="3" t="s">
@@ -10626,7 +10625,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="53" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>154</v>
       </c>
@@ -10664,59 +10663,59 @@
         <v>7</v>
       </c>
       <c r="M53" s="3">
-        <f>+IF(I53="SFK Freight Forwarder",L53,9)</f>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="N53" s="3">
         <v>7</v>
       </c>
       <c r="O53" s="3">
-        <f>IF(I53="SFK Freight Forwarder",M53,M53+N53-1)</f>
+        <f t="shared" si="23"/>
         <v>15</v>
       </c>
       <c r="P53" s="3">
-        <f>+IF(I53="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="37"/>
         <v>5</v>
       </c>
       <c r="Q53" s="3">
-        <f>+IF(I53="SFK Freight Forwarder",O53,O53+P53-1)</f>
+        <f t="shared" si="24"/>
         <v>19</v>
       </c>
       <c r="R53" s="3">
-        <f>9+N53</f>
+        <f t="shared" si="38"/>
         <v>16</v>
       </c>
       <c r="S53" s="3">
         <v>3</v>
       </c>
       <c r="T53" s="3">
-        <f>+R53+S53-1</f>
+        <f t="shared" si="25"/>
         <v>18</v>
       </c>
       <c r="U53" s="3">
-        <f>+T53+1</f>
+        <f t="shared" si="39"/>
         <v>19</v>
       </c>
       <c r="V53" s="3">
         <v>5</v>
       </c>
       <c r="W53" s="3">
-        <f>+U53+V53-1</f>
+        <f t="shared" si="26"/>
         <v>23</v>
       </c>
       <c r="X53" s="3">
         <v>2</v>
       </c>
       <c r="Y53" s="3">
-        <f>+ROUNDDOWN(W53/7,0)*7+X53</f>
+        <f t="shared" si="18"/>
         <v>23</v>
       </c>
       <c r="Z53" s="6">
-        <f>+Y53+X53-1</f>
+        <f t="shared" si="36"/>
         <v>24</v>
       </c>
       <c r="AA53" s="6">
-        <f>+Z53+AB53-1</f>
+        <f t="shared" si="19"/>
         <v>26</v>
       </c>
       <c r="AB53" s="3">
@@ -10732,21 +10731,21 @@
         <v>34</v>
       </c>
       <c r="AF53" s="3">
-        <f>+AE53+AA53-1</f>
+        <f t="shared" si="27"/>
         <v>59</v>
       </c>
       <c r="AG53" s="6">
         <v>3</v>
       </c>
       <c r="AH53" s="6">
-        <f>+AF53+AG53</f>
+        <f t="shared" si="28"/>
         <v>62</v>
       </c>
       <c r="AI53" s="3">
         <v>7</v>
       </c>
       <c r="AJ53" s="3">
-        <f>+AI53+AH53</f>
+        <f t="shared" si="29"/>
         <v>69</v>
       </c>
       <c r="AK53" s="3">
@@ -10756,36 +10755,36 @@
         <v>6</v>
       </c>
       <c r="AM53" s="3">
-        <f>+AJ53+AL53</f>
+        <f t="shared" si="30"/>
         <v>75</v>
       </c>
       <c r="AN53" s="3">
         <v>2</v>
       </c>
       <c r="AO53" s="3">
-        <f>+AM53+AN53</f>
+        <f t="shared" si="31"/>
         <v>77</v>
       </c>
       <c r="AP53" s="3">
         <v>0</v>
       </c>
       <c r="AQ53" s="3">
-        <f>+AO53+AP53</f>
+        <f t="shared" si="32"/>
         <v>77</v>
       </c>
       <c r="AR53" s="3">
-        <f>+AQ53+7</f>
+        <f t="shared" si="33"/>
         <v>84</v>
       </c>
       <c r="AS53" s="3">
-        <f>+AR53+7+AT53</f>
+        <f t="shared" si="34"/>
         <v>91</v>
       </c>
       <c r="AT53" s="3">
         <v>0</v>
       </c>
       <c r="AU53" s="3">
-        <f>+AA53-R53</f>
+        <f t="shared" si="35"/>
         <v>10</v>
       </c>
       <c r="AV53" s="3" t="s">
@@ -10803,7 +10802,13 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
+  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="INFIMOTION"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K16:K1048196 C16:E1048196 K2:K12 C2:E12" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D8FA55-00D3-49FB-BC7F-CC936D077B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05D4012-0B3E-452D-A88C-57561EF47EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="19090" yWindow="-1340" windowWidth="19420" windowHeight="11500" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -1551,13 +1551,13 @@
     <col min="2" max="2" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="15.5703125" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="15.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="28" width="10.42578125" customWidth="1"/>
@@ -7359,14 +7359,14 @@
         <v>7</v>
       </c>
       <c r="M34" s="3">
-        <f t="shared" ref="M34:M65" si="22">+IF(I34="SFK Freight Forwarder",L34,9)</f>
+        <f t="shared" ref="M34:M53" si="22">+IF(I34="SFK Freight Forwarder",L34,9)</f>
         <v>7</v>
       </c>
       <c r="N34" s="3">
         <v>14</v>
       </c>
       <c r="O34" s="3">
-        <f t="shared" ref="O34:O65" si="23">IF(I34="SFK Freight Forwarder",M34,M34+N34-1)</f>
+        <f t="shared" ref="O34:O53" si="23">IF(I34="SFK Freight Forwarder",M34,M34+N34-1)</f>
         <v>7</v>
       </c>
       <c r="P34" s="3">
@@ -7374,7 +7374,7 @@
         <v>0</v>
       </c>
       <c r="Q34" s="3">
-        <f t="shared" ref="Q34:Q65" si="24">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
+        <f t="shared" ref="Q34:Q53" si="24">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
         <v>7</v>
       </c>
       <c r="R34" s="3">
@@ -7385,7 +7385,7 @@
         <v>7</v>
       </c>
       <c r="T34" s="3">
-        <f t="shared" ref="T34:T65" si="25">+R34+S34-1</f>
+        <f t="shared" ref="T34:T53" si="25">+R34+S34-1</f>
         <v>29</v>
       </c>
       <c r="U34" s="3">
@@ -7396,7 +7396,7 @@
         <v>1</v>
       </c>
       <c r="W34" s="3">
-        <f t="shared" ref="W34:W65" si="26">+U34+V34-1</f>
+        <f t="shared" ref="W34:W53" si="26">+U34+V34-1</f>
         <v>30</v>
       </c>
       <c r="X34" s="3">
@@ -7427,21 +7427,21 @@
         <v>60</v>
       </c>
       <c r="AF34" s="3">
-        <f t="shared" ref="AF34:AF65" si="27">+AE34+AA34-1</f>
+        <f t="shared" ref="AF34:AF53" si="27">+AE34+AA34-1</f>
         <v>93</v>
       </c>
       <c r="AG34" s="6">
         <v>3</v>
       </c>
       <c r="AH34" s="6">
-        <f t="shared" ref="AH34:AH65" si="28">+AF34+AG34</f>
+        <f t="shared" ref="AH34:AH53" si="28">+AF34+AG34</f>
         <v>96</v>
       </c>
       <c r="AI34" s="3">
         <v>0</v>
       </c>
       <c r="AJ34" s="3">
-        <f t="shared" ref="AJ34:AJ65" si="29">+AI34+AH34</f>
+        <f t="shared" ref="AJ34:AJ53" si="29">+AI34+AH34</f>
         <v>96</v>
       </c>
       <c r="AK34" s="3" t="s">
@@ -7451,29 +7451,29 @@
         <v>2</v>
       </c>
       <c r="AM34" s="3">
-        <f t="shared" ref="AM34:AM65" si="30">+AJ34+AL34</f>
+        <f t="shared" ref="AM34:AM53" si="30">+AJ34+AL34</f>
         <v>98</v>
       </c>
       <c r="AN34" s="3">
         <v>2</v>
       </c>
       <c r="AO34" s="3">
-        <f t="shared" ref="AO34:AO65" si="31">+AM34+AN34</f>
+        <f t="shared" ref="AO34:AO53" si="31">+AM34+AN34</f>
         <v>100</v>
       </c>
       <c r="AP34" s="3">
         <v>0</v>
       </c>
       <c r="AQ34" s="3">
-        <f t="shared" ref="AQ34:AQ65" si="32">+AO34+AP34</f>
+        <f t="shared" ref="AQ34:AQ53" si="32">+AO34+AP34</f>
         <v>100</v>
       </c>
       <c r="AR34" s="3">
-        <f t="shared" ref="AR34:AR65" si="33">+AQ34+7</f>
+        <f t="shared" ref="AR34:AR53" si="33">+AQ34+7</f>
         <v>107</v>
       </c>
       <c r="AS34" s="3">
-        <f t="shared" ref="AS34:AS65" si="34">+AR34+7+AT34</f>
+        <f t="shared" ref="AS34:AS53" si="34">+AR34+7+AT34</f>
         <v>127</v>
       </c>
       <c r="AT34" s="3">
@@ -9581,7 +9581,7 @@
         <v>57</v>
       </c>
       <c r="AY46" s="37">
-        <v>46143</v>
+        <v>46508</v>
       </c>
     </row>
     <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05D4012-0B3E-452D-A88C-57561EF47EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42016719-E28C-4D92-9897-093C7292BA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-1340" windowWidth="19420" windowHeight="11500" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -1551,13 +1551,13 @@
     <col min="2" max="2" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="15.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="15.5703125" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="28" width="10.42578125" customWidth="1"/>
@@ -9514,25 +9514,25 @@
       <c r="AC46" s="23"/>
       <c r="AD46" s="23"/>
       <c r="AE46" s="33">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AF46" s="23">
         <f t="shared" si="27"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AG46" s="23">
         <v>3</v>
       </c>
       <c r="AH46" s="23">
         <f t="shared" si="28"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI46" s="23">
         <v>7</v>
       </c>
       <c r="AJ46" s="23">
         <f t="shared" si="29"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK46" s="23"/>
       <c r="AL46" s="23">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="AM46" s="23">
         <f t="shared" si="30"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN46" s="23">
         <v>2</v>
       </c>
       <c r="AO46" s="23">
         <f t="shared" si="31"/>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AP46" s="23">
         <v>2</v>
       </c>
       <c r="AQ46" s="23">
         <f t="shared" si="32"/>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AR46" s="23">
         <f t="shared" si="33"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AS46" s="23">
         <f t="shared" si="34"/>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AT46" s="23">
         <v>14</v>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42016719-E28C-4D92-9897-093C7292BA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED7C35A-062F-4CB2-9A65-A3844F7896EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="18860" yWindow="-890" windowWidth="21600" windowHeight="11300" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -1551,13 +1551,13 @@
     <col min="2" max="2" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="15.5703125" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="15.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="28" width="10.42578125" customWidth="1"/>
@@ -9456,35 +9456,34 @@
         <v>5</v>
       </c>
       <c r="M46" s="3">
-        <f t="shared" si="22"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N46" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O46" s="3">
         <f t="shared" si="23"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P46" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q46" s="3">
         <f t="shared" si="24"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R46" s="23">
         <v>9</v>
       </c>
       <c r="S46" s="23">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T46" s="23">
         <f t="shared" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U46" s="23">
-        <f t="shared" si="6"/>
+        <f>+T46+2</f>
         <v>22</v>
       </c>
       <c r="V46" s="23">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED7C35A-062F-4CB2-9A65-A3844F7896EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4836CB71-1AF2-4E4E-A6D4-E64D71C60F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18860" yWindow="-890" windowWidth="21600" windowHeight="11300" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="19090" yWindow="-1340" windowWidth="19420" windowHeight="11500" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -1808,7 +1808,7 @@
         <v>22</v>
       </c>
       <c r="U2" s="3">
-        <f t="shared" ref="U2:U46" si="6">+T2+1</f>
+        <f t="shared" ref="U2:U45" si="6">+T2+1</f>
         <v>23</v>
       </c>
       <c r="V2" s="3">
@@ -9487,21 +9487,19 @@
         <v>22</v>
       </c>
       <c r="V46" s="23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W46" s="23">
         <f t="shared" si="26"/>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X46" s="23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y46" s="3">
-        <f t="shared" si="18"/>
         <v>29</v>
       </c>
       <c r="Z46" s="6">
-        <f t="shared" ref="Z46:Z53" si="36">+Y46+X46-1</f>
         <v>29</v>
       </c>
       <c r="AA46" s="6">
@@ -9542,26 +9540,25 @@
         <v>84</v>
       </c>
       <c r="AN46" s="23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO46" s="23">
-        <f t="shared" si="31"/>
-        <v>86</v>
+        <f>+AM46+AN46</f>
+        <v>89</v>
       </c>
       <c r="AP46" s="23">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AQ46" s="23">
-        <f t="shared" si="32"/>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AR46" s="23">
-        <f t="shared" si="33"/>
-        <v>95</v>
+        <f>+AQ46+4</f>
+        <v>96</v>
       </c>
       <c r="AS46" s="23">
         <f t="shared" si="34"/>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AT46" s="23">
         <v>14</v>
@@ -9666,7 +9663,7 @@
         <v>22</v>
       </c>
       <c r="Z47" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="Z46:Z53" si="36">+Y47+X47-1</f>
         <v>22</v>
       </c>
       <c r="AA47" s="6">
@@ -10802,9 +10799,9 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="10">
+    <filterColumn colId="0">
       <filters>
-        <filter val="INFIMOTION"/>
+        <filter val="O001"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4836CB71-1AF2-4E4E-A6D4-E64D71C60F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADCB057-91A1-4EB7-99C7-3C9756A39F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-1340" windowWidth="19420" windowHeight="11500" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -366,7 +366,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="171">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -876,6 +876,9 @@
   </si>
   <si>
     <t>Directos flujos confirmados</t>
+  </si>
+  <si>
+    <t>O009</t>
   </si>
 </sst>
 </file>
@@ -1544,7 +1547,7 @@
   <sheetPr codeName="Feuil4" filterMode="1">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:BF53"/>
+  <dimension ref="A1:BF54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -5752,7 +5755,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -5831,10 +5834,9 @@
         <v>30</v>
       </c>
       <c r="X25" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="3">
-        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="Z25" s="6">
@@ -9418,7 +9420,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>139</v>
       </c>
@@ -9663,7 +9665,7 @@
         <v>22</v>
       </c>
       <c r="Z47" s="6">
-        <f t="shared" ref="Z46:Z53" si="36">+Y47+X47-1</f>
+        <f t="shared" ref="Z47:Z53" si="36">+Y47+X47-1</f>
         <v>22</v>
       </c>
       <c r="AA47" s="6">
@@ -10796,21 +10798,184 @@
         <v>46142</v>
       </c>
     </row>
+    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="F54" s="19">
+        <v>90014400</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H54" s="2">
+        <v>0</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J54" s="2">
+        <v>29159</v>
+      </c>
+      <c r="K54" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="L54" s="3">
+        <v>5</v>
+      </c>
+      <c r="M54" s="3">
+        <f t="shared" ref="M54" si="40">+IF(I54="SFK Freight Forwarder",L54,9)</f>
+        <v>9</v>
+      </c>
+      <c r="N54" s="23">
+        <v>2</v>
+      </c>
+      <c r="O54" s="3">
+        <f t="shared" ref="O54" si="41">IF(I54="SFK Freight Forwarder",M54,M54+N54-1)</f>
+        <v>10</v>
+      </c>
+      <c r="P54" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q54" s="3">
+        <f t="shared" ref="Q54" si="42">+IF(I54="SFK Freight Forwarder",O54,O54+P54-1)</f>
+        <v>14</v>
+      </c>
+      <c r="R54" s="23">
+        <v>0</v>
+      </c>
+      <c r="S54" s="23">
+        <v>0</v>
+      </c>
+      <c r="T54" s="25">
+        <v>0</v>
+      </c>
+      <c r="U54" s="23">
+        <v>15</v>
+      </c>
+      <c r="V54" s="23">
+        <v>4</v>
+      </c>
+      <c r="W54" s="23">
+        <f t="shared" ref="W54" si="43">+U54+V54-1</f>
+        <v>18</v>
+      </c>
+      <c r="X54" s="23">
+        <v>1</v>
+      </c>
+      <c r="Y54" s="3">
+        <v>18</v>
+      </c>
+      <c r="Z54" s="6">
+        <v>19</v>
+      </c>
+      <c r="AA54" s="6">
+        <f t="shared" ref="AA54" si="44">+Z54+AB54-1</f>
+        <v>22</v>
+      </c>
+      <c r="AB54" s="23">
+        <v>4</v>
+      </c>
+      <c r="AC54" s="23"/>
+      <c r="AD54" s="23"/>
+      <c r="AE54" s="23">
+        <v>46</v>
+      </c>
+      <c r="AF54" s="23">
+        <f t="shared" ref="AF54" si="45">+AE54+AA54-1</f>
+        <v>67</v>
+      </c>
+      <c r="AG54" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH54" s="23">
+        <f t="shared" ref="AH54" si="46">+AF54+AG54</f>
+        <v>70</v>
+      </c>
+      <c r="AI54" s="23">
+        <v>7</v>
+      </c>
+      <c r="AJ54" s="23">
+        <f t="shared" ref="AJ54" si="47">+AI54+AH54</f>
+        <v>77</v>
+      </c>
+      <c r="AK54" s="23"/>
+      <c r="AL54" s="23">
+        <v>3</v>
+      </c>
+      <c r="AM54" s="23">
+        <f t="shared" ref="AM54" si="48">+AJ54+AL54</f>
+        <v>80</v>
+      </c>
+      <c r="AN54" s="23">
+        <v>2</v>
+      </c>
+      <c r="AO54" s="23">
+        <f t="shared" ref="AO54" si="49">+AM54+AN54</f>
+        <v>82</v>
+      </c>
+      <c r="AP54" s="23">
+        <v>2</v>
+      </c>
+      <c r="AQ54" s="23">
+        <f t="shared" ref="AQ54" si="50">+AO54+AP54</f>
+        <v>84</v>
+      </c>
+      <c r="AR54" s="23">
+        <f t="shared" ref="AR54" si="51">+AQ54+7</f>
+        <v>91</v>
+      </c>
+      <c r="AS54" s="23">
+        <f t="shared" ref="AS54" si="52">+AR54+7+AT54</f>
+        <v>112</v>
+      </c>
+      <c r="AT54" s="23">
+        <v>14</v>
+      </c>
+      <c r="AU54" s="3">
+        <f t="shared" ref="AU54" si="53">+AA54-R54</f>
+        <v>22</v>
+      </c>
+      <c r="AV54" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="AW54" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="AX54" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY54" s="37">
+        <v>46143</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
+  <autoFilter ref="A1:AY54" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
     <filterColumn colId="0">
       <filters>
-        <filter val="O001"/>
+        <filter val="927"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K16:K1048196 C16:E1048196 K2:K12 C2:E12" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 C16:E1048196 K16:K1048196" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
       <formula1>shippername</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H54:K1048196 C2:E1048196 K2:K53 J12:J53 I2:I53 J3:J10" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 K2:K54 J12:J54 I2:I54 C2:E1048196 H55:K1048196" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
       <formula1>AILNname</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048196" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADCB057-91A1-4EB7-99C7-3C9756A39F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC818A12-C9FF-4124-8DDC-E051A0BBBF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="28980" windowHeight="15585" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -1559,7 +1559,7 @@
     <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="15.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" customWidth="1"/>
@@ -1996,10 +1996,9 @@
         <v>31</v>
       </c>
       <c r="X3" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3">
-        <f>+ROUNDDOWN(W3/7,0)*7+X3</f>
         <v>33</v>
       </c>
       <c r="Z3" s="6">
@@ -2170,10 +2169,9 @@
         <v>32</v>
       </c>
       <c r="X4" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3">
-        <f>+ROUNDDOWN(W4/7,0)*7+X4</f>
         <v>33</v>
       </c>
       <c r="Z4" s="6">
@@ -4266,10 +4264,9 @@
         <v>33</v>
       </c>
       <c r="X16" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="3">
-        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z16" s="6">
@@ -4614,10 +4611,9 @@
         <v>26</v>
       </c>
       <c r="X18" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="3">
-        <f t="shared" si="18"/>
         <v>26</v>
       </c>
       <c r="Z18" s="6">
@@ -4788,10 +4784,9 @@
         <v>31</v>
       </c>
       <c r="X19" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="3">
-        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z19" s="6">
@@ -4918,7 +4913,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M20" s="3">
         <f t="shared" si="0"/>
@@ -4962,10 +4957,9 @@
         <v>31</v>
       </c>
       <c r="X20" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
-        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z20" s="6">
@@ -5232,7 +5226,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5311,14 +5305,12 @@
         <v>32</v>
       </c>
       <c r="X22" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="3">
-        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z22" s="6">
-        <f>+Y22+X22-1</f>
         <v>37</v>
       </c>
       <c r="AA22" s="6">
@@ -5660,10 +5652,9 @@
         <v>31</v>
       </c>
       <c r="X24" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <f t="shared" si="18"/>
         <v>32</v>
       </c>
       <c r="Z24" s="6">
@@ -5755,7 +5746,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -9424,13 +9415,13 @@
       <c r="A46" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B46" s="38" t="s">
+      <c r="B46" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C46" s="39" t="s">
+      <c r="C46" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D46" s="5" t="s">
         <v>137</v>
       </c>
       <c r="E46" s="32" t="s">
@@ -10112,7 +10103,7 @@
         <v>100</v>
       </c>
       <c r="E50" s="38" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="F50" s="19">
         <v>91017500</v>
@@ -10966,7 +10957,7 @@
   <autoFilter ref="A1:AY54" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
     <filterColumn colId="0">
       <filters>
-        <filter val="927"/>
+        <filter val="921"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC818A12-C9FF-4124-8DDC-E051A0BBBF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B08539-604C-451E-8BFD-100524CF3B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="28980" windowHeight="15585" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-60" yWindow="0" windowWidth="28935" windowHeight="15585" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -366,7 +366,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="172">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -500,9 +500,6 @@
     <t>TANGER</t>
   </si>
   <si>
-    <t>DACIA MONT</t>
-  </si>
-  <si>
     <t>REVOZ</t>
   </si>
   <si>
@@ -879,6 +876,12 @@
   </si>
   <si>
     <t>O009</t>
+  </si>
+  <si>
+    <t>INKAT</t>
+  </si>
+  <si>
+    <t>MAERSK</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1092,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1207,6 +1210,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1547,7 +1553,7 @@
   <sheetPr codeName="Feuil4" filterMode="1">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:BF54"/>
+  <dimension ref="A1:BF53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -1581,7 +1587,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C1" s="31" t="s">
         <v>6</v>
@@ -1596,70 +1602,70 @@
         <v>0</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J1" s="12" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="L1" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="M1" s="13" t="s">
         <v>103</v>
-      </c>
-      <c r="M1" s="13" t="s">
-        <v>104</v>
       </c>
       <c r="N1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="O1" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="R1" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="T1" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="U1" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="W1" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="X1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y1" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="P1" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="R1" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="S1" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="T1" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="U1" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="V1" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="W1" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="X1" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y1" s="16" t="s">
+      <c r="Z1" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="Z1" s="30" t="s">
+      <c r="AA1" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="AA1" s="16" t="s">
-        <v>108</v>
-      </c>
       <c r="AB1" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AC1" s="24" t="s">
         <v>8</v>
@@ -1671,19 +1677,19 @@
         <v>10</v>
       </c>
       <c r="AF1" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG1" s="11" t="s">
         <v>12</v>
       </c>
       <c r="AH1" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AI1" s="11" t="s">
         <v>13</v>
       </c>
       <c r="AJ1" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK1" s="29" t="s">
         <v>14</v>
@@ -1692,37 +1698,37 @@
         <v>15</v>
       </c>
       <c r="AM1" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AN1" s="11" t="s">
         <v>16</v>
       </c>
       <c r="AO1" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AP1" s="11" t="s">
         <v>17</v>
       </c>
       <c r="AQ1" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="AR1" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="AR1" s="11" t="s">
+      <c r="AS1" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="AS1" s="11" t="s">
+      <c r="AT1" s="17" t="s">
         <v>116</v>
-      </c>
-      <c r="AT1" s="17" t="s">
-        <v>117</v>
       </c>
       <c r="AU1" s="17" t="s">
         <v>18</v>
       </c>
       <c r="AV1" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AW1" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AX1" s="11" t="s">
         <v>19</v>
@@ -1740,7 +1746,7 @@
         <v>63</v>
       </c>
       <c r="BF1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
@@ -1748,47 +1754,47 @@
         <v>60</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2" s="19">
         <v>90009500</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H2" s="2">
         <v>92000100</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J2" s="2">
         <v>92000100</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L2" s="3">
         <v>7</v>
       </c>
       <c r="M2" s="3">
-        <f t="shared" ref="M2:M33" si="0">+IF(I2="SFK Freight Forwarder",L2,9)</f>
+        <f t="shared" ref="M2:M29" si="0">+IF(I2="SFK Freight Forwarder",L2,9)</f>
         <v>9</v>
       </c>
       <c r="N2" s="3">
         <v>7</v>
       </c>
       <c r="O2" s="3">
-        <f t="shared" ref="O2:O33" si="1">IF(I2="SFK Freight Forwarder",M2,M2+N2-1)</f>
+        <f t="shared" ref="O2:O32" si="1">IF(I2="SFK Freight Forwarder",M2,M2+N2-1)</f>
         <v>15</v>
       </c>
       <c r="P2" s="3">
@@ -1796,36 +1802,35 @@
         <v>5</v>
       </c>
       <c r="Q2" s="3">
-        <f t="shared" ref="Q2:Q33" si="3">+IF(I2="SFK Freight Forwarder",O2,O2+P2-1)</f>
+        <f t="shared" ref="Q2:Q32" si="3">+IF(I2="SFK Freight Forwarder",O2,O2+P2-1)</f>
         <v>19</v>
       </c>
       <c r="R2" s="3">
-        <f t="shared" ref="R2:R45" si="4">9+N2</f>
+        <f t="shared" ref="R2:R44" si="4">9+N2</f>
         <v>16</v>
       </c>
       <c r="S2" s="3">
         <v>7</v>
       </c>
       <c r="T2" s="3">
-        <f t="shared" ref="T2:T33" si="5">+R2+S2-1</f>
+        <f t="shared" ref="T2:T32" si="5">+R2+S2-1</f>
         <v>22</v>
       </c>
       <c r="U2" s="3">
-        <f t="shared" ref="U2:U45" si="6">+T2+1</f>
+        <f t="shared" ref="U2:U44" si="6">+T2+1</f>
         <v>23</v>
       </c>
       <c r="V2" s="3">
         <v>1</v>
       </c>
       <c r="W2" s="3">
-        <f t="shared" ref="W2:W33" si="7">+U2+V2-1</f>
+        <f t="shared" ref="W2:W32" si="7">+U2+V2-1</f>
         <v>23</v>
       </c>
       <c r="X2" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3">
-        <f>+ROUNDDOWN(W2/7,0)*7+X2</f>
         <v>25</v>
       </c>
       <c r="Z2" s="6">
@@ -1848,70 +1853,70 @@
         <v>46</v>
       </c>
       <c r="AF2" s="3">
-        <f t="shared" ref="AF2:AF33" si="9">+AE2+AA2-1</f>
+        <f t="shared" ref="AF2:AF32" si="9">+AE2+AA2-1</f>
         <v>72</v>
       </c>
       <c r="AG2" s="6">
         <v>3</v>
       </c>
       <c r="AH2" s="6">
-        <f t="shared" ref="AH2:AH33" si="10">+AF2+AG2</f>
+        <f t="shared" ref="AH2:AH32" si="10">+AF2+AG2</f>
         <v>75</v>
       </c>
       <c r="AI2" s="3">
         <v>7</v>
       </c>
       <c r="AJ2" s="3">
-        <f t="shared" ref="AJ2:AJ33" si="11">+AI2+AH2</f>
+        <f t="shared" ref="AJ2:AJ32" si="11">+AI2+AH2</f>
         <v>82</v>
       </c>
       <c r="AK2" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL2" s="3">
         <v>2</v>
       </c>
       <c r="AM2" s="3">
-        <f t="shared" ref="AM2:AM33" si="12">+AJ2+AL2</f>
+        <f t="shared" ref="AM2:AM32" si="12">+AJ2+AL2</f>
         <v>84</v>
       </c>
       <c r="AN2" s="3">
         <v>2</v>
       </c>
       <c r="AO2" s="3">
-        <f t="shared" ref="AO2:AO33" si="13">+AM2+AN2</f>
+        <f t="shared" ref="AO2:AO32" si="13">+AM2+AN2</f>
         <v>86</v>
       </c>
       <c r="AP2" s="3">
         <v>5</v>
       </c>
       <c r="AQ2" s="3">
-        <f t="shared" ref="AQ2:AQ33" si="14">+AO2+AP2</f>
+        <f t="shared" ref="AQ2:AQ32" si="14">+AO2+AP2</f>
         <v>91</v>
       </c>
       <c r="AR2" s="3">
-        <f t="shared" ref="AR2:AR33" si="15">+AQ2+7</f>
+        <f t="shared" ref="AR2:AR32" si="15">+AQ2+7</f>
         <v>98</v>
       </c>
       <c r="AS2" s="3">
-        <f t="shared" ref="AS2:AS33" si="16">+AR2+7+AT2</f>
+        <f t="shared" ref="AS2:AS32" si="16">+AR2+7+AT2</f>
         <v>115</v>
       </c>
       <c r="AT2" s="3">
         <v>10</v>
       </c>
       <c r="AU2" s="3">
-        <f t="shared" ref="AU2:AU33" si="17">+AA2-R2</f>
+        <f t="shared" ref="AU2:AU32" si="17">+AA2-R2</f>
         <v>11</v>
       </c>
       <c r="AV2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW2" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW2" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX2" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY2" s="21">
         <v>46507</v>
@@ -1922,22 +1927,22 @@
         <v>120</v>
       </c>
       <c r="B3" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="D3" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F3" s="19">
         <v>90009500</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H3" s="2">
         <v>2533780546</v>
@@ -2039,7 +2044,7 @@
         <v>112</v>
       </c>
       <c r="AK3" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL3" s="3">
         <v>2</v>
@@ -2078,13 +2083,13 @@
         <v>12</v>
       </c>
       <c r="AV3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW3" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW3" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX3" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY3" s="21">
         <v>46507</v>
@@ -2095,22 +2100,22 @@
         <v>121</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F4" s="19">
         <v>90009500</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H4" s="2">
         <v>2533780535</v>
@@ -2212,7 +2217,7 @@
         <v>119</v>
       </c>
       <c r="AK4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL4" s="3">
         <v>2</v>
@@ -2251,13 +2256,13 @@
         <v>12</v>
       </c>
       <c r="AV4" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW4" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW4" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX4" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY4" s="21">
         <v>46507</v>
@@ -2268,22 +2273,22 @@
         <v>233</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="F5" s="19">
         <v>90009500</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H5" s="2">
         <v>91018400</v>
@@ -2342,14 +2347,12 @@
         <v>24</v>
       </c>
       <c r="X5" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3">
-        <f>+ROUNDDOWN(W5/7,0)*7+X5</f>
         <v>26</v>
       </c>
       <c r="Z5" s="27">
-        <f>+X5+Y5</f>
         <v>31</v>
       </c>
       <c r="AA5" s="6">
@@ -2387,7 +2390,7 @@
         <v>76</v>
       </c>
       <c r="AK5" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AL5" s="3">
         <v>2</v>
@@ -2426,13 +2429,13 @@
         <v>17</v>
       </c>
       <c r="AV5" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW5" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW5" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX5" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY5" s="21">
         <v>46507</v>
@@ -2443,22 +2446,22 @@
         <v>416</v>
       </c>
       <c r="B6" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="D6" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F6" s="19">
         <v>90014400</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H6" s="2">
         <v>95207</v>
@@ -2517,14 +2520,12 @@
         <v>26</v>
       </c>
       <c r="X6" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3">
-        <f>+ROUNDDOWN(W6/7,0)*7+X6</f>
         <v>26</v>
       </c>
       <c r="Z6" s="6">
-        <f>+Y6+X6-1</f>
         <v>30</v>
       </c>
       <c r="AA6" s="6">
@@ -2562,7 +2563,7 @@
         <v>80</v>
       </c>
       <c r="AK6" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AL6" s="3">
         <v>4</v>
@@ -2601,13 +2602,13 @@
         <v>16</v>
       </c>
       <c r="AV6" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW6" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW6" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX6" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AY6" s="21">
         <v>46507</v>
@@ -2618,16 +2619,16 @@
         <v>752</v>
       </c>
       <c r="B7" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="D7" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F7" s="19">
         <v>90018000</v>
@@ -2651,15 +2652,13 @@
         <v>7</v>
       </c>
       <c r="M7" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N7" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O7" s="3">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P7" s="3">
         <f t="shared" si="2"/>
@@ -2667,10 +2666,9 @@
       </c>
       <c r="Q7" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S7" s="3">
@@ -2692,14 +2690,13 @@
         <v>30</v>
       </c>
       <c r="X7" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="26">
         <f>+W7+1</f>
         <v>31</v>
       </c>
       <c r="Z7" s="6">
-        <f>+Y7+X7-1</f>
         <v>33</v>
       </c>
       <c r="AA7" s="6">
@@ -2716,76 +2713,76 @@
         <v>5</v>
       </c>
       <c r="AE7" s="3">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="AF7" s="3">
         <f t="shared" si="9"/>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AG7" s="6">
         <v>3</v>
       </c>
       <c r="AH7" s="6">
         <f t="shared" si="10"/>
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI7" s="3">
         <v>0</v>
       </c>
       <c r="AJ7" s="3">
         <f t="shared" si="11"/>
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AK7" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AL7" s="3">
         <v>2</v>
       </c>
       <c r="AM7" s="3">
         <f t="shared" si="12"/>
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AN7" s="3">
         <v>2</v>
       </c>
       <c r="AO7" s="3">
         <f t="shared" si="13"/>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AP7" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AQ7" s="3">
         <f t="shared" si="14"/>
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AR7" s="3">
         <f t="shared" si="15"/>
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AS7" s="3">
         <f t="shared" si="16"/>
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="AT7" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AU7" s="3">
         <f t="shared" si="17"/>
         <v>19</v>
       </c>
       <c r="AV7" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW7" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX7" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="AY7" s="37">
-        <v>46142</v>
+        <v>69</v>
+      </c>
+      <c r="AY7" s="40">
+        <v>46507</v>
       </c>
     </row>
     <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
@@ -2793,16 +2790,16 @@
         <v>761</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F8" s="19">
         <v>90016900</v>
@@ -2826,15 +2823,14 @@
         <v>7</v>
       </c>
       <c r="M8" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="2"/>
@@ -2842,10 +2838,9 @@
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S8" s="3">
@@ -2867,19 +2862,16 @@
         <v>30</v>
       </c>
       <c r="X8" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <f>+ROUNDDOWN(W8/7,0)*7+X8</f>
         <v>31</v>
       </c>
       <c r="Z8" s="6">
-        <f>+Y8+X8-1</f>
         <v>33</v>
       </c>
       <c r="AA8" s="6">
-        <f t="shared" si="8"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB8" s="3">
         <v>4</v>
@@ -2891,7 +2883,7 @@
         <v>6</v>
       </c>
       <c r="AE8" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AF8" s="3">
         <f t="shared" si="9"/>
@@ -2912,7 +2904,7 @@
         <v>82</v>
       </c>
       <c r="AK8" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AL8" s="3">
         <v>3</v>
@@ -2922,14 +2914,14 @@
         <v>85</v>
       </c>
       <c r="AN8" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO8" s="3">
         <f t="shared" si="13"/>
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AP8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ8" s="3">
         <f t="shared" si="14"/>
@@ -2941,26 +2933,26 @@
       </c>
       <c r="AS8" s="3">
         <f t="shared" si="16"/>
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AT8" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AU8" s="3">
         <f t="shared" si="17"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV8" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW8" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX8" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="AY8" s="37">
-        <v>46142</v>
+        <v>69</v>
+      </c>
+      <c r="AY8" s="40">
+        <v>46507</v>
       </c>
     </row>
     <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
@@ -2968,22 +2960,22 @@
         <v>888</v>
       </c>
       <c r="B9" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>75</v>
-      </c>
       <c r="E9" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F9" s="19">
         <v>26549502</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -3001,15 +2993,14 @@
         <v>5</v>
       </c>
       <c r="M9" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3">
         <v>7</v>
       </c>
       <c r="O9" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3">
         <f t="shared" si="2"/>
@@ -3017,7 +3008,7 @@
       </c>
       <c r="Q9" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3">
         <f t="shared" si="4"/>
@@ -3042,14 +3033,12 @@
         <v>30</v>
       </c>
       <c r="X9" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="26">
-        <f>+W9+1</f>
         <v>31</v>
       </c>
       <c r="Z9" s="27">
-        <f>+Y9+X9</f>
         <v>36</v>
       </c>
       <c r="AA9" s="6">
@@ -3087,7 +3076,7 @@
         <v>63</v>
       </c>
       <c r="AK9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL9" s="3">
         <v>4</v>
@@ -3126,13 +3115,13 @@
         <v>22</v>
       </c>
       <c r="AV9" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW9" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX9" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AY9" s="21">
         <v>46507</v>
@@ -3143,22 +3132,22 @@
         <v>901</v>
       </c>
       <c r="B10" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="E10" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F10" s="19">
         <v>90012500</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H10" s="2">
         <v>95207</v>
@@ -3217,14 +3206,12 @@
         <v>26</v>
       </c>
       <c r="X10" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3">
-        <f t="shared" ref="Y10:Y53" si="18">+ROUNDDOWN(W10/7,0)*7+X10</f>
         <v>26</v>
       </c>
       <c r="Z10" s="6">
-        <f>+Y10+X10-1</f>
         <v>30</v>
       </c>
       <c r="AA10" s="6">
@@ -3262,7 +3249,7 @@
         <v>83</v>
       </c>
       <c r="AK10" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AL10" s="3">
         <v>1</v>
@@ -3301,13 +3288,13 @@
         <v>16</v>
       </c>
       <c r="AV10" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW10" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW10" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX10" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY10" s="21">
         <v>46507</v>
@@ -3318,22 +3305,22 @@
         <v>904</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F11" s="19">
         <v>90014400</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H11" s="2">
         <v>95436</v>
@@ -3392,10 +3379,9 @@
         <v>30</v>
       </c>
       <c r="X11" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="3">
-        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z11" s="6">
@@ -3436,7 +3422,7 @@
         <v>112</v>
       </c>
       <c r="AK11" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL11" s="3">
         <v>4</v>
@@ -3475,13 +3461,13 @@
         <v>16</v>
       </c>
       <c r="AV11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW11" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW11" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX11" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY11" s="21">
         <v>46507</v>
@@ -3492,22 +3478,22 @@
         <v>906</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F12" s="19">
         <v>90018600</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H12" s="2">
         <v>95436</v>
@@ -3566,14 +3552,12 @@
         <v>30</v>
       </c>
       <c r="X12" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="3">
-        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z12" s="6">
-        <f>+Y12+X12-1</f>
         <v>37</v>
       </c>
       <c r="AA12" s="6">
@@ -3611,7 +3595,7 @@
         <v>101</v>
       </c>
       <c r="AK12" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL12" s="3">
         <v>2</v>
@@ -3650,13 +3634,13 @@
         <v>15</v>
       </c>
       <c r="AV12" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW12" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW12" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX12" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY12" s="21">
         <v>46507</v>
@@ -3667,22 +3651,22 @@
         <v>907</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="19">
         <v>90018600</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H13" s="2">
         <v>95112</v>
@@ -3741,10 +3725,9 @@
         <v>23</v>
       </c>
       <c r="X13" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="3">
-        <f t="shared" si="18"/>
         <v>26</v>
       </c>
       <c r="Z13" s="6">
@@ -3785,7 +3768,7 @@
         <v>76</v>
       </c>
       <c r="AK13" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AL13" s="3">
         <v>2</v>
@@ -3824,13 +3807,13 @@
         <v>18</v>
       </c>
       <c r="AV13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW13" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW13" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX13" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY13" s="21">
         <v>46507</v>
@@ -3841,22 +3824,22 @@
         <v>908</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="F14" s="19">
         <v>90018600</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H14" s="2">
         <v>28390</v>
@@ -3915,10 +3898,9 @@
         <v>33</v>
       </c>
       <c r="X14" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="3">
-        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="Z14" s="6">
@@ -3959,7 +3941,7 @@
         <v>83</v>
       </c>
       <c r="AK14" s="28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL14" s="3">
         <v>2</v>
@@ -3998,13 +3980,13 @@
         <v>14</v>
       </c>
       <c r="AV14" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW14" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW14" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX14" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY14" s="21">
         <v>46507</v>
@@ -4015,34 +3997,34 @@
         <v>910</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F15" s="19">
         <v>90018600</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H15" s="2">
         <v>92000100</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J15" s="2">
         <v>92000100</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L15" s="3">
         <v>7</v>
@@ -4089,10 +4071,9 @@
         <v>30</v>
       </c>
       <c r="X15" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3">
-        <f t="shared" si="18"/>
         <v>36</v>
       </c>
       <c r="Z15" s="6">
@@ -4134,7 +4115,7 @@
         <v>81</v>
       </c>
       <c r="AK15" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AL15" s="3">
         <v>2</v>
@@ -4173,13 +4154,13 @@
         <v>16</v>
       </c>
       <c r="AV15" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW15" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW15" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX15" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY15" s="21">
         <v>46507</v>
@@ -4190,22 +4171,22 @@
         <v>912</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F16" s="19">
         <v>90018600</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H16" s="2">
         <v>2533780535</v>
@@ -4307,7 +4288,7 @@
         <v>88</v>
       </c>
       <c r="AK16" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL16" s="3">
         <v>2</v>
@@ -4346,13 +4327,13 @@
         <v>12</v>
       </c>
       <c r="AV16" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW16" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW16" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX16" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY16" s="21">
         <v>46507</v>
@@ -4363,22 +4344,22 @@
         <v>915</v>
       </c>
       <c r="B17" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="E17" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F17" s="19">
         <v>90012500</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H17" s="2">
         <v>2533780546</v>
@@ -4437,14 +4418,12 @@
         <v>31</v>
       </c>
       <c r="X17" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="3">
-        <f t="shared" si="18"/>
         <v>32</v>
       </c>
       <c r="Z17" s="6">
-        <f>+Y17+X17-1</f>
         <v>35</v>
       </c>
       <c r="AA17" s="6">
@@ -4481,7 +4460,7 @@
         <v>97</v>
       </c>
       <c r="AK17" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL17" s="3">
         <v>1</v>
@@ -4520,13 +4499,13 @@
         <v>15</v>
       </c>
       <c r="AV17" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW17" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW17" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX17" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY17" s="21">
         <v>46507</v>
@@ -4537,22 +4516,22 @@
         <v>916</v>
       </c>
       <c r="B18" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="F18" s="19">
         <v>91017700</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H18" s="2">
         <v>95207</v>
@@ -4620,7 +4599,7 @@
         <v>31</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" ref="AA18:AA53" si="19">+Z18+AB18-1</f>
+        <f t="shared" ref="AA18:AA52" si="18">+Z18+AB18-1</f>
         <v>33</v>
       </c>
       <c r="AB18" s="3">
@@ -4654,7 +4633,7 @@
         <v>69</v>
       </c>
       <c r="AK18" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AL18" s="3">
         <v>2</v>
@@ -4693,13 +4672,13 @@
         <v>17</v>
       </c>
       <c r="AV18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW18" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX18" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY18" s="21">
         <v>46507</v>
@@ -4710,22 +4689,22 @@
         <v>917</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F19" s="19">
         <v>90014400</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H19" s="2">
         <v>2533780546</v>
@@ -4793,7 +4772,7 @@
         <v>36</v>
       </c>
       <c r="AA19" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>37</v>
       </c>
       <c r="AB19" s="3">
@@ -4827,7 +4806,7 @@
         <v>90</v>
       </c>
       <c r="AK19" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL19" s="3">
         <v>2</v>
@@ -4866,13 +4845,13 @@
         <v>14</v>
       </c>
       <c r="AV19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW19" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW19" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX19" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY19" s="21">
         <v>46507</v>
@@ -4883,22 +4862,22 @@
         <v>918</v>
       </c>
       <c r="B20" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="F20" s="19">
         <v>91017700</v>
       </c>
       <c r="G20" s="35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H20" s="2">
         <v>2533780546</v>
@@ -4966,7 +4945,7 @@
         <v>35</v>
       </c>
       <c r="AA20" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>37</v>
       </c>
       <c r="AB20" s="3">
@@ -5000,7 +4979,7 @@
         <v>89</v>
       </c>
       <c r="AK20" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL20" s="3">
         <v>2</v>
@@ -5039,13 +5018,13 @@
         <v>14</v>
       </c>
       <c r="AV20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW20" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW20" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX20" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY20" s="21">
         <v>46507</v>
@@ -5056,22 +5035,22 @@
         <v>920</v>
       </c>
       <c r="B21" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="F21" s="19">
         <v>91017500</v>
       </c>
       <c r="G21" s="35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H21" s="2">
         <v>2533780535</v>
@@ -5130,18 +5109,16 @@
         <v>32</v>
       </c>
       <c r="X21" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="3">
+        <v>33</v>
+      </c>
+      <c r="Z21" s="6">
+        <v>37</v>
+      </c>
+      <c r="AA21" s="6">
         <f t="shared" si="18"/>
-        <v>33</v>
-      </c>
-      <c r="Z21" s="6">
-        <f>+Y21+X21-1</f>
-        <v>37</v>
-      </c>
-      <c r="AA21" s="6">
-        <f t="shared" si="19"/>
         <v>39</v>
       </c>
       <c r="AB21" s="3">
@@ -5175,7 +5152,7 @@
         <v>80</v>
       </c>
       <c r="AK21" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL21" s="3">
         <v>3</v>
@@ -5214,39 +5191,39 @@
         <v>16</v>
       </c>
       <c r="AV21" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW21" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW21" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX21" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY21" s="21">
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>921</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F22" s="19">
         <v>90014400</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H22" s="2">
         <v>2533780535</v>
@@ -5314,7 +5291,7 @@
         <v>37</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>39</v>
       </c>
       <c r="AB22" s="3">
@@ -5348,7 +5325,7 @@
         <v>94</v>
       </c>
       <c r="AK22" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL22" s="3">
         <v>2</v>
@@ -5387,13 +5364,13 @@
         <v>16</v>
       </c>
       <c r="AV22" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW22" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW22" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX22" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY22" s="21">
         <v>46507</v>
@@ -5404,22 +5381,22 @@
         <v>924</v>
       </c>
       <c r="B23" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="E23" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F23" s="19">
         <v>90012500</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H23" s="2">
         <v>92050300</v>
@@ -5478,17 +5455,16 @@
         <v>25</v>
       </c>
       <c r="X23" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <f t="shared" si="18"/>
         <v>25</v>
       </c>
       <c r="Z23" s="6">
         <v>30</v>
       </c>
       <c r="AA23" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>32</v>
       </c>
       <c r="AB23" s="3">
@@ -5522,7 +5498,7 @@
         <v>55</v>
       </c>
       <c r="AK23" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL23" s="3">
         <v>1</v>
@@ -5561,13 +5537,13 @@
         <v>16</v>
       </c>
       <c r="AV23" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW23" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW23" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX23" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AY23" s="21">
         <v>46507</v>
@@ -5578,22 +5554,22 @@
         <v>925</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F24" s="19">
         <v>90018600</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H24" s="2">
         <v>2533780546</v>
@@ -5661,7 +5637,7 @@
         <v>33</v>
       </c>
       <c r="AA24" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>35</v>
       </c>
       <c r="AB24" s="3">
@@ -5695,7 +5671,7 @@
         <v>91</v>
       </c>
       <c r="AK24" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL24" s="3">
         <v>2</v>
@@ -5734,13 +5710,13 @@
         <v>12</v>
       </c>
       <c r="AV24" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW24" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW24" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX24" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY24" s="21">
         <v>46507</v>
@@ -5751,22 +5727,22 @@
         <v>927</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F25" s="19">
         <v>90014400</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H25" s="2">
         <v>26037000</v>
@@ -5834,7 +5810,7 @@
         <v>30</v>
       </c>
       <c r="AA25" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>32</v>
       </c>
       <c r="AB25" s="3">
@@ -5868,7 +5844,7 @@
         <v>94</v>
       </c>
       <c r="AK25" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL25" s="3">
         <v>4</v>
@@ -5907,13 +5883,13 @@
         <v>9</v>
       </c>
       <c r="AV25" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW25" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW25" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX25" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY25" s="21">
         <v>46507</v>
@@ -5924,22 +5900,22 @@
         <v>928</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F26" s="19">
         <v>90018600</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H26" s="2">
         <v>91018400</v>
@@ -5998,17 +5974,16 @@
         <v>24</v>
       </c>
       <c r="X26" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="3">
-        <f t="shared" si="18"/>
         <v>26</v>
       </c>
       <c r="Z26" s="6">
         <v>31</v>
       </c>
       <c r="AA26" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
       <c r="AB26" s="3">
@@ -6042,7 +6017,7 @@
         <v>63</v>
       </c>
       <c r="AK26" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AL26" s="3">
         <v>2</v>
@@ -6081,13 +6056,13 @@
         <v>17</v>
       </c>
       <c r="AV26" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW26" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW26" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX26" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY26" s="21">
         <v>46507</v>
@@ -6098,22 +6073,22 @@
         <v>930</v>
       </c>
       <c r="B27" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="F27" s="19">
         <v>91017700</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H27" s="2">
         <v>26037000</v>
@@ -6171,17 +6146,16 @@
         <v>30</v>
       </c>
       <c r="X27" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="Z27" s="6">
         <v>35</v>
       </c>
       <c r="AA27" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>37</v>
       </c>
       <c r="AB27" s="3">
@@ -6215,7 +6189,7 @@
         <v>86</v>
       </c>
       <c r="AK27" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL27" s="3">
         <v>3</v>
@@ -6254,13 +6228,13 @@
         <v>14</v>
       </c>
       <c r="AV27" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW27" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW27" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX27" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY27" s="21">
         <v>46507</v>
@@ -6271,22 +6245,22 @@
         <v>931</v>
       </c>
       <c r="B28" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="D28" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F28" s="19">
         <v>90018600</v>
       </c>
       <c r="G28" s="36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H28" s="2">
         <v>26037000</v>
@@ -6315,7 +6289,7 @@
         <v>22</v>
       </c>
       <c r="P28" s="3">
-        <f t="shared" ref="P28:P45" si="20">+IF(I28="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P28:P44" si="19">+IF(I28="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q28" s="3">
@@ -6345,17 +6319,16 @@
         <v>30</v>
       </c>
       <c r="X28" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y28" s="3">
-        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="Z28" s="6">
         <v>33</v>
       </c>
       <c r="AA28" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>35</v>
       </c>
       <c r="AB28" s="3">
@@ -6389,7 +6362,7 @@
         <v>87</v>
       </c>
       <c r="AK28" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL28" s="3">
         <v>2</v>
@@ -6428,13 +6401,13 @@
         <v>12</v>
       </c>
       <c r="AV28" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW28" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW28" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX28" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY28" s="21">
         <v>46507</v>
@@ -6445,22 +6418,22 @@
         <v>932</v>
       </c>
       <c r="B29" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="E29" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F29" s="19">
         <v>90012500</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H29" s="2">
         <v>26037000</v>
@@ -6489,7 +6462,7 @@
         <v>22</v>
       </c>
       <c r="P29" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="Q29" s="3">
@@ -6519,17 +6492,16 @@
         <v>30</v>
       </c>
       <c r="X29" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="3">
-        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="Z29" s="6">
         <v>35</v>
       </c>
       <c r="AA29" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>37</v>
       </c>
       <c r="AB29" s="3">
@@ -6563,7 +6535,7 @@
         <v>104</v>
       </c>
       <c r="AK29" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AL29" s="3">
         <v>1</v>
@@ -6602,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="AV29" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW29" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW29" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX29" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY29" s="21">
         <v>46507</v>
@@ -6619,16 +6591,16 @@
         <v>1005</v>
       </c>
       <c r="B30" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="D30" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>92</v>
-      </c>
       <c r="E30" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F30" s="19">
         <v>9510600</v>
@@ -6652,23 +6624,22 @@
         <v>7</v>
       </c>
       <c r="M30" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N30" s="3">
         <v>14</v>
       </c>
       <c r="O30" s="3">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P30" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q30" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R30" s="3">
         <f t="shared" si="4"/>
@@ -6693,22 +6664,20 @@
         <v>30</v>
       </c>
       <c r="X30" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="3">
+        <v>31</v>
+      </c>
+      <c r="Z30" s="6">
+        <v>31</v>
+      </c>
+      <c r="AA30" s="6">
         <f t="shared" si="18"/>
-        <v>31</v>
-      </c>
-      <c r="Z30" s="6">
-        <f t="shared" ref="Z30:Z41" si="21">+Y30+X30-1</f>
         <v>33</v>
       </c>
-      <c r="AA30" s="6">
-        <f t="shared" si="19"/>
-        <v>34</v>
-      </c>
       <c r="AB30" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC30" s="3">
         <v>4</v>
@@ -6717,76 +6686,76 @@
         <v>11</v>
       </c>
       <c r="AE30" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AF30" s="3">
         <f t="shared" si="9"/>
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AG30" s="6">
         <v>3</v>
       </c>
       <c r="AH30" s="6">
         <f t="shared" si="10"/>
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AI30" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AJ30" s="3">
         <f t="shared" si="11"/>
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AK30" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AL30" s="3">
         <v>0</v>
       </c>
       <c r="AM30" s="3">
         <f t="shared" si="12"/>
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AN30" s="3">
         <v>0</v>
       </c>
       <c r="AO30" s="3">
         <f t="shared" si="13"/>
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AP30" s="3">
         <v>1</v>
       </c>
       <c r="AQ30" s="3">
         <f t="shared" si="14"/>
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AR30" s="3">
         <f t="shared" si="15"/>
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="16"/>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="AT30" s="3">
         <v>0</v>
       </c>
       <c r="AU30" s="3">
         <f t="shared" si="17"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV30" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW30" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX30" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY30" s="37">
-        <v>46142</v>
+        <v>75</v>
+      </c>
+      <c r="AY30" s="40">
+        <v>46507</v>
       </c>
     </row>
     <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
@@ -6794,16 +6763,16 @@
         <v>1006</v>
       </c>
       <c r="B31" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="E31" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F31" s="19">
         <v>90038200</v>
@@ -6827,23 +6796,22 @@
         <v>7</v>
       </c>
       <c r="M31" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N31" s="3">
         <v>14</v>
       </c>
       <c r="O31" s="3">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P31" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q31" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R31" s="3">
         <f t="shared" si="4"/>
@@ -6868,22 +6836,20 @@
         <v>30</v>
       </c>
       <c r="X31" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="3">
+        <v>31</v>
+      </c>
+      <c r="Z31" s="6">
+        <v>31</v>
+      </c>
+      <c r="AA31" s="6">
         <f t="shared" si="18"/>
-        <v>31</v>
-      </c>
-      <c r="Z31" s="6">
-        <f t="shared" si="21"/>
-        <v>33</v>
-      </c>
-      <c r="AA31" s="6">
-        <f t="shared" si="19"/>
         <v>34</v>
       </c>
       <c r="AB31" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC31" s="3">
         <v>4</v>
@@ -6892,76 +6858,76 @@
         <v>11</v>
       </c>
       <c r="AE31" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AF31" s="3">
         <f t="shared" si="9"/>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG31" s="6">
         <v>3</v>
       </c>
       <c r="AH31" s="6">
         <f t="shared" si="10"/>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI31" s="3">
         <v>0</v>
       </c>
       <c r="AJ31" s="3">
         <f t="shared" si="11"/>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AK31" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AL31" s="3">
         <v>1</v>
       </c>
       <c r="AM31" s="3">
         <f t="shared" si="12"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AN31" s="3">
         <v>4</v>
       </c>
       <c r="AO31" s="3">
         <f t="shared" si="13"/>
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AP31" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AQ31" s="3">
         <f t="shared" si="14"/>
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AR31" s="3">
         <f t="shared" si="15"/>
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="16"/>
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="AT31" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AU31" s="3">
         <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="AV31" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW31" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX31" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AY31" s="37">
-        <v>46142</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
@@ -6969,16 +6935,16 @@
         <v>1007</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F32" s="19">
         <v>900383</v>
@@ -7002,23 +6968,22 @@
         <v>7</v>
       </c>
       <c r="M32" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>14</v>
       </c>
       <c r="O32" s="3">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q32" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <f t="shared" si="4"/>
@@ -7046,19 +7011,19 @@
         <v>3</v>
       </c>
       <c r="Y32" s="3">
+        <f t="shared" ref="Y32:Y52" si="20">+ROUNDDOWN(W32/7,0)*7+X32</f>
+        <v>31</v>
+      </c>
+      <c r="Z32" s="6">
+        <f t="shared" ref="Z32:Z40" si="21">+Y32+X32-1</f>
+        <v>33</v>
+      </c>
+      <c r="AA32" s="6">
         <f t="shared" si="18"/>
-        <v>31</v>
-      </c>
-      <c r="Z32" s="6">
-        <f t="shared" si="21"/>
-        <v>33</v>
-      </c>
-      <c r="AA32" s="6">
-        <f t="shared" si="19"/>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="AB32" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC32" s="3">
         <v>7</v>
@@ -7067,96 +7032,96 @@
         <v>7</v>
       </c>
       <c r="AE32" s="3">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AF32" s="3">
         <f t="shared" si="9"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AG32" s="6">
         <v>3</v>
       </c>
       <c r="AH32" s="6">
         <f t="shared" si="10"/>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AI32" s="3">
         <v>7</v>
       </c>
       <c r="AJ32" s="3">
         <f t="shared" si="11"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AK32" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AL32" s="3">
         <v>3</v>
       </c>
       <c r="AM32" s="3">
         <f t="shared" si="12"/>
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN32" s="3">
         <v>1</v>
       </c>
       <c r="AO32" s="3">
         <f t="shared" si="13"/>
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AP32" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AQ32" s="3">
         <f t="shared" si="14"/>
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AR32" s="3">
         <f t="shared" si="15"/>
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="16"/>
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="AT32" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AU32" s="3">
         <f t="shared" si="17"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AV32" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW32" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX32" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY32" s="37">
-        <v>46142</v>
+        <v>75</v>
+      </c>
+      <c r="AY32" s="40">
+        <v>46507</v>
       </c>
     </row>
     <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="F33" s="19">
-        <v>90016800</v>
+        <v>90016700</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>44</v>
@@ -7177,23 +7142,22 @@
         <v>7</v>
       </c>
       <c r="M33" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N33" s="3">
         <v>14</v>
       </c>
       <c r="O33" s="3">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <f t="shared" ref="O33:O52" si="22">IF(I33="SFK Freight Forwarder",M33,M33+N33-1)</f>
+        <v>0</v>
       </c>
       <c r="P33" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <f t="shared" ref="Q33:Q52" si="23">+IF(I33="SFK Freight Forwarder",O33,O33+P33-1)</f>
+        <v>0</v>
       </c>
       <c r="R33" s="3">
         <f t="shared" si="4"/>
@@ -7203,7 +7167,7 @@
         <v>7</v>
       </c>
       <c r="T33" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="T33:T52" si="24">+R33+S33-1</f>
         <v>29</v>
       </c>
       <c r="U33" s="3">
@@ -7214,127 +7178,125 @@
         <v>1</v>
       </c>
       <c r="W33" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="W33:W52" si="25">+U33+V33-1</f>
         <v>30</v>
       </c>
       <c r="X33" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="3">
+        <v>31</v>
+      </c>
+      <c r="Z33" s="6">
+        <v>36</v>
+      </c>
+      <c r="AA33" s="6">
         <f t="shared" si="18"/>
-        <v>31</v>
-      </c>
-      <c r="Z33" s="6">
-        <f t="shared" si="21"/>
-        <v>33</v>
-      </c>
-      <c r="AA33" s="6">
-        <f t="shared" si="19"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AB33" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC33" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD33" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE33" s="3">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="AF33" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="AF33:AF52" si="26">+AE33+AA33-1</f>
+        <v>89</v>
+      </c>
+      <c r="AG33" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH33" s="6">
+        <f t="shared" ref="AH33:AH52" si="27">+AF33+AG33</f>
+        <v>92</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="3">
+        <f t="shared" ref="AJ33:AJ52" si="28">+AI33+AH33</f>
+        <v>92</v>
+      </c>
+      <c r="AK33" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL33" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM33" s="3">
+        <f t="shared" ref="AM33:AM52" si="29">+AJ33+AL33</f>
+        <v>94</v>
+      </c>
+      <c r="AN33" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO33" s="3">
+        <f t="shared" ref="AO33:AO52" si="30">+AM33+AN33</f>
+        <v>96</v>
+      </c>
+      <c r="AP33" s="3">
+        <v>2</v>
+      </c>
+      <c r="AQ33" s="3">
+        <f t="shared" ref="AQ33:AQ52" si="31">+AO33+AP33</f>
+        <v>98</v>
+      </c>
+      <c r="AR33" s="3">
+        <f t="shared" ref="AR33:AR52" si="32">+AQ33+7</f>
+        <v>105</v>
+      </c>
+      <c r="AS33" s="3">
+        <f t="shared" ref="AS33:AS52" si="33">+AR33+7+AT33</f>
         <v>112</v>
       </c>
-      <c r="AG33" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH33" s="6">
-        <f t="shared" si="10"/>
-        <v>115</v>
-      </c>
-      <c r="AI33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="3">
-        <f t="shared" si="11"/>
-        <v>115</v>
-      </c>
-      <c r="AK33" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL33" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM33" s="3">
-        <f t="shared" si="12"/>
-        <v>116</v>
-      </c>
-      <c r="AN33" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO33" s="3">
-        <f t="shared" si="13"/>
-        <v>117</v>
-      </c>
-      <c r="AP33" s="3">
-        <v>4</v>
-      </c>
-      <c r="AQ33" s="3">
-        <f t="shared" si="14"/>
-        <v>121</v>
-      </c>
-      <c r="AR33" s="3">
-        <f t="shared" si="15"/>
-        <v>128</v>
-      </c>
-      <c r="AS33" s="3">
-        <f t="shared" si="16"/>
-        <v>147</v>
-      </c>
       <c r="AT33" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU33" s="3">
-        <f t="shared" si="17"/>
-        <v>12</v>
+        <f t="shared" ref="AU33:AU52" si="34">+AA33-R33</f>
+        <v>14</v>
       </c>
       <c r="AV33" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW33" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX33" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY33" s="37">
-        <v>46142</v>
+        <v>75</v>
+      </c>
+      <c r="AY33" s="40">
+        <v>46507</v>
       </c>
     </row>
     <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F34" s="19">
-        <v>90016700</v>
+        <v>90017000</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H34" s="2">
         <v>0</v>
@@ -7352,23 +7314,22 @@
         <v>7</v>
       </c>
       <c r="M34" s="3">
-        <f t="shared" ref="M34:M53" si="22">+IF(I34="SFK Freight Forwarder",L34,9)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N34" s="3">
         <v>14</v>
       </c>
       <c r="O34" s="3">
-        <f t="shared" ref="O34:O53" si="23">IF(I34="SFK Freight Forwarder",M34,M34+N34-1)</f>
-        <v>7</v>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="P34" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q34" s="3">
-        <f t="shared" ref="Q34:Q53" si="24">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
-        <v>7</v>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="R34" s="3">
         <f t="shared" si="4"/>
@@ -7378,7 +7339,7 @@
         <v>7</v>
       </c>
       <c r="T34" s="3">
-        <f t="shared" ref="T34:T53" si="25">+R34+S34-1</f>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U34" s="3">
@@ -7389,26 +7350,24 @@
         <v>1</v>
       </c>
       <c r="W34" s="3">
-        <f t="shared" ref="W34:W53" si="26">+U34+V34-1</f>
+        <f t="shared" si="25"/>
         <v>30</v>
       </c>
       <c r="X34" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="3">
+        <v>31</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>33</v>
+      </c>
+      <c r="AA34" s="6">
         <f t="shared" si="18"/>
-        <v>31</v>
-      </c>
-      <c r="Z34" s="6">
-        <f t="shared" si="21"/>
-        <v>33</v>
-      </c>
-      <c r="AA34" s="6">
-        <f t="shared" si="19"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB34" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC34" s="3">
         <v>4</v>
@@ -7417,99 +7376,99 @@
         <v>11</v>
       </c>
       <c r="AE34" s="3">
+        <v>63</v>
+      </c>
+      <c r="AF34" s="3">
+        <f t="shared" si="26"/>
+        <v>98</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH34" s="6">
+        <f t="shared" si="27"/>
+        <v>101</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="3">
+        <f t="shared" si="28"/>
+        <v>101</v>
+      </c>
+      <c r="AK34" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AF34" s="3">
-        <f t="shared" ref="AF34:AF53" si="27">+AE34+AA34-1</f>
-        <v>93</v>
-      </c>
-      <c r="AG34" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH34" s="6">
-        <f t="shared" ref="AH34:AH53" si="28">+AF34+AG34</f>
-        <v>96</v>
-      </c>
-      <c r="AI34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="3">
-        <f t="shared" ref="AJ34:AJ53" si="29">+AI34+AH34</f>
-        <v>96</v>
-      </c>
-      <c r="AK34" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="AL34" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM34" s="3">
-        <f t="shared" ref="AM34:AM53" si="30">+AJ34+AL34</f>
-        <v>98</v>
+        <f t="shared" si="29"/>
+        <v>105</v>
       </c>
       <c r="AN34" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO34" s="3">
-        <f t="shared" ref="AO34:AO53" si="31">+AM34+AN34</f>
-        <v>100</v>
+        <f t="shared" si="30"/>
+        <v>108</v>
       </c>
       <c r="AP34" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AQ34" s="3">
-        <f t="shared" ref="AQ34:AQ53" si="32">+AO34+AP34</f>
-        <v>100</v>
+        <f t="shared" si="31"/>
+        <v>112</v>
       </c>
       <c r="AR34" s="3">
-        <f t="shared" ref="AR34:AR53" si="33">+AQ34+7</f>
-        <v>107</v>
+        <f t="shared" si="32"/>
+        <v>119</v>
       </c>
       <c r="AS34" s="3">
-        <f t="shared" ref="AS34:AS53" si="34">+AR34+7+AT34</f>
-        <v>127</v>
+        <f t="shared" si="33"/>
+        <v>126</v>
       </c>
       <c r="AT34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU34" s="3">
+        <f t="shared" si="34"/>
         <v>13</v>
       </c>
-      <c r="AU34" s="3">
-        <f t="shared" ref="AU34:AU53" si="35">+AA34-R34</f>
-        <v>11</v>
-      </c>
       <c r="AV34" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW34" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX34" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AY34" s="37">
-        <v>46142</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B35" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="E35" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F35" s="19">
-        <v>90017000</v>
+        <v>90018000</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H35" s="2">
         <v>0</v>
@@ -7527,23 +7486,22 @@
         <v>7</v>
       </c>
       <c r="M35" s="3">
-        <f t="shared" si="22"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3">
         <v>14</v>
       </c>
       <c r="O35" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="P35" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3">
-        <f t="shared" si="24"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R35" s="3">
         <f t="shared" si="4"/>
@@ -7553,7 +7511,7 @@
         <v>7</v>
       </c>
       <c r="T35" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U35" s="3">
@@ -7564,14 +7522,13 @@
         <v>1</v>
       </c>
       <c r="W35" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>30</v>
       </c>
       <c r="X35" s="3">
         <v>3</v>
       </c>
       <c r="Y35" s="3">
-        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="Z35" s="6">
@@ -7579,11 +7536,11 @@
         <v>33</v>
       </c>
       <c r="AA35" s="6">
-        <f t="shared" si="19"/>
-        <v>34</v>
+        <f t="shared" si="18"/>
+        <v>37</v>
       </c>
       <c r="AB35" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC35" s="3">
         <v>4</v>
@@ -7592,99 +7549,99 @@
         <v>11</v>
       </c>
       <c r="AE35" s="3">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="AF35" s="3">
+        <f t="shared" si="26"/>
+        <v>84</v>
+      </c>
+      <c r="AG35" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH35" s="6">
         <f t="shared" si="27"/>
-        <v>95</v>
-      </c>
-      <c r="AG35" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH35" s="6">
+        <v>87</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>14</v>
+      </c>
+      <c r="AJ35" s="3">
         <f t="shared" si="28"/>
-        <v>98</v>
-      </c>
-      <c r="AI35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="3">
+        <v>101</v>
+      </c>
+      <c r="AK35" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL35" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM35" s="3">
         <f t="shared" si="29"/>
-        <v>98</v>
-      </c>
-      <c r="AK35" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL35" s="3">
-        <v>4</v>
-      </c>
-      <c r="AM35" s="3">
-        <f t="shared" si="30"/>
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AN35" s="3">
         <v>2</v>
       </c>
       <c r="AO35" s="3">
+        <f t="shared" si="30"/>
+        <v>105</v>
+      </c>
+      <c r="AP35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ35" s="3">
         <f t="shared" si="31"/>
-        <v>104</v>
-      </c>
-      <c r="AP35" s="3">
-        <v>3</v>
-      </c>
-      <c r="AQ35" s="3">
+        <v>105</v>
+      </c>
+      <c r="AR35" s="3">
         <f t="shared" si="32"/>
-        <v>107</v>
-      </c>
-      <c r="AR35" s="3">
+        <v>112</v>
+      </c>
+      <c r="AS35" s="3">
         <f t="shared" si="33"/>
-        <v>114</v>
-      </c>
-      <c r="AS35" s="3">
+        <v>119</v>
+      </c>
+      <c r="AT35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU35" s="3">
         <f t="shared" si="34"/>
-        <v>135</v>
-      </c>
-      <c r="AT35" s="3">
         <v>14</v>
       </c>
-      <c r="AU35" s="3">
-        <f t="shared" si="35"/>
-        <v>11</v>
-      </c>
       <c r="AV35" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW35" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX35" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY35" s="37">
-        <v>46142</v>
+        <v>75</v>
+      </c>
+      <c r="AY35" s="40">
+        <v>46507</v>
       </c>
     </row>
     <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F36" s="19">
-        <v>90018000</v>
+        <v>9510600</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H36" s="2">
         <v>0</v>
@@ -7693,32 +7650,31 @@
         <v>26</v>
       </c>
       <c r="J36" s="2">
-        <v>119640</v>
+        <v>261427</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L36" s="3">
         <v>7</v>
       </c>
       <c r="M36" s="3">
-        <f t="shared" si="22"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N36" s="3">
         <v>14</v>
       </c>
       <c r="O36" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P36" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="3">
         <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="P36" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q36" s="3">
-        <f t="shared" si="24"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R36" s="3">
         <f t="shared" si="4"/>
@@ -7728,7 +7684,7 @@
         <v>7</v>
       </c>
       <c r="T36" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U36" s="3">
@@ -7736,130 +7692,128 @@
         <v>30</v>
       </c>
       <c r="V36" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W36" s="3">
+        <f t="shared" si="25"/>
+        <v>31</v>
+      </c>
+      <c r="X36" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <v>33</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>39</v>
+      </c>
+      <c r="AA36" s="6">
+        <f t="shared" si="18"/>
+        <v>44</v>
+      </c>
+      <c r="AB36" s="3">
+        <v>6</v>
+      </c>
+      <c r="AC36" s="3">
+        <v>8</v>
+      </c>
+      <c r="AD36" s="3">
+        <v>8</v>
+      </c>
+      <c r="AE36" s="3">
+        <v>17</v>
+      </c>
+      <c r="AF36" s="3">
         <f t="shared" si="26"/>
-        <v>30</v>
-      </c>
-      <c r="X36" s="3">
-        <v>3</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="18"/>
-        <v>31</v>
-      </c>
-      <c r="Z36" s="6">
-        <f t="shared" si="21"/>
-        <v>33</v>
-      </c>
-      <c r="AA36" s="6">
-        <f t="shared" si="19"/>
-        <v>34</v>
-      </c>
-      <c r="AB36" s="3">
-        <v>2</v>
-      </c>
-      <c r="AC36" s="3">
-        <v>4</v>
-      </c>
-      <c r="AD36" s="3">
-        <v>11</v>
-      </c>
-      <c r="AE36" s="3">
-        <v>57</v>
-      </c>
-      <c r="AF36" s="3">
+        <v>60</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH36" s="6">
         <f t="shared" si="27"/>
-        <v>90</v>
-      </c>
-      <c r="AG36" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH36" s="6">
+        <v>63</v>
+      </c>
+      <c r="AI36" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="3">
         <f t="shared" si="28"/>
-        <v>93</v>
-      </c>
-      <c r="AI36" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="3">
+        <v>63</v>
+      </c>
+      <c r="AK36" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL36" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="3">
         <f t="shared" si="29"/>
-        <v>93</v>
-      </c>
-      <c r="AK36" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL36" s="3">
-        <v>2</v>
-      </c>
-      <c r="AM36" s="3">
+        <v>63</v>
+      </c>
+      <c r="AN36" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="3">
         <f t="shared" si="30"/>
-        <v>95</v>
-      </c>
-      <c r="AN36" s="3">
-        <v>2</v>
-      </c>
-      <c r="AO36" s="3">
+        <v>63</v>
+      </c>
+      <c r="AP36" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ36" s="3">
         <f t="shared" si="31"/>
-        <v>97</v>
-      </c>
-      <c r="AP36" s="3">
-        <v>3</v>
-      </c>
-      <c r="AQ36" s="3">
+        <v>63</v>
+      </c>
+      <c r="AR36" s="3">
         <f t="shared" si="32"/>
+        <v>70</v>
+      </c>
+      <c r="AS36" s="3">
+        <f t="shared" si="33"/>
+        <v>77</v>
+      </c>
+      <c r="AT36" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU36" s="3">
+        <f t="shared" si="34"/>
+        <v>21</v>
+      </c>
+      <c r="AV36" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AW36" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AX36" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY36" s="40">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>1015</v>
+      </c>
+      <c r="B37" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="AR36" s="3">
-        <f t="shared" si="33"/>
-        <v>107</v>
-      </c>
-      <c r="AS36" s="3">
-        <f t="shared" si="34"/>
-        <v>124</v>
-      </c>
-      <c r="AT36" s="3">
-        <v>10</v>
-      </c>
-      <c r="AU36" s="3">
-        <f t="shared" si="35"/>
-        <v>11</v>
-      </c>
-      <c r="AV36" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AW36" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AX36" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY36" s="37">
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
-        <v>1014</v>
-      </c>
-      <c r="B37" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="D37" s="6" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F37" s="19">
-        <v>9510600</v>
+        <v>90018000</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -7877,23 +7831,22 @@
         <v>7</v>
       </c>
       <c r="M37" s="3">
-        <f t="shared" si="22"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N37" s="3">
         <v>14</v>
       </c>
       <c r="O37" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P37" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="3">
         <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="P37" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q37" s="3">
-        <f t="shared" si="24"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R37" s="3">
         <f t="shared" si="4"/>
@@ -7903,7 +7856,7 @@
         <v>7</v>
       </c>
       <c r="T37" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U37" s="3">
@@ -7914,23 +7867,21 @@
         <v>2</v>
       </c>
       <c r="W37" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="X37" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y37" s="3">
+        <v>33</v>
+      </c>
+      <c r="Z37" s="6">
+        <v>39</v>
+      </c>
+      <c r="AA37" s="6">
         <f t="shared" si="18"/>
-        <v>33</v>
-      </c>
-      <c r="Z37" s="6">
-        <f t="shared" si="21"/>
-        <v>37</v>
-      </c>
-      <c r="AA37" s="6">
-        <f t="shared" si="19"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB37" s="3">
         <v>6</v>
@@ -7942,99 +7893,99 @@
         <v>8</v>
       </c>
       <c r="AE37" s="3">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="AF37" s="3">
+        <f t="shared" si="26"/>
+        <v>77</v>
+      </c>
+      <c r="AG37" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH37" s="6">
         <f t="shared" si="27"/>
-        <v>54</v>
-      </c>
-      <c r="AG37" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH37" s="6">
+        <v>80</v>
+      </c>
+      <c r="AI37" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="3">
         <f t="shared" si="28"/>
-        <v>57</v>
-      </c>
-      <c r="AI37" s="3">
-        <v>7</v>
-      </c>
-      <c r="AJ37" s="3">
+        <v>80</v>
+      </c>
+      <c r="AK37" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL37" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM37" s="3">
         <f t="shared" si="29"/>
-        <v>64</v>
-      </c>
-      <c r="AK37" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL37" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM37" s="3">
+        <v>82</v>
+      </c>
+      <c r="AN37" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO37" s="3">
         <f t="shared" si="30"/>
-        <v>64</v>
-      </c>
-      <c r="AN37" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="3">
+        <v>84</v>
+      </c>
+      <c r="AP37" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="3">
         <f t="shared" si="31"/>
-        <v>64</v>
-      </c>
-      <c r="AP37" s="3">
-        <v>5</v>
-      </c>
-      <c r="AQ37" s="3">
+        <v>84</v>
+      </c>
+      <c r="AR37" s="3">
         <f t="shared" si="32"/>
-        <v>69</v>
-      </c>
-      <c r="AR37" s="3">
+        <v>91</v>
+      </c>
+      <c r="AS37" s="3">
         <f t="shared" si="33"/>
-        <v>76</v>
-      </c>
-      <c r="AS37" s="3">
+        <v>98</v>
+      </c>
+      <c r="AT37" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU37" s="3">
         <f t="shared" si="34"/>
-        <v>83</v>
-      </c>
-      <c r="AT37" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU37" s="3">
-        <f t="shared" si="35"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV37" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW37" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX37" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY37" s="37">
-        <v>46142</v>
+        <v>75</v>
+      </c>
+      <c r="AY37" s="40">
+        <v>46507</v>
       </c>
     </row>
     <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>1015</v>
+        <v>1034</v>
       </c>
       <c r="B38" s="33" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="F38" s="19">
-        <v>90018000</v>
+        <v>91017300</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
@@ -8043,32 +7994,31 @@
         <v>26</v>
       </c>
       <c r="J38" s="2">
-        <v>261427</v>
+        <v>119640</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L38" s="3">
         <v>7</v>
       </c>
       <c r="M38" s="3">
-        <f t="shared" si="22"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N38" s="3">
         <v>14</v>
       </c>
       <c r="O38" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P38" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="3">
         <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="P38" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q38" s="3">
-        <f t="shared" si="24"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R38" s="3">
         <f t="shared" si="4"/>
@@ -8078,7 +8028,7 @@
         <v>7</v>
       </c>
       <c r="T38" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U38" s="3">
@@ -8086,130 +8036,128 @@
         <v>30</v>
       </c>
       <c r="V38" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W38" s="3">
+        <f t="shared" si="25"/>
+        <v>30</v>
+      </c>
+      <c r="X38" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <v>31</v>
+      </c>
+      <c r="Z38" s="6">
+        <v>33</v>
+      </c>
+      <c r="AA38" s="6">
+        <f t="shared" si="18"/>
+        <v>35</v>
+      </c>
+      <c r="AB38" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC38" s="3">
+        <v>4</v>
+      </c>
+      <c r="AD38" s="3">
+        <v>11</v>
+      </c>
+      <c r="AE38" s="3">
+        <v>53</v>
+      </c>
+      <c r="AF38" s="3">
         <f t="shared" si="26"/>
-        <v>31</v>
-      </c>
-      <c r="X38" s="3">
-        <v>5</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="18"/>
-        <v>33</v>
-      </c>
-      <c r="Z38" s="6">
-        <f t="shared" si="21"/>
-        <v>37</v>
-      </c>
-      <c r="AA38" s="6">
-        <f t="shared" si="19"/>
-        <v>42</v>
-      </c>
-      <c r="AB38" s="3">
-        <v>6</v>
-      </c>
-      <c r="AC38" s="3">
-        <v>8</v>
-      </c>
-      <c r="AD38" s="3">
-        <v>8</v>
-      </c>
-      <c r="AE38" s="3">
-        <v>32</v>
-      </c>
-      <c r="AF38" s="3">
+        <v>87</v>
+      </c>
+      <c r="AG38" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH38" s="6">
         <f t="shared" si="27"/>
-        <v>73</v>
-      </c>
-      <c r="AG38" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH38" s="6">
+        <v>90</v>
+      </c>
+      <c r="AI38" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="3">
         <f t="shared" si="28"/>
-        <v>76</v>
-      </c>
-      <c r="AI38" s="3">
-        <v>7</v>
-      </c>
-      <c r="AJ38" s="3">
-        <f t="shared" si="29"/>
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="AK38" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AL38" s="3">
         <v>2</v>
       </c>
       <c r="AM38" s="3">
+        <f t="shared" si="29"/>
+        <v>92</v>
+      </c>
+      <c r="AN38" s="3">
+        <v>6</v>
+      </c>
+      <c r="AO38" s="3">
         <f t="shared" si="30"/>
-        <v>85</v>
-      </c>
-      <c r="AN38" s="3">
-        <v>2</v>
-      </c>
-      <c r="AO38" s="3">
+        <v>98</v>
+      </c>
+      <c r="AP38" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="3">
         <f t="shared" si="31"/>
-        <v>87</v>
-      </c>
-      <c r="AP38" s="3">
-        <v>3</v>
-      </c>
-      <c r="AQ38" s="3">
+        <v>98</v>
+      </c>
+      <c r="AR38" s="3">
         <f t="shared" si="32"/>
-        <v>90</v>
-      </c>
-      <c r="AR38" s="3">
+        <v>105</v>
+      </c>
+      <c r="AS38" s="3">
         <f t="shared" si="33"/>
-        <v>97</v>
-      </c>
-      <c r="AS38" s="3">
+        <v>112</v>
+      </c>
+      <c r="AT38" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU38" s="3">
         <f t="shared" si="34"/>
-        <v>104</v>
-      </c>
-      <c r="AT38" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU38" s="3">
-        <f t="shared" si="35"/>
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AV38" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW38" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX38" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY38" s="37">
-        <v>46142</v>
+        <v>75</v>
+      </c>
+      <c r="AY38" s="40">
+        <v>46507</v>
       </c>
     </row>
     <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B39" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="F39" s="19">
-        <v>91017300</v>
+        <v>91017200</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -8218,32 +8166,31 @@
         <v>26</v>
       </c>
       <c r="J39" s="2">
-        <v>119640</v>
+        <v>261427</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L39" s="3">
         <v>7</v>
       </c>
       <c r="M39" s="3">
-        <f t="shared" si="22"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N39" s="3">
         <v>14</v>
       </c>
       <c r="O39" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P39" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="3">
         <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="P39" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q39" s="3">
-        <f t="shared" si="24"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R39" s="3">
         <f t="shared" si="4"/>
@@ -8253,7 +8200,7 @@
         <v>7</v>
       </c>
       <c r="T39" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U39" s="3">
@@ -8261,130 +8208,128 @@
         <v>30</v>
       </c>
       <c r="V39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W39" s="3">
+        <f t="shared" si="25"/>
+        <v>31</v>
+      </c>
+      <c r="X39" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <v>33</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>34</v>
+      </c>
+      <c r="AA39" s="6">
+        <f t="shared" si="18"/>
+        <v>36</v>
+      </c>
+      <c r="AB39" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC39" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD39" s="3">
+        <v>12</v>
+      </c>
+      <c r="AE39" s="3">
+        <v>31</v>
+      </c>
+      <c r="AF39" s="3">
         <f t="shared" si="26"/>
-        <v>30</v>
-      </c>
-      <c r="X39" s="3">
-        <v>3</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="18"/>
-        <v>31</v>
-      </c>
-      <c r="Z39" s="6">
-        <f t="shared" si="21"/>
-        <v>33</v>
-      </c>
-      <c r="AA39" s="6">
-        <f t="shared" si="19"/>
-        <v>34</v>
-      </c>
-      <c r="AB39" s="3">
-        <v>2</v>
-      </c>
-      <c r="AC39" s="3">
-        <v>4</v>
-      </c>
-      <c r="AD39" s="3">
-        <v>11</v>
-      </c>
-      <c r="AE39" s="3">
-        <v>52</v>
-      </c>
-      <c r="AF39" s="3">
+        <v>66</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH39" s="6">
         <f t="shared" si="27"/>
-        <v>85</v>
-      </c>
-      <c r="AG39" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH39" s="6">
+        <v>69</v>
+      </c>
+      <c r="AI39" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="3">
         <f t="shared" si="28"/>
-        <v>88</v>
-      </c>
-      <c r="AI39" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="3">
-        <f t="shared" si="29"/>
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="AK39" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AL39" s="3">
         <v>2</v>
       </c>
       <c r="AM39" s="3">
+        <f t="shared" si="29"/>
+        <v>71</v>
+      </c>
+      <c r="AN39" s="3">
+        <v>5</v>
+      </c>
+      <c r="AO39" s="3">
         <f t="shared" si="30"/>
-        <v>90</v>
-      </c>
-      <c r="AN39" s="3">
-        <v>3</v>
-      </c>
-      <c r="AO39" s="3">
+        <v>76</v>
+      </c>
+      <c r="AP39" s="3">
+        <v>1</v>
+      </c>
+      <c r="AQ39" s="3">
         <f t="shared" si="31"/>
-        <v>93</v>
-      </c>
-      <c r="AP39" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="3">
+        <v>77</v>
+      </c>
+      <c r="AR39" s="3">
         <f t="shared" si="32"/>
-        <v>93</v>
-      </c>
-      <c r="AR39" s="3">
+        <v>84</v>
+      </c>
+      <c r="AS39" s="3">
         <f t="shared" si="33"/>
-        <v>100</v>
-      </c>
-      <c r="AS39" s="3">
+        <v>91</v>
+      </c>
+      <c r="AT39" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU39" s="3">
         <f t="shared" si="34"/>
-        <v>107</v>
-      </c>
-      <c r="AT39" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU39" s="3">
-        <f t="shared" si="35"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV39" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW39" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX39" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY39" s="37">
-        <v>46142</v>
+        <v>75</v>
+      </c>
+      <c r="AY39" s="40">
+        <v>46507</v>
       </c>
     </row>
     <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B40" s="33" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F40" s="19">
-        <v>91017200</v>
+        <v>90016000</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
@@ -8393,32 +8338,31 @@
         <v>26</v>
       </c>
       <c r="J40" s="2">
-        <v>261427</v>
+        <v>119640</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L40" s="3">
         <v>7</v>
       </c>
       <c r="M40" s="3">
-        <f t="shared" si="22"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N40" s="3">
         <v>14</v>
       </c>
       <c r="O40" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P40" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="3">
         <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="P40" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="3">
-        <f t="shared" si="24"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R40" s="3">
         <f t="shared" si="4"/>
@@ -8428,7 +8372,7 @@
         <v>7</v>
       </c>
       <c r="T40" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U40" s="3">
@@ -8436,724 +8380,715 @@
         <v>30</v>
       </c>
       <c r="V40" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W40" s="3">
+        <f t="shared" si="25"/>
+        <v>30</v>
+      </c>
+      <c r="X40" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <v>31</v>
+      </c>
+      <c r="Z40" s="6">
+        <v>33</v>
+      </c>
+      <c r="AA40" s="6">
+        <f t="shared" si="18"/>
+        <v>36</v>
+      </c>
+      <c r="AB40" s="3">
+        <v>4</v>
+      </c>
+      <c r="AC40" s="3">
+        <v>4</v>
+      </c>
+      <c r="AD40" s="3">
+        <v>11</v>
+      </c>
+      <c r="AE40" s="3">
+        <v>67</v>
+      </c>
+      <c r="AF40" s="3">
         <f t="shared" si="26"/>
-        <v>31</v>
-      </c>
-      <c r="X40" s="3">
-        <v>5</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="18"/>
-        <v>33</v>
-      </c>
-      <c r="Z40" s="6">
-        <f t="shared" si="21"/>
-        <v>37</v>
-      </c>
-      <c r="AA40" s="6">
-        <f t="shared" si="19"/>
-        <v>39</v>
-      </c>
-      <c r="AB40" s="3">
-        <v>3</v>
-      </c>
-      <c r="AC40" s="3">
-        <v>5</v>
-      </c>
-      <c r="AD40" s="3">
-        <v>12</v>
-      </c>
-      <c r="AE40" s="3">
-        <v>28</v>
-      </c>
-      <c r="AF40" s="3">
+        <v>102</v>
+      </c>
+      <c r="AG40" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH40" s="6">
         <f t="shared" si="27"/>
-        <v>66</v>
-      </c>
-      <c r="AG40" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH40" s="6">
+        <v>105</v>
+      </c>
+      <c r="AI40" s="3">
+        <v>7</v>
+      </c>
+      <c r="AJ40" s="3">
         <f t="shared" si="28"/>
-        <v>69</v>
-      </c>
-      <c r="AI40" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ40" s="3">
+        <v>112</v>
+      </c>
+      <c r="AK40" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL40" s="3">
+        <v>3</v>
+      </c>
+      <c r="AM40" s="3">
         <f t="shared" si="29"/>
-        <v>69</v>
-      </c>
-      <c r="AK40" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL40" s="3">
-        <v>2</v>
-      </c>
-      <c r="AM40" s="3">
+        <v>115</v>
+      </c>
+      <c r="AN40" s="3">
+        <v>3</v>
+      </c>
+      <c r="AO40" s="3">
         <f t="shared" si="30"/>
-        <v>71</v>
-      </c>
-      <c r="AN40" s="3">
-        <v>2</v>
-      </c>
-      <c r="AO40" s="3">
-        <f t="shared" si="31"/>
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="AP40" s="3">
         <v>1</v>
       </c>
       <c r="AQ40" s="3">
+        <f t="shared" si="31"/>
+        <v>119</v>
+      </c>
+      <c r="AR40" s="3">
         <f t="shared" si="32"/>
-        <v>74</v>
-      </c>
-      <c r="AR40" s="3">
+        <v>126</v>
+      </c>
+      <c r="AS40" s="3">
         <f t="shared" si="33"/>
-        <v>81</v>
-      </c>
-      <c r="AS40" s="3">
+        <v>133</v>
+      </c>
+      <c r="AT40" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU40" s="3">
         <f t="shared" si="34"/>
-        <v>88</v>
-      </c>
-      <c r="AT40" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU40" s="3">
-        <f t="shared" si="35"/>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AV40" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AW40" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX40" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY40" s="37">
-        <v>46142</v>
+        <v>75</v>
+      </c>
+      <c r="AY40" s="40">
+        <v>46507</v>
       </c>
     </row>
     <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F41" s="19">
-        <v>90016000</v>
+        <v>91017700</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>34</v>
+        <v>158</v>
       </c>
       <c r="H41" s="2">
-        <v>0</v>
+        <v>222222</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="J41" s="2">
-        <v>119640</v>
+        <v>222222</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L41" s="3">
         <v>7</v>
       </c>
       <c r="M41" s="3">
+        <f t="shared" ref="M33:M52" si="35">+IF(I41="SFK Freight Forwarder",L41,9)</f>
+        <v>9</v>
+      </c>
+      <c r="N41" s="3">
+        <v>21</v>
+      </c>
+      <c r="O41" s="3">
         <f t="shared" si="22"/>
-        <v>7</v>
-      </c>
-      <c r="N41" s="3">
-        <v>14</v>
-      </c>
-      <c r="O41" s="3">
+        <v>29</v>
+      </c>
+      <c r="P41" s="3">
+        <f t="shared" si="19"/>
+        <v>5</v>
+      </c>
+      <c r="Q41" s="3">
         <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="P41" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3">
-        <f t="shared" si="24"/>
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="R41" s="3">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="S41" s="3">
         <v>7</v>
       </c>
       <c r="T41" s="3">
-        <f t="shared" si="25"/>
-        <v>29</v>
+        <f t="shared" si="24"/>
+        <v>36</v>
       </c>
       <c r="U41" s="3">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="V41" s="3">
         <v>1</v>
       </c>
       <c r="W41" s="3">
-        <f t="shared" si="26"/>
-        <v>30</v>
+        <f t="shared" si="25"/>
+        <v>37</v>
       </c>
       <c r="X41" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="3">
+        <v>37</v>
+      </c>
+      <c r="Z41" s="6">
+        <v>42</v>
+      </c>
+      <c r="AA41" s="6">
         <f t="shared" si="18"/>
-        <v>31</v>
-      </c>
-      <c r="Z41" s="6">
-        <f t="shared" si="21"/>
-        <v>33</v>
-      </c>
-      <c r="AA41" s="6">
-        <f t="shared" si="19"/>
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AB41" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC41" s="3">
         <v>4</v>
       </c>
       <c r="AD41" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE41" s="3">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AF41" s="3">
+        <f t="shared" si="26"/>
+        <v>83</v>
+      </c>
+      <c r="AG41" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH41" s="6">
         <f t="shared" si="27"/>
-        <v>95</v>
-      </c>
-      <c r="AG41" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH41" s="6">
+        <v>86</v>
+      </c>
+      <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="3">
         <f t="shared" si="28"/>
+        <v>86</v>
+      </c>
+      <c r="AK41" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL41" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM41" s="3">
+        <f t="shared" si="29"/>
+        <v>88</v>
+      </c>
+      <c r="AN41" s="3">
+        <v>3</v>
+      </c>
+      <c r="AO41" s="3">
+        <f t="shared" si="30"/>
+        <v>91</v>
+      </c>
+      <c r="AP41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ41" s="3">
+        <f t="shared" si="31"/>
+        <v>91</v>
+      </c>
+      <c r="AR41" s="3">
+        <f t="shared" si="32"/>
         <v>98</v>
       </c>
-      <c r="AI41" s="3">
-        <v>7</v>
-      </c>
-      <c r="AJ41" s="3">
-        <f t="shared" si="29"/>
+      <c r="AS41" s="3">
+        <f t="shared" si="33"/>
         <v>105</v>
       </c>
-      <c r="AK41" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL41" s="3">
-        <v>3</v>
-      </c>
-      <c r="AM41" s="3">
-        <f t="shared" si="30"/>
-        <v>108</v>
-      </c>
-      <c r="AN41" s="3">
-        <v>3</v>
-      </c>
-      <c r="AO41" s="3">
-        <f t="shared" si="31"/>
-        <v>111</v>
-      </c>
-      <c r="AP41" s="3">
-        <v>3</v>
-      </c>
-      <c r="AQ41" s="3">
-        <f t="shared" si="32"/>
-        <v>114</v>
-      </c>
-      <c r="AR41" s="3">
-        <f t="shared" si="33"/>
-        <v>121</v>
-      </c>
-      <c r="AS41" s="3">
+      <c r="AT41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU41" s="3">
         <f t="shared" si="34"/>
-        <v>136</v>
-      </c>
-      <c r="AT41" s="3">
-        <v>8</v>
-      </c>
-      <c r="AU41" s="3">
-        <f t="shared" si="35"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AV41" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AW41" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX41" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY41" s="37">
-        <v>46142</v>
+        <v>75</v>
+      </c>
+      <c r="AY41" s="21">
+        <v>46507</v>
       </c>
     </row>
     <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B42" s="33" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F42" s="19">
-        <v>91017700</v>
+        <v>26549502</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>159</v>
+        <v>48</v>
       </c>
       <c r="H42" s="2">
-        <v>222222</v>
+        <v>0</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="J42" s="2">
-        <v>222222</v>
+        <v>119640</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L42" s="3">
         <v>7</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>14</v>
+      </c>
+      <c r="O42" s="3">
         <f t="shared" si="22"/>
-        <v>9</v>
-      </c>
-      <c r="N42" s="3">
-        <v>21</v>
-      </c>
-      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <f t="shared" si="23"/>
-        <v>29</v>
-      </c>
-      <c r="P42" s="3">
-        <f t="shared" si="20"/>
-        <v>5</v>
-      </c>
-      <c r="Q42" s="3">
-        <f t="shared" si="24"/>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R42" s="3">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="S42" s="3">
         <v>7</v>
       </c>
       <c r="T42" s="3">
-        <f t="shared" si="25"/>
-        <v>36</v>
+        <f t="shared" si="24"/>
+        <v>29</v>
       </c>
       <c r="U42" s="3">
         <f t="shared" si="6"/>
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="V42" s="3">
         <v>1</v>
       </c>
       <c r="W42" s="3">
+        <f t="shared" si="25"/>
+        <v>30</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>31</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>33</v>
+      </c>
+      <c r="AA42" s="6">
+        <f t="shared" si="18"/>
+        <v>36</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>4</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>11</v>
+      </c>
+      <c r="AD42" s="3">
+        <v>11</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>32</v>
+      </c>
+      <c r="AF42" s="3">
         <f t="shared" si="26"/>
-        <v>37</v>
-      </c>
-      <c r="X42" s="3">
-        <v>2</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="18"/>
-        <v>37</v>
-      </c>
-      <c r="Z42" s="6">
-        <v>42</v>
-      </c>
-      <c r="AA42" s="6">
-        <f t="shared" si="19"/>
-        <v>44</v>
-      </c>
-      <c r="AB42" s="3">
-        <v>3</v>
-      </c>
-      <c r="AC42" s="3">
+        <v>67</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH42" s="6">
+        <f t="shared" si="27"/>
+        <v>70</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3">
+        <f t="shared" si="28"/>
+        <v>70</v>
+      </c>
+      <c r="AK42" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL42" s="3">
         <v>4</v>
       </c>
-      <c r="AD42" s="3">
-        <v>4</v>
-      </c>
-      <c r="AE42" s="3">
-        <v>40</v>
-      </c>
-      <c r="AF42" s="3">
-        <f t="shared" si="27"/>
-        <v>83</v>
-      </c>
-      <c r="AG42" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH42" s="6">
-        <f t="shared" si="28"/>
-        <v>86</v>
-      </c>
-      <c r="AI42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ42" s="3">
+      <c r="AM42" s="3">
         <f t="shared" si="29"/>
-        <v>86</v>
-      </c>
-      <c r="AK42" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL42" s="3">
-        <v>2</v>
-      </c>
-      <c r="AM42" s="3">
+        <v>74</v>
+      </c>
+      <c r="AN42" s="3">
+        <v>3</v>
+      </c>
+      <c r="AO42" s="3">
         <f t="shared" si="30"/>
-        <v>88</v>
-      </c>
-      <c r="AN42" s="3">
-        <v>3</v>
-      </c>
-      <c r="AO42" s="3">
+        <v>77</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="3">
         <f t="shared" si="31"/>
+        <v>77</v>
+      </c>
+      <c r="AR42" s="3">
+        <f t="shared" si="32"/>
+        <v>84</v>
+      </c>
+      <c r="AS42" s="3">
+        <f t="shared" si="33"/>
         <v>91</v>
       </c>
-      <c r="AP42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ42" s="3">
-        <f t="shared" si="32"/>
-        <v>91</v>
-      </c>
-      <c r="AR42" s="3">
-        <f t="shared" si="33"/>
-        <v>98</v>
-      </c>
-      <c r="AS42" s="3">
+      <c r="AT42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU42" s="3">
         <f t="shared" si="34"/>
-        <v>105</v>
-      </c>
-      <c r="AT42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU42" s="3">
-        <f t="shared" si="35"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV42" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AW42" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW42" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX42" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY42" s="21">
+        <v>75</v>
+      </c>
+      <c r="AY42" s="40">
         <v>46507</v>
       </c>
     </row>
     <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F43" s="19">
-        <v>26549502</v>
+        <v>90014400</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c r="H43" s="2">
-        <v>0</v>
+        <v>222222</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="J43" s="2">
-        <v>119640</v>
+        <v>222222</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L43" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M43" s="3">
+        <f t="shared" si="35"/>
+        <v>9</v>
+      </c>
+      <c r="N43" s="3">
+        <v>21</v>
+      </c>
+      <c r="O43" s="3">
         <f t="shared" si="22"/>
-        <v>7</v>
-      </c>
-      <c r="N43" s="3">
-        <v>14</v>
-      </c>
-      <c r="O43" s="3">
+        <v>29</v>
+      </c>
+      <c r="P43" s="3">
+        <f t="shared" si="19"/>
+        <v>5</v>
+      </c>
+      <c r="Q43" s="3">
         <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="P43" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
-        <f t="shared" si="24"/>
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="R43" s="3">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="S43" s="3">
         <v>7</v>
       </c>
       <c r="T43" s="3">
-        <f t="shared" si="25"/>
-        <v>29</v>
+        <f t="shared" si="24"/>
+        <v>36</v>
       </c>
       <c r="U43" s="3">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="V43" s="3">
         <v>1</v>
       </c>
       <c r="W43" s="3">
+        <f t="shared" si="25"/>
+        <v>37</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>37</v>
+      </c>
+      <c r="Z43" s="6">
+        <v>37</v>
+      </c>
+      <c r="AA43" s="6">
+        <f t="shared" si="18"/>
+        <v>39</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>46</v>
+      </c>
+      <c r="AF43" s="3">
         <f t="shared" si="26"/>
-        <v>30</v>
-      </c>
-      <c r="X43" s="3">
-        <v>3</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="18"/>
-        <v>31</v>
-      </c>
-      <c r="Z43" s="6">
-        <f>+Y43+X43-1</f>
-        <v>33</v>
-      </c>
-      <c r="AA43" s="6">
-        <f t="shared" si="19"/>
-        <v>37</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>5</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>11</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>11</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>32</v>
-      </c>
-      <c r="AF43" s="3">
+        <v>84</v>
+      </c>
+      <c r="AG43" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH43" s="6">
         <f t="shared" si="27"/>
-        <v>68</v>
-      </c>
-      <c r="AG43" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH43" s="6">
+        <v>87</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>7</v>
+      </c>
+      <c r="AJ43" s="3">
         <f t="shared" si="28"/>
-        <v>71</v>
-      </c>
-      <c r="AI43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ43" s="3">
+        <v>94</v>
+      </c>
+      <c r="AK43" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL43" s="3">
+        <v>4</v>
+      </c>
+      <c r="AM43" s="3">
         <f t="shared" si="29"/>
-        <v>71</v>
-      </c>
-      <c r="AK43" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL43" s="3">
-        <v>6</v>
-      </c>
-      <c r="AM43" s="3">
+        <v>98</v>
+      </c>
+      <c r="AN43" s="3">
+        <v>3</v>
+      </c>
+      <c r="AO43" s="3">
         <f t="shared" si="30"/>
-        <v>77</v>
-      </c>
-      <c r="AN43" s="3">
-        <v>3</v>
-      </c>
-      <c r="AO43" s="3">
+        <v>101</v>
+      </c>
+      <c r="AP43" s="3">
+        <v>4</v>
+      </c>
+      <c r="AQ43" s="3">
         <f t="shared" si="31"/>
-        <v>80</v>
-      </c>
-      <c r="AP43" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ43" s="3">
+        <v>105</v>
+      </c>
+      <c r="AR43" s="3">
         <f t="shared" si="32"/>
-        <v>82</v>
-      </c>
-      <c r="AR43" s="3">
+        <v>112</v>
+      </c>
+      <c r="AS43" s="3">
         <f t="shared" si="33"/>
-        <v>89</v>
-      </c>
-      <c r="AS43" s="3">
+        <v>119</v>
+      </c>
+      <c r="AT43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU43" s="3">
         <f t="shared" si="34"/>
-        <v>96</v>
-      </c>
-      <c r="AT43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU43" s="3">
-        <f t="shared" si="35"/>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AV43" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AW43" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX43" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY43" s="37">
-        <v>46142</v>
+        <v>88</v>
+      </c>
+      <c r="AY43" s="21">
+        <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>1045</v>
+        <v>1084</v>
       </c>
       <c r="B44" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="E44" s="6" t="s">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="F44" s="19">
-        <v>90014400</v>
+        <v>90018600</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>157</v>
       </c>
       <c r="H44" s="2">
-        <v>222222</v>
+        <v>333333</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J44" s="2">
-        <v>222222</v>
+        <v>333333</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L44" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M44" s="3">
+        <f t="shared" si="35"/>
+        <v>9</v>
+      </c>
+      <c r="N44" s="3">
+        <v>14</v>
+      </c>
+      <c r="O44" s="3">
         <f t="shared" si="22"/>
-        <v>9</v>
-      </c>
-      <c r="N44" s="3">
-        <v>21</v>
-      </c>
-      <c r="O44" s="3">
+        <v>22</v>
+      </c>
+      <c r="P44" s="3">
+        <f t="shared" si="19"/>
+        <v>5</v>
+      </c>
+      <c r="Q44" s="3">
         <f t="shared" si="23"/>
-        <v>29</v>
-      </c>
-      <c r="P44" s="3">
-        <f t="shared" si="20"/>
-        <v>5</v>
-      </c>
-      <c r="Q44" s="3">
-        <f t="shared" si="24"/>
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="R44" s="3">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="S44" s="3">
         <v>7</v>
       </c>
       <c r="T44" s="3">
-        <f t="shared" si="25"/>
-        <v>36</v>
+        <f t="shared" si="24"/>
+        <v>29</v>
       </c>
       <c r="U44" s="3">
         <f t="shared" si="6"/>
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="V44" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="3">
-        <f t="shared" si="26"/>
-        <v>37</v>
+        <f t="shared" si="25"/>
+        <v>31</v>
       </c>
       <c r="X44" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="3">
+        <v>36</v>
+      </c>
+      <c r="Z44" s="6">
+        <v>39</v>
+      </c>
+      <c r="AA44" s="6">
         <f t="shared" si="18"/>
-        <v>37</v>
-      </c>
-      <c r="Z44" s="6">
-        <v>37</v>
-      </c>
-      <c r="AA44" s="6">
-        <f t="shared" si="19"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AB44" s="3">
         <v>3</v>
@@ -9165,578 +9100,579 @@
         <v>5</v>
       </c>
       <c r="AE44" s="3">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="AF44" s="3">
+        <f t="shared" si="26"/>
+        <v>75</v>
+      </c>
+      <c r="AG44" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH44" s="6">
         <f t="shared" si="27"/>
+        <v>78</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="3">
+        <f t="shared" si="28"/>
+        <v>78</v>
+      </c>
+      <c r="AK44" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL44" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM44" s="3">
+        <f t="shared" si="29"/>
+        <v>80</v>
+      </c>
+      <c r="AN44" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO44" s="3">
+        <f t="shared" si="30"/>
+        <v>82</v>
+      </c>
+      <c r="AP44" s="3">
+        <v>2</v>
+      </c>
+      <c r="AQ44" s="3">
+        <f t="shared" si="31"/>
         <v>84</v>
       </c>
-      <c r="AG44" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH44" s="6">
-        <f t="shared" si="28"/>
-        <v>87</v>
-      </c>
-      <c r="AI44" s="3">
-        <v>7</v>
-      </c>
-      <c r="AJ44" s="3">
-        <f t="shared" si="29"/>
-        <v>94</v>
-      </c>
-      <c r="AK44" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL44" s="3">
-        <v>4</v>
-      </c>
-      <c r="AM44" s="3">
-        <f t="shared" si="30"/>
+      <c r="AR44" s="3">
+        <f t="shared" si="32"/>
+        <v>91</v>
+      </c>
+      <c r="AS44" s="3">
+        <f t="shared" si="33"/>
         <v>98</v>
       </c>
-      <c r="AN44" s="3">
-        <v>3</v>
-      </c>
-      <c r="AO44" s="3">
-        <f t="shared" si="31"/>
-        <v>101</v>
-      </c>
-      <c r="AP44" s="3">
-        <v>4</v>
-      </c>
-      <c r="AQ44" s="3">
-        <f t="shared" si="32"/>
-        <v>105</v>
-      </c>
-      <c r="AR44" s="3">
-        <f t="shared" si="33"/>
-        <v>112</v>
-      </c>
-      <c r="AS44" s="3">
+      <c r="AT44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU44" s="3">
         <f t="shared" si="34"/>
-        <v>119</v>
-      </c>
-      <c r="AT44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU44" s="3">
-        <f t="shared" si="35"/>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AV44" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AW44" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AX44" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY44" s="21">
         <v>46507</v>
       </c>
     </row>
     <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
-        <v>1084</v>
-      </c>
-      <c r="B45" s="33" t="s">
+      <c r="A45" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>54</v>
+      <c r="D45" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="F45" s="19">
-        <v>90018600</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>158</v>
+        <v>90016500</v>
+      </c>
+      <c r="G45" s="23" t="s">
+        <v>159</v>
       </c>
       <c r="H45" s="2">
-        <v>333333</v>
+        <v>0</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="J45" s="2">
-        <v>333333</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>50</v>
+        <v>29159</v>
+      </c>
+      <c r="K45" s="23" t="s">
+        <v>137</v>
       </c>
       <c r="L45" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M45" s="3">
+        <v>8</v>
+      </c>
+      <c r="N45" s="23">
+        <v>1</v>
+      </c>
+      <c r="O45" s="3">
         <f t="shared" si="22"/>
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
+        <v>6</v>
+      </c>
+      <c r="Q45" s="3">
+        <f t="shared" si="23"/>
+        <v>13</v>
+      </c>
+      <c r="R45" s="23">
         <v>9</v>
       </c>
-      <c r="N45" s="3">
+      <c r="S45" s="23">
+        <v>12</v>
+      </c>
+      <c r="T45" s="23">
+        <f t="shared" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="U45" s="23">
+        <f>+T45+2</f>
+        <v>22</v>
+      </c>
+      <c r="V45" s="23">
+        <v>5</v>
+      </c>
+      <c r="W45" s="23">
+        <f t="shared" si="25"/>
+        <v>26</v>
+      </c>
+      <c r="X45" s="23">
+        <v>4</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>29</v>
+      </c>
+      <c r="Z45" s="6">
+        <v>29</v>
+      </c>
+      <c r="AA45" s="6">
+        <v>31</v>
+      </c>
+      <c r="AB45" s="23">
+        <v>4</v>
+      </c>
+      <c r="AC45" s="23"/>
+      <c r="AD45" s="23"/>
+      <c r="AE45" s="33">
+        <v>41</v>
+      </c>
+      <c r="AF45" s="23">
+        <f t="shared" si="26"/>
+        <v>71</v>
+      </c>
+      <c r="AG45" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH45" s="23">
+        <f t="shared" si="27"/>
+        <v>74</v>
+      </c>
+      <c r="AI45" s="23">
+        <v>7</v>
+      </c>
+      <c r="AJ45" s="23">
+        <f t="shared" si="28"/>
+        <v>81</v>
+      </c>
+      <c r="AK45" s="23"/>
+      <c r="AL45" s="23">
+        <v>3</v>
+      </c>
+      <c r="AM45" s="23">
+        <f t="shared" si="29"/>
+        <v>84</v>
+      </c>
+      <c r="AN45" s="23">
+        <v>5</v>
+      </c>
+      <c r="AO45" s="23">
+        <f>+AM45+AN45</f>
+        <v>89</v>
+      </c>
+      <c r="AP45" s="23">
+        <v>6</v>
+      </c>
+      <c r="AQ45" s="23">
+        <v>92</v>
+      </c>
+      <c r="AR45" s="23">
+        <f>+AQ45+4</f>
+        <v>96</v>
+      </c>
+      <c r="AS45" s="23">
+        <f t="shared" si="33"/>
+        <v>117</v>
+      </c>
+      <c r="AT45" s="23">
         <v>14</v>
       </c>
-      <c r="O45" s="3">
-        <f t="shared" si="23"/>
+      <c r="AU45" s="3">
+        <f t="shared" si="34"/>
         <v>22</v>
       </c>
-      <c r="P45" s="3">
-        <f t="shared" si="20"/>
-        <v>5</v>
-      </c>
-      <c r="Q45" s="3">
-        <f t="shared" si="24"/>
-        <v>26</v>
-      </c>
-      <c r="R45" s="3">
-        <f t="shared" si="4"/>
-        <v>23</v>
-      </c>
-      <c r="S45" s="3">
-        <v>7</v>
-      </c>
-      <c r="T45" s="3">
-        <f t="shared" si="25"/>
-        <v>29</v>
-      </c>
-      <c r="U45" s="3">
-        <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-      <c r="V45" s="3">
-        <v>2</v>
-      </c>
-      <c r="W45" s="3">
-        <f t="shared" si="26"/>
-        <v>31</v>
-      </c>
-      <c r="X45" s="3">
-        <v>8</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="18"/>
-        <v>36</v>
-      </c>
-      <c r="Z45" s="6">
-        <v>39</v>
-      </c>
-      <c r="AA45" s="6">
-        <f t="shared" si="19"/>
-        <v>41</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>3</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>5</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>5</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>35</v>
-      </c>
-      <c r="AF45" s="3">
-        <f t="shared" si="27"/>
-        <v>75</v>
-      </c>
-      <c r="AG45" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH45" s="6">
-        <f t="shared" si="28"/>
-        <v>78</v>
-      </c>
-      <c r="AI45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ45" s="3">
-        <f t="shared" si="29"/>
-        <v>78</v>
-      </c>
-      <c r="AK45" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL45" s="3">
-        <v>2</v>
-      </c>
-      <c r="AM45" s="3">
-        <f t="shared" si="30"/>
-        <v>80</v>
-      </c>
-      <c r="AN45" s="3">
-        <v>2</v>
-      </c>
-      <c r="AO45" s="3">
-        <f t="shared" si="31"/>
-        <v>82</v>
-      </c>
-      <c r="AP45" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ45" s="3">
-        <f t="shared" si="32"/>
-        <v>84</v>
-      </c>
-      <c r="AR45" s="3">
-        <f t="shared" si="33"/>
-        <v>91</v>
-      </c>
-      <c r="AS45" s="3">
-        <f t="shared" si="34"/>
-        <v>98</v>
-      </c>
-      <c r="AT45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU45" s="3">
-        <f t="shared" si="35"/>
-        <v>18</v>
-      </c>
-      <c r="AV45" s="3" t="s">
+      <c r="AV45" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW45" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="AW45" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="AX45" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY45" s="21">
-        <v>46507</v>
+        <v>56</v>
+      </c>
+      <c r="AY45" s="37">
+        <v>46508</v>
       </c>
     </row>
     <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B46" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="19">
+        <v>91017700</v>
+      </c>
+      <c r="G46" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0</v>
+      </c>
+      <c r="I46" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E46" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="F46" s="19">
-        <v>90016500</v>
-      </c>
-      <c r="G46" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="H46" s="2">
-        <v>0</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="J46" s="2">
         <v>29159</v>
       </c>
       <c r="K46" s="23" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L46" s="3">
         <v>5</v>
       </c>
       <c r="M46" s="3">
-        <v>8</v>
+        <f t="shared" si="35"/>
+        <v>9</v>
       </c>
       <c r="N46" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O46" s="3">
+        <f t="shared" si="22"/>
+        <v>10</v>
+      </c>
+      <c r="P46" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="3">
         <f t="shared" si="23"/>
-        <v>8</v>
-      </c>
-      <c r="P46" s="3">
-        <v>6</v>
-      </c>
-      <c r="Q46" s="3">
-        <f t="shared" si="24"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R46" s="23">
         <v>9</v>
       </c>
       <c r="S46" s="23">
-        <v>12</v>
-      </c>
-      <c r="T46" s="23">
+        <v>13</v>
+      </c>
+      <c r="T46" s="25">
+        <f t="shared" si="24"/>
+        <v>21</v>
+      </c>
+      <c r="U46" s="23">
+        <v>16</v>
+      </c>
+      <c r="V46" s="23">
+        <v>7</v>
+      </c>
+      <c r="W46" s="23">
         <f t="shared" si="25"/>
-        <v>20</v>
-      </c>
-      <c r="U46" s="23">
-        <f>+T46+2</f>
         <v>22</v>
       </c>
-      <c r="V46" s="23">
-        <v>5</v>
-      </c>
-      <c r="W46" s="23">
-        <f t="shared" si="26"/>
-        <v>26</v>
-      </c>
       <c r="X46" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y46" s="3">
-        <v>29</v>
+        <f t="shared" si="20"/>
+        <v>22</v>
       </c>
       <c r="Z46" s="6">
-        <v>29</v>
+        <f t="shared" ref="Z46:Z52" si="36">+Y46+X46-1</f>
+        <v>22</v>
       </c>
       <c r="AA46" s="6">
-        <v>31</v>
+        <f t="shared" si="18"/>
+        <v>25</v>
       </c>
       <c r="AB46" s="23">
         <v>4</v>
       </c>
       <c r="AC46" s="23"/>
       <c r="AD46" s="23"/>
-      <c r="AE46" s="33">
-        <v>41</v>
+      <c r="AE46" s="23">
+        <v>39</v>
       </c>
       <c r="AF46" s="23">
+        <f t="shared" si="26"/>
+        <v>63</v>
+      </c>
+      <c r="AG46" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH46" s="23">
         <f t="shared" si="27"/>
-        <v>71</v>
-      </c>
-      <c r="AG46" s="23">
-        <v>3</v>
-      </c>
-      <c r="AH46" s="23">
+        <v>66</v>
+      </c>
+      <c r="AI46" s="23">
+        <v>7</v>
+      </c>
+      <c r="AJ46" s="23">
         <f t="shared" si="28"/>
-        <v>74</v>
-      </c>
-      <c r="AI46" s="23">
-        <v>7</v>
-      </c>
-      <c r="AJ46" s="23">
-        <f t="shared" si="29"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AK46" s="23"/>
       <c r="AL46" s="23">
         <v>3</v>
       </c>
       <c r="AM46" s="23">
+        <f t="shared" si="29"/>
+        <v>76</v>
+      </c>
+      <c r="AN46" s="23">
+        <v>2</v>
+      </c>
+      <c r="AO46" s="23">
         <f t="shared" si="30"/>
-        <v>84</v>
-      </c>
-      <c r="AN46" s="23">
-        <v>5</v>
-      </c>
-      <c r="AO46" s="23">
-        <f>+AM46+AN46</f>
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AP46" s="23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AQ46" s="23">
-        <v>92</v>
+        <f t="shared" si="31"/>
+        <v>80</v>
       </c>
       <c r="AR46" s="23">
-        <f>+AQ46+4</f>
-        <v>96</v>
+        <f t="shared" si="32"/>
+        <v>87</v>
       </c>
       <c r="AS46" s="23">
-        <f t="shared" si="34"/>
-        <v>117</v>
+        <f t="shared" si="33"/>
+        <v>108</v>
       </c>
       <c r="AT46" s="23">
         <v>14</v>
       </c>
       <c r="AU46" s="3">
-        <f t="shared" si="35"/>
-        <v>22</v>
+        <f t="shared" si="34"/>
+        <v>16</v>
       </c>
       <c r="AV46" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AW46" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX46" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY46" s="37">
-        <v>46508</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B47" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="C47" s="39" t="s">
-        <v>69</v>
+        <v>144</v>
+      </c>
+      <c r="B47" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="38" t="s">
+        <v>87</v>
       </c>
       <c r="D47" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E47" s="33" t="s">
-        <v>54</v>
-      </c>
       <c r="F47" s="19">
-        <v>91017700</v>
-      </c>
-      <c r="G47" s="35" t="s">
-        <v>159</v>
+        <v>90018600</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J47" s="2">
-        <v>29159</v>
-      </c>
-      <c r="K47" s="23" t="s">
-        <v>141</v>
+        <v>112741</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="L47" s="3">
+        <v>7</v>
+      </c>
+      <c r="M47" s="3">
+        <f t="shared" si="35"/>
+        <v>9</v>
+      </c>
+      <c r="N47" s="3">
+        <v>14</v>
+      </c>
+      <c r="O47" s="3">
+        <f t="shared" si="22"/>
+        <v>22</v>
+      </c>
+      <c r="P47" s="3">
+        <f t="shared" ref="P47:P52" si="37">+IF(I47="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
-      <c r="M47" s="3">
-        <f t="shared" si="22"/>
-        <v>9</v>
-      </c>
-      <c r="N47" s="23">
+      <c r="Q47" s="3">
+        <f t="shared" si="23"/>
+        <v>26</v>
+      </c>
+      <c r="R47" s="3">
+        <f t="shared" ref="R47:R52" si="38">9+N47</f>
+        <v>23</v>
+      </c>
+      <c r="S47" s="3">
+        <v>7</v>
+      </c>
+      <c r="T47" s="3">
+        <f t="shared" si="24"/>
+        <v>29</v>
+      </c>
+      <c r="U47" s="3">
+        <f t="shared" ref="U47:U52" si="39">+T47+1</f>
+        <v>30</v>
+      </c>
+      <c r="V47" s="3">
         <v>2</v>
       </c>
-      <c r="O47" s="3">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
-      <c r="P47" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q47" s="3">
-        <f t="shared" si="24"/>
-        <v>14</v>
-      </c>
-      <c r="R47" s="23">
-        <v>9</v>
-      </c>
-      <c r="S47" s="23">
-        <v>13</v>
-      </c>
-      <c r="T47" s="25">
+      <c r="W47" s="3">
         <f t="shared" si="25"/>
-        <v>21</v>
-      </c>
-      <c r="U47" s="23">
-        <v>16</v>
-      </c>
-      <c r="V47" s="23">
-        <v>7</v>
-      </c>
-      <c r="W47" s="23">
+        <v>31</v>
+      </c>
+      <c r="X47" s="3">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="20"/>
+        <v>31</v>
+      </c>
+      <c r="Z47" s="6">
+        <f t="shared" si="36"/>
+        <v>33</v>
+      </c>
+      <c r="AA47" s="6">
+        <f t="shared" si="18"/>
+        <v>34</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>2</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>4</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>11</v>
+      </c>
+      <c r="AE47" s="3">
+        <v>40</v>
+      </c>
+      <c r="AF47" s="3">
         <f t="shared" si="26"/>
-        <v>22</v>
-      </c>
-      <c r="X47" s="23">
-        <v>1</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="18"/>
-        <v>22</v>
-      </c>
-      <c r="Z47" s="6">
-        <f t="shared" ref="Z47:Z53" si="36">+Y47+X47-1</f>
-        <v>22</v>
-      </c>
-      <c r="AA47" s="6">
-        <f t="shared" si="19"/>
-        <v>25</v>
-      </c>
-      <c r="AB47" s="23">
-        <v>4</v>
-      </c>
-      <c r="AC47" s="23"/>
-      <c r="AD47" s="23"/>
-      <c r="AE47" s="23">
-        <v>39</v>
-      </c>
-      <c r="AF47" s="23">
+        <v>73</v>
+      </c>
+      <c r="AG47" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH47" s="6">
         <f t="shared" si="27"/>
-        <v>63</v>
-      </c>
-      <c r="AG47" s="23">
-        <v>3</v>
-      </c>
-      <c r="AH47" s="23">
+        <v>76</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3">
         <f t="shared" si="28"/>
-        <v>66</v>
-      </c>
-      <c r="AI47" s="23">
-        <v>7</v>
-      </c>
-      <c r="AJ47" s="23">
+        <v>76</v>
+      </c>
+      <c r="AK47" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL47" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM47" s="3">
         <f t="shared" si="29"/>
-        <v>73</v>
-      </c>
-      <c r="AK47" s="23"/>
-      <c r="AL47" s="23">
-        <v>3</v>
-      </c>
-      <c r="AM47" s="23">
+        <v>78</v>
+      </c>
+      <c r="AN47" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO47" s="3">
         <f t="shared" si="30"/>
-        <v>76</v>
-      </c>
-      <c r="AN47" s="23">
-        <v>2</v>
-      </c>
-      <c r="AO47" s="23">
+        <v>80</v>
+      </c>
+      <c r="AP47" s="3">
+        <v>6</v>
+      </c>
+      <c r="AQ47" s="3">
         <f t="shared" si="31"/>
-        <v>78</v>
-      </c>
-      <c r="AP47" s="23">
-        <v>2</v>
-      </c>
-      <c r="AQ47" s="23">
+        <v>86</v>
+      </c>
+      <c r="AR47" s="3">
         <f t="shared" si="32"/>
-        <v>80</v>
-      </c>
-      <c r="AR47" s="23">
+        <v>93</v>
+      </c>
+      <c r="AS47" s="3">
         <f t="shared" si="33"/>
-        <v>87</v>
-      </c>
-      <c r="AS47" s="23">
+        <v>100</v>
+      </c>
+      <c r="AT47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU47" s="3">
         <f t="shared" si="34"/>
-        <v>108</v>
-      </c>
-      <c r="AT47" s="23">
-        <v>14</v>
-      </c>
-      <c r="AU47" s="3">
-        <f t="shared" si="35"/>
-        <v>16</v>
-      </c>
-      <c r="AV47" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="AW47" s="23" t="s">
-        <v>132</v>
+        <v>11</v>
+      </c>
+      <c r="AV47" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW47" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="AX47" s="20" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="AY47" s="37">
-        <v>46143</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
@@ -9744,171 +9680,171 @@
         <v>145</v>
       </c>
       <c r="B48" s="39" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="E48" s="32" t="s">
-        <v>60</v>
+        <v>77</v>
+      </c>
+      <c r="E48" s="38" t="s">
+        <v>85</v>
       </c>
       <c r="F48" s="19">
-        <v>90018600</v>
+        <v>90012500</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J48" s="2">
-        <v>112741</v>
-      </c>
-      <c r="K48" s="7" t="s">
-        <v>38</v>
+        <v>29159</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="L48" s="3">
         <v>7</v>
       </c>
       <c r="M48" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="35"/>
         <v>9</v>
       </c>
       <c r="N48" s="3">
         <v>14</v>
       </c>
       <c r="O48" s="3">
+        <f t="shared" si="22"/>
+        <v>22</v>
+      </c>
+      <c r="P48" s="3">
+        <f t="shared" si="37"/>
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3">
         <f t="shared" si="23"/>
-        <v>22</v>
-      </c>
-      <c r="P48" s="3">
-        <f t="shared" ref="P48:P53" si="37">+IF(I48="SFK Freight Forwarder",0,5)</f>
-        <v>5</v>
-      </c>
-      <c r="Q48" s="3">
+        <v>26</v>
+      </c>
+      <c r="R48" s="3">
+        <f t="shared" si="38"/>
+        <v>23</v>
+      </c>
+      <c r="S48" s="3">
+        <v>7</v>
+      </c>
+      <c r="T48" s="3">
         <f t="shared" si="24"/>
-        <v>26</v>
-      </c>
-      <c r="R48" s="3">
-        <f t="shared" ref="R48:R53" si="38">9+N48</f>
-        <v>23</v>
-      </c>
-      <c r="S48" s="3">
-        <v>7</v>
-      </c>
-      <c r="T48" s="3">
-        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="U48" s="3">
-        <f t="shared" ref="U48:U53" si="39">+T48+1</f>
+        <f t="shared" si="39"/>
         <v>30</v>
       </c>
       <c r="V48" s="3">
         <v>2</v>
       </c>
       <c r="W48" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="X48" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y48" s="3">
+        <f t="shared" si="20"/>
+        <v>30</v>
+      </c>
+      <c r="Z48" s="6">
+        <f t="shared" si="36"/>
+        <v>31</v>
+      </c>
+      <c r="AA48" s="6">
         <f t="shared" si="18"/>
         <v>31</v>
       </c>
-      <c r="Z48" s="6">
-        <f t="shared" si="36"/>
-        <v>33</v>
-      </c>
-      <c r="AA48" s="6">
-        <f t="shared" si="19"/>
-        <v>34</v>
-      </c>
       <c r="AB48" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC48" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD48" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE48" s="3">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="AF48" s="3">
+        <f t="shared" si="26"/>
+        <v>88</v>
+      </c>
+      <c r="AG48" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH48" s="6">
         <f t="shared" si="27"/>
-        <v>73</v>
-      </c>
-      <c r="AG48" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH48" s="6">
+        <v>91</v>
+      </c>
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="3">
         <f t="shared" si="28"/>
-        <v>76</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ48" s="3">
-        <f t="shared" si="29"/>
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="AK48" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AL48" s="3">
         <v>2</v>
       </c>
       <c r="AM48" s="3">
+        <f t="shared" si="29"/>
+        <v>93</v>
+      </c>
+      <c r="AN48" s="3">
+        <v>7</v>
+      </c>
+      <c r="AO48" s="3">
         <f t="shared" si="30"/>
-        <v>78</v>
-      </c>
-      <c r="AN48" s="3">
-        <v>2</v>
-      </c>
-      <c r="AO48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP48" s="3">
+        <v>5</v>
+      </c>
+      <c r="AQ48" s="3">
         <f t="shared" si="31"/>
-        <v>80</v>
-      </c>
-      <c r="AP48" s="3">
-        <v>6</v>
-      </c>
-      <c r="AQ48" s="3">
+        <v>105</v>
+      </c>
+      <c r="AR48" s="3">
         <f t="shared" si="32"/>
-        <v>86</v>
-      </c>
-      <c r="AR48" s="3">
+        <v>112</v>
+      </c>
+      <c r="AS48" s="3">
         <f t="shared" si="33"/>
-        <v>93</v>
-      </c>
-      <c r="AS48" s="3">
+        <v>119</v>
+      </c>
+      <c r="AT48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU48" s="3">
         <f t="shared" si="34"/>
-        <v>100</v>
-      </c>
-      <c r="AT48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU48" s="3">
-        <f t="shared" si="35"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AV48" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AW48" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX48" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY48" s="37">
         <v>46142</v>
@@ -9919,47 +9855,47 @@
         <v>146</v>
       </c>
       <c r="B49" s="39" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C49" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="D49" s="38" t="s">
-        <v>78</v>
-      </c>
       <c r="E49" s="38" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="F49" s="19">
-        <v>90012500</v>
+        <v>91017500</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J49" s="2">
         <v>29159</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L49" s="3">
         <v>7</v>
       </c>
       <c r="M49" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="35"/>
         <v>9</v>
       </c>
       <c r="N49" s="3">
         <v>14</v>
       </c>
       <c r="O49" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>22</v>
       </c>
       <c r="P49" s="3">
@@ -9967,7 +9903,7 @@
         <v>5</v>
       </c>
       <c r="Q49" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>26</v>
       </c>
       <c r="R49" s="3">
@@ -9978,7 +9914,7 @@
         <v>7</v>
       </c>
       <c r="T49" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U49" s="3">
@@ -9989,14 +9925,14 @@
         <v>2</v>
       </c>
       <c r="W49" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="X49" s="3">
         <v>2</v>
       </c>
       <c r="Y49" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="Z49" s="6">
@@ -10004,86 +9940,86 @@
         <v>31</v>
       </c>
       <c r="AA49" s="6">
-        <f t="shared" si="19"/>
-        <v>31</v>
+        <f t="shared" si="18"/>
+        <v>36</v>
       </c>
       <c r="AB49" s="3">
+        <v>6</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>7</v>
+      </c>
+      <c r="AD49" s="3">
+        <v>7</v>
+      </c>
+      <c r="AE49" s="3">
+        <v>42</v>
+      </c>
+      <c r="AF49" s="3">
+        <f t="shared" si="26"/>
+        <v>77</v>
+      </c>
+      <c r="AG49" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH49" s="6">
+        <f t="shared" si="27"/>
+        <v>80</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="3">
+        <f t="shared" si="28"/>
+        <v>80</v>
+      </c>
+      <c r="AK49" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL49" s="3">
         <v>1</v>
       </c>
-      <c r="AC49" s="3">
-        <v>3</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>10</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>58</v>
-      </c>
-      <c r="AF49" s="3">
-        <f t="shared" si="27"/>
+      <c r="AM49" s="3">
+        <f t="shared" si="29"/>
+        <v>81</v>
+      </c>
+      <c r="AN49" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO49" s="3">
+        <f t="shared" si="30"/>
+        <v>82</v>
+      </c>
+      <c r="AP49" s="3">
+        <v>3</v>
+      </c>
+      <c r="AQ49" s="3">
+        <f t="shared" si="31"/>
+        <v>85</v>
+      </c>
+      <c r="AR49" s="3">
+        <f t="shared" si="32"/>
+        <v>92</v>
+      </c>
+      <c r="AS49" s="3">
+        <f t="shared" si="33"/>
+        <v>99</v>
+      </c>
+      <c r="AT49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU49" s="3">
+        <f t="shared" si="34"/>
+        <v>13</v>
+      </c>
+      <c r="AV49" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW49" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AX49" s="20" t="s">
         <v>88</v>
-      </c>
-      <c r="AG49" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH49" s="6">
-        <f t="shared" si="28"/>
-        <v>91</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ49" s="3">
-        <f t="shared" si="29"/>
-        <v>91</v>
-      </c>
-      <c r="AK49" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL49" s="3">
-        <v>2</v>
-      </c>
-      <c r="AM49" s="3">
-        <f t="shared" si="30"/>
-        <v>93</v>
-      </c>
-      <c r="AN49" s="3">
-        <v>7</v>
-      </c>
-      <c r="AO49" s="3">
-        <f t="shared" si="31"/>
-        <v>100</v>
-      </c>
-      <c r="AP49" s="3">
-        <v>5</v>
-      </c>
-      <c r="AQ49" s="3">
-        <f t="shared" si="32"/>
-        <v>105</v>
-      </c>
-      <c r="AR49" s="3">
-        <f t="shared" si="33"/>
-        <v>112</v>
-      </c>
-      <c r="AS49" s="3">
-        <f t="shared" si="34"/>
-        <v>119</v>
-      </c>
-      <c r="AT49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU49" s="3">
-        <f t="shared" si="35"/>
-        <v>8</v>
-      </c>
-      <c r="AV49" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AW49" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AX49" s="20" t="s">
-        <v>89</v>
       </c>
       <c r="AY49" s="37">
         <v>46142</v>
@@ -10094,47 +10030,47 @@
         <v>147</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E50" s="38" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F50" s="19">
-        <v>91017500</v>
+        <v>92000100</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="H50" s="2">
         <v>0</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J50" s="2">
         <v>29159</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L50" s="3">
         <v>7</v>
       </c>
       <c r="M50" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="35"/>
         <v>9</v>
       </c>
       <c r="N50" s="3">
         <v>14</v>
       </c>
       <c r="O50" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>22</v>
       </c>
       <c r="P50" s="3">
@@ -10142,7 +10078,7 @@
         <v>5</v>
       </c>
       <c r="Q50" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>26</v>
       </c>
       <c r="R50" s="3">
@@ -10153,7 +10089,7 @@
         <v>7</v>
       </c>
       <c r="T50" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U50" s="3">
@@ -10164,14 +10100,14 @@
         <v>2</v>
       </c>
       <c r="W50" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="X50" s="3">
         <v>2</v>
       </c>
       <c r="Y50" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="Z50" s="6">
@@ -10179,137 +10115,137 @@
         <v>31</v>
       </c>
       <c r="AA50" s="6">
-        <f t="shared" si="19"/>
-        <v>36</v>
+        <f t="shared" si="18"/>
+        <v>34</v>
       </c>
       <c r="AB50" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC50" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD50" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE50" s="3">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF50" s="3">
+        <f t="shared" si="26"/>
+        <v>81</v>
+      </c>
+      <c r="AG50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="6">
         <f t="shared" si="27"/>
-        <v>77</v>
-      </c>
-      <c r="AG50" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH50" s="6">
+        <v>81</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="3">
         <f t="shared" si="28"/>
-        <v>80</v>
-      </c>
-      <c r="AI50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ50" s="3">
+        <v>81</v>
+      </c>
+      <c r="AK50" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>3</v>
+      </c>
+      <c r="AM50" s="3">
         <f t="shared" si="29"/>
-        <v>80</v>
-      </c>
-      <c r="AK50" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL50" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM50" s="3">
+        <v>84</v>
+      </c>
+      <c r="AN50" s="3">
+        <v>8</v>
+      </c>
+      <c r="AO50" s="3">
         <f t="shared" si="30"/>
-        <v>81</v>
-      </c>
-      <c r="AN50" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO50" s="3">
+        <v>92</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
         <f t="shared" si="31"/>
-        <v>82</v>
-      </c>
-      <c r="AP50" s="3">
-        <v>3</v>
-      </c>
-      <c r="AQ50" s="3">
+        <v>92</v>
+      </c>
+      <c r="AR50" s="3">
         <f t="shared" si="32"/>
-        <v>85</v>
-      </c>
-      <c r="AR50" s="3">
+        <v>99</v>
+      </c>
+      <c r="AS50" s="3">
         <f t="shared" si="33"/>
-        <v>92</v>
-      </c>
-      <c r="AS50" s="3">
+        <v>106</v>
+      </c>
+      <c r="AT50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU50" s="3">
         <f t="shared" si="34"/>
-        <v>99</v>
-      </c>
-      <c r="AT50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU50" s="3">
-        <f t="shared" si="35"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AV50" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AW50" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX50" s="20" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AY50" s="37">
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>148</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E51" s="38" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F51" s="19">
-        <v>92000100</v>
+        <v>90014400</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>48</v>
+        <v>156</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J51" s="2">
-        <v>29159</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>144</v>
+        <v>112741</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="L51" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M51" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="35"/>
         <v>9</v>
       </c>
       <c r="N51" s="3">
         <v>14</v>
       </c>
       <c r="O51" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>22</v>
       </c>
       <c r="P51" s="3">
@@ -10317,7 +10253,7 @@
         <v>5</v>
       </c>
       <c r="Q51" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>26</v>
       </c>
       <c r="R51" s="3">
@@ -10328,7 +10264,7 @@
         <v>7</v>
       </c>
       <c r="T51" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="U51" s="3">
@@ -10339,101 +10275,101 @@
         <v>2</v>
       </c>
       <c r="W51" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="X51" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y51" s="3">
-        <f t="shared" si="18"/>
-        <v>30</v>
+        <f t="shared" si="20"/>
+        <v>31</v>
       </c>
       <c r="Z51" s="6">
         <f t="shared" si="36"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA51" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>34</v>
       </c>
       <c r="AB51" s="3">
+        <v>2</v>
+      </c>
+      <c r="AC51" s="3">
         <v>4</v>
       </c>
-      <c r="AC51" s="3">
-        <v>5</v>
-      </c>
       <c r="AD51" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE51" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF51" s="3">
+        <f t="shared" si="26"/>
+        <v>83</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH51" s="6">
         <f t="shared" si="27"/>
-        <v>81</v>
-      </c>
-      <c r="AG51" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="6">
+        <v>86</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3">
         <f t="shared" si="28"/>
-        <v>81</v>
-      </c>
-      <c r="AI51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ51" s="3">
+        <v>86</v>
+      </c>
+      <c r="AK51" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>4</v>
+      </c>
+      <c r="AM51" s="3">
         <f t="shared" si="29"/>
-        <v>81</v>
-      </c>
-      <c r="AK51" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL51" s="3">
-        <v>3</v>
-      </c>
-      <c r="AM51" s="3">
+        <v>90</v>
+      </c>
+      <c r="AN51" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO51" s="3">
         <f t="shared" si="30"/>
-        <v>84</v>
-      </c>
-      <c r="AN51" s="3">
-        <v>8</v>
-      </c>
-      <c r="AO51" s="3">
+        <v>92</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>1</v>
+      </c>
+      <c r="AQ51" s="3">
         <f t="shared" si="31"/>
-        <v>92</v>
-      </c>
-      <c r="AP51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ51" s="3">
+        <v>93</v>
+      </c>
+      <c r="AR51" s="3">
         <f t="shared" si="32"/>
-        <v>92</v>
-      </c>
-      <c r="AR51" s="3">
+        <v>100</v>
+      </c>
+      <c r="AS51" s="3">
         <f t="shared" si="33"/>
-        <v>99</v>
-      </c>
-      <c r="AS51" s="3">
+        <v>107</v>
+      </c>
+      <c r="AT51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU51" s="3">
         <f t="shared" si="34"/>
-        <v>106</v>
-      </c>
-      <c r="AT51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU51" s="3">
-        <f t="shared" si="35"/>
         <v>11</v>
       </c>
       <c r="AV51" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AW51" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AX51" s="20" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AY51" s="37">
         <v>46142</v>
@@ -10441,535 +10377,361 @@
     </row>
     <row r="52" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B52" s="39" t="s">
-        <v>62</v>
+        <v>153</v>
+      </c>
+      <c r="B52" s="38" t="s">
+        <v>83</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E52" s="38" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F52" s="19">
-        <v>90014400</v>
+        <v>90016000</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>157</v>
+        <v>34</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J52" s="2">
-        <v>112741</v>
-      </c>
-      <c r="K52" s="7" t="s">
-        <v>38</v>
+        <v>5915200</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="L52" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M52" s="3">
+        <f t="shared" si="35"/>
+        <v>9</v>
+      </c>
+      <c r="N52" s="3">
+        <v>7</v>
+      </c>
+      <c r="O52" s="3">
         <f t="shared" si="22"/>
-        <v>9</v>
-      </c>
-      <c r="N52" s="3">
-        <v>14</v>
-      </c>
-      <c r="O52" s="3">
-        <f t="shared" si="23"/>
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="P52" s="3">
         <f t="shared" si="37"/>
         <v>5</v>
       </c>
       <c r="Q52" s="3">
-        <f t="shared" si="24"/>
-        <v>26</v>
+        <f t="shared" si="23"/>
+        <v>19</v>
       </c>
       <c r="R52" s="3">
         <f t="shared" si="38"/>
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="S52" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T52" s="3">
-        <f t="shared" si="25"/>
-        <v>29</v>
+        <f t="shared" si="24"/>
+        <v>18</v>
       </c>
       <c r="U52" s="3">
         <f t="shared" si="39"/>
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="V52" s="3">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3">
+        <f t="shared" si="25"/>
+        <v>23</v>
+      </c>
+      <c r="X52" s="3">
         <v>2</v>
       </c>
-      <c r="W52" s="3">
-        <f t="shared" si="26"/>
-        <v>31</v>
-      </c>
-      <c r="X52" s="3">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3">
-        <f t="shared" si="18"/>
-        <v>31</v>
+        <f t="shared" si="20"/>
+        <v>23</v>
       </c>
       <c r="Z52" s="6">
         <f t="shared" si="36"/>
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="AA52" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
+        <v>26</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>34</v>
       </c>
-      <c r="AB52" s="3">
-        <v>2</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>4</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>11</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>50</v>
-      </c>
       <c r="AF52" s="3">
+        <f t="shared" si="26"/>
+        <v>59</v>
+      </c>
+      <c r="AG52" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH52" s="6">
         <f t="shared" si="27"/>
-        <v>83</v>
-      </c>
-      <c r="AG52" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH52" s="6">
+        <v>62</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>7</v>
+      </c>
+      <c r="AJ52" s="3">
         <f t="shared" si="28"/>
-        <v>86</v>
-      </c>
-      <c r="AI52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ52" s="3">
+        <v>69</v>
+      </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="3">
+        <v>6</v>
+      </c>
+      <c r="AM52" s="3">
         <f t="shared" si="29"/>
-        <v>86</v>
-      </c>
-      <c r="AK52" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL52" s="3">
-        <v>4</v>
-      </c>
-      <c r="AM52" s="3">
-        <f t="shared" si="30"/>
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN52" s="3">
         <v>2</v>
       </c>
       <c r="AO52" s="3">
+        <f t="shared" si="30"/>
+        <v>77</v>
+      </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="3">
         <f t="shared" si="31"/>
-        <v>92</v>
-      </c>
-      <c r="AP52" s="3">
-        <v>1</v>
-      </c>
-      <c r="AQ52" s="3">
+        <v>77</v>
+      </c>
+      <c r="AR52" s="3">
         <f t="shared" si="32"/>
-        <v>93</v>
-      </c>
-      <c r="AR52" s="3">
+        <v>84</v>
+      </c>
+      <c r="AS52" s="3">
         <f t="shared" si="33"/>
-        <v>100</v>
-      </c>
-      <c r="AS52" s="3">
+        <v>91</v>
+      </c>
+      <c r="AT52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU52" s="3">
         <f t="shared" si="34"/>
-        <v>107</v>
-      </c>
-      <c r="AT52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU52" s="3">
-        <f t="shared" si="35"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV52" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW52" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="AW52" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="AX52" s="20" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="AY52" s="37">
         <v>46142</v>
       </c>
     </row>
-    <row r="53" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="B53" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="E53" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="F53" s="19">
+        <v>90014400</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J53" s="2">
+        <v>29159</v>
+      </c>
+      <c r="K53" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="L53" s="3">
+        <v>5</v>
+      </c>
+      <c r="M53" s="3">
+        <f t="shared" ref="M53" si="40">+IF(I53="SFK Freight Forwarder",L53,9)</f>
+        <v>9</v>
+      </c>
+      <c r="N53" s="23">
+        <v>2</v>
+      </c>
+      <c r="O53" s="3">
+        <f t="shared" ref="O53" si="41">IF(I53="SFK Freight Forwarder",M53,M53+N53-1)</f>
+        <v>10</v>
+      </c>
+      <c r="P53" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q53" s="3">
+        <f t="shared" ref="Q53" si="42">+IF(I53="SFK Freight Forwarder",O53,O53+P53-1)</f>
+        <v>14</v>
+      </c>
+      <c r="R53" s="23">
+        <v>0</v>
+      </c>
+      <c r="S53" s="23">
+        <v>0</v>
+      </c>
+      <c r="T53" s="25">
+        <v>0</v>
+      </c>
+      <c r="U53" s="23">
+        <v>15</v>
+      </c>
+      <c r="V53" s="23">
+        <v>4</v>
+      </c>
+      <c r="W53" s="23">
+        <f t="shared" ref="W53" si="43">+U53+V53-1</f>
+        <v>18</v>
+      </c>
+      <c r="X53" s="23">
+        <v>1</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>18</v>
+      </c>
+      <c r="Z53" s="6">
+        <v>19</v>
+      </c>
+      <c r="AA53" s="6">
+        <f t="shared" ref="AA53" si="44">+Z53+AB53-1</f>
+        <v>22</v>
+      </c>
+      <c r="AB53" s="23">
+        <v>4</v>
+      </c>
+      <c r="AC53" s="23"/>
+      <c r="AD53" s="23"/>
+      <c r="AE53" s="23">
+        <v>46</v>
+      </c>
+      <c r="AF53" s="23">
+        <f t="shared" ref="AF53" si="45">+AE53+AA53-1</f>
+        <v>67</v>
+      </c>
+      <c r="AG53" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH53" s="23">
+        <f t="shared" ref="AH53" si="46">+AF53+AG53</f>
+        <v>70</v>
+      </c>
+      <c r="AI53" s="23">
+        <v>7</v>
+      </c>
+      <c r="AJ53" s="23">
+        <f t="shared" ref="AJ53" si="47">+AI53+AH53</f>
+        <v>77</v>
+      </c>
+      <c r="AK53" s="23"/>
+      <c r="AL53" s="23">
+        <v>3</v>
+      </c>
+      <c r="AM53" s="23">
+        <f t="shared" ref="AM53" si="48">+AJ53+AL53</f>
+        <v>80</v>
+      </c>
+      <c r="AN53" s="23">
+        <v>2</v>
+      </c>
+      <c r="AO53" s="23">
+        <f t="shared" ref="AO53" si="49">+AM53+AN53</f>
+        <v>82</v>
+      </c>
+      <c r="AP53" s="23">
+        <v>2</v>
+      </c>
+      <c r="AQ53" s="23">
+        <f t="shared" ref="AQ53" si="50">+AO53+AP53</f>
         <v>84</v>
       </c>
-      <c r="C53" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="D53" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="E53" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="F53" s="19">
-        <v>90016000</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H53" s="2">
-        <v>0</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="J53" s="2">
-        <v>5915200</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="L53" s="3">
-        <v>7</v>
-      </c>
-      <c r="M53" s="3">
-        <f t="shared" si="22"/>
-        <v>9</v>
-      </c>
-      <c r="N53" s="3">
-        <v>7</v>
-      </c>
-      <c r="O53" s="3">
-        <f t="shared" si="23"/>
-        <v>15</v>
-      </c>
-      <c r="P53" s="3">
-        <f t="shared" si="37"/>
-        <v>5</v>
-      </c>
-      <c r="Q53" s="3">
-        <f t="shared" si="24"/>
-        <v>19</v>
-      </c>
-      <c r="R53" s="3">
-        <f t="shared" si="38"/>
-        <v>16</v>
-      </c>
-      <c r="S53" s="3">
-        <v>3</v>
-      </c>
-      <c r="T53" s="3">
-        <f t="shared" si="25"/>
-        <v>18</v>
-      </c>
-      <c r="U53" s="3">
-        <f t="shared" si="39"/>
-        <v>19</v>
-      </c>
-      <c r="V53" s="3">
-        <v>5</v>
-      </c>
-      <c r="W53" s="3">
-        <f t="shared" si="26"/>
-        <v>23</v>
-      </c>
-      <c r="X53" s="3">
-        <v>2</v>
-      </c>
-      <c r="Y53" s="3">
-        <f t="shared" si="18"/>
-        <v>23</v>
-      </c>
-      <c r="Z53" s="6">
-        <f t="shared" si="36"/>
-        <v>24</v>
-      </c>
-      <c r="AA53" s="6">
-        <f t="shared" si="19"/>
-        <v>26</v>
-      </c>
-      <c r="AB53" s="3">
-        <v>3</v>
-      </c>
-      <c r="AC53" s="3">
-        <v>5</v>
-      </c>
-      <c r="AD53" s="3">
-        <v>5</v>
-      </c>
-      <c r="AE53" s="3">
-        <v>34</v>
-      </c>
-      <c r="AF53" s="3">
-        <f t="shared" si="27"/>
-        <v>59</v>
-      </c>
-      <c r="AG53" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH53" s="6">
-        <f t="shared" si="28"/>
-        <v>62</v>
-      </c>
-      <c r="AI53" s="3">
-        <v>7</v>
-      </c>
-      <c r="AJ53" s="3">
-        <f t="shared" si="29"/>
-        <v>69</v>
-      </c>
-      <c r="AK53" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL53" s="3">
-        <v>6</v>
-      </c>
-      <c r="AM53" s="3">
-        <f t="shared" si="30"/>
-        <v>75</v>
-      </c>
-      <c r="AN53" s="3">
-        <v>2</v>
-      </c>
-      <c r="AO53" s="3">
-        <f t="shared" si="31"/>
-        <v>77</v>
-      </c>
-      <c r="AP53" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ53" s="3">
-        <f t="shared" si="32"/>
-        <v>77</v>
-      </c>
-      <c r="AR53" s="3">
-        <f t="shared" si="33"/>
-        <v>84</v>
-      </c>
-      <c r="AS53" s="3">
-        <f t="shared" si="34"/>
+      <c r="AR53" s="23">
+        <f t="shared" ref="AR53" si="51">+AQ53+7</f>
         <v>91</v>
       </c>
-      <c r="AT53" s="3">
-        <v>0</v>
+      <c r="AS53" s="23">
+        <f t="shared" ref="AS53" si="52">+AR53+7+AT53</f>
+        <v>112</v>
+      </c>
+      <c r="AT53" s="23">
+        <v>14</v>
       </c>
       <c r="AU53" s="3">
-        <f t="shared" si="35"/>
-        <v>10</v>
-      </c>
-      <c r="AV53" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AW53" s="3" t="s">
-        <v>135</v>
+        <f t="shared" ref="AU53" si="53">+AA53-R53</f>
+        <v>22</v>
+      </c>
+      <c r="AV53" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW53" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="AX53" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AY53" s="37">
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B54" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="C54" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="D54" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="E54" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="F54" s="19">
-        <v>90014400</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="H54" s="2">
-        <v>0</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="J54" s="2">
-        <v>29159</v>
-      </c>
-      <c r="K54" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="L54" s="3">
-        <v>5</v>
-      </c>
-      <c r="M54" s="3">
-        <f t="shared" ref="M54" si="40">+IF(I54="SFK Freight Forwarder",L54,9)</f>
-        <v>9</v>
-      </c>
-      <c r="N54" s="23">
-        <v>2</v>
-      </c>
-      <c r="O54" s="3">
-        <f t="shared" ref="O54" si="41">IF(I54="SFK Freight Forwarder",M54,M54+N54-1)</f>
-        <v>10</v>
-      </c>
-      <c r="P54" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q54" s="3">
-        <f t="shared" ref="Q54" si="42">+IF(I54="SFK Freight Forwarder",O54,O54+P54-1)</f>
-        <v>14</v>
-      </c>
-      <c r="R54" s="23">
-        <v>0</v>
-      </c>
-      <c r="S54" s="23">
-        <v>0</v>
-      </c>
-      <c r="T54" s="25">
-        <v>0</v>
-      </c>
-      <c r="U54" s="23">
-        <v>15</v>
-      </c>
-      <c r="V54" s="23">
-        <v>4</v>
-      </c>
-      <c r="W54" s="23">
-        <f t="shared" ref="W54" si="43">+U54+V54-1</f>
-        <v>18</v>
-      </c>
-      <c r="X54" s="23">
-        <v>1</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>18</v>
-      </c>
-      <c r="Z54" s="6">
-        <v>19</v>
-      </c>
-      <c r="AA54" s="6">
-        <f t="shared" ref="AA54" si="44">+Z54+AB54-1</f>
-        <v>22</v>
-      </c>
-      <c r="AB54" s="23">
-        <v>4</v>
-      </c>
-      <c r="AC54" s="23"/>
-      <c r="AD54" s="23"/>
-      <c r="AE54" s="23">
-        <v>46</v>
-      </c>
-      <c r="AF54" s="23">
-        <f t="shared" ref="AF54" si="45">+AE54+AA54-1</f>
-        <v>67</v>
-      </c>
-      <c r="AG54" s="23">
-        <v>3</v>
-      </c>
-      <c r="AH54" s="23">
-        <f t="shared" ref="AH54" si="46">+AF54+AG54</f>
-        <v>70</v>
-      </c>
-      <c r="AI54" s="23">
-        <v>7</v>
-      </c>
-      <c r="AJ54" s="23">
-        <f t="shared" ref="AJ54" si="47">+AI54+AH54</f>
-        <v>77</v>
-      </c>
-      <c r="AK54" s="23"/>
-      <c r="AL54" s="23">
-        <v>3</v>
-      </c>
-      <c r="AM54" s="23">
-        <f t="shared" ref="AM54" si="48">+AJ54+AL54</f>
-        <v>80</v>
-      </c>
-      <c r="AN54" s="23">
-        <v>2</v>
-      </c>
-      <c r="AO54" s="23">
-        <f t="shared" ref="AO54" si="49">+AM54+AN54</f>
-        <v>82</v>
-      </c>
-      <c r="AP54" s="23">
-        <v>2</v>
-      </c>
-      <c r="AQ54" s="23">
-        <f t="shared" ref="AQ54" si="50">+AO54+AP54</f>
-        <v>84</v>
-      </c>
-      <c r="AR54" s="23">
-        <f t="shared" ref="AR54" si="51">+AQ54+7</f>
-        <v>91</v>
-      </c>
-      <c r="AS54" s="23">
-        <f t="shared" ref="AS54" si="52">+AR54+7+AT54</f>
-        <v>112</v>
-      </c>
-      <c r="AT54" s="23">
-        <v>14</v>
-      </c>
-      <c r="AU54" s="3">
-        <f t="shared" ref="AU54" si="53">+AA54-R54</f>
-        <v>22</v>
-      </c>
-      <c r="AV54" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="AW54" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="AX54" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="AY54" s="37">
         <v>46143</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY54" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
+  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
     <filterColumn colId="0">
       <filters>
-        <filter val="921"/>
+        <filter val="1015"/>
+        <filter val="1084"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 C16:E1048196 K16:K1048196" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 K16:K1048195 C16:E1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
       <formula1>shippername</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 K2:K54 J12:J54 I2:I54 C2:E1048196 H55:K1048196" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 H54:K1048195 C2:E1048195 I2:I53 J12:J53 K2:K53" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
       <formula1>AILNname</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048196" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048195" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">
       <formula1>plantname</formula1>
     </dataValidation>
   </dataValidations>
@@ -10989,35 +10751,35 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" t="s">
         <v>163</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" t="s">
         <v>164</v>
-      </c>
-      <c r="D2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" t="s">
         <v>166</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" t="s">
         <v>167</v>
-      </c>
-      <c r="D3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B08539-604C-451E-8BFD-100524CF3B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF73077-3B47-4431-97C9-86DBA6AD94CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="0" windowWidth="28935" windowHeight="15585" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="51765" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -1749,7 +1749,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>60</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>1015</v>
       </c>
@@ -8999,7 +8999,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>1084</v>
       </c>
@@ -10718,8 +10718,7 @@
   <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
     <filterColumn colId="0">
       <filters>
-        <filter val="1015"/>
-        <filter val="1084"/>
+        <filter val="60"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF73077-3B47-4431-97C9-86DBA6AD94CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61087A30-B407-45A1-A38A-714E690EB8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="51765" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -1212,7 +1212,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1550,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4" filterMode="1">
+  <sheetPr codeName="Feuil4">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF53"/>
@@ -1922,7 +1922,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>120</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>121</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>233</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>416</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>752</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>761</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>888</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>901</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>904</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>906</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>907</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>908</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>910</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>912</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>916</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>917</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>918</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>920</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5376,7 +5376,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>924</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>925</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>928</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>930</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>931</v>
       </c>
@@ -6413,7 +6413,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>932</v>
       </c>
@@ -6586,7 +6586,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>1005</v>
       </c>
@@ -6758,7 +6758,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>1006</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>1007</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>31</v>
       </c>
       <c r="Z32" s="6">
-        <f t="shared" ref="Z32:Z40" si="21">+Y32+X32-1</f>
+        <f t="shared" ref="Z32:Z35" si="21">+Y32+X32-1</f>
         <v>33</v>
       </c>
       <c r="AA32" s="6">
@@ -7104,7 +7104,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>1009</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>1010</v>
       </c>
@@ -7448,7 +7448,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>1012</v>
       </c>
@@ -7621,7 +7621,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>1014</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>1015</v>
       </c>
@@ -7965,7 +7965,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>1034</v>
       </c>
@@ -8137,7 +8137,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1036</v>
       </c>
@@ -8309,7 +8309,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>1037</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>1039</v>
       </c>
@@ -8519,7 +8519,7 @@
         <v>7</v>
       </c>
       <c r="M41" s="3">
-        <f t="shared" ref="M33:M52" si="35">+IF(I41="SFK Freight Forwarder",L41,9)</f>
+        <f t="shared" ref="M41:M52" si="35">+IF(I41="SFK Freight Forwarder",L41,9)</f>
         <v>9</v>
       </c>
       <c r="N41" s="3">
@@ -8654,7 +8654,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>1040</v>
       </c>
@@ -8826,7 +8826,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>1045</v>
       </c>
@@ -8999,7 +8999,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>1084</v>
       </c>
@@ -9172,7 +9172,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>138</v>
       </c>
@@ -9334,7 +9334,7 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>141</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>144</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>145</v>
       </c>
@@ -9850,7 +9850,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>146</v>
       </c>
@@ -10025,7 +10025,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="50" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>147</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>148</v>
       </c>
@@ -10375,7 +10375,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="52" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>153</v>
       </c>
@@ -10550,7 +10550,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>169</v>
       </c>
@@ -10715,13 +10715,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="60"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 K16:K1048195 C16:E1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61087A30-B407-45A1-A38A-714E690EB8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D324782C-1A39-4779-954A-12B55EB239D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -366,7 +366,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="173">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -791,9 +791,6 @@
     <t>WUHAN JINRUI TECH</t>
   </si>
   <si>
-    <t>O002</t>
-  </si>
-  <si>
     <t xml:space="preserve"> ILN/FF</t>
   </si>
   <si>
@@ -882,6 +879,12 @@
   </si>
   <si>
     <t>MAERSK</t>
+  </si>
+  <si>
+    <t>O010</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1095,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1213,6 +1216,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1550,7 +1556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4">
+  <sheetPr codeName="Feuil4" filterMode="1">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF53"/>
@@ -1608,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J1" s="12" t="s">
         <v>4</v>
@@ -1746,10 +1752,10 @@
         <v>63</v>
       </c>
       <c r="BF1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>60</v>
       </c>
@@ -1769,19 +1775,19 @@
         <v>90009500</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H2" s="2">
         <v>92000100</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J2" s="2">
         <v>92000100</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L2" s="3">
         <v>7</v>
@@ -1922,7 +1928,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>120</v>
       </c>
@@ -1942,7 +1948,7 @@
         <v>90009500</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H3" s="2">
         <v>2533780546</v>
@@ -2095,7 +2101,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>121</v>
       </c>
@@ -2115,7 +2121,7 @@
         <v>90009500</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H4" s="2">
         <v>2533780535</v>
@@ -2268,7 +2274,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>233</v>
       </c>
@@ -2288,7 +2294,7 @@
         <v>90009500</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H5" s="2">
         <v>91018400</v>
@@ -2441,7 +2447,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>416</v>
       </c>
@@ -2461,7 +2467,7 @@
         <v>90014400</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H6" s="2">
         <v>95207</v>
@@ -2614,7 +2620,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>752</v>
       </c>
@@ -2785,7 +2791,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>761</v>
       </c>
@@ -2955,7 +2961,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>888</v>
       </c>
@@ -3127,7 +3133,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>901</v>
       </c>
@@ -3147,7 +3153,7 @@
         <v>90012500</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H10" s="2">
         <v>95207</v>
@@ -3300,7 +3306,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>904</v>
       </c>
@@ -3314,13 +3320,13 @@
         <v>50</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F11" s="19">
         <v>90014400</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H11" s="2">
         <v>95436</v>
@@ -3473,7 +3479,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>906</v>
       </c>
@@ -3487,13 +3493,13 @@
         <v>62</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F12" s="19">
         <v>90018600</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H12" s="2">
         <v>95436</v>
@@ -3646,7 +3652,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>907</v>
       </c>
@@ -3666,7 +3672,7 @@
         <v>90018600</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H13" s="2">
         <v>95112</v>
@@ -3819,7 +3825,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>908</v>
       </c>
@@ -3839,7 +3845,7 @@
         <v>90018600</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H14" s="2">
         <v>28390</v>
@@ -3992,7 +3998,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>910</v>
       </c>
@@ -4006,25 +4012,25 @@
         <v>62</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F15" s="19">
         <v>90018600</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H15" s="2">
         <v>92000100</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J15" s="2">
         <v>92000100</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L15" s="3">
         <v>7</v>
@@ -4166,7 +4172,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>912</v>
       </c>
@@ -4186,7 +4192,7 @@
         <v>90018600</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H16" s="2">
         <v>2533780535</v>
@@ -4339,7 +4345,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -4359,7 +4365,7 @@
         <v>90012500</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H17" s="2">
         <v>2533780546</v>
@@ -4511,7 +4517,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>916</v>
       </c>
@@ -4531,7 +4537,7 @@
         <v>91017700</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H18" s="2">
         <v>95207</v>
@@ -4684,7 +4690,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>917</v>
       </c>
@@ -4704,7 +4710,7 @@
         <v>90014400</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H19" s="2">
         <v>2533780546</v>
@@ -4857,7 +4863,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>918</v>
       </c>
@@ -4877,7 +4883,7 @@
         <v>91017700</v>
       </c>
       <c r="G20" s="35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H20" s="2">
         <v>2533780546</v>
@@ -5030,7 +5036,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>920</v>
       </c>
@@ -5050,7 +5056,7 @@
         <v>91017500</v>
       </c>
       <c r="G21" s="35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H21" s="2">
         <v>2533780535</v>
@@ -5203,7 +5209,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5223,7 +5229,7 @@
         <v>90014400</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H22" s="2">
         <v>2533780535</v>
@@ -5376,7 +5382,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>924</v>
       </c>
@@ -5396,7 +5402,7 @@
         <v>90012500</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H23" s="2">
         <v>92050300</v>
@@ -5549,7 +5555,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>925</v>
       </c>
@@ -5557,7 +5563,7 @@
         <v>67</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>62</v>
@@ -5569,7 +5575,7 @@
         <v>90018600</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H24" s="2">
         <v>2533780546</v>
@@ -5722,7 +5728,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -5742,7 +5748,7 @@
         <v>90014400</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H25" s="2">
         <v>26037000</v>
@@ -5895,7 +5901,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>928</v>
       </c>
@@ -5915,7 +5921,7 @@
         <v>90018600</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H26" s="2">
         <v>91018400</v>
@@ -6068,7 +6074,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>930</v>
       </c>
@@ -6088,7 +6094,7 @@
         <v>91017700</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H27" s="2">
         <v>26037000</v>
@@ -6240,7 +6246,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>931</v>
       </c>
@@ -6260,7 +6266,7 @@
         <v>90018600</v>
       </c>
       <c r="G28" s="36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H28" s="2">
         <v>26037000</v>
@@ -6413,7 +6419,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>932</v>
       </c>
@@ -6433,7 +6439,7 @@
         <v>90012500</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H29" s="2">
         <v>26037000</v>
@@ -6586,7 +6592,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>1005</v>
       </c>
@@ -6758,7 +6764,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>1006</v>
       </c>
@@ -6930,7 +6936,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>1007</v>
       </c>
@@ -7104,7 +7110,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>1009</v>
       </c>
@@ -7118,7 +7124,7 @@
         <v>95</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F33" s="19">
         <v>90016700</v>
@@ -7276,7 +7282,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>1010</v>
       </c>
@@ -7448,7 +7454,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>1012</v>
       </c>
@@ -7621,7 +7627,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>1014</v>
       </c>
@@ -7793,7 +7799,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>1015</v>
       </c>
@@ -7965,7 +7971,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>1034</v>
       </c>
@@ -8137,7 +8143,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1036</v>
       </c>
@@ -8309,7 +8315,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>1037</v>
       </c>
@@ -8481,7 +8487,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>1039</v>
       </c>
@@ -8501,7 +8507,7 @@
         <v>91017700</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H41" s="2">
         <v>222222</v>
@@ -8654,7 +8660,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>1040</v>
       </c>
@@ -8826,7 +8832,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>1045</v>
       </c>
@@ -8846,7 +8852,7 @@
         <v>90014400</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H43" s="2">
         <v>222222</v>
@@ -8999,7 +9005,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>1084</v>
       </c>
@@ -9013,13 +9019,13 @@
         <v>62</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F44" s="19">
         <v>90018600</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H44" s="2">
         <v>333333</v>
@@ -9172,7 +9178,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>138</v>
       </c>
@@ -9192,7 +9198,7 @@
         <v>90016500</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -9334,27 +9340,27 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B46" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C46" s="39" t="s">
+      <c r="C46" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D46" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="E46" s="33" t="s">
-        <v>53</v>
+      <c r="D46" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="F46" s="19">
-        <v>91017700</v>
-      </c>
-      <c r="G46" s="35" t="s">
-        <v>158</v>
+        <v>90016500</v>
+      </c>
+      <c r="G46" s="23" t="s">
+        <v>159</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -9366,126 +9372,122 @@
         <v>29159</v>
       </c>
       <c r="K46" s="23" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L46" s="3">
         <v>5</v>
       </c>
       <c r="M46" s="3">
-        <f t="shared" si="35"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N46" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O46" s="3">
-        <f t="shared" si="22"/>
-        <v>10</v>
+        <f t="shared" ref="O46" si="36">IF(I46="SFK Freight Forwarder",M46,M46+N46-1)</f>
+        <v>8</v>
       </c>
       <c r="P46" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q46" s="3">
-        <f t="shared" si="23"/>
-        <v>14</v>
+        <f t="shared" ref="Q46" si="37">+IF(I46="SFK Freight Forwarder",O46,O46+P46-1)</f>
+        <v>13</v>
       </c>
       <c r="R46" s="23">
         <v>9</v>
       </c>
       <c r="S46" s="23">
-        <v>13</v>
-      </c>
-      <c r="T46" s="25">
-        <f t="shared" si="24"/>
-        <v>21</v>
+        <v>12</v>
+      </c>
+      <c r="T46" s="23">
+        <f t="shared" ref="T46" si="38">+R46+S46-1</f>
+        <v>20</v>
       </c>
       <c r="U46" s="23">
-        <v>16</v>
+        <f>+T46+2</f>
+        <v>22</v>
       </c>
       <c r="V46" s="23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W46" s="23">
-        <f t="shared" si="25"/>
-        <v>22</v>
+        <f t="shared" ref="W46" si="39">+U46+V46-1</f>
+        <v>26</v>
       </c>
       <c r="X46" s="23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y46" s="3">
-        <f t="shared" si="20"/>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Z46" s="6">
-        <f t="shared" ref="Z46:Z52" si="36">+Y46+X46-1</f>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AA46" s="6">
-        <f t="shared" si="18"/>
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AB46" s="23">
         <v>4</v>
       </c>
       <c r="AC46" s="23"/>
       <c r="AD46" s="23"/>
-      <c r="AE46" s="23">
-        <v>39</v>
+      <c r="AE46" s="33">
+        <v>34</v>
       </c>
       <c r="AF46" s="23">
-        <f t="shared" si="26"/>
-        <v>63</v>
+        <f t="shared" ref="AF46" si="40">+AE46+AA46-1</f>
+        <v>69</v>
       </c>
       <c r="AG46" s="23">
         <v>3</v>
       </c>
       <c r="AH46" s="23">
-        <f t="shared" si="27"/>
-        <v>66</v>
+        <f t="shared" ref="AH46" si="41">+AF46+AG46</f>
+        <v>72</v>
       </c>
       <c r="AI46" s="23">
         <v>7</v>
       </c>
       <c r="AJ46" s="23">
-        <f t="shared" si="28"/>
-        <v>73</v>
+        <f t="shared" ref="AJ46" si="42">+AI46+AH46</f>
+        <v>79</v>
       </c>
       <c r="AK46" s="23"/>
       <c r="AL46" s="23">
         <v>3</v>
       </c>
       <c r="AM46" s="23">
-        <f t="shared" si="29"/>
-        <v>76</v>
+        <f t="shared" ref="AM46" si="43">+AJ46+AL46</f>
+        <v>82</v>
       </c>
       <c r="AN46" s="23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO46" s="23">
-        <f t="shared" si="30"/>
-        <v>78</v>
+        <f>+AM46+AN46</f>
+        <v>87</v>
       </c>
       <c r="AP46" s="23">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AQ46" s="23">
-        <f t="shared" si="31"/>
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AR46" s="23">
-        <f t="shared" si="32"/>
-        <v>87</v>
+        <f>+AQ46+4</f>
+        <v>96</v>
       </c>
       <c r="AS46" s="23">
-        <f t="shared" si="33"/>
-        <v>108</v>
+        <f t="shared" ref="AS46" si="44">+AR46+7+AT46</f>
+        <v>117</v>
       </c>
       <c r="AT46" s="23">
         <v>14</v>
       </c>
       <c r="AU46" s="3">
-        <f t="shared" si="34"/>
-        <v>16</v>
+        <f t="shared" ref="AU46" si="45">+AA46-R46</f>
+        <v>27</v>
       </c>
       <c r="AV46" s="23" t="s">
         <v>133</v>
@@ -9497,12 +9499,12 @@
         <v>56</v>
       </c>
       <c r="AY46" s="37">
-        <v>46143</v>
+        <v>46508</v>
       </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B47" s="39" t="s">
         <v>67</v>
@@ -9520,7 +9522,7 @@
         <v>90018600</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -9549,7 +9551,7 @@
         <v>22</v>
       </c>
       <c r="P47" s="3">
-        <f t="shared" ref="P47:P52" si="37">+IF(I47="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P47:P52" si="46">+IF(I47="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q47" s="3">
@@ -9557,7 +9559,7 @@
         <v>26</v>
       </c>
       <c r="R47" s="3">
-        <f t="shared" ref="R47:R52" si="38">9+N47</f>
+        <f t="shared" ref="R47:R52" si="47">9+N47</f>
         <v>23</v>
       </c>
       <c r="S47" s="3">
@@ -9568,7 +9570,7 @@
         <v>29</v>
       </c>
       <c r="U47" s="3">
-        <f t="shared" ref="U47:U52" si="39">+T47+1</f>
+        <f t="shared" ref="U47:U52" si="48">+T47+1</f>
         <v>30</v>
       </c>
       <c r="V47" s="3">
@@ -9586,7 +9588,7 @@
         <v>31</v>
       </c>
       <c r="Z47" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="Z46:Z52" si="49">+Y47+X47-1</f>
         <v>33</v>
       </c>
       <c r="AA47" s="6">
@@ -9677,7 +9679,7 @@
     </row>
     <row r="48" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B48" s="39" t="s">
         <v>76</v>
@@ -9689,13 +9691,13 @@
         <v>77</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>85</v>
+        <v>172</v>
       </c>
       <c r="F48" s="19">
         <v>90012500</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
@@ -9707,7 +9709,7 @@
         <v>29159</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L48" s="3">
         <v>7</v>
@@ -9724,7 +9726,7 @@
         <v>22</v>
       </c>
       <c r="P48" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>5</v>
       </c>
       <c r="Q48" s="3">
@@ -9732,7 +9734,7 @@
         <v>26</v>
       </c>
       <c r="R48" s="3">
-        <f t="shared" si="38"/>
+        <f t="shared" si="47"/>
         <v>23</v>
       </c>
       <c r="S48" s="3">
@@ -9743,7 +9745,7 @@
         <v>29</v>
       </c>
       <c r="U48" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="48"/>
         <v>30</v>
       </c>
       <c r="V48" s="3">
@@ -9754,19 +9756,16 @@
         <v>31</v>
       </c>
       <c r="X48" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="3">
-        <f t="shared" si="20"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z48" s="6">
-        <f t="shared" si="36"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA48" s="6">
-        <f t="shared" si="18"/>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="AB48" s="3">
         <v>1</v>
@@ -9778,25 +9777,25 @@
         <v>10</v>
       </c>
       <c r="AE48" s="3">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="AF48" s="3">
         <f t="shared" si="26"/>
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="AG48" s="6">
         <v>3</v>
       </c>
       <c r="AH48" s="6">
         <f t="shared" si="27"/>
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="AI48" s="3">
         <v>0</v>
       </c>
       <c r="AJ48" s="3">
         <f t="shared" si="28"/>
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="AK48" s="3" t="s">
         <v>60</v>
@@ -9806,36 +9805,36 @@
       </c>
       <c r="AM48" s="3">
         <f t="shared" si="29"/>
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="AN48" s="3">
         <v>7</v>
       </c>
       <c r="AO48" s="3">
         <f t="shared" si="30"/>
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="AP48" s="3">
         <v>5</v>
       </c>
       <c r="AQ48" s="3">
         <f t="shared" si="31"/>
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="AR48" s="3">
         <f t="shared" si="32"/>
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="AS48" s="3">
         <f t="shared" si="33"/>
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="AT48" s="3">
         <v>0</v>
       </c>
       <c r="AU48" s="3">
         <f t="shared" si="34"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AV48" s="3" t="s">
         <v>133</v>
@@ -9847,12 +9846,12 @@
         <v>88</v>
       </c>
       <c r="AY48" s="37">
-        <v>46142</v>
+        <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B49" s="39" t="s">
         <v>80</v>
@@ -9867,10 +9866,10 @@
         <v>53</v>
       </c>
       <c r="F49" s="19">
-        <v>91017500</v>
+        <v>90016500</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -9882,7 +9881,7 @@
         <v>29159</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L49" s="3">
         <v>7</v>
@@ -9899,7 +9898,7 @@
         <v>22</v>
       </c>
       <c r="P49" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>5</v>
       </c>
       <c r="Q49" s="3">
@@ -9907,7 +9906,7 @@
         <v>26</v>
       </c>
       <c r="R49" s="3">
-        <f t="shared" si="38"/>
+        <f t="shared" si="47"/>
         <v>23</v>
       </c>
       <c r="S49" s="3">
@@ -9918,7 +9917,7 @@
         <v>29</v>
       </c>
       <c r="U49" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="48"/>
         <v>30</v>
       </c>
       <c r="V49" s="3">
@@ -9932,16 +9931,14 @@
         <v>2</v>
       </c>
       <c r="Y49" s="3">
-        <f t="shared" si="20"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Z49" s="6">
-        <f t="shared" si="36"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA49" s="6">
         <f t="shared" si="18"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB49" s="3">
         <v>6</v>
@@ -9953,25 +9950,25 @@
         <v>7</v>
       </c>
       <c r="AE49" s="3">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AF49" s="3">
         <f t="shared" si="26"/>
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AG49" s="6">
         <v>3</v>
       </c>
       <c r="AH49" s="6">
         <f t="shared" si="27"/>
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AI49" s="3">
         <v>0</v>
       </c>
       <c r="AJ49" s="3">
         <f t="shared" si="28"/>
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>60</v>
@@ -9981,36 +9978,36 @@
       </c>
       <c r="AM49" s="3">
         <f t="shared" si="29"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AN49" s="3">
         <v>1</v>
       </c>
       <c r="AO49" s="3">
         <f t="shared" si="30"/>
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AP49" s="3">
         <v>3</v>
       </c>
       <c r="AQ49" s="3">
         <f t="shared" si="31"/>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AR49" s="3">
         <f t="shared" si="32"/>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="AS49" s="3">
         <f t="shared" si="33"/>
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="AT49" s="3">
         <v>0</v>
       </c>
       <c r="AU49" s="3">
         <f t="shared" si="34"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AV49" s="3" t="s">
         <v>133</v>
@@ -10021,13 +10018,13 @@
       <c r="AX49" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="AY49" s="37">
-        <v>46142</v>
+      <c r="AY49" s="41">
+        <v>46507</v>
       </c>
     </row>
-    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B50" s="39" t="s">
         <v>70</v>
@@ -10057,7 +10054,7 @@
         <v>29159</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L50" s="3">
         <v>7</v>
@@ -10074,7 +10071,7 @@
         <v>22</v>
       </c>
       <c r="P50" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>5</v>
       </c>
       <c r="Q50" s="3">
@@ -10082,7 +10079,7 @@
         <v>26</v>
       </c>
       <c r="R50" s="3">
-        <f t="shared" si="38"/>
+        <f t="shared" si="47"/>
         <v>23</v>
       </c>
       <c r="S50" s="3">
@@ -10093,7 +10090,7 @@
         <v>29</v>
       </c>
       <c r="U50" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="48"/>
         <v>30</v>
       </c>
       <c r="V50" s="3">
@@ -10111,7 +10108,7 @@
         <v>30</v>
       </c>
       <c r="Z50" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="49"/>
         <v>31</v>
       </c>
       <c r="AA50" s="6">
@@ -10200,9 +10197,9 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B51" s="39" t="s">
         <v>61</v>
@@ -10220,7 +10217,7 @@
         <v>90014400</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
@@ -10249,7 +10246,7 @@
         <v>22</v>
       </c>
       <c r="P51" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>5</v>
       </c>
       <c r="Q51" s="3">
@@ -10257,7 +10254,7 @@
         <v>26</v>
       </c>
       <c r="R51" s="3">
-        <f t="shared" si="38"/>
+        <f t="shared" si="47"/>
         <v>23</v>
       </c>
       <c r="S51" s="3">
@@ -10268,7 +10265,7 @@
         <v>29</v>
       </c>
       <c r="U51" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="48"/>
         <v>30</v>
       </c>
       <c r="V51" s="3">
@@ -10286,7 +10283,7 @@
         <v>31</v>
       </c>
       <c r="Z51" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="49"/>
         <v>33</v>
       </c>
       <c r="AA51" s="6">
@@ -10375,9 +10372,9 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="52" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B52" s="38" t="s">
         <v>83</v>
@@ -10389,7 +10386,7 @@
         <v>86</v>
       </c>
       <c r="E52" s="38" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F52" s="19">
         <v>90016000</v>
@@ -10407,7 +10404,7 @@
         <v>5915200</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L52" s="3">
         <v>7</v>
@@ -10424,7 +10421,7 @@
         <v>15</v>
       </c>
       <c r="P52" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>5</v>
       </c>
       <c r="Q52" s="3">
@@ -10432,7 +10429,7 @@
         <v>19</v>
       </c>
       <c r="R52" s="3">
-        <f t="shared" si="38"/>
+        <f t="shared" si="47"/>
         <v>16</v>
       </c>
       <c r="S52" s="3">
@@ -10443,7 +10440,7 @@
         <v>18</v>
       </c>
       <c r="U52" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="48"/>
         <v>19</v>
       </c>
       <c r="V52" s="3">
@@ -10461,12 +10458,11 @@
         <v>23</v>
       </c>
       <c r="Z52" s="6">
-        <f t="shared" si="36"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA52" s="6">
         <f t="shared" si="18"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB52" s="3">
         <v>3</v>
@@ -10478,25 +10474,25 @@
         <v>5</v>
       </c>
       <c r="AE52" s="3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AF52" s="3">
         <f t="shared" si="26"/>
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AG52" s="6">
         <v>3</v>
       </c>
       <c r="AH52" s="6">
         <f t="shared" si="27"/>
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="AI52" s="3">
         <v>7</v>
       </c>
       <c r="AJ52" s="3">
         <f t="shared" si="28"/>
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="AK52" s="3">
         <v>0</v>
@@ -10506,36 +10502,36 @@
       </c>
       <c r="AM52" s="3">
         <f t="shared" si="29"/>
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN52" s="3">
         <v>2</v>
       </c>
       <c r="AO52" s="3">
         <f t="shared" si="30"/>
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AP52" s="3">
         <v>0</v>
       </c>
       <c r="AQ52" s="3">
         <f t="shared" si="31"/>
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AR52" s="3">
         <f t="shared" si="32"/>
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AS52" s="3">
         <f t="shared" si="33"/>
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="AT52" s="3">
         <v>0</v>
       </c>
       <c r="AU52" s="3">
         <f t="shared" si="34"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV52" s="3" t="s">
         <v>133</v>
@@ -10546,13 +10542,13 @@
       <c r="AX52" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AY52" s="37">
-        <v>46142</v>
+      <c r="AY52" s="41">
+        <v>46507</v>
       </c>
     </row>
-    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B53" s="38" t="s">
         <v>61</v>
@@ -10570,7 +10566,7 @@
         <v>90014400</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -10588,21 +10584,21 @@
         <v>5</v>
       </c>
       <c r="M53" s="3">
-        <f t="shared" ref="M53" si="40">+IF(I53="SFK Freight Forwarder",L53,9)</f>
+        <f t="shared" ref="M53" si="50">+IF(I53="SFK Freight Forwarder",L53,9)</f>
         <v>9</v>
       </c>
       <c r="N53" s="23">
         <v>2</v>
       </c>
       <c r="O53" s="3">
-        <f t="shared" ref="O53" si="41">IF(I53="SFK Freight Forwarder",M53,M53+N53-1)</f>
+        <f t="shared" ref="O53" si="51">IF(I53="SFK Freight Forwarder",M53,M53+N53-1)</f>
         <v>10</v>
       </c>
       <c r="P53" s="3">
         <v>5</v>
       </c>
       <c r="Q53" s="3">
-        <f t="shared" ref="Q53" si="42">+IF(I53="SFK Freight Forwarder",O53,O53+P53-1)</f>
+        <f t="shared" ref="Q53" si="52">+IF(I53="SFK Freight Forwarder",O53,O53+P53-1)</f>
         <v>14</v>
       </c>
       <c r="R53" s="23">
@@ -10621,7 +10617,7 @@
         <v>4</v>
       </c>
       <c r="W53" s="23">
-        <f t="shared" ref="W53" si="43">+U53+V53-1</f>
+        <f t="shared" ref="W53" si="53">+U53+V53-1</f>
         <v>18</v>
       </c>
       <c r="X53" s="23">
@@ -10634,7 +10630,7 @@
         <v>19</v>
       </c>
       <c r="AA53" s="6">
-        <f t="shared" ref="AA53" si="44">+Z53+AB53-1</f>
+        <f t="shared" ref="AA53" si="54">+Z53+AB53-1</f>
         <v>22</v>
       </c>
       <c r="AB53" s="23">
@@ -10646,21 +10642,21 @@
         <v>46</v>
       </c>
       <c r="AF53" s="23">
-        <f t="shared" ref="AF53" si="45">+AE53+AA53-1</f>
+        <f t="shared" ref="AF53" si="55">+AE53+AA53-1</f>
         <v>67</v>
       </c>
       <c r="AG53" s="23">
         <v>3</v>
       </c>
       <c r="AH53" s="23">
-        <f t="shared" ref="AH53" si="46">+AF53+AG53</f>
+        <f t="shared" ref="AH53" si="56">+AF53+AG53</f>
         <v>70</v>
       </c>
       <c r="AI53" s="23">
         <v>7</v>
       </c>
       <c r="AJ53" s="23">
-        <f t="shared" ref="AJ53" si="47">+AI53+AH53</f>
+        <f t="shared" ref="AJ53" si="57">+AI53+AH53</f>
         <v>77</v>
       </c>
       <c r="AK53" s="23"/>
@@ -10668,36 +10664,36 @@
         <v>3</v>
       </c>
       <c r="AM53" s="23">
-        <f t="shared" ref="AM53" si="48">+AJ53+AL53</f>
+        <f t="shared" ref="AM53" si="58">+AJ53+AL53</f>
         <v>80</v>
       </c>
       <c r="AN53" s="23">
         <v>2</v>
       </c>
       <c r="AO53" s="23">
-        <f t="shared" ref="AO53" si="49">+AM53+AN53</f>
+        <f t="shared" ref="AO53" si="59">+AM53+AN53</f>
         <v>82</v>
       </c>
       <c r="AP53" s="23">
         <v>2</v>
       </c>
       <c r="AQ53" s="23">
-        <f t="shared" ref="AQ53" si="50">+AO53+AP53</f>
+        <f t="shared" ref="AQ53" si="60">+AO53+AP53</f>
         <v>84</v>
       </c>
       <c r="AR53" s="23">
-        <f t="shared" ref="AR53" si="51">+AQ53+7</f>
+        <f t="shared" ref="AR53" si="61">+AQ53+7</f>
         <v>91</v>
       </c>
       <c r="AS53" s="23">
-        <f t="shared" ref="AS53" si="52">+AR53+7+AT53</f>
+        <f t="shared" ref="AS53" si="62">+AR53+7+AT53</f>
         <v>112</v>
       </c>
       <c r="AT53" s="23">
         <v>14</v>
       </c>
       <c r="AU53" s="3">
-        <f t="shared" ref="AU53" si="53">+AA53-R53</f>
+        <f t="shared" ref="AU53" si="63">+AA53-R53</f>
         <v>22</v>
       </c>
       <c r="AV53" s="23" t="s">
@@ -10715,13 +10711,24 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
+  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="O004"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="JPYOK"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 K16:K1048195 C16:E1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
       <formula1>shippername</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 H54:K1048195 C2:E1048195 I2:I53 J12:J53 K2:K53" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 H54:K1048195 K2:K53 J12:J53 I2:I53 C2:E1048195" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
       <formula1>AILNname</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048195" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">
@@ -10744,35 +10751,35 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" t="s">
         <v>162</v>
-      </c>
-      <c r="C2" t="s">
-        <v>163</v>
       </c>
       <c r="D2" t="s">
         <v>133</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" t="s">
         <v>165</v>
-      </c>
-      <c r="C3" t="s">
-        <v>166</v>
       </c>
       <c r="D3" t="s">
         <v>133</v>
       </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D324782C-1A39-4779-954A-12B55EB239D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B982F05A-18E9-4BA7-92FB-206CDAEABDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -1556,7 +1556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4" filterMode="1">
+  <sheetPr codeName="Feuil4">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF53"/>
@@ -1755,7 +1755,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>60</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>120</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>121</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>233</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>416</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>752</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>761</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>888</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>901</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>904</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>906</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>907</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>908</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>910</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>912</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>916</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>917</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>918</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>920</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>924</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>925</v>
       </c>
@@ -5728,7 +5728,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>928</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>930</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>931</v>
       </c>
@@ -6419,7 +6419,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>932</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>1005</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>1006</v>
       </c>
@@ -6936,7 +6936,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>1007</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>1009</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>1010</v>
       </c>
@@ -7454,7 +7454,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>1012</v>
       </c>
@@ -7627,7 +7627,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>1014</v>
       </c>
@@ -7799,7 +7799,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>1015</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>1034</v>
       </c>
@@ -8143,7 +8143,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1036</v>
       </c>
@@ -8315,7 +8315,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>1037</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>1039</v>
       </c>
@@ -8660,7 +8660,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>1040</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>1045</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>1084</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>138</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>171</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>143</v>
       </c>
@@ -9849,7 +9849,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>145</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="50" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>146</v>
       </c>
@@ -10197,7 +10197,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>147</v>
       </c>
@@ -10372,7 +10372,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="52" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>152</v>
       </c>
@@ -10546,7 +10546,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>168</v>
       </c>
@@ -10559,7 +10559,7 @@
       <c r="D53" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="E53" s="33" t="s">
+      <c r="E53" s="38" t="s">
         <v>81</v>
       </c>
       <c r="F53" s="19">
@@ -10711,18 +10711,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="O004"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="JPYOK"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 K16:K1048195 C16:E1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B982F05A-18E9-4BA7-92FB-206CDAEABDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FB66B7-7CC1-4730-AC7F-497F91A353D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -881,10 +881,10 @@
     <t>MAERSK</t>
   </si>
   <si>
-    <t>O010</t>
-  </si>
-  <si>
     <t>Hapag-Lloyd</t>
+  </si>
+  <si>
+    <t>O002</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1095,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1216,9 +1216,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1556,39 +1553,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4">
+  <sheetPr codeName="Feuil4" filterMode="1">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.453125" defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.42578125" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="1" max="1" width="9.54296875" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.453125" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.453125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="10.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" customWidth="1"/>
-    <col min="15" max="28" width="10.42578125" customWidth="1"/>
-    <col min="29" max="30" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="31" max="34" width="10.42578125" customWidth="1"/>
-    <col min="35" max="36" width="15.140625" customWidth="1"/>
-    <col min="37" max="37" width="15.85546875" customWidth="1"/>
-    <col min="38" max="39" width="9.5703125" customWidth="1"/>
-    <col min="40" max="41" width="15.42578125" customWidth="1"/>
-    <col min="42" max="42" width="10.42578125" customWidth="1" collapsed="1"/>
-    <col min="43" max="49" width="10.42578125" customWidth="1"/>
-    <col min="50" max="50" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.26953125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.54296875" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.81640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.453125" style="9" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="10.453125" customWidth="1"/>
+    <col min="14" max="14" width="14.54296875" customWidth="1"/>
+    <col min="15" max="28" width="10.453125" customWidth="1"/>
+    <col min="29" max="30" width="10.453125" hidden="1" customWidth="1"/>
+    <col min="31" max="34" width="10.453125" customWidth="1"/>
+    <col min="35" max="36" width="15.1796875" customWidth="1"/>
+    <col min="37" max="37" width="15.81640625" customWidth="1"/>
+    <col min="38" max="39" width="9.54296875" customWidth="1"/>
+    <col min="40" max="41" width="15.453125" customWidth="1"/>
+    <col min="42" max="42" width="10.453125" customWidth="1" collapsed="1"/>
+    <col min="43" max="49" width="10.453125" customWidth="1"/>
+    <col min="50" max="50" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.26953125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
@@ -1755,7 +1752,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>60</v>
       </c>
@@ -1928,7 +1925,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>120</v>
       </c>
@@ -2101,7 +2098,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>121</v>
       </c>
@@ -2274,7 +2271,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>233</v>
       </c>
@@ -2447,7 +2444,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>416</v>
       </c>
@@ -2620,7 +2617,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>752</v>
       </c>
@@ -2791,7 +2788,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>761</v>
       </c>
@@ -2961,7 +2958,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>888</v>
       </c>
@@ -3133,7 +3130,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>901</v>
       </c>
@@ -3306,7 +3303,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>904</v>
       </c>
@@ -3479,7 +3476,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>906</v>
       </c>
@@ -3652,7 +3649,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>907</v>
       </c>
@@ -3825,7 +3822,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>908</v>
       </c>
@@ -3998,7 +3995,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>910</v>
       </c>
@@ -4172,7 +4169,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>912</v>
       </c>
@@ -4345,7 +4342,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -4517,7 +4514,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>916</v>
       </c>
@@ -4690,7 +4687,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>917</v>
       </c>
@@ -4863,7 +4860,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>918</v>
       </c>
@@ -5036,7 +5033,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>920</v>
       </c>
@@ -5209,7 +5206,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5382,7 +5379,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>924</v>
       </c>
@@ -5555,7 +5552,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>925</v>
       </c>
@@ -5728,7 +5725,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -5901,7 +5898,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>928</v>
       </c>
@@ -6074,7 +6071,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>930</v>
       </c>
@@ -6246,7 +6243,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>931</v>
       </c>
@@ -6419,7 +6416,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>932</v>
       </c>
@@ -6592,7 +6589,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>1005</v>
       </c>
@@ -6764,7 +6761,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>1006</v>
       </c>
@@ -6936,7 +6933,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>1007</v>
       </c>
@@ -7110,7 +7107,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>1009</v>
       </c>
@@ -7282,7 +7279,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>1010</v>
       </c>
@@ -7454,7 +7451,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>1012</v>
       </c>
@@ -7627,7 +7624,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>1014</v>
       </c>
@@ -7799,7 +7796,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>1015</v>
       </c>
@@ -7971,7 +7968,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>1034</v>
       </c>
@@ -8143,7 +8140,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>1036</v>
       </c>
@@ -8315,7 +8312,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>1037</v>
       </c>
@@ -8487,7 +8484,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>1039</v>
       </c>
@@ -8660,7 +8657,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>1040</v>
       </c>
@@ -8832,7 +8829,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>1045</v>
       </c>
@@ -9005,7 +9002,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>1084</v>
       </c>
@@ -9178,7 +9175,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>138</v>
       </c>
@@ -9340,9 +9337,9 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>80</v>
@@ -9502,7 +9499,7 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>143</v>
       </c>
@@ -9588,7 +9585,7 @@
         <v>31</v>
       </c>
       <c r="Z47" s="6">
-        <f t="shared" ref="Z46:Z52" si="49">+Y47+X47-1</f>
+        <f t="shared" ref="Z47:Z51" si="49">+Y47+X47-1</f>
         <v>33</v>
       </c>
       <c r="AA47" s="6">
@@ -9677,7 +9674,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>144</v>
       </c>
@@ -9691,7 +9688,7 @@
         <v>77</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F48" s="19">
         <v>90012500</v>
@@ -9849,7 +9846,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>145</v>
       </c>
@@ -10018,11 +10015,11 @@
       <c r="AX49" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="AY49" s="41">
+      <c r="AY49" s="40">
         <v>46507</v>
       </c>
     </row>
-    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>146</v>
       </c>
@@ -10197,7 +10194,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>147</v>
       </c>
@@ -10372,7 +10369,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="52" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>152</v>
       </c>
@@ -10542,11 +10539,11 @@
       <c r="AX52" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AY52" s="41">
+      <c r="AY52" s="40">
         <v>46507</v>
       </c>
     </row>
-    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>168</v>
       </c>
@@ -10711,7 +10708,14 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
+  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="O001"/>
+        <filter val="O010"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 K16:K1048195 C16:E1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
@@ -10736,9 +10740,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7007F1-B98C-4FB4-AD1E-FC672D1A14BF}">
   <dimension ref="B2:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>161</v>
       </c>
@@ -10752,7 +10756,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>164</v>
       </c>
@@ -10766,7 +10770,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>167</v>
       </c>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FB66B7-7CC1-4730-AC7F-497F91A353D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299C0D66-B1FC-400E-8B21-2E18B4E1B090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -3995,7 +3995,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>910</v>
       </c>
@@ -4111,11 +4111,11 @@
         <v>67</v>
       </c>
       <c r="AI15" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AJ15" s="3">
         <f t="shared" si="11"/>
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AK15" s="3" t="s">
         <v>65</v>
@@ -4125,29 +4125,29 @@
       </c>
       <c r="AM15" s="3">
         <f t="shared" si="12"/>
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AN15" s="3">
         <v>2</v>
       </c>
       <c r="AO15" s="3">
         <f t="shared" si="13"/>
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AP15" s="3">
         <v>6</v>
       </c>
       <c r="AQ15" s="3">
         <f t="shared" si="14"/>
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AR15" s="3">
         <f t="shared" si="15"/>
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="AT15" s="3">
         <v>14</v>
@@ -6202,14 +6202,14 @@
         <v>89</v>
       </c>
       <c r="AN27" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO27" s="3">
         <f t="shared" si="13"/>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AP27" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ27" s="3">
         <f t="shared" si="14"/>
@@ -9175,7 +9175,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>138</v>
       </c>
@@ -9337,7 +9337,7 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>172</v>
       </c>
@@ -10711,8 +10711,7 @@
   <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
     <filterColumn colId="0">
       <filters>
-        <filter val="O001"/>
-        <filter val="O010"/>
+        <filter val="910"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299C0D66-B1FC-400E-8B21-2E18B4E1B090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA28F970-B2FB-461C-8EB5-EB6F689ED244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1553,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4" filterMode="1">
+  <sheetPr codeName="Feuil4">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF53"/>
@@ -1752,7 +1752,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>60</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>19</v>
       </c>
       <c r="R2" s="3">
-        <f t="shared" ref="R2:R44" si="4">9+N2</f>
+        <f t="shared" ref="R2:R43" si="4">9+N2</f>
         <v>16</v>
       </c>
       <c r="S2" s="3">
@@ -1820,7 +1820,7 @@
         <v>22</v>
       </c>
       <c r="U2" s="3">
-        <f t="shared" ref="U2:U44" si="6">+T2+1</f>
+        <f t="shared" ref="U2:U43" si="6">+T2+1</f>
         <v>23</v>
       </c>
       <c r="V2" s="3">
@@ -1925,7 +1925,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>120</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>121</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>233</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>416</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>752</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>761</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>888</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>901</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>904</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>906</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>907</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>908</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>912</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>916</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>31</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" ref="AA18:AA52" si="18">+Z18+AB18-1</f>
+        <f t="shared" ref="AA18:AA51" si="18">+Z18+AB18-1</f>
         <v>33</v>
       </c>
       <c r="AB18" s="3">
@@ -4687,7 +4687,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>917</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>918</v>
       </c>
@@ -5033,7 +5033,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>920</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>924</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>925</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>928</v>
       </c>
@@ -6071,7 +6071,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>930</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>931</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>22</v>
       </c>
       <c r="P28" s="3">
-        <f t="shared" ref="P28:P44" si="19">+IF(I28="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P28:P43" si="19">+IF(I28="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q28" s="3">
@@ -6416,7 +6416,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>932</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>1005</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>1006</v>
       </c>
@@ -6933,7 +6933,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>1007</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>3</v>
       </c>
       <c r="Y32" s="3">
-        <f t="shared" ref="Y32:Y52" si="20">+ROUNDDOWN(W32/7,0)*7+X32</f>
+        <f t="shared" ref="Y32:Y51" si="20">+ROUNDDOWN(W32/7,0)*7+X32</f>
         <v>31</v>
       </c>
       <c r="Z32" s="6">
@@ -7107,7 +7107,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>1009</v>
       </c>
@@ -7151,7 +7151,7 @@
         <v>14</v>
       </c>
       <c r="O33" s="3">
-        <f t="shared" ref="O33:O52" si="22">IF(I33="SFK Freight Forwarder",M33,M33+N33-1)</f>
+        <f t="shared" ref="O33:O51" si="22">IF(I33="SFK Freight Forwarder",M33,M33+N33-1)</f>
         <v>0</v>
       </c>
       <c r="P33" s="3">
@@ -7159,7 +7159,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <f t="shared" ref="Q33:Q52" si="23">+IF(I33="SFK Freight Forwarder",O33,O33+P33-1)</f>
+        <f t="shared" ref="Q33:Q51" si="23">+IF(I33="SFK Freight Forwarder",O33,O33+P33-1)</f>
         <v>0</v>
       </c>
       <c r="R33" s="3">
@@ -7170,7 +7170,7 @@
         <v>7</v>
       </c>
       <c r="T33" s="3">
-        <f t="shared" ref="T33:T52" si="24">+R33+S33-1</f>
+        <f t="shared" ref="T33:T51" si="24">+R33+S33-1</f>
         <v>29</v>
       </c>
       <c r="U33" s="3">
@@ -7181,7 +7181,7 @@
         <v>1</v>
       </c>
       <c r="W33" s="3">
-        <f t="shared" ref="W33:W52" si="25">+U33+V33-1</f>
+        <f t="shared" ref="W33:W51" si="25">+U33+V33-1</f>
         <v>30</v>
       </c>
       <c r="X33" s="3">
@@ -7210,21 +7210,21 @@
         <v>53</v>
       </c>
       <c r="AF33" s="3">
-        <f t="shared" ref="AF33:AF52" si="26">+AE33+AA33-1</f>
+        <f t="shared" ref="AF33:AF51" si="26">+AE33+AA33-1</f>
         <v>89</v>
       </c>
       <c r="AG33" s="6">
         <v>3</v>
       </c>
       <c r="AH33" s="6">
-        <f t="shared" ref="AH33:AH52" si="27">+AF33+AG33</f>
+        <f t="shared" ref="AH33:AH51" si="27">+AF33+AG33</f>
         <v>92</v>
       </c>
       <c r="AI33" s="3">
         <v>0</v>
       </c>
       <c r="AJ33" s="3">
-        <f t="shared" ref="AJ33:AJ52" si="28">+AI33+AH33</f>
+        <f t="shared" ref="AJ33:AJ51" si="28">+AI33+AH33</f>
         <v>92</v>
       </c>
       <c r="AK33" s="3" t="s">
@@ -7234,36 +7234,36 @@
         <v>2</v>
       </c>
       <c r="AM33" s="3">
-        <f t="shared" ref="AM33:AM52" si="29">+AJ33+AL33</f>
+        <f t="shared" ref="AM33:AM51" si="29">+AJ33+AL33</f>
         <v>94</v>
       </c>
       <c r="AN33" s="3">
         <v>2</v>
       </c>
       <c r="AO33" s="3">
-        <f t="shared" ref="AO33:AO52" si="30">+AM33+AN33</f>
+        <f t="shared" ref="AO33:AO51" si="30">+AM33+AN33</f>
         <v>96</v>
       </c>
       <c r="AP33" s="3">
         <v>2</v>
       </c>
       <c r="AQ33" s="3">
-        <f t="shared" ref="AQ33:AQ52" si="31">+AO33+AP33</f>
+        <f t="shared" ref="AQ33:AQ51" si="31">+AO33+AP33</f>
         <v>98</v>
       </c>
       <c r="AR33" s="3">
-        <f t="shared" ref="AR33:AR52" si="32">+AQ33+7</f>
+        <f t="shared" ref="AR33:AR51" si="32">+AQ33+7</f>
         <v>105</v>
       </c>
       <c r="AS33" s="3">
-        <f t="shared" ref="AS33:AS52" si="33">+AR33+7+AT33</f>
+        <f t="shared" ref="AS33:AS51" si="33">+AR33+7+AT33</f>
         <v>112</v>
       </c>
       <c r="AT33" s="3">
         <v>0</v>
       </c>
       <c r="AU33" s="3">
-        <f t="shared" ref="AU33:AU52" si="34">+AA33-R33</f>
+        <f t="shared" ref="AU33:AU51" si="34">+AA33-R33</f>
         <v>14</v>
       </c>
       <c r="AV33" s="3" t="s">
@@ -7279,7 +7279,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>1010</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>1012</v>
       </c>
@@ -7624,7 +7624,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>1014</v>
       </c>
@@ -7796,7 +7796,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>1015</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>1034</v>
       </c>
@@ -8140,7 +8140,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>1036</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>1037</v>
       </c>
@@ -8484,168 +8484,167 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F41" s="19">
-        <v>91017700</v>
+        <v>26549502</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c r="H41" s="2">
-        <v>222222</v>
+        <v>0</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="J41" s="2">
-        <v>222222</v>
+        <v>119640</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L41" s="3">
         <v>7</v>
       </c>
       <c r="M41" s="3">
-        <f t="shared" ref="M41:M52" si="35">+IF(I41="SFK Freight Forwarder",L41,9)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N41" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O41" s="3">
         <f t="shared" si="22"/>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="P41" s="3">
         <f t="shared" si="19"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="3">
         <f t="shared" si="23"/>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R41" s="3">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="S41" s="3">
         <v>7</v>
       </c>
       <c r="T41" s="3">
         <f t="shared" si="24"/>
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="U41" s="3">
         <f t="shared" si="6"/>
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="V41" s="3">
         <v>1</v>
       </c>
       <c r="W41" s="3">
         <f t="shared" si="25"/>
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="X41" s="3">
         <v>0</v>
       </c>
       <c r="Y41" s="3">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Z41" s="6">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="AA41" s="6">
         <f t="shared" si="18"/>
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AB41" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC41" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AD41" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AE41" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AF41" s="3">
         <f t="shared" si="26"/>
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="AG41" s="6">
         <v>3</v>
       </c>
       <c r="AH41" s="6">
         <f t="shared" si="27"/>
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="AI41" s="3">
         <v>0</v>
       </c>
       <c r="AJ41" s="3">
         <f t="shared" si="28"/>
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="AK41" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL41" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM41" s="3">
         <f t="shared" si="29"/>
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AN41" s="3">
         <v>3</v>
       </c>
       <c r="AO41" s="3">
         <f t="shared" si="30"/>
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AP41" s="3">
         <v>0</v>
       </c>
       <c r="AQ41" s="3">
         <f t="shared" si="31"/>
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AR41" s="3">
         <f t="shared" si="32"/>
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="33"/>
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="AT41" s="3">
         <v>0</v>
       </c>
       <c r="AU41" s="3">
         <f t="shared" si="34"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV41" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AW41" s="3" t="s">
         <v>131</v>
@@ -8653,229 +8652,230 @@
       <c r="AX41" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="AY41" s="21">
+      <c r="AY41" s="40">
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="B42" s="33" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F42" s="19">
-        <v>26549502</v>
+        <v>90014400</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="H42" s="2">
-        <v>0</v>
+        <v>222222</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="J42" s="2">
-        <v>119640</v>
+        <v>222222</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L42" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M42" s="3">
-        <v>0</v>
+        <f t="shared" ref="M42:M51" si="35">+IF(I42="SFK Freight Forwarder",L42,9)</f>
+        <v>9</v>
       </c>
       <c r="N42" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O42" s="3">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="P42" s="3">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q42" s="3">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R42" s="3">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="S42" s="3">
         <v>7</v>
       </c>
       <c r="T42" s="3">
         <f t="shared" si="24"/>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="U42" s="3">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="V42" s="3">
         <v>1</v>
       </c>
       <c r="W42" s="3">
         <f t="shared" si="25"/>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
       <c r="Y42" s="3">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="Z42" s="6">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AA42" s="6">
         <f t="shared" si="18"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AB42" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC42" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AD42" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE42" s="3">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AF42" s="3">
         <f t="shared" si="26"/>
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="AG42" s="6">
         <v>3</v>
       </c>
       <c r="AH42" s="6">
         <f t="shared" si="27"/>
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="AI42" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ42" s="3">
         <f t="shared" si="28"/>
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="AK42" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL42" s="3">
         <v>4</v>
       </c>
       <c r="AM42" s="3">
         <f t="shared" si="29"/>
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AN42" s="3">
         <v>3</v>
       </c>
       <c r="AO42" s="3">
         <f t="shared" si="30"/>
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AP42" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AQ42" s="3">
         <f t="shared" si="31"/>
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AR42" s="3">
         <f t="shared" si="32"/>
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="AS42" s="3">
         <f t="shared" si="33"/>
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="AT42" s="3">
         <v>0</v>
       </c>
       <c r="AU42" s="3">
         <f t="shared" si="34"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AV42" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AW42" s="3" t="s">
         <v>131</v>
       </c>
       <c r="AX42" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="AY42" s="40">
+        <v>88</v>
+      </c>
+      <c r="AY42" s="21">
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
-        <v>1045</v>
+        <v>1084</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="F43" s="19">
-        <v>90014400</v>
+        <v>90018600</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H43" s="2">
-        <v>222222</v>
+        <v>333333</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J43" s="2">
-        <v>222222</v>
+        <v>333333</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L43" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M43" s="3">
         <f t="shared" si="35"/>
         <v>9</v>
       </c>
       <c r="N43" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O43" s="3">
         <f t="shared" si="22"/>
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="P43" s="3">
         <f t="shared" si="19"/>
@@ -8883,42 +8883,42 @@
       </c>
       <c r="Q43" s="3">
         <f t="shared" si="23"/>
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="R43" s="3">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="S43" s="3">
         <v>7</v>
       </c>
       <c r="T43" s="3">
         <f t="shared" si="24"/>
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="U43" s="3">
         <f t="shared" si="6"/>
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="V43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W43" s="3">
         <f t="shared" si="25"/>
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
       <c r="Y43" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z43" s="6">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA43" s="6">
         <f t="shared" si="18"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AB43" s="3">
         <v>3</v>
@@ -8930,70 +8930,70 @@
         <v>5</v>
       </c>
       <c r="AE43" s="3">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="AF43" s="3">
         <f t="shared" si="26"/>
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AG43" s="6">
         <v>3</v>
       </c>
       <c r="AH43" s="6">
         <f t="shared" si="27"/>
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI43" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ43" s="3">
         <f t="shared" si="28"/>
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="AK43" s="3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL43" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AM43" s="3">
         <f t="shared" si="29"/>
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="AN43" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO43" s="3">
         <f t="shared" si="30"/>
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="AP43" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AQ43" s="3">
         <f t="shared" si="31"/>
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="AR43" s="3">
         <f t="shared" si="32"/>
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="AS43" s="3">
         <f t="shared" si="33"/>
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="AT43" s="3">
         <v>0</v>
       </c>
       <c r="AU43" s="3">
         <f t="shared" si="34"/>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AV43" s="3" t="s">
         <v>130</v>
       </c>
       <c r="AW43" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AX43" s="20" t="s">
         <v>88</v>
@@ -9002,191 +9002,180 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="5">
-        <v>1084</v>
-      </c>
-      <c r="B44" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>170</v>
+    <row r="44" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="A44" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E44" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="F44" s="19">
-        <v>90018600</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>156</v>
+        <v>90016500</v>
+      </c>
+      <c r="G44" s="23" t="s">
+        <v>158</v>
       </c>
       <c r="H44" s="2">
-        <v>333333</v>
+        <v>0</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="J44" s="2">
-        <v>333333</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>49</v>
+        <v>29159</v>
+      </c>
+      <c r="K44" s="23" t="s">
+        <v>137</v>
       </c>
       <c r="L44" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M44" s="3">
-        <f t="shared" si="35"/>
-        <v>9</v>
-      </c>
-      <c r="N44" s="3">
-        <v>14</v>
+        <v>8</v>
+      </c>
+      <c r="N44" s="23">
+        <v>1</v>
       </c>
       <c r="O44" s="3">
         <f t="shared" si="22"/>
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="P44" s="3">
-        <f t="shared" si="19"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q44" s="3">
         <f t="shared" si="23"/>
+        <v>13</v>
+      </c>
+      <c r="R44" s="23">
+        <v>9</v>
+      </c>
+      <c r="S44" s="23">
+        <v>12</v>
+      </c>
+      <c r="T44" s="23">
+        <f t="shared" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="U44" s="23">
+        <f>+T44+2</f>
+        <v>22</v>
+      </c>
+      <c r="V44" s="23">
+        <v>5</v>
+      </c>
+      <c r="W44" s="23">
+        <f t="shared" si="25"/>
         <v>26</v>
       </c>
-      <c r="R44" s="3">
-        <f t="shared" si="4"/>
-        <v>23</v>
-      </c>
-      <c r="S44" s="3">
-        <v>7</v>
-      </c>
-      <c r="T44" s="3">
-        <f t="shared" si="24"/>
+      <c r="X44" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
         <v>29</v>
       </c>
-      <c r="U44" s="3">
-        <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-      <c r="V44" s="3">
-        <v>2</v>
-      </c>
-      <c r="W44" s="3">
-        <f t="shared" si="25"/>
+      <c r="Z44" s="6">
+        <v>29</v>
+      </c>
+      <c r="AA44" s="6">
         <v>31</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>36</v>
-      </c>
-      <c r="Z44" s="6">
-        <v>39</v>
-      </c>
-      <c r="AA44" s="6">
-        <f t="shared" si="18"/>
+      <c r="AB44" s="23">
+        <v>4</v>
+      </c>
+      <c r="AC44" s="23"/>
+      <c r="AD44" s="23"/>
+      <c r="AE44" s="33">
         <v>41</v>
       </c>
-      <c r="AB44" s="3">
-        <v>3</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AF44" s="23">
+        <f t="shared" si="26"/>
+        <v>71</v>
+      </c>
+      <c r="AG44" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH44" s="23">
+        <f t="shared" si="27"/>
+        <v>74</v>
+      </c>
+      <c r="AI44" s="23">
+        <v>7</v>
+      </c>
+      <c r="AJ44" s="23">
+        <f t="shared" si="28"/>
+        <v>81</v>
+      </c>
+      <c r="AK44" s="23"/>
+      <c r="AL44" s="23">
+        <v>3</v>
+      </c>
+      <c r="AM44" s="23">
+        <f t="shared" si="29"/>
+        <v>84</v>
+      </c>
+      <c r="AN44" s="23">
         <v>5</v>
       </c>
-      <c r="AD44" s="3">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="3">
-        <v>35</v>
-      </c>
-      <c r="AF44" s="3">
-        <f t="shared" si="26"/>
-        <v>75</v>
-      </c>
-      <c r="AG44" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH44" s="6">
-        <f t="shared" si="27"/>
-        <v>78</v>
-      </c>
-      <c r="AI44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ44" s="3">
-        <f t="shared" si="28"/>
-        <v>78</v>
-      </c>
-      <c r="AK44" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AL44" s="3">
-        <v>2</v>
-      </c>
-      <c r="AM44" s="3">
-        <f t="shared" si="29"/>
-        <v>80</v>
-      </c>
-      <c r="AN44" s="3">
-        <v>2</v>
-      </c>
-      <c r="AO44" s="3">
-        <f t="shared" si="30"/>
-        <v>82</v>
-      </c>
-      <c r="AP44" s="3">
-        <v>2</v>
+      <c r="AO44" s="23">
+        <f>+AM44+AN44</f>
+        <v>89</v>
+      </c>
+      <c r="AP44" s="23">
+        <v>6</v>
       </c>
       <c r="AQ44" s="3">
-        <f t="shared" si="31"/>
-        <v>84</v>
-      </c>
-      <c r="AR44" s="3">
-        <f t="shared" si="32"/>
-        <v>91</v>
-      </c>
-      <c r="AS44" s="3">
+        <v>92</v>
+      </c>
+      <c r="AR44" s="23">
+        <f>+AQ44+4</f>
+        <v>96</v>
+      </c>
+      <c r="AS44" s="23">
         <f t="shared" si="33"/>
-        <v>98</v>
-      </c>
-      <c r="AT44" s="3">
-        <v>0</v>
+        <v>117</v>
+      </c>
+      <c r="AT44" s="23">
+        <v>14</v>
       </c>
       <c r="AU44" s="3">
         <f t="shared" si="34"/>
-        <v>18</v>
-      </c>
-      <c r="AV44" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AW44" s="3" t="s">
-        <v>134</v>
+        <v>22</v>
+      </c>
+      <c r="AV44" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW44" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="AX44" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY44" s="21">
-        <v>46507</v>
+        <v>56</v>
+      </c>
+      <c r="AY44" s="37">
+        <v>46508</v>
       </c>
     </row>
-    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>68</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="E45" s="32" t="s">
         <v>81</v>
@@ -9195,7 +9184,7 @@
         <v>90016500</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -9219,14 +9208,14 @@
         <v>1</v>
       </c>
       <c r="O45" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="O45" si="36">IF(I45="SFK Freight Forwarder",M45,M45+N45-1)</f>
         <v>8</v>
       </c>
       <c r="P45" s="3">
         <v>6</v>
       </c>
       <c r="Q45" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="Q45" si="37">+IF(I45="SFK Freight Forwarder",O45,O45+P45-1)</f>
         <v>13</v>
       </c>
       <c r="R45" s="23">
@@ -9236,7 +9225,7 @@
         <v>12</v>
       </c>
       <c r="T45" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="T45" si="38">+R45+S45-1</f>
         <v>20</v>
       </c>
       <c r="U45" s="23">
@@ -9247,7 +9236,7 @@
         <v>5</v>
       </c>
       <c r="W45" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="W45" si="39">+U45+V45-1</f>
         <v>26</v>
       </c>
       <c r="X45" s="23">
@@ -9257,10 +9246,10 @@
         <v>29</v>
       </c>
       <c r="Z45" s="6">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA45" s="6">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="AB45" s="23">
         <v>4</v>
@@ -9268,61 +9257,62 @@
       <c r="AC45" s="23"/>
       <c r="AD45" s="23"/>
       <c r="AE45" s="33">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="AF45" s="23">
-        <f t="shared" si="26"/>
-        <v>71</v>
+        <f t="shared" ref="AF45" si="40">+AE45+AA45-1</f>
+        <v>69</v>
       </c>
       <c r="AG45" s="23">
         <v>3</v>
       </c>
       <c r="AH45" s="23">
-        <f t="shared" si="27"/>
-        <v>74</v>
+        <f t="shared" ref="AH45" si="41">+AF45+AG45</f>
+        <v>72</v>
       </c>
       <c r="AI45" s="23">
         <v>7</v>
       </c>
       <c r="AJ45" s="23">
-        <f t="shared" si="28"/>
-        <v>81</v>
+        <f t="shared" ref="AJ45" si="42">+AI45+AH45</f>
+        <v>79</v>
       </c>
       <c r="AK45" s="23"/>
       <c r="AL45" s="23">
         <v>3</v>
       </c>
       <c r="AM45" s="23">
-        <f t="shared" si="29"/>
-        <v>84</v>
+        <f t="shared" ref="AM45" si="43">+AJ45+AL45</f>
+        <v>82</v>
       </c>
       <c r="AN45" s="23">
         <v>5</v>
       </c>
       <c r="AO45" s="23">
         <f>+AM45+AN45</f>
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AP45" s="23">
-        <v>6</v>
-      </c>
-      <c r="AQ45" s="23">
-        <v>92</v>
+        <v>4</v>
+      </c>
+      <c r="AQ45" s="3">
+        <f t="shared" si="31"/>
+        <v>91</v>
       </c>
       <c r="AR45" s="23">
         <f>+AQ45+4</f>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AS45" s="23">
-        <f t="shared" si="33"/>
-        <v>117</v>
+        <f t="shared" ref="AS45" si="44">+AR45+7+AT45</f>
+        <v>116</v>
       </c>
       <c r="AT45" s="23">
         <v>14</v>
       </c>
       <c r="AU45" s="3">
-        <f t="shared" si="34"/>
-        <v>22</v>
+        <f t="shared" ref="AU45" si="45">+AA45-R45</f>
+        <v>27</v>
       </c>
       <c r="AV45" s="23" t="s">
         <v>133</v>
@@ -9337,27 +9327,27 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>99</v>
+        <v>143</v>
+      </c>
+      <c r="B46" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="D46" s="38" t="s">
+        <v>62</v>
       </c>
       <c r="E46" s="32" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F46" s="19">
-        <v>90016500</v>
-      </c>
-      <c r="G46" s="23" t="s">
-        <v>159</v>
+        <v>90018600</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -9366,160 +9356,173 @@
         <v>139</v>
       </c>
       <c r="J46" s="2">
-        <v>29159</v>
-      </c>
-      <c r="K46" s="23" t="s">
-        <v>137</v>
+        <v>112741</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="L46" s="3">
+        <v>7</v>
+      </c>
+      <c r="M46" s="3">
+        <f t="shared" si="35"/>
+        <v>9</v>
+      </c>
+      <c r="N46" s="3">
+        <v>14</v>
+      </c>
+      <c r="O46" s="3">
+        <f t="shared" si="22"/>
+        <v>22</v>
+      </c>
+      <c r="P46" s="3">
+        <f t="shared" ref="P46:P51" si="46">+IF(I46="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
-      <c r="M46" s="3">
-        <v>8</v>
-      </c>
-      <c r="N46" s="23">
-        <v>1</v>
-      </c>
-      <c r="O46" s="3">
-        <f t="shared" ref="O46" si="36">IF(I46="SFK Freight Forwarder",M46,M46+N46-1)</f>
-        <v>8</v>
-      </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
+        <f t="shared" si="23"/>
+        <v>26</v>
+      </c>
+      <c r="R46" s="3">
+        <f t="shared" ref="R46:R51" si="47">9+N46</f>
+        <v>23</v>
+      </c>
+      <c r="S46" s="3">
+        <v>7</v>
+      </c>
+      <c r="T46" s="3">
+        <f t="shared" si="24"/>
+        <v>29</v>
+      </c>
+      <c r="U46" s="3">
+        <f t="shared" ref="U46:U51" si="48">+T46+1</f>
+        <v>30</v>
+      </c>
+      <c r="V46" s="3">
+        <v>2</v>
+      </c>
+      <c r="W46" s="3">
+        <f t="shared" si="25"/>
+        <v>31</v>
+      </c>
+      <c r="X46" s="3">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="20"/>
+        <v>31</v>
+      </c>
+      <c r="Z46" s="6">
+        <f t="shared" ref="Z46:Z50" si="49">+Y46+X46-1</f>
+        <v>33</v>
+      </c>
+      <c r="AA46" s="6">
+        <f t="shared" si="18"/>
+        <v>34</v>
+      </c>
+      <c r="AB46" s="3">
+        <v>2</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>4</v>
+      </c>
+      <c r="AD46" s="3">
+        <v>11</v>
+      </c>
+      <c r="AE46" s="3">
+        <v>40</v>
+      </c>
+      <c r="AF46" s="3">
+        <f t="shared" si="26"/>
+        <v>73</v>
+      </c>
+      <c r="AG46" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH46" s="6">
+        <f t="shared" si="27"/>
+        <v>76</v>
+      </c>
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="3">
+        <f t="shared" si="28"/>
+        <v>76</v>
+      </c>
+      <c r="AK46" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL46" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM46" s="3">
+        <f t="shared" si="29"/>
+        <v>78</v>
+      </c>
+      <c r="AN46" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO46" s="3">
+        <f t="shared" si="30"/>
+        <v>80</v>
+      </c>
+      <c r="AP46" s="3">
         <v>6</v>
       </c>
-      <c r="Q46" s="3">
-        <f t="shared" ref="Q46" si="37">+IF(I46="SFK Freight Forwarder",O46,O46+P46-1)</f>
-        <v>13</v>
-      </c>
-      <c r="R46" s="23">
-        <v>9</v>
-      </c>
-      <c r="S46" s="23">
-        <v>12</v>
-      </c>
-      <c r="T46" s="23">
-        <f t="shared" ref="T46" si="38">+R46+S46-1</f>
-        <v>20</v>
-      </c>
-      <c r="U46" s="23">
-        <f>+T46+2</f>
-        <v>22</v>
-      </c>
-      <c r="V46" s="23">
-        <v>5</v>
-      </c>
-      <c r="W46" s="23">
-        <f t="shared" ref="W46" si="39">+U46+V46-1</f>
-        <v>26</v>
-      </c>
-      <c r="X46" s="23">
-        <v>4</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>29</v>
-      </c>
-      <c r="Z46" s="6">
-        <v>34</v>
-      </c>
-      <c r="AA46" s="6">
-        <v>36</v>
-      </c>
-      <c r="AB46" s="23">
-        <v>4</v>
-      </c>
-      <c r="AC46" s="23"/>
-      <c r="AD46" s="23"/>
-      <c r="AE46" s="33">
-        <v>34</v>
-      </c>
-      <c r="AF46" s="23">
-        <f t="shared" ref="AF46" si="40">+AE46+AA46-1</f>
-        <v>69</v>
-      </c>
-      <c r="AG46" s="23">
-        <v>3</v>
-      </c>
-      <c r="AH46" s="23">
-        <f t="shared" ref="AH46" si="41">+AF46+AG46</f>
-        <v>72</v>
-      </c>
-      <c r="AI46" s="23">
-        <v>7</v>
-      </c>
-      <c r="AJ46" s="23">
-        <f t="shared" ref="AJ46" si="42">+AI46+AH46</f>
-        <v>79</v>
-      </c>
-      <c r="AK46" s="23"/>
-      <c r="AL46" s="23">
-        <v>3</v>
-      </c>
-      <c r="AM46" s="23">
-        <f t="shared" ref="AM46" si="43">+AJ46+AL46</f>
-        <v>82</v>
-      </c>
-      <c r="AN46" s="23">
-        <v>5</v>
-      </c>
-      <c r="AO46" s="23">
-        <f>+AM46+AN46</f>
-        <v>87</v>
-      </c>
-      <c r="AP46" s="23">
-        <v>6</v>
-      </c>
-      <c r="AQ46" s="23">
-        <v>92</v>
-      </c>
-      <c r="AR46" s="23">
-        <f>+AQ46+4</f>
-        <v>96</v>
-      </c>
-      <c r="AS46" s="23">
-        <f t="shared" ref="AS46" si="44">+AR46+7+AT46</f>
-        <v>117</v>
-      </c>
-      <c r="AT46" s="23">
-        <v>14</v>
+      <c r="AQ46" s="3">
+        <f t="shared" si="31"/>
+        <v>86</v>
+      </c>
+      <c r="AR46" s="3">
+        <f t="shared" si="32"/>
+        <v>93</v>
+      </c>
+      <c r="AS46" s="3">
+        <f t="shared" si="33"/>
+        <v>100</v>
+      </c>
+      <c r="AT46" s="3">
+        <v>0</v>
       </c>
       <c r="AU46" s="3">
-        <f t="shared" ref="AU46" si="45">+AA46-R46</f>
-        <v>27</v>
-      </c>
-      <c r="AV46" s="23" t="s">
+        <f t="shared" si="34"/>
+        <v>11</v>
+      </c>
+      <c r="AV46" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="AW46" s="23" t="s">
+      <c r="AW46" s="3" t="s">
         <v>131</v>
       </c>
       <c r="AX46" s="20" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="AY46" s="37">
-        <v>46508</v>
+        <v>46142</v>
       </c>
     </row>
-    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B47" s="39" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="32" t="s">
-        <v>59</v>
+        <v>77</v>
+      </c>
+      <c r="E47" s="38" t="s">
+        <v>171</v>
       </c>
       <c r="F47" s="19">
-        <v>90018600</v>
+        <v>90012500</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -9528,10 +9531,10 @@
         <v>139</v>
       </c>
       <c r="J47" s="2">
-        <v>112741</v>
-      </c>
-      <c r="K47" s="7" t="s">
-        <v>38</v>
+        <v>29159</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="L47" s="3">
         <v>7</v>
@@ -9548,7 +9551,7 @@
         <v>22</v>
       </c>
       <c r="P47" s="3">
-        <f t="shared" ref="P47:P52" si="46">+IF(I47="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="46"/>
         <v>5</v>
       </c>
       <c r="Q47" s="3">
@@ -9556,7 +9559,7 @@
         <v>26</v>
       </c>
       <c r="R47" s="3">
-        <f t="shared" ref="R47:R52" si="47">9+N47</f>
+        <f t="shared" si="47"/>
         <v>23</v>
       </c>
       <c r="S47" s="3">
@@ -9567,7 +9570,7 @@
         <v>29</v>
       </c>
       <c r="U47" s="3">
-        <f t="shared" ref="U47:U52" si="48">+T47+1</f>
+        <f t="shared" si="48"/>
         <v>30</v>
       </c>
       <c r="V47" s="3">
@@ -9578,49 +9581,46 @@
         <v>31</v>
       </c>
       <c r="X47" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y47" s="3">
-        <f t="shared" si="20"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z47" s="6">
-        <f t="shared" ref="Z47:Z51" si="49">+Y47+X47-1</f>
         <v>33</v>
       </c>
       <c r="AA47" s="6">
-        <f t="shared" si="18"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB47" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC47" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD47" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE47" s="3">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="AF47" s="3">
         <f t="shared" si="26"/>
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="AG47" s="6">
         <v>3</v>
       </c>
       <c r="AH47" s="6">
         <f t="shared" si="27"/>
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="AI47" s="3">
         <v>0</v>
       </c>
       <c r="AJ47" s="3">
         <f t="shared" si="28"/>
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="AK47" s="3" t="s">
         <v>60</v>
@@ -9630,36 +9630,36 @@
       </c>
       <c r="AM47" s="3">
         <f t="shared" si="29"/>
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN47" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AO47" s="3">
         <f t="shared" si="30"/>
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AP47" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ47" s="3">
         <f t="shared" si="31"/>
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="AR47" s="3">
         <f t="shared" si="32"/>
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="AS47" s="3">
         <f t="shared" si="33"/>
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="AT47" s="3">
         <v>0</v>
       </c>
       <c r="AU47" s="3">
         <f t="shared" si="34"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV47" s="3" t="s">
         <v>133</v>
@@ -9671,30 +9671,30 @@
         <v>88</v>
       </c>
       <c r="AY47" s="37">
-        <v>46142</v>
+        <v>46507</v>
       </c>
     </row>
-    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B48" s="39" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C48" s="38" t="s">
         <v>98</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="F48" s="19">
-        <v>90012500</v>
+        <v>90016500</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
@@ -9753,85 +9753,86 @@
         <v>31</v>
       </c>
       <c r="X48" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y48" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z48" s="6">
         <v>33</v>
       </c>
       <c r="AA48" s="6">
-        <v>36</v>
+        <f t="shared" si="18"/>
+        <v>38</v>
       </c>
       <c r="AB48" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC48" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AD48" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE48" s="3">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="AF48" s="3">
         <f t="shared" si="26"/>
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AG48" s="6">
         <v>3</v>
       </c>
       <c r="AH48" s="6">
         <f t="shared" si="27"/>
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="AI48" s="3">
         <v>0</v>
       </c>
       <c r="AJ48" s="3">
         <f t="shared" si="28"/>
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="AK48" s="3" t="s">
         <v>60</v>
       </c>
       <c r="AL48" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM48" s="3">
         <f t="shared" si="29"/>
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="AN48" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AO48" s="3">
         <f t="shared" si="30"/>
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="AP48" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ48" s="3">
         <f t="shared" si="31"/>
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AR48" s="3">
         <f t="shared" si="32"/>
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="AS48" s="3">
         <f t="shared" si="33"/>
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="AT48" s="3">
         <v>0</v>
       </c>
       <c r="AU48" s="3">
         <f t="shared" si="34"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AV48" s="3" t="s">
         <v>133</v>
@@ -9842,31 +9843,31 @@
       <c r="AX48" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="AY48" s="37">
+      <c r="AY48" s="40">
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B49" s="39" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C49" s="38" t="s">
         <v>98</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="F49" s="19">
-        <v>90016500</v>
+        <v>92000100</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -9928,83 +9929,85 @@
         <v>2</v>
       </c>
       <c r="Y49" s="3">
-        <v>33</v>
+        <f t="shared" si="20"/>
+        <v>30</v>
       </c>
       <c r="Z49" s="6">
-        <v>33</v>
+        <f t="shared" si="49"/>
+        <v>31</v>
       </c>
       <c r="AA49" s="6">
         <f t="shared" si="18"/>
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB49" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC49" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD49" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE49" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF49" s="3">
         <f t="shared" si="26"/>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AG49" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH49" s="6">
         <f t="shared" si="27"/>
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AI49" s="3">
         <v>0</v>
       </c>
       <c r="AJ49" s="3">
         <f t="shared" si="28"/>
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>60</v>
       </c>
       <c r="AL49" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM49" s="3">
         <f t="shared" si="29"/>
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AN49" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AO49" s="3">
         <f t="shared" si="30"/>
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AP49" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AQ49" s="3">
         <f t="shared" si="31"/>
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AR49" s="3">
         <f t="shared" si="32"/>
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AS49" s="3">
         <f t="shared" si="33"/>
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AT49" s="3">
         <v>0</v>
       </c>
       <c r="AU49" s="3">
         <f t="shared" si="34"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AV49" s="3" t="s">
         <v>133</v>
@@ -10013,33 +10016,33 @@
         <v>131</v>
       </c>
       <c r="AX49" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY49" s="40">
-        <v>46507</v>
+        <v>75</v>
+      </c>
+      <c r="AY49" s="37">
+        <v>46142</v>
       </c>
     </row>
-    <row r="50" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E50" s="38" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F50" s="19">
-        <v>92000100</v>
+        <v>90014400</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>47</v>
+        <v>155</v>
       </c>
       <c r="H50" s="2">
         <v>0</v>
@@ -10048,13 +10051,13 @@
         <v>139</v>
       </c>
       <c r="J50" s="2">
-        <v>29159</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>142</v>
+        <v>112741</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="L50" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M50" s="3">
         <f t="shared" si="35"/>
@@ -10098,81 +10101,81 @@
         <v>31</v>
       </c>
       <c r="X50" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y50" s="3">
         <f t="shared" si="20"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z50" s="6">
         <f t="shared" si="49"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA50" s="6">
         <f t="shared" si="18"/>
         <v>34</v>
       </c>
       <c r="AB50" s="3">
+        <v>2</v>
+      </c>
+      <c r="AC50" s="3">
         <v>4</v>
       </c>
-      <c r="AC50" s="3">
-        <v>5</v>
-      </c>
       <c r="AD50" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE50" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF50" s="3">
         <f t="shared" si="26"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AG50" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH50" s="6">
         <f t="shared" si="27"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AI50" s="3">
         <v>0</v>
       </c>
       <c r="AJ50" s="3">
         <f t="shared" si="28"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AK50" s="3" t="s">
         <v>60</v>
       </c>
       <c r="AL50" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM50" s="3">
         <f t="shared" si="29"/>
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="AN50" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AO50" s="3">
         <f t="shared" si="30"/>
         <v>92</v>
       </c>
       <c r="AP50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ50" s="3">
         <f t="shared" si="31"/>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AR50" s="3">
         <f t="shared" si="32"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AS50" s="3">
         <f t="shared" si="33"/>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AT50" s="3">
         <v>0</v>
@@ -10188,33 +10191,33 @@
         <v>131</v>
       </c>
       <c r="AX50" s="20" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="AY50" s="37">
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B51" s="39" t="s">
-        <v>61</v>
+        <v>152</v>
+      </c>
+      <c r="B51" s="38" t="s">
+        <v>83</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E51" s="38" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F51" s="19">
-        <v>90014400</v>
+        <v>90016000</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>155</v>
+        <v>34</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
@@ -10223,24 +10226,24 @@
         <v>139</v>
       </c>
       <c r="J51" s="2">
-        <v>112741</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>38</v>
+        <v>5915200</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="L51" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M51" s="3">
         <f t="shared" si="35"/>
         <v>9</v>
       </c>
       <c r="N51" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O51" s="3">
         <f t="shared" si="22"/>
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="P51" s="3">
         <f t="shared" si="46"/>
@@ -10248,148 +10251,147 @@
       </c>
       <c r="Q51" s="3">
         <f t="shared" si="23"/>
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="R51" s="3">
         <f t="shared" si="47"/>
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="S51" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T51" s="3">
         <f t="shared" si="24"/>
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="U51" s="3">
         <f t="shared" si="48"/>
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="V51" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W51" s="3">
         <f t="shared" si="25"/>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="X51" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y51" s="3">
         <f t="shared" si="20"/>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="Z51" s="6">
-        <f t="shared" si="49"/>
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="AA51" s="6">
         <f t="shared" si="18"/>
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AB51" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC51" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD51" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE51" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AF51" s="3">
         <f t="shared" si="26"/>
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="AG51" s="6">
         <v>3</v>
       </c>
       <c r="AH51" s="6">
         <f t="shared" si="27"/>
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="AI51" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ51" s="3">
         <f t="shared" si="28"/>
-        <v>86</v>
-      </c>
-      <c r="AK51" s="3" t="s">
-        <v>60</v>
+        <v>74</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
       </c>
       <c r="AL51" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM51" s="3">
         <f t="shared" si="29"/>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN51" s="3">
         <v>2</v>
       </c>
       <c r="AO51" s="3">
         <f t="shared" si="30"/>
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AP51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ51" s="3">
         <f t="shared" si="31"/>
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AR51" s="3">
         <f t="shared" si="32"/>
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="AS51" s="3">
         <f t="shared" si="33"/>
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="AT51" s="3">
         <v>0</v>
       </c>
       <c r="AU51" s="3">
         <f t="shared" si="34"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV51" s="3" t="s">
         <v>133</v>
       </c>
       <c r="AW51" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AX51" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY51" s="37">
-        <v>46142</v>
+        <v>56</v>
+      </c>
+      <c r="AY51" s="40">
+        <v>46507</v>
       </c>
     </row>
-    <row r="52" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" s="38" t="s">
-        <v>72</v>
+        <v>61</v>
+      </c>
+      <c r="C52" s="39" t="s">
+        <v>68</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="E52" s="38" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="F52" s="19">
-        <v>90016000</v>
+        <v>90014400</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>34</v>
+        <v>155</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -10398,332 +10400,325 @@
         <v>139</v>
       </c>
       <c r="J52" s="2">
-        <v>5915200</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>151</v>
+        <v>29159</v>
+      </c>
+      <c r="K52" s="23" t="s">
+        <v>140</v>
       </c>
       <c r="L52" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M52" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="M52:M53" si="50">+IF(I52="SFK Freight Forwarder",L52,9)</f>
         <v>9</v>
       </c>
-      <c r="N52" s="3">
-        <v>7</v>
+      <c r="N52" s="23">
+        <v>2</v>
       </c>
       <c r="O52" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="O52:O53" si="51">IF(I52="SFK Freight Forwarder",M52,M52+N52-1)</f>
+        <v>10</v>
+      </c>
+      <c r="P52" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3">
+        <f t="shared" ref="Q52:Q53" si="52">+IF(I52="SFK Freight Forwarder",O52,O52+P52-1)</f>
+        <v>14</v>
+      </c>
+      <c r="R52" s="23">
+        <v>0</v>
+      </c>
+      <c r="S52" s="23">
+        <v>0</v>
+      </c>
+      <c r="T52" s="25">
+        <v>0</v>
+      </c>
+      <c r="U52" s="23">
         <v>15</v>
       </c>
-      <c r="P52" s="3">
-        <f t="shared" si="46"/>
-        <v>5</v>
-      </c>
-      <c r="Q52" s="3">
-        <f t="shared" si="23"/>
+      <c r="V52" s="23">
+        <v>4</v>
+      </c>
+      <c r="W52" s="23">
+        <f t="shared" ref="W52:W53" si="53">+U52+V52-1</f>
+        <v>18</v>
+      </c>
+      <c r="X52" s="23">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>18</v>
+      </c>
+      <c r="Z52" s="6">
         <v>19</v>
       </c>
-      <c r="R52" s="3">
-        <f t="shared" si="47"/>
-        <v>16</v>
-      </c>
-      <c r="S52" s="3">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3">
-        <f t="shared" si="24"/>
-        <v>18</v>
-      </c>
-      <c r="U52" s="3">
-        <f t="shared" si="48"/>
-        <v>19</v>
-      </c>
-      <c r="V52" s="3">
-        <v>5</v>
-      </c>
-      <c r="W52" s="3">
-        <f t="shared" si="25"/>
-        <v>23</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="AA52" s="6">
+        <f t="shared" ref="AA52:AA53" si="54">+Z52+AB52-1</f>
+        <v>22</v>
+      </c>
+      <c r="AB52" s="23">
+        <v>4</v>
+      </c>
+      <c r="AC52" s="23"/>
+      <c r="AD52" s="23"/>
+      <c r="AE52" s="23">
+        <v>46</v>
+      </c>
+      <c r="AF52" s="23">
+        <f t="shared" ref="AF52:AF53" si="55">+AE52+AA52-1</f>
+        <v>67</v>
+      </c>
+      <c r="AG52" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH52" s="23">
+        <f t="shared" ref="AH52:AH53" si="56">+AF52+AG52</f>
+        <v>70</v>
+      </c>
+      <c r="AI52" s="23">
+        <v>7</v>
+      </c>
+      <c r="AJ52" s="23">
+        <f t="shared" ref="AJ52:AJ53" si="57">+AI52+AH52</f>
+        <v>77</v>
+      </c>
+      <c r="AK52" s="23"/>
+      <c r="AL52" s="23">
+        <v>3</v>
+      </c>
+      <c r="AM52" s="23">
+        <f t="shared" ref="AM52:AM53" si="58">+AJ52+AL52</f>
+        <v>80</v>
+      </c>
+      <c r="AN52" s="23">
         <v>2</v>
       </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="20"/>
-        <v>23</v>
-      </c>
-      <c r="Z52" s="6">
-        <v>23</v>
-      </c>
-      <c r="AA52" s="6">
-        <f t="shared" si="18"/>
-        <v>25</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>3</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>40</v>
-      </c>
-      <c r="AF52" s="3">
-        <f t="shared" si="26"/>
-        <v>64</v>
-      </c>
-      <c r="AG52" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH52" s="6">
-        <f t="shared" si="27"/>
-        <v>67</v>
-      </c>
-      <c r="AI52" s="3">
-        <v>7</v>
-      </c>
-      <c r="AJ52" s="3">
-        <f t="shared" si="28"/>
-        <v>74</v>
-      </c>
-      <c r="AK52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL52" s="3">
-        <v>6</v>
-      </c>
-      <c r="AM52" s="3">
-        <f t="shared" si="29"/>
-        <v>80</v>
-      </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="23">
+        <f t="shared" ref="AO52:AO53" si="59">+AM52+AN52</f>
+        <v>82</v>
+      </c>
+      <c r="AP52" s="23">
         <v>2</v>
       </c>
-      <c r="AO52" s="3">
-        <f t="shared" si="30"/>
-        <v>82</v>
-      </c>
-      <c r="AP52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ52" s="3">
-        <f t="shared" si="31"/>
-        <v>82</v>
-      </c>
-      <c r="AR52" s="3">
-        <f t="shared" si="32"/>
-        <v>89</v>
-      </c>
-      <c r="AS52" s="3">
-        <f t="shared" si="33"/>
-        <v>96</v>
-      </c>
-      <c r="AT52" s="3">
-        <v>0</v>
+      <c r="AQ52" s="23">
+        <f t="shared" ref="AQ52:AQ53" si="60">+AO52+AP52</f>
+        <v>84</v>
+      </c>
+      <c r="AR52" s="23">
+        <f t="shared" ref="AR52:AR53" si="61">+AQ52+7</f>
+        <v>91</v>
+      </c>
+      <c r="AS52" s="23">
+        <f t="shared" ref="AS52:AS53" si="62">+AR52+7+AT52</f>
+        <v>112</v>
+      </c>
+      <c r="AT52" s="23">
+        <v>14</v>
       </c>
       <c r="AU52" s="3">
-        <f t="shared" si="34"/>
-        <v>9</v>
-      </c>
-      <c r="AV52" s="3" t="s">
+        <f t="shared" ref="AU52:AU53" si="63">+AA52-R52</f>
+        <v>22</v>
+      </c>
+      <c r="AV52" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="AW52" s="3" t="s">
-        <v>134</v>
+      <c r="AW52" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="AX52" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AY52" s="40">
+      <c r="AY52" s="37">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="A53" s="5">
+        <v>1039</v>
+      </c>
+      <c r="B53" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F53" s="19">
+        <v>91017700</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H53" s="2">
+        <v>222222</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J53" s="2">
+        <v>222222</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L53" s="3">
+        <v>7</v>
+      </c>
+      <c r="M53" s="3">
+        <f t="shared" si="50"/>
+        <v>9</v>
+      </c>
+      <c r="N53" s="3">
+        <v>21</v>
+      </c>
+      <c r="O53" s="3">
+        <f t="shared" si="51"/>
+        <v>29</v>
+      </c>
+      <c r="P53" s="3">
+        <f t="shared" ref="P53" si="64">+IF(I53="SFK Freight Forwarder",0,5)</f>
+        <v>5</v>
+      </c>
+      <c r="Q53" s="3">
+        <f t="shared" si="52"/>
+        <v>33</v>
+      </c>
+      <c r="R53" s="3">
+        <f t="shared" ref="R53" si="65">9+N53</f>
+        <v>30</v>
+      </c>
+      <c r="S53" s="3">
+        <v>7</v>
+      </c>
+      <c r="T53" s="3">
+        <f t="shared" ref="T53" si="66">+R53+S53-1</f>
+        <v>36</v>
+      </c>
+      <c r="U53" s="3">
+        <f t="shared" ref="U53" si="67">+T53+1</f>
+        <v>37</v>
+      </c>
+      <c r="V53" s="3">
+        <v>1</v>
+      </c>
+      <c r="W53" s="3">
+        <f t="shared" si="53"/>
+        <v>37</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>37</v>
+      </c>
+      <c r="Z53" s="6">
+        <v>42</v>
+      </c>
+      <c r="AA53" s="6">
+        <f t="shared" si="54"/>
+        <v>44</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>4</v>
+      </c>
+      <c r="AD53" s="3">
+        <v>4</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>40</v>
+      </c>
+      <c r="AF53" s="3">
+        <f t="shared" si="55"/>
+        <v>83</v>
+      </c>
+      <c r="AG53" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH53" s="6">
+        <f t="shared" si="56"/>
+        <v>86</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3">
+        <f t="shared" si="57"/>
+        <v>86</v>
+      </c>
+      <c r="AK53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM53" s="3">
+        <f t="shared" si="58"/>
+        <v>88</v>
+      </c>
+      <c r="AN53" s="3">
+        <v>3</v>
+      </c>
+      <c r="AO53" s="3">
+        <f t="shared" si="59"/>
+        <v>91</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <f t="shared" si="60"/>
+        <v>91</v>
+      </c>
+      <c r="AR53" s="3">
+        <f t="shared" si="61"/>
+        <v>98</v>
+      </c>
+      <c r="AS53" s="3">
+        <f t="shared" si="62"/>
+        <v>105</v>
+      </c>
+      <c r="AT53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU53" s="3">
+        <f t="shared" si="63"/>
+        <v>14</v>
+      </c>
+      <c r="AV53" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW53" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AX53" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY53" s="21">
         <v>46507</v>
-      </c>
-    </row>
-    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B53" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="C53" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="D53" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="E53" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="F53" s="19">
-        <v>90014400</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="H53" s="2">
-        <v>0</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="J53" s="2">
-        <v>29159</v>
-      </c>
-      <c r="K53" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="L53" s="3">
-        <v>5</v>
-      </c>
-      <c r="M53" s="3">
-        <f t="shared" ref="M53" si="50">+IF(I53="SFK Freight Forwarder",L53,9)</f>
-        <v>9</v>
-      </c>
-      <c r="N53" s="23">
-        <v>2</v>
-      </c>
-      <c r="O53" s="3">
-        <f t="shared" ref="O53" si="51">IF(I53="SFK Freight Forwarder",M53,M53+N53-1)</f>
-        <v>10</v>
-      </c>
-      <c r="P53" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q53" s="3">
-        <f t="shared" ref="Q53" si="52">+IF(I53="SFK Freight Forwarder",O53,O53+P53-1)</f>
-        <v>14</v>
-      </c>
-      <c r="R53" s="23">
-        <v>0</v>
-      </c>
-      <c r="S53" s="23">
-        <v>0</v>
-      </c>
-      <c r="T53" s="25">
-        <v>0</v>
-      </c>
-      <c r="U53" s="23">
-        <v>15</v>
-      </c>
-      <c r="V53" s="23">
-        <v>4</v>
-      </c>
-      <c r="W53" s="23">
-        <f t="shared" ref="W53" si="53">+U53+V53-1</f>
-        <v>18</v>
-      </c>
-      <c r="X53" s="23">
-        <v>1</v>
-      </c>
-      <c r="Y53" s="3">
-        <v>18</v>
-      </c>
-      <c r="Z53" s="6">
-        <v>19</v>
-      </c>
-      <c r="AA53" s="6">
-        <f t="shared" ref="AA53" si="54">+Z53+AB53-1</f>
-        <v>22</v>
-      </c>
-      <c r="AB53" s="23">
-        <v>4</v>
-      </c>
-      <c r="AC53" s="23"/>
-      <c r="AD53" s="23"/>
-      <c r="AE53" s="23">
-        <v>46</v>
-      </c>
-      <c r="AF53" s="23">
-        <f t="shared" ref="AF53" si="55">+AE53+AA53-1</f>
-        <v>67</v>
-      </c>
-      <c r="AG53" s="23">
-        <v>3</v>
-      </c>
-      <c r="AH53" s="23">
-        <f t="shared" ref="AH53" si="56">+AF53+AG53</f>
-        <v>70</v>
-      </c>
-      <c r="AI53" s="23">
-        <v>7</v>
-      </c>
-      <c r="AJ53" s="23">
-        <f t="shared" ref="AJ53" si="57">+AI53+AH53</f>
-        <v>77</v>
-      </c>
-      <c r="AK53" s="23"/>
-      <c r="AL53" s="23">
-        <v>3</v>
-      </c>
-      <c r="AM53" s="23">
-        <f t="shared" ref="AM53" si="58">+AJ53+AL53</f>
-        <v>80</v>
-      </c>
-      <c r="AN53" s="23">
-        <v>2</v>
-      </c>
-      <c r="AO53" s="23">
-        <f t="shared" ref="AO53" si="59">+AM53+AN53</f>
-        <v>82</v>
-      </c>
-      <c r="AP53" s="23">
-        <v>2</v>
-      </c>
-      <c r="AQ53" s="23">
-        <f t="shared" ref="AQ53" si="60">+AO53+AP53</f>
-        <v>84</v>
-      </c>
-      <c r="AR53" s="23">
-        <f t="shared" ref="AR53" si="61">+AQ53+7</f>
-        <v>91</v>
-      </c>
-      <c r="AS53" s="23">
-        <f t="shared" ref="AS53" si="62">+AR53+7+AT53</f>
-        <v>112</v>
-      </c>
-      <c r="AT53" s="23">
-        <v>14</v>
-      </c>
-      <c r="AU53" s="3">
-        <f t="shared" ref="AU53" si="63">+AA53-R53</f>
-        <v>22</v>
-      </c>
-      <c r="AV53" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="AW53" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="AX53" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="AY53" s="37">
-        <v>46143</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY53" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="910"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AY52" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 K16:K1048195 C16:E1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 K16:K1048194 C16:E1048194" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
       <formula1>shippername</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 H54:K1048195 K2:K53 J12:J53 I2:I53 C2:E1048195" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 H54:K1048194 C2:E1048194 I2:I53 J12:J53 K2:K53" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
       <formula1>AILNname</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048195" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048194" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">
       <formula1>plantname</formula1>
     </dataValidation>
   </dataValidations>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA28F970-B2FB-461C-8EB5-EB6F689ED244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9744A0-E752-4503-951E-25F4975C4361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -366,7 +366,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="173">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -895,7 +895,7 @@
     <numFmt numFmtId="164" formatCode="0000000000"/>
     <numFmt numFmtId="165" formatCode="00########"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -979,6 +979,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="15">
@@ -1095,7 +1101,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1217,6 +1223,16 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1553,23 +1569,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4">
+  <sheetPr codeName="Feuil4" filterMode="1">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:BF53"/>
+  <dimension ref="A1:BF71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.453125" defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.54296875" customWidth="1"/>
     <col min="2" max="2" width="12.81640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.453125" customWidth="1"/>
     <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.453125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.26953125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.54296875" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.81640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.453125" style="9" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.453125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.453125" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.26953125" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.54296875" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.81640625" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.453125" style="9" customWidth="1"/>
     <col min="13" max="13" width="10.453125" customWidth="1"/>
     <col min="14" max="14" width="14.54296875" customWidth="1"/>
     <col min="15" max="28" width="10.453125" customWidth="1"/>
@@ -1752,7 +1768,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>60</v>
       </c>
@@ -1925,7 +1941,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>120</v>
       </c>
@@ -2098,7 +2114,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>121</v>
       </c>
@@ -2271,7 +2287,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>233</v>
       </c>
@@ -2444,7 +2460,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>416</v>
       </c>
@@ -2617,7 +2633,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>752</v>
       </c>
@@ -2788,7 +2804,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>761</v>
       </c>
@@ -2958,7 +2974,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>888</v>
       </c>
@@ -3130,7 +3146,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>901</v>
       </c>
@@ -3303,7 +3319,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>904</v>
       </c>
@@ -3476,7 +3492,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>906</v>
       </c>
@@ -3649,7 +3665,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>907</v>
       </c>
@@ -3822,7 +3838,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>908</v>
       </c>
@@ -3995,7 +4011,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>910</v>
       </c>
@@ -4169,7 +4185,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>912</v>
       </c>
@@ -4342,7 +4358,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -4515,179 +4531,169 @@
       </c>
     </row>
     <row r="18" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="A18" s="5">
-        <v>916</v>
-      </c>
-      <c r="B18" s="32" t="s">
+      <c r="A18" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="C18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="32" t="s">
         <v>81</v>
       </c>
       <c r="F18" s="19">
-        <v>91017700</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>157</v>
+        <v>90016500</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>159</v>
       </c>
       <c r="H18" s="2">
-        <v>95207</v>
+        <v>0</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="J18" s="2">
-        <v>95207</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>30</v>
+        <v>29159</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>137</v>
       </c>
       <c r="L18" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M18" s="3">
-        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="N18" s="23">
+        <v>1</v>
+      </c>
+      <c r="O18" s="3">
+        <f>IF(I18="SFK Freight Forwarder",M18,M18+N18-1)</f>
+        <v>8</v>
+      </c>
+      <c r="P18" s="3">
+        <v>6</v>
+      </c>
+      <c r="Q18" s="3">
+        <f>+IF(I18="SFK Freight Forwarder",O18,O18+P18-1)</f>
+        <v>13</v>
+      </c>
+      <c r="R18" s="23">
         <v>9</v>
       </c>
-      <c r="N18" s="3">
-        <v>7</v>
-      </c>
-      <c r="O18" s="3">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="P18" s="3">
-        <f t="shared" si="2"/>
+      <c r="S18" s="23">
+        <v>12</v>
+      </c>
+      <c r="T18" s="23">
+        <f>+R18+S18-1</f>
+        <v>20</v>
+      </c>
+      <c r="U18" s="23">
+        <f>+T18+2</f>
+        <v>22</v>
+      </c>
+      <c r="V18" s="23">
         <v>5</v>
       </c>
-      <c r="Q18" s="3">
-        <f t="shared" si="3"/>
-        <v>19</v>
-      </c>
-      <c r="R18" s="3">
-        <f t="shared" si="4"/>
-        <v>16</v>
-      </c>
-      <c r="S18" s="3">
-        <v>7</v>
-      </c>
-      <c r="T18" s="3">
-        <f t="shared" si="5"/>
-        <v>22</v>
-      </c>
-      <c r="U18" s="3">
-        <f t="shared" si="6"/>
-        <v>23</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="23">
+        <f>+U18+V18-1</f>
+        <v>26</v>
+      </c>
+      <c r="X18" s="23">
         <v>4</v>
       </c>
-      <c r="W18" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
-      </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z18" s="6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" ref="AA18:AA51" si="18">+Z18+AB18-1</f>
-        <v>33</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>3</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>5</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>12</v>
-      </c>
-      <c r="AE18" s="3">
+        <v>36</v>
+      </c>
+      <c r="AB18" s="23">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="23"/>
+      <c r="AD18" s="23"/>
+      <c r="AE18" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF18" s="23">
+        <f>+AE18+AA18-1</f>
+        <v>69</v>
+      </c>
+      <c r="AG18" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH18" s="23">
+        <f>+AF18+AG18</f>
+        <v>72</v>
+      </c>
+      <c r="AI18" s="23">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="23">
+        <f>+AI18+AH18</f>
+        <v>72</v>
+      </c>
+      <c r="AK18" s="23"/>
+      <c r="AL18" s="23">
+        <v>2</v>
+      </c>
+      <c r="AM18" s="23">
+        <f>+AJ18+AL18</f>
+        <v>74</v>
+      </c>
+      <c r="AN18" s="23">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="23">
+        <f>+AM18+AN18</f>
+        <v>75</v>
+      </c>
+      <c r="AP18" s="23">
+        <v>3</v>
+      </c>
+      <c r="AQ18" s="3">
+        <f>+AO18+AP18</f>
+        <v>78</v>
+      </c>
+      <c r="AR18" s="23">
+        <f>+AQ18+4</f>
+        <v>82</v>
+      </c>
+      <c r="AS18" s="23">
+        <f>+AR18+7+AT18</f>
+        <v>103</v>
+      </c>
+      <c r="AT18" s="23">
+        <v>14</v>
+      </c>
+      <c r="AU18" s="3">
+        <f>+AA18-R18</f>
         <v>27</v>
       </c>
-      <c r="AF18" s="3">
-        <f t="shared" si="9"/>
-        <v>59</v>
-      </c>
-      <c r="AG18" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH18" s="6">
-        <f t="shared" si="10"/>
-        <v>62</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>7</v>
-      </c>
-      <c r="AJ18" s="3">
-        <f t="shared" si="11"/>
-        <v>69</v>
-      </c>
-      <c r="AK18" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AL18" s="3">
-        <v>2</v>
-      </c>
-      <c r="AM18" s="3">
-        <f t="shared" si="12"/>
-        <v>71</v>
-      </c>
-      <c r="AN18" s="3">
-        <v>9</v>
-      </c>
-      <c r="AO18" s="3">
-        <f t="shared" si="13"/>
-        <v>80</v>
-      </c>
-      <c r="AP18" s="3">
-        <v>4</v>
-      </c>
-      <c r="AQ18" s="3">
-        <f t="shared" si="14"/>
-        <v>84</v>
-      </c>
-      <c r="AR18" s="3">
-        <f t="shared" si="15"/>
-        <v>91</v>
-      </c>
-      <c r="AS18" s="3">
-        <f t="shared" si="16"/>
-        <v>111</v>
-      </c>
-      <c r="AT18" s="3">
-        <v>13</v>
-      </c>
-      <c r="AU18" s="3">
-        <f t="shared" si="17"/>
-        <v>17</v>
-      </c>
-      <c r="AV18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AW18" s="3" t="s">
+      <c r="AV18" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW18" s="23" t="s">
         <v>131</v>
       </c>
       <c r="AX18" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AY18" s="21">
-        <v>46507</v>
+      <c r="AY18" s="40">
+        <v>46508</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>917</v>
       </c>
@@ -4725,44 +4731,44 @@
         <v>2</v>
       </c>
       <c r="M19" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I19="SFK Freight Forwarder",L19,9)</f>
         <v>9</v>
       </c>
       <c r="N19" s="3">
         <v>14</v>
       </c>
       <c r="O19" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I19="SFK Freight Forwarder",M19,M19+N19-1)</f>
         <v>22</v>
       </c>
       <c r="P19" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I19="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q19" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I19="SFK Freight Forwarder",O19,O19+P19-1)</f>
         <v>26</v>
       </c>
       <c r="R19" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N19</f>
         <v>23</v>
       </c>
       <c r="S19" s="3">
         <v>7</v>
       </c>
       <c r="T19" s="3">
-        <f t="shared" si="5"/>
+        <f>+R19+S19-1</f>
         <v>29</v>
       </c>
       <c r="U19" s="3">
-        <f t="shared" si="6"/>
+        <f>+T19+1</f>
         <v>30</v>
       </c>
       <c r="V19" s="3">
         <v>2</v>
       </c>
       <c r="W19" s="3">
-        <f t="shared" si="7"/>
+        <f>+U19+V19-1</f>
         <v>31</v>
       </c>
       <c r="X19" s="3">
@@ -4775,7 +4781,7 @@
         <v>36</v>
       </c>
       <c r="AA19" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z19+AB19-1</f>
         <v>37</v>
       </c>
       <c r="AB19" s="3">
@@ -4791,21 +4797,21 @@
         <v>37</v>
       </c>
       <c r="AF19" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE19+AA19-1</f>
         <v>73</v>
       </c>
       <c r="AG19" s="6">
         <v>3</v>
       </c>
       <c r="AH19" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF19+AG19</f>
         <v>76</v>
       </c>
       <c r="AI19" s="3">
         <v>14</v>
       </c>
       <c r="AJ19" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI19+AH19</f>
         <v>90</v>
       </c>
       <c r="AK19" s="3" t="s">
@@ -4815,36 +4821,36 @@
         <v>2</v>
       </c>
       <c r="AM19" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ19+AL19</f>
         <v>92</v>
       </c>
       <c r="AN19" s="3">
         <v>2</v>
       </c>
       <c r="AO19" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM19+AN19</f>
         <v>94</v>
       </c>
       <c r="AP19" s="3">
         <v>4</v>
       </c>
       <c r="AQ19" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO19+AP19</f>
         <v>98</v>
       </c>
       <c r="AR19" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ19+7</f>
         <v>105</v>
       </c>
       <c r="AS19" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR19+7+AT19</f>
         <v>126</v>
       </c>
       <c r="AT19" s="3">
         <v>14</v>
       </c>
       <c r="AU19" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA19-R19</f>
         <v>14</v>
       </c>
       <c r="AV19" s="3" t="s">
@@ -4861,187 +4867,187 @@
       </c>
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="A20" s="5">
-        <v>918</v>
-      </c>
-      <c r="B20" s="33" t="s">
+      <c r="A20" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>81</v>
+      <c r="C20" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>53</v>
       </c>
       <c r="F20" s="19">
-        <v>91017700</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>157</v>
+        <v>90016500</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>159</v>
       </c>
       <c r="H20" s="2">
-        <v>2533780546</v>
+        <v>0</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="J20" s="2">
-        <v>2533780546</v>
+        <v>29159</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="L20" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M20" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I20="SFK Freight Forwarder",L20,9)</f>
         <v>9</v>
       </c>
       <c r="N20" s="3">
         <v>14</v>
       </c>
       <c r="O20" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I20="SFK Freight Forwarder",M20,M20+N20-1)</f>
         <v>22</v>
       </c>
       <c r="P20" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I20="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q20" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I20="SFK Freight Forwarder",O20,O20+P20-1)</f>
         <v>26</v>
       </c>
       <c r="R20" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N20</f>
         <v>23</v>
       </c>
       <c r="S20" s="3">
         <v>7</v>
       </c>
       <c r="T20" s="3">
-        <f t="shared" si="5"/>
+        <f>+R20+S20-1</f>
         <v>29</v>
       </c>
       <c r="U20" s="3">
-        <f t="shared" si="6"/>
+        <f>+T20+1</f>
         <v>30</v>
       </c>
       <c r="V20" s="3">
         <v>2</v>
       </c>
       <c r="W20" s="3">
-        <f t="shared" si="7"/>
+        <f>+U20+V20-1</f>
         <v>31</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y20" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Z20" s="6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AA20" s="6">
-        <f t="shared" si="18"/>
-        <v>37</v>
+        <f>+Z20+AB20-1</f>
+        <v>38</v>
       </c>
       <c r="AB20" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC20" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD20" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE20" s="3">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF20" s="3">
-        <f t="shared" si="9"/>
-        <v>72</v>
+        <f>+AE20+AA20-1</f>
+        <v>79</v>
       </c>
       <c r="AG20" s="6">
         <v>3</v>
       </c>
       <c r="AH20" s="6">
-        <f t="shared" si="10"/>
-        <v>75</v>
+        <f>+AF20+AG20</f>
+        <v>82</v>
       </c>
       <c r="AI20" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AJ20" s="3">
-        <f t="shared" si="11"/>
-        <v>89</v>
+        <f>+AI20+AH20</f>
+        <v>82</v>
       </c>
       <c r="AK20" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL20" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM20" s="3">
-        <f t="shared" si="12"/>
-        <v>91</v>
+        <f>+AJ20+AL20</f>
+        <v>83</v>
       </c>
       <c r="AN20" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AO20" s="3">
-        <f t="shared" si="13"/>
-        <v>98</v>
+        <f>+AM20+AN20</f>
+        <v>84</v>
       </c>
       <c r="AP20" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ20" s="3">
-        <f t="shared" si="14"/>
-        <v>98</v>
+        <f>+AO20+AP20</f>
+        <v>87</v>
       </c>
       <c r="AR20" s="3">
-        <f t="shared" si="15"/>
-        <v>105</v>
+        <f>+AQ20+7</f>
+        <v>94</v>
       </c>
       <c r="AS20" s="3">
-        <f t="shared" si="16"/>
-        <v>126</v>
+        <f>+AR20+7+AT20</f>
+        <v>101</v>
       </c>
       <c r="AT20" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AU20" s="3">
-        <f t="shared" si="17"/>
-        <v>14</v>
+        <f>+AA20-R20</f>
+        <v>15</v>
       </c>
       <c r="AV20" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AW20" s="3" t="s">
         <v>131</v>
       </c>
       <c r="AX20" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="AY20" s="21">
+        <v>88</v>
+      </c>
+      <c r="AY20" s="40">
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
-        <v>920</v>
-      </c>
-      <c r="B21" s="33" t="s">
+        <v>916</v>
+      </c>
+      <c r="B21" s="32" t="s">
         <v>80</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>58</v>
@@ -5050,148 +5056,148 @@
         <v>81</v>
       </c>
       <c r="F21" s="19">
-        <v>91017500</v>
-      </c>
-      <c r="G21" s="35" t="s">
+        <v>91017700</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>157</v>
       </c>
       <c r="H21" s="2">
-        <v>2533780535</v>
+        <v>95207</v>
       </c>
       <c r="I21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21" s="2">
+        <v>95207</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L21" s="3">
+        <v>7</v>
+      </c>
+      <c r="M21" s="3">
+        <f>+IF(I21="SFK Freight Forwarder",L21,9)</f>
+        <v>9</v>
+      </c>
+      <c r="N21" s="3">
+        <v>7</v>
+      </c>
+      <c r="O21" s="3">
+        <f>IF(I21="SFK Freight Forwarder",M21,M21+N21-1)</f>
+        <v>15</v>
+      </c>
+      <c r="P21" s="3">
+        <f>+IF(I21="SFK Freight Forwarder",0,5)</f>
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
+        <f>+IF(I21="SFK Freight Forwarder",O21,O21+P21-1)</f>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3">
+        <f>9+N21</f>
+        <v>16</v>
+      </c>
+      <c r="S21" s="3">
+        <v>7</v>
+      </c>
+      <c r="T21" s="3">
+        <f>+R21+S21-1</f>
         <v>22</v>
       </c>
-      <c r="J21" s="2">
-        <v>2533780535</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" s="3">
-        <v>7</v>
-      </c>
-      <c r="M21" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="N21" s="3">
-        <v>14</v>
-      </c>
-      <c r="O21" s="3">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="P21" s="3">
-        <f t="shared" si="2"/>
+      <c r="U21" s="3">
+        <f>+T21+1</f>
+        <v>23</v>
+      </c>
+      <c r="V21" s="3">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3">
+        <f>+U21+V21-1</f>
+        <v>26</v>
+      </c>
+      <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>26</v>
+      </c>
+      <c r="Z21" s="6">
+        <v>31</v>
+      </c>
+      <c r="AA21" s="6">
+        <f>+Z21+AB21-1</f>
+        <v>33</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
-        <f t="shared" si="3"/>
-        <v>26</v>
-      </c>
-      <c r="R21" s="3">
-        <f t="shared" si="4"/>
-        <v>23</v>
-      </c>
-      <c r="S21" s="3">
-        <v>7</v>
-      </c>
-      <c r="T21" s="3">
-        <f t="shared" si="5"/>
-        <v>29</v>
-      </c>
-      <c r="U21" s="3">
-        <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-      <c r="V21" s="3">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3">
-        <f t="shared" si="7"/>
-        <v>32</v>
-      </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>33</v>
-      </c>
-      <c r="Z21" s="6">
-        <v>37</v>
-      </c>
-      <c r="AA21" s="6">
-        <f t="shared" si="18"/>
-        <v>39</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>3</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>6</v>
-      </c>
       <c r="AD21" s="3">
+        <v>12</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>27</v>
+      </c>
+      <c r="AF21" s="3">
+        <f>+AE21+AA21-1</f>
+        <v>59</v>
+      </c>
+      <c r="AG21" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH21" s="6">
+        <f>+AF21+AG21</f>
+        <v>62</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>7</v>
+      </c>
+      <c r="AJ21" s="3">
+        <f>+AI21+AH21</f>
+        <v>69</v>
+      </c>
+      <c r="AK21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL21" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM21" s="3">
+        <f>+AJ21+AL21</f>
+        <v>71</v>
+      </c>
+      <c r="AN21" s="3">
+        <v>8</v>
+      </c>
+      <c r="AO21" s="3">
+        <f>+AM21+AN21</f>
+        <v>79</v>
+      </c>
+      <c r="AP21" s="3">
+        <v>2</v>
+      </c>
+      <c r="AQ21" s="3">
+        <f>+AO21+AP21</f>
+        <v>81</v>
+      </c>
+      <c r="AR21" s="3">
+        <f>+AQ21+7</f>
+        <v>88</v>
+      </c>
+      <c r="AS21" s="3">
+        <f>+AR21+7+AT21</f>
+        <v>108</v>
+      </c>
+      <c r="AT21" s="3">
         <v>13</v>
       </c>
-      <c r="AE21" s="3">
-        <v>39</v>
-      </c>
-      <c r="AF21" s="3">
-        <f t="shared" si="9"/>
-        <v>77</v>
-      </c>
-      <c r="AG21" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH21" s="6">
-        <f t="shared" si="10"/>
-        <v>80</v>
-      </c>
-      <c r="AI21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="3">
-        <f t="shared" si="11"/>
-        <v>80</v>
-      </c>
-      <c r="AK21" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL21" s="3">
-        <v>3</v>
-      </c>
-      <c r="AM21" s="3">
-        <f t="shared" si="12"/>
-        <v>83</v>
-      </c>
-      <c r="AN21" s="3">
-        <v>9</v>
-      </c>
-      <c r="AO21" s="3">
-        <f t="shared" si="13"/>
-        <v>92</v>
-      </c>
-      <c r="AP21" s="3">
-        <v>6</v>
-      </c>
-      <c r="AQ21" s="3">
-        <f t="shared" si="14"/>
-        <v>98</v>
-      </c>
-      <c r="AR21" s="3">
-        <f t="shared" si="15"/>
-        <v>105</v>
-      </c>
-      <c r="AS21" s="3">
-        <f t="shared" si="16"/>
-        <v>126</v>
-      </c>
-      <c r="AT21" s="3">
-        <v>14</v>
-      </c>
       <c r="AU21" s="3">
-        <f t="shared" si="17"/>
-        <v>16</v>
+        <f>+AA21-R21</f>
+        <v>17</v>
       </c>
       <c r="AV21" s="3" t="s">
         <v>130</v>
@@ -5206,7 +5212,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5244,44 +5250,44 @@
         <v>2</v>
       </c>
       <c r="M22" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I22="SFK Freight Forwarder",L22,9)</f>
         <v>9</v>
       </c>
       <c r="N22" s="3">
         <v>14</v>
       </c>
       <c r="O22" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I22="SFK Freight Forwarder",M22,M22+N22-1)</f>
         <v>22</v>
       </c>
       <c r="P22" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I22="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q22" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I22="SFK Freight Forwarder",O22,O22+P22-1)</f>
         <v>26</v>
       </c>
       <c r="R22" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N22</f>
         <v>23</v>
       </c>
       <c r="S22" s="3">
         <v>7</v>
       </c>
       <c r="T22" s="3">
-        <f t="shared" si="5"/>
+        <f>+R22+S22-1</f>
         <v>29</v>
       </c>
       <c r="U22" s="3">
-        <f t="shared" si="6"/>
+        <f>+T22+1</f>
         <v>30</v>
       </c>
       <c r="V22" s="3">
         <v>3</v>
       </c>
       <c r="W22" s="3">
-        <f t="shared" si="7"/>
+        <f>+U22+V22-1</f>
         <v>32</v>
       </c>
       <c r="X22" s="3">
@@ -5294,7 +5300,7 @@
         <v>37</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z22+AB22-1</f>
         <v>39</v>
       </c>
       <c r="AB22" s="3">
@@ -5310,21 +5316,21 @@
         <v>46</v>
       </c>
       <c r="AF22" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE22+AA22-1</f>
         <v>84</v>
       </c>
       <c r="AG22" s="6">
         <v>3</v>
       </c>
       <c r="AH22" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF22+AG22</f>
         <v>87</v>
       </c>
       <c r="AI22" s="3">
         <v>7</v>
       </c>
       <c r="AJ22" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI22+AH22</f>
         <v>94</v>
       </c>
       <c r="AK22" s="3" t="s">
@@ -5334,36 +5340,36 @@
         <v>2</v>
       </c>
       <c r="AM22" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ22+AL22</f>
         <v>96</v>
       </c>
       <c r="AN22" s="3">
         <v>2</v>
       </c>
       <c r="AO22" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM22+AN22</f>
         <v>98</v>
       </c>
       <c r="AP22" s="3">
         <v>0</v>
       </c>
       <c r="AQ22" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO22+AP22</f>
         <v>98</v>
       </c>
       <c r="AR22" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ22+7</f>
         <v>105</v>
       </c>
       <c r="AS22" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR22+7+AT22</f>
         <v>126</v>
       </c>
       <c r="AT22" s="3">
         <v>14</v>
       </c>
       <c r="AU22" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA22-R22</f>
         <v>16</v>
       </c>
       <c r="AV22" s="3" t="s">
@@ -5379,7 +5385,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>924</v>
       </c>
@@ -5417,44 +5423,44 @@
         <v>7</v>
       </c>
       <c r="M23" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I23="SFK Freight Forwarder",L23,9)</f>
         <v>9</v>
       </c>
       <c r="N23" s="3">
         <v>7</v>
       </c>
       <c r="O23" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I23="SFK Freight Forwarder",M23,M23+N23-1)</f>
         <v>15</v>
       </c>
       <c r="P23" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I23="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q23" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I23="SFK Freight Forwarder",O23,O23+P23-1)</f>
         <v>19</v>
       </c>
       <c r="R23" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N23</f>
         <v>16</v>
       </c>
       <c r="S23" s="3">
         <v>7</v>
       </c>
       <c r="T23" s="3">
-        <f t="shared" si="5"/>
+        <f>+R23+S23-1</f>
         <v>22</v>
       </c>
       <c r="U23" s="3">
-        <f t="shared" si="6"/>
+        <f>+T23+1</f>
         <v>23</v>
       </c>
       <c r="V23" s="3">
         <v>3</v>
       </c>
       <c r="W23" s="3">
-        <f t="shared" si="7"/>
+        <f>+U23+V23-1</f>
         <v>25</v>
       </c>
       <c r="X23" s="3">
@@ -5467,7 +5473,7 @@
         <v>30</v>
       </c>
       <c r="AA23" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z23+AB23-1</f>
         <v>32</v>
       </c>
       <c r="AB23" s="3">
@@ -5483,21 +5489,21 @@
         <v>21</v>
       </c>
       <c r="AF23" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE23+AA23-1</f>
         <v>52</v>
       </c>
       <c r="AG23" s="6">
         <v>3</v>
       </c>
       <c r="AH23" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF23+AG23</f>
         <v>55</v>
       </c>
       <c r="AI23" s="3">
         <v>0</v>
       </c>
       <c r="AJ23" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI23+AH23</f>
         <v>55</v>
       </c>
       <c r="AK23" s="3" t="s">
@@ -5507,36 +5513,36 @@
         <v>1</v>
       </c>
       <c r="AM23" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ23+AL23</f>
         <v>56</v>
       </c>
       <c r="AN23" s="3">
         <v>8</v>
       </c>
       <c r="AO23" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM23+AN23</f>
         <v>64</v>
       </c>
       <c r="AP23" s="3">
         <v>6</v>
       </c>
       <c r="AQ23" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO23+AP23</f>
         <v>70</v>
       </c>
       <c r="AR23" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ23+7</f>
         <v>77</v>
       </c>
       <c r="AS23" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR23+7+AT23</f>
         <v>84</v>
       </c>
       <c r="AT23" s="3">
         <v>0</v>
       </c>
       <c r="AU23" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA23-R23</f>
         <v>16</v>
       </c>
       <c r="AV23" s="3" t="s">
@@ -5552,7 +5558,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>925</v>
       </c>
@@ -5590,44 +5596,44 @@
         <v>7</v>
       </c>
       <c r="M24" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I24="SFK Freight Forwarder",L24,9)</f>
         <v>9</v>
       </c>
       <c r="N24" s="3">
         <v>14</v>
       </c>
       <c r="O24" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I24="SFK Freight Forwarder",M24,M24+N24-1)</f>
         <v>22</v>
       </c>
       <c r="P24" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I24="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q24" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I24="SFK Freight Forwarder",O24,O24+P24-1)</f>
         <v>26</v>
       </c>
       <c r="R24" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N24</f>
         <v>23</v>
       </c>
       <c r="S24" s="3">
         <v>7</v>
       </c>
       <c r="T24" s="3">
-        <f t="shared" si="5"/>
+        <f>+R24+S24-1</f>
         <v>29</v>
       </c>
       <c r="U24" s="3">
-        <f t="shared" si="6"/>
+        <f>+T24+1</f>
         <v>30</v>
       </c>
       <c r="V24" s="3">
         <v>2</v>
       </c>
       <c r="W24" s="3">
-        <f t="shared" si="7"/>
+        <f>+U24+V24-1</f>
         <v>31</v>
       </c>
       <c r="X24" s="3">
@@ -5640,7 +5646,7 @@
         <v>33</v>
       </c>
       <c r="AA24" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z24+AB24-1</f>
         <v>35</v>
       </c>
       <c r="AB24" s="3">
@@ -5656,21 +5662,21 @@
         <v>40</v>
       </c>
       <c r="AF24" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE24+AA24-1</f>
         <v>74</v>
       </c>
       <c r="AG24" s="6">
         <v>3</v>
       </c>
       <c r="AH24" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF24+AG24</f>
         <v>77</v>
       </c>
       <c r="AI24" s="3">
         <v>14</v>
       </c>
       <c r="AJ24" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI24+AH24</f>
         <v>91</v>
       </c>
       <c r="AK24" s="3" t="s">
@@ -5680,36 +5686,36 @@
         <v>2</v>
       </c>
       <c r="AM24" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ24+AL24</f>
         <v>93</v>
       </c>
       <c r="AN24" s="3">
         <v>2</v>
       </c>
       <c r="AO24" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM24+AN24</f>
         <v>95</v>
       </c>
       <c r="AP24" s="3">
         <v>3</v>
       </c>
       <c r="AQ24" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO24+AP24</f>
         <v>98</v>
       </c>
       <c r="AR24" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ24+7</f>
         <v>105</v>
       </c>
       <c r="AS24" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR24+7+AT24</f>
         <v>126</v>
       </c>
       <c r="AT24" s="3">
         <v>14</v>
       </c>
       <c r="AU24" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA24-R24</f>
         <v>12</v>
       </c>
       <c r="AV24" s="3" t="s">
@@ -5725,7 +5731,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -5763,44 +5769,44 @@
         <v>2</v>
       </c>
       <c r="M25" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I25="SFK Freight Forwarder",L25,9)</f>
         <v>9</v>
       </c>
       <c r="N25" s="3">
         <v>14</v>
       </c>
       <c r="O25" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I25="SFK Freight Forwarder",M25,M25+N25-1)</f>
         <v>22</v>
       </c>
       <c r="P25" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I25="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q25" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I25="SFK Freight Forwarder",O25,O25+P25-1)</f>
         <v>26</v>
       </c>
       <c r="R25" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N25</f>
         <v>23</v>
       </c>
       <c r="S25" s="3">
         <v>7</v>
       </c>
       <c r="T25" s="3">
-        <f t="shared" si="5"/>
+        <f>+R25+S25-1</f>
         <v>29</v>
       </c>
       <c r="U25" s="3">
-        <f t="shared" si="6"/>
+        <f>+T25+1</f>
         <v>30</v>
       </c>
       <c r="V25" s="3">
         <v>1</v>
       </c>
       <c r="W25" s="3">
-        <f t="shared" si="7"/>
+        <f>+U25+V25-1</f>
         <v>30</v>
       </c>
       <c r="X25" s="3">
@@ -5813,7 +5819,7 @@
         <v>30</v>
       </c>
       <c r="AA25" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z25+AB25-1</f>
         <v>32</v>
       </c>
       <c r="AB25" s="3">
@@ -5829,21 +5835,21 @@
         <v>46</v>
       </c>
       <c r="AF25" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE25+AA25-1</f>
         <v>77</v>
       </c>
       <c r="AG25" s="6">
         <v>3</v>
       </c>
       <c r="AH25" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF25+AG25</f>
         <v>80</v>
       </c>
       <c r="AI25" s="3">
         <v>14</v>
       </c>
       <c r="AJ25" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI25+AH25</f>
         <v>94</v>
       </c>
       <c r="AK25" s="3" t="s">
@@ -5853,36 +5859,36 @@
         <v>4</v>
       </c>
       <c r="AM25" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ25+AL25</f>
         <v>98</v>
       </c>
       <c r="AN25" s="3">
         <v>3</v>
       </c>
       <c r="AO25" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM25+AN25</f>
         <v>101</v>
       </c>
       <c r="AP25" s="3">
         <v>4</v>
       </c>
       <c r="AQ25" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO25+AP25</f>
         <v>105</v>
       </c>
       <c r="AR25" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ25+7</f>
         <v>112</v>
       </c>
       <c r="AS25" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR25+7+AT25</f>
         <v>133</v>
       </c>
       <c r="AT25" s="3">
         <v>14</v>
       </c>
       <c r="AU25" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA25-R25</f>
         <v>9</v>
       </c>
       <c r="AV25" s="3" t="s">
@@ -5898,7 +5904,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>928</v>
       </c>
@@ -5936,44 +5942,44 @@
         <v>7</v>
       </c>
       <c r="M26" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I26="SFK Freight Forwarder",L26,9)</f>
         <v>9</v>
       </c>
       <c r="N26" s="3">
         <v>7</v>
       </c>
       <c r="O26" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I26="SFK Freight Forwarder",M26,M26+N26-1)</f>
         <v>15</v>
       </c>
       <c r="P26" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I26="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q26" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I26="SFK Freight Forwarder",O26,O26+P26-1)</f>
         <v>19</v>
       </c>
       <c r="R26" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N26</f>
         <v>16</v>
       </c>
       <c r="S26" s="3">
         <v>7</v>
       </c>
       <c r="T26" s="3">
-        <f t="shared" si="5"/>
+        <f>+R26+S26-1</f>
         <v>22</v>
       </c>
       <c r="U26" s="3">
-        <f t="shared" si="6"/>
+        <f>+T26+1</f>
         <v>23</v>
       </c>
       <c r="V26" s="3">
         <v>2</v>
       </c>
       <c r="W26" s="3">
-        <f t="shared" si="7"/>
+        <f>+U26+V26-1</f>
         <v>24</v>
       </c>
       <c r="X26" s="3">
@@ -5986,7 +5992,7 @@
         <v>31</v>
       </c>
       <c r="AA26" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z26+AB26-1</f>
         <v>33</v>
       </c>
       <c r="AB26" s="3">
@@ -6002,21 +6008,21 @@
         <v>21</v>
       </c>
       <c r="AF26" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE26+AA26-1</f>
         <v>53</v>
       </c>
       <c r="AG26" s="6">
         <v>3</v>
       </c>
       <c r="AH26" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF26+AG26</f>
         <v>56</v>
       </c>
       <c r="AI26" s="3">
         <v>7</v>
       </c>
       <c r="AJ26" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI26+AH26</f>
         <v>63</v>
       </c>
       <c r="AK26" s="3" t="s">
@@ -6026,36 +6032,36 @@
         <v>2</v>
       </c>
       <c r="AM26" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ26+AL26</f>
         <v>65</v>
       </c>
       <c r="AN26" s="3">
         <v>2</v>
       </c>
       <c r="AO26" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM26+AN26</f>
         <v>67</v>
       </c>
       <c r="AP26" s="3">
         <v>3</v>
       </c>
       <c r="AQ26" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO26+AP26</f>
         <v>70</v>
       </c>
       <c r="AR26" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ26+7</f>
         <v>77</v>
       </c>
       <c r="AS26" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR26+7+AT26</f>
         <v>98</v>
       </c>
       <c r="AT26" s="3">
         <v>14</v>
       </c>
       <c r="AU26" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA26-R26</f>
         <v>17</v>
       </c>
       <c r="AV26" s="3" t="s">
@@ -6071,15 +6077,15 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
-        <v>930</v>
-      </c>
-      <c r="B27" s="32" t="s">
+        <v>918</v>
+      </c>
+      <c r="B27" s="33" t="s">
         <v>80</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>58</v>
@@ -6090,144 +6096,145 @@
       <c r="F27" s="19">
         <v>91017700</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="35" t="s">
         <v>157</v>
       </c>
       <c r="H27" s="2">
-        <v>26037000</v>
+        <v>2533780546</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="J27" s="2">
-        <v>26037000</v>
+        <v>2533780546</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="L27" s="3">
         <v>2</v>
       </c>
       <c r="M27" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I27="SFK Freight Forwarder",L27,9)</f>
         <v>9</v>
       </c>
       <c r="N27" s="3">
         <v>14</v>
       </c>
       <c r="O27" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I27="SFK Freight Forwarder",M27,M27+N27-1)</f>
         <v>22</v>
       </c>
       <c r="P27" s="3">
+        <f>+IF(I27="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q27" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I27="SFK Freight Forwarder",O27,O27+P27-1)</f>
         <v>26</v>
       </c>
       <c r="R27" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N27</f>
         <v>23</v>
       </c>
       <c r="S27" s="3">
         <v>7</v>
       </c>
       <c r="T27" s="3">
-        <f t="shared" si="5"/>
+        <f>+R27+S27-1</f>
         <v>29</v>
       </c>
       <c r="U27" s="3">
-        <f t="shared" si="6"/>
+        <f>+T27+1</f>
         <v>30</v>
       </c>
       <c r="V27" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W27" s="3">
-        <f t="shared" si="7"/>
-        <v>30</v>
+        <f>+U27+V27-1</f>
+        <v>31</v>
       </c>
       <c r="X27" s="3">
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z27" s="6">
         <v>35</v>
       </c>
       <c r="AA27" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z27+AB27-1</f>
         <v>37</v>
       </c>
       <c r="AB27" s="3">
         <v>3</v>
       </c>
       <c r="AC27" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AD27" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE27" s="3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF27" s="3">
-        <f t="shared" si="9"/>
-        <v>76</v>
+        <f>+AE27+AA27-1</f>
+        <v>72</v>
       </c>
       <c r="AG27" s="6">
         <v>3</v>
       </c>
       <c r="AH27" s="6">
-        <f t="shared" si="10"/>
-        <v>79</v>
+        <f>+AF27+AG27</f>
+        <v>75</v>
       </c>
       <c r="AI27" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AJ27" s="3">
-        <f t="shared" si="11"/>
-        <v>86</v>
+        <f>+AI27+AH27</f>
+        <v>89</v>
       </c>
       <c r="AK27" s="3" t="s">
         <v>55</v>
       </c>
       <c r="AL27" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM27" s="3">
-        <f t="shared" si="12"/>
-        <v>89</v>
+        <f>+AJ27+AL27</f>
+        <v>91</v>
       </c>
       <c r="AN27" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO27" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM27+AN27</f>
         <v>99</v>
       </c>
       <c r="AP27" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AQ27" s="3">
-        <f t="shared" si="14"/>
-        <v>105</v>
+        <f>+AO27+AP27</f>
+        <v>101</v>
       </c>
       <c r="AR27" s="3">
-        <f t="shared" si="15"/>
-        <v>112</v>
+        <f>+AQ27+7</f>
+        <v>108</v>
       </c>
       <c r="AS27" s="3">
-        <f t="shared" si="16"/>
-        <v>136</v>
+        <f>+AR27+7+AT27</f>
+        <v>129</v>
       </c>
       <c r="AT27" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AU27" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA27-R27</f>
         <v>14</v>
       </c>
       <c r="AV27" s="3" t="s">
@@ -6243,7 +6250,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>931</v>
       </c>
@@ -6281,44 +6288,44 @@
         <v>7</v>
       </c>
       <c r="M28" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I28="SFK Freight Forwarder",L28,9)</f>
         <v>9</v>
       </c>
       <c r="N28" s="3">
         <v>14</v>
       </c>
       <c r="O28" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I28="SFK Freight Forwarder",M28,M28+N28-1)</f>
         <v>22</v>
       </c>
       <c r="P28" s="3">
-        <f t="shared" ref="P28:P43" si="19">+IF(I28="SFK Freight Forwarder",0,5)</f>
+        <f>+IF(I28="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q28" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I28="SFK Freight Forwarder",O28,O28+P28-1)</f>
         <v>26</v>
       </c>
       <c r="R28" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N28</f>
         <v>23</v>
       </c>
       <c r="S28" s="3">
         <v>7</v>
       </c>
       <c r="T28" s="3">
-        <f t="shared" si="5"/>
+        <f>+R28+S28-1</f>
         <v>29</v>
       </c>
       <c r="U28" s="3">
-        <f t="shared" si="6"/>
+        <f>+T28+1</f>
         <v>30</v>
       </c>
       <c r="V28" s="3">
         <v>1</v>
       </c>
       <c r="W28" s="3">
-        <f t="shared" si="7"/>
+        <f>+U28+V28-1</f>
         <v>30</v>
       </c>
       <c r="X28" s="3">
@@ -6331,7 +6338,7 @@
         <v>33</v>
       </c>
       <c r="AA28" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z28+AB28-1</f>
         <v>35</v>
       </c>
       <c r="AB28" s="3">
@@ -6347,21 +6354,21 @@
         <v>43</v>
       </c>
       <c r="AF28" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE28+AA28-1</f>
         <v>77</v>
       </c>
       <c r="AG28" s="6">
         <v>3</v>
       </c>
       <c r="AH28" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF28+AG28</f>
         <v>80</v>
       </c>
       <c r="AI28" s="3">
         <v>7</v>
       </c>
       <c r="AJ28" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI28+AH28</f>
         <v>87</v>
       </c>
       <c r="AK28" s="3" t="s">
@@ -6371,36 +6378,36 @@
         <v>2</v>
       </c>
       <c r="AM28" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ28+AL28</f>
         <v>89</v>
       </c>
       <c r="AN28" s="3">
         <v>2</v>
       </c>
       <c r="AO28" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM28+AN28</f>
         <v>91</v>
       </c>
       <c r="AP28" s="3">
         <v>0</v>
       </c>
       <c r="AQ28" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO28+AP28</f>
         <v>91</v>
       </c>
       <c r="AR28" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ28+7</f>
         <v>98</v>
       </c>
       <c r="AS28" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR28+7+AT28</f>
         <v>122</v>
       </c>
       <c r="AT28" s="3">
         <v>17</v>
       </c>
       <c r="AU28" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA28-R28</f>
         <v>12</v>
       </c>
       <c r="AV28" s="3" t="s">
@@ -6416,7 +6423,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>932</v>
       </c>
@@ -6454,44 +6461,44 @@
         <v>7</v>
       </c>
       <c r="M29" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I29="SFK Freight Forwarder",L29,9)</f>
         <v>9</v>
       </c>
       <c r="N29" s="3">
         <v>14</v>
       </c>
       <c r="O29" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I29="SFK Freight Forwarder",M29,M29+N29-1)</f>
         <v>22</v>
       </c>
       <c r="P29" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I29="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q29" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I29="SFK Freight Forwarder",O29,O29+P29-1)</f>
         <v>26</v>
       </c>
       <c r="R29" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N29</f>
         <v>23</v>
       </c>
       <c r="S29" s="3">
         <v>7</v>
       </c>
       <c r="T29" s="3">
-        <f t="shared" si="5"/>
+        <f>+R29+S29-1</f>
         <v>29</v>
       </c>
       <c r="U29" s="3">
-        <f t="shared" si="6"/>
+        <f>+T29+1</f>
         <v>30</v>
       </c>
       <c r="V29" s="3">
         <v>1</v>
       </c>
       <c r="W29" s="3">
-        <f t="shared" si="7"/>
+        <f>+U29+V29-1</f>
         <v>30</v>
       </c>
       <c r="X29" s="3">
@@ -6504,7 +6511,7 @@
         <v>35</v>
       </c>
       <c r="AA29" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z29+AB29-1</f>
         <v>37</v>
       </c>
       <c r="AB29" s="3">
@@ -6520,21 +6527,21 @@
         <v>58</v>
       </c>
       <c r="AF29" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE29+AA29-1</f>
         <v>94</v>
       </c>
       <c r="AG29" s="6">
         <v>3</v>
       </c>
       <c r="AH29" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF29+AG29</f>
         <v>97</v>
       </c>
       <c r="AI29" s="3">
         <v>7</v>
       </c>
       <c r="AJ29" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI29+AH29</f>
         <v>104</v>
       </c>
       <c r="AK29" s="3" t="s">
@@ -6544,36 +6551,36 @@
         <v>1</v>
       </c>
       <c r="AM29" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ29+AL29</f>
         <v>105</v>
       </c>
       <c r="AN29" s="3">
         <v>8</v>
       </c>
       <c r="AO29" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM29+AN29</f>
         <v>113</v>
       </c>
       <c r="AP29" s="3">
         <v>6</v>
       </c>
       <c r="AQ29" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO29+AP29</f>
         <v>119</v>
       </c>
       <c r="AR29" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ29+7</f>
         <v>126</v>
       </c>
       <c r="AS29" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR29+7+AT29</f>
         <v>147</v>
       </c>
       <c r="AT29" s="3">
         <v>14</v>
       </c>
       <c r="AU29" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA29-R29</f>
         <v>14</v>
       </c>
       <c r="AV29" s="3" t="s">
@@ -6589,7 +6596,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>1005</v>
       </c>
@@ -6633,37 +6640,37 @@
         <v>14</v>
       </c>
       <c r="O30" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I30="SFK Freight Forwarder",M30,M30+N30-1)</f>
         <v>0</v>
       </c>
       <c r="P30" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I30="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q30" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I30="SFK Freight Forwarder",O30,O30+P30-1)</f>
         <v>0</v>
       </c>
       <c r="R30" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N30</f>
         <v>23</v>
       </c>
       <c r="S30" s="3">
         <v>7</v>
       </c>
       <c r="T30" s="3">
-        <f t="shared" si="5"/>
+        <f>+R30+S30-1</f>
         <v>29</v>
       </c>
       <c r="U30" s="3">
-        <f t="shared" si="6"/>
+        <f>+T30+1</f>
         <v>30</v>
       </c>
       <c r="V30" s="3">
         <v>1</v>
       </c>
       <c r="W30" s="3">
-        <f t="shared" si="7"/>
+        <f>+U30+V30-1</f>
         <v>30</v>
       </c>
       <c r="X30" s="3">
@@ -6676,7 +6683,7 @@
         <v>31</v>
       </c>
       <c r="AA30" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z30+AB30-1</f>
         <v>33</v>
       </c>
       <c r="AB30" s="3">
@@ -6692,21 +6699,21 @@
         <v>34</v>
       </c>
       <c r="AF30" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE30+AA30-1</f>
         <v>66</v>
       </c>
       <c r="AG30" s="6">
         <v>3</v>
       </c>
       <c r="AH30" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF30+AG30</f>
         <v>69</v>
       </c>
       <c r="AI30" s="3">
         <v>14</v>
       </c>
       <c r="AJ30" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI30+AH30</f>
         <v>83</v>
       </c>
       <c r="AK30" s="3" t="s">
@@ -6716,36 +6723,36 @@
         <v>0</v>
       </c>
       <c r="AM30" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ30+AL30</f>
         <v>83</v>
       </c>
       <c r="AN30" s="3">
         <v>0</v>
       </c>
       <c r="AO30" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM30+AN30</f>
         <v>83</v>
       </c>
       <c r="AP30" s="3">
         <v>1</v>
       </c>
       <c r="AQ30" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO30+AP30</f>
         <v>84</v>
       </c>
       <c r="AR30" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ30+7</f>
         <v>91</v>
       </c>
       <c r="AS30" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR30+7+AT30</f>
         <v>98</v>
       </c>
       <c r="AT30" s="3">
         <v>0</v>
       </c>
       <c r="AU30" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA30-R30</f>
         <v>10</v>
       </c>
       <c r="AV30" s="3" t="s">
@@ -6761,7 +6768,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>1006</v>
       </c>
@@ -6805,37 +6812,37 @@
         <v>14</v>
       </c>
       <c r="O31" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I31="SFK Freight Forwarder",M31,M31+N31-1)</f>
         <v>0</v>
       </c>
       <c r="P31" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I31="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q31" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I31="SFK Freight Forwarder",O31,O31+P31-1)</f>
         <v>0</v>
       </c>
       <c r="R31" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N31</f>
         <v>23</v>
       </c>
       <c r="S31" s="3">
         <v>7</v>
       </c>
       <c r="T31" s="3">
-        <f t="shared" si="5"/>
+        <f>+R31+S31-1</f>
         <v>29</v>
       </c>
       <c r="U31" s="3">
-        <f t="shared" si="6"/>
+        <f>+T31+1</f>
         <v>30</v>
       </c>
       <c r="V31" s="3">
         <v>1</v>
       </c>
       <c r="W31" s="3">
-        <f t="shared" si="7"/>
+        <f>+U31+V31-1</f>
         <v>30</v>
       </c>
       <c r="X31" s="3">
@@ -6848,7 +6855,7 @@
         <v>31</v>
       </c>
       <c r="AA31" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z31+AB31-1</f>
         <v>34</v>
       </c>
       <c r="AB31" s="3">
@@ -6864,21 +6871,21 @@
         <v>58</v>
       </c>
       <c r="AF31" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE31+AA31-1</f>
         <v>91</v>
       </c>
       <c r="AG31" s="6">
         <v>3</v>
       </c>
       <c r="AH31" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF31+AG31</f>
         <v>94</v>
       </c>
       <c r="AI31" s="3">
         <v>0</v>
       </c>
       <c r="AJ31" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI31+AH31</f>
         <v>94</v>
       </c>
       <c r="AK31" s="3" t="s">
@@ -6888,36 +6895,36 @@
         <v>1</v>
       </c>
       <c r="AM31" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ31+AL31</f>
         <v>95</v>
       </c>
       <c r="AN31" s="3">
         <v>4</v>
       </c>
       <c r="AO31" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM31+AN31</f>
         <v>99</v>
       </c>
       <c r="AP31" s="3">
         <v>6</v>
       </c>
       <c r="AQ31" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO31+AP31</f>
         <v>105</v>
       </c>
       <c r="AR31" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ31+7</f>
         <v>112</v>
       </c>
       <c r="AS31" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR31+7+AT31</f>
         <v>119</v>
       </c>
       <c r="AT31" s="3">
         <v>0</v>
       </c>
       <c r="AU31" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA31-R31</f>
         <v>11</v>
       </c>
       <c r="AV31" s="3" t="s">
@@ -6933,7 +6940,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>1007</v>
       </c>
@@ -6977,52 +6984,52 @@
         <v>14</v>
       </c>
       <c r="O32" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I32="SFK Freight Forwarder",M32,M32+N32-1)</f>
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I32="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I32="SFK Freight Forwarder",O32,O32+P32-1)</f>
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N32</f>
         <v>23</v>
       </c>
       <c r="S32" s="3">
         <v>7</v>
       </c>
       <c r="T32" s="3">
-        <f t="shared" si="5"/>
+        <f>+R32+S32-1</f>
         <v>29</v>
       </c>
       <c r="U32" s="3">
-        <f t="shared" si="6"/>
+        <f>+T32+1</f>
         <v>30</v>
       </c>
       <c r="V32" s="3">
         <v>1</v>
       </c>
       <c r="W32" s="3">
-        <f t="shared" si="7"/>
+        <f>+U32+V32-1</f>
         <v>30</v>
       </c>
       <c r="X32" s="3">
         <v>3</v>
       </c>
       <c r="Y32" s="3">
-        <f t="shared" ref="Y32:Y51" si="20">+ROUNDDOWN(W32/7,0)*7+X32</f>
+        <f>+ROUNDDOWN(W32/7,0)*7+X32</f>
         <v>31</v>
       </c>
       <c r="Z32" s="6">
-        <f t="shared" ref="Z32:Z35" si="21">+Y32+X32-1</f>
+        <f>+Y32+X32-1</f>
         <v>33</v>
       </c>
       <c r="AA32" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z32+AB32-1</f>
         <v>35</v>
       </c>
       <c r="AB32" s="3">
@@ -7038,21 +7045,21 @@
         <v>49</v>
       </c>
       <c r="AF32" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE32+AA32-1</f>
         <v>83</v>
       </c>
       <c r="AG32" s="6">
         <v>3</v>
       </c>
       <c r="AH32" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF32+AG32</f>
         <v>86</v>
       </c>
       <c r="AI32" s="3">
         <v>7</v>
       </c>
       <c r="AJ32" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI32+AH32</f>
         <v>93</v>
       </c>
       <c r="AK32" s="3" t="s">
@@ -7062,36 +7069,36 @@
         <v>3</v>
       </c>
       <c r="AM32" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ32+AL32</f>
         <v>96</v>
       </c>
       <c r="AN32" s="3">
         <v>1</v>
       </c>
       <c r="AO32" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM32+AN32</f>
         <v>97</v>
       </c>
       <c r="AP32" s="3">
         <v>1</v>
       </c>
       <c r="AQ32" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO32+AP32</f>
         <v>98</v>
       </c>
       <c r="AR32" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ32+7</f>
         <v>105</v>
       </c>
       <c r="AS32" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR32+7+AT32</f>
         <v>112</v>
       </c>
       <c r="AT32" s="3">
         <v>0</v>
       </c>
       <c r="AU32" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA32-R32</f>
         <v>12</v>
       </c>
       <c r="AV32" s="3" t="s">
@@ -7107,7 +7114,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>1009</v>
       </c>
@@ -7151,37 +7158,37 @@
         <v>14</v>
       </c>
       <c r="O33" s="3">
-        <f t="shared" ref="O33:O51" si="22">IF(I33="SFK Freight Forwarder",M33,M33+N33-1)</f>
+        <f>IF(I33="SFK Freight Forwarder",M33,M33+N33-1)</f>
         <v>0</v>
       </c>
       <c r="P33" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I33="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <f t="shared" ref="Q33:Q51" si="23">+IF(I33="SFK Freight Forwarder",O33,O33+P33-1)</f>
+        <f>+IF(I33="SFK Freight Forwarder",O33,O33+P33-1)</f>
         <v>0</v>
       </c>
       <c r="R33" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N33</f>
         <v>23</v>
       </c>
       <c r="S33" s="3">
         <v>7</v>
       </c>
       <c r="T33" s="3">
-        <f t="shared" ref="T33:T51" si="24">+R33+S33-1</f>
+        <f>+R33+S33-1</f>
         <v>29</v>
       </c>
       <c r="U33" s="3">
-        <f t="shared" si="6"/>
+        <f>+T33+1</f>
         <v>30</v>
       </c>
       <c r="V33" s="3">
         <v>1</v>
       </c>
       <c r="W33" s="3">
-        <f t="shared" ref="W33:W51" si="25">+U33+V33-1</f>
+        <f>+U33+V33-1</f>
         <v>30</v>
       </c>
       <c r="X33" s="3">
@@ -7194,7 +7201,7 @@
         <v>36</v>
       </c>
       <c r="AA33" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z33+AB33-1</f>
         <v>37</v>
       </c>
       <c r="AB33" s="3">
@@ -7210,21 +7217,21 @@
         <v>53</v>
       </c>
       <c r="AF33" s="3">
-        <f t="shared" ref="AF33:AF51" si="26">+AE33+AA33-1</f>
+        <f>+AE33+AA33-1</f>
         <v>89</v>
       </c>
       <c r="AG33" s="6">
         <v>3</v>
       </c>
       <c r="AH33" s="6">
-        <f t="shared" ref="AH33:AH51" si="27">+AF33+AG33</f>
+        <f>+AF33+AG33</f>
         <v>92</v>
       </c>
       <c r="AI33" s="3">
         <v>0</v>
       </c>
       <c r="AJ33" s="3">
-        <f t="shared" ref="AJ33:AJ51" si="28">+AI33+AH33</f>
+        <f>+AI33+AH33</f>
         <v>92</v>
       </c>
       <c r="AK33" s="3" t="s">
@@ -7234,36 +7241,36 @@
         <v>2</v>
       </c>
       <c r="AM33" s="3">
-        <f t="shared" ref="AM33:AM51" si="29">+AJ33+AL33</f>
+        <f>+AJ33+AL33</f>
         <v>94</v>
       </c>
       <c r="AN33" s="3">
         <v>2</v>
       </c>
       <c r="AO33" s="3">
-        <f t="shared" ref="AO33:AO51" si="30">+AM33+AN33</f>
+        <f>+AM33+AN33</f>
         <v>96</v>
       </c>
       <c r="AP33" s="3">
         <v>2</v>
       </c>
       <c r="AQ33" s="3">
-        <f t="shared" ref="AQ33:AQ51" si="31">+AO33+AP33</f>
+        <f>+AO33+AP33</f>
         <v>98</v>
       </c>
       <c r="AR33" s="3">
-        <f t="shared" ref="AR33:AR51" si="32">+AQ33+7</f>
+        <f>+AQ33+7</f>
         <v>105</v>
       </c>
       <c r="AS33" s="3">
-        <f t="shared" ref="AS33:AS51" si="33">+AR33+7+AT33</f>
+        <f>+AR33+7+AT33</f>
         <v>112</v>
       </c>
       <c r="AT33" s="3">
         <v>0</v>
       </c>
       <c r="AU33" s="3">
-        <f t="shared" ref="AU33:AU51" si="34">+AA33-R33</f>
+        <f>+AA33-R33</f>
         <v>14</v>
       </c>
       <c r="AV33" s="3" t="s">
@@ -7279,7 +7286,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>1010</v>
       </c>
@@ -7323,37 +7330,37 @@
         <v>14</v>
       </c>
       <c r="O34" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I34="SFK Freight Forwarder",M34,M34+N34-1)</f>
         <v>0</v>
       </c>
       <c r="P34" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I34="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q34" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
         <v>0</v>
       </c>
       <c r="R34" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N34</f>
         <v>23</v>
       </c>
       <c r="S34" s="3">
         <v>7</v>
       </c>
       <c r="T34" s="3">
-        <f t="shared" si="24"/>
+        <f>+R34+S34-1</f>
         <v>29</v>
       </c>
       <c r="U34" s="3">
-        <f t="shared" si="6"/>
+        <f>+T34+1</f>
         <v>30</v>
       </c>
       <c r="V34" s="3">
         <v>1</v>
       </c>
       <c r="W34" s="3">
-        <f t="shared" si="25"/>
+        <f>+U34+V34-1</f>
         <v>30</v>
       </c>
       <c r="X34" s="3">
@@ -7366,7 +7373,7 @@
         <v>33</v>
       </c>
       <c r="AA34" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z34+AB34-1</f>
         <v>36</v>
       </c>
       <c r="AB34" s="3">
@@ -7382,21 +7389,21 @@
         <v>63</v>
       </c>
       <c r="AF34" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE34+AA34-1</f>
         <v>98</v>
       </c>
       <c r="AG34" s="6">
         <v>3</v>
       </c>
       <c r="AH34" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF34+AG34</f>
         <v>101</v>
       </c>
       <c r="AI34" s="3">
         <v>0</v>
       </c>
       <c r="AJ34" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI34+AH34</f>
         <v>101</v>
       </c>
       <c r="AK34" s="3" t="s">
@@ -7406,36 +7413,36 @@
         <v>4</v>
       </c>
       <c r="AM34" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ34+AL34</f>
         <v>105</v>
       </c>
       <c r="AN34" s="3">
         <v>3</v>
       </c>
       <c r="AO34" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM34+AN34</f>
         <v>108</v>
       </c>
       <c r="AP34" s="3">
         <v>4</v>
       </c>
       <c r="AQ34" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO34+AP34</f>
         <v>112</v>
       </c>
       <c r="AR34" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ34+7</f>
         <v>119</v>
       </c>
       <c r="AS34" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR34+7+AT34</f>
         <v>126</v>
       </c>
       <c r="AT34" s="3">
         <v>0</v>
       </c>
       <c r="AU34" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA34-R34</f>
         <v>13</v>
       </c>
       <c r="AV34" s="3" t="s">
@@ -7451,7 +7458,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>1012</v>
       </c>
@@ -7495,37 +7502,37 @@
         <v>14</v>
       </c>
       <c r="O35" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I35="SFK Freight Forwarder",M35,M35+N35-1)</f>
         <v>0</v>
       </c>
       <c r="P35" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I35="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I35="SFK Freight Forwarder",O35,O35+P35-1)</f>
         <v>0</v>
       </c>
       <c r="R35" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N35</f>
         <v>23</v>
       </c>
       <c r="S35" s="3">
         <v>7</v>
       </c>
       <c r="T35" s="3">
-        <f t="shared" si="24"/>
+        <f>+R35+S35-1</f>
         <v>29</v>
       </c>
       <c r="U35" s="3">
-        <f t="shared" si="6"/>
+        <f>+T35+1</f>
         <v>30</v>
       </c>
       <c r="V35" s="3">
         <v>1</v>
       </c>
       <c r="W35" s="3">
-        <f t="shared" si="25"/>
+        <f>+U35+V35-1</f>
         <v>30</v>
       </c>
       <c r="X35" s="3">
@@ -7535,11 +7542,11 @@
         <v>31</v>
       </c>
       <c r="Z35" s="6">
-        <f t="shared" si="21"/>
+        <f>+Y35+X35-1</f>
         <v>33</v>
       </c>
       <c r="AA35" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z35+AB35-1</f>
         <v>37</v>
       </c>
       <c r="AB35" s="3">
@@ -7555,21 +7562,21 @@
         <v>48</v>
       </c>
       <c r="AF35" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE35+AA35-1</f>
         <v>84</v>
       </c>
       <c r="AG35" s="6">
         <v>3</v>
       </c>
       <c r="AH35" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF35+AG35</f>
         <v>87</v>
       </c>
       <c r="AI35" s="3">
         <v>14</v>
       </c>
       <c r="AJ35" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI35+AH35</f>
         <v>101</v>
       </c>
       <c r="AK35" s="3" t="s">
@@ -7579,36 +7586,36 @@
         <v>2</v>
       </c>
       <c r="AM35" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ35+AL35</f>
         <v>103</v>
       </c>
       <c r="AN35" s="3">
         <v>2</v>
       </c>
       <c r="AO35" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM35+AN35</f>
         <v>105</v>
       </c>
       <c r="AP35" s="3">
         <v>0</v>
       </c>
       <c r="AQ35" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO35+AP35</f>
         <v>105</v>
       </c>
       <c r="AR35" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ35+7</f>
         <v>112</v>
       </c>
       <c r="AS35" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR35+7+AT35</f>
         <v>119</v>
       </c>
       <c r="AT35" s="3">
         <v>0</v>
       </c>
       <c r="AU35" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA35-R35</f>
         <v>14</v>
       </c>
       <c r="AV35" s="3" t="s">
@@ -7624,7 +7631,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>1014</v>
       </c>
@@ -7668,37 +7675,37 @@
         <v>14</v>
       </c>
       <c r="O36" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I36="SFK Freight Forwarder",M36,M36+N36-1)</f>
         <v>0</v>
       </c>
       <c r="P36" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I36="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q36" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I36="SFK Freight Forwarder",O36,O36+P36-1)</f>
         <v>0</v>
       </c>
       <c r="R36" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N36</f>
         <v>23</v>
       </c>
       <c r="S36" s="3">
         <v>7</v>
       </c>
       <c r="T36" s="3">
-        <f t="shared" si="24"/>
+        <f>+R36+S36-1</f>
         <v>29</v>
       </c>
       <c r="U36" s="3">
-        <f t="shared" si="6"/>
+        <f>+T36+1</f>
         <v>30</v>
       </c>
       <c r="V36" s="3">
         <v>2</v>
       </c>
       <c r="W36" s="3">
-        <f t="shared" si="25"/>
+        <f>+U36+V36-1</f>
         <v>31</v>
       </c>
       <c r="X36" s="3">
@@ -7711,7 +7718,7 @@
         <v>39</v>
       </c>
       <c r="AA36" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z36+AB36-1</f>
         <v>44</v>
       </c>
       <c r="AB36" s="3">
@@ -7727,21 +7734,21 @@
         <v>17</v>
       </c>
       <c r="AF36" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE36+AA36-1</f>
         <v>60</v>
       </c>
       <c r="AG36" s="6">
         <v>3</v>
       </c>
       <c r="AH36" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF36+AG36</f>
         <v>63</v>
       </c>
       <c r="AI36" s="3">
         <v>0</v>
       </c>
       <c r="AJ36" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI36+AH36</f>
         <v>63</v>
       </c>
       <c r="AK36" s="3" t="s">
@@ -7751,36 +7758,36 @@
         <v>0</v>
       </c>
       <c r="AM36" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ36+AL36</f>
         <v>63</v>
       </c>
       <c r="AN36" s="3">
         <v>0</v>
       </c>
       <c r="AO36" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM36+AN36</f>
         <v>63</v>
       </c>
       <c r="AP36" s="3">
         <v>0</v>
       </c>
       <c r="AQ36" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO36+AP36</f>
         <v>63</v>
       </c>
       <c r="AR36" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ36+7</f>
         <v>70</v>
       </c>
       <c r="AS36" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR36+7+AT36</f>
         <v>77</v>
       </c>
       <c r="AT36" s="3">
         <v>0</v>
       </c>
       <c r="AU36" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA36-R36</f>
         <v>21</v>
       </c>
       <c r="AV36" s="3" t="s">
@@ -7796,7 +7803,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>1015</v>
       </c>
@@ -7840,37 +7847,37 @@
         <v>14</v>
       </c>
       <c r="O37" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I37="SFK Freight Forwarder",M37,M37+N37-1)</f>
         <v>0</v>
       </c>
       <c r="P37" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I37="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q37" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I37="SFK Freight Forwarder",O37,O37+P37-1)</f>
         <v>0</v>
       </c>
       <c r="R37" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N37</f>
         <v>23</v>
       </c>
       <c r="S37" s="3">
         <v>7</v>
       </c>
       <c r="T37" s="3">
-        <f t="shared" si="24"/>
+        <f>+R37+S37-1</f>
         <v>29</v>
       </c>
       <c r="U37" s="3">
-        <f t="shared" si="6"/>
+        <f>+T37+1</f>
         <v>30</v>
       </c>
       <c r="V37" s="3">
         <v>2</v>
       </c>
       <c r="W37" s="3">
-        <f t="shared" si="25"/>
+        <f>+U37+V37-1</f>
         <v>31</v>
       </c>
       <c r="X37" s="3">
@@ -7883,7 +7890,7 @@
         <v>39</v>
       </c>
       <c r="AA37" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z37+AB37-1</f>
         <v>44</v>
       </c>
       <c r="AB37" s="3">
@@ -7899,21 +7906,21 @@
         <v>34</v>
       </c>
       <c r="AF37" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE37+AA37-1</f>
         <v>77</v>
       </c>
       <c r="AG37" s="6">
         <v>3</v>
       </c>
       <c r="AH37" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF37+AG37</f>
         <v>80</v>
       </c>
       <c r="AI37" s="3">
         <v>0</v>
       </c>
       <c r="AJ37" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI37+AH37</f>
         <v>80</v>
       </c>
       <c r="AK37" s="3" t="s">
@@ -7923,36 +7930,36 @@
         <v>2</v>
       </c>
       <c r="AM37" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ37+AL37</f>
         <v>82</v>
       </c>
       <c r="AN37" s="3">
         <v>2</v>
       </c>
       <c r="AO37" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM37+AN37</f>
         <v>84</v>
       </c>
       <c r="AP37" s="3">
         <v>0</v>
       </c>
       <c r="AQ37" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO37+AP37</f>
         <v>84</v>
       </c>
       <c r="AR37" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ37+7</f>
         <v>91</v>
       </c>
       <c r="AS37" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR37+7+AT37</f>
         <v>98</v>
       </c>
       <c r="AT37" s="3">
         <v>0</v>
       </c>
       <c r="AU37" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA37-R37</f>
         <v>21</v>
       </c>
       <c r="AV37" s="3" t="s">
@@ -7968,7 +7975,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>1034</v>
       </c>
@@ -8012,37 +8019,37 @@
         <v>14</v>
       </c>
       <c r="O38" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I38="SFK Freight Forwarder",M38,M38+N38-1)</f>
         <v>0</v>
       </c>
       <c r="P38" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I38="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q38" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I38="SFK Freight Forwarder",O38,O38+P38-1)</f>
         <v>0</v>
       </c>
       <c r="R38" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N38</f>
         <v>23</v>
       </c>
       <c r="S38" s="3">
         <v>7</v>
       </c>
       <c r="T38" s="3">
-        <f t="shared" si="24"/>
+        <f>+R38+S38-1</f>
         <v>29</v>
       </c>
       <c r="U38" s="3">
-        <f t="shared" si="6"/>
+        <f>+T38+1</f>
         <v>30</v>
       </c>
       <c r="V38" s="3">
         <v>1</v>
       </c>
       <c r="W38" s="3">
-        <f t="shared" si="25"/>
+        <f>+U38+V38-1</f>
         <v>30</v>
       </c>
       <c r="X38" s="3">
@@ -8055,7 +8062,7 @@
         <v>33</v>
       </c>
       <c r="AA38" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z38+AB38-1</f>
         <v>35</v>
       </c>
       <c r="AB38" s="3">
@@ -8071,21 +8078,21 @@
         <v>53</v>
       </c>
       <c r="AF38" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE38+AA38-1</f>
         <v>87</v>
       </c>
       <c r="AG38" s="6">
         <v>3</v>
       </c>
       <c r="AH38" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF38+AG38</f>
         <v>90</v>
       </c>
       <c r="AI38" s="3">
         <v>0</v>
       </c>
       <c r="AJ38" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI38+AH38</f>
         <v>90</v>
       </c>
       <c r="AK38" s="3" t="s">
@@ -8095,36 +8102,36 @@
         <v>2</v>
       </c>
       <c r="AM38" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ38+AL38</f>
         <v>92</v>
       </c>
       <c r="AN38" s="3">
         <v>6</v>
       </c>
       <c r="AO38" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM38+AN38</f>
         <v>98</v>
       </c>
       <c r="AP38" s="3">
         <v>0</v>
       </c>
       <c r="AQ38" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO38+AP38</f>
         <v>98</v>
       </c>
       <c r="AR38" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ38+7</f>
         <v>105</v>
       </c>
       <c r="AS38" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR38+7+AT38</f>
         <v>112</v>
       </c>
       <c r="AT38" s="3">
         <v>0</v>
       </c>
       <c r="AU38" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA38-R38</f>
         <v>12</v>
       </c>
       <c r="AV38" s="3" t="s">
@@ -8140,7 +8147,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>1036</v>
       </c>
@@ -8184,37 +8191,37 @@
         <v>14</v>
       </c>
       <c r="O39" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I39="SFK Freight Forwarder",M39,M39+N39-1)</f>
         <v>0</v>
       </c>
       <c r="P39" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I39="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q39" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I39="SFK Freight Forwarder",O39,O39+P39-1)</f>
         <v>0</v>
       </c>
       <c r="R39" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N39</f>
         <v>23</v>
       </c>
       <c r="S39" s="3">
         <v>7</v>
       </c>
       <c r="T39" s="3">
-        <f t="shared" si="24"/>
+        <f>+R39+S39-1</f>
         <v>29</v>
       </c>
       <c r="U39" s="3">
-        <f t="shared" si="6"/>
+        <f>+T39+1</f>
         <v>30</v>
       </c>
       <c r="V39" s="3">
         <v>2</v>
       </c>
       <c r="W39" s="3">
-        <f t="shared" si="25"/>
+        <f>+U39+V39-1</f>
         <v>31</v>
       </c>
       <c r="X39" s="3">
@@ -8227,7 +8234,7 @@
         <v>34</v>
       </c>
       <c r="AA39" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z39+AB39-1</f>
         <v>36</v>
       </c>
       <c r="AB39" s="3">
@@ -8243,21 +8250,21 @@
         <v>31</v>
       </c>
       <c r="AF39" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE39+AA39-1</f>
         <v>66</v>
       </c>
       <c r="AG39" s="6">
         <v>3</v>
       </c>
       <c r="AH39" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF39+AG39</f>
         <v>69</v>
       </c>
       <c r="AI39" s="3">
         <v>0</v>
       </c>
       <c r="AJ39" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI39+AH39</f>
         <v>69</v>
       </c>
       <c r="AK39" s="3" t="s">
@@ -8267,36 +8274,36 @@
         <v>2</v>
       </c>
       <c r="AM39" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ39+AL39</f>
         <v>71</v>
       </c>
       <c r="AN39" s="3">
         <v>5</v>
       </c>
       <c r="AO39" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM39+AN39</f>
         <v>76</v>
       </c>
       <c r="AP39" s="3">
         <v>1</v>
       </c>
       <c r="AQ39" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO39+AP39</f>
         <v>77</v>
       </c>
       <c r="AR39" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ39+7</f>
         <v>84</v>
       </c>
       <c r="AS39" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR39+7+AT39</f>
         <v>91</v>
       </c>
       <c r="AT39" s="3">
         <v>0</v>
       </c>
       <c r="AU39" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA39-R39</f>
         <v>13</v>
       </c>
       <c r="AV39" s="3" t="s">
@@ -8312,7 +8319,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>1037</v>
       </c>
@@ -8356,37 +8363,37 @@
         <v>14</v>
       </c>
       <c r="O40" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I40="SFK Freight Forwarder",M40,M40+N40-1)</f>
         <v>0</v>
       </c>
       <c r="P40" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I40="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q40" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I40="SFK Freight Forwarder",O40,O40+P40-1)</f>
         <v>0</v>
       </c>
       <c r="R40" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N40</f>
         <v>23</v>
       </c>
       <c r="S40" s="3">
         <v>7</v>
       </c>
       <c r="T40" s="3">
-        <f t="shared" si="24"/>
+        <f>+R40+S40-1</f>
         <v>29</v>
       </c>
       <c r="U40" s="3">
-        <f t="shared" si="6"/>
+        <f>+T40+1</f>
         <v>30</v>
       </c>
       <c r="V40" s="3">
         <v>1</v>
       </c>
       <c r="W40" s="3">
-        <f t="shared" si="25"/>
+        <f>+U40+V40-1</f>
         <v>30</v>
       </c>
       <c r="X40" s="3">
@@ -8399,7 +8406,7 @@
         <v>33</v>
       </c>
       <c r="AA40" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z40+AB40-1</f>
         <v>36</v>
       </c>
       <c r="AB40" s="3">
@@ -8415,21 +8422,21 @@
         <v>67</v>
       </c>
       <c r="AF40" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE40+AA40-1</f>
         <v>102</v>
       </c>
       <c r="AG40" s="6">
         <v>3</v>
       </c>
       <c r="AH40" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF40+AG40</f>
         <v>105</v>
       </c>
       <c r="AI40" s="3">
         <v>7</v>
       </c>
       <c r="AJ40" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI40+AH40</f>
         <v>112</v>
       </c>
       <c r="AK40" s="3" t="s">
@@ -8439,36 +8446,36 @@
         <v>3</v>
       </c>
       <c r="AM40" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ40+AL40</f>
         <v>115</v>
       </c>
       <c r="AN40" s="3">
         <v>3</v>
       </c>
       <c r="AO40" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM40+AN40</f>
         <v>118</v>
       </c>
       <c r="AP40" s="3">
         <v>1</v>
       </c>
       <c r="AQ40" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO40+AP40</f>
         <v>119</v>
       </c>
       <c r="AR40" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ40+7</f>
         <v>126</v>
       </c>
       <c r="AS40" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR40+7+AT40</f>
         <v>133</v>
       </c>
       <c r="AT40" s="3">
         <v>0</v>
       </c>
       <c r="AU40" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA40-R40</f>
         <v>13</v>
       </c>
       <c r="AV40" s="3" t="s">
@@ -8484,7 +8491,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>1040</v>
       </c>
@@ -8528,37 +8535,37 @@
         <v>14</v>
       </c>
       <c r="O41" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I41="SFK Freight Forwarder",M41,M41+N41-1)</f>
         <v>0</v>
       </c>
       <c r="P41" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I41="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q41" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I41="SFK Freight Forwarder",O41,O41+P41-1)</f>
         <v>0</v>
       </c>
       <c r="R41" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N41</f>
         <v>23</v>
       </c>
       <c r="S41" s="3">
         <v>7</v>
       </c>
       <c r="T41" s="3">
-        <f t="shared" si="24"/>
+        <f>+R41+S41-1</f>
         <v>29</v>
       </c>
       <c r="U41" s="3">
-        <f t="shared" si="6"/>
+        <f>+T41+1</f>
         <v>30</v>
       </c>
       <c r="V41" s="3">
         <v>1</v>
       </c>
       <c r="W41" s="3">
-        <f t="shared" si="25"/>
+        <f>+U41+V41-1</f>
         <v>30</v>
       </c>
       <c r="X41" s="3">
@@ -8571,7 +8578,7 @@
         <v>33</v>
       </c>
       <c r="AA41" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z41+AB41-1</f>
         <v>36</v>
       </c>
       <c r="AB41" s="3">
@@ -8587,21 +8594,21 @@
         <v>32</v>
       </c>
       <c r="AF41" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE41+AA41-1</f>
         <v>67</v>
       </c>
       <c r="AG41" s="6">
         <v>3</v>
       </c>
       <c r="AH41" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF41+AG41</f>
         <v>70</v>
       </c>
       <c r="AI41" s="3">
         <v>0</v>
       </c>
       <c r="AJ41" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI41+AH41</f>
         <v>70</v>
       </c>
       <c r="AK41" s="3" t="s">
@@ -8611,36 +8618,36 @@
         <v>4</v>
       </c>
       <c r="AM41" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ41+AL41</f>
         <v>74</v>
       </c>
       <c r="AN41" s="3">
         <v>3</v>
       </c>
       <c r="AO41" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM41+AN41</f>
         <v>77</v>
       </c>
       <c r="AP41" s="3">
         <v>0</v>
       </c>
       <c r="AQ41" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO41+AP41</f>
         <v>77</v>
       </c>
       <c r="AR41" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ41+7</f>
         <v>84</v>
       </c>
       <c r="AS41" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR41+7+AT41</f>
         <v>91</v>
       </c>
       <c r="AT41" s="3">
         <v>0</v>
       </c>
       <c r="AU41" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA41-R41</f>
         <v>13</v>
       </c>
       <c r="AV41" s="3" t="s">
@@ -8656,7 +8663,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>1045</v>
       </c>
@@ -8694,44 +8701,44 @@
         <v>2</v>
       </c>
       <c r="M42" s="3">
-        <f t="shared" ref="M42:M51" si="35">+IF(I42="SFK Freight Forwarder",L42,9)</f>
+        <f>+IF(I42="SFK Freight Forwarder",L42,9)</f>
         <v>9</v>
       </c>
       <c r="N42" s="3">
         <v>21</v>
       </c>
       <c r="O42" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I42="SFK Freight Forwarder",M42,M42+N42-1)</f>
         <v>29</v>
       </c>
       <c r="P42" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I42="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q42" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I42="SFK Freight Forwarder",O42,O42+P42-1)</f>
         <v>33</v>
       </c>
       <c r="R42" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N42</f>
         <v>30</v>
       </c>
       <c r="S42" s="3">
         <v>7</v>
       </c>
       <c r="T42" s="3">
-        <f t="shared" si="24"/>
+        <f>+R42+S42-1</f>
         <v>36</v>
       </c>
       <c r="U42" s="3">
-        <f t="shared" si="6"/>
+        <f>+T42+1</f>
         <v>37</v>
       </c>
       <c r="V42" s="3">
         <v>1</v>
       </c>
       <c r="W42" s="3">
-        <f t="shared" si="25"/>
+        <f>+U42+V42-1</f>
         <v>37</v>
       </c>
       <c r="X42" s="3">
@@ -8744,7 +8751,7 @@
         <v>37</v>
       </c>
       <c r="AA42" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z42+AB42-1</f>
         <v>39</v>
       </c>
       <c r="AB42" s="3">
@@ -8760,21 +8767,21 @@
         <v>46</v>
       </c>
       <c r="AF42" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE42+AA42-1</f>
         <v>84</v>
       </c>
       <c r="AG42" s="6">
         <v>3</v>
       </c>
       <c r="AH42" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF42+AG42</f>
         <v>87</v>
       </c>
       <c r="AI42" s="3">
         <v>7</v>
       </c>
       <c r="AJ42" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI42+AH42</f>
         <v>94</v>
       </c>
       <c r="AK42" s="3" t="s">
@@ -8784,36 +8791,36 @@
         <v>4</v>
       </c>
       <c r="AM42" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ42+AL42</f>
         <v>98</v>
       </c>
       <c r="AN42" s="3">
         <v>3</v>
       </c>
       <c r="AO42" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM42+AN42</f>
         <v>101</v>
       </c>
       <c r="AP42" s="3">
         <v>4</v>
       </c>
       <c r="AQ42" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO42+AP42</f>
         <v>105</v>
       </c>
       <c r="AR42" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ42+7</f>
         <v>112</v>
       </c>
       <c r="AS42" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR42+7+AT42</f>
         <v>119</v>
       </c>
       <c r="AT42" s="3">
         <v>0</v>
       </c>
       <c r="AU42" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA42-R42</f>
         <v>9</v>
       </c>
       <c r="AV42" s="3" t="s">
@@ -8829,7 +8836,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>1084</v>
       </c>
@@ -8867,44 +8874,44 @@
         <v>7</v>
       </c>
       <c r="M43" s="3">
-        <f t="shared" si="35"/>
+        <f>+IF(I43="SFK Freight Forwarder",L43,9)</f>
         <v>9</v>
       </c>
       <c r="N43" s="3">
         <v>14</v>
       </c>
       <c r="O43" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I43="SFK Freight Forwarder",M43,M43+N43-1)</f>
         <v>22</v>
       </c>
       <c r="P43" s="3">
-        <f t="shared" si="19"/>
+        <f>+IF(I43="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q43" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I43="SFK Freight Forwarder",O43,O43+P43-1)</f>
         <v>26</v>
       </c>
       <c r="R43" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N43</f>
         <v>23</v>
       </c>
       <c r="S43" s="3">
         <v>7</v>
       </c>
       <c r="T43" s="3">
-        <f t="shared" si="24"/>
+        <f>+R43+S43-1</f>
         <v>29</v>
       </c>
       <c r="U43" s="3">
-        <f t="shared" si="6"/>
+        <f>+T43+1</f>
         <v>30</v>
       </c>
       <c r="V43" s="3">
         <v>2</v>
       </c>
       <c r="W43" s="3">
-        <f t="shared" si="25"/>
+        <f>+U43+V43-1</f>
         <v>31</v>
       </c>
       <c r="X43" s="3">
@@ -8917,7 +8924,7 @@
         <v>39</v>
       </c>
       <c r="AA43" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z43+AB43-1</f>
         <v>41</v>
       </c>
       <c r="AB43" s="3">
@@ -8933,21 +8940,21 @@
         <v>35</v>
       </c>
       <c r="AF43" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE43+AA43-1</f>
         <v>75</v>
       </c>
       <c r="AG43" s="6">
         <v>3</v>
       </c>
       <c r="AH43" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF43+AG43</f>
         <v>78</v>
       </c>
       <c r="AI43" s="3">
         <v>0</v>
       </c>
       <c r="AJ43" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI43+AH43</f>
         <v>78</v>
       </c>
       <c r="AK43" s="3" t="s">
@@ -8957,36 +8964,36 @@
         <v>2</v>
       </c>
       <c r="AM43" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ43+AL43</f>
         <v>80</v>
       </c>
       <c r="AN43" s="3">
         <v>2</v>
       </c>
       <c r="AO43" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM43+AN43</f>
         <v>82</v>
       </c>
       <c r="AP43" s="3">
         <v>2</v>
       </c>
       <c r="AQ43" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO43+AP43</f>
         <v>84</v>
       </c>
       <c r="AR43" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ43+7</f>
         <v>91</v>
       </c>
       <c r="AS43" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR43+7+AT43</f>
         <v>98</v>
       </c>
       <c r="AT43" s="3">
         <v>0</v>
       </c>
       <c r="AU43" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA43-R43</f>
         <v>18</v>
       </c>
       <c r="AV43" s="3" t="s">
@@ -9002,20 +9009,20 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="E44" s="32" t="s">
+      <c r="E44" s="33" t="s">
         <v>81</v>
       </c>
       <c r="F44" s="19">
@@ -9046,14 +9053,14 @@
         <v>1</v>
       </c>
       <c r="O44" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I44="SFK Freight Forwarder",M44,M44+N44-1)</f>
         <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>6</v>
       </c>
       <c r="Q44" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I44="SFK Freight Forwarder",O44,O44+P44-1)</f>
         <v>13</v>
       </c>
       <c r="R44" s="23">
@@ -9063,7 +9070,7 @@
         <v>12</v>
       </c>
       <c r="T44" s="23">
-        <f t="shared" si="24"/>
+        <f>+R44+S44-1</f>
         <v>20</v>
       </c>
       <c r="U44" s="23">
@@ -9074,7 +9081,7 @@
         <v>5</v>
       </c>
       <c r="W44" s="23">
-        <f t="shared" si="25"/>
+        <f>+U44+V44-1</f>
         <v>26</v>
       </c>
       <c r="X44" s="23">
@@ -9098,21 +9105,21 @@
         <v>41</v>
       </c>
       <c r="AF44" s="23">
-        <f t="shared" si="26"/>
+        <f>+AE44+AA44-1</f>
         <v>71</v>
       </c>
       <c r="AG44" s="23">
         <v>3</v>
       </c>
       <c r="AH44" s="23">
-        <f t="shared" si="27"/>
+        <f>+AF44+AG44</f>
         <v>74</v>
       </c>
       <c r="AI44" s="23">
         <v>7</v>
       </c>
       <c r="AJ44" s="23">
-        <f t="shared" si="28"/>
+        <f>+AI44+AH44</f>
         <v>81</v>
       </c>
       <c r="AK44" s="23"/>
@@ -9120,7 +9127,7 @@
         <v>3</v>
       </c>
       <c r="AM44" s="23">
-        <f t="shared" si="29"/>
+        <f>+AJ44+AL44</f>
         <v>84</v>
       </c>
       <c r="AN44" s="23">
@@ -9141,14 +9148,14 @@
         <v>96</v>
       </c>
       <c r="AS44" s="23">
-        <f t="shared" si="33"/>
+        <f>+AR44+7+AT44</f>
         <v>117</v>
       </c>
       <c r="AT44" s="23">
         <v>14</v>
       </c>
       <c r="AU44" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA44-R44</f>
         <v>22</v>
       </c>
       <c r="AV44" s="23" t="s">
@@ -9164,183 +9171,193 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="A45" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B45" s="5" t="s">
+    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="5">
+        <v>920</v>
+      </c>
+      <c r="B45" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E45" s="32" t="s">
+      <c r="C45" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" s="33" t="s">
         <v>81</v>
       </c>
       <c r="F45" s="19">
-        <v>90016500</v>
-      </c>
-      <c r="G45" s="23" t="s">
-        <v>159</v>
+        <v>91017500</v>
+      </c>
+      <c r="G45" s="35" t="s">
+        <v>157</v>
       </c>
       <c r="H45" s="2">
-        <v>0</v>
+        <v>2533780535</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="J45" s="2">
-        <v>29159</v>
-      </c>
-      <c r="K45" s="23" t="s">
-        <v>137</v>
+        <v>2533780535</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="L45" s="3">
+        <v>7</v>
+      </c>
+      <c r="M45" s="3">
+        <f>+IF(I45="SFK Freight Forwarder",L45,9)</f>
+        <v>9</v>
+      </c>
+      <c r="N45" s="3">
+        <v>14</v>
+      </c>
+      <c r="O45" s="3">
+        <f>IF(I45="SFK Freight Forwarder",M45,M45+N45-1)</f>
+        <v>22</v>
+      </c>
+      <c r="P45" s="3">
+        <f>+IF(I45="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
+        <f>+IF(I45="SFK Freight Forwarder",O45,O45+P45-1)</f>
+        <v>26</v>
+      </c>
+      <c r="R45" s="3">
+        <f>9+N45</f>
+        <v>23</v>
+      </c>
+      <c r="S45" s="3">
+        <v>7</v>
+      </c>
+      <c r="T45" s="3">
+        <f>+R45+S45-1</f>
+        <v>29</v>
+      </c>
+      <c r="U45" s="3">
+        <f>+T45+1</f>
+        <v>30</v>
+      </c>
+      <c r="V45" s="3">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3">
+        <f>+U45+V45-1</f>
+        <v>32</v>
+      </c>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>33</v>
+      </c>
+      <c r="Z45" s="6">
+        <v>37</v>
+      </c>
+      <c r="AA45" s="6">
+        <f>+Z45+AB45-1</f>
+        <v>39</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>6</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>13</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>39</v>
+      </c>
+      <c r="AF45" s="3">
+        <f>+AE45+AA45-1</f>
+        <v>77</v>
+      </c>
+      <c r="AG45" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH45" s="6">
+        <f>+AF45+AG45</f>
+        <v>80</v>
+      </c>
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="3">
+        <f>+AI45+AH45</f>
+        <v>80</v>
+      </c>
+      <c r="AK45" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL45" s="3">
+        <v>3</v>
+      </c>
+      <c r="AM45" s="3">
+        <f>+AJ45+AL45</f>
+        <v>83</v>
+      </c>
+      <c r="AN45" s="3">
         <v>8</v>
       </c>
-      <c r="N45" s="23">
-        <v>1</v>
-      </c>
-      <c r="O45" s="3">
-        <f t="shared" ref="O45" si="36">IF(I45="SFK Freight Forwarder",M45,M45+N45-1)</f>
-        <v>8</v>
-      </c>
-      <c r="P45" s="3">
-        <v>6</v>
-      </c>
-      <c r="Q45" s="3">
-        <f t="shared" ref="Q45" si="37">+IF(I45="SFK Freight Forwarder",O45,O45+P45-1)</f>
-        <v>13</v>
-      </c>
-      <c r="R45" s="23">
-        <v>9</v>
-      </c>
-      <c r="S45" s="23">
-        <v>12</v>
-      </c>
-      <c r="T45" s="23">
-        <f t="shared" ref="T45" si="38">+R45+S45-1</f>
-        <v>20</v>
-      </c>
-      <c r="U45" s="23">
-        <f>+T45+2</f>
-        <v>22</v>
-      </c>
-      <c r="V45" s="23">
-        <v>5</v>
-      </c>
-      <c r="W45" s="23">
-        <f t="shared" ref="W45" si="39">+U45+V45-1</f>
-        <v>26</v>
-      </c>
-      <c r="X45" s="23">
-        <v>4</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>29</v>
-      </c>
-      <c r="Z45" s="6">
-        <v>34</v>
-      </c>
-      <c r="AA45" s="6">
-        <v>36</v>
-      </c>
-      <c r="AB45" s="23">
-        <v>4</v>
-      </c>
-      <c r="AC45" s="23"/>
-      <c r="AD45" s="23"/>
-      <c r="AE45" s="33">
-        <v>34</v>
-      </c>
-      <c r="AF45" s="23">
-        <f t="shared" ref="AF45" si="40">+AE45+AA45-1</f>
-        <v>69</v>
-      </c>
-      <c r="AG45" s="23">
-        <v>3</v>
-      </c>
-      <c r="AH45" s="23">
-        <f t="shared" ref="AH45" si="41">+AF45+AG45</f>
-        <v>72</v>
-      </c>
-      <c r="AI45" s="23">
-        <v>7</v>
-      </c>
-      <c r="AJ45" s="23">
-        <f t="shared" ref="AJ45" si="42">+AI45+AH45</f>
-        <v>79</v>
-      </c>
-      <c r="AK45" s="23"/>
-      <c r="AL45" s="23">
-        <v>3</v>
-      </c>
-      <c r="AM45" s="23">
-        <f t="shared" ref="AM45" si="43">+AJ45+AL45</f>
-        <v>82</v>
-      </c>
-      <c r="AN45" s="23">
-        <v>5</v>
-      </c>
-      <c r="AO45" s="23">
+      <c r="AO45" s="3">
         <f>+AM45+AN45</f>
-        <v>87</v>
-      </c>
-      <c r="AP45" s="23">
-        <v>4</v>
+        <v>91</v>
+      </c>
+      <c r="AP45" s="3">
+        <v>2</v>
       </c>
       <c r="AQ45" s="3">
-        <f t="shared" si="31"/>
-        <v>91</v>
-      </c>
-      <c r="AR45" s="23">
-        <f>+AQ45+4</f>
-        <v>95</v>
-      </c>
-      <c r="AS45" s="23">
-        <f t="shared" ref="AS45" si="44">+AR45+7+AT45</f>
-        <v>116</v>
-      </c>
-      <c r="AT45" s="23">
+        <f>+AO45+AP45</f>
+        <v>93</v>
+      </c>
+      <c r="AR45" s="3">
+        <f>+AQ45+7</f>
+        <v>100</v>
+      </c>
+      <c r="AS45" s="3">
+        <f>+AR45+7+AT45</f>
+        <v>121</v>
+      </c>
+      <c r="AT45" s="3">
         <v>14</v>
       </c>
       <c r="AU45" s="3">
-        <f t="shared" ref="AU45" si="45">+AA45-R45</f>
-        <v>27</v>
-      </c>
-      <c r="AV45" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="AW45" s="23" t="s">
+        <f>+AA45-R45</f>
+        <v>16</v>
+      </c>
+      <c r="AV45" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW45" s="3" t="s">
         <v>131</v>
       </c>
       <c r="AX45" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AY45" s="37">
-        <v>46508</v>
+      <c r="AY45" s="21">
+        <v>46507</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B46" s="39" t="s">
+      <c r="B46" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="38" t="s">
+      <c r="C46" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D46" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="E46" s="32" t="s">
+      <c r="E46" s="33" t="s">
         <v>59</v>
       </c>
       <c r="F46" s="19">
@@ -9365,59 +9382,59 @@
         <v>7</v>
       </c>
       <c r="M46" s="3">
-        <f t="shared" si="35"/>
+        <f>+IF(I46="SFK Freight Forwarder",L46,9)</f>
         <v>9</v>
       </c>
       <c r="N46" s="3">
         <v>14</v>
       </c>
       <c r="O46" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I46="SFK Freight Forwarder",M46,M46+N46-1)</f>
         <v>22</v>
       </c>
       <c r="P46" s="3">
-        <f t="shared" ref="P46:P51" si="46">+IF(I46="SFK Freight Forwarder",0,5)</f>
+        <f>+IF(I46="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q46" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I46="SFK Freight Forwarder",O46,O46+P46-1)</f>
         <v>26</v>
       </c>
       <c r="R46" s="3">
-        <f t="shared" ref="R46:R51" si="47">9+N46</f>
+        <f>9+N46</f>
         <v>23</v>
       </c>
       <c r="S46" s="3">
         <v>7</v>
       </c>
       <c r="T46" s="3">
-        <f t="shared" si="24"/>
+        <f>+R46+S46-1</f>
         <v>29</v>
       </c>
       <c r="U46" s="3">
-        <f t="shared" ref="U46:U51" si="48">+T46+1</f>
+        <f>+T46+1</f>
         <v>30</v>
       </c>
       <c r="V46" s="3">
         <v>2</v>
       </c>
       <c r="W46" s="3">
-        <f t="shared" si="25"/>
+        <f>+U46+V46-1</f>
         <v>31</v>
       </c>
       <c r="X46" s="3">
         <v>3</v>
       </c>
       <c r="Y46" s="3">
-        <f t="shared" si="20"/>
+        <f>+ROUNDDOWN(W46/7,0)*7+X46</f>
         <v>31</v>
       </c>
       <c r="Z46" s="6">
-        <f t="shared" ref="Z46:Z50" si="49">+Y46+X46-1</f>
+        <f>+Y46+X46-1</f>
         <v>33</v>
       </c>
       <c r="AA46" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z46+AB46-1</f>
         <v>34</v>
       </c>
       <c r="AB46" s="3">
@@ -9433,21 +9450,21 @@
         <v>40</v>
       </c>
       <c r="AF46" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE46+AA46-1</f>
         <v>73</v>
       </c>
       <c r="AG46" s="6">
         <v>3</v>
       </c>
       <c r="AH46" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF46+AG46</f>
         <v>76</v>
       </c>
       <c r="AI46" s="3">
         <v>0</v>
       </c>
       <c r="AJ46" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI46+AH46</f>
         <v>76</v>
       </c>
       <c r="AK46" s="3" t="s">
@@ -9457,36 +9474,36 @@
         <v>2</v>
       </c>
       <c r="AM46" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ46+AL46</f>
         <v>78</v>
       </c>
       <c r="AN46" s="3">
         <v>2</v>
       </c>
       <c r="AO46" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM46+AN46</f>
         <v>80</v>
       </c>
       <c r="AP46" s="3">
         <v>6</v>
       </c>
       <c r="AQ46" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO46+AP46</f>
         <v>86</v>
       </c>
       <c r="AR46" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ46+7</f>
         <v>93</v>
       </c>
       <c r="AS46" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR46+7+AT46</f>
         <v>100</v>
       </c>
       <c r="AT46" s="3">
         <v>0</v>
       </c>
       <c r="AU46" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA46-R46</f>
         <v>11</v>
       </c>
       <c r="AV46" s="3" t="s">
@@ -9502,20 +9519,20 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B47" s="39" t="s">
+      <c r="B47" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="C47" s="38" t="s">
+      <c r="C47" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="D47" s="38" t="s">
+      <c r="D47" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="E47" s="38" t="s">
+      <c r="E47" s="33" t="s">
         <v>171</v>
       </c>
       <c r="F47" s="19">
@@ -9540,44 +9557,44 @@
         <v>7</v>
       </c>
       <c r="M47" s="3">
-        <f t="shared" si="35"/>
+        <f>+IF(I47="SFK Freight Forwarder",L47,9)</f>
         <v>9</v>
       </c>
       <c r="N47" s="3">
         <v>14</v>
       </c>
       <c r="O47" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I47="SFK Freight Forwarder",M47,M47+N47-1)</f>
         <v>22</v>
       </c>
       <c r="P47" s="3">
-        <f t="shared" si="46"/>
+        <f>+IF(I47="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q47" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I47="SFK Freight Forwarder",O47,O47+P47-1)</f>
         <v>26</v>
       </c>
       <c r="R47" s="3">
-        <f t="shared" si="47"/>
+        <f>9+N47</f>
         <v>23</v>
       </c>
       <c r="S47" s="3">
         <v>7</v>
       </c>
       <c r="T47" s="3">
-        <f t="shared" si="24"/>
+        <f>+R47+S47-1</f>
         <v>29</v>
       </c>
       <c r="U47" s="3">
-        <f t="shared" si="48"/>
+        <f>+T47+1</f>
         <v>30</v>
       </c>
       <c r="V47" s="3">
         <v>2</v>
       </c>
       <c r="W47" s="3">
-        <f t="shared" si="25"/>
+        <f>+U47+V47-1</f>
         <v>31</v>
       </c>
       <c r="X47" s="3">
@@ -9605,21 +9622,21 @@
         <v>68</v>
       </c>
       <c r="AF47" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE47+AA47-1</f>
         <v>103</v>
       </c>
       <c r="AG47" s="6">
         <v>3</v>
       </c>
       <c r="AH47" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF47+AG47</f>
         <v>106</v>
       </c>
       <c r="AI47" s="3">
         <v>0</v>
       </c>
       <c r="AJ47" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI47+AH47</f>
         <v>106</v>
       </c>
       <c r="AK47" s="3" t="s">
@@ -9629,36 +9646,36 @@
         <v>2</v>
       </c>
       <c r="AM47" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ47+AL47</f>
         <v>108</v>
       </c>
       <c r="AN47" s="3">
         <v>7</v>
       </c>
       <c r="AO47" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM47+AN47</f>
         <v>115</v>
       </c>
       <c r="AP47" s="3">
         <v>5</v>
       </c>
       <c r="AQ47" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO47+AP47</f>
         <v>120</v>
       </c>
       <c r="AR47" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ47+7</f>
         <v>127</v>
       </c>
       <c r="AS47" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR47+7+AT47</f>
         <v>134</v>
       </c>
       <c r="AT47" s="3">
         <v>0</v>
       </c>
       <c r="AU47" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA47-R47</f>
         <v>13</v>
       </c>
       <c r="AV47" s="3" t="s">
@@ -9674,193 +9691,192 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="A48" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B48" s="39" t="s">
+    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="5">
+        <v>930</v>
+      </c>
+      <c r="B48" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C48" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="D48" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="E48" s="38" t="s">
-        <v>53</v>
+      <c r="C48" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>81</v>
       </c>
       <c r="F48" s="19">
-        <v>90016500</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>159</v>
+        <v>91017700</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>157</v>
       </c>
       <c r="H48" s="2">
-        <v>0</v>
+        <v>26037000</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="J48" s="2">
-        <v>29159</v>
+        <v>26037000</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="L48" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M48" s="3">
-        <f t="shared" si="35"/>
+        <f>+IF(I48="SFK Freight Forwarder",L48,9)</f>
         <v>9</v>
       </c>
       <c r="N48" s="3">
         <v>14</v>
       </c>
       <c r="O48" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I48="SFK Freight Forwarder",M48,M48+N48-1)</f>
         <v>22</v>
       </c>
       <c r="P48" s="3">
-        <f t="shared" si="46"/>
         <v>5</v>
       </c>
       <c r="Q48" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I48="SFK Freight Forwarder",O48,O48+P48-1)</f>
         <v>26</v>
       </c>
       <c r="R48" s="3">
-        <f t="shared" si="47"/>
+        <f>9+N48</f>
         <v>23</v>
       </c>
       <c r="S48" s="3">
         <v>7</v>
       </c>
       <c r="T48" s="3">
-        <f t="shared" si="24"/>
+        <f>+R48+S48-1</f>
         <v>29</v>
       </c>
       <c r="U48" s="3">
-        <f t="shared" si="48"/>
+        <f>+T48+1</f>
         <v>30</v>
       </c>
       <c r="V48" s="3">
+        <v>1</v>
+      </c>
+      <c r="W48" s="3">
+        <f>+U48+V48-1</f>
+        <v>30</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>30</v>
+      </c>
+      <c r="Z48" s="6">
+        <v>35</v>
+      </c>
+      <c r="AA48" s="6">
+        <f>+Z48+AB48-1</f>
+        <v>37</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>8</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>8</v>
+      </c>
+      <c r="AE48" s="3">
+        <v>40</v>
+      </c>
+      <c r="AF48" s="3">
+        <f>+AE48+AA48-1</f>
+        <v>76</v>
+      </c>
+      <c r="AG48" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH48" s="6">
+        <f>+AF48+AG48</f>
+        <v>79</v>
+      </c>
+      <c r="AI48" s="3">
+        <v>7</v>
+      </c>
+      <c r="AJ48" s="3">
+        <f>+AI48+AH48</f>
+        <v>86</v>
+      </c>
+      <c r="AK48" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL48" s="3">
+        <v>3</v>
+      </c>
+      <c r="AM48" s="3">
+        <f>+AJ48+AL48</f>
+        <v>89</v>
+      </c>
+      <c r="AN48" s="3">
+        <v>8</v>
+      </c>
+      <c r="AO48" s="3">
+        <f>+AM48+AN48</f>
+        <v>97</v>
+      </c>
+      <c r="AP48" s="3">
         <v>2</v>
       </c>
-      <c r="W48" s="3">
-        <f t="shared" si="25"/>
-        <v>31</v>
-      </c>
-      <c r="X48" s="3">
-        <v>2</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>33</v>
-      </c>
-      <c r="Z48" s="6">
-        <v>33</v>
-      </c>
-      <c r="AA48" s="6">
-        <f t="shared" si="18"/>
-        <v>38</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>6</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>7</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>7</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>45</v>
-      </c>
-      <c r="AF48" s="3">
-        <f t="shared" si="26"/>
-        <v>82</v>
-      </c>
-      <c r="AG48" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH48" s="6">
-        <f t="shared" si="27"/>
-        <v>85</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ48" s="3">
-        <f t="shared" si="28"/>
-        <v>85</v>
-      </c>
-      <c r="AK48" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AL48" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM48" s="3">
-        <f t="shared" si="29"/>
-        <v>86</v>
-      </c>
-      <c r="AN48" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO48" s="3">
-        <f t="shared" si="30"/>
-        <v>87</v>
-      </c>
-      <c r="AP48" s="3">
-        <v>3</v>
-      </c>
       <c r="AQ48" s="3">
-        <f t="shared" si="31"/>
-        <v>90</v>
+        <f>+AO48+AP48</f>
+        <v>99</v>
       </c>
       <c r="AR48" s="3">
-        <f t="shared" si="32"/>
-        <v>97</v>
+        <f>+AQ48+7</f>
+        <v>106</v>
       </c>
       <c r="AS48" s="3">
-        <f t="shared" si="33"/>
-        <v>104</v>
+        <f>+AR48+7+AT48</f>
+        <v>130</v>
       </c>
       <c r="AT48" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU48" s="3">
-        <f t="shared" si="34"/>
-        <v>15</v>
+        <f>+AA48-R48</f>
+        <v>14</v>
       </c>
       <c r="AV48" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AW48" s="3" t="s">
         <v>131</v>
       </c>
       <c r="AX48" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY48" s="40">
+        <v>56</v>
+      </c>
+      <c r="AY48" s="21">
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B49" s="39" t="s">
+      <c r="B49" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="C49" s="38" t="s">
+      <c r="C49" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="D49" s="38" t="s">
+      <c r="D49" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="E49" s="38" t="s">
+      <c r="E49" s="33" t="s">
         <v>71</v>
       </c>
       <c r="F49" s="19">
@@ -9885,59 +9901,59 @@
         <v>7</v>
       </c>
       <c r="M49" s="3">
-        <f t="shared" si="35"/>
+        <f>+IF(I49="SFK Freight Forwarder",L49,9)</f>
         <v>9</v>
       </c>
       <c r="N49" s="3">
         <v>14</v>
       </c>
       <c r="O49" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I49="SFK Freight Forwarder",M49,M49+N49-1)</f>
         <v>22</v>
       </c>
       <c r="P49" s="3">
-        <f t="shared" si="46"/>
+        <f>+IF(I49="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q49" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I49="SFK Freight Forwarder",O49,O49+P49-1)</f>
         <v>26</v>
       </c>
       <c r="R49" s="3">
-        <f t="shared" si="47"/>
+        <f>9+N49</f>
         <v>23</v>
       </c>
       <c r="S49" s="3">
         <v>7</v>
       </c>
       <c r="T49" s="3">
-        <f t="shared" si="24"/>
+        <f>+R49+S49-1</f>
         <v>29</v>
       </c>
       <c r="U49" s="3">
-        <f t="shared" si="48"/>
+        <f>+T49+1</f>
         <v>30</v>
       </c>
       <c r="V49" s="3">
         <v>2</v>
       </c>
       <c r="W49" s="3">
-        <f t="shared" si="25"/>
+        <f>+U49+V49-1</f>
         <v>31</v>
       </c>
       <c r="X49" s="3">
         <v>2</v>
       </c>
       <c r="Y49" s="3">
-        <f t="shared" si="20"/>
+        <f>+ROUNDDOWN(W49/7,0)*7+X49</f>
         <v>30</v>
       </c>
       <c r="Z49" s="6">
-        <f t="shared" si="49"/>
+        <f>+Y49+X49-1</f>
         <v>31</v>
       </c>
       <c r="AA49" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z49+AB49-1</f>
         <v>34</v>
       </c>
       <c r="AB49" s="3">
@@ -9953,21 +9969,21 @@
         <v>48</v>
       </c>
       <c r="AF49" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE49+AA49-1</f>
         <v>81</v>
       </c>
       <c r="AG49" s="6">
         <v>0</v>
       </c>
       <c r="AH49" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF49+AG49</f>
         <v>81</v>
       </c>
       <c r="AI49" s="3">
         <v>0</v>
       </c>
       <c r="AJ49" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI49+AH49</f>
         <v>81</v>
       </c>
       <c r="AK49" s="3" t="s">
@@ -9977,36 +9993,36 @@
         <v>3</v>
       </c>
       <c r="AM49" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ49+AL49</f>
         <v>84</v>
       </c>
       <c r="AN49" s="3">
         <v>8</v>
       </c>
       <c r="AO49" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM49+AN49</f>
         <v>92</v>
       </c>
       <c r="AP49" s="3">
         <v>0</v>
       </c>
       <c r="AQ49" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO49+AP49</f>
         <v>92</v>
       </c>
       <c r="AR49" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ49+7</f>
         <v>99</v>
       </c>
       <c r="AS49" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR49+7+AT49</f>
         <v>106</v>
       </c>
       <c r="AT49" s="3">
         <v>0</v>
       </c>
       <c r="AU49" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA49-R49</f>
         <v>11</v>
       </c>
       <c r="AV49" s="3" t="s">
@@ -10022,20 +10038,20 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="50" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B50" s="39" t="s">
+      <c r="B50" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="C50" s="38" t="s">
+      <c r="C50" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="D50" s="38" t="s">
+      <c r="D50" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="E50" s="38" t="s">
+      <c r="E50" s="33" t="s">
         <v>59</v>
       </c>
       <c r="F50" s="19">
@@ -10060,59 +10076,59 @@
         <v>2</v>
       </c>
       <c r="M50" s="3">
-        <f t="shared" si="35"/>
+        <f>+IF(I50="SFK Freight Forwarder",L50,9)</f>
         <v>9</v>
       </c>
       <c r="N50" s="3">
         <v>14</v>
       </c>
       <c r="O50" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I50="SFK Freight Forwarder",M50,M50+N50-1)</f>
         <v>22</v>
       </c>
       <c r="P50" s="3">
-        <f t="shared" si="46"/>
+        <f>+IF(I50="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q50" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I50="SFK Freight Forwarder",O50,O50+P50-1)</f>
         <v>26</v>
       </c>
       <c r="R50" s="3">
-        <f t="shared" si="47"/>
+        <f>9+N50</f>
         <v>23</v>
       </c>
       <c r="S50" s="3">
         <v>7</v>
       </c>
       <c r="T50" s="3">
-        <f t="shared" si="24"/>
+        <f>+R50+S50-1</f>
         <v>29</v>
       </c>
       <c r="U50" s="3">
-        <f t="shared" si="48"/>
+        <f>+T50+1</f>
         <v>30</v>
       </c>
       <c r="V50" s="3">
         <v>2</v>
       </c>
       <c r="W50" s="3">
-        <f t="shared" si="25"/>
+        <f>+U50+V50-1</f>
         <v>31</v>
       </c>
       <c r="X50" s="3">
         <v>3</v>
       </c>
       <c r="Y50" s="3">
-        <f t="shared" si="20"/>
+        <f>+ROUNDDOWN(W50/7,0)*7+X50</f>
         <v>31</v>
       </c>
       <c r="Z50" s="6">
-        <f t="shared" si="49"/>
+        <f>+Y50+X50-1</f>
         <v>33</v>
       </c>
       <c r="AA50" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z50+AB50-1</f>
         <v>34</v>
       </c>
       <c r="AB50" s="3">
@@ -10128,21 +10144,21 @@
         <v>50</v>
       </c>
       <c r="AF50" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE50+AA50-1</f>
         <v>83</v>
       </c>
       <c r="AG50" s="6">
         <v>3</v>
       </c>
       <c r="AH50" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF50+AG50</f>
         <v>86</v>
       </c>
       <c r="AI50" s="3">
         <v>0</v>
       </c>
       <c r="AJ50" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI50+AH50</f>
         <v>86</v>
       </c>
       <c r="AK50" s="3" t="s">
@@ -10152,36 +10168,36 @@
         <v>4</v>
       </c>
       <c r="AM50" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ50+AL50</f>
         <v>90</v>
       </c>
       <c r="AN50" s="3">
         <v>2</v>
       </c>
       <c r="AO50" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM50+AN50</f>
         <v>92</v>
       </c>
       <c r="AP50" s="3">
         <v>1</v>
       </c>
       <c r="AQ50" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO50+AP50</f>
         <v>93</v>
       </c>
       <c r="AR50" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ50+7</f>
         <v>100</v>
       </c>
       <c r="AS50" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR50+7+AT50</f>
         <v>107</v>
       </c>
       <c r="AT50" s="3">
         <v>0</v>
       </c>
       <c r="AU50" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA50-R50</f>
         <v>11</v>
       </c>
       <c r="AV50" s="3" t="s">
@@ -10197,20 +10213,20 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B51" s="38" t="s">
+      <c r="B51" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="C51" s="38" t="s">
+      <c r="C51" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="D51" s="38" t="s">
+      <c r="D51" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="E51" s="38" t="s">
+      <c r="E51" s="33" t="s">
         <v>53</v>
       </c>
       <c r="F51" s="19">
@@ -10235,58 +10251,58 @@
         <v>7</v>
       </c>
       <c r="M51" s="3">
-        <f t="shared" si="35"/>
+        <f>+IF(I51="SFK Freight Forwarder",L51,9)</f>
         <v>9</v>
       </c>
       <c r="N51" s="3">
         <v>7</v>
       </c>
       <c r="O51" s="3">
-        <f t="shared" si="22"/>
+        <f>IF(I51="SFK Freight Forwarder",M51,M51+N51-1)</f>
         <v>15</v>
       </c>
       <c r="P51" s="3">
-        <f t="shared" si="46"/>
+        <f>+IF(I51="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q51" s="3">
-        <f t="shared" si="23"/>
+        <f>+IF(I51="SFK Freight Forwarder",O51,O51+P51-1)</f>
         <v>19</v>
       </c>
       <c r="R51" s="3">
-        <f t="shared" si="47"/>
+        <f>9+N51</f>
         <v>16</v>
       </c>
       <c r="S51" s="3">
         <v>3</v>
       </c>
       <c r="T51" s="3">
-        <f t="shared" si="24"/>
+        <f>+R51+S51-1</f>
         <v>18</v>
       </c>
       <c r="U51" s="3">
-        <f t="shared" si="48"/>
+        <f>+T51+1</f>
         <v>19</v>
       </c>
       <c r="V51" s="3">
         <v>5</v>
       </c>
       <c r="W51" s="3">
-        <f t="shared" si="25"/>
+        <f>+U51+V51-1</f>
         <v>23</v>
       </c>
       <c r="X51" s="3">
         <v>2</v>
       </c>
       <c r="Y51" s="3">
-        <f t="shared" si="20"/>
+        <f>+ROUNDDOWN(W51/7,0)*7+X51</f>
         <v>23</v>
       </c>
       <c r="Z51" s="6">
         <v>23</v>
       </c>
       <c r="AA51" s="6">
-        <f t="shared" si="18"/>
+        <f>+Z51+AB51-1</f>
         <v>25</v>
       </c>
       <c r="AB51" s="3">
@@ -10302,21 +10318,21 @@
         <v>40</v>
       </c>
       <c r="AF51" s="3">
-        <f t="shared" si="26"/>
+        <f>+AE51+AA51-1</f>
         <v>64</v>
       </c>
       <c r="AG51" s="6">
         <v>3</v>
       </c>
       <c r="AH51" s="6">
-        <f t="shared" si="27"/>
+        <f>+AF51+AG51</f>
         <v>67</v>
       </c>
       <c r="AI51" s="3">
         <v>7</v>
       </c>
       <c r="AJ51" s="3">
-        <f t="shared" si="28"/>
+        <f>+AI51+AH51</f>
         <v>74</v>
       </c>
       <c r="AK51" s="3">
@@ -10326,36 +10342,36 @@
         <v>6</v>
       </c>
       <c r="AM51" s="3">
-        <f t="shared" si="29"/>
+        <f>+AJ51+AL51</f>
         <v>80</v>
       </c>
       <c r="AN51" s="3">
         <v>2</v>
       </c>
       <c r="AO51" s="3">
-        <f t="shared" si="30"/>
+        <f>+AM51+AN51</f>
         <v>82</v>
       </c>
       <c r="AP51" s="3">
         <v>0</v>
       </c>
       <c r="AQ51" s="3">
-        <f t="shared" si="31"/>
+        <f>+AO51+AP51</f>
         <v>82</v>
       </c>
       <c r="AR51" s="3">
-        <f t="shared" si="32"/>
+        <f>+AQ51+7</f>
         <v>89</v>
       </c>
       <c r="AS51" s="3">
-        <f t="shared" si="33"/>
+        <f>+AR51+7+AT51</f>
         <v>96</v>
       </c>
       <c r="AT51" s="3">
         <v>0</v>
       </c>
       <c r="AU51" s="3">
-        <f t="shared" si="34"/>
+        <f>+AA51-R51</f>
         <v>9</v>
       </c>
       <c r="AV51" s="3" t="s">
@@ -10371,7 +10387,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="52" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>168</v>
       </c>
@@ -10409,21 +10425,21 @@
         <v>5</v>
       </c>
       <c r="M52" s="3">
-        <f t="shared" ref="M52:M53" si="50">+IF(I52="SFK Freight Forwarder",L52,9)</f>
+        <f>+IF(I52="SFK Freight Forwarder",L52,9)</f>
         <v>9</v>
       </c>
       <c r="N52" s="23">
         <v>2</v>
       </c>
       <c r="O52" s="3">
-        <f t="shared" ref="O52:O53" si="51">IF(I52="SFK Freight Forwarder",M52,M52+N52-1)</f>
+        <f>IF(I52="SFK Freight Forwarder",M52,M52+N52-1)</f>
         <v>10</v>
       </c>
       <c r="P52" s="3">
         <v>5</v>
       </c>
       <c r="Q52" s="3">
-        <f t="shared" ref="Q52:Q53" si="52">+IF(I52="SFK Freight Forwarder",O52,O52+P52-1)</f>
+        <f>+IF(I52="SFK Freight Forwarder",O52,O52+P52-1)</f>
         <v>14</v>
       </c>
       <c r="R52" s="23">
@@ -10442,7 +10458,7 @@
         <v>4</v>
       </c>
       <c r="W52" s="23">
-        <f t="shared" ref="W52:W53" si="53">+U52+V52-1</f>
+        <f>+U52+V52-1</f>
         <v>18</v>
       </c>
       <c r="X52" s="23">
@@ -10455,7 +10471,7 @@
         <v>19</v>
       </c>
       <c r="AA52" s="6">
-        <f t="shared" ref="AA52:AA53" si="54">+Z52+AB52-1</f>
+        <f>+Z52+AB52-1</f>
         <v>22</v>
       </c>
       <c r="AB52" s="23">
@@ -10467,21 +10483,21 @@
         <v>46</v>
       </c>
       <c r="AF52" s="23">
-        <f t="shared" ref="AF52:AF53" si="55">+AE52+AA52-1</f>
+        <f>+AE52+AA52-1</f>
         <v>67</v>
       </c>
       <c r="AG52" s="23">
         <v>3</v>
       </c>
       <c r="AH52" s="23">
-        <f t="shared" ref="AH52:AH53" si="56">+AF52+AG52</f>
+        <f>+AF52+AG52</f>
         <v>70</v>
       </c>
       <c r="AI52" s="23">
         <v>7</v>
       </c>
       <c r="AJ52" s="23">
-        <f t="shared" ref="AJ52:AJ53" si="57">+AI52+AH52</f>
+        <f>+AI52+AH52</f>
         <v>77</v>
       </c>
       <c r="AK52" s="23"/>
@@ -10489,36 +10505,36 @@
         <v>3</v>
       </c>
       <c r="AM52" s="23">
-        <f t="shared" ref="AM52:AM53" si="58">+AJ52+AL52</f>
+        <f>+AJ52+AL52</f>
         <v>80</v>
       </c>
       <c r="AN52" s="23">
         <v>2</v>
       </c>
       <c r="AO52" s="23">
-        <f t="shared" ref="AO52:AO53" si="59">+AM52+AN52</f>
+        <f>+AM52+AN52</f>
         <v>82</v>
       </c>
       <c r="AP52" s="23">
         <v>2</v>
       </c>
       <c r="AQ52" s="23">
-        <f t="shared" ref="AQ52:AQ53" si="60">+AO52+AP52</f>
+        <f>+AO52+AP52</f>
         <v>84</v>
       </c>
       <c r="AR52" s="23">
-        <f t="shared" ref="AR52:AR53" si="61">+AQ52+7</f>
+        <f>+AQ52+7</f>
         <v>91</v>
       </c>
       <c r="AS52" s="23">
-        <f t="shared" ref="AS52:AS53" si="62">+AR52+7+AT52</f>
+        <f>+AR52+7+AT52</f>
         <v>112</v>
       </c>
       <c r="AT52" s="23">
         <v>14</v>
       </c>
       <c r="AU52" s="3">
-        <f t="shared" ref="AU52:AU53" si="63">+AA52-R52</f>
+        <f>+AA52-R52</f>
         <v>22</v>
       </c>
       <c r="AV52" s="23" t="s">
@@ -10534,191 +10550,381 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="53" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="A53" s="5">
+    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B53" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="C53" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="F53" s="19">
+        <v>90014400</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J53" s="2">
+        <v>29159</v>
+      </c>
+      <c r="K53" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="L53" s="3">
+        <v>5</v>
+      </c>
+      <c r="M53" s="3">
+        <f>+IF(I53="SFK Freight Forwarder",L53,9)</f>
+        <v>9</v>
+      </c>
+      <c r="N53" s="23">
+        <v>2</v>
+      </c>
+      <c r="O53" s="3">
+        <f>IF(I53="SFK Freight Forwarder",M53,M53+N53-1)</f>
+        <v>10</v>
+      </c>
+      <c r="P53" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q53" s="3">
+        <f>+IF(I53="SFK Freight Forwarder",O53,O53+P53-1)</f>
+        <v>14</v>
+      </c>
+      <c r="R53" s="23">
+        <v>0</v>
+      </c>
+      <c r="S53" s="23">
+        <v>0</v>
+      </c>
+      <c r="T53" s="25">
+        <v>0</v>
+      </c>
+      <c r="U53" s="23">
+        <v>15</v>
+      </c>
+      <c r="V53" s="23">
+        <v>4</v>
+      </c>
+      <c r="W53" s="23">
+        <f>+U53+V53-1</f>
+        <v>18</v>
+      </c>
+      <c r="X53" s="23">
+        <v>1</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>18</v>
+      </c>
+      <c r="Z53" s="6">
+        <v>19</v>
+      </c>
+      <c r="AA53" s="6">
+        <f>+Z53+AB53-1</f>
+        <v>22</v>
+      </c>
+      <c r="AB53" s="23">
+        <v>4</v>
+      </c>
+      <c r="AC53" s="23"/>
+      <c r="AD53" s="23"/>
+      <c r="AE53" s="23">
+        <v>46</v>
+      </c>
+      <c r="AF53" s="23">
+        <f>+AE53+AA53-1</f>
+        <v>67</v>
+      </c>
+      <c r="AG53" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH53" s="23">
+        <f>+AF53+AG53</f>
+        <v>70</v>
+      </c>
+      <c r="AI53" s="23">
+        <v>7</v>
+      </c>
+      <c r="AJ53" s="23">
+        <f>+AI53+AH53</f>
+        <v>77</v>
+      </c>
+      <c r="AK53" s="23"/>
+      <c r="AL53" s="23">
+        <v>3</v>
+      </c>
+      <c r="AM53" s="23">
+        <f>+AJ53+AL53</f>
+        <v>80</v>
+      </c>
+      <c r="AN53" s="23">
+        <v>2</v>
+      </c>
+      <c r="AO53" s="23">
+        <f>+AM53+AN53</f>
+        <v>82</v>
+      </c>
+      <c r="AP53" s="23">
+        <v>2</v>
+      </c>
+      <c r="AQ53" s="23">
+        <f>+AO53+AP53</f>
+        <v>84</v>
+      </c>
+      <c r="AR53" s="23">
+        <f>+AQ53+7</f>
+        <v>91</v>
+      </c>
+      <c r="AS53" s="23">
+        <f>+AR53+7+AT53</f>
+        <v>112</v>
+      </c>
+      <c r="AT53" s="23">
+        <v>14</v>
+      </c>
+      <c r="AU53" s="3">
+        <f>+AA53-R53</f>
+        <v>22</v>
+      </c>
+      <c r="AV53" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW53" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="AX53" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="AY53" s="37">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="5">
         <v>1039</v>
       </c>
-      <c r="B53" s="33" t="s">
+      <c r="B54" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C54" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D54" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E54" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F53" s="19">
+      <c r="F54" s="19">
         <v>91017700</v>
       </c>
-      <c r="G53" s="5" t="s">
+      <c r="G54" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H54" s="2">
         <v>222222</v>
       </c>
-      <c r="I53" s="4" t="s">
+      <c r="I54" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J54" s="2">
         <v>222222</v>
       </c>
-      <c r="K53" s="4" t="s">
+      <c r="K54" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="L53" s="3">
-        <v>7</v>
-      </c>
-      <c r="M53" s="3">
-        <f t="shared" si="50"/>
+      <c r="L54" s="3">
+        <v>7</v>
+      </c>
+      <c r="M54" s="3">
+        <f>+IF(I54="SFK Freight Forwarder",L54,9)</f>
         <v>9</v>
       </c>
-      <c r="N53" s="3">
+      <c r="N54" s="3">
         <v>21</v>
       </c>
-      <c r="O53" s="3">
-        <f t="shared" si="51"/>
+      <c r="O54" s="3">
+        <f>IF(I54="SFK Freight Forwarder",M54,M54+N54-1)</f>
         <v>29</v>
       </c>
-      <c r="P53" s="3">
-        <f t="shared" ref="P53" si="64">+IF(I53="SFK Freight Forwarder",0,5)</f>
+      <c r="P54" s="3">
+        <f>+IF(I54="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
-      <c r="Q53" s="3">
-        <f t="shared" si="52"/>
+      <c r="Q54" s="3">
+        <f>+IF(I54="SFK Freight Forwarder",O54,O54+P54-1)</f>
         <v>33</v>
       </c>
-      <c r="R53" s="3">
-        <f t="shared" ref="R53" si="65">9+N53</f>
+      <c r="R54" s="3">
+        <f>9+N54</f>
         <v>30</v>
       </c>
-      <c r="S53" s="3">
-        <v>7</v>
-      </c>
-      <c r="T53" s="3">
-        <f t="shared" ref="T53" si="66">+R53+S53-1</f>
+      <c r="S54" s="3">
+        <v>7</v>
+      </c>
+      <c r="T54" s="3">
+        <f>+R54+S54-1</f>
         <v>36</v>
       </c>
-      <c r="U53" s="3">
-        <f t="shared" ref="U53" si="67">+T53+1</f>
+      <c r="U54" s="3">
+        <f>+T54+1</f>
         <v>37</v>
       </c>
-      <c r="V53" s="3">
+      <c r="V54" s="3">
         <v>1</v>
       </c>
-      <c r="W53" s="3">
-        <f t="shared" si="53"/>
+      <c r="W54" s="3">
+        <f>+U54+V54-1</f>
         <v>37</v>
       </c>
-      <c r="X53" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="3">
+      <c r="X54" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="3">
         <v>37</v>
       </c>
-      <c r="Z53" s="6">
+      <c r="Z54" s="6">
         <v>42</v>
       </c>
-      <c r="AA53" s="6">
-        <f t="shared" si="54"/>
+      <c r="AA54" s="6">
+        <f>+Z54+AB54-1</f>
         <v>44</v>
       </c>
-      <c r="AB53" s="3">
-        <v>3</v>
-      </c>
-      <c r="AC53" s="3">
+      <c r="AB54" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC54" s="3">
         <v>4</v>
       </c>
-      <c r="AD53" s="3">
+      <c r="AD54" s="3">
         <v>4</v>
       </c>
-      <c r="AE53" s="3">
+      <c r="AE54" s="3">
         <v>40</v>
       </c>
-      <c r="AF53" s="3">
-        <f t="shared" si="55"/>
+      <c r="AF54" s="3">
+        <f>+AE54+AA54-1</f>
         <v>83</v>
       </c>
-      <c r="AG53" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH53" s="6">
-        <f t="shared" si="56"/>
+      <c r="AG54" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH54" s="6">
+        <f>+AF54+AG54</f>
         <v>86</v>
       </c>
-      <c r="AI53" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ53" s="3">
-        <f t="shared" si="57"/>
+      <c r="AI54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="3">
+        <f>+AI54+AH54</f>
         <v>86</v>
       </c>
-      <c r="AK53" s="3" t="s">
+      <c r="AK54" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AL53" s="3">
+      <c r="AL54" s="3">
         <v>2</v>
       </c>
-      <c r="AM53" s="3">
-        <f t="shared" si="58"/>
+      <c r="AM54" s="3">
+        <f>+AJ54+AL54</f>
         <v>88</v>
       </c>
-      <c r="AN53" s="3">
-        <v>3</v>
-      </c>
-      <c r="AO53" s="3">
-        <f t="shared" si="59"/>
-        <v>91</v>
-      </c>
-      <c r="AP53" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ53" s="3">
-        <f t="shared" si="60"/>
-        <v>91</v>
-      </c>
-      <c r="AR53" s="3">
-        <f t="shared" si="61"/>
+      <c r="AN54" s="3">
+        <v>8</v>
+      </c>
+      <c r="AO54" s="3">
+        <f>+AM54+AN54</f>
+        <v>96</v>
+      </c>
+      <c r="AP54" s="3">
+        <v>2</v>
+      </c>
+      <c r="AQ54" s="3">
+        <f>+AO54+AP54</f>
         <v>98</v>
       </c>
-      <c r="AS53" s="3">
-        <f t="shared" si="62"/>
+      <c r="AR54" s="3">
+        <f>+AQ54+7</f>
         <v>105</v>
       </c>
-      <c r="AT53" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU53" s="3">
-        <f t="shared" si="63"/>
+      <c r="AS54" s="3">
+        <f>+AR54+7+AT54</f>
+        <v>112</v>
+      </c>
+      <c r="AT54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU54" s="3">
+        <f>+AA54-R54</f>
         <v>14</v>
       </c>
-      <c r="AV53" s="3" t="s">
+      <c r="AV54" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AW53" s="3" t="s">
+      <c r="AW54" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AX53" s="20" t="s">
+      <c r="AX54" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="AY53" s="21">
+      <c r="AY54" s="21">
         <v>46507</v>
       </c>
+    </row>
+    <row r="61" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="D61" s="41"/>
+    </row>
+    <row r="63" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="D63" s="42"/>
+    </row>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D65" s="41"/>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D67" s="42"/>
+    </row>
+    <row r="69" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D69" s="41"/>
+    </row>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D70" s="42"/>
+    </row>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D71" s="42"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY52" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
+  <autoFilter ref="A1:AY54" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Horse Sevilla"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 K16:K1048194 C16:E1048194" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 C53:C1048195 E53:E1048195 D53:D60 D72:D1048195 C16:E52 K16:K1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
       <formula1>shippername</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 H54:K1048194 C2:E1048194 I2:I53 J12:J53 K2:K53" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 H55:K1048195 C53:C1048195 E53:E1048195 D53:D60 D72:D1048195 C2:E52 J12:J54 I2:I54 K2:K54" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
       <formula1>AILNname</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048194" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048195" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">
       <formula1>plantname</formula1>
     </dataValidation>
   </dataValidations>
@@ -10733,6 +10939,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7007F1-B98C-4FB4-AD1E-FC672D1A14BF}">
+  <sheetPr codeName="Hoja1"/>
   <dimension ref="B2:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9744A0-E752-4503-951E-25F4975C4361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FBF124-78C4-4A26-851A-49B3AD6AE224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -366,7 +366,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="174">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -885,6 +885,9 @@
   </si>
   <si>
     <t>O002</t>
+  </si>
+  <si>
+    <t>O010</t>
   </si>
 </sst>
 </file>
@@ -895,7 +898,7 @@
     <numFmt numFmtId="164" formatCode="0000000000"/>
     <numFmt numFmtId="165" formatCode="00########"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -985,6 +988,13 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="15">
@@ -1228,11 +1238,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1573,35 +1584,35 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF71"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.453125" defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.453125" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.453125" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.26953125" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.54296875" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.81640625" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.453125" style="9" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" customWidth="1"/>
-    <col min="14" max="14" width="14.54296875" customWidth="1"/>
-    <col min="15" max="28" width="10.453125" customWidth="1"/>
-    <col min="29" max="30" width="10.453125" hidden="1" customWidth="1"/>
-    <col min="31" max="34" width="10.453125" customWidth="1"/>
-    <col min="35" max="36" width="15.1796875" customWidth="1"/>
-    <col min="37" max="37" width="15.81640625" customWidth="1"/>
-    <col min="38" max="39" width="9.54296875" customWidth="1"/>
-    <col min="40" max="41" width="15.453125" customWidth="1"/>
-    <col min="42" max="42" width="10.453125" customWidth="1" collapsed="1"/>
-    <col min="43" max="49" width="10.453125" customWidth="1"/>
-    <col min="50" max="50" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.26953125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="10.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="15" max="28" width="10.42578125" customWidth="1"/>
+    <col min="29" max="30" width="10.42578125" hidden="1" customWidth="1"/>
+    <col min="31" max="34" width="10.42578125" customWidth="1"/>
+    <col min="35" max="36" width="15.140625" customWidth="1"/>
+    <col min="37" max="37" width="15.85546875" customWidth="1"/>
+    <col min="38" max="39" width="9.5703125" customWidth="1"/>
+    <col min="40" max="41" width="15.42578125" customWidth="1"/>
+    <col min="42" max="42" width="10.42578125" customWidth="1" collapsed="1"/>
+    <col min="43" max="49" width="10.42578125" customWidth="1"/>
+    <col min="50" max="50" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
@@ -1768,7 +1779,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>60</v>
       </c>
@@ -1806,44 +1817,44 @@
         <v>7</v>
       </c>
       <c r="M2" s="3">
-        <f t="shared" ref="M2:M29" si="0">+IF(I2="SFK Freight Forwarder",L2,9)</f>
+        <f>+IF(I2="SFK Freight Forwarder",L2,9)</f>
         <v>9</v>
       </c>
       <c r="N2" s="3">
         <v>7</v>
       </c>
       <c r="O2" s="3">
-        <f t="shared" ref="O2:O32" si="1">IF(I2="SFK Freight Forwarder",M2,M2+N2-1)</f>
+        <f>IF(I2="SFK Freight Forwarder",M2,M2+N2-1)</f>
         <v>15</v>
       </c>
       <c r="P2" s="3">
-        <f t="shared" ref="P2:P26" si="2">+IF(I2="SFK Freight Forwarder",0,5)</f>
+        <f>+IF(I2="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q2" s="3">
-        <f t="shared" ref="Q2:Q32" si="3">+IF(I2="SFK Freight Forwarder",O2,O2+P2-1)</f>
+        <f>+IF(I2="SFK Freight Forwarder",O2,O2+P2-1)</f>
         <v>19</v>
       </c>
       <c r="R2" s="3">
-        <f t="shared" ref="R2:R43" si="4">9+N2</f>
+        <f>9+N2</f>
         <v>16</v>
       </c>
       <c r="S2" s="3">
         <v>7</v>
       </c>
       <c r="T2" s="3">
-        <f t="shared" ref="T2:T32" si="5">+R2+S2-1</f>
+        <f>+R2+S2-1</f>
         <v>22</v>
       </c>
       <c r="U2" s="3">
-        <f t="shared" ref="U2:U43" si="6">+T2+1</f>
+        <f>+T2+1</f>
         <v>23</v>
       </c>
       <c r="V2" s="3">
         <v>1</v>
       </c>
       <c r="W2" s="3">
-        <f t="shared" ref="W2:W32" si="7">+U2+V2-1</f>
+        <f>+U2+V2-1</f>
         <v>23</v>
       </c>
       <c r="X2" s="3">
@@ -1856,7 +1867,7 @@
         <v>25</v>
       </c>
       <c r="AA2" s="6">
-        <f t="shared" ref="AA2:AA16" si="8">+Z2+AB2-1</f>
+        <f>+Z2+AB2-1</f>
         <v>27</v>
       </c>
       <c r="AB2" s="3">
@@ -1872,21 +1883,21 @@
         <v>46</v>
       </c>
       <c r="AF2" s="3">
-        <f t="shared" ref="AF2:AF32" si="9">+AE2+AA2-1</f>
+        <f>+AE2+AA2-1</f>
         <v>72</v>
       </c>
       <c r="AG2" s="6">
         <v>3</v>
       </c>
       <c r="AH2" s="6">
-        <f t="shared" ref="AH2:AH32" si="10">+AF2+AG2</f>
+        <f>+AF2+AG2</f>
         <v>75</v>
       </c>
       <c r="AI2" s="3">
         <v>7</v>
       </c>
       <c r="AJ2" s="3">
-        <f t="shared" ref="AJ2:AJ32" si="11">+AI2+AH2</f>
+        <f>+AI2+AH2</f>
         <v>82</v>
       </c>
       <c r="AK2" s="3" t="s">
@@ -1896,36 +1907,36 @@
         <v>2</v>
       </c>
       <c r="AM2" s="3">
-        <f t="shared" ref="AM2:AM32" si="12">+AJ2+AL2</f>
+        <f>+AJ2+AL2</f>
         <v>84</v>
       </c>
       <c r="AN2" s="3">
         <v>2</v>
       </c>
       <c r="AO2" s="3">
-        <f t="shared" ref="AO2:AO32" si="13">+AM2+AN2</f>
+        <f>+AM2+AN2</f>
         <v>86</v>
       </c>
       <c r="AP2" s="3">
         <v>5</v>
       </c>
       <c r="AQ2" s="3">
-        <f t="shared" ref="AQ2:AQ32" si="14">+AO2+AP2</f>
+        <f>+AO2+AP2</f>
         <v>91</v>
       </c>
       <c r="AR2" s="3">
-        <f t="shared" ref="AR2:AR32" si="15">+AQ2+7</f>
+        <f>+AQ2+7</f>
         <v>98</v>
       </c>
       <c r="AS2" s="3">
-        <f t="shared" ref="AS2:AS32" si="16">+AR2+7+AT2</f>
+        <f>+AR2+7+AT2</f>
         <v>115</v>
       </c>
       <c r="AT2" s="3">
         <v>10</v>
       </c>
       <c r="AU2" s="3">
-        <f t="shared" ref="AU2:AU32" si="17">+AA2-R2</f>
+        <f>+AA2-R2</f>
         <v>11</v>
       </c>
       <c r="AV2" s="3" t="s">
@@ -1941,7 +1952,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>120</v>
       </c>
@@ -1979,44 +1990,44 @@
         <v>7</v>
       </c>
       <c r="M3" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I3="SFK Freight Forwarder",L3,9)</f>
         <v>9</v>
       </c>
       <c r="N3" s="3">
         <v>14</v>
       </c>
       <c r="O3" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I3="SFK Freight Forwarder",M3,M3+N3-1)</f>
         <v>22</v>
       </c>
       <c r="P3" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I3="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q3" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I3="SFK Freight Forwarder",O3,O3+P3-1)</f>
         <v>26</v>
       </c>
       <c r="R3" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N3</f>
         <v>23</v>
       </c>
       <c r="S3" s="3">
         <v>7</v>
       </c>
       <c r="T3" s="3">
-        <f t="shared" si="5"/>
+        <f>+R3+S3-1</f>
         <v>29</v>
       </c>
       <c r="U3" s="3">
-        <f t="shared" si="6"/>
+        <f>+T3+1</f>
         <v>30</v>
       </c>
       <c r="V3" s="3">
         <v>2</v>
       </c>
       <c r="W3" s="3">
-        <f t="shared" si="7"/>
+        <f>+U3+V3-1</f>
         <v>31</v>
       </c>
       <c r="X3" s="3">
@@ -2029,7 +2040,7 @@
         <v>33</v>
       </c>
       <c r="AA3" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z3+AB3-1</f>
         <v>35</v>
       </c>
       <c r="AB3" s="3">
@@ -2045,21 +2056,21 @@
         <v>68</v>
       </c>
       <c r="AF3" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE3+AA3-1</f>
         <v>102</v>
       </c>
       <c r="AG3" s="6">
         <v>3</v>
       </c>
       <c r="AH3" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF3+AG3</f>
         <v>105</v>
       </c>
       <c r="AI3" s="3">
         <v>7</v>
       </c>
       <c r="AJ3" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI3+AH3</f>
         <v>112</v>
       </c>
       <c r="AK3" s="3" t="s">
@@ -2069,36 +2080,36 @@
         <v>2</v>
       </c>
       <c r="AM3" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ3+AL3</f>
         <v>114</v>
       </c>
       <c r="AN3" s="3">
         <v>2</v>
       </c>
       <c r="AO3" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM3+AN3</f>
         <v>116</v>
       </c>
       <c r="AP3" s="3">
         <v>3</v>
       </c>
       <c r="AQ3" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO3+AP3</f>
         <v>119</v>
       </c>
       <c r="AR3" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ3+7</f>
         <v>126</v>
       </c>
       <c r="AS3" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR3+7+AT3</f>
         <v>143</v>
       </c>
       <c r="AT3" s="3">
         <v>10</v>
       </c>
       <c r="AU3" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA3-R3</f>
         <v>12</v>
       </c>
       <c r="AV3" s="3" t="s">
@@ -2114,7 +2125,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>121</v>
       </c>
@@ -2152,44 +2163,44 @@
         <v>7</v>
       </c>
       <c r="M4" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I4="SFK Freight Forwarder",L4,9)</f>
         <v>9</v>
       </c>
       <c r="N4" s="3">
         <v>14</v>
       </c>
       <c r="O4" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I4="SFK Freight Forwarder",M4,M4+N4-1)</f>
         <v>22</v>
       </c>
       <c r="P4" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I4="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q4" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I4="SFK Freight Forwarder",O4,O4+P4-1)</f>
         <v>26</v>
       </c>
       <c r="R4" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N4</f>
         <v>23</v>
       </c>
       <c r="S4" s="3">
         <v>7</v>
       </c>
       <c r="T4" s="3">
-        <f t="shared" si="5"/>
+        <f>+R4+S4-1</f>
         <v>29</v>
       </c>
       <c r="U4" s="3">
-        <f t="shared" si="6"/>
+        <f>+T4+1</f>
         <v>30</v>
       </c>
       <c r="V4" s="3">
         <v>3</v>
       </c>
       <c r="W4" s="3">
-        <f t="shared" si="7"/>
+        <f>+U4+V4-1</f>
         <v>32</v>
       </c>
       <c r="X4" s="3">
@@ -2202,7 +2213,7 @@
         <v>33</v>
       </c>
       <c r="AA4" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z4+AB4-1</f>
         <v>35</v>
       </c>
       <c r="AB4" s="3">
@@ -2218,21 +2229,21 @@
         <v>75</v>
       </c>
       <c r="AF4" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE4+AA4-1</f>
         <v>109</v>
       </c>
       <c r="AG4" s="6">
         <v>3</v>
       </c>
       <c r="AH4" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF4+AG4</f>
         <v>112</v>
       </c>
       <c r="AI4" s="3">
         <v>7</v>
       </c>
       <c r="AJ4" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI4+AH4</f>
         <v>119</v>
       </c>
       <c r="AK4" s="3" t="s">
@@ -2242,36 +2253,36 @@
         <v>2</v>
       </c>
       <c r="AM4" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ4+AL4</f>
         <v>121</v>
       </c>
       <c r="AN4" s="3">
         <v>2</v>
       </c>
       <c r="AO4" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM4+AN4</f>
         <v>123</v>
       </c>
       <c r="AP4" s="3">
         <v>3</v>
       </c>
       <c r="AQ4" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO4+AP4</f>
         <v>126</v>
       </c>
       <c r="AR4" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ4+7</f>
         <v>133</v>
       </c>
       <c r="AS4" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR4+7+AT4</f>
         <v>150</v>
       </c>
       <c r="AT4" s="3">
         <v>10</v>
       </c>
       <c r="AU4" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA4-R4</f>
         <v>12</v>
       </c>
       <c r="AV4" s="3" t="s">
@@ -2287,7 +2298,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>233</v>
       </c>
@@ -2325,44 +2336,44 @@
         <v>7</v>
       </c>
       <c r="M5" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I5="SFK Freight Forwarder",L5,9)</f>
         <v>9</v>
       </c>
       <c r="N5" s="3">
         <v>7</v>
       </c>
       <c r="O5" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I5="SFK Freight Forwarder",M5,M5+N5-1)</f>
         <v>15</v>
       </c>
       <c r="P5" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I5="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q5" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I5="SFK Freight Forwarder",O5,O5+P5-1)</f>
         <v>19</v>
       </c>
       <c r="R5" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N5</f>
         <v>16</v>
       </c>
       <c r="S5" s="3">
         <v>7</v>
       </c>
       <c r="T5" s="3">
-        <f t="shared" si="5"/>
+        <f>+R5+S5-1</f>
         <v>22</v>
       </c>
       <c r="U5" s="3">
-        <f t="shared" si="6"/>
+        <f>+T5+1</f>
         <v>23</v>
       </c>
       <c r="V5" s="3">
         <v>2</v>
       </c>
       <c r="W5" s="3">
-        <f t="shared" si="7"/>
+        <f>+U5+V5-1</f>
         <v>24</v>
       </c>
       <c r="X5" s="3">
@@ -2375,7 +2386,7 @@
         <v>31</v>
       </c>
       <c r="AA5" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z5+AB5-1</f>
         <v>33</v>
       </c>
       <c r="AB5" s="3">
@@ -2391,21 +2402,21 @@
         <v>41</v>
       </c>
       <c r="AF5" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE5+AA5-1</f>
         <v>73</v>
       </c>
       <c r="AG5" s="6">
         <v>3</v>
       </c>
       <c r="AH5" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF5+AG5</f>
         <v>76</v>
       </c>
       <c r="AI5" s="3">
         <v>0</v>
       </c>
       <c r="AJ5" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI5+AH5</f>
         <v>76</v>
       </c>
       <c r="AK5" s="3" t="s">
@@ -2415,36 +2426,36 @@
         <v>2</v>
       </c>
       <c r="AM5" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ5+AL5</f>
         <v>78</v>
       </c>
       <c r="AN5" s="3">
         <v>2</v>
       </c>
       <c r="AO5" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM5+AN5</f>
         <v>80</v>
       </c>
       <c r="AP5" s="3">
         <v>4</v>
       </c>
       <c r="AQ5" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO5+AP5</f>
         <v>84</v>
       </c>
       <c r="AR5" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ5+7</f>
         <v>91</v>
       </c>
       <c r="AS5" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR5+7+AT5</f>
         <v>104</v>
       </c>
       <c r="AT5" s="3">
         <v>6</v>
       </c>
       <c r="AU5" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA5-R5</f>
         <v>17</v>
       </c>
       <c r="AV5" s="3" t="s">
@@ -2460,7 +2471,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>416</v>
       </c>
@@ -2498,44 +2509,44 @@
         <v>7</v>
       </c>
       <c r="M6" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I6="SFK Freight Forwarder",L6,9)</f>
         <v>9</v>
       </c>
       <c r="N6" s="3">
         <v>7</v>
       </c>
       <c r="O6" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I6="SFK Freight Forwarder",M6,M6+N6-1)</f>
         <v>15</v>
       </c>
       <c r="P6" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I6="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q6" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I6="SFK Freight Forwarder",O6,O6+P6-1)</f>
         <v>19</v>
       </c>
       <c r="R6" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N6</f>
         <v>16</v>
       </c>
       <c r="S6" s="3">
         <v>7</v>
       </c>
       <c r="T6" s="3">
-        <f t="shared" si="5"/>
+        <f>+R6+S6-1</f>
         <v>22</v>
       </c>
       <c r="U6" s="3">
-        <f t="shared" si="6"/>
+        <f>+T6+1</f>
         <v>23</v>
       </c>
       <c r="V6" s="3">
         <v>4</v>
       </c>
       <c r="W6" s="3">
-        <f t="shared" si="7"/>
+        <f>+U6+V6-1</f>
         <v>26</v>
       </c>
       <c r="X6" s="3">
@@ -2548,7 +2559,7 @@
         <v>30</v>
       </c>
       <c r="AA6" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z6+AB6-1</f>
         <v>32</v>
       </c>
       <c r="AB6" s="3">
@@ -2564,21 +2575,21 @@
         <v>46</v>
       </c>
       <c r="AF6" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE6+AA6-1</f>
         <v>77</v>
       </c>
       <c r="AG6" s="6">
         <v>3</v>
       </c>
       <c r="AH6" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF6+AG6</f>
         <v>80</v>
       </c>
       <c r="AI6" s="3">
         <v>0</v>
       </c>
       <c r="AJ6" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI6+AH6</f>
         <v>80</v>
       </c>
       <c r="AK6" s="3" t="s">
@@ -2588,36 +2599,36 @@
         <v>4</v>
       </c>
       <c r="AM6" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ6+AL6</f>
         <v>84</v>
       </c>
       <c r="AN6" s="3">
         <v>3</v>
       </c>
       <c r="AO6" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM6+AN6</f>
         <v>87</v>
       </c>
       <c r="AP6" s="3">
         <v>4</v>
       </c>
       <c r="AQ6" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO6+AP6</f>
         <v>91</v>
       </c>
       <c r="AR6" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ6+7</f>
         <v>98</v>
       </c>
       <c r="AS6" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR6+7+AT6</f>
         <v>112</v>
       </c>
       <c r="AT6" s="3">
         <v>7</v>
       </c>
       <c r="AU6" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA6-R6</f>
         <v>16</v>
       </c>
       <c r="AV6" s="3" t="s">
@@ -2633,7 +2644,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>752</v>
       </c>
@@ -2680,11 +2691,11 @@
         <v>0</v>
       </c>
       <c r="P7" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I7="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q7" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I7="SFK Freight Forwarder",O7,O7+P7-1)</f>
         <v>0</v>
       </c>
       <c r="R7" s="3">
@@ -2694,18 +2705,18 @@
         <v>7</v>
       </c>
       <c r="T7" s="3">
-        <f t="shared" si="5"/>
+        <f>+R7+S7-1</f>
         <v>22</v>
       </c>
       <c r="U7" s="3">
-        <f t="shared" si="6"/>
+        <f>+T7+1</f>
         <v>23</v>
       </c>
       <c r="V7" s="3">
         <v>8</v>
       </c>
       <c r="W7" s="3">
-        <f t="shared" si="7"/>
+        <f>+U7+V7-1</f>
         <v>30</v>
       </c>
       <c r="X7" s="3">
@@ -2719,7 +2730,7 @@
         <v>33</v>
       </c>
       <c r="AA7" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z7+AB7-1</f>
         <v>35</v>
       </c>
       <c r="AB7" s="3">
@@ -2735,21 +2746,21 @@
         <v>43</v>
       </c>
       <c r="AF7" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE7+AA7-1</f>
         <v>77</v>
       </c>
       <c r="AG7" s="6">
         <v>3</v>
       </c>
       <c r="AH7" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF7+AG7</f>
         <v>80</v>
       </c>
       <c r="AI7" s="3">
         <v>0</v>
       </c>
       <c r="AJ7" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI7+AH7</f>
         <v>80</v>
       </c>
       <c r="AK7" s="3" t="s">
@@ -2759,36 +2770,36 @@
         <v>2</v>
       </c>
       <c r="AM7" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ7+AL7</f>
         <v>82</v>
       </c>
       <c r="AN7" s="3">
         <v>2</v>
       </c>
       <c r="AO7" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM7+AN7</f>
         <v>84</v>
       </c>
       <c r="AP7" s="3">
         <v>0</v>
       </c>
       <c r="AQ7" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO7+AP7</f>
         <v>84</v>
       </c>
       <c r="AR7" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ7+7</f>
         <v>91</v>
       </c>
       <c r="AS7" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR7+7+AT7</f>
         <v>98</v>
       </c>
       <c r="AT7" s="3">
         <v>0</v>
       </c>
       <c r="AU7" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA7-R7</f>
         <v>19</v>
       </c>
       <c r="AV7" s="3" t="s">
@@ -2804,7 +2815,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>761</v>
       </c>
@@ -2848,15 +2859,15 @@
         <v>0</v>
       </c>
       <c r="O8" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I8="SFK Freight Forwarder",M8,M8+N8-1)</f>
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I8="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q8" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I8="SFK Freight Forwarder",O8,O8+P8-1)</f>
         <v>0</v>
       </c>
       <c r="R8" s="3">
@@ -2866,18 +2877,18 @@
         <v>7</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" si="5"/>
+        <f>+R8+S8-1</f>
         <v>22</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" si="6"/>
+        <f>+T8+1</f>
         <v>23</v>
       </c>
       <c r="V8" s="3">
         <v>8</v>
       </c>
       <c r="W8" s="3">
-        <f t="shared" si="7"/>
+        <f>+U8+V8-1</f>
         <v>30</v>
       </c>
       <c r="X8" s="3">
@@ -2905,21 +2916,21 @@
         <v>38</v>
       </c>
       <c r="AF8" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE8+AA8-1</f>
         <v>72</v>
       </c>
       <c r="AG8" s="6">
         <v>3</v>
       </c>
       <c r="AH8" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF8+AG8</f>
         <v>75</v>
       </c>
       <c r="AI8" s="3">
         <v>7</v>
       </c>
       <c r="AJ8" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI8+AH8</f>
         <v>82</v>
       </c>
       <c r="AK8" s="3" t="s">
@@ -2929,36 +2940,36 @@
         <v>3</v>
       </c>
       <c r="AM8" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ8+AL8</f>
         <v>85</v>
       </c>
       <c r="AN8" s="3">
         <v>6</v>
       </c>
       <c r="AO8" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM8+AN8</f>
         <v>91</v>
       </c>
       <c r="AP8" s="3">
         <v>0</v>
       </c>
       <c r="AQ8" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO8+AP8</f>
         <v>91</v>
       </c>
       <c r="AR8" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ8+7</f>
         <v>98</v>
       </c>
       <c r="AS8" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR8+7+AT8</f>
         <v>105</v>
       </c>
       <c r="AT8" s="3">
         <v>0</v>
       </c>
       <c r="AU8" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA8-R8</f>
         <v>19</v>
       </c>
       <c r="AV8" s="3" t="s">
@@ -2974,7 +2985,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>888</v>
       </c>
@@ -3018,37 +3029,37 @@
         <v>7</v>
       </c>
       <c r="O9" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I9="SFK Freight Forwarder",M9,M9+N9-1)</f>
         <v>0</v>
       </c>
       <c r="P9" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I9="SFK Freight Forwarder",0,5)</f>
         <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I9="SFK Freight Forwarder",O9,O9+P9-1)</f>
         <v>0</v>
       </c>
       <c r="R9" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N9</f>
         <v>16</v>
       </c>
       <c r="S9" s="3">
         <v>7</v>
       </c>
       <c r="T9" s="3">
-        <f t="shared" si="5"/>
+        <f>+R9+S9-1</f>
         <v>22</v>
       </c>
       <c r="U9" s="3">
-        <f t="shared" si="6"/>
+        <f>+T9+1</f>
         <v>23</v>
       </c>
       <c r="V9" s="3">
         <v>8</v>
       </c>
       <c r="W9" s="3">
-        <f t="shared" si="7"/>
+        <f>+U9+V9-1</f>
         <v>30</v>
       </c>
       <c r="X9" s="3">
@@ -3061,7 +3072,7 @@
         <v>36</v>
       </c>
       <c r="AA9" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z9+AB9-1</f>
         <v>38</v>
       </c>
       <c r="AB9" s="3">
@@ -3077,21 +3088,21 @@
         <v>16</v>
       </c>
       <c r="AF9" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE9+AA9-1</f>
         <v>53</v>
       </c>
       <c r="AG9" s="6">
         <v>3</v>
       </c>
       <c r="AH9" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF9+AG9</f>
         <v>56</v>
       </c>
       <c r="AI9" s="3">
         <v>7</v>
       </c>
       <c r="AJ9" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI9+AH9</f>
         <v>63</v>
       </c>
       <c r="AK9" s="3" t="s">
@@ -3101,36 +3112,36 @@
         <v>4</v>
       </c>
       <c r="AM9" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ9+AL9</f>
         <v>67</v>
       </c>
       <c r="AN9" s="3">
         <v>3</v>
       </c>
       <c r="AO9" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM9+AN9</f>
         <v>70</v>
       </c>
       <c r="AP9" s="3">
         <v>0</v>
       </c>
       <c r="AQ9" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO9+AP9</f>
         <v>70</v>
       </c>
       <c r="AR9" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ9+7</f>
         <v>77</v>
       </c>
       <c r="AS9" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR9+7+AT9</f>
         <v>84</v>
       </c>
       <c r="AT9" s="3">
         <v>0</v>
       </c>
       <c r="AU9" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA9-R9</f>
         <v>22</v>
       </c>
       <c r="AV9" s="3" t="s">
@@ -3146,7 +3157,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>901</v>
       </c>
@@ -3184,44 +3195,44 @@
         <v>7</v>
       </c>
       <c r="M10" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I10="SFK Freight Forwarder",L10,9)</f>
         <v>9</v>
       </c>
       <c r="N10" s="3">
         <v>7</v>
       </c>
       <c r="O10" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I10="SFK Freight Forwarder",M10,M10+N10-1)</f>
         <v>15</v>
       </c>
       <c r="P10" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I10="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q10" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I10="SFK Freight Forwarder",O10,O10+P10-1)</f>
         <v>19</v>
       </c>
       <c r="R10" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N10</f>
         <v>16</v>
       </c>
       <c r="S10" s="3">
         <v>7</v>
       </c>
       <c r="T10" s="3">
-        <f t="shared" si="5"/>
+        <f>+R10+S10-1</f>
         <v>22</v>
       </c>
       <c r="U10" s="3">
-        <f t="shared" si="6"/>
+        <f>+T10+1</f>
         <v>23</v>
       </c>
       <c r="V10" s="3">
         <v>4</v>
       </c>
       <c r="W10" s="3">
-        <f t="shared" si="7"/>
+        <f>+U10+V10-1</f>
         <v>26</v>
       </c>
       <c r="X10" s="3">
@@ -3234,7 +3245,7 @@
         <v>30</v>
       </c>
       <c r="AA10" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z10+AB10-1</f>
         <v>32</v>
       </c>
       <c r="AB10" s="3">
@@ -3250,21 +3261,21 @@
         <v>49</v>
       </c>
       <c r="AF10" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE10+AA10-1</f>
         <v>80</v>
       </c>
       <c r="AG10" s="6">
         <v>3</v>
       </c>
       <c r="AH10" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF10+AG10</f>
         <v>83</v>
       </c>
       <c r="AI10" s="3">
         <v>0</v>
       </c>
       <c r="AJ10" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI10+AH10</f>
         <v>83</v>
       </c>
       <c r="AK10" s="3" t="s">
@@ -3274,36 +3285,36 @@
         <v>1</v>
       </c>
       <c r="AM10" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ10+AL10</f>
         <v>84</v>
       </c>
       <c r="AN10" s="3">
         <v>8</v>
       </c>
       <c r="AO10" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM10+AN10</f>
         <v>92</v>
       </c>
       <c r="AP10" s="3">
         <v>6</v>
       </c>
       <c r="AQ10" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO10+AP10</f>
         <v>98</v>
       </c>
       <c r="AR10" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ10+7</f>
         <v>105</v>
       </c>
       <c r="AS10" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR10+7+AT10</f>
         <v>119</v>
       </c>
       <c r="AT10" s="3">
         <v>7</v>
       </c>
       <c r="AU10" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA10-R10</f>
         <v>16</v>
       </c>
       <c r="AV10" s="3" t="s">
@@ -3319,7 +3330,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>904</v>
       </c>
@@ -3357,44 +3368,44 @@
         <v>2</v>
       </c>
       <c r="M11" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I11="SFK Freight Forwarder",L11,9)</f>
         <v>9</v>
       </c>
       <c r="N11" s="3">
         <v>14</v>
       </c>
       <c r="O11" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I11="SFK Freight Forwarder",M11,M11+N11-1)</f>
         <v>22</v>
       </c>
       <c r="P11" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I11="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q11" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I11="SFK Freight Forwarder",O11,O11+P11-1)</f>
         <v>26</v>
       </c>
       <c r="R11" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N11</f>
         <v>23</v>
       </c>
       <c r="S11" s="3">
         <v>7</v>
       </c>
       <c r="T11" s="3">
-        <f t="shared" si="5"/>
+        <f>+R11+S11-1</f>
         <v>29</v>
       </c>
       <c r="U11" s="3">
-        <f t="shared" si="6"/>
+        <f>+T11+1</f>
         <v>30</v>
       </c>
       <c r="V11" s="3">
         <v>1</v>
       </c>
       <c r="W11" s="3">
-        <f t="shared" si="7"/>
+        <f>+U11+V11-1</f>
         <v>30</v>
       </c>
       <c r="X11" s="3">
@@ -3407,7 +3418,7 @@
         <v>37</v>
       </c>
       <c r="AA11" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z11+AB11-1</f>
         <v>39</v>
       </c>
       <c r="AB11" s="3">
@@ -3423,21 +3434,21 @@
         <v>57</v>
       </c>
       <c r="AF11" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE11+AA11-1</f>
         <v>95</v>
       </c>
       <c r="AG11" s="6">
         <v>3</v>
       </c>
       <c r="AH11" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF11+AG11</f>
         <v>98</v>
       </c>
       <c r="AI11" s="3">
         <v>14</v>
       </c>
       <c r="AJ11" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI11+AH11</f>
         <v>112</v>
       </c>
       <c r="AK11" s="3" t="s">
@@ -3447,36 +3458,36 @@
         <v>4</v>
       </c>
       <c r="AM11" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ11+AL11</f>
         <v>116</v>
       </c>
       <c r="AN11" s="3">
         <v>3</v>
       </c>
       <c r="AO11" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM11+AN11</f>
         <v>119</v>
       </c>
       <c r="AP11" s="3">
         <v>0</v>
       </c>
       <c r="AQ11" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO11+AP11</f>
         <v>119</v>
       </c>
       <c r="AR11" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ11+7</f>
         <v>126</v>
       </c>
       <c r="AS11" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR11+7+AT11</f>
         <v>147</v>
       </c>
       <c r="AT11" s="3">
         <v>14</v>
       </c>
       <c r="AU11" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA11-R11</f>
         <v>16</v>
       </c>
       <c r="AV11" s="3" t="s">
@@ -3492,7 +3503,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>906</v>
       </c>
@@ -3530,44 +3541,44 @@
         <v>7</v>
       </c>
       <c r="M12" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I12="SFK Freight Forwarder",L12,9)</f>
         <v>9</v>
       </c>
       <c r="N12" s="3">
         <v>14</v>
       </c>
       <c r="O12" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I12="SFK Freight Forwarder",M12,M12+N12-1)</f>
         <v>22</v>
       </c>
       <c r="P12" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I12="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q12" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I12="SFK Freight Forwarder",O12,O12+P12-1)</f>
         <v>26</v>
       </c>
       <c r="R12" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N12</f>
         <v>23</v>
       </c>
       <c r="S12" s="3">
         <v>7</v>
       </c>
       <c r="T12" s="3">
-        <f t="shared" si="5"/>
+        <f>+R12+S12-1</f>
         <v>29</v>
       </c>
       <c r="U12" s="3">
-        <f t="shared" si="6"/>
+        <f>+T12+1</f>
         <v>30</v>
       </c>
       <c r="V12" s="3">
         <v>1</v>
       </c>
       <c r="W12" s="3">
-        <f t="shared" si="7"/>
+        <f>+U12+V12-1</f>
         <v>30</v>
       </c>
       <c r="X12" s="3">
@@ -3580,7 +3591,7 @@
         <v>37</v>
       </c>
       <c r="AA12" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z12+AB12-1</f>
         <v>38</v>
       </c>
       <c r="AB12" s="3">
@@ -3596,21 +3607,21 @@
         <v>47</v>
       </c>
       <c r="AF12" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE12+AA12-1</f>
         <v>84</v>
       </c>
       <c r="AG12" s="6">
         <v>3</v>
       </c>
       <c r="AH12" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF12+AG12</f>
         <v>87</v>
       </c>
       <c r="AI12" s="3">
         <v>14</v>
       </c>
       <c r="AJ12" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI12+AH12</f>
         <v>101</v>
       </c>
       <c r="AK12" s="3" t="s">
@@ -3620,36 +3631,36 @@
         <v>2</v>
       </c>
       <c r="AM12" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ12+AL12</f>
         <v>103</v>
       </c>
       <c r="AN12" s="3">
         <v>2</v>
       </c>
       <c r="AO12" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM12+AN12</f>
         <v>105</v>
       </c>
       <c r="AP12" s="3">
         <v>0</v>
       </c>
       <c r="AQ12" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO12+AP12</f>
         <v>105</v>
       </c>
       <c r="AR12" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ12+7</f>
         <v>112</v>
       </c>
       <c r="AS12" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR12+7+AT12</f>
         <v>134</v>
       </c>
       <c r="AT12" s="3">
         <v>15</v>
       </c>
       <c r="AU12" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA12-R12</f>
         <v>15</v>
       </c>
       <c r="AV12" s="3" t="s">
@@ -3665,7 +3676,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>907</v>
       </c>
@@ -3703,44 +3714,44 @@
         <v>7</v>
       </c>
       <c r="M13" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I13="SFK Freight Forwarder",L13,9)</f>
         <v>9</v>
       </c>
       <c r="N13" s="3">
         <v>7</v>
       </c>
       <c r="O13" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I13="SFK Freight Forwarder",M13,M13+N13-1)</f>
         <v>15</v>
       </c>
       <c r="P13" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I13="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q13" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I13="SFK Freight Forwarder",O13,O13+P13-1)</f>
         <v>19</v>
       </c>
       <c r="R13" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N13</f>
         <v>16</v>
       </c>
       <c r="S13" s="3">
         <v>7</v>
       </c>
       <c r="T13" s="3">
-        <f t="shared" si="5"/>
+        <f>+R13+S13-1</f>
         <v>22</v>
       </c>
       <c r="U13" s="3">
-        <f t="shared" si="6"/>
+        <f>+T13+1</f>
         <v>23</v>
       </c>
       <c r="V13" s="3">
         <v>1</v>
       </c>
       <c r="W13" s="3">
-        <f t="shared" si="7"/>
+        <f>+U13+V13-1</f>
         <v>23</v>
       </c>
       <c r="X13" s="3">
@@ -3753,7 +3764,7 @@
         <v>31</v>
       </c>
       <c r="AA13" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z13+AB13-1</f>
         <v>34</v>
       </c>
       <c r="AB13" s="3">
@@ -3769,21 +3780,21 @@
         <v>40</v>
       </c>
       <c r="AF13" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE13+AA13-1</f>
         <v>73</v>
       </c>
       <c r="AG13" s="6">
         <v>3</v>
       </c>
       <c r="AH13" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF13+AG13</f>
         <v>76</v>
       </c>
       <c r="AI13" s="3">
         <v>0</v>
       </c>
       <c r="AJ13" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI13+AH13</f>
         <v>76</v>
       </c>
       <c r="AK13" s="3" t="s">
@@ -3793,36 +3804,36 @@
         <v>2</v>
       </c>
       <c r="AM13" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ13+AL13</f>
         <v>78</v>
       </c>
       <c r="AN13" s="3">
         <v>2</v>
       </c>
       <c r="AO13" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM13+AN13</f>
         <v>80</v>
       </c>
       <c r="AP13" s="3">
         <v>4</v>
       </c>
       <c r="AQ13" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO13+AP13</f>
         <v>84</v>
       </c>
       <c r="AR13" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ13+7</f>
         <v>91</v>
       </c>
       <c r="AS13" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR13+7+AT13</f>
         <v>112</v>
       </c>
       <c r="AT13" s="3">
         <v>14</v>
       </c>
       <c r="AU13" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA13-R13</f>
         <v>18</v>
       </c>
       <c r="AV13" s="3" t="s">
@@ -3838,7 +3849,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>908</v>
       </c>
@@ -3876,44 +3887,44 @@
         <v>7</v>
       </c>
       <c r="M14" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I14="SFK Freight Forwarder",L14,9)</f>
         <v>9</v>
       </c>
       <c r="N14" s="3">
         <v>14</v>
       </c>
       <c r="O14" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I14="SFK Freight Forwarder",M14,M14+N14-1)</f>
         <v>22</v>
       </c>
       <c r="P14" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I14="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q14" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I14="SFK Freight Forwarder",O14,O14+P14-1)</f>
         <v>26</v>
       </c>
       <c r="R14" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N14</f>
         <v>23</v>
       </c>
       <c r="S14" s="3">
         <v>7</v>
       </c>
       <c r="T14" s="3">
-        <f t="shared" si="5"/>
+        <f>+R14+S14-1</f>
         <v>29</v>
       </c>
       <c r="U14" s="3">
-        <f t="shared" si="6"/>
+        <f>+T14+1</f>
         <v>30</v>
       </c>
       <c r="V14" s="3">
         <v>4</v>
       </c>
       <c r="W14" s="3">
-        <f t="shared" si="7"/>
+        <f>+U14+V14-1</f>
         <v>33</v>
       </c>
       <c r="X14" s="3">
@@ -3926,7 +3937,7 @@
         <v>36</v>
       </c>
       <c r="AA14" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z14+AB14-1</f>
         <v>37</v>
       </c>
       <c r="AB14" s="3">
@@ -3942,21 +3953,21 @@
         <v>37</v>
       </c>
       <c r="AF14" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE14+AA14-1</f>
         <v>73</v>
       </c>
       <c r="AG14" s="6">
         <v>3</v>
       </c>
       <c r="AH14" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF14+AG14</f>
         <v>76</v>
       </c>
       <c r="AI14" s="3">
         <v>7</v>
       </c>
       <c r="AJ14" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI14+AH14</f>
         <v>83</v>
       </c>
       <c r="AK14" s="28" t="s">
@@ -3966,36 +3977,36 @@
         <v>2</v>
       </c>
       <c r="AM14" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ14+AL14</f>
         <v>85</v>
       </c>
       <c r="AN14" s="3">
         <v>2</v>
       </c>
       <c r="AO14" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM14+AN14</f>
         <v>87</v>
       </c>
       <c r="AP14" s="3">
         <v>4</v>
       </c>
       <c r="AQ14" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO14+AP14</f>
         <v>91</v>
       </c>
       <c r="AR14" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ14+7</f>
         <v>98</v>
       </c>
       <c r="AS14" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR14+7+AT14</f>
         <v>121</v>
       </c>
       <c r="AT14" s="3">
         <v>16</v>
       </c>
       <c r="AU14" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA14-R14</f>
         <v>14</v>
       </c>
       <c r="AV14" s="3" t="s">
@@ -4011,7 +4022,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>910</v>
       </c>
@@ -4049,44 +4060,44 @@
         <v>7</v>
       </c>
       <c r="M15" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I15="SFK Freight Forwarder",L15,9)</f>
         <v>9</v>
       </c>
       <c r="N15" s="3">
         <v>14</v>
       </c>
       <c r="O15" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I15="SFK Freight Forwarder",M15,M15+N15-1)</f>
         <v>22</v>
       </c>
       <c r="P15" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I15="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q15" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I15="SFK Freight Forwarder",O15,O15+P15-1)</f>
         <v>26</v>
       </c>
       <c r="R15" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N15</f>
         <v>23</v>
       </c>
       <c r="S15" s="3">
         <v>7</v>
       </c>
       <c r="T15" s="3">
-        <f t="shared" si="5"/>
+        <f>+R15+S15-1</f>
         <v>29</v>
       </c>
       <c r="U15" s="3">
-        <f t="shared" si="6"/>
+        <f>+T15+1</f>
         <v>30</v>
       </c>
       <c r="V15" s="3">
         <v>1</v>
       </c>
       <c r="W15" s="3">
-        <f t="shared" si="7"/>
+        <f>+U15+V15-1</f>
         <v>30</v>
       </c>
       <c r="X15" s="3">
@@ -4100,7 +4111,7 @@
         <v>37</v>
       </c>
       <c r="AA15" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z15+AB15-1</f>
         <v>39</v>
       </c>
       <c r="AB15" s="3">
@@ -4116,21 +4127,21 @@
         <v>26</v>
       </c>
       <c r="AF15" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE15+AA15-1</f>
         <v>64</v>
       </c>
       <c r="AG15" s="6">
         <v>3</v>
       </c>
       <c r="AH15" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF15+AG15</f>
         <v>67</v>
       </c>
       <c r="AI15" s="3">
         <v>7</v>
       </c>
       <c r="AJ15" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI15+AH15</f>
         <v>74</v>
       </c>
       <c r="AK15" s="3" t="s">
@@ -4140,36 +4151,36 @@
         <v>2</v>
       </c>
       <c r="AM15" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ15+AL15</f>
         <v>76</v>
       </c>
       <c r="AN15" s="3">
         <v>2</v>
       </c>
       <c r="AO15" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM15+AN15</f>
         <v>78</v>
       </c>
       <c r="AP15" s="3">
         <v>6</v>
       </c>
       <c r="AQ15" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO15+AP15</f>
         <v>84</v>
       </c>
       <c r="AR15" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ15+7</f>
         <v>91</v>
       </c>
       <c r="AS15" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR15+7+AT15</f>
         <v>112</v>
       </c>
       <c r="AT15" s="3">
         <v>14</v>
       </c>
       <c r="AU15" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA15-R15</f>
         <v>16</v>
       </c>
       <c r="AV15" s="3" t="s">
@@ -4185,7 +4196,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>912</v>
       </c>
@@ -4223,44 +4234,44 @@
         <v>7</v>
       </c>
       <c r="M16" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I16="SFK Freight Forwarder",L16,9)</f>
         <v>9</v>
       </c>
       <c r="N16" s="3">
         <v>14</v>
       </c>
       <c r="O16" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I16="SFK Freight Forwarder",M16,M16+N16-1)</f>
         <v>22</v>
       </c>
       <c r="P16" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I16="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q16" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I16="SFK Freight Forwarder",O16,O16+P16-1)</f>
         <v>26</v>
       </c>
       <c r="R16" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N16</f>
         <v>23</v>
       </c>
       <c r="S16" s="3">
         <v>7</v>
       </c>
       <c r="T16" s="3">
-        <f t="shared" si="5"/>
+        <f>+R16+S16-1</f>
         <v>29</v>
       </c>
       <c r="U16" s="3">
-        <f t="shared" si="6"/>
+        <f>+T16+1</f>
         <v>30</v>
       </c>
       <c r="V16" s="3">
         <v>4</v>
       </c>
       <c r="W16" s="3">
-        <f t="shared" si="7"/>
+        <f>+U16+V16-1</f>
         <v>33</v>
       </c>
       <c r="X16" s="3">
@@ -4273,7 +4284,7 @@
         <v>33</v>
       </c>
       <c r="AA16" s="6">
-        <f t="shared" si="8"/>
+        <f>+Z16+AB16-1</f>
         <v>35</v>
       </c>
       <c r="AB16" s="3">
@@ -4289,21 +4300,21 @@
         <v>44</v>
       </c>
       <c r="AF16" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE16+AA16-1</f>
         <v>78</v>
       </c>
       <c r="AG16" s="6">
         <v>3</v>
       </c>
       <c r="AH16" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF16+AG16</f>
         <v>81</v>
       </c>
       <c r="AI16" s="3">
         <v>7</v>
       </c>
       <c r="AJ16" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI16+AH16</f>
         <v>88</v>
       </c>
       <c r="AK16" s="3" t="s">
@@ -4313,36 +4324,36 @@
         <v>2</v>
       </c>
       <c r="AM16" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ16+AL16</f>
         <v>90</v>
       </c>
       <c r="AN16" s="3">
         <v>2</v>
       </c>
       <c r="AO16" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM16+AN16</f>
         <v>92</v>
       </c>
       <c r="AP16" s="3">
         <v>6</v>
       </c>
       <c r="AQ16" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO16+AP16</f>
         <v>98</v>
       </c>
       <c r="AR16" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ16+7</f>
         <v>105</v>
       </c>
       <c r="AS16" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR16+7+AT16</f>
         <v>121</v>
       </c>
       <c r="AT16" s="3">
         <v>9</v>
       </c>
       <c r="AU16" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA16-R16</f>
         <v>12</v>
       </c>
       <c r="AV16" s="3" t="s">
@@ -4358,7 +4369,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -4396,44 +4407,44 @@
         <v>7</v>
       </c>
       <c r="M17" s="3">
-        <f t="shared" si="0"/>
+        <f>+IF(I17="SFK Freight Forwarder",L17,9)</f>
         <v>9</v>
       </c>
       <c r="N17" s="3">
         <v>14</v>
       </c>
       <c r="O17" s="3">
-        <f t="shared" si="1"/>
+        <f>IF(I17="SFK Freight Forwarder",M17,M17+N17-1)</f>
         <v>22</v>
       </c>
       <c r="P17" s="3">
-        <f t="shared" si="2"/>
+        <f>+IF(I17="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q17" s="3">
-        <f t="shared" si="3"/>
+        <f>+IF(I17="SFK Freight Forwarder",O17,O17+P17-1)</f>
         <v>26</v>
       </c>
       <c r="R17" s="3">
-        <f t="shared" si="4"/>
+        <f>9+N17</f>
         <v>23</v>
       </c>
       <c r="S17" s="3">
         <v>7</v>
       </c>
       <c r="T17" s="3">
-        <f t="shared" si="5"/>
+        <f>+R17+S17-1</f>
         <v>29</v>
       </c>
       <c r="U17" s="3">
-        <f t="shared" si="6"/>
+        <f>+T17+1</f>
         <v>30</v>
       </c>
       <c r="V17" s="3">
         <v>2</v>
       </c>
       <c r="W17" s="3">
-        <f t="shared" si="7"/>
+        <f>+U17+V17-1</f>
         <v>31</v>
       </c>
       <c r="X17" s="3">
@@ -4461,21 +4472,21 @@
         <v>43</v>
       </c>
       <c r="AF17" s="3">
-        <f t="shared" si="9"/>
+        <f>+AE17+AA17-1</f>
         <v>80</v>
       </c>
       <c r="AG17" s="6">
         <v>3</v>
       </c>
       <c r="AH17" s="6">
-        <f t="shared" si="10"/>
+        <f>+AF17+AG17</f>
         <v>83</v>
       </c>
       <c r="AI17" s="3">
         <v>14</v>
       </c>
       <c r="AJ17" s="3">
-        <f t="shared" si="11"/>
+        <f>+AI17+AH17</f>
         <v>97</v>
       </c>
       <c r="AK17" s="3" t="s">
@@ -4485,36 +4496,36 @@
         <v>1</v>
       </c>
       <c r="AM17" s="3">
-        <f t="shared" si="12"/>
+        <f>+AJ17+AL17</f>
         <v>98</v>
       </c>
       <c r="AN17" s="3">
         <v>8</v>
       </c>
       <c r="AO17" s="3">
-        <f t="shared" si="13"/>
+        <f>+AM17+AN17</f>
         <v>106</v>
       </c>
       <c r="AP17" s="3">
         <v>6</v>
       </c>
       <c r="AQ17" s="3">
-        <f t="shared" si="14"/>
+        <f>+AO17+AP17</f>
         <v>112</v>
       </c>
       <c r="AR17" s="3">
-        <f t="shared" si="15"/>
+        <f>+AQ17+7</f>
         <v>119</v>
       </c>
       <c r="AS17" s="3">
-        <f t="shared" si="16"/>
+        <f>+AR17+7+AT17</f>
         <v>139</v>
       </c>
       <c r="AT17" s="3">
         <v>13</v>
       </c>
       <c r="AU17" s="3">
-        <f t="shared" si="17"/>
+        <f>+AA17-R17</f>
         <v>15</v>
       </c>
       <c r="AV17" s="3" t="s">
@@ -4530,170 +4541,180 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B18" s="5" t="s">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>916</v>
+      </c>
+      <c r="B18" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" s="32" t="s">
+      <c r="C18" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F18" s="19">
-        <v>90016500</v>
-      </c>
-      <c r="G18" s="23" t="s">
-        <v>159</v>
+        <v>91017700</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="H18" s="2">
-        <v>0</v>
+        <v>95207</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="J18" s="2">
-        <v>29159</v>
-      </c>
-      <c r="K18" s="23" t="s">
-        <v>137</v>
+        <v>95207</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="L18" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M18" s="3">
-        <v>8</v>
-      </c>
-      <c r="N18" s="23">
-        <v>1</v>
+        <f>+IF(I18="SFK Freight Forwarder",L18,9)</f>
+        <v>9</v>
+      </c>
+      <c r="N18" s="3">
+        <v>7</v>
       </c>
       <c r="O18" s="3">
         <f>IF(I18="SFK Freight Forwarder",M18,M18+N18-1)</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P18" s="3">
-        <v>6</v>
+        <f>+IF(I18="SFK Freight Forwarder",0,5)</f>
+        <v>5</v>
       </c>
       <c r="Q18" s="3">
         <f>+IF(I18="SFK Freight Forwarder",O18,O18+P18-1)</f>
-        <v>13</v>
-      </c>
-      <c r="R18" s="23">
-        <v>9</v>
-      </c>
-      <c r="S18" s="23">
-        <v>12</v>
-      </c>
-      <c r="T18" s="23">
+        <v>19</v>
+      </c>
+      <c r="R18" s="3">
+        <f>9+N18</f>
+        <v>16</v>
+      </c>
+      <c r="S18" s="3">
+        <v>7</v>
+      </c>
+      <c r="T18" s="3">
         <f>+R18+S18-1</f>
-        <v>20</v>
-      </c>
-      <c r="U18" s="23">
-        <f>+T18+2</f>
         <v>22</v>
       </c>
-      <c r="V18" s="23">
-        <v>5</v>
-      </c>
-      <c r="W18" s="23">
+      <c r="U18" s="3">
+        <f>+T18+1</f>
+        <v>23</v>
+      </c>
+      <c r="V18" s="3">
+        <v>4</v>
+      </c>
+      <c r="W18" s="3">
         <f>+U18+V18-1</f>
         <v>26</v>
       </c>
-      <c r="X18" s="23">
-        <v>4</v>
+      <c r="X18" s="3">
+        <v>0</v>
       </c>
       <c r="Y18" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Z18" s="6">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="AA18" s="6">
-        <v>36</v>
-      </c>
-      <c r="AB18" s="23">
-        <v>4</v>
-      </c>
-      <c r="AC18" s="23"/>
-      <c r="AD18" s="23"/>
-      <c r="AE18" s="33">
-        <v>34</v>
-      </c>
-      <c r="AF18" s="23">
+        <f>+Z18+AB18-1</f>
+        <v>33</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>12</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>27</v>
+      </c>
+      <c r="AF18" s="3">
         <f>+AE18+AA18-1</f>
+        <v>59</v>
+      </c>
+      <c r="AG18" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH18" s="6">
+        <f>+AF18+AG18</f>
+        <v>62</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>7</v>
+      </c>
+      <c r="AJ18" s="3">
+        <f>+AI18+AH18</f>
         <v>69</v>
       </c>
-      <c r="AG18" s="23">
-        <v>3</v>
-      </c>
-      <c r="AH18" s="23">
-        <f>+AF18+AG18</f>
-        <v>72</v>
-      </c>
-      <c r="AI18" s="23">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="23">
-        <f>+AI18+AH18</f>
-        <v>72</v>
-      </c>
-      <c r="AK18" s="23"/>
-      <c r="AL18" s="23">
+      <c r="AK18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL18" s="3">
         <v>2</v>
       </c>
-      <c r="AM18" s="23">
+      <c r="AM18" s="3">
         <f>+AJ18+AL18</f>
-        <v>74</v>
-      </c>
-      <c r="AN18" s="23">
-        <v>1</v>
-      </c>
-      <c r="AO18" s="23">
+        <v>71</v>
+      </c>
+      <c r="AN18" s="3">
+        <v>8</v>
+      </c>
+      <c r="AO18" s="3">
         <f>+AM18+AN18</f>
-        <v>75</v>
-      </c>
-      <c r="AP18" s="23">
-        <v>3</v>
+        <v>79</v>
+      </c>
+      <c r="AP18" s="3">
+        <v>2</v>
       </c>
       <c r="AQ18" s="3">
         <f>+AO18+AP18</f>
-        <v>78</v>
-      </c>
-      <c r="AR18" s="23">
-        <f>+AQ18+4</f>
-        <v>82</v>
-      </c>
-      <c r="AS18" s="23">
+        <v>81</v>
+      </c>
+      <c r="AR18" s="3">
+        <f>+AQ18+7</f>
+        <v>88</v>
+      </c>
+      <c r="AS18" s="3">
         <f>+AR18+7+AT18</f>
-        <v>103</v>
-      </c>
-      <c r="AT18" s="23">
-        <v>14</v>
+        <v>108</v>
+      </c>
+      <c r="AT18" s="3">
+        <v>13</v>
       </c>
       <c r="AU18" s="3">
         <f>+AA18-R18</f>
-        <v>27</v>
-      </c>
-      <c r="AV18" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="AW18" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW18" s="3" t="s">
         <v>131</v>
       </c>
       <c r="AX18" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AY18" s="40">
-        <v>46508</v>
+      <c r="AY18" s="21">
+        <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>917</v>
       </c>
@@ -4866,42 +4887,42 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B20" s="43" t="s">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>918</v>
+      </c>
+      <c r="B20" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" s="44" t="s">
-        <v>53</v>
+      <c r="C20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="F20" s="19">
-        <v>90016500</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>159</v>
+        <v>91017700</v>
+      </c>
+      <c r="G20" s="35" t="s">
+        <v>157</v>
       </c>
       <c r="H20" s="2">
-        <v>0</v>
+        <v>2533780546</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="J20" s="2">
-        <v>29159</v>
+        <v>2533780546</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="L20" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M20" s="3">
         <f>+IF(I20="SFK Freight Forwarder",L20,9)</f>
@@ -4945,133 +4966,133 @@
         <v>31</v>
       </c>
       <c r="X20" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Z20" s="6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AA20" s="6">
         <f>+Z20+AB20-1</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB20" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3">
         <v>6</v>
       </c>
-      <c r="AC20" s="3">
-        <v>7</v>
-      </c>
       <c r="AD20" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE20" s="3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF20" s="3">
         <f>+AE20+AA20-1</f>
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AG20" s="6">
         <v>3</v>
       </c>
       <c r="AH20" s="6">
         <f>+AF20+AG20</f>
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI20" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AJ20" s="3">
         <f>+AI20+AH20</f>
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AK20" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL20" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM20" s="3">
         <f>+AJ20+AL20</f>
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AN20" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AO20" s="3">
         <f>+AM20+AN20</f>
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="AP20" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ20" s="3">
         <f>+AO20+AP20</f>
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="AR20" s="3">
         <f>+AQ20+7</f>
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="AS20" s="3">
         <f>+AR20+7+AT20</f>
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="AT20" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU20" s="3">
         <f>+AA20-R20</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV20" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AW20" s="3" t="s">
         <v>131</v>
       </c>
       <c r="AX20" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY20" s="40">
+        <v>56</v>
+      </c>
+      <c r="AY20" s="21">
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>916</v>
-      </c>
-      <c r="B21" s="32" t="s">
+        <v>920</v>
+      </c>
+      <c r="B21" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="C21" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="33" t="s">
         <v>81</v>
       </c>
       <c r="F21" s="19">
-        <v>91017700</v>
-      </c>
-      <c r="G21" s="5" t="s">
+        <v>91017500</v>
+      </c>
+      <c r="G21" s="35" t="s">
         <v>157</v>
       </c>
       <c r="H21" s="2">
-        <v>95207</v>
+        <v>2533780535</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J21" s="2">
-        <v>95207</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>30</v>
+        <v>2533780535</v>
+      </c>
+      <c r="K21" s="44" t="s">
+        <v>22</v>
       </c>
       <c r="L21" s="3">
         <v>7</v>
@@ -5081,11 +5102,11 @@
         <v>9</v>
       </c>
       <c r="N21" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O21" s="3">
         <f>IF(I21="SFK Freight Forwarder",M21,M21+N21-1)</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="P21" s="3">
         <f>+IF(I21="SFK Freight Forwarder",0,5)</f>
@@ -5093,111 +5114,111 @@
       </c>
       <c r="Q21" s="3">
         <f>+IF(I21="SFK Freight Forwarder",O21,O21+P21-1)</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="R21" s="3">
         <f>9+N21</f>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S21" s="3">
         <v>7</v>
       </c>
       <c r="T21" s="3">
         <f>+R21+S21-1</f>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="U21" s="3">
         <f>+T21+1</f>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="V21" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W21" s="3">
         <f>+U21+V21-1</f>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="X21" s="3">
         <v>0</v>
       </c>
       <c r="Y21" s="3">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="Z21" s="6">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AA21" s="6">
         <f>+Z21+AB21-1</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AB21" s="3">
         <v>3</v>
       </c>
       <c r="AC21" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD21" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE21" s="3">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="AF21" s="3">
         <f>+AE21+AA21-1</f>
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="AG21" s="6">
         <v>3</v>
       </c>
       <c r="AH21" s="6">
         <f>+AF21+AG21</f>
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AI21" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ21" s="3">
         <f>+AI21+AH21</f>
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="AK21" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL21" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM21" s="3">
         <f>+AJ21+AL21</f>
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="AN21" s="3">
         <v>8</v>
       </c>
       <c r="AO21" s="3">
         <f>+AM21+AN21</f>
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AP21" s="3">
         <v>2</v>
       </c>
       <c r="AQ21" s="3">
         <f>+AO21+AP21</f>
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AR21" s="3">
         <f>+AQ21+7</f>
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="AS21" s="3">
         <f>+AR21+7+AT21</f>
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="AT21" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU21" s="3">
         <f>+AA21-R21</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV21" s="3" t="s">
         <v>130</v>
@@ -5212,7 +5233,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5385,7 +5406,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>924</v>
       </c>
@@ -5558,7 +5579,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>925</v>
       </c>
@@ -5731,7 +5752,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -5904,7 +5925,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>928</v>
       </c>
@@ -6077,39 +6098,39 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>918</v>
+        <v>930</v>
       </c>
       <c r="B27" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="C27" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="33" t="s">
         <v>81</v>
       </c>
       <c r="F27" s="19">
         <v>91017700</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="G27" s="4" t="s">
         <v>157</v>
       </c>
       <c r="H27" s="2">
-        <v>2533780546</v>
+        <v>26037000</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="J27" s="2">
-        <v>2533780546</v>
+        <v>26037000</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="L27" s="3">
         <v>2</v>
@@ -6126,7 +6147,6 @@
         <v>22</v>
       </c>
       <c r="P27" s="3">
-        <f>+IF(I27="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q27" s="3">
@@ -6149,17 +6169,17 @@
         <v>30</v>
       </c>
       <c r="V27" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W27" s="3">
         <f>+U27+V27-1</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X27" s="3">
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Z27" s="6">
         <v>35</v>
@@ -6172,66 +6192,66 @@
         <v>3</v>
       </c>
       <c r="AC27" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD27" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE27" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AF27" s="3">
         <f>+AE27+AA27-1</f>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AG27" s="6">
         <v>3</v>
       </c>
       <c r="AH27" s="6">
         <f>+AF27+AG27</f>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI27" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AJ27" s="3">
         <f>+AI27+AH27</f>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AK27" s="3" t="s">
         <v>55</v>
       </c>
       <c r="AL27" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM27" s="3">
         <f>+AJ27+AL27</f>
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AN27" s="3">
         <v>8</v>
       </c>
       <c r="AO27" s="3">
         <f>+AM27+AN27</f>
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AP27" s="3">
         <v>2</v>
       </c>
       <c r="AQ27" s="3">
         <f>+AO27+AP27</f>
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AR27" s="3">
         <f>+AQ27+7</f>
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AS27" s="3">
         <f>+AR27+7+AT27</f>
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AT27" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AU27" s="3">
         <f>+AA27-R27</f>
@@ -6250,7 +6270,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>931</v>
       </c>
@@ -6423,7 +6443,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>932</v>
       </c>
@@ -6596,7 +6616,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>1005</v>
       </c>
@@ -6768,7 +6788,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>1006</v>
       </c>
@@ -6940,7 +6960,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>1007</v>
       </c>
@@ -7114,7 +7134,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>1009</v>
       </c>
@@ -7286,7 +7306,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>1010</v>
       </c>
@@ -7458,7 +7478,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>1012</v>
       </c>
@@ -7631,7 +7651,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>1014</v>
       </c>
@@ -7803,7 +7823,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>1015</v>
       </c>
@@ -7975,7 +7995,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>1034</v>
       </c>
@@ -8147,7 +8167,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1036</v>
       </c>
@@ -8319,7 +8339,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>1037</v>
       </c>
@@ -8491,167 +8511,168 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F41" s="19">
-        <v>26549502</v>
+        <v>91017700</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="H41" s="2">
-        <v>0</v>
+        <v>222222</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="J41" s="2">
-        <v>119640</v>
+        <v>222222</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L41" s="3">
         <v>7</v>
       </c>
       <c r="M41" s="3">
-        <v>0</v>
+        <f>+IF(I41="SFK Freight Forwarder",L41,9)</f>
+        <v>9</v>
       </c>
       <c r="N41" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O41" s="3">
         <f>IF(I41="SFK Freight Forwarder",M41,M41+N41-1)</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="P41" s="3">
         <f>+IF(I41="SFK Freight Forwarder",0,5)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q41" s="3">
         <f>+IF(I41="SFK Freight Forwarder",O41,O41+P41-1)</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R41" s="3">
         <f>9+N41</f>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="S41" s="3">
         <v>7</v>
       </c>
       <c r="T41" s="3">
         <f>+R41+S41-1</f>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="U41" s="3">
         <f>+T41+1</f>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="V41" s="3">
         <v>1</v>
       </c>
       <c r="W41" s="3">
         <f>+U41+V41-1</f>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="X41" s="3">
         <v>0</v>
       </c>
       <c r="Y41" s="3">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="Z41" s="6">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="AA41" s="6">
         <f>+Z41+AB41-1</f>
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AB41" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC41" s="3">
         <v>4</v>
       </c>
-      <c r="AC41" s="3">
-        <v>11</v>
-      </c>
       <c r="AD41" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE41" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AF41" s="3">
         <f>+AE41+AA41-1</f>
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="AG41" s="6">
         <v>3</v>
       </c>
       <c r="AH41" s="6">
         <f>+AF41+AG41</f>
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="AI41" s="3">
         <v>0</v>
       </c>
       <c r="AJ41" s="3">
         <f>+AI41+AH41</f>
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="AK41" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL41" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AM41" s="3">
         <f>+AJ41+AL41</f>
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AN41" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AO41" s="3">
         <f>+AM41+AN41</f>
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AP41" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ41" s="3">
         <f>+AO41+AP41</f>
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AR41" s="3">
         <f>+AQ41+7</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="AS41" s="3">
         <f>+AR41+7+AT41</f>
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="AT41" s="3">
         <v>0</v>
       </c>
       <c r="AU41" s="3">
         <f>+AA41-R41</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV41" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AW41" s="3" t="s">
         <v>131</v>
@@ -8659,230 +8680,229 @@
       <c r="AX41" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="AY41" s="40">
+      <c r="AY41" s="21">
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="B42" s="33" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F42" s="19">
-        <v>90014400</v>
+        <v>26549502</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="H42" s="2">
-        <v>222222</v>
+        <v>0</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="J42" s="2">
-        <v>222222</v>
+        <v>119640</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L42" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M42" s="3">
-        <f>+IF(I42="SFK Freight Forwarder",L42,9)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N42" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O42" s="3">
         <f>IF(I42="SFK Freight Forwarder",M42,M42+N42-1)</f>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="P42" s="3">
         <f>+IF(I42="SFK Freight Forwarder",0,5)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="3">
         <f>+IF(I42="SFK Freight Forwarder",O42,O42+P42-1)</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R42" s="3">
         <f>9+N42</f>
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="S42" s="3">
         <v>7</v>
       </c>
       <c r="T42" s="3">
         <f>+R42+S42-1</f>
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="U42" s="3">
         <f>+T42+1</f>
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="V42" s="3">
         <v>1</v>
       </c>
       <c r="W42" s="3">
         <f>+U42+V42-1</f>
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
       <c r="Y42" s="3">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Z42" s="6">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AA42" s="6">
         <f>+Z42+AB42-1</f>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AB42" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC42" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AD42" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE42" s="3">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AF42" s="3">
         <f>+AE42+AA42-1</f>
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="AG42" s="6">
         <v>3</v>
       </c>
       <c r="AH42" s="6">
         <f>+AF42+AG42</f>
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="AI42" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ42" s="3">
         <f>+AI42+AH42</f>
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="AK42" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL42" s="3">
         <v>4</v>
       </c>
       <c r="AM42" s="3">
         <f>+AJ42+AL42</f>
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AN42" s="3">
         <v>3</v>
       </c>
       <c r="AO42" s="3">
         <f>+AM42+AN42</f>
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AP42" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AQ42" s="3">
         <f>+AO42+AP42</f>
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AR42" s="3">
         <f>+AQ42+7</f>
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="AS42" s="3">
         <f>+AR42+7+AT42</f>
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="AT42" s="3">
         <v>0</v>
       </c>
       <c r="AU42" s="3">
         <f>+AA42-R42</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AV42" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AW42" s="3" t="s">
         <v>131</v>
       </c>
       <c r="AX42" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY42" s="21">
+        <v>75</v>
+      </c>
+      <c r="AY42" s="40">
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>1084</v>
+        <v>1045</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="F43" s="19">
-        <v>90018600</v>
+        <v>90014400</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H43" s="2">
-        <v>333333</v>
+        <v>222222</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J43" s="2">
-        <v>333333</v>
+        <v>222222</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L43" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M43" s="3">
         <f>+IF(I43="SFK Freight Forwarder",L43,9)</f>
         <v>9</v>
       </c>
       <c r="N43" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O43" s="3">
         <f>IF(I43="SFK Freight Forwarder",M43,M43+N43-1)</f>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="P43" s="3">
         <f>+IF(I43="SFK Freight Forwarder",0,5)</f>
@@ -8890,42 +8910,42 @@
       </c>
       <c r="Q43" s="3">
         <f>+IF(I43="SFK Freight Forwarder",O43,O43+P43-1)</f>
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="R43" s="3">
         <f>9+N43</f>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="S43" s="3">
         <v>7</v>
       </c>
       <c r="T43" s="3">
         <f>+R43+S43-1</f>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="U43" s="3">
         <f>+T43+1</f>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="V43" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W43" s="3">
         <f>+U43+V43-1</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
       <c r="Y43" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z43" s="6">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AA43" s="6">
         <f>+Z43+AB43-1</f>
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AB43" s="3">
         <v>3</v>
@@ -8937,70 +8957,70 @@
         <v>5</v>
       </c>
       <c r="AE43" s="3">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="AF43" s="3">
         <f>+AE43+AA43-1</f>
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AG43" s="6">
         <v>3</v>
       </c>
       <c r="AH43" s="6">
         <f>+AF43+AG43</f>
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI43" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ43" s="3">
         <f>+AI43+AH43</f>
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="AK43" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL43" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM43" s="3">
         <f>+AJ43+AL43</f>
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="AN43" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO43" s="3">
         <f>+AM43+AN43</f>
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="AP43" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AQ43" s="3">
         <f>+AO43+AP43</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="AR43" s="3">
         <f>+AQ43+7</f>
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="AS43" s="3">
         <f>+AR43+7+AT43</f>
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="AT43" s="3">
         <v>0</v>
       </c>
       <c r="AU43" s="3">
         <f>+AA43-R43</f>
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AV43" s="3" t="s">
         <v>130</v>
       </c>
       <c r="AW43" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="AX43" s="20" t="s">
         <v>88</v>
@@ -9009,362 +9029,362 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>138</v>
+    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>1084</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="C44" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="D44" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="E44" s="33" t="s">
-        <v>81</v>
+        <v>67</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="F44" s="19">
-        <v>90016500</v>
-      </c>
-      <c r="G44" s="23" t="s">
-        <v>158</v>
+        <v>90018600</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="H44" s="2">
-        <v>0</v>
+        <v>333333</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="J44" s="2">
-        <v>29159</v>
-      </c>
-      <c r="K44" s="23" t="s">
-        <v>137</v>
+        <v>333333</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="L44" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M44" s="3">
-        <v>8</v>
-      </c>
-      <c r="N44" s="23">
-        <v>1</v>
+        <f>+IF(I44="SFK Freight Forwarder",L44,9)</f>
+        <v>9</v>
+      </c>
+      <c r="N44" s="3">
+        <v>14</v>
       </c>
       <c r="O44" s="3">
         <f>IF(I44="SFK Freight Forwarder",M44,M44+N44-1)</f>
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="P44" s="3">
-        <v>6</v>
+        <f>+IF(I44="SFK Freight Forwarder",0,5)</f>
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <f>+IF(I44="SFK Freight Forwarder",O44,O44+P44-1)</f>
-        <v>13</v>
-      </c>
-      <c r="R44" s="23">
-        <v>9</v>
-      </c>
-      <c r="S44" s="23">
-        <v>12</v>
-      </c>
-      <c r="T44" s="23">
+        <v>26</v>
+      </c>
+      <c r="R44" s="3">
+        <f>9+N44</f>
+        <v>23</v>
+      </c>
+      <c r="S44" s="3">
+        <v>7</v>
+      </c>
+      <c r="T44" s="3">
         <f>+R44+S44-1</f>
-        <v>20</v>
-      </c>
-      <c r="U44" s="23">
-        <f>+T44+2</f>
-        <v>22</v>
-      </c>
-      <c r="V44" s="23">
+        <v>29</v>
+      </c>
+      <c r="U44" s="3">
+        <f>+T44+1</f>
+        <v>30</v>
+      </c>
+      <c r="V44" s="3">
+        <v>2</v>
+      </c>
+      <c r="W44" s="3">
+        <f>+U44+V44-1</f>
+        <v>31</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>36</v>
+      </c>
+      <c r="Z44" s="6">
+        <v>39</v>
+      </c>
+      <c r="AA44" s="6">
+        <f>+Z44+AB44-1</f>
+        <v>41</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC44" s="3">
         <v>5</v>
       </c>
-      <c r="W44" s="23">
-        <f>+U44+V44-1</f>
-        <v>26</v>
-      </c>
-      <c r="X44" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>29</v>
-      </c>
-      <c r="Z44" s="6">
-        <v>29</v>
-      </c>
-      <c r="AA44" s="6">
-        <v>31</v>
-      </c>
-      <c r="AB44" s="23">
-        <v>4</v>
-      </c>
-      <c r="AC44" s="23"/>
-      <c r="AD44" s="23"/>
-      <c r="AE44" s="33">
-        <v>41</v>
-      </c>
-      <c r="AF44" s="23">
+      <c r="AD44" s="3">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>35</v>
+      </c>
+      <c r="AF44" s="3">
         <f>+AE44+AA44-1</f>
-        <v>71</v>
-      </c>
-      <c r="AG44" s="23">
-        <v>3</v>
-      </c>
-      <c r="AH44" s="23">
+        <v>75</v>
+      </c>
+      <c r="AG44" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH44" s="6">
         <f>+AF44+AG44</f>
-        <v>74</v>
-      </c>
-      <c r="AI44" s="23">
-        <v>7</v>
-      </c>
-      <c r="AJ44" s="23">
+        <v>78</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="3">
         <f>+AI44+AH44</f>
-        <v>81</v>
-      </c>
-      <c r="AK44" s="23"/>
-      <c r="AL44" s="23">
-        <v>3</v>
-      </c>
-      <c r="AM44" s="23">
+        <v>78</v>
+      </c>
+      <c r="AK44" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL44" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM44" s="3">
         <f>+AJ44+AL44</f>
+        <v>80</v>
+      </c>
+      <c r="AN44" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO44" s="3">
+        <f>+AM44+AN44</f>
+        <v>82</v>
+      </c>
+      <c r="AP44" s="3">
+        <v>2</v>
+      </c>
+      <c r="AQ44" s="3">
+        <f>+AO44+AP44</f>
         <v>84</v>
       </c>
-      <c r="AN44" s="23">
-        <v>5</v>
-      </c>
-      <c r="AO44" s="23">
-        <f>+AM44+AN44</f>
-        <v>89</v>
-      </c>
-      <c r="AP44" s="23">
-        <v>6</v>
-      </c>
-      <c r="AQ44" s="3">
-        <v>92</v>
-      </c>
-      <c r="AR44" s="23">
-        <f>+AQ44+4</f>
-        <v>96</v>
-      </c>
-      <c r="AS44" s="23">
+      <c r="AR44" s="3">
+        <f>+AQ44+7</f>
+        <v>91</v>
+      </c>
+      <c r="AS44" s="3">
         <f>+AR44+7+AT44</f>
-        <v>117</v>
-      </c>
-      <c r="AT44" s="23">
-        <v>14</v>
+        <v>98</v>
+      </c>
+      <c r="AT44" s="3">
+        <v>0</v>
       </c>
       <c r="AU44" s="3">
         <f>+AA44-R44</f>
-        <v>22</v>
-      </c>
-      <c r="AV44" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="AW44" s="23" t="s">
-        <v>131</v>
+        <v>18</v>
+      </c>
+      <c r="AV44" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW44" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="AX44" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="AY44" s="37">
-        <v>46508</v>
+        <v>88</v>
+      </c>
+      <c r="AY44" s="21">
+        <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="5">
-        <v>920</v>
+    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="E45" s="33" t="s">
         <v>81</v>
       </c>
       <c r="F45" s="19">
-        <v>91017500</v>
-      </c>
-      <c r="G45" s="35" t="s">
-        <v>157</v>
+        <v>90016500</v>
+      </c>
+      <c r="G45" s="23" t="s">
+        <v>158</v>
       </c>
       <c r="H45" s="2">
-        <v>2533780535</v>
+        <v>0</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="J45" s="2">
-        <v>2533780535</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>22</v>
+        <v>29159</v>
+      </c>
+      <c r="K45" s="23" t="s">
+        <v>137</v>
       </c>
       <c r="L45" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M45" s="3">
-        <f>+IF(I45="SFK Freight Forwarder",L45,9)</f>
-        <v>9</v>
-      </c>
-      <c r="N45" s="3">
-        <v>14</v>
+        <v>8</v>
+      </c>
+      <c r="N45" s="23">
+        <v>1</v>
       </c>
       <c r="O45" s="3">
         <f>IF(I45="SFK Freight Forwarder",M45,M45+N45-1)</f>
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="P45" s="3">
-        <f>+IF(I45="SFK Freight Forwarder",0,5)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q45" s="3">
         <f>+IF(I45="SFK Freight Forwarder",O45,O45+P45-1)</f>
+        <v>13</v>
+      </c>
+      <c r="R45" s="23">
+        <v>9</v>
+      </c>
+      <c r="S45" s="23">
+        <v>12</v>
+      </c>
+      <c r="T45" s="23">
+        <f>+R45+S45-1</f>
+        <v>20</v>
+      </c>
+      <c r="U45" s="23">
+        <f>+T45+2</f>
+        <v>22</v>
+      </c>
+      <c r="V45" s="23">
+        <v>5</v>
+      </c>
+      <c r="W45" s="23">
+        <f>+U45+V45-1</f>
         <v>26</v>
       </c>
-      <c r="R45" s="3">
-        <f>9+N45</f>
-        <v>23</v>
-      </c>
-      <c r="S45" s="3">
-        <v>7</v>
-      </c>
-      <c r="T45" s="3">
-        <f>+R45+S45-1</f>
+      <c r="X45" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
         <v>29</v>
       </c>
-      <c r="U45" s="3">
-        <f>+T45+1</f>
-        <v>30</v>
-      </c>
-      <c r="V45" s="3">
-        <v>3</v>
-      </c>
-      <c r="W45" s="3">
-        <f>+U45+V45-1</f>
-        <v>32</v>
-      </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>33</v>
-      </c>
       <c r="Z45" s="6">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="AA45" s="6">
-        <f>+Z45+AB45-1</f>
-        <v>39</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>3</v>
-      </c>
-      <c r="AC45" s="3">
+        <v>31</v>
+      </c>
+      <c r="AB45" s="23">
+        <v>4</v>
+      </c>
+      <c r="AC45" s="23"/>
+      <c r="AD45" s="23"/>
+      <c r="AE45" s="33">
+        <v>41</v>
+      </c>
+      <c r="AF45" s="23">
+        <f>+AE45+AA45-1</f>
+        <v>71</v>
+      </c>
+      <c r="AG45" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH45" s="23">
+        <f>+AF45+AG45</f>
+        <v>74</v>
+      </c>
+      <c r="AI45" s="23">
+        <v>7</v>
+      </c>
+      <c r="AJ45" s="23">
+        <f>+AI45+AH45</f>
+        <v>81</v>
+      </c>
+      <c r="AK45" s="23"/>
+      <c r="AL45" s="23">
+        <v>3</v>
+      </c>
+      <c r="AM45" s="23">
+        <f>+AJ45+AL45</f>
+        <v>84</v>
+      </c>
+      <c r="AN45" s="23">
+        <v>5</v>
+      </c>
+      <c r="AO45" s="23">
+        <f>+AM45+AN45</f>
+        <v>89</v>
+      </c>
+      <c r="AP45" s="23">
         <v>6</v>
       </c>
-      <c r="AD45" s="3">
-        <v>13</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>39</v>
-      </c>
-      <c r="AF45" s="3">
-        <f>+AE45+AA45-1</f>
-        <v>77</v>
-      </c>
-      <c r="AG45" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH45" s="6">
-        <f>+AF45+AG45</f>
-        <v>80</v>
-      </c>
-      <c r="AI45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ45" s="3">
-        <f>+AI45+AH45</f>
-        <v>80</v>
-      </c>
-      <c r="AK45" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL45" s="3">
-        <v>3</v>
-      </c>
-      <c r="AM45" s="3">
-        <f>+AJ45+AL45</f>
-        <v>83</v>
-      </c>
-      <c r="AN45" s="3">
-        <v>8</v>
-      </c>
-      <c r="AO45" s="3">
-        <f>+AM45+AN45</f>
-        <v>91</v>
-      </c>
-      <c r="AP45" s="3">
-        <v>2</v>
-      </c>
       <c r="AQ45" s="3">
-        <f>+AO45+AP45</f>
-        <v>93</v>
-      </c>
-      <c r="AR45" s="3">
-        <f>+AQ45+7</f>
-        <v>100</v>
-      </c>
-      <c r="AS45" s="3">
+        <v>92</v>
+      </c>
+      <c r="AR45" s="23">
+        <f>+AQ45+4</f>
+        <v>96</v>
+      </c>
+      <c r="AS45" s="23">
         <f>+AR45+7+AT45</f>
-        <v>121</v>
-      </c>
-      <c r="AT45" s="3">
+        <v>117</v>
+      </c>
+      <c r="AT45" s="23">
         <v>14</v>
       </c>
       <c r="AU45" s="3">
         <f>+AA45-R45</f>
-        <v>16</v>
-      </c>
-      <c r="AV45" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AW45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AV45" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW45" s="23" t="s">
         <v>131</v>
       </c>
       <c r="AX45" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AY45" s="21">
-        <v>46507</v>
+      <c r="AY45" s="37">
+        <v>46508</v>
       </c>
     </row>
-    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B46" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="C46" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="D46" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46" s="33" t="s">
-        <v>59</v>
+        <v>172</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="F46" s="19">
-        <v>90018600</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>156</v>
+        <v>90016500</v>
+      </c>
+      <c r="G46" s="23" t="s">
+        <v>159</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -9373,173 +9393,161 @@
         <v>139</v>
       </c>
       <c r="J46" s="2">
-        <v>112741</v>
-      </c>
-      <c r="K46" s="7" t="s">
-        <v>38</v>
+        <v>29159</v>
+      </c>
+      <c r="K46" s="23" t="s">
+        <v>137</v>
       </c>
       <c r="L46" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M46" s="3">
-        <f>+IF(I46="SFK Freight Forwarder",L46,9)</f>
-        <v>9</v>
-      </c>
-      <c r="N46" s="3">
-        <v>14</v>
+        <v>8</v>
+      </c>
+      <c r="N46" s="23">
+        <v>1</v>
       </c>
       <c r="O46" s="3">
         <f>IF(I46="SFK Freight Forwarder",M46,M46+N46-1)</f>
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="P46" s="3">
-        <f>+IF(I46="SFK Freight Forwarder",0,5)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q46" s="3">
         <f>+IF(I46="SFK Freight Forwarder",O46,O46+P46-1)</f>
+        <v>13</v>
+      </c>
+      <c r="R46" s="23">
+        <v>9</v>
+      </c>
+      <c r="S46" s="23">
+        <v>12</v>
+      </c>
+      <c r="T46" s="23">
+        <f>+R46+S46-1</f>
+        <v>20</v>
+      </c>
+      <c r="U46" s="23">
+        <f>+T46+2</f>
+        <v>22</v>
+      </c>
+      <c r="V46" s="23">
+        <v>5</v>
+      </c>
+      <c r="W46" s="23">
+        <f>+U46+V46-1</f>
         <v>26</v>
       </c>
-      <c r="R46" s="3">
-        <f>9+N46</f>
-        <v>23</v>
-      </c>
-      <c r="S46" s="3">
-        <v>7</v>
-      </c>
-      <c r="T46" s="3">
-        <f>+R46+S46-1</f>
+      <c r="X46" s="23">
+        <v>4</v>
+      </c>
+      <c r="Y46" s="3">
         <v>29</v>
       </c>
-      <c r="U46" s="3">
-        <f>+T46+1</f>
-        <v>30</v>
-      </c>
-      <c r="V46" s="3">
+      <c r="Z46" s="6">
+        <v>34</v>
+      </c>
+      <c r="AA46" s="6">
+        <v>36</v>
+      </c>
+      <c r="AB46" s="23">
+        <v>4</v>
+      </c>
+      <c r="AC46" s="23"/>
+      <c r="AD46" s="23"/>
+      <c r="AE46" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF46" s="23">
+        <f>+AE46+AA46-1</f>
+        <v>69</v>
+      </c>
+      <c r="AG46" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH46" s="23">
+        <f>+AF46+AG46</f>
+        <v>72</v>
+      </c>
+      <c r="AI46" s="23">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="23">
+        <f>+AI46+AH46</f>
+        <v>72</v>
+      </c>
+      <c r="AK46" s="23"/>
+      <c r="AL46" s="23">
         <v>2</v>
       </c>
-      <c r="W46" s="3">
-        <f>+U46+V46-1</f>
-        <v>31</v>
-      </c>
-      <c r="X46" s="3">
-        <v>3</v>
-      </c>
-      <c r="Y46" s="3">
-        <f>+ROUNDDOWN(W46/7,0)*7+X46</f>
-        <v>31</v>
-      </c>
-      <c r="Z46" s="6">
-        <f>+Y46+X46-1</f>
-        <v>33</v>
-      </c>
-      <c r="AA46" s="6">
-        <f>+Z46+AB46-1</f>
-        <v>34</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>2</v>
-      </c>
-      <c r="AC46" s="3">
-        <v>4</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>11</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>40</v>
-      </c>
-      <c r="AF46" s="3">
-        <f>+AE46+AA46-1</f>
-        <v>73</v>
-      </c>
-      <c r="AG46" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH46" s="6">
-        <f>+AF46+AG46</f>
-        <v>76</v>
-      </c>
-      <c r="AI46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ46" s="3">
-        <f>+AI46+AH46</f>
-        <v>76</v>
-      </c>
-      <c r="AK46" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AL46" s="3">
-        <v>2</v>
-      </c>
-      <c r="AM46" s="3">
+      <c r="AM46" s="23">
         <f>+AJ46+AL46</f>
-        <v>78</v>
-      </c>
-      <c r="AN46" s="3">
-        <v>2</v>
-      </c>
-      <c r="AO46" s="3">
+        <v>74</v>
+      </c>
+      <c r="AN46" s="23">
+        <v>1</v>
+      </c>
+      <c r="AO46" s="23">
         <f>+AM46+AN46</f>
-        <v>80</v>
-      </c>
-      <c r="AP46" s="3">
-        <v>6</v>
+        <v>75</v>
+      </c>
+      <c r="AP46" s="23">
+        <v>3</v>
       </c>
       <c r="AQ46" s="3">
         <f>+AO46+AP46</f>
-        <v>86</v>
-      </c>
-      <c r="AR46" s="3">
-        <f>+AQ46+7</f>
-        <v>93</v>
-      </c>
-      <c r="AS46" s="3">
+        <v>78</v>
+      </c>
+      <c r="AR46" s="23">
+        <f>+AQ46+4</f>
+        <v>82</v>
+      </c>
+      <c r="AS46" s="23">
         <f>+AR46+7+AT46</f>
-        <v>100</v>
-      </c>
-      <c r="AT46" s="3">
-        <v>0</v>
+        <v>103</v>
+      </c>
+      <c r="AT46" s="23">
+        <v>14</v>
       </c>
       <c r="AU46" s="3">
         <f>+AA46-R46</f>
-        <v>11</v>
-      </c>
-      <c r="AV46" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV46" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="AW46" s="3" t="s">
+      <c r="AW46" s="23" t="s">
         <v>131</v>
       </c>
       <c r="AX46" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY46" s="37">
-        <v>46142</v>
+        <v>56</v>
+      </c>
+      <c r="AY46" s="40">
+        <v>46508</v>
       </c>
     </row>
-    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>171</v>
+        <v>59</v>
       </c>
       <c r="F47" s="19">
-        <v>90012500</v>
+        <v>90018600</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -9548,10 +9556,10 @@
         <v>139</v>
       </c>
       <c r="J47" s="2">
-        <v>29159</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>142</v>
+        <v>112741</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="L47" s="3">
         <v>7</v>
@@ -9598,46 +9606,49 @@
         <v>31</v>
       </c>
       <c r="X47" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
-        <v>32</v>
+        <f>+ROUNDDOWN(W47/7,0)*7+X47</f>
+        <v>31</v>
       </c>
       <c r="Z47" s="6">
+        <f>+Y47+X47-1</f>
         <v>33</v>
       </c>
       <c r="AA47" s="6">
-        <v>36</v>
+        <f>+Z47+AB47-1</f>
+        <v>34</v>
       </c>
       <c r="AB47" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC47" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD47" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE47" s="3">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="AF47" s="3">
         <f>+AE47+AA47-1</f>
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="AG47" s="6">
         <v>3</v>
       </c>
       <c r="AH47" s="6">
         <f>+AF47+AG47</f>
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="AI47" s="3">
         <v>0</v>
       </c>
       <c r="AJ47" s="3">
         <f>+AI47+AH47</f>
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="AK47" s="3" t="s">
         <v>60</v>
@@ -9647,36 +9658,36 @@
       </c>
       <c r="AM47" s="3">
         <f>+AJ47+AL47</f>
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN47" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AO47" s="3">
         <f>+AM47+AN47</f>
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AP47" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ47" s="3">
         <f>+AO47+AP47</f>
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="AR47" s="3">
         <f>+AQ47+7</f>
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="AS47" s="3">
         <f>+AR47+7+AT47</f>
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="AT47" s="3">
         <v>0</v>
       </c>
       <c r="AU47" s="3">
         <f>+AA47-R47</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AV47" s="3" t="s">
         <v>133</v>
@@ -9688,45 +9699,45 @@
         <v>88</v>
       </c>
       <c r="AY47" s="37">
-        <v>46507</v>
+        <v>46142</v>
       </c>
     </row>
-    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="5">
-        <v>930</v>
+    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C48" s="33" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D48" s="33" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="F48" s="19">
-        <v>91017700</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>157</v>
+        <v>90012500</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="H48" s="2">
-        <v>26037000</v>
+        <v>0</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
       <c r="J48" s="2">
-        <v>26037000</v>
+        <v>29159</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>35</v>
+        <v>142</v>
       </c>
       <c r="L48" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M48" s="3">
         <f>+IF(I48="SFK Freight Forwarder",L48,9)</f>
@@ -9740,6 +9751,7 @@
         <v>22</v>
       </c>
       <c r="P48" s="3">
+        <f>+IF(I48="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q48" s="3">
@@ -9762,128 +9774,127 @@
         <v>30</v>
       </c>
       <c r="V48" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W48" s="3">
         <f>+U48+V48-1</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
       </c>
       <c r="Y48" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z48" s="6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AA48" s="6">
-        <f>+Z48+AB48-1</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB48" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC48" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AD48" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE48" s="3">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="AF48" s="3">
         <f>+AE48+AA48-1</f>
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="AG48" s="6">
         <v>3</v>
       </c>
       <c r="AH48" s="6">
         <f>+AF48+AG48</f>
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="AI48" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ48" s="3">
         <f>+AI48+AH48</f>
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="AK48" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL48" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM48" s="3">
         <f>+AJ48+AL48</f>
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="AN48" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO48" s="3">
         <f>+AM48+AN48</f>
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AP48" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AQ48" s="3">
         <f>+AO48+AP48</f>
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="AR48" s="3">
         <f>+AQ48+7</f>
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="AS48" s="3">
         <f>+AR48+7+AT48</f>
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AT48" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AU48" s="3">
         <f>+AA48-R48</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV48" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AW48" s="3" t="s">
         <v>131</v>
       </c>
       <c r="AX48" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="AY48" s="21">
+        <v>88</v>
+      </c>
+      <c r="AY48" s="37">
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B49" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="D49" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="33" t="s">
-        <v>71</v>
+      <c r="D49" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49" s="43" t="s">
+        <v>53</v>
       </c>
       <c r="F49" s="19">
-        <v>92000100</v>
+        <v>90016500</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -9945,85 +9956,83 @@
         <v>2</v>
       </c>
       <c r="Y49" s="3">
-        <f>+ROUNDDOWN(W49/7,0)*7+X49</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Z49" s="6">
-        <f>+Y49+X49-1</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA49" s="6">
         <f>+Z49+AB49-1</f>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AB49" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC49" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD49" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE49" s="3">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF49" s="3">
         <f>+AE49+AA49-1</f>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AG49" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH49" s="6">
         <f>+AF49+AG49</f>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI49" s="3">
         <v>0</v>
       </c>
       <c r="AJ49" s="3">
         <f>+AI49+AH49</f>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>60</v>
       </c>
       <c r="AL49" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM49" s="3">
         <f>+AJ49+AL49</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN49" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AO49" s="3">
         <f>+AM49+AN49</f>
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="AP49" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ49" s="3">
         <f>+AO49+AP49</f>
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AR49" s="3">
         <f>+AQ49+7</f>
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="AS49" s="3">
         <f>+AR49+7+AT49</f>
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="AT49" s="3">
         <v>0</v>
       </c>
       <c r="AU49" s="3">
         <f>+AA49-R49</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AV49" s="3" t="s">
         <v>133</v>
@@ -10032,33 +10041,33 @@
         <v>131</v>
       </c>
       <c r="AX49" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="AY49" s="37">
-        <v>46142</v>
+        <v>88</v>
+      </c>
+      <c r="AY49" s="40">
+        <v>46507</v>
       </c>
     </row>
-    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B50" s="33" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C50" s="33" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F50" s="19">
-        <v>90014400</v>
+        <v>92000100</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="H50" s="2">
         <v>0</v>
@@ -10067,13 +10076,13 @@
         <v>139</v>
       </c>
       <c r="J50" s="2">
-        <v>112741</v>
-      </c>
-      <c r="K50" s="7" t="s">
-        <v>38</v>
+        <v>29159</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="L50" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M50" s="3">
         <f>+IF(I50="SFK Freight Forwarder",L50,9)</f>
@@ -10117,81 +10126,81 @@
         <v>31</v>
       </c>
       <c r="X50" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y50" s="3">
         <f>+ROUNDDOWN(W50/7,0)*7+X50</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Z50" s="6">
         <f>+Y50+X50-1</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="AA50" s="6">
         <f>+Z50+AB50-1</f>
         <v>34</v>
       </c>
       <c r="AB50" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC50" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD50" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE50" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF50" s="3">
         <f>+AE50+AA50-1</f>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AG50" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH50" s="6">
         <f>+AF50+AG50</f>
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AI50" s="3">
         <v>0</v>
       </c>
       <c r="AJ50" s="3">
         <f>+AI50+AH50</f>
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AK50" s="3" t="s">
         <v>60</v>
       </c>
       <c r="AL50" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM50" s="3">
         <f>+AJ50+AL50</f>
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="AN50" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AO50" s="3">
         <f>+AM50+AN50</f>
         <v>92</v>
       </c>
       <c r="AP50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ50" s="3">
         <f>+AO50+AP50</f>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AR50" s="3">
         <f>+AQ50+7</f>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AS50" s="3">
         <f>+AR50+7+AT50</f>
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AT50" s="3">
         <v>0</v>
@@ -10207,33 +10216,33 @@
         <v>131</v>
       </c>
       <c r="AX50" s="20" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="AY50" s="37">
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C51" s="33" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D51" s="33" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="E51" s="33" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F51" s="19">
-        <v>90016000</v>
+        <v>90014400</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>34</v>
+        <v>155</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
@@ -10242,24 +10251,24 @@
         <v>139</v>
       </c>
       <c r="J51" s="2">
-        <v>5915200</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>151</v>
+        <v>112741</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="L51" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M51" s="3">
         <f>+IF(I51="SFK Freight Forwarder",L51,9)</f>
         <v>9</v>
       </c>
       <c r="N51" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O51" s="3">
         <f>IF(I51="SFK Freight Forwarder",M51,M51+N51-1)</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="P51" s="3">
         <f>+IF(I51="SFK Freight Forwarder",0,5)</f>
@@ -10267,147 +10276,148 @@
       </c>
       <c r="Q51" s="3">
         <f>+IF(I51="SFK Freight Forwarder",O51,O51+P51-1)</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="R51" s="3">
         <f>9+N51</f>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S51" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T51" s="3">
         <f>+R51+S51-1</f>
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="U51" s="3">
         <f>+T51+1</f>
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="V51" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W51" s="3">
         <f>+U51+V51-1</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="X51" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y51" s="3">
         <f>+ROUNDDOWN(W51/7,0)*7+X51</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="Z51" s="6">
-        <v>23</v>
+        <f>+Y51+X51-1</f>
+        <v>33</v>
       </c>
       <c r="AA51" s="6">
         <f>+Z51+AB51-1</f>
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AB51" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC51" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD51" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE51" s="3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AF51" s="3">
         <f>+AE51+AA51-1</f>
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="AG51" s="6">
         <v>3</v>
       </c>
       <c r="AH51" s="6">
         <f>+AF51+AG51</f>
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="AI51" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ51" s="3">
         <f>+AI51+AH51</f>
-        <v>74</v>
-      </c>
-      <c r="AK51" s="3">
-        <v>0</v>
+        <v>86</v>
+      </c>
+      <c r="AK51" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="AL51" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AM51" s="3">
         <f>+AJ51+AL51</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN51" s="3">
         <v>2</v>
       </c>
       <c r="AO51" s="3">
         <f>+AM51+AN51</f>
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AP51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ51" s="3">
         <f>+AO51+AP51</f>
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AR51" s="3">
         <f>+AQ51+7</f>
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AS51" s="3">
         <f>+AR51+7+AT51</f>
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="AT51" s="3">
         <v>0</v>
       </c>
       <c r="AU51" s="3">
         <f>+AA51-R51</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV51" s="3" t="s">
         <v>133</v>
       </c>
       <c r="AW51" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="AX51" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="AY51" s="40">
-        <v>46507</v>
+        <v>88</v>
+      </c>
+      <c r="AY51" s="37">
+        <v>46142</v>
       </c>
     </row>
-    <row r="52" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B52" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="C52" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="D52" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="E52" s="38" t="s">
-        <v>81</v>
+        <v>152</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D52" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E52" s="33" t="s">
+        <v>53</v>
       </c>
       <c r="F52" s="19">
-        <v>90014400</v>
+        <v>90016000</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>155</v>
+        <v>34</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -10416,152 +10426,163 @@
         <v>139</v>
       </c>
       <c r="J52" s="2">
-        <v>29159</v>
-      </c>
-      <c r="K52" s="23" t="s">
-        <v>140</v>
+        <v>5915200</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="L52" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M52" s="3">
         <f>+IF(I52="SFK Freight Forwarder",L52,9)</f>
         <v>9</v>
       </c>
-      <c r="N52" s="23">
-        <v>2</v>
+      <c r="N52" s="3">
+        <v>7</v>
       </c>
       <c r="O52" s="3">
         <f>IF(I52="SFK Freight Forwarder",M52,M52+N52-1)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P52" s="3">
+        <f>+IF(I52="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q52" s="3">
         <f>+IF(I52="SFK Freight Forwarder",O52,O52+P52-1)</f>
-        <v>14</v>
-      </c>
-      <c r="R52" s="23">
-        <v>0</v>
-      </c>
-      <c r="S52" s="23">
-        <v>0</v>
-      </c>
-      <c r="T52" s="25">
-        <v>0</v>
-      </c>
-      <c r="U52" s="23">
-        <v>15</v>
-      </c>
-      <c r="V52" s="23">
-        <v>4</v>
-      </c>
-      <c r="W52" s="23">
+        <v>19</v>
+      </c>
+      <c r="R52" s="3">
+        <f>9+N52</f>
+        <v>16</v>
+      </c>
+      <c r="S52" s="3">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3">
+        <f>+R52+S52-1</f>
+        <v>18</v>
+      </c>
+      <c r="U52" s="3">
+        <f>+T52+1</f>
+        <v>19</v>
+      </c>
+      <c r="V52" s="3">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3">
         <f>+U52+V52-1</f>
-        <v>18</v>
-      </c>
-      <c r="X52" s="23">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="X52" s="3">
+        <v>2</v>
       </c>
       <c r="Y52" s="3">
-        <v>18</v>
+        <f>+ROUNDDOWN(W52/7,0)*7+X52</f>
+        <v>23</v>
       </c>
       <c r="Z52" s="6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AA52" s="6">
         <f>+Z52+AB52-1</f>
-        <v>22</v>
-      </c>
-      <c r="AB52" s="23">
-        <v>4</v>
-      </c>
-      <c r="AC52" s="23"/>
-      <c r="AD52" s="23"/>
-      <c r="AE52" s="23">
-        <v>46</v>
-      </c>
-      <c r="AF52" s="23">
+        <v>25</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
+        <v>40</v>
+      </c>
+      <c r="AF52" s="3">
         <f>+AE52+AA52-1</f>
+        <v>64</v>
+      </c>
+      <c r="AG52" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH52" s="6">
+        <f>+AF52+AG52</f>
         <v>67</v>
       </c>
-      <c r="AG52" s="23">
-        <v>3</v>
-      </c>
-      <c r="AH52" s="23">
-        <f>+AF52+AG52</f>
-        <v>70</v>
-      </c>
-      <c r="AI52" s="23">
-        <v>7</v>
-      </c>
-      <c r="AJ52" s="23">
+      <c r="AI52" s="3">
+        <v>7</v>
+      </c>
+      <c r="AJ52" s="3">
         <f>+AI52+AH52</f>
-        <v>77</v>
-      </c>
-      <c r="AK52" s="23"/>
-      <c r="AL52" s="23">
-        <v>3</v>
-      </c>
-      <c r="AM52" s="23">
+        <v>74</v>
+      </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="3">
+        <v>6</v>
+      </c>
+      <c r="AM52" s="3">
         <f>+AJ52+AL52</f>
         <v>80</v>
       </c>
-      <c r="AN52" s="23">
+      <c r="AN52" s="3">
         <v>2</v>
       </c>
-      <c r="AO52" s="23">
+      <c r="AO52" s="3">
         <f>+AM52+AN52</f>
         <v>82</v>
       </c>
-      <c r="AP52" s="23">
-        <v>2</v>
-      </c>
-      <c r="AQ52" s="23">
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="3">
         <f>+AO52+AP52</f>
-        <v>84</v>
-      </c>
-      <c r="AR52" s="23">
+        <v>82</v>
+      </c>
+      <c r="AR52" s="3">
         <f>+AQ52+7</f>
-        <v>91</v>
-      </c>
-      <c r="AS52" s="23">
+        <v>89</v>
+      </c>
+      <c r="AS52" s="3">
         <f>+AR52+7+AT52</f>
-        <v>112</v>
-      </c>
-      <c r="AT52" s="23">
-        <v>14</v>
+        <v>96</v>
+      </c>
+      <c r="AT52" s="3">
+        <v>0</v>
       </c>
       <c r="AU52" s="3">
         <f>+AA52-R52</f>
-        <v>22</v>
-      </c>
-      <c r="AV52" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV52" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="AW52" s="23" t="s">
-        <v>131</v>
+      <c r="AW52" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="AX52" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AY52" s="37">
-        <v>46143</v>
+      <c r="AY52" s="40">
+        <v>46507</v>
       </c>
     </row>
-    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C53" s="39" t="s">
         <v>68</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E53" s="38" t="s">
         <v>81</v>
@@ -10713,206 +10734,201 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="5">
-        <v>1039</v>
-      </c>
-      <c r="B54" s="33" t="s">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="38" t="s">
         <v>81</v>
       </c>
       <c r="F54" s="19">
-        <v>91017700</v>
+        <v>90014400</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H54" s="2">
-        <v>222222</v>
+        <v>0</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="J54" s="2">
-        <v>222222</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>46</v>
+        <v>29159</v>
+      </c>
+      <c r="K54" s="23" t="s">
+        <v>140</v>
       </c>
       <c r="L54" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M54" s="3">
         <f>+IF(I54="SFK Freight Forwarder",L54,9)</f>
         <v>9</v>
       </c>
-      <c r="N54" s="3">
-        <v>21</v>
+      <c r="N54" s="23">
+        <v>2</v>
       </c>
       <c r="O54" s="3">
         <f>IF(I54="SFK Freight Forwarder",M54,M54+N54-1)</f>
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="P54" s="3">
-        <f>+IF(I54="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q54" s="3">
         <f>+IF(I54="SFK Freight Forwarder",O54,O54+P54-1)</f>
-        <v>33</v>
-      </c>
-      <c r="R54" s="3">
-        <f>9+N54</f>
-        <v>30</v>
-      </c>
-      <c r="S54" s="3">
-        <v>7</v>
-      </c>
-      <c r="T54" s="3">
-        <f>+R54+S54-1</f>
-        <v>36</v>
-      </c>
-      <c r="U54" s="3">
-        <f>+T54+1</f>
-        <v>37</v>
-      </c>
-      <c r="V54" s="3">
+        <v>14</v>
+      </c>
+      <c r="R54" s="23">
+        <v>10</v>
+      </c>
+      <c r="S54" s="23">
+        <v>12</v>
+      </c>
+      <c r="T54" s="25">
+        <v>21</v>
+      </c>
+      <c r="U54" s="23">
+        <v>16</v>
+      </c>
+      <c r="V54" s="23">
+        <v>7</v>
+      </c>
+      <c r="W54" s="23">
+        <v>22</v>
+      </c>
+      <c r="X54" s="23">
         <v>1</v>
       </c>
-      <c r="W54" s="3">
-        <f>+U54+V54-1</f>
-        <v>37</v>
-      </c>
-      <c r="X54" s="3">
-        <v>0</v>
-      </c>
       <c r="Y54" s="3">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="Z54" s="6">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AA54" s="6">
         <f>+Z54+AB54-1</f>
-        <v>44</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>3</v>
-      </c>
-      <c r="AC54" s="3">
+        <v>25</v>
+      </c>
+      <c r="AB54" s="23">
         <v>4</v>
       </c>
-      <c r="AD54" s="3">
-        <v>4</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>40</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AC54" s="23"/>
+      <c r="AD54" s="23"/>
+      <c r="AE54" s="23">
+        <v>39</v>
+      </c>
+      <c r="AF54" s="23">
         <f>+AE54+AA54-1</f>
-        <v>83</v>
-      </c>
-      <c r="AG54" s="6">
-        <v>3</v>
-      </c>
-      <c r="AH54" s="6">
+        <v>63</v>
+      </c>
+      <c r="AG54" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH54" s="23">
         <f>+AF54+AG54</f>
+        <v>66</v>
+      </c>
+      <c r="AI54" s="23">
+        <v>7</v>
+      </c>
+      <c r="AJ54" s="23">
+        <f>+AI54+AH54</f>
+        <v>73</v>
+      </c>
+      <c r="AK54" s="23"/>
+      <c r="AL54" s="23">
+        <v>3</v>
+      </c>
+      <c r="AM54" s="23">
+        <f>+AJ54+AL54</f>
+        <v>76</v>
+      </c>
+      <c r="AN54" s="23">
+        <v>8</v>
+      </c>
+      <c r="AO54" s="23">
+        <f>+AM54+AN54</f>
+        <v>84</v>
+      </c>
+      <c r="AP54" s="23">
+        <v>2</v>
+      </c>
+      <c r="AQ54" s="23">
+        <f>+AO54+AP54</f>
         <v>86</v>
       </c>
-      <c r="AI54" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ54" s="3">
-        <f>+AI54+AH54</f>
-        <v>86</v>
-      </c>
-      <c r="AK54" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL54" s="3">
-        <v>2</v>
-      </c>
-      <c r="AM54" s="3">
-        <f>+AJ54+AL54</f>
-        <v>88</v>
-      </c>
-      <c r="AN54" s="3">
-        <v>8</v>
-      </c>
-      <c r="AO54" s="3">
-        <f>+AM54+AN54</f>
-        <v>96</v>
-      </c>
-      <c r="AP54" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ54" s="3">
-        <f>+AO54+AP54</f>
-        <v>98</v>
-      </c>
-      <c r="AR54" s="3">
+      <c r="AR54" s="23">
         <f>+AQ54+7</f>
-        <v>105</v>
-      </c>
-      <c r="AS54" s="3">
+        <v>93</v>
+      </c>
+      <c r="AS54" s="23">
         <f>+AR54+7+AT54</f>
-        <v>112</v>
-      </c>
-      <c r="AT54" s="3">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="AT54" s="23">
+        <v>14</v>
       </c>
       <c r="AU54" s="3">
         <f>+AA54-R54</f>
-        <v>14</v>
-      </c>
-      <c r="AV54" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AW54" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AV54" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW54" s="23" t="s">
         <v>131</v>
       </c>
       <c r="AX54" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="AY54" s="21">
-        <v>46507</v>
+        <v>56</v>
+      </c>
+      <c r="AY54" s="37">
+        <v>46143</v>
       </c>
     </row>
-    <row r="61" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
       <c r="D61" s="41"/>
     </row>
-    <row r="63" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
       <c r="D63" s="42"/>
     </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D65" s="41"/>
     </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D67" s="42"/>
     </row>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D69" s="41"/>
     </row>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D70" s="42"/>
     </row>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D71" s="42"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <autoFilter ref="A1:AY54" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="6">
+    <filterColumn colId="3">
       <filters>
-        <filter val="Horse Sevilla"/>
+        <filter val="ESVLC"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="47">
+      <filters>
+        <filter val="Direct"/>
+        <filter val="Indirect"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -10941,9 +10957,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7007F1-B98C-4FB4-AD1E-FC672D1A14BF}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="B2:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>161</v>
       </c>
@@ -10957,7 +10973,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>164</v>
       </c>
@@ -10971,7 +10987,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>167</v>
       </c>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FBF124-78C4-4A26-851A-49B3AD6AE224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A3F1A2-026A-4FF1-B43F-E5D6A23AFA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$54</definedName>
@@ -365,8 +366,67 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>ZHAO Tengda</author>
+  </authors>
+  <commentList>
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{103C42D8-428E-42D9-8F1C-1CF097BFEAFC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0" shapeId="0" xr:uid="{943AA605-AB84-475D-B08B-8EA82563EA21}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+clé POD?
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="175">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -888,6 +948,9 @@
   </si>
   <si>
     <t>O010</t>
+  </si>
+  <si>
+    <t>Customs (days)</t>
   </si>
 </sst>
 </file>
@@ -1111,7 +1174,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1243,6 +1306,16 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1590,13 +1663,13 @@
     <col min="2" max="2" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.85546875" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="28" width="10.42578125" customWidth="1"/>
@@ -5062,37 +5135,37 @@
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>920</v>
+        <v>1039</v>
       </c>
       <c r="B21" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="33" t="s">
+      <c r="C21" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F21" s="19">
-        <v>91017500</v>
-      </c>
-      <c r="G21" s="35" t="s">
+        <v>91017700</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>157</v>
       </c>
       <c r="H21" s="2">
-        <v>2533780535</v>
+        <v>222222</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J21" s="2">
-        <v>2533780535</v>
-      </c>
-      <c r="K21" s="44" t="s">
-        <v>22</v>
+        <v>222222</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="L21" s="3">
         <v>7</v>
@@ -5102,11 +5175,11 @@
         <v>9</v>
       </c>
       <c r="N21" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O21" s="3">
         <f>IF(I21="SFK Freight Forwarder",M21,M21+N21-1)</f>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="P21" s="3">
         <f>+IF(I21="SFK Freight Forwarder",0,5)</f>
@@ -5114,111 +5187,111 @@
       </c>
       <c r="Q21" s="3">
         <f>+IF(I21="SFK Freight Forwarder",O21,O21+P21-1)</f>
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="R21" s="3">
         <f>9+N21</f>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="S21" s="3">
         <v>7</v>
       </c>
       <c r="T21" s="3">
         <f>+R21+S21-1</f>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="U21" s="3">
         <f>+T21+1</f>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="V21" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W21" s="3">
         <f>+U21+V21-1</f>
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="X21" s="3">
         <v>0</v>
       </c>
       <c r="Y21" s="3">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Z21" s="6">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AA21" s="6">
         <f>+Z21+AB21-1</f>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AB21" s="3">
         <v>3</v>
       </c>
       <c r="AC21" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD21" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE21" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AF21" s="3">
         <f>+AE21+AA21-1</f>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AG21" s="6">
         <v>3</v>
       </c>
       <c r="AH21" s="6">
         <f>+AF21+AG21</f>
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI21" s="3">
         <v>0</v>
       </c>
       <c r="AJ21" s="3">
         <f>+AI21+AH21</f>
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AK21" s="3" t="s">
         <v>55</v>
       </c>
       <c r="AL21" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM21" s="3">
         <f>+AJ21+AL21</f>
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AN21" s="3">
         <v>8</v>
       </c>
       <c r="AO21" s="3">
         <f>+AM21+AN21</f>
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="AP21" s="3">
         <v>2</v>
       </c>
       <c r="AQ21" s="3">
         <f>+AO21+AP21</f>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="AR21" s="3">
         <f>+AQ21+7</f>
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AS21" s="3">
         <f>+AR21+7+AT21</f>
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="AT21" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AU21" s="3">
         <f>+AA21-R21</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV21" s="3" t="s">
         <v>130</v>
@@ -5227,7 +5300,7 @@
         <v>131</v>
       </c>
       <c r="AX21" s="20" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="AY21" s="21">
         <v>46507</v>
@@ -6100,13 +6173,13 @@
     </row>
     <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>930</v>
+        <v>920</v>
       </c>
       <c r="B27" s="33" t="s">
         <v>80</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D27" s="33" t="s">
         <v>58</v>
@@ -6115,25 +6188,25 @@
         <v>81</v>
       </c>
       <c r="F27" s="19">
-        <v>91017700</v>
-      </c>
-      <c r="G27" s="4" t="s">
+        <v>91017500</v>
+      </c>
+      <c r="G27" s="35" t="s">
         <v>157</v>
       </c>
       <c r="H27" s="2">
-        <v>26037000</v>
+        <v>2533780535</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="J27" s="2">
-        <v>26037000</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>35</v>
+        <v>2533780535</v>
+      </c>
+      <c r="K27" s="44" t="s">
+        <v>22</v>
       </c>
       <c r="L27" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M27" s="3">
         <f>+IF(I27="SFK Freight Forwarder",L27,9)</f>
@@ -6147,6 +6220,7 @@
         <v>22</v>
       </c>
       <c r="P27" s="3">
+        <f>+IF(I27="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q27" s="3">
@@ -6169,54 +6243,54 @@
         <v>30</v>
       </c>
       <c r="V27" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W27" s="3">
         <f>+U27+V27-1</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X27" s="3">
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Z27" s="6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AA27" s="6">
         <f>+Z27+AB27-1</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AB27" s="3">
         <v>3</v>
       </c>
       <c r="AC27" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AD27" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE27" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF27" s="3">
         <f>+AE27+AA27-1</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG27" s="6">
         <v>3</v>
       </c>
       <c r="AH27" s="6">
         <f>+AF27+AG27</f>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI27" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ27" s="3">
         <f>+AI27+AH27</f>
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AK27" s="3" t="s">
         <v>55</v>
@@ -6226,36 +6300,36 @@
       </c>
       <c r="AM27" s="3">
         <f>+AJ27+AL27</f>
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="AN27" s="3">
         <v>8</v>
       </c>
       <c r="AO27" s="3">
         <f>+AM27+AN27</f>
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="AP27" s="3">
         <v>2</v>
       </c>
       <c r="AQ27" s="3">
         <f>+AO27+AP27</f>
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="AR27" s="3">
         <f>+AQ27+7</f>
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="AS27" s="3">
         <f>+AR27+7+AT27</f>
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="AT27" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AU27" s="3">
         <f>+AA27-R27</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV27" s="3" t="s">
         <v>130</v>
@@ -7995,7 +8069,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>1034</v>
       </c>
@@ -8167,7 +8241,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1036</v>
       </c>
@@ -8513,120 +8587,119 @@
     </row>
     <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>1039</v>
+        <v>930</v>
       </c>
       <c r="B41" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="33" t="s">
         <v>81</v>
       </c>
       <c r="F41" s="19">
         <v>91017700</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="4" t="s">
         <v>157</v>
       </c>
       <c r="H41" s="2">
-        <v>222222</v>
+        <v>26037000</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="J41" s="2">
-        <v>222222</v>
+        <v>26037000</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="L41" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M41" s="3">
         <f>+IF(I41="SFK Freight Forwarder",L41,9)</f>
         <v>9</v>
       </c>
       <c r="N41" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O41" s="3">
         <f>IF(I41="SFK Freight Forwarder",M41,M41+N41-1)</f>
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="P41" s="3">
-        <f>+IF(I41="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q41" s="3">
         <f>+IF(I41="SFK Freight Forwarder",O41,O41+P41-1)</f>
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="R41" s="3">
         <f>9+N41</f>
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="S41" s="3">
         <v>7</v>
       </c>
       <c r="T41" s="3">
         <f>+R41+S41-1</f>
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="U41" s="3">
         <f>+T41+1</f>
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="V41" s="3">
         <v>1</v>
       </c>
       <c r="W41" s="3">
         <f>+U41+V41-1</f>
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="X41" s="3">
         <v>0</v>
       </c>
       <c r="Y41" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Z41" s="6">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="AA41" s="6">
         <f>+Z41+AB41-1</f>
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AB41" s="3">
         <v>3</v>
       </c>
       <c r="AC41" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AD41" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE41" s="3">
         <v>40</v>
       </c>
       <c r="AF41" s="3">
         <f>+AE41+AA41-1</f>
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AG41" s="6">
         <v>3</v>
       </c>
       <c r="AH41" s="6">
         <f>+AF41+AG41</f>
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI41" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ41" s="3">
         <f>+AI41+AH41</f>
@@ -8636,36 +8709,36 @@
         <v>55</v>
       </c>
       <c r="AL41" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM41" s="3">
         <f>+AJ41+AL41</f>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AN41" s="3">
         <v>8</v>
       </c>
       <c r="AO41" s="3">
         <f>+AM41+AN41</f>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AP41" s="3">
         <v>2</v>
       </c>
       <c r="AQ41" s="3">
         <f>+AO41+AP41</f>
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AR41" s="3">
         <f>+AQ41+7</f>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AS41" s="3">
         <f>+AR41+7+AT41</f>
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="AT41" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU41" s="3">
         <f>+AA41-R41</f>
@@ -8678,7 +8751,7 @@
         <v>131</v>
       </c>
       <c r="AX41" s="20" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="AY41" s="21">
         <v>46507</v>
@@ -9364,7 +9437,7 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>172</v>
       </c>
@@ -9874,7 +9947,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>145</v>
       </c>
@@ -10751,10 +10824,10 @@
         <v>81</v>
       </c>
       <c r="F54" s="19">
-        <v>90014400</v>
+        <v>91017700</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -10922,13 +10995,8 @@
   <autoFilter ref="A1:AY54" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
     <filterColumn colId="3">
       <filters>
+        <filter val="ESALG"/>
         <filter val="ESVLC"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="47">
-      <filters>
-        <filter val="Direct"/>
-        <filter val="Indirect"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -10997,6 +11065,221 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20166134-0068-44E4-897C-A3439A6356AD}">
+  <dimension ref="D7:H17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="4:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="D7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D8" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D9" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D10" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D11" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D12" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D13" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D14" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D15" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="H15" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D16" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D17" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="H17" s="23">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8:E17 G8:G17" xr:uid="{16D324CE-DCDC-4F4A-BBFF-154EE6D698CE}">
+      <formula1>AILNname</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8:E17 G8:G17" xr:uid="{26742100-A0A8-4425-B2CC-95CA7C31FB4E}">
+      <formula1>shippername</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="F8:F17" xr:uid="{B3243257-A0FC-4113-B54C-6EBC8B09FC6C}">
+      <formula1>plantname</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9999a5d2-caa4-4f63-bace-dd6824b086db}" enabled="1" method="Standard" siteId="{de415ce7-227e-480f-88c9-c7dab50e161a}" contentBits="2" removed="0"/>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A3F1A2-026A-4FF1-B43F-E5D6A23AFA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD0B8B9-3AC4-4CDC-B54E-88F8E53200E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="190" yWindow="260" windowWidth="19010" windowHeight="11370" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Hoja2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja2!$D$7:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -961,7 +962,7 @@
     <numFmt numFmtId="164" formatCode="0000000000"/>
     <numFmt numFmtId="165" formatCode="00########"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1055,6 +1056,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1308,15 +1317,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1663,13 +1671,13 @@
     <col min="2" max="2" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.85546875" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="28" width="10.42578125" customWidth="1"/>
@@ -1901,11 +1909,11 @@
         <v>15</v>
       </c>
       <c r="P2" s="3">
-        <f>+IF(I2="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P2:P40" si="0">+IF(I2="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q2" s="3">
-        <f>+IF(I2="SFK Freight Forwarder",O2,O2+P2-1)</f>
+        <f t="shared" ref="Q2:Q33" si="1">+IF(I2="SFK Freight Forwarder",O2,O2+P2-1)</f>
         <v>19</v>
       </c>
       <c r="R2" s="3">
@@ -1916,18 +1924,18 @@
         <v>7</v>
       </c>
       <c r="T2" s="3">
-        <f>+R2+S2-1</f>
+        <f t="shared" ref="T2:T33" si="2">+R2+S2-1</f>
         <v>22</v>
       </c>
       <c r="U2" s="3">
-        <f>+T2+1</f>
+        <f t="shared" ref="U2:U44" si="3">+T2+1</f>
         <v>23</v>
       </c>
       <c r="V2" s="3">
         <v>1</v>
       </c>
       <c r="W2" s="3">
-        <f>+U2+V2-1</f>
+        <f t="shared" ref="W2:W33" si="4">+U2+V2-1</f>
         <v>23</v>
       </c>
       <c r="X2" s="3">
@@ -1940,7 +1948,7 @@
         <v>25</v>
       </c>
       <c r="AA2" s="6">
-        <f>+Z2+AB2-1</f>
+        <f t="shared" ref="AA2:AA7" si="5">+Z2+AB2-1</f>
         <v>27</v>
       </c>
       <c r="AB2" s="3">
@@ -1956,21 +1964,21 @@
         <v>46</v>
       </c>
       <c r="AF2" s="3">
-        <f>+AE2+AA2-1</f>
+        <f t="shared" ref="AF2:AF33" si="6">+AE2+AA2-1</f>
         <v>72</v>
       </c>
       <c r="AG2" s="6">
         <v>3</v>
       </c>
       <c r="AH2" s="6">
-        <f>+AF2+AG2</f>
+        <f t="shared" ref="AH2:AH33" si="7">+AF2+AG2</f>
         <v>75</v>
       </c>
       <c r="AI2" s="3">
         <v>7</v>
       </c>
       <c r="AJ2" s="3">
-        <f>+AI2+AH2</f>
+        <f t="shared" ref="AJ2:AJ33" si="8">+AI2+AH2</f>
         <v>82</v>
       </c>
       <c r="AK2" s="3" t="s">
@@ -1980,36 +1988,36 @@
         <v>2</v>
       </c>
       <c r="AM2" s="3">
-        <f>+AJ2+AL2</f>
+        <f t="shared" ref="AM2:AM33" si="9">+AJ2+AL2</f>
         <v>84</v>
       </c>
       <c r="AN2" s="3">
         <v>2</v>
       </c>
       <c r="AO2" s="3">
-        <f>+AM2+AN2</f>
+        <f t="shared" ref="AO2:AO33" si="10">+AM2+AN2</f>
         <v>86</v>
       </c>
       <c r="AP2" s="3">
         <v>5</v>
       </c>
       <c r="AQ2" s="3">
-        <f>+AO2+AP2</f>
+        <f t="shared" ref="AQ2:AQ44" si="11">+AO2+AP2</f>
         <v>91</v>
       </c>
       <c r="AR2" s="3">
-        <f>+AQ2+7</f>
+        <f t="shared" ref="AR2:AR44" si="12">+AQ2+7</f>
         <v>98</v>
       </c>
       <c r="AS2" s="3">
-        <f>+AR2+7+AT2</f>
+        <f t="shared" ref="AS2:AS33" si="13">+AR2+7+AT2</f>
         <v>115</v>
       </c>
       <c r="AT2" s="3">
         <v>10</v>
       </c>
       <c r="AU2" s="3">
-        <f>+AA2-R2</f>
+        <f t="shared" ref="AU2:AU33" si="14">+AA2-R2</f>
         <v>11</v>
       </c>
       <c r="AV2" s="3" t="s">
@@ -2074,11 +2082,11 @@
         <v>22</v>
       </c>
       <c r="P3" s="3">
-        <f>+IF(I3="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q3" s="3">
-        <f>+IF(I3="SFK Freight Forwarder",O3,O3+P3-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R3" s="3">
@@ -2089,18 +2097,18 @@
         <v>7</v>
       </c>
       <c r="T3" s="3">
-        <f>+R3+S3-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U3" s="3">
-        <f>+T3+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V3" s="3">
         <v>2</v>
       </c>
       <c r="W3" s="3">
-        <f>+U3+V3-1</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="X3" s="3">
@@ -2113,7 +2121,7 @@
         <v>33</v>
       </c>
       <c r="AA3" s="6">
-        <f>+Z3+AB3-1</f>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="AB3" s="3">
@@ -2129,21 +2137,21 @@
         <v>68</v>
       </c>
       <c r="AF3" s="3">
-        <f>+AE3+AA3-1</f>
+        <f t="shared" si="6"/>
         <v>102</v>
       </c>
       <c r="AG3" s="6">
         <v>3</v>
       </c>
       <c r="AH3" s="6">
-        <f>+AF3+AG3</f>
+        <f t="shared" si="7"/>
         <v>105</v>
       </c>
       <c r="AI3" s="3">
         <v>7</v>
       </c>
       <c r="AJ3" s="3">
-        <f>+AI3+AH3</f>
+        <f t="shared" si="8"/>
         <v>112</v>
       </c>
       <c r="AK3" s="3" t="s">
@@ -2153,36 +2161,36 @@
         <v>2</v>
       </c>
       <c r="AM3" s="3">
-        <f>+AJ3+AL3</f>
+        <f t="shared" si="9"/>
         <v>114</v>
       </c>
       <c r="AN3" s="3">
         <v>2</v>
       </c>
       <c r="AO3" s="3">
-        <f>+AM3+AN3</f>
+        <f t="shared" si="10"/>
         <v>116</v>
       </c>
       <c r="AP3" s="3">
         <v>3</v>
       </c>
       <c r="AQ3" s="3">
-        <f>+AO3+AP3</f>
+        <f t="shared" si="11"/>
         <v>119</v>
       </c>
       <c r="AR3" s="3">
-        <f>+AQ3+7</f>
+        <f t="shared" si="12"/>
         <v>126</v>
       </c>
       <c r="AS3" s="3">
-        <f>+AR3+7+AT3</f>
+        <f t="shared" si="13"/>
         <v>143</v>
       </c>
       <c r="AT3" s="3">
         <v>10</v>
       </c>
       <c r="AU3" s="3">
-        <f>+AA3-R3</f>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="AV3" s="3" t="s">
@@ -2247,11 +2255,11 @@
         <v>22</v>
       </c>
       <c r="P4" s="3">
-        <f>+IF(I4="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q4" s="3">
-        <f>+IF(I4="SFK Freight Forwarder",O4,O4+P4-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R4" s="3">
@@ -2262,18 +2270,18 @@
         <v>7</v>
       </c>
       <c r="T4" s="3">
-        <f>+R4+S4-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U4" s="3">
-        <f>+T4+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V4" s="3">
         <v>3</v>
       </c>
       <c r="W4" s="3">
-        <f>+U4+V4-1</f>
+        <f t="shared" si="4"/>
         <v>32</v>
       </c>
       <c r="X4" s="3">
@@ -2286,7 +2294,7 @@
         <v>33</v>
       </c>
       <c r="AA4" s="6">
-        <f>+Z4+AB4-1</f>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="AB4" s="3">
@@ -2302,21 +2310,21 @@
         <v>75</v>
       </c>
       <c r="AF4" s="3">
-        <f>+AE4+AA4-1</f>
+        <f t="shared" si="6"/>
         <v>109</v>
       </c>
       <c r="AG4" s="6">
         <v>3</v>
       </c>
       <c r="AH4" s="6">
-        <f>+AF4+AG4</f>
+        <f t="shared" si="7"/>
         <v>112</v>
       </c>
       <c r="AI4" s="3">
         <v>7</v>
       </c>
       <c r="AJ4" s="3">
-        <f>+AI4+AH4</f>
+        <f t="shared" si="8"/>
         <v>119</v>
       </c>
       <c r="AK4" s="3" t="s">
@@ -2326,36 +2334,36 @@
         <v>2</v>
       </c>
       <c r="AM4" s="3">
-        <f>+AJ4+AL4</f>
+        <f t="shared" si="9"/>
         <v>121</v>
       </c>
       <c r="AN4" s="3">
         <v>2</v>
       </c>
       <c r="AO4" s="3">
-        <f>+AM4+AN4</f>
+        <f t="shared" si="10"/>
         <v>123</v>
       </c>
       <c r="AP4" s="3">
         <v>3</v>
       </c>
       <c r="AQ4" s="3">
-        <f>+AO4+AP4</f>
+        <f t="shared" si="11"/>
         <v>126</v>
       </c>
       <c r="AR4" s="3">
-        <f>+AQ4+7</f>
+        <f t="shared" si="12"/>
         <v>133</v>
       </c>
       <c r="AS4" s="3">
-        <f>+AR4+7+AT4</f>
+        <f t="shared" si="13"/>
         <v>150</v>
       </c>
       <c r="AT4" s="3">
         <v>10</v>
       </c>
       <c r="AU4" s="3">
-        <f>+AA4-R4</f>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="AV4" s="3" t="s">
@@ -2420,11 +2428,11 @@
         <v>15</v>
       </c>
       <c r="P5" s="3">
-        <f>+IF(I5="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q5" s="3">
-        <f>+IF(I5="SFK Freight Forwarder",O5,O5+P5-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R5" s="3">
@@ -2435,18 +2443,18 @@
         <v>7</v>
       </c>
       <c r="T5" s="3">
-        <f>+R5+S5-1</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="U5" s="3">
-        <f>+T5+1</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="V5" s="3">
         <v>2</v>
       </c>
       <c r="W5" s="3">
-        <f>+U5+V5-1</f>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="X5" s="3">
@@ -2459,7 +2467,7 @@
         <v>31</v>
       </c>
       <c r="AA5" s="6">
-        <f>+Z5+AB5-1</f>
+        <f t="shared" si="5"/>
         <v>33</v>
       </c>
       <c r="AB5" s="3">
@@ -2475,21 +2483,21 @@
         <v>41</v>
       </c>
       <c r="AF5" s="3">
-        <f>+AE5+AA5-1</f>
+        <f t="shared" si="6"/>
         <v>73</v>
       </c>
       <c r="AG5" s="6">
         <v>3</v>
       </c>
       <c r="AH5" s="6">
-        <f>+AF5+AG5</f>
+        <f t="shared" si="7"/>
         <v>76</v>
       </c>
       <c r="AI5" s="3">
         <v>0</v>
       </c>
       <c r="AJ5" s="3">
-        <f>+AI5+AH5</f>
+        <f t="shared" si="8"/>
         <v>76</v>
       </c>
       <c r="AK5" s="3" t="s">
@@ -2499,36 +2507,36 @@
         <v>2</v>
       </c>
       <c r="AM5" s="3">
-        <f>+AJ5+AL5</f>
+        <f t="shared" si="9"/>
         <v>78</v>
       </c>
       <c r="AN5" s="3">
         <v>2</v>
       </c>
       <c r="AO5" s="3">
-        <f>+AM5+AN5</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="AP5" s="3">
         <v>4</v>
       </c>
       <c r="AQ5" s="3">
-        <f>+AO5+AP5</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR5" s="3">
-        <f>+AQ5+7</f>
+        <f t="shared" si="12"/>
         <v>91</v>
       </c>
       <c r="AS5" s="3">
-        <f>+AR5+7+AT5</f>
+        <f t="shared" si="13"/>
         <v>104</v>
       </c>
       <c r="AT5" s="3">
         <v>6</v>
       </c>
       <c r="AU5" s="3">
-        <f>+AA5-R5</f>
+        <f t="shared" si="14"/>
         <v>17</v>
       </c>
       <c r="AV5" s="3" t="s">
@@ -2593,11 +2601,11 @@
         <v>15</v>
       </c>
       <c r="P6" s="3">
-        <f>+IF(I6="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q6" s="3">
-        <f>+IF(I6="SFK Freight Forwarder",O6,O6+P6-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R6" s="3">
@@ -2608,18 +2616,18 @@
         <v>7</v>
       </c>
       <c r="T6" s="3">
-        <f>+R6+S6-1</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="U6" s="3">
-        <f>+T6+1</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="V6" s="3">
         <v>4</v>
       </c>
       <c r="W6" s="3">
-        <f>+U6+V6-1</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="X6" s="3">
@@ -2632,7 +2640,7 @@
         <v>30</v>
       </c>
       <c r="AA6" s="6">
-        <f>+Z6+AB6-1</f>
+        <f t="shared" si="5"/>
         <v>32</v>
       </c>
       <c r="AB6" s="3">
@@ -2648,21 +2656,21 @@
         <v>46</v>
       </c>
       <c r="AF6" s="3">
-        <f>+AE6+AA6-1</f>
+        <f t="shared" si="6"/>
         <v>77</v>
       </c>
       <c r="AG6" s="6">
         <v>3</v>
       </c>
       <c r="AH6" s="6">
-        <f>+AF6+AG6</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="AI6" s="3">
         <v>0</v>
       </c>
       <c r="AJ6" s="3">
-        <f>+AI6+AH6</f>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="AK6" s="3" t="s">
@@ -2672,36 +2680,36 @@
         <v>4</v>
       </c>
       <c r="AM6" s="3">
-        <f>+AJ6+AL6</f>
+        <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="AN6" s="3">
         <v>3</v>
       </c>
       <c r="AO6" s="3">
-        <f>+AM6+AN6</f>
+        <f t="shared" si="10"/>
         <v>87</v>
       </c>
       <c r="AP6" s="3">
         <v>4</v>
       </c>
       <c r="AQ6" s="3">
-        <f>+AO6+AP6</f>
+        <f t="shared" si="11"/>
         <v>91</v>
       </c>
       <c r="AR6" s="3">
-        <f>+AQ6+7</f>
+        <f t="shared" si="12"/>
         <v>98</v>
       </c>
       <c r="AS6" s="3">
-        <f>+AR6+7+AT6</f>
+        <f t="shared" si="13"/>
         <v>112</v>
       </c>
       <c r="AT6" s="3">
         <v>7</v>
       </c>
       <c r="AU6" s="3">
-        <f>+AA6-R6</f>
+        <f t="shared" si="14"/>
         <v>16</v>
       </c>
       <c r="AV6" s="3" t="s">
@@ -2764,11 +2772,11 @@
         <v>0</v>
       </c>
       <c r="P7" s="3">
-        <f>+IF(I7="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q7" s="3">
-        <f>+IF(I7="SFK Freight Forwarder",O7,O7+P7-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R7" s="3">
@@ -2778,18 +2786,18 @@
         <v>7</v>
       </c>
       <c r="T7" s="3">
-        <f>+R7+S7-1</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="U7" s="3">
-        <f>+T7+1</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="V7" s="3">
         <v>8</v>
       </c>
       <c r="W7" s="3">
-        <f>+U7+V7-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X7" s="3">
@@ -2803,7 +2811,7 @@
         <v>33</v>
       </c>
       <c r="AA7" s="6">
-        <f>+Z7+AB7-1</f>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="AB7" s="3">
@@ -2819,21 +2827,21 @@
         <v>43</v>
       </c>
       <c r="AF7" s="3">
-        <f>+AE7+AA7-1</f>
+        <f t="shared" si="6"/>
         <v>77</v>
       </c>
       <c r="AG7" s="6">
         <v>3</v>
       </c>
       <c r="AH7" s="6">
-        <f>+AF7+AG7</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="AI7" s="3">
         <v>0</v>
       </c>
       <c r="AJ7" s="3">
-        <f>+AI7+AH7</f>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="AK7" s="3" t="s">
@@ -2843,36 +2851,36 @@
         <v>2</v>
       </c>
       <c r="AM7" s="3">
-        <f>+AJ7+AL7</f>
+        <f t="shared" si="9"/>
         <v>82</v>
       </c>
       <c r="AN7" s="3">
         <v>2</v>
       </c>
       <c r="AO7" s="3">
-        <f>+AM7+AN7</f>
+        <f t="shared" si="10"/>
         <v>84</v>
       </c>
       <c r="AP7" s="3">
         <v>0</v>
       </c>
       <c r="AQ7" s="3">
-        <f>+AO7+AP7</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR7" s="3">
-        <f>+AQ7+7</f>
+        <f t="shared" si="12"/>
         <v>91</v>
       </c>
       <c r="AS7" s="3">
-        <f>+AR7+7+AT7</f>
+        <f t="shared" si="13"/>
         <v>98</v>
       </c>
       <c r="AT7" s="3">
         <v>0</v>
       </c>
       <c r="AU7" s="3">
-        <f>+AA7-R7</f>
+        <f t="shared" si="14"/>
         <v>19</v>
       </c>
       <c r="AV7" s="3" t="s">
@@ -2932,15 +2940,15 @@
         <v>0</v>
       </c>
       <c r="O8" s="3">
-        <f>IF(I8="SFK Freight Forwarder",M8,M8+N8-1)</f>
+        <f t="shared" ref="O8:O54" si="15">IF(I8="SFK Freight Forwarder",M8,M8+N8-1)</f>
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <f>+IF(I8="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q8" s="3">
-        <f>+IF(I8="SFK Freight Forwarder",O8,O8+P8-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R8" s="3">
@@ -2950,18 +2958,18 @@
         <v>7</v>
       </c>
       <c r="T8" s="3">
-        <f>+R8+S8-1</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="U8" s="3">
-        <f>+T8+1</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="V8" s="3">
         <v>8</v>
       </c>
       <c r="W8" s="3">
-        <f>+U8+V8-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X8" s="3">
@@ -2989,21 +2997,21 @@
         <v>38</v>
       </c>
       <c r="AF8" s="3">
-        <f>+AE8+AA8-1</f>
+        <f t="shared" si="6"/>
         <v>72</v>
       </c>
       <c r="AG8" s="6">
         <v>3</v>
       </c>
       <c r="AH8" s="6">
-        <f>+AF8+AG8</f>
+        <f t="shared" si="7"/>
         <v>75</v>
       </c>
       <c r="AI8" s="3">
         <v>7</v>
       </c>
       <c r="AJ8" s="3">
-        <f>+AI8+AH8</f>
+        <f t="shared" si="8"/>
         <v>82</v>
       </c>
       <c r="AK8" s="3" t="s">
@@ -3013,36 +3021,36 @@
         <v>3</v>
       </c>
       <c r="AM8" s="3">
-        <f>+AJ8+AL8</f>
+        <f t="shared" si="9"/>
         <v>85</v>
       </c>
       <c r="AN8" s="3">
         <v>6</v>
       </c>
       <c r="AO8" s="3">
-        <f>+AM8+AN8</f>
+        <f t="shared" si="10"/>
         <v>91</v>
       </c>
       <c r="AP8" s="3">
         <v>0</v>
       </c>
       <c r="AQ8" s="3">
-        <f>+AO8+AP8</f>
+        <f t="shared" si="11"/>
         <v>91</v>
       </c>
       <c r="AR8" s="3">
-        <f>+AQ8+7</f>
+        <f t="shared" si="12"/>
         <v>98</v>
       </c>
       <c r="AS8" s="3">
-        <f>+AR8+7+AT8</f>
+        <f t="shared" si="13"/>
         <v>105</v>
       </c>
       <c r="AT8" s="3">
         <v>0</v>
       </c>
       <c r="AU8" s="3">
-        <f>+AA8-R8</f>
+        <f t="shared" si="14"/>
         <v>19</v>
       </c>
       <c r="AV8" s="3" t="s">
@@ -3102,37 +3110,37 @@
         <v>7</v>
       </c>
       <c r="O9" s="3">
-        <f>IF(I9="SFK Freight Forwarder",M9,M9+N9-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P9" s="3">
-        <f>+IF(I9="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <f>+IF(I9="SFK Freight Forwarder",O9,O9+P9-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R9" s="3">
-        <f>9+N9</f>
+        <f t="shared" ref="R9:R44" si="16">9+N9</f>
         <v>16</v>
       </c>
       <c r="S9" s="3">
         <v>7</v>
       </c>
       <c r="T9" s="3">
-        <f>+R9+S9-1</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="U9" s="3">
-        <f>+T9+1</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="V9" s="3">
         <v>8</v>
       </c>
       <c r="W9" s="3">
-        <f>+U9+V9-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X9" s="3">
@@ -3145,7 +3153,7 @@
         <v>36</v>
       </c>
       <c r="AA9" s="6">
-        <f>+Z9+AB9-1</f>
+        <f t="shared" ref="AA9:AA16" si="17">+Z9+AB9-1</f>
         <v>38</v>
       </c>
       <c r="AB9" s="3">
@@ -3161,21 +3169,21 @@
         <v>16</v>
       </c>
       <c r="AF9" s="3">
-        <f>+AE9+AA9-1</f>
+        <f t="shared" si="6"/>
         <v>53</v>
       </c>
       <c r="AG9" s="6">
         <v>3</v>
       </c>
       <c r="AH9" s="6">
-        <f>+AF9+AG9</f>
+        <f t="shared" si="7"/>
         <v>56</v>
       </c>
       <c r="AI9" s="3">
         <v>7</v>
       </c>
       <c r="AJ9" s="3">
-        <f>+AI9+AH9</f>
+        <f t="shared" si="8"/>
         <v>63</v>
       </c>
       <c r="AK9" s="3" t="s">
@@ -3185,36 +3193,36 @@
         <v>4</v>
       </c>
       <c r="AM9" s="3">
-        <f>+AJ9+AL9</f>
+        <f t="shared" si="9"/>
         <v>67</v>
       </c>
       <c r="AN9" s="3">
         <v>3</v>
       </c>
       <c r="AO9" s="3">
-        <f>+AM9+AN9</f>
+        <f t="shared" si="10"/>
         <v>70</v>
       </c>
       <c r="AP9" s="3">
         <v>0</v>
       </c>
       <c r="AQ9" s="3">
-        <f>+AO9+AP9</f>
+        <f t="shared" si="11"/>
         <v>70</v>
       </c>
       <c r="AR9" s="3">
-        <f>+AQ9+7</f>
+        <f t="shared" si="12"/>
         <v>77</v>
       </c>
       <c r="AS9" s="3">
-        <f>+AR9+7+AT9</f>
+        <f t="shared" si="13"/>
         <v>84</v>
       </c>
       <c r="AT9" s="3">
         <v>0</v>
       </c>
       <c r="AU9" s="3">
-        <f>+AA9-R9</f>
+        <f t="shared" si="14"/>
         <v>22</v>
       </c>
       <c r="AV9" s="3" t="s">
@@ -3268,44 +3276,44 @@
         <v>7</v>
       </c>
       <c r="M10" s="3">
-        <f>+IF(I10="SFK Freight Forwarder",L10,9)</f>
+        <f t="shared" ref="M10:M29" si="18">+IF(I10="SFK Freight Forwarder",L10,9)</f>
         <v>9</v>
       </c>
       <c r="N10" s="3">
         <v>7</v>
       </c>
       <c r="O10" s="3">
-        <f>IF(I10="SFK Freight Forwarder",M10,M10+N10-1)</f>
+        <f t="shared" si="15"/>
         <v>15</v>
       </c>
       <c r="P10" s="3">
-        <f>+IF(I10="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q10" s="3">
-        <f>+IF(I10="SFK Freight Forwarder",O10,O10+P10-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R10" s="3">
-        <f>9+N10</f>
+        <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="S10" s="3">
         <v>7</v>
       </c>
       <c r="T10" s="3">
-        <f>+R10+S10-1</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="U10" s="3">
-        <f>+T10+1</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="V10" s="3">
         <v>4</v>
       </c>
       <c r="W10" s="3">
-        <f>+U10+V10-1</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="X10" s="3">
@@ -3318,7 +3326,7 @@
         <v>30</v>
       </c>
       <c r="AA10" s="6">
-        <f>+Z10+AB10-1</f>
+        <f t="shared" si="17"/>
         <v>32</v>
       </c>
       <c r="AB10" s="3">
@@ -3334,21 +3342,21 @@
         <v>49</v>
       </c>
       <c r="AF10" s="3">
-        <f>+AE10+AA10-1</f>
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="AG10" s="6">
         <v>3</v>
       </c>
       <c r="AH10" s="6">
-        <f>+AF10+AG10</f>
+        <f t="shared" si="7"/>
         <v>83</v>
       </c>
       <c r="AI10" s="3">
         <v>0</v>
       </c>
       <c r="AJ10" s="3">
-        <f>+AI10+AH10</f>
+        <f t="shared" si="8"/>
         <v>83</v>
       </c>
       <c r="AK10" s="3" t="s">
@@ -3358,36 +3366,36 @@
         <v>1</v>
       </c>
       <c r="AM10" s="3">
-        <f>+AJ10+AL10</f>
+        <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="AN10" s="3">
         <v>8</v>
       </c>
       <c r="AO10" s="3">
-        <f>+AM10+AN10</f>
+        <f t="shared" si="10"/>
         <v>92</v>
       </c>
       <c r="AP10" s="3">
         <v>6</v>
       </c>
       <c r="AQ10" s="3">
-        <f>+AO10+AP10</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR10" s="3">
-        <f>+AQ10+7</f>
+        <f t="shared" si="12"/>
         <v>105</v>
       </c>
       <c r="AS10" s="3">
-        <f>+AR10+7+AT10</f>
+        <f t="shared" si="13"/>
         <v>119</v>
       </c>
       <c r="AT10" s="3">
         <v>7</v>
       </c>
       <c r="AU10" s="3">
-        <f>+AA10-R10</f>
+        <f t="shared" si="14"/>
         <v>16</v>
       </c>
       <c r="AV10" s="3" t="s">
@@ -3441,44 +3449,44 @@
         <v>2</v>
       </c>
       <c r="M11" s="3">
-        <f>+IF(I11="SFK Freight Forwarder",L11,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N11" s="3">
         <v>14</v>
       </c>
       <c r="O11" s="3">
-        <f>IF(I11="SFK Freight Forwarder",M11,M11+N11-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P11" s="3">
-        <f>+IF(I11="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q11" s="3">
-        <f>+IF(I11="SFK Freight Forwarder",O11,O11+P11-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R11" s="3">
-        <f>9+N11</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S11" s="3">
         <v>7</v>
       </c>
       <c r="T11" s="3">
-        <f>+R11+S11-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U11" s="3">
-        <f>+T11+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V11" s="3">
         <v>1</v>
       </c>
       <c r="W11" s="3">
-        <f>+U11+V11-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X11" s="3">
@@ -3491,7 +3499,7 @@
         <v>37</v>
       </c>
       <c r="AA11" s="6">
-        <f>+Z11+AB11-1</f>
+        <f t="shared" si="17"/>
         <v>39</v>
       </c>
       <c r="AB11" s="3">
@@ -3507,21 +3515,21 @@
         <v>57</v>
       </c>
       <c r="AF11" s="3">
-        <f>+AE11+AA11-1</f>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="AG11" s="6">
         <v>3</v>
       </c>
       <c r="AH11" s="6">
-        <f>+AF11+AG11</f>
+        <f t="shared" si="7"/>
         <v>98</v>
       </c>
       <c r="AI11" s="3">
         <v>14</v>
       </c>
       <c r="AJ11" s="3">
-        <f>+AI11+AH11</f>
+        <f t="shared" si="8"/>
         <v>112</v>
       </c>
       <c r="AK11" s="3" t="s">
@@ -3531,36 +3539,36 @@
         <v>4</v>
       </c>
       <c r="AM11" s="3">
-        <f>+AJ11+AL11</f>
+        <f t="shared" si="9"/>
         <v>116</v>
       </c>
       <c r="AN11" s="3">
         <v>3</v>
       </c>
       <c r="AO11" s="3">
-        <f>+AM11+AN11</f>
+        <f t="shared" si="10"/>
         <v>119</v>
       </c>
       <c r="AP11" s="3">
         <v>0</v>
       </c>
       <c r="AQ11" s="3">
-        <f>+AO11+AP11</f>
+        <f t="shared" si="11"/>
         <v>119</v>
       </c>
       <c r="AR11" s="3">
-        <f>+AQ11+7</f>
+        <f t="shared" si="12"/>
         <v>126</v>
       </c>
       <c r="AS11" s="3">
-        <f>+AR11+7+AT11</f>
+        <f t="shared" si="13"/>
         <v>147</v>
       </c>
       <c r="AT11" s="3">
         <v>14</v>
       </c>
       <c r="AU11" s="3">
-        <f>+AA11-R11</f>
+        <f t="shared" si="14"/>
         <v>16</v>
       </c>
       <c r="AV11" s="3" t="s">
@@ -3614,44 +3622,44 @@
         <v>7</v>
       </c>
       <c r="M12" s="3">
-        <f>+IF(I12="SFK Freight Forwarder",L12,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N12" s="3">
         <v>14</v>
       </c>
       <c r="O12" s="3">
-        <f>IF(I12="SFK Freight Forwarder",M12,M12+N12-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P12" s="3">
-        <f>+IF(I12="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q12" s="3">
-        <f>+IF(I12="SFK Freight Forwarder",O12,O12+P12-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R12" s="3">
-        <f>9+N12</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S12" s="3">
         <v>7</v>
       </c>
       <c r="T12" s="3">
-        <f>+R12+S12-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U12" s="3">
-        <f>+T12+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V12" s="3">
         <v>1</v>
       </c>
       <c r="W12" s="3">
-        <f>+U12+V12-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X12" s="3">
@@ -3664,7 +3672,7 @@
         <v>37</v>
       </c>
       <c r="AA12" s="6">
-        <f>+Z12+AB12-1</f>
+        <f t="shared" si="17"/>
         <v>38</v>
       </c>
       <c r="AB12" s="3">
@@ -3680,21 +3688,21 @@
         <v>47</v>
       </c>
       <c r="AF12" s="3">
-        <f>+AE12+AA12-1</f>
+        <f t="shared" si="6"/>
         <v>84</v>
       </c>
       <c r="AG12" s="6">
         <v>3</v>
       </c>
       <c r="AH12" s="6">
-        <f>+AF12+AG12</f>
+        <f t="shared" si="7"/>
         <v>87</v>
       </c>
       <c r="AI12" s="3">
         <v>14</v>
       </c>
       <c r="AJ12" s="3">
-        <f>+AI12+AH12</f>
+        <f t="shared" si="8"/>
         <v>101</v>
       </c>
       <c r="AK12" s="3" t="s">
@@ -3704,36 +3712,36 @@
         <v>2</v>
       </c>
       <c r="AM12" s="3">
-        <f>+AJ12+AL12</f>
+        <f t="shared" si="9"/>
         <v>103</v>
       </c>
       <c r="AN12" s="3">
         <v>2</v>
       </c>
       <c r="AO12" s="3">
-        <f>+AM12+AN12</f>
+        <f t="shared" si="10"/>
         <v>105</v>
       </c>
       <c r="AP12" s="3">
         <v>0</v>
       </c>
       <c r="AQ12" s="3">
-        <f>+AO12+AP12</f>
+        <f t="shared" si="11"/>
         <v>105</v>
       </c>
       <c r="AR12" s="3">
-        <f>+AQ12+7</f>
+        <f t="shared" si="12"/>
         <v>112</v>
       </c>
       <c r="AS12" s="3">
-        <f>+AR12+7+AT12</f>
+        <f t="shared" si="13"/>
         <v>134</v>
       </c>
       <c r="AT12" s="3">
         <v>15</v>
       </c>
       <c r="AU12" s="3">
-        <f>+AA12-R12</f>
+        <f t="shared" si="14"/>
         <v>15</v>
       </c>
       <c r="AV12" s="3" t="s">
@@ -3787,44 +3795,44 @@
         <v>7</v>
       </c>
       <c r="M13" s="3">
-        <f>+IF(I13="SFK Freight Forwarder",L13,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N13" s="3">
         <v>7</v>
       </c>
       <c r="O13" s="3">
-        <f>IF(I13="SFK Freight Forwarder",M13,M13+N13-1)</f>
+        <f t="shared" si="15"/>
         <v>15</v>
       </c>
       <c r="P13" s="3">
-        <f>+IF(I13="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q13" s="3">
-        <f>+IF(I13="SFK Freight Forwarder",O13,O13+P13-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R13" s="3">
-        <f>9+N13</f>
+        <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="S13" s="3">
         <v>7</v>
       </c>
       <c r="T13" s="3">
-        <f>+R13+S13-1</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="U13" s="3">
-        <f>+T13+1</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="V13" s="3">
         <v>1</v>
       </c>
       <c r="W13" s="3">
-        <f>+U13+V13-1</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="X13" s="3">
@@ -3837,7 +3845,7 @@
         <v>31</v>
       </c>
       <c r="AA13" s="6">
-        <f>+Z13+AB13-1</f>
+        <f t="shared" si="17"/>
         <v>34</v>
       </c>
       <c r="AB13" s="3">
@@ -3853,21 +3861,21 @@
         <v>40</v>
       </c>
       <c r="AF13" s="3">
-        <f>+AE13+AA13-1</f>
+        <f t="shared" si="6"/>
         <v>73</v>
       </c>
       <c r="AG13" s="6">
         <v>3</v>
       </c>
       <c r="AH13" s="6">
-        <f>+AF13+AG13</f>
+        <f t="shared" si="7"/>
         <v>76</v>
       </c>
       <c r="AI13" s="3">
         <v>0</v>
       </c>
       <c r="AJ13" s="3">
-        <f>+AI13+AH13</f>
+        <f t="shared" si="8"/>
         <v>76</v>
       </c>
       <c r="AK13" s="3" t="s">
@@ -3877,36 +3885,36 @@
         <v>2</v>
       </c>
       <c r="AM13" s="3">
-        <f>+AJ13+AL13</f>
+        <f t="shared" si="9"/>
         <v>78</v>
       </c>
       <c r="AN13" s="3">
         <v>2</v>
       </c>
       <c r="AO13" s="3">
-        <f>+AM13+AN13</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="AP13" s="3">
         <v>4</v>
       </c>
       <c r="AQ13" s="3">
-        <f>+AO13+AP13</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR13" s="3">
-        <f>+AQ13+7</f>
+        <f t="shared" si="12"/>
         <v>91</v>
       </c>
       <c r="AS13" s="3">
-        <f>+AR13+7+AT13</f>
+        <f t="shared" si="13"/>
         <v>112</v>
       </c>
       <c r="AT13" s="3">
         <v>14</v>
       </c>
       <c r="AU13" s="3">
-        <f>+AA13-R13</f>
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
       <c r="AV13" s="3" t="s">
@@ -3960,44 +3968,44 @@
         <v>7</v>
       </c>
       <c r="M14" s="3">
-        <f>+IF(I14="SFK Freight Forwarder",L14,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N14" s="3">
         <v>14</v>
       </c>
       <c r="O14" s="3">
-        <f>IF(I14="SFK Freight Forwarder",M14,M14+N14-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P14" s="3">
-        <f>+IF(I14="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q14" s="3">
-        <f>+IF(I14="SFK Freight Forwarder",O14,O14+P14-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R14" s="3">
-        <f>9+N14</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S14" s="3">
         <v>7</v>
       </c>
       <c r="T14" s="3">
-        <f>+R14+S14-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U14" s="3">
-        <f>+T14+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V14" s="3">
         <v>4</v>
       </c>
       <c r="W14" s="3">
-        <f>+U14+V14-1</f>
+        <f t="shared" si="4"/>
         <v>33</v>
       </c>
       <c r="X14" s="3">
@@ -4010,7 +4018,7 @@
         <v>36</v>
       </c>
       <c r="AA14" s="6">
-        <f>+Z14+AB14-1</f>
+        <f t="shared" si="17"/>
         <v>37</v>
       </c>
       <c r="AB14" s="3">
@@ -4026,21 +4034,21 @@
         <v>37</v>
       </c>
       <c r="AF14" s="3">
-        <f>+AE14+AA14-1</f>
+        <f t="shared" si="6"/>
         <v>73</v>
       </c>
       <c r="AG14" s="6">
         <v>3</v>
       </c>
       <c r="AH14" s="6">
-        <f>+AF14+AG14</f>
+        <f t="shared" si="7"/>
         <v>76</v>
       </c>
       <c r="AI14" s="3">
         <v>7</v>
       </c>
       <c r="AJ14" s="3">
-        <f>+AI14+AH14</f>
+        <f t="shared" si="8"/>
         <v>83</v>
       </c>
       <c r="AK14" s="28" t="s">
@@ -4050,36 +4058,36 @@
         <v>2</v>
       </c>
       <c r="AM14" s="3">
-        <f>+AJ14+AL14</f>
+        <f t="shared" si="9"/>
         <v>85</v>
       </c>
       <c r="AN14" s="3">
         <v>2</v>
       </c>
       <c r="AO14" s="3">
-        <f>+AM14+AN14</f>
+        <f t="shared" si="10"/>
         <v>87</v>
       </c>
       <c r="AP14" s="3">
         <v>4</v>
       </c>
       <c r="AQ14" s="3">
-        <f>+AO14+AP14</f>
+        <f t="shared" si="11"/>
         <v>91</v>
       </c>
       <c r="AR14" s="3">
-        <f>+AQ14+7</f>
+        <f t="shared" si="12"/>
         <v>98</v>
       </c>
       <c r="AS14" s="3">
-        <f>+AR14+7+AT14</f>
+        <f t="shared" si="13"/>
         <v>121</v>
       </c>
       <c r="AT14" s="3">
         <v>16</v>
       </c>
       <c r="AU14" s="3">
-        <f>+AA14-R14</f>
+        <f t="shared" si="14"/>
         <v>14</v>
       </c>
       <c r="AV14" s="3" t="s">
@@ -4133,44 +4141,44 @@
         <v>7</v>
       </c>
       <c r="M15" s="3">
-        <f>+IF(I15="SFK Freight Forwarder",L15,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N15" s="3">
         <v>14</v>
       </c>
       <c r="O15" s="3">
-        <f>IF(I15="SFK Freight Forwarder",M15,M15+N15-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P15" s="3">
-        <f>+IF(I15="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q15" s="3">
-        <f>+IF(I15="SFK Freight Forwarder",O15,O15+P15-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R15" s="3">
-        <f>9+N15</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S15" s="3">
         <v>7</v>
       </c>
       <c r="T15" s="3">
-        <f>+R15+S15-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U15" s="3">
-        <f>+T15+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V15" s="3">
         <v>1</v>
       </c>
       <c r="W15" s="3">
-        <f>+U15+V15-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X15" s="3">
@@ -4184,7 +4192,7 @@
         <v>37</v>
       </c>
       <c r="AA15" s="6">
-        <f>+Z15+AB15-1</f>
+        <f t="shared" si="17"/>
         <v>39</v>
       </c>
       <c r="AB15" s="3">
@@ -4200,21 +4208,21 @@
         <v>26</v>
       </c>
       <c r="AF15" s="3">
-        <f>+AE15+AA15-1</f>
+        <f t="shared" si="6"/>
         <v>64</v>
       </c>
       <c r="AG15" s="6">
         <v>3</v>
       </c>
       <c r="AH15" s="6">
-        <f>+AF15+AG15</f>
+        <f t="shared" si="7"/>
         <v>67</v>
       </c>
       <c r="AI15" s="3">
         <v>7</v>
       </c>
       <c r="AJ15" s="3">
-        <f>+AI15+AH15</f>
+        <f t="shared" si="8"/>
         <v>74</v>
       </c>
       <c r="AK15" s="3" t="s">
@@ -4224,36 +4232,36 @@
         <v>2</v>
       </c>
       <c r="AM15" s="3">
-        <f>+AJ15+AL15</f>
+        <f t="shared" si="9"/>
         <v>76</v>
       </c>
       <c r="AN15" s="3">
         <v>2</v>
       </c>
       <c r="AO15" s="3">
-        <f>+AM15+AN15</f>
+        <f t="shared" si="10"/>
         <v>78</v>
       </c>
       <c r="AP15" s="3">
         <v>6</v>
       </c>
       <c r="AQ15" s="3">
-        <f>+AO15+AP15</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR15" s="3">
-        <f>+AQ15+7</f>
+        <f t="shared" si="12"/>
         <v>91</v>
       </c>
       <c r="AS15" s="3">
-        <f>+AR15+7+AT15</f>
+        <f t="shared" si="13"/>
         <v>112</v>
       </c>
       <c r="AT15" s="3">
         <v>14</v>
       </c>
       <c r="AU15" s="3">
-        <f>+AA15-R15</f>
+        <f t="shared" si="14"/>
         <v>16</v>
       </c>
       <c r="AV15" s="3" t="s">
@@ -4307,44 +4315,44 @@
         <v>7</v>
       </c>
       <c r="M16" s="3">
-        <f>+IF(I16="SFK Freight Forwarder",L16,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N16" s="3">
         <v>14</v>
       </c>
       <c r="O16" s="3">
-        <f>IF(I16="SFK Freight Forwarder",M16,M16+N16-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P16" s="3">
-        <f>+IF(I16="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q16" s="3">
-        <f>+IF(I16="SFK Freight Forwarder",O16,O16+P16-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R16" s="3">
-        <f>9+N16</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S16" s="3">
         <v>7</v>
       </c>
       <c r="T16" s="3">
-        <f>+R16+S16-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U16" s="3">
-        <f>+T16+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V16" s="3">
         <v>4</v>
       </c>
       <c r="W16" s="3">
-        <f>+U16+V16-1</f>
+        <f t="shared" si="4"/>
         <v>33</v>
       </c>
       <c r="X16" s="3">
@@ -4357,7 +4365,7 @@
         <v>33</v>
       </c>
       <c r="AA16" s="6">
-        <f>+Z16+AB16-1</f>
+        <f t="shared" si="17"/>
         <v>35</v>
       </c>
       <c r="AB16" s="3">
@@ -4373,21 +4381,21 @@
         <v>44</v>
       </c>
       <c r="AF16" s="3">
-        <f>+AE16+AA16-1</f>
+        <f t="shared" si="6"/>
         <v>78</v>
       </c>
       <c r="AG16" s="6">
         <v>3</v>
       </c>
       <c r="AH16" s="6">
-        <f>+AF16+AG16</f>
+        <f t="shared" si="7"/>
         <v>81</v>
       </c>
       <c r="AI16" s="3">
         <v>7</v>
       </c>
       <c r="AJ16" s="3">
-        <f>+AI16+AH16</f>
+        <f t="shared" si="8"/>
         <v>88</v>
       </c>
       <c r="AK16" s="3" t="s">
@@ -4397,36 +4405,36 @@
         <v>2</v>
       </c>
       <c r="AM16" s="3">
-        <f>+AJ16+AL16</f>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="AN16" s="3">
         <v>2</v>
       </c>
       <c r="AO16" s="3">
-        <f>+AM16+AN16</f>
+        <f t="shared" si="10"/>
         <v>92</v>
       </c>
       <c r="AP16" s="3">
         <v>6</v>
       </c>
       <c r="AQ16" s="3">
-        <f>+AO16+AP16</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR16" s="3">
-        <f>+AQ16+7</f>
+        <f t="shared" si="12"/>
         <v>105</v>
       </c>
       <c r="AS16" s="3">
-        <f>+AR16+7+AT16</f>
+        <f t="shared" si="13"/>
         <v>121</v>
       </c>
       <c r="AT16" s="3">
         <v>9</v>
       </c>
       <c r="AU16" s="3">
-        <f>+AA16-R16</f>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="AV16" s="3" t="s">
@@ -4480,44 +4488,44 @@
         <v>7</v>
       </c>
       <c r="M17" s="3">
-        <f>+IF(I17="SFK Freight Forwarder",L17,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N17" s="3">
         <v>14</v>
       </c>
       <c r="O17" s="3">
-        <f>IF(I17="SFK Freight Forwarder",M17,M17+N17-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P17" s="3">
-        <f>+IF(I17="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q17" s="3">
-        <f>+IF(I17="SFK Freight Forwarder",O17,O17+P17-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R17" s="3">
-        <f>9+N17</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S17" s="3">
         <v>7</v>
       </c>
       <c r="T17" s="3">
-        <f>+R17+S17-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U17" s="3">
-        <f>+T17+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V17" s="3">
         <v>2</v>
       </c>
       <c r="W17" s="3">
-        <f>+U17+V17-1</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="X17" s="3">
@@ -4545,21 +4553,21 @@
         <v>43</v>
       </c>
       <c r="AF17" s="3">
-        <f>+AE17+AA17-1</f>
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="AG17" s="6">
         <v>3</v>
       </c>
       <c r="AH17" s="6">
-        <f>+AF17+AG17</f>
+        <f t="shared" si="7"/>
         <v>83</v>
       </c>
       <c r="AI17" s="3">
         <v>14</v>
       </c>
       <c r="AJ17" s="3">
-        <f>+AI17+AH17</f>
+        <f t="shared" si="8"/>
         <v>97</v>
       </c>
       <c r="AK17" s="3" t="s">
@@ -4569,36 +4577,36 @@
         <v>1</v>
       </c>
       <c r="AM17" s="3">
-        <f>+AJ17+AL17</f>
+        <f t="shared" si="9"/>
         <v>98</v>
       </c>
       <c r="AN17" s="3">
         <v>8</v>
       </c>
       <c r="AO17" s="3">
-        <f>+AM17+AN17</f>
+        <f t="shared" si="10"/>
         <v>106</v>
       </c>
       <c r="AP17" s="3">
         <v>6</v>
       </c>
       <c r="AQ17" s="3">
-        <f>+AO17+AP17</f>
+        <f t="shared" si="11"/>
         <v>112</v>
       </c>
       <c r="AR17" s="3">
-        <f>+AQ17+7</f>
+        <f t="shared" si="12"/>
         <v>119</v>
       </c>
       <c r="AS17" s="3">
-        <f>+AR17+7+AT17</f>
+        <f t="shared" si="13"/>
         <v>139</v>
       </c>
       <c r="AT17" s="3">
         <v>13</v>
       </c>
       <c r="AU17" s="3">
-        <f>+AA17-R17</f>
+        <f t="shared" si="14"/>
         <v>15</v>
       </c>
       <c r="AV17" s="3" t="s">
@@ -4652,44 +4660,44 @@
         <v>7</v>
       </c>
       <c r="M18" s="3">
-        <f>+IF(I18="SFK Freight Forwarder",L18,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N18" s="3">
         <v>7</v>
       </c>
       <c r="O18" s="3">
-        <f>IF(I18="SFK Freight Forwarder",M18,M18+N18-1)</f>
+        <f t="shared" si="15"/>
         <v>15</v>
       </c>
       <c r="P18" s="3">
-        <f>+IF(I18="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q18" s="3">
-        <f>+IF(I18="SFK Freight Forwarder",O18,O18+P18-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R18" s="3">
-        <f>9+N18</f>
+        <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="S18" s="3">
         <v>7</v>
       </c>
       <c r="T18" s="3">
-        <f>+R18+S18-1</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="U18" s="3">
-        <f>+T18+1</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="V18" s="3">
         <v>4</v>
       </c>
       <c r="W18" s="3">
-        <f>+U18+V18-1</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="X18" s="3">
@@ -4702,7 +4710,7 @@
         <v>31</v>
       </c>
       <c r="AA18" s="6">
-        <f>+Z18+AB18-1</f>
+        <f t="shared" ref="AA18:AA44" si="19">+Z18+AB18-1</f>
         <v>33</v>
       </c>
       <c r="AB18" s="3">
@@ -4718,21 +4726,21 @@
         <v>27</v>
       </c>
       <c r="AF18" s="3">
-        <f>+AE18+AA18-1</f>
+        <f t="shared" si="6"/>
         <v>59</v>
       </c>
       <c r="AG18" s="6">
         <v>3</v>
       </c>
       <c r="AH18" s="6">
-        <f>+AF18+AG18</f>
+        <f t="shared" si="7"/>
         <v>62</v>
       </c>
       <c r="AI18" s="3">
         <v>7</v>
       </c>
       <c r="AJ18" s="3">
-        <f>+AI18+AH18</f>
+        <f t="shared" si="8"/>
         <v>69</v>
       </c>
       <c r="AK18" s="3" t="s">
@@ -4742,36 +4750,36 @@
         <v>2</v>
       </c>
       <c r="AM18" s="3">
-        <f>+AJ18+AL18</f>
+        <f t="shared" si="9"/>
         <v>71</v>
       </c>
       <c r="AN18" s="3">
         <v>8</v>
       </c>
       <c r="AO18" s="3">
-        <f>+AM18+AN18</f>
+        <f t="shared" si="10"/>
         <v>79</v>
       </c>
       <c r="AP18" s="3">
         <v>2</v>
       </c>
       <c r="AQ18" s="3">
-        <f>+AO18+AP18</f>
+        <f t="shared" si="11"/>
         <v>81</v>
       </c>
       <c r="AR18" s="3">
-        <f>+AQ18+7</f>
+        <f t="shared" si="12"/>
         <v>88</v>
       </c>
       <c r="AS18" s="3">
-        <f>+AR18+7+AT18</f>
+        <f t="shared" si="13"/>
         <v>108</v>
       </c>
       <c r="AT18" s="3">
         <v>13</v>
       </c>
       <c r="AU18" s="3">
-        <f>+AA18-R18</f>
+        <f t="shared" si="14"/>
         <v>17</v>
       </c>
       <c r="AV18" s="3" t="s">
@@ -4825,44 +4833,44 @@
         <v>2</v>
       </c>
       <c r="M19" s="3">
-        <f>+IF(I19="SFK Freight Forwarder",L19,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N19" s="3">
         <v>14</v>
       </c>
       <c r="O19" s="3">
-        <f>IF(I19="SFK Freight Forwarder",M19,M19+N19-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P19" s="3">
-        <f>+IF(I19="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q19" s="3">
-        <f>+IF(I19="SFK Freight Forwarder",O19,O19+P19-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R19" s="3">
-        <f>9+N19</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S19" s="3">
         <v>7</v>
       </c>
       <c r="T19" s="3">
-        <f>+R19+S19-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U19" s="3">
-        <f>+T19+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V19" s="3">
         <v>2</v>
       </c>
       <c r="W19" s="3">
-        <f>+U19+V19-1</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="X19" s="3">
@@ -4875,7 +4883,7 @@
         <v>36</v>
       </c>
       <c r="AA19" s="6">
-        <f>+Z19+AB19-1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="AB19" s="3">
@@ -4891,21 +4899,21 @@
         <v>37</v>
       </c>
       <c r="AF19" s="3">
-        <f>+AE19+AA19-1</f>
+        <f t="shared" si="6"/>
         <v>73</v>
       </c>
       <c r="AG19" s="6">
         <v>3</v>
       </c>
       <c r="AH19" s="6">
-        <f>+AF19+AG19</f>
+        <f t="shared" si="7"/>
         <v>76</v>
       </c>
       <c r="AI19" s="3">
         <v>14</v>
       </c>
       <c r="AJ19" s="3">
-        <f>+AI19+AH19</f>
+        <f t="shared" si="8"/>
         <v>90</v>
       </c>
       <c r="AK19" s="3" t="s">
@@ -4915,36 +4923,36 @@
         <v>2</v>
       </c>
       <c r="AM19" s="3">
-        <f>+AJ19+AL19</f>
+        <f t="shared" si="9"/>
         <v>92</v>
       </c>
       <c r="AN19" s="3">
         <v>2</v>
       </c>
       <c r="AO19" s="3">
-        <f>+AM19+AN19</f>
+        <f t="shared" si="10"/>
         <v>94</v>
       </c>
       <c r="AP19" s="3">
         <v>4</v>
       </c>
       <c r="AQ19" s="3">
-        <f>+AO19+AP19</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR19" s="3">
-        <f>+AQ19+7</f>
+        <f t="shared" si="12"/>
         <v>105</v>
       </c>
       <c r="AS19" s="3">
-        <f>+AR19+7+AT19</f>
+        <f t="shared" si="13"/>
         <v>126</v>
       </c>
       <c r="AT19" s="3">
         <v>14</v>
       </c>
       <c r="AU19" s="3">
-        <f>+AA19-R19</f>
+        <f t="shared" si="14"/>
         <v>14</v>
       </c>
       <c r="AV19" s="3" t="s">
@@ -4998,44 +5006,44 @@
         <v>2</v>
       </c>
       <c r="M20" s="3">
-        <f>+IF(I20="SFK Freight Forwarder",L20,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N20" s="3">
         <v>14</v>
       </c>
       <c r="O20" s="3">
-        <f>IF(I20="SFK Freight Forwarder",M20,M20+N20-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P20" s="3">
-        <f>+IF(I20="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q20" s="3">
-        <f>+IF(I20="SFK Freight Forwarder",O20,O20+P20-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R20" s="3">
-        <f>9+N20</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S20" s="3">
         <v>7</v>
       </c>
       <c r="T20" s="3">
-        <f>+R20+S20-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U20" s="3">
-        <f>+T20+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V20" s="3">
         <v>2</v>
       </c>
       <c r="W20" s="3">
-        <f>+U20+V20-1</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="X20" s="3">
@@ -5048,7 +5056,7 @@
         <v>35</v>
       </c>
       <c r="AA20" s="6">
-        <f>+Z20+AB20-1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="AB20" s="3">
@@ -5064,21 +5072,21 @@
         <v>36</v>
       </c>
       <c r="AF20" s="3">
-        <f>+AE20+AA20-1</f>
+        <f t="shared" si="6"/>
         <v>72</v>
       </c>
       <c r="AG20" s="6">
         <v>3</v>
       </c>
       <c r="AH20" s="6">
-        <f>+AF20+AG20</f>
+        <f t="shared" si="7"/>
         <v>75</v>
       </c>
       <c r="AI20" s="3">
         <v>14</v>
       </c>
       <c r="AJ20" s="3">
-        <f>+AI20+AH20</f>
+        <f t="shared" si="8"/>
         <v>89</v>
       </c>
       <c r="AK20" s="3" t="s">
@@ -5088,36 +5096,36 @@
         <v>2</v>
       </c>
       <c r="AM20" s="3">
-        <f>+AJ20+AL20</f>
+        <f t="shared" si="9"/>
         <v>91</v>
       </c>
       <c r="AN20" s="3">
         <v>8</v>
       </c>
       <c r="AO20" s="3">
-        <f>+AM20+AN20</f>
+        <f t="shared" si="10"/>
         <v>99</v>
       </c>
       <c r="AP20" s="3">
         <v>2</v>
       </c>
       <c r="AQ20" s="3">
-        <f>+AO20+AP20</f>
+        <f t="shared" si="11"/>
         <v>101</v>
       </c>
       <c r="AR20" s="3">
-        <f>+AQ20+7</f>
+        <f t="shared" si="12"/>
         <v>108</v>
       </c>
       <c r="AS20" s="3">
-        <f>+AR20+7+AT20</f>
+        <f t="shared" si="13"/>
         <v>129</v>
       </c>
       <c r="AT20" s="3">
         <v>14</v>
       </c>
       <c r="AU20" s="3">
-        <f>+AA20-R20</f>
+        <f t="shared" si="14"/>
         <v>14</v>
       </c>
       <c r="AV20" s="3" t="s">
@@ -5171,44 +5179,44 @@
         <v>7</v>
       </c>
       <c r="M21" s="3">
-        <f>+IF(I21="SFK Freight Forwarder",L21,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N21" s="3">
         <v>21</v>
       </c>
       <c r="O21" s="3">
-        <f>IF(I21="SFK Freight Forwarder",M21,M21+N21-1)</f>
+        <f t="shared" si="15"/>
         <v>29</v>
       </c>
       <c r="P21" s="3">
-        <f>+IF(I21="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q21" s="3">
-        <f>+IF(I21="SFK Freight Forwarder",O21,O21+P21-1)</f>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="R21" s="3">
-        <f>9+N21</f>
+        <f t="shared" si="16"/>
         <v>30</v>
       </c>
       <c r="S21" s="3">
         <v>7</v>
       </c>
       <c r="T21" s="3">
-        <f>+R21+S21-1</f>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="U21" s="3">
-        <f>+T21+1</f>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="V21" s="3">
         <v>1</v>
       </c>
       <c r="W21" s="3">
-        <f>+U21+V21-1</f>
+        <f t="shared" si="4"/>
         <v>37</v>
       </c>
       <c r="X21" s="3">
@@ -5221,7 +5229,7 @@
         <v>42</v>
       </c>
       <c r="AA21" s="6">
-        <f>+Z21+AB21-1</f>
+        <f t="shared" si="19"/>
         <v>44</v>
       </c>
       <c r="AB21" s="3">
@@ -5237,21 +5245,21 @@
         <v>40</v>
       </c>
       <c r="AF21" s="3">
-        <f>+AE21+AA21-1</f>
+        <f t="shared" si="6"/>
         <v>83</v>
       </c>
       <c r="AG21" s="6">
         <v>3</v>
       </c>
       <c r="AH21" s="6">
-        <f>+AF21+AG21</f>
+        <f t="shared" si="7"/>
         <v>86</v>
       </c>
       <c r="AI21" s="3">
         <v>0</v>
       </c>
       <c r="AJ21" s="3">
-        <f>+AI21+AH21</f>
+        <f t="shared" si="8"/>
         <v>86</v>
       </c>
       <c r="AK21" s="3" t="s">
@@ -5261,36 +5269,36 @@
         <v>2</v>
       </c>
       <c r="AM21" s="3">
-        <f>+AJ21+AL21</f>
+        <f t="shared" si="9"/>
         <v>88</v>
       </c>
       <c r="AN21" s="3">
         <v>8</v>
       </c>
       <c r="AO21" s="3">
-        <f>+AM21+AN21</f>
+        <f t="shared" si="10"/>
         <v>96</v>
       </c>
       <c r="AP21" s="3">
         <v>2</v>
       </c>
       <c r="AQ21" s="3">
-        <f>+AO21+AP21</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR21" s="3">
-        <f>+AQ21+7</f>
+        <f t="shared" si="12"/>
         <v>105</v>
       </c>
       <c r="AS21" s="3">
-        <f>+AR21+7+AT21</f>
+        <f t="shared" si="13"/>
         <v>112</v>
       </c>
       <c r="AT21" s="3">
         <v>0</v>
       </c>
       <c r="AU21" s="3">
-        <f>+AA21-R21</f>
+        <f t="shared" si="14"/>
         <v>14</v>
       </c>
       <c r="AV21" s="3" t="s">
@@ -5344,44 +5352,44 @@
         <v>2</v>
       </c>
       <c r="M22" s="3">
-        <f>+IF(I22="SFK Freight Forwarder",L22,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N22" s="3">
         <v>14</v>
       </c>
       <c r="O22" s="3">
-        <f>IF(I22="SFK Freight Forwarder",M22,M22+N22-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P22" s="3">
-        <f>+IF(I22="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q22" s="3">
-        <f>+IF(I22="SFK Freight Forwarder",O22,O22+P22-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R22" s="3">
-        <f>9+N22</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S22" s="3">
         <v>7</v>
       </c>
       <c r="T22" s="3">
-        <f>+R22+S22-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U22" s="3">
-        <f>+T22+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V22" s="3">
         <v>3</v>
       </c>
       <c r="W22" s="3">
-        <f>+U22+V22-1</f>
+        <f t="shared" si="4"/>
         <v>32</v>
       </c>
       <c r="X22" s="3">
@@ -5394,7 +5402,7 @@
         <v>37</v>
       </c>
       <c r="AA22" s="6">
-        <f>+Z22+AB22-1</f>
+        <f t="shared" si="19"/>
         <v>39</v>
       </c>
       <c r="AB22" s="3">
@@ -5410,21 +5418,21 @@
         <v>46</v>
       </c>
       <c r="AF22" s="3">
-        <f>+AE22+AA22-1</f>
+        <f t="shared" si="6"/>
         <v>84</v>
       </c>
       <c r="AG22" s="6">
         <v>3</v>
       </c>
       <c r="AH22" s="6">
-        <f>+AF22+AG22</f>
+        <f t="shared" si="7"/>
         <v>87</v>
       </c>
       <c r="AI22" s="3">
         <v>7</v>
       </c>
       <c r="AJ22" s="3">
-        <f>+AI22+AH22</f>
+        <f t="shared" si="8"/>
         <v>94</v>
       </c>
       <c r="AK22" s="3" t="s">
@@ -5434,36 +5442,36 @@
         <v>2</v>
       </c>
       <c r="AM22" s="3">
-        <f>+AJ22+AL22</f>
+        <f t="shared" si="9"/>
         <v>96</v>
       </c>
       <c r="AN22" s="3">
         <v>2</v>
       </c>
       <c r="AO22" s="3">
-        <f>+AM22+AN22</f>
+        <f t="shared" si="10"/>
         <v>98</v>
       </c>
       <c r="AP22" s="3">
         <v>0</v>
       </c>
       <c r="AQ22" s="3">
-        <f>+AO22+AP22</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR22" s="3">
-        <f>+AQ22+7</f>
+        <f t="shared" si="12"/>
         <v>105</v>
       </c>
       <c r="AS22" s="3">
-        <f>+AR22+7+AT22</f>
+        <f t="shared" si="13"/>
         <v>126</v>
       </c>
       <c r="AT22" s="3">
         <v>14</v>
       </c>
       <c r="AU22" s="3">
-        <f>+AA22-R22</f>
+        <f t="shared" si="14"/>
         <v>16</v>
       </c>
       <c r="AV22" s="3" t="s">
@@ -5517,44 +5525,44 @@
         <v>7</v>
       </c>
       <c r="M23" s="3">
-        <f>+IF(I23="SFK Freight Forwarder",L23,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N23" s="3">
         <v>7</v>
       </c>
       <c r="O23" s="3">
-        <f>IF(I23="SFK Freight Forwarder",M23,M23+N23-1)</f>
+        <f t="shared" si="15"/>
         <v>15</v>
       </c>
       <c r="P23" s="3">
-        <f>+IF(I23="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q23" s="3">
-        <f>+IF(I23="SFK Freight Forwarder",O23,O23+P23-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R23" s="3">
-        <f>9+N23</f>
+        <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="S23" s="3">
         <v>7</v>
       </c>
       <c r="T23" s="3">
-        <f>+R23+S23-1</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="U23" s="3">
-        <f>+T23+1</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="V23" s="3">
         <v>3</v>
       </c>
       <c r="W23" s="3">
-        <f>+U23+V23-1</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="X23" s="3">
@@ -5567,7 +5575,7 @@
         <v>30</v>
       </c>
       <c r="AA23" s="6">
-        <f>+Z23+AB23-1</f>
+        <f t="shared" si="19"/>
         <v>32</v>
       </c>
       <c r="AB23" s="3">
@@ -5583,21 +5591,21 @@
         <v>21</v>
       </c>
       <c r="AF23" s="3">
-        <f>+AE23+AA23-1</f>
+        <f t="shared" si="6"/>
         <v>52</v>
       </c>
       <c r="AG23" s="6">
         <v>3</v>
       </c>
       <c r="AH23" s="6">
-        <f>+AF23+AG23</f>
+        <f t="shared" si="7"/>
         <v>55</v>
       </c>
       <c r="AI23" s="3">
         <v>0</v>
       </c>
       <c r="AJ23" s="3">
-        <f>+AI23+AH23</f>
+        <f t="shared" si="8"/>
         <v>55</v>
       </c>
       <c r="AK23" s="3" t="s">
@@ -5607,36 +5615,36 @@
         <v>1</v>
       </c>
       <c r="AM23" s="3">
-        <f>+AJ23+AL23</f>
+        <f t="shared" si="9"/>
         <v>56</v>
       </c>
       <c r="AN23" s="3">
         <v>8</v>
       </c>
       <c r="AO23" s="3">
-        <f>+AM23+AN23</f>
+        <f t="shared" si="10"/>
         <v>64</v>
       </c>
       <c r="AP23" s="3">
         <v>6</v>
       </c>
       <c r="AQ23" s="3">
-        <f>+AO23+AP23</f>
+        <f t="shared" si="11"/>
         <v>70</v>
       </c>
       <c r="AR23" s="3">
-        <f>+AQ23+7</f>
+        <f t="shared" si="12"/>
         <v>77</v>
       </c>
       <c r="AS23" s="3">
-        <f>+AR23+7+AT23</f>
+        <f t="shared" si="13"/>
         <v>84</v>
       </c>
       <c r="AT23" s="3">
         <v>0</v>
       </c>
       <c r="AU23" s="3">
-        <f>+AA23-R23</f>
+        <f t="shared" si="14"/>
         <v>16</v>
       </c>
       <c r="AV23" s="3" t="s">
@@ -5690,44 +5698,44 @@
         <v>7</v>
       </c>
       <c r="M24" s="3">
-        <f>+IF(I24="SFK Freight Forwarder",L24,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N24" s="3">
         <v>14</v>
       </c>
       <c r="O24" s="3">
-        <f>IF(I24="SFK Freight Forwarder",M24,M24+N24-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P24" s="3">
-        <f>+IF(I24="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q24" s="3">
-        <f>+IF(I24="SFK Freight Forwarder",O24,O24+P24-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R24" s="3">
-        <f>9+N24</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S24" s="3">
         <v>7</v>
       </c>
       <c r="T24" s="3">
-        <f>+R24+S24-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U24" s="3">
-        <f>+T24+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V24" s="3">
         <v>2</v>
       </c>
       <c r="W24" s="3">
-        <f>+U24+V24-1</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="X24" s="3">
@@ -5740,7 +5748,7 @@
         <v>33</v>
       </c>
       <c r="AA24" s="6">
-        <f>+Z24+AB24-1</f>
+        <f t="shared" si="19"/>
         <v>35</v>
       </c>
       <c r="AB24" s="3">
@@ -5756,21 +5764,21 @@
         <v>40</v>
       </c>
       <c r="AF24" s="3">
-        <f>+AE24+AA24-1</f>
+        <f t="shared" si="6"/>
         <v>74</v>
       </c>
       <c r="AG24" s="6">
         <v>3</v>
       </c>
       <c r="AH24" s="6">
-        <f>+AF24+AG24</f>
+        <f t="shared" si="7"/>
         <v>77</v>
       </c>
       <c r="AI24" s="3">
         <v>14</v>
       </c>
       <c r="AJ24" s="3">
-        <f>+AI24+AH24</f>
+        <f t="shared" si="8"/>
         <v>91</v>
       </c>
       <c r="AK24" s="3" t="s">
@@ -5780,36 +5788,36 @@
         <v>2</v>
       </c>
       <c r="AM24" s="3">
-        <f>+AJ24+AL24</f>
+        <f t="shared" si="9"/>
         <v>93</v>
       </c>
       <c r="AN24" s="3">
         <v>2</v>
       </c>
       <c r="AO24" s="3">
-        <f>+AM24+AN24</f>
+        <f t="shared" si="10"/>
         <v>95</v>
       </c>
       <c r="AP24" s="3">
         <v>3</v>
       </c>
       <c r="AQ24" s="3">
-        <f>+AO24+AP24</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR24" s="3">
-        <f>+AQ24+7</f>
+        <f t="shared" si="12"/>
         <v>105</v>
       </c>
       <c r="AS24" s="3">
-        <f>+AR24+7+AT24</f>
+        <f t="shared" si="13"/>
         <v>126</v>
       </c>
       <c r="AT24" s="3">
         <v>14</v>
       </c>
       <c r="AU24" s="3">
-        <f>+AA24-R24</f>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="AV24" s="3" t="s">
@@ -5863,44 +5871,44 @@
         <v>2</v>
       </c>
       <c r="M25" s="3">
-        <f>+IF(I25="SFK Freight Forwarder",L25,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N25" s="3">
         <v>14</v>
       </c>
       <c r="O25" s="3">
-        <f>IF(I25="SFK Freight Forwarder",M25,M25+N25-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P25" s="3">
-        <f>+IF(I25="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q25" s="3">
-        <f>+IF(I25="SFK Freight Forwarder",O25,O25+P25-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R25" s="3">
-        <f>9+N25</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S25" s="3">
         <v>7</v>
       </c>
       <c r="T25" s="3">
-        <f>+R25+S25-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U25" s="3">
-        <f>+T25+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V25" s="3">
         <v>1</v>
       </c>
       <c r="W25" s="3">
-        <f>+U25+V25-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X25" s="3">
@@ -5913,7 +5921,7 @@
         <v>30</v>
       </c>
       <c r="AA25" s="6">
-        <f>+Z25+AB25-1</f>
+        <f t="shared" si="19"/>
         <v>32</v>
       </c>
       <c r="AB25" s="3">
@@ -5929,21 +5937,21 @@
         <v>46</v>
       </c>
       <c r="AF25" s="3">
-        <f>+AE25+AA25-1</f>
+        <f t="shared" si="6"/>
         <v>77</v>
       </c>
       <c r="AG25" s="6">
         <v>3</v>
       </c>
       <c r="AH25" s="6">
-        <f>+AF25+AG25</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="AI25" s="3">
         <v>14</v>
       </c>
       <c r="AJ25" s="3">
-        <f>+AI25+AH25</f>
+        <f t="shared" si="8"/>
         <v>94</v>
       </c>
       <c r="AK25" s="3" t="s">
@@ -5953,36 +5961,36 @@
         <v>4</v>
       </c>
       <c r="AM25" s="3">
-        <f>+AJ25+AL25</f>
+        <f t="shared" si="9"/>
         <v>98</v>
       </c>
       <c r="AN25" s="3">
         <v>3</v>
       </c>
       <c r="AO25" s="3">
-        <f>+AM25+AN25</f>
+        <f t="shared" si="10"/>
         <v>101</v>
       </c>
       <c r="AP25" s="3">
         <v>4</v>
       </c>
       <c r="AQ25" s="3">
-        <f>+AO25+AP25</f>
+        <f t="shared" si="11"/>
         <v>105</v>
       </c>
       <c r="AR25" s="3">
-        <f>+AQ25+7</f>
+        <f t="shared" si="12"/>
         <v>112</v>
       </c>
       <c r="AS25" s="3">
-        <f>+AR25+7+AT25</f>
+        <f t="shared" si="13"/>
         <v>133</v>
       </c>
       <c r="AT25" s="3">
         <v>14</v>
       </c>
       <c r="AU25" s="3">
-        <f>+AA25-R25</f>
+        <f t="shared" si="14"/>
         <v>9</v>
       </c>
       <c r="AV25" s="3" t="s">
@@ -6036,44 +6044,44 @@
         <v>7</v>
       </c>
       <c r="M26" s="3">
-        <f>+IF(I26="SFK Freight Forwarder",L26,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N26" s="3">
         <v>7</v>
       </c>
       <c r="O26" s="3">
-        <f>IF(I26="SFK Freight Forwarder",M26,M26+N26-1)</f>
+        <f t="shared" si="15"/>
         <v>15</v>
       </c>
       <c r="P26" s="3">
-        <f>+IF(I26="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q26" s="3">
-        <f>+IF(I26="SFK Freight Forwarder",O26,O26+P26-1)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="R26" s="3">
-        <f>9+N26</f>
+        <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="S26" s="3">
         <v>7</v>
       </c>
       <c r="T26" s="3">
-        <f>+R26+S26-1</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="U26" s="3">
-        <f>+T26+1</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="V26" s="3">
         <v>2</v>
       </c>
       <c r="W26" s="3">
-        <f>+U26+V26-1</f>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="X26" s="3">
@@ -6086,7 +6094,7 @@
         <v>31</v>
       </c>
       <c r="AA26" s="6">
-        <f>+Z26+AB26-1</f>
+        <f t="shared" si="19"/>
         <v>33</v>
       </c>
       <c r="AB26" s="3">
@@ -6102,21 +6110,21 @@
         <v>21</v>
       </c>
       <c r="AF26" s="3">
-        <f>+AE26+AA26-1</f>
+        <f t="shared" si="6"/>
         <v>53</v>
       </c>
       <c r="AG26" s="6">
         <v>3</v>
       </c>
       <c r="AH26" s="6">
-        <f>+AF26+AG26</f>
+        <f t="shared" si="7"/>
         <v>56</v>
       </c>
       <c r="AI26" s="3">
         <v>7</v>
       </c>
       <c r="AJ26" s="3">
-        <f>+AI26+AH26</f>
+        <f t="shared" si="8"/>
         <v>63</v>
       </c>
       <c r="AK26" s="3" t="s">
@@ -6126,36 +6134,36 @@
         <v>2</v>
       </c>
       <c r="AM26" s="3">
-        <f>+AJ26+AL26</f>
+        <f t="shared" si="9"/>
         <v>65</v>
       </c>
       <c r="AN26" s="3">
         <v>2</v>
       </c>
       <c r="AO26" s="3">
-        <f>+AM26+AN26</f>
+        <f t="shared" si="10"/>
         <v>67</v>
       </c>
       <c r="AP26" s="3">
         <v>3</v>
       </c>
       <c r="AQ26" s="3">
-        <f>+AO26+AP26</f>
+        <f t="shared" si="11"/>
         <v>70</v>
       </c>
       <c r="AR26" s="3">
-        <f>+AQ26+7</f>
+        <f t="shared" si="12"/>
         <v>77</v>
       </c>
       <c r="AS26" s="3">
-        <f>+AR26+7+AT26</f>
+        <f t="shared" si="13"/>
         <v>98</v>
       </c>
       <c r="AT26" s="3">
         <v>14</v>
       </c>
       <c r="AU26" s="3">
-        <f>+AA26-R26</f>
+        <f t="shared" si="14"/>
         <v>17</v>
       </c>
       <c r="AV26" s="3" t="s">
@@ -6209,44 +6217,44 @@
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <f>+IF(I27="SFK Freight Forwarder",L27,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N27" s="3">
         <v>14</v>
       </c>
       <c r="O27" s="3">
-        <f>IF(I27="SFK Freight Forwarder",M27,M27+N27-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P27" s="3">
-        <f>+IF(I27="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q27" s="3">
-        <f>+IF(I27="SFK Freight Forwarder",O27,O27+P27-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R27" s="3">
-        <f>9+N27</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S27" s="3">
         <v>7</v>
       </c>
       <c r="T27" s="3">
-        <f>+R27+S27-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U27" s="3">
-        <f>+T27+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V27" s="3">
         <v>3</v>
       </c>
       <c r="W27" s="3">
-        <f>+U27+V27-1</f>
+        <f t="shared" si="4"/>
         <v>32</v>
       </c>
       <c r="X27" s="3">
@@ -6259,7 +6267,7 @@
         <v>37</v>
       </c>
       <c r="AA27" s="6">
-        <f>+Z27+AB27-1</f>
+        <f t="shared" si="19"/>
         <v>39</v>
       </c>
       <c r="AB27" s="3">
@@ -6275,60 +6283,60 @@
         <v>39</v>
       </c>
       <c r="AF27" s="3">
-        <f>+AE27+AA27-1</f>
+        <f t="shared" si="6"/>
         <v>77</v>
       </c>
       <c r="AG27" s="6">
         <v>3</v>
       </c>
       <c r="AH27" s="6">
-        <f>+AF27+AG27</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="AI27" s="3">
         <v>0</v>
       </c>
       <c r="AJ27" s="3">
-        <f>+AI27+AH27</f>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="AK27" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AL27" s="3">
-        <v>3</v>
+      <c r="AL27" s="46">
+        <v>2</v>
       </c>
       <c r="AM27" s="3">
-        <f>+AJ27+AL27</f>
-        <v>83</v>
+        <f t="shared" si="9"/>
+        <v>82</v>
       </c>
       <c r="AN27" s="3">
         <v>8</v>
       </c>
       <c r="AO27" s="3">
-        <f>+AM27+AN27</f>
-        <v>91</v>
+        <f t="shared" si="10"/>
+        <v>90</v>
       </c>
       <c r="AP27" s="3">
         <v>2</v>
       </c>
       <c r="AQ27" s="3">
-        <f>+AO27+AP27</f>
-        <v>93</v>
+        <f t="shared" si="11"/>
+        <v>92</v>
       </c>
       <c r="AR27" s="3">
-        <f>+AQ27+7</f>
-        <v>100</v>
+        <f t="shared" si="12"/>
+        <v>99</v>
       </c>
       <c r="AS27" s="3">
-        <f>+AR27+7+AT27</f>
-        <v>121</v>
+        <f t="shared" si="13"/>
+        <v>120</v>
       </c>
       <c r="AT27" s="3">
         <v>14</v>
       </c>
       <c r="AU27" s="3">
-        <f>+AA27-R27</f>
+        <f t="shared" si="14"/>
         <v>16</v>
       </c>
       <c r="AV27" s="3" t="s">
@@ -6382,44 +6390,44 @@
         <v>7</v>
       </c>
       <c r="M28" s="3">
-        <f>+IF(I28="SFK Freight Forwarder",L28,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N28" s="3">
         <v>14</v>
       </c>
       <c r="O28" s="3">
-        <f>IF(I28="SFK Freight Forwarder",M28,M28+N28-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P28" s="3">
-        <f>+IF(I28="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q28" s="3">
-        <f>+IF(I28="SFK Freight Forwarder",O28,O28+P28-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R28" s="3">
-        <f>9+N28</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S28" s="3">
         <v>7</v>
       </c>
       <c r="T28" s="3">
-        <f>+R28+S28-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U28" s="3">
-        <f>+T28+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V28" s="3">
         <v>1</v>
       </c>
       <c r="W28" s="3">
-        <f>+U28+V28-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X28" s="3">
@@ -6432,7 +6440,7 @@
         <v>33</v>
       </c>
       <c r="AA28" s="6">
-        <f>+Z28+AB28-1</f>
+        <f t="shared" si="19"/>
         <v>35</v>
       </c>
       <c r="AB28" s="3">
@@ -6448,21 +6456,21 @@
         <v>43</v>
       </c>
       <c r="AF28" s="3">
-        <f>+AE28+AA28-1</f>
+        <f t="shared" si="6"/>
         <v>77</v>
       </c>
       <c r="AG28" s="6">
         <v>3</v>
       </c>
       <c r="AH28" s="6">
-        <f>+AF28+AG28</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="AI28" s="3">
         <v>7</v>
       </c>
       <c r="AJ28" s="3">
-        <f>+AI28+AH28</f>
+        <f t="shared" si="8"/>
         <v>87</v>
       </c>
       <c r="AK28" s="3" t="s">
@@ -6472,36 +6480,36 @@
         <v>2</v>
       </c>
       <c r="AM28" s="3">
-        <f>+AJ28+AL28</f>
+        <f t="shared" si="9"/>
         <v>89</v>
       </c>
       <c r="AN28" s="3">
         <v>2</v>
       </c>
       <c r="AO28" s="3">
-        <f>+AM28+AN28</f>
+        <f t="shared" si="10"/>
         <v>91</v>
       </c>
       <c r="AP28" s="3">
         <v>0</v>
       </c>
       <c r="AQ28" s="3">
-        <f>+AO28+AP28</f>
+        <f t="shared" si="11"/>
         <v>91</v>
       </c>
       <c r="AR28" s="3">
-        <f>+AQ28+7</f>
+        <f t="shared" si="12"/>
         <v>98</v>
       </c>
       <c r="AS28" s="3">
-        <f>+AR28+7+AT28</f>
+        <f t="shared" si="13"/>
         <v>122</v>
       </c>
       <c r="AT28" s="3">
         <v>17</v>
       </c>
       <c r="AU28" s="3">
-        <f>+AA28-R28</f>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="AV28" s="3" t="s">
@@ -6555,44 +6563,44 @@
         <v>7</v>
       </c>
       <c r="M29" s="3">
-        <f>+IF(I29="SFK Freight Forwarder",L29,9)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="N29" s="3">
         <v>14</v>
       </c>
       <c r="O29" s="3">
-        <f>IF(I29="SFK Freight Forwarder",M29,M29+N29-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P29" s="3">
-        <f>+IF(I29="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q29" s="3">
-        <f>+IF(I29="SFK Freight Forwarder",O29,O29+P29-1)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="R29" s="3">
-        <f>9+N29</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S29" s="3">
         <v>7</v>
       </c>
       <c r="T29" s="3">
-        <f>+R29+S29-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U29" s="3">
-        <f>+T29+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V29" s="3">
         <v>1</v>
       </c>
       <c r="W29" s="3">
-        <f>+U29+V29-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X29" s="3">
@@ -6605,7 +6613,7 @@
         <v>35</v>
       </c>
       <c r="AA29" s="6">
-        <f>+Z29+AB29-1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="AB29" s="3">
@@ -6621,21 +6629,21 @@
         <v>58</v>
       </c>
       <c r="AF29" s="3">
-        <f>+AE29+AA29-1</f>
+        <f t="shared" si="6"/>
         <v>94</v>
       </c>
       <c r="AG29" s="6">
         <v>3</v>
       </c>
       <c r="AH29" s="6">
-        <f>+AF29+AG29</f>
+        <f t="shared" si="7"/>
         <v>97</v>
       </c>
       <c r="AI29" s="3">
         <v>7</v>
       </c>
       <c r="AJ29" s="3">
-        <f>+AI29+AH29</f>
+        <f t="shared" si="8"/>
         <v>104</v>
       </c>
       <c r="AK29" s="3" t="s">
@@ -6645,36 +6653,36 @@
         <v>1</v>
       </c>
       <c r="AM29" s="3">
-        <f>+AJ29+AL29</f>
+        <f t="shared" si="9"/>
         <v>105</v>
       </c>
       <c r="AN29" s="3">
         <v>8</v>
       </c>
       <c r="AO29" s="3">
-        <f>+AM29+AN29</f>
+        <f t="shared" si="10"/>
         <v>113</v>
       </c>
       <c r="AP29" s="3">
         <v>6</v>
       </c>
       <c r="AQ29" s="3">
-        <f>+AO29+AP29</f>
+        <f t="shared" si="11"/>
         <v>119</v>
       </c>
       <c r="AR29" s="3">
-        <f>+AQ29+7</f>
+        <f t="shared" si="12"/>
         <v>126</v>
       </c>
       <c r="AS29" s="3">
-        <f>+AR29+7+AT29</f>
+        <f t="shared" si="13"/>
         <v>147</v>
       </c>
       <c r="AT29" s="3">
         <v>14</v>
       </c>
       <c r="AU29" s="3">
-        <f>+AA29-R29</f>
+        <f t="shared" si="14"/>
         <v>14</v>
       </c>
       <c r="AV29" s="3" t="s">
@@ -6734,37 +6742,37 @@
         <v>14</v>
       </c>
       <c r="O30" s="3">
-        <f>IF(I30="SFK Freight Forwarder",M30,M30+N30-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P30" s="3">
-        <f>+IF(I30="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q30" s="3">
-        <f>+IF(I30="SFK Freight Forwarder",O30,O30+P30-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R30" s="3">
-        <f>9+N30</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S30" s="3">
         <v>7</v>
       </c>
       <c r="T30" s="3">
-        <f>+R30+S30-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U30" s="3">
-        <f>+T30+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V30" s="3">
         <v>1</v>
       </c>
       <c r="W30" s="3">
-        <f>+U30+V30-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X30" s="3">
@@ -6777,7 +6785,7 @@
         <v>31</v>
       </c>
       <c r="AA30" s="6">
-        <f>+Z30+AB30-1</f>
+        <f t="shared" si="19"/>
         <v>33</v>
       </c>
       <c r="AB30" s="3">
@@ -6793,21 +6801,21 @@
         <v>34</v>
       </c>
       <c r="AF30" s="3">
-        <f>+AE30+AA30-1</f>
+        <f t="shared" si="6"/>
         <v>66</v>
       </c>
       <c r="AG30" s="6">
         <v>3</v>
       </c>
       <c r="AH30" s="6">
-        <f>+AF30+AG30</f>
+        <f t="shared" si="7"/>
         <v>69</v>
       </c>
       <c r="AI30" s="3">
         <v>14</v>
       </c>
       <c r="AJ30" s="3">
-        <f>+AI30+AH30</f>
+        <f t="shared" si="8"/>
         <v>83</v>
       </c>
       <c r="AK30" s="3" t="s">
@@ -6817,36 +6825,36 @@
         <v>0</v>
       </c>
       <c r="AM30" s="3">
-        <f>+AJ30+AL30</f>
+        <f t="shared" si="9"/>
         <v>83</v>
       </c>
       <c r="AN30" s="3">
         <v>0</v>
       </c>
       <c r="AO30" s="3">
-        <f>+AM30+AN30</f>
+        <f t="shared" si="10"/>
         <v>83</v>
       </c>
       <c r="AP30" s="3">
         <v>1</v>
       </c>
       <c r="AQ30" s="3">
-        <f>+AO30+AP30</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR30" s="3">
-        <f>+AQ30+7</f>
+        <f t="shared" si="12"/>
         <v>91</v>
       </c>
       <c r="AS30" s="3">
-        <f>+AR30+7+AT30</f>
+        <f t="shared" si="13"/>
         <v>98</v>
       </c>
       <c r="AT30" s="3">
         <v>0</v>
       </c>
       <c r="AU30" s="3">
-        <f>+AA30-R30</f>
+        <f t="shared" si="14"/>
         <v>10</v>
       </c>
       <c r="AV30" s="3" t="s">
@@ -6906,37 +6914,37 @@
         <v>14</v>
       </c>
       <c r="O31" s="3">
-        <f>IF(I31="SFK Freight Forwarder",M31,M31+N31-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P31" s="3">
-        <f>+IF(I31="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q31" s="3">
-        <f>+IF(I31="SFK Freight Forwarder",O31,O31+P31-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R31" s="3">
-        <f>9+N31</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S31" s="3">
         <v>7</v>
       </c>
       <c r="T31" s="3">
-        <f>+R31+S31-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U31" s="3">
-        <f>+T31+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V31" s="3">
         <v>1</v>
       </c>
       <c r="W31" s="3">
-        <f>+U31+V31-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X31" s="3">
@@ -6949,7 +6957,7 @@
         <v>31</v>
       </c>
       <c r="AA31" s="6">
-        <f>+Z31+AB31-1</f>
+        <f t="shared" si="19"/>
         <v>34</v>
       </c>
       <c r="AB31" s="3">
@@ -6965,21 +6973,21 @@
         <v>58</v>
       </c>
       <c r="AF31" s="3">
-        <f>+AE31+AA31-1</f>
+        <f t="shared" si="6"/>
         <v>91</v>
       </c>
       <c r="AG31" s="6">
         <v>3</v>
       </c>
       <c r="AH31" s="6">
-        <f>+AF31+AG31</f>
+        <f t="shared" si="7"/>
         <v>94</v>
       </c>
       <c r="AI31" s="3">
         <v>0</v>
       </c>
       <c r="AJ31" s="3">
-        <f>+AI31+AH31</f>
+        <f t="shared" si="8"/>
         <v>94</v>
       </c>
       <c r="AK31" s="3" t="s">
@@ -6989,36 +6997,36 @@
         <v>1</v>
       </c>
       <c r="AM31" s="3">
-        <f>+AJ31+AL31</f>
+        <f t="shared" si="9"/>
         <v>95</v>
       </c>
       <c r="AN31" s="3">
         <v>4</v>
       </c>
       <c r="AO31" s="3">
-        <f>+AM31+AN31</f>
+        <f t="shared" si="10"/>
         <v>99</v>
       </c>
       <c r="AP31" s="3">
         <v>6</v>
       </c>
       <c r="AQ31" s="3">
-        <f>+AO31+AP31</f>
+        <f t="shared" si="11"/>
         <v>105</v>
       </c>
       <c r="AR31" s="3">
-        <f>+AQ31+7</f>
+        <f t="shared" si="12"/>
         <v>112</v>
       </c>
       <c r="AS31" s="3">
-        <f>+AR31+7+AT31</f>
+        <f t="shared" si="13"/>
         <v>119</v>
       </c>
       <c r="AT31" s="3">
         <v>0</v>
       </c>
       <c r="AU31" s="3">
-        <f>+AA31-R31</f>
+        <f t="shared" si="14"/>
         <v>11</v>
       </c>
       <c r="AV31" s="3" t="s">
@@ -7078,37 +7086,37 @@
         <v>14</v>
       </c>
       <c r="O32" s="3">
-        <f>IF(I32="SFK Freight Forwarder",M32,M32+N32-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <f>+IF(I32="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <f>+IF(I32="SFK Freight Forwarder",O32,O32+P32-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <f>9+N32</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S32" s="3">
         <v>7</v>
       </c>
       <c r="T32" s="3">
-        <f>+R32+S32-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U32" s="3">
-        <f>+T32+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V32" s="3">
         <v>1</v>
       </c>
       <c r="W32" s="3">
-        <f>+U32+V32-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X32" s="3">
@@ -7123,7 +7131,7 @@
         <v>33</v>
       </c>
       <c r="AA32" s="6">
-        <f>+Z32+AB32-1</f>
+        <f t="shared" si="19"/>
         <v>35</v>
       </c>
       <c r="AB32" s="3">
@@ -7139,21 +7147,21 @@
         <v>49</v>
       </c>
       <c r="AF32" s="3">
-        <f>+AE32+AA32-1</f>
+        <f t="shared" si="6"/>
         <v>83</v>
       </c>
       <c r="AG32" s="6">
         <v>3</v>
       </c>
       <c r="AH32" s="6">
-        <f>+AF32+AG32</f>
+        <f t="shared" si="7"/>
         <v>86</v>
       </c>
       <c r="AI32" s="3">
         <v>7</v>
       </c>
       <c r="AJ32" s="3">
-        <f>+AI32+AH32</f>
+        <f t="shared" si="8"/>
         <v>93</v>
       </c>
       <c r="AK32" s="3" t="s">
@@ -7163,36 +7171,36 @@
         <v>3</v>
       </c>
       <c r="AM32" s="3">
-        <f>+AJ32+AL32</f>
+        <f t="shared" si="9"/>
         <v>96</v>
       </c>
       <c r="AN32" s="3">
         <v>1</v>
       </c>
       <c r="AO32" s="3">
-        <f>+AM32+AN32</f>
+        <f t="shared" si="10"/>
         <v>97</v>
       </c>
       <c r="AP32" s="3">
         <v>1</v>
       </c>
       <c r="AQ32" s="3">
-        <f>+AO32+AP32</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR32" s="3">
-        <f>+AQ32+7</f>
+        <f t="shared" si="12"/>
         <v>105</v>
       </c>
       <c r="AS32" s="3">
-        <f>+AR32+7+AT32</f>
+        <f t="shared" si="13"/>
         <v>112</v>
       </c>
       <c r="AT32" s="3">
         <v>0</v>
       </c>
       <c r="AU32" s="3">
-        <f>+AA32-R32</f>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="AV32" s="3" t="s">
@@ -7252,37 +7260,37 @@
         <v>14</v>
       </c>
       <c r="O33" s="3">
-        <f>IF(I33="SFK Freight Forwarder",M33,M33+N33-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P33" s="3">
-        <f>+IF(I33="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <f>+IF(I33="SFK Freight Forwarder",O33,O33+P33-1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R33" s="3">
-        <f>9+N33</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S33" s="3">
         <v>7</v>
       </c>
       <c r="T33" s="3">
-        <f>+R33+S33-1</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="U33" s="3">
-        <f>+T33+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V33" s="3">
         <v>1</v>
       </c>
       <c r="W33" s="3">
-        <f>+U33+V33-1</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="X33" s="3">
@@ -7295,7 +7303,7 @@
         <v>36</v>
       </c>
       <c r="AA33" s="6">
-        <f>+Z33+AB33-1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="AB33" s="3">
@@ -7311,21 +7319,21 @@
         <v>53</v>
       </c>
       <c r="AF33" s="3">
-        <f>+AE33+AA33-1</f>
+        <f t="shared" si="6"/>
         <v>89</v>
       </c>
       <c r="AG33" s="6">
         <v>3</v>
       </c>
       <c r="AH33" s="6">
-        <f>+AF33+AG33</f>
+        <f t="shared" si="7"/>
         <v>92</v>
       </c>
       <c r="AI33" s="3">
         <v>0</v>
       </c>
       <c r="AJ33" s="3">
-        <f>+AI33+AH33</f>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="AK33" s="3" t="s">
@@ -7335,36 +7343,36 @@
         <v>2</v>
       </c>
       <c r="AM33" s="3">
-        <f>+AJ33+AL33</f>
+        <f t="shared" si="9"/>
         <v>94</v>
       </c>
       <c r="AN33" s="3">
         <v>2</v>
       </c>
       <c r="AO33" s="3">
-        <f>+AM33+AN33</f>
+        <f t="shared" si="10"/>
         <v>96</v>
       </c>
       <c r="AP33" s="3">
         <v>2</v>
       </c>
       <c r="AQ33" s="3">
-        <f>+AO33+AP33</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR33" s="3">
-        <f>+AQ33+7</f>
+        <f t="shared" si="12"/>
         <v>105</v>
       </c>
       <c r="AS33" s="3">
-        <f>+AR33+7+AT33</f>
+        <f t="shared" si="13"/>
         <v>112</v>
       </c>
       <c r="AT33" s="3">
         <v>0</v>
       </c>
       <c r="AU33" s="3">
-        <f>+AA33-R33</f>
+        <f t="shared" si="14"/>
         <v>14</v>
       </c>
       <c r="AV33" s="3" t="s">
@@ -7424,37 +7432,37 @@
         <v>14</v>
       </c>
       <c r="O34" s="3">
-        <f>IF(I34="SFK Freight Forwarder",M34,M34+N34-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P34" s="3">
-        <f>+IF(I34="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q34" s="3">
-        <f>+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
+        <f t="shared" ref="Q34:Q65" si="20">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
         <v>0</v>
       </c>
       <c r="R34" s="3">
-        <f>9+N34</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S34" s="3">
         <v>7</v>
       </c>
       <c r="T34" s="3">
-        <f>+R34+S34-1</f>
+        <f t="shared" ref="T34:T65" si="21">+R34+S34-1</f>
         <v>29</v>
       </c>
       <c r="U34" s="3">
-        <f>+T34+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V34" s="3">
         <v>1</v>
       </c>
       <c r="W34" s="3">
-        <f>+U34+V34-1</f>
+        <f t="shared" ref="W34:W65" si="22">+U34+V34-1</f>
         <v>30</v>
       </c>
       <c r="X34" s="3">
@@ -7467,7 +7475,7 @@
         <v>33</v>
       </c>
       <c r="AA34" s="6">
-        <f>+Z34+AB34-1</f>
+        <f t="shared" si="19"/>
         <v>36</v>
       </c>
       <c r="AB34" s="3">
@@ -7483,21 +7491,21 @@
         <v>63</v>
       </c>
       <c r="AF34" s="3">
-        <f>+AE34+AA34-1</f>
+        <f t="shared" ref="AF34:AF65" si="23">+AE34+AA34-1</f>
         <v>98</v>
       </c>
       <c r="AG34" s="6">
         <v>3</v>
       </c>
       <c r="AH34" s="6">
-        <f>+AF34+AG34</f>
+        <f t="shared" ref="AH34:AH65" si="24">+AF34+AG34</f>
         <v>101</v>
       </c>
       <c r="AI34" s="3">
         <v>0</v>
       </c>
       <c r="AJ34" s="3">
-        <f>+AI34+AH34</f>
+        <f t="shared" ref="AJ34:AJ65" si="25">+AI34+AH34</f>
         <v>101</v>
       </c>
       <c r="AK34" s="3" t="s">
@@ -7507,36 +7515,36 @@
         <v>4</v>
       </c>
       <c r="AM34" s="3">
-        <f>+AJ34+AL34</f>
+        <f t="shared" ref="AM34:AM65" si="26">+AJ34+AL34</f>
         <v>105</v>
       </c>
       <c r="AN34" s="3">
         <v>3</v>
       </c>
       <c r="AO34" s="3">
-        <f>+AM34+AN34</f>
+        <f t="shared" ref="AO34:AO65" si="27">+AM34+AN34</f>
         <v>108</v>
       </c>
       <c r="AP34" s="3">
         <v>4</v>
       </c>
       <c r="AQ34" s="3">
-        <f>+AO34+AP34</f>
+        <f t="shared" si="11"/>
         <v>112</v>
       </c>
       <c r="AR34" s="3">
-        <f>+AQ34+7</f>
+        <f t="shared" si="12"/>
         <v>119</v>
       </c>
       <c r="AS34" s="3">
-        <f>+AR34+7+AT34</f>
+        <f t="shared" ref="AS34:AS65" si="28">+AR34+7+AT34</f>
         <v>126</v>
       </c>
       <c r="AT34" s="3">
         <v>0</v>
       </c>
       <c r="AU34" s="3">
-        <f>+AA34-R34</f>
+        <f t="shared" ref="AU34:AU54" si="29">+AA34-R34</f>
         <v>13</v>
       </c>
       <c r="AV34" s="3" t="s">
@@ -7596,37 +7604,37 @@
         <v>14</v>
       </c>
       <c r="O35" s="3">
-        <f>IF(I35="SFK Freight Forwarder",M35,M35+N35-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P35" s="3">
-        <f>+IF(I35="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <f>+IF(I35="SFK Freight Forwarder",O35,O35+P35-1)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R35" s="3">
-        <f>9+N35</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S35" s="3">
         <v>7</v>
       </c>
       <c r="T35" s="3">
-        <f>+R35+S35-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U35" s="3">
-        <f>+T35+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V35" s="3">
         <v>1</v>
       </c>
       <c r="W35" s="3">
-        <f>+U35+V35-1</f>
+        <f t="shared" si="22"/>
         <v>30</v>
       </c>
       <c r="X35" s="3">
@@ -7640,7 +7648,7 @@
         <v>33</v>
       </c>
       <c r="AA35" s="6">
-        <f>+Z35+AB35-1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="AB35" s="3">
@@ -7656,21 +7664,21 @@
         <v>48</v>
       </c>
       <c r="AF35" s="3">
-        <f>+AE35+AA35-1</f>
+        <f t="shared" si="23"/>
         <v>84</v>
       </c>
       <c r="AG35" s="6">
         <v>3</v>
       </c>
       <c r="AH35" s="6">
-        <f>+AF35+AG35</f>
+        <f t="shared" si="24"/>
         <v>87</v>
       </c>
       <c r="AI35" s="3">
         <v>14</v>
       </c>
       <c r="AJ35" s="3">
-        <f>+AI35+AH35</f>
+        <f t="shared" si="25"/>
         <v>101</v>
       </c>
       <c r="AK35" s="3" t="s">
@@ -7680,36 +7688,36 @@
         <v>2</v>
       </c>
       <c r="AM35" s="3">
-        <f>+AJ35+AL35</f>
+        <f t="shared" si="26"/>
         <v>103</v>
       </c>
       <c r="AN35" s="3">
         <v>2</v>
       </c>
       <c r="AO35" s="3">
-        <f>+AM35+AN35</f>
+        <f t="shared" si="27"/>
         <v>105</v>
       </c>
       <c r="AP35" s="3">
         <v>0</v>
       </c>
       <c r="AQ35" s="3">
-        <f>+AO35+AP35</f>
+        <f t="shared" si="11"/>
         <v>105</v>
       </c>
       <c r="AR35" s="3">
-        <f>+AQ35+7</f>
+        <f t="shared" si="12"/>
         <v>112</v>
       </c>
       <c r="AS35" s="3">
-        <f>+AR35+7+AT35</f>
+        <f t="shared" si="28"/>
         <v>119</v>
       </c>
       <c r="AT35" s="3">
         <v>0</v>
       </c>
       <c r="AU35" s="3">
-        <f>+AA35-R35</f>
+        <f t="shared" si="29"/>
         <v>14</v>
       </c>
       <c r="AV35" s="3" t="s">
@@ -7769,37 +7777,37 @@
         <v>14</v>
       </c>
       <c r="O36" s="3">
-        <f>IF(I36="SFK Freight Forwarder",M36,M36+N36-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P36" s="3">
-        <f>+IF(I36="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q36" s="3">
-        <f>+IF(I36="SFK Freight Forwarder",O36,O36+P36-1)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R36" s="3">
-        <f>9+N36</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S36" s="3">
         <v>7</v>
       </c>
       <c r="T36" s="3">
-        <f>+R36+S36-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U36" s="3">
-        <f>+T36+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V36" s="3">
         <v>2</v>
       </c>
       <c r="W36" s="3">
-        <f>+U36+V36-1</f>
+        <f t="shared" si="22"/>
         <v>31</v>
       </c>
       <c r="X36" s="3">
@@ -7812,7 +7820,7 @@
         <v>39</v>
       </c>
       <c r="AA36" s="6">
-        <f>+Z36+AB36-1</f>
+        <f t="shared" si="19"/>
         <v>44</v>
       </c>
       <c r="AB36" s="3">
@@ -7828,21 +7836,21 @@
         <v>17</v>
       </c>
       <c r="AF36" s="3">
-        <f>+AE36+AA36-1</f>
+        <f t="shared" si="23"/>
         <v>60</v>
       </c>
       <c r="AG36" s="6">
         <v>3</v>
       </c>
       <c r="AH36" s="6">
-        <f>+AF36+AG36</f>
+        <f t="shared" si="24"/>
         <v>63</v>
       </c>
       <c r="AI36" s="3">
         <v>0</v>
       </c>
       <c r="AJ36" s="3">
-        <f>+AI36+AH36</f>
+        <f t="shared" si="25"/>
         <v>63</v>
       </c>
       <c r="AK36" s="3" t="s">
@@ -7852,36 +7860,36 @@
         <v>0</v>
       </c>
       <c r="AM36" s="3">
-        <f>+AJ36+AL36</f>
+        <f t="shared" si="26"/>
         <v>63</v>
       </c>
       <c r="AN36" s="3">
         <v>0</v>
       </c>
       <c r="AO36" s="3">
-        <f>+AM36+AN36</f>
+        <f t="shared" si="27"/>
         <v>63</v>
       </c>
       <c r="AP36" s="3">
         <v>0</v>
       </c>
       <c r="AQ36" s="3">
-        <f>+AO36+AP36</f>
+        <f t="shared" si="11"/>
         <v>63</v>
       </c>
       <c r="AR36" s="3">
-        <f>+AQ36+7</f>
+        <f t="shared" si="12"/>
         <v>70</v>
       </c>
       <c r="AS36" s="3">
-        <f>+AR36+7+AT36</f>
+        <f t="shared" si="28"/>
         <v>77</v>
       </c>
       <c r="AT36" s="3">
         <v>0</v>
       </c>
       <c r="AU36" s="3">
-        <f>+AA36-R36</f>
+        <f t="shared" si="29"/>
         <v>21</v>
       </c>
       <c r="AV36" s="3" t="s">
@@ -7941,37 +7949,37 @@
         <v>14</v>
       </c>
       <c r="O37" s="3">
-        <f>IF(I37="SFK Freight Forwarder",M37,M37+N37-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P37" s="3">
-        <f>+IF(I37="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q37" s="3">
-        <f>+IF(I37="SFK Freight Forwarder",O37,O37+P37-1)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R37" s="3">
-        <f>9+N37</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S37" s="3">
         <v>7</v>
       </c>
       <c r="T37" s="3">
-        <f>+R37+S37-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U37" s="3">
-        <f>+T37+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V37" s="3">
         <v>2</v>
       </c>
       <c r="W37" s="3">
-        <f>+U37+V37-1</f>
+        <f t="shared" si="22"/>
         <v>31</v>
       </c>
       <c r="X37" s="3">
@@ -7984,7 +7992,7 @@
         <v>39</v>
       </c>
       <c r="AA37" s="6">
-        <f>+Z37+AB37-1</f>
+        <f t="shared" si="19"/>
         <v>44</v>
       </c>
       <c r="AB37" s="3">
@@ -8000,21 +8008,21 @@
         <v>34</v>
       </c>
       <c r="AF37" s="3">
-        <f>+AE37+AA37-1</f>
+        <f t="shared" si="23"/>
         <v>77</v>
       </c>
       <c r="AG37" s="6">
         <v>3</v>
       </c>
       <c r="AH37" s="6">
-        <f>+AF37+AG37</f>
+        <f t="shared" si="24"/>
         <v>80</v>
       </c>
       <c r="AI37" s="3">
         <v>0</v>
       </c>
       <c r="AJ37" s="3">
-        <f>+AI37+AH37</f>
+        <f t="shared" si="25"/>
         <v>80</v>
       </c>
       <c r="AK37" s="3" t="s">
@@ -8024,36 +8032,36 @@
         <v>2</v>
       </c>
       <c r="AM37" s="3">
-        <f>+AJ37+AL37</f>
+        <f t="shared" si="26"/>
         <v>82</v>
       </c>
       <c r="AN37" s="3">
         <v>2</v>
       </c>
       <c r="AO37" s="3">
-        <f>+AM37+AN37</f>
+        <f t="shared" si="27"/>
         <v>84</v>
       </c>
       <c r="AP37" s="3">
         <v>0</v>
       </c>
       <c r="AQ37" s="3">
-        <f>+AO37+AP37</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR37" s="3">
-        <f>+AQ37+7</f>
+        <f t="shared" si="12"/>
         <v>91</v>
       </c>
       <c r="AS37" s="3">
-        <f>+AR37+7+AT37</f>
+        <f t="shared" si="28"/>
         <v>98</v>
       </c>
       <c r="AT37" s="3">
         <v>0</v>
       </c>
       <c r="AU37" s="3">
-        <f>+AA37-R37</f>
+        <f t="shared" si="29"/>
         <v>21</v>
       </c>
       <c r="AV37" s="3" t="s">
@@ -8069,7 +8077,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>1034</v>
       </c>
@@ -8113,37 +8121,37 @@
         <v>14</v>
       </c>
       <c r="O38" s="3">
-        <f>IF(I38="SFK Freight Forwarder",M38,M38+N38-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P38" s="3">
-        <f>+IF(I38="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q38" s="3">
-        <f>+IF(I38="SFK Freight Forwarder",O38,O38+P38-1)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R38" s="3">
-        <f>9+N38</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S38" s="3">
         <v>7</v>
       </c>
       <c r="T38" s="3">
-        <f>+R38+S38-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U38" s="3">
-        <f>+T38+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V38" s="3">
         <v>1</v>
       </c>
       <c r="W38" s="3">
-        <f>+U38+V38-1</f>
+        <f t="shared" si="22"/>
         <v>30</v>
       </c>
       <c r="X38" s="3">
@@ -8156,7 +8164,7 @@
         <v>33</v>
       </c>
       <c r="AA38" s="6">
-        <f>+Z38+AB38-1</f>
+        <f t="shared" si="19"/>
         <v>35</v>
       </c>
       <c r="AB38" s="3">
@@ -8172,21 +8180,21 @@
         <v>53</v>
       </c>
       <c r="AF38" s="3">
-        <f>+AE38+AA38-1</f>
+        <f t="shared" si="23"/>
         <v>87</v>
       </c>
       <c r="AG38" s="6">
         <v>3</v>
       </c>
       <c r="AH38" s="6">
-        <f>+AF38+AG38</f>
+        <f t="shared" si="24"/>
         <v>90</v>
       </c>
       <c r="AI38" s="3">
         <v>0</v>
       </c>
       <c r="AJ38" s="3">
-        <f>+AI38+AH38</f>
+        <f t="shared" si="25"/>
         <v>90</v>
       </c>
       <c r="AK38" s="3" t="s">
@@ -8196,36 +8204,36 @@
         <v>2</v>
       </c>
       <c r="AM38" s="3">
-        <f>+AJ38+AL38</f>
+        <f t="shared" si="26"/>
         <v>92</v>
       </c>
       <c r="AN38" s="3">
         <v>6</v>
       </c>
       <c r="AO38" s="3">
-        <f>+AM38+AN38</f>
+        <f t="shared" si="27"/>
         <v>98</v>
       </c>
       <c r="AP38" s="3">
         <v>0</v>
       </c>
       <c r="AQ38" s="3">
-        <f>+AO38+AP38</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="AR38" s="3">
-        <f>+AQ38+7</f>
+        <f t="shared" si="12"/>
         <v>105</v>
       </c>
       <c r="AS38" s="3">
-        <f>+AR38+7+AT38</f>
+        <f t="shared" si="28"/>
         <v>112</v>
       </c>
       <c r="AT38" s="3">
         <v>0</v>
       </c>
       <c r="AU38" s="3">
-        <f>+AA38-R38</f>
+        <f t="shared" si="29"/>
         <v>12</v>
       </c>
       <c r="AV38" s="3" t="s">
@@ -8241,7 +8249,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1036</v>
       </c>
@@ -8285,37 +8293,37 @@
         <v>14</v>
       </c>
       <c r="O39" s="3">
-        <f>IF(I39="SFK Freight Forwarder",M39,M39+N39-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P39" s="3">
-        <f>+IF(I39="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q39" s="3">
-        <f>+IF(I39="SFK Freight Forwarder",O39,O39+P39-1)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R39" s="3">
-        <f>9+N39</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S39" s="3">
         <v>7</v>
       </c>
       <c r="T39" s="3">
-        <f>+R39+S39-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U39" s="3">
-        <f>+T39+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V39" s="3">
         <v>2</v>
       </c>
       <c r="W39" s="3">
-        <f>+U39+V39-1</f>
+        <f t="shared" si="22"/>
         <v>31</v>
       </c>
       <c r="X39" s="3">
@@ -8328,7 +8336,7 @@
         <v>34</v>
       </c>
       <c r="AA39" s="6">
-        <f>+Z39+AB39-1</f>
+        <f t="shared" si="19"/>
         <v>36</v>
       </c>
       <c r="AB39" s="3">
@@ -8344,21 +8352,21 @@
         <v>31</v>
       </c>
       <c r="AF39" s="3">
-        <f>+AE39+AA39-1</f>
+        <f t="shared" si="23"/>
         <v>66</v>
       </c>
       <c r="AG39" s="6">
         <v>3</v>
       </c>
       <c r="AH39" s="6">
-        <f>+AF39+AG39</f>
+        <f t="shared" si="24"/>
         <v>69</v>
       </c>
       <c r="AI39" s="3">
         <v>0</v>
       </c>
       <c r="AJ39" s="3">
-        <f>+AI39+AH39</f>
+        <f t="shared" si="25"/>
         <v>69</v>
       </c>
       <c r="AK39" s="3" t="s">
@@ -8368,36 +8376,36 @@
         <v>2</v>
       </c>
       <c r="AM39" s="3">
-        <f>+AJ39+AL39</f>
+        <f t="shared" si="26"/>
         <v>71</v>
       </c>
       <c r="AN39" s="3">
         <v>5</v>
       </c>
       <c r="AO39" s="3">
-        <f>+AM39+AN39</f>
+        <f t="shared" si="27"/>
         <v>76</v>
       </c>
       <c r="AP39" s="3">
         <v>1</v>
       </c>
       <c r="AQ39" s="3">
-        <f>+AO39+AP39</f>
+        <f t="shared" si="11"/>
         <v>77</v>
       </c>
       <c r="AR39" s="3">
-        <f>+AQ39+7</f>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="AS39" s="3">
-        <f>+AR39+7+AT39</f>
+        <f t="shared" si="28"/>
         <v>91</v>
       </c>
       <c r="AT39" s="3">
         <v>0</v>
       </c>
       <c r="AU39" s="3">
-        <f>+AA39-R39</f>
+        <f t="shared" si="29"/>
         <v>13</v>
       </c>
       <c r="AV39" s="3" t="s">
@@ -8457,37 +8465,37 @@
         <v>14</v>
       </c>
       <c r="O40" s="3">
-        <f>IF(I40="SFK Freight Forwarder",M40,M40+N40-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P40" s="3">
-        <f>+IF(I40="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q40" s="3">
-        <f>+IF(I40="SFK Freight Forwarder",O40,O40+P40-1)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R40" s="3">
-        <f>9+N40</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S40" s="3">
         <v>7</v>
       </c>
       <c r="T40" s="3">
-        <f>+R40+S40-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U40" s="3">
-        <f>+T40+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V40" s="3">
         <v>1</v>
       </c>
       <c r="W40" s="3">
-        <f>+U40+V40-1</f>
+        <f t="shared" si="22"/>
         <v>30</v>
       </c>
       <c r="X40" s="3">
@@ -8500,7 +8508,7 @@
         <v>33</v>
       </c>
       <c r="AA40" s="6">
-        <f>+Z40+AB40-1</f>
+        <f t="shared" si="19"/>
         <v>36</v>
       </c>
       <c r="AB40" s="3">
@@ -8516,21 +8524,21 @@
         <v>67</v>
       </c>
       <c r="AF40" s="3">
-        <f>+AE40+AA40-1</f>
+        <f t="shared" si="23"/>
         <v>102</v>
       </c>
       <c r="AG40" s="6">
         <v>3</v>
       </c>
       <c r="AH40" s="6">
-        <f>+AF40+AG40</f>
+        <f t="shared" si="24"/>
         <v>105</v>
       </c>
       <c r="AI40" s="3">
         <v>7</v>
       </c>
       <c r="AJ40" s="3">
-        <f>+AI40+AH40</f>
+        <f t="shared" si="25"/>
         <v>112</v>
       </c>
       <c r="AK40" s="3" t="s">
@@ -8540,36 +8548,36 @@
         <v>3</v>
       </c>
       <c r="AM40" s="3">
-        <f>+AJ40+AL40</f>
+        <f t="shared" si="26"/>
         <v>115</v>
       </c>
       <c r="AN40" s="3">
         <v>3</v>
       </c>
       <c r="AO40" s="3">
-        <f>+AM40+AN40</f>
+        <f t="shared" si="27"/>
         <v>118</v>
       </c>
       <c r="AP40" s="3">
         <v>1</v>
       </c>
       <c r="AQ40" s="3">
-        <f>+AO40+AP40</f>
+        <f t="shared" si="11"/>
         <v>119</v>
       </c>
       <c r="AR40" s="3">
-        <f>+AQ40+7</f>
+        <f t="shared" si="12"/>
         <v>126</v>
       </c>
       <c r="AS40" s="3">
-        <f>+AR40+7+AT40</f>
+        <f t="shared" si="28"/>
         <v>133</v>
       </c>
       <c r="AT40" s="3">
         <v>0</v>
       </c>
       <c r="AU40" s="3">
-        <f>+AA40-R40</f>
+        <f t="shared" si="29"/>
         <v>13</v>
       </c>
       <c r="AV40" s="3" t="s">
@@ -8630,36 +8638,36 @@
         <v>14</v>
       </c>
       <c r="O41" s="3">
-        <f>IF(I41="SFK Freight Forwarder",M41,M41+N41-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P41" s="3">
         <v>5</v>
       </c>
       <c r="Q41" s="3">
-        <f>+IF(I41="SFK Freight Forwarder",O41,O41+P41-1)</f>
+        <f t="shared" si="20"/>
         <v>26</v>
       </c>
       <c r="R41" s="3">
-        <f>9+N41</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S41" s="3">
         <v>7</v>
       </c>
       <c r="T41" s="3">
-        <f>+R41+S41-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U41" s="3">
-        <f>+T41+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V41" s="3">
         <v>1</v>
       </c>
       <c r="W41" s="3">
-        <f>+U41+V41-1</f>
+        <f t="shared" si="22"/>
         <v>30</v>
       </c>
       <c r="X41" s="3">
@@ -8672,7 +8680,7 @@
         <v>35</v>
       </c>
       <c r="AA41" s="6">
-        <f>+Z41+AB41-1</f>
+        <f t="shared" si="19"/>
         <v>37</v>
       </c>
       <c r="AB41" s="3">
@@ -8688,60 +8696,60 @@
         <v>40</v>
       </c>
       <c r="AF41" s="3">
-        <f>+AE41+AA41-1</f>
+        <f t="shared" si="23"/>
         <v>76</v>
       </c>
       <c r="AG41" s="6">
         <v>3</v>
       </c>
       <c r="AH41" s="6">
-        <f>+AF41+AG41</f>
+        <f t="shared" si="24"/>
         <v>79</v>
       </c>
       <c r="AI41" s="3">
         <v>7</v>
       </c>
       <c r="AJ41" s="3">
-        <f>+AI41+AH41</f>
+        <f t="shared" si="25"/>
         <v>86</v>
       </c>
       <c r="AK41" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AL41" s="3">
-        <v>3</v>
+      <c r="AL41" s="46">
+        <v>2</v>
       </c>
       <c r="AM41" s="3">
-        <f>+AJ41+AL41</f>
-        <v>89</v>
+        <f t="shared" si="26"/>
+        <v>88</v>
       </c>
       <c r="AN41" s="3">
         <v>8</v>
       </c>
       <c r="AO41" s="3">
-        <f>+AM41+AN41</f>
-        <v>97</v>
+        <f t="shared" si="27"/>
+        <v>96</v>
       </c>
       <c r="AP41" s="3">
         <v>2</v>
       </c>
       <c r="AQ41" s="3">
-        <f>+AO41+AP41</f>
-        <v>99</v>
+        <f t="shared" si="11"/>
+        <v>98</v>
       </c>
       <c r="AR41" s="3">
-        <f>+AQ41+7</f>
-        <v>106</v>
+        <f t="shared" si="12"/>
+        <v>105</v>
       </c>
       <c r="AS41" s="3">
-        <f>+AR41+7+AT41</f>
-        <v>130</v>
+        <f t="shared" si="28"/>
+        <v>129</v>
       </c>
       <c r="AT41" s="3">
         <v>17</v>
       </c>
       <c r="AU41" s="3">
-        <f>+AA41-R41</f>
+        <f t="shared" si="29"/>
         <v>14</v>
       </c>
       <c r="AV41" s="3" t="s">
@@ -8801,7 +8809,7 @@
         <v>14</v>
       </c>
       <c r="O42" s="3">
-        <f>IF(I42="SFK Freight Forwarder",M42,M42+N42-1)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P42" s="3">
@@ -8809,29 +8817,29 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
-        <f>+IF(I42="SFK Freight Forwarder",O42,O42+P42-1)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R42" s="3">
-        <f>9+N42</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S42" s="3">
         <v>7</v>
       </c>
       <c r="T42" s="3">
-        <f>+R42+S42-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U42" s="3">
-        <f>+T42+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V42" s="3">
         <v>1</v>
       </c>
       <c r="W42" s="3">
-        <f>+U42+V42-1</f>
+        <f t="shared" si="22"/>
         <v>30</v>
       </c>
       <c r="X42" s="3">
@@ -8844,7 +8852,7 @@
         <v>33</v>
       </c>
       <c r="AA42" s="6">
-        <f>+Z42+AB42-1</f>
+        <f t="shared" si="19"/>
         <v>36</v>
       </c>
       <c r="AB42" s="3">
@@ -8860,21 +8868,21 @@
         <v>32</v>
       </c>
       <c r="AF42" s="3">
-        <f>+AE42+AA42-1</f>
+        <f t="shared" si="23"/>
         <v>67</v>
       </c>
       <c r="AG42" s="6">
         <v>3</v>
       </c>
       <c r="AH42" s="6">
-        <f>+AF42+AG42</f>
+        <f t="shared" si="24"/>
         <v>70</v>
       </c>
       <c r="AI42" s="3">
         <v>0</v>
       </c>
       <c r="AJ42" s="3">
-        <f>+AI42+AH42</f>
+        <f t="shared" si="25"/>
         <v>70</v>
       </c>
       <c r="AK42" s="3" t="s">
@@ -8884,36 +8892,36 @@
         <v>4</v>
       </c>
       <c r="AM42" s="3">
-        <f>+AJ42+AL42</f>
+        <f t="shared" si="26"/>
         <v>74</v>
       </c>
       <c r="AN42" s="3">
         <v>3</v>
       </c>
       <c r="AO42" s="3">
-        <f>+AM42+AN42</f>
+        <f t="shared" si="27"/>
         <v>77</v>
       </c>
       <c r="AP42" s="3">
         <v>0</v>
       </c>
       <c r="AQ42" s="3">
-        <f>+AO42+AP42</f>
+        <f t="shared" si="11"/>
         <v>77</v>
       </c>
       <c r="AR42" s="3">
-        <f>+AQ42+7</f>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="AS42" s="3">
-        <f>+AR42+7+AT42</f>
+        <f t="shared" si="28"/>
         <v>91</v>
       </c>
       <c r="AT42" s="3">
         <v>0</v>
       </c>
       <c r="AU42" s="3">
-        <f>+AA42-R42</f>
+        <f t="shared" si="29"/>
         <v>13</v>
       </c>
       <c r="AV42" s="3" t="s">
@@ -8974,7 +8982,7 @@
         <v>21</v>
       </c>
       <c r="O43" s="3">
-        <f>IF(I43="SFK Freight Forwarder",M43,M43+N43-1)</f>
+        <f t="shared" si="15"/>
         <v>29</v>
       </c>
       <c r="P43" s="3">
@@ -8982,29 +8990,29 @@
         <v>5</v>
       </c>
       <c r="Q43" s="3">
-        <f>+IF(I43="SFK Freight Forwarder",O43,O43+P43-1)</f>
+        <f t="shared" si="20"/>
         <v>33</v>
       </c>
       <c r="R43" s="3">
-        <f>9+N43</f>
+        <f t="shared" si="16"/>
         <v>30</v>
       </c>
       <c r="S43" s="3">
         <v>7</v>
       </c>
       <c r="T43" s="3">
-        <f>+R43+S43-1</f>
+        <f t="shared" si="21"/>
         <v>36</v>
       </c>
       <c r="U43" s="3">
-        <f>+T43+1</f>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="V43" s="3">
         <v>1</v>
       </c>
       <c r="W43" s="3">
-        <f>+U43+V43-1</f>
+        <f t="shared" si="22"/>
         <v>37</v>
       </c>
       <c r="X43" s="3">
@@ -9017,7 +9025,7 @@
         <v>37</v>
       </c>
       <c r="AA43" s="6">
-        <f>+Z43+AB43-1</f>
+        <f t="shared" si="19"/>
         <v>39</v>
       </c>
       <c r="AB43" s="3">
@@ -9033,21 +9041,21 @@
         <v>46</v>
       </c>
       <c r="AF43" s="3">
-        <f>+AE43+AA43-1</f>
+        <f t="shared" si="23"/>
         <v>84</v>
       </c>
       <c r="AG43" s="6">
         <v>3</v>
       </c>
       <c r="AH43" s="6">
-        <f>+AF43+AG43</f>
+        <f t="shared" si="24"/>
         <v>87</v>
       </c>
       <c r="AI43" s="3">
         <v>7</v>
       </c>
       <c r="AJ43" s="3">
-        <f>+AI43+AH43</f>
+        <f t="shared" si="25"/>
         <v>94</v>
       </c>
       <c r="AK43" s="3" t="s">
@@ -9057,36 +9065,36 @@
         <v>4</v>
       </c>
       <c r="AM43" s="3">
-        <f>+AJ43+AL43</f>
+        <f t="shared" si="26"/>
         <v>98</v>
       </c>
       <c r="AN43" s="3">
         <v>3</v>
       </c>
       <c r="AO43" s="3">
-        <f>+AM43+AN43</f>
+        <f t="shared" si="27"/>
         <v>101</v>
       </c>
       <c r="AP43" s="3">
         <v>4</v>
       </c>
       <c r="AQ43" s="3">
-        <f>+AO43+AP43</f>
+        <f t="shared" si="11"/>
         <v>105</v>
       </c>
       <c r="AR43" s="3">
-        <f>+AQ43+7</f>
+        <f t="shared" si="12"/>
         <v>112</v>
       </c>
       <c r="AS43" s="3">
-        <f>+AR43+7+AT43</f>
+        <f t="shared" si="28"/>
         <v>119</v>
       </c>
       <c r="AT43" s="3">
         <v>0</v>
       </c>
       <c r="AU43" s="3">
-        <f>+AA43-R43</f>
+        <f t="shared" si="29"/>
         <v>9</v>
       </c>
       <c r="AV43" s="3" t="s">
@@ -9147,7 +9155,7 @@
         <v>14</v>
       </c>
       <c r="O44" s="3">
-        <f>IF(I44="SFK Freight Forwarder",M44,M44+N44-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P44" s="3">
@@ -9155,29 +9163,29 @@
         <v>5</v>
       </c>
       <c r="Q44" s="3">
-        <f>+IF(I44="SFK Freight Forwarder",O44,O44+P44-1)</f>
+        <f t="shared" si="20"/>
         <v>26</v>
       </c>
       <c r="R44" s="3">
-        <f>9+N44</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="S44" s="3">
         <v>7</v>
       </c>
       <c r="T44" s="3">
-        <f>+R44+S44-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U44" s="3">
-        <f>+T44+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V44" s="3">
         <v>2</v>
       </c>
       <c r="W44" s="3">
-        <f>+U44+V44-1</f>
+        <f t="shared" si="22"/>
         <v>31</v>
       </c>
       <c r="X44" s="3">
@@ -9190,7 +9198,7 @@
         <v>39</v>
       </c>
       <c r="AA44" s="6">
-        <f>+Z44+AB44-1</f>
+        <f t="shared" si="19"/>
         <v>41</v>
       </c>
       <c r="AB44" s="3">
@@ -9206,21 +9214,21 @@
         <v>35</v>
       </c>
       <c r="AF44" s="3">
-        <f>+AE44+AA44-1</f>
+        <f t="shared" si="23"/>
         <v>75</v>
       </c>
       <c r="AG44" s="6">
         <v>3</v>
       </c>
       <c r="AH44" s="6">
-        <f>+AF44+AG44</f>
+        <f t="shared" si="24"/>
         <v>78</v>
       </c>
       <c r="AI44" s="3">
         <v>0</v>
       </c>
       <c r="AJ44" s="3">
-        <f>+AI44+AH44</f>
+        <f t="shared" si="25"/>
         <v>78</v>
       </c>
       <c r="AK44" s="3" t="s">
@@ -9230,36 +9238,36 @@
         <v>2</v>
       </c>
       <c r="AM44" s="3">
-        <f>+AJ44+AL44</f>
+        <f t="shared" si="26"/>
         <v>80</v>
       </c>
       <c r="AN44" s="3">
         <v>2</v>
       </c>
       <c r="AO44" s="3">
-        <f>+AM44+AN44</f>
+        <f t="shared" si="27"/>
         <v>82</v>
       </c>
       <c r="AP44" s="3">
         <v>2</v>
       </c>
       <c r="AQ44" s="3">
-        <f>+AO44+AP44</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AR44" s="3">
-        <f>+AQ44+7</f>
+        <f t="shared" si="12"/>
         <v>91</v>
       </c>
       <c r="AS44" s="3">
-        <f>+AR44+7+AT44</f>
+        <f t="shared" si="28"/>
         <v>98</v>
       </c>
       <c r="AT44" s="3">
         <v>0</v>
       </c>
       <c r="AU44" s="3">
-        <f>+AA44-R44</f>
+        <f t="shared" si="29"/>
         <v>18</v>
       </c>
       <c r="AV44" s="3" t="s">
@@ -9319,14 +9327,14 @@
         <v>1</v>
       </c>
       <c r="O45" s="3">
-        <f>IF(I45="SFK Freight Forwarder",M45,M45+N45-1)</f>
+        <f t="shared" si="15"/>
         <v>8</v>
       </c>
       <c r="P45" s="3">
         <v>6</v>
       </c>
       <c r="Q45" s="3">
-        <f>+IF(I45="SFK Freight Forwarder",O45,O45+P45-1)</f>
+        <f t="shared" si="20"/>
         <v>13</v>
       </c>
       <c r="R45" s="23">
@@ -9336,7 +9344,7 @@
         <v>12</v>
       </c>
       <c r="T45" s="23">
-        <f>+R45+S45-1</f>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="U45" s="23">
@@ -9347,7 +9355,7 @@
         <v>5</v>
       </c>
       <c r="W45" s="23">
-        <f>+U45+V45-1</f>
+        <f t="shared" si="22"/>
         <v>26</v>
       </c>
       <c r="X45" s="23">
@@ -9371,21 +9379,21 @@
         <v>41</v>
       </c>
       <c r="AF45" s="23">
-        <f>+AE45+AA45-1</f>
+        <f t="shared" si="23"/>
         <v>71</v>
       </c>
       <c r="AG45" s="23">
         <v>3</v>
       </c>
       <c r="AH45" s="23">
-        <f>+AF45+AG45</f>
+        <f t="shared" si="24"/>
         <v>74</v>
       </c>
       <c r="AI45" s="23">
         <v>7</v>
       </c>
       <c r="AJ45" s="23">
-        <f>+AI45+AH45</f>
+        <f t="shared" si="25"/>
         <v>81</v>
       </c>
       <c r="AK45" s="23"/>
@@ -9393,14 +9401,14 @@
         <v>3</v>
       </c>
       <c r="AM45" s="23">
-        <f>+AJ45+AL45</f>
+        <f t="shared" si="26"/>
         <v>84</v>
       </c>
       <c r="AN45" s="23">
         <v>5</v>
       </c>
       <c r="AO45" s="23">
-        <f>+AM45+AN45</f>
+        <f t="shared" si="27"/>
         <v>89</v>
       </c>
       <c r="AP45" s="23">
@@ -9414,14 +9422,14 @@
         <v>96</v>
       </c>
       <c r="AS45" s="23">
-        <f>+AR45+7+AT45</f>
+        <f t="shared" si="28"/>
         <v>117</v>
       </c>
       <c r="AT45" s="23">
         <v>14</v>
       </c>
       <c r="AU45" s="3">
-        <f>+AA45-R45</f>
+        <f t="shared" si="29"/>
         <v>22</v>
       </c>
       <c r="AV45" s="23" t="s">
@@ -9481,14 +9489,14 @@
         <v>1</v>
       </c>
       <c r="O46" s="3">
-        <f>IF(I46="SFK Freight Forwarder",M46,M46+N46-1)</f>
+        <f t="shared" si="15"/>
         <v>8</v>
       </c>
       <c r="P46" s="3">
         <v>6</v>
       </c>
       <c r="Q46" s="3">
-        <f>+IF(I46="SFK Freight Forwarder",O46,O46+P46-1)</f>
+        <f t="shared" si="20"/>
         <v>13</v>
       </c>
       <c r="R46" s="23">
@@ -9498,7 +9506,7 @@
         <v>12</v>
       </c>
       <c r="T46" s="23">
-        <f>+R46+S46-1</f>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="U46" s="23">
@@ -9509,7 +9517,7 @@
         <v>5</v>
       </c>
       <c r="W46" s="23">
-        <f>+U46+V46-1</f>
+        <f t="shared" si="22"/>
         <v>26</v>
       </c>
       <c r="X46" s="23">
@@ -9533,21 +9541,21 @@
         <v>34</v>
       </c>
       <c r="AF46" s="23">
-        <f>+AE46+AA46-1</f>
+        <f t="shared" si="23"/>
         <v>69</v>
       </c>
       <c r="AG46" s="23">
         <v>3</v>
       </c>
       <c r="AH46" s="23">
-        <f>+AF46+AG46</f>
+        <f t="shared" si="24"/>
         <v>72</v>
       </c>
       <c r="AI46" s="23">
         <v>0</v>
       </c>
       <c r="AJ46" s="23">
-        <f>+AI46+AH46</f>
+        <f t="shared" si="25"/>
         <v>72</v>
       </c>
       <c r="AK46" s="23"/>
@@ -9555,21 +9563,21 @@
         <v>2</v>
       </c>
       <c r="AM46" s="23">
-        <f>+AJ46+AL46</f>
+        <f t="shared" si="26"/>
         <v>74</v>
       </c>
       <c r="AN46" s="23">
         <v>1</v>
       </c>
       <c r="AO46" s="23">
-        <f>+AM46+AN46</f>
+        <f t="shared" si="27"/>
         <v>75</v>
       </c>
       <c r="AP46" s="23">
         <v>3</v>
       </c>
       <c r="AQ46" s="3">
-        <f>+AO46+AP46</f>
+        <f t="shared" ref="AQ46:AQ54" si="30">+AO46+AP46</f>
         <v>78</v>
       </c>
       <c r="AR46" s="23">
@@ -9577,14 +9585,14 @@
         <v>82</v>
       </c>
       <c r="AS46" s="23">
-        <f>+AR46+7+AT46</f>
+        <f t="shared" si="28"/>
         <v>103</v>
       </c>
       <c r="AT46" s="23">
         <v>14</v>
       </c>
       <c r="AU46" s="3">
-        <f>+AA46-R46</f>
+        <f t="shared" si="29"/>
         <v>27</v>
       </c>
       <c r="AV46" s="23" t="s">
@@ -9597,7 +9605,7 @@
         <v>56</v>
       </c>
       <c r="AY46" s="40">
-        <v>46508</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
@@ -9638,44 +9646,44 @@
         <v>7</v>
       </c>
       <c r="M47" s="3">
-        <f>+IF(I47="SFK Freight Forwarder",L47,9)</f>
+        <f t="shared" ref="M47:M54" si="31">+IF(I47="SFK Freight Forwarder",L47,9)</f>
         <v>9</v>
       </c>
       <c r="N47" s="3">
         <v>14</v>
       </c>
       <c r="O47" s="3">
-        <f>IF(I47="SFK Freight Forwarder",M47,M47+N47-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P47" s="3">
-        <f>+IF(I47="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P47:P52" si="32">+IF(I47="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q47" s="3">
-        <f>+IF(I47="SFK Freight Forwarder",O47,O47+P47-1)</f>
+        <f t="shared" si="20"/>
         <v>26</v>
       </c>
       <c r="R47" s="3">
-        <f>9+N47</f>
+        <f t="shared" ref="R47:R52" si="33">9+N47</f>
         <v>23</v>
       </c>
       <c r="S47" s="3">
         <v>7</v>
       </c>
       <c r="T47" s="3">
-        <f>+R47+S47-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U47" s="3">
-        <f>+T47+1</f>
+        <f t="shared" ref="U47:U52" si="34">+T47+1</f>
         <v>30</v>
       </c>
       <c r="V47" s="3">
         <v>2</v>
       </c>
       <c r="W47" s="3">
-        <f>+U47+V47-1</f>
+        <f t="shared" si="22"/>
         <v>31</v>
       </c>
       <c r="X47" s="3">
@@ -9706,21 +9714,21 @@
         <v>40</v>
       </c>
       <c r="AF47" s="3">
-        <f>+AE47+AA47-1</f>
+        <f t="shared" si="23"/>
         <v>73</v>
       </c>
       <c r="AG47" s="6">
         <v>3</v>
       </c>
       <c r="AH47" s="6">
-        <f>+AF47+AG47</f>
+        <f t="shared" si="24"/>
         <v>76</v>
       </c>
       <c r="AI47" s="3">
         <v>0</v>
       </c>
       <c r="AJ47" s="3">
-        <f>+AI47+AH47</f>
+        <f t="shared" si="25"/>
         <v>76</v>
       </c>
       <c r="AK47" s="3" t="s">
@@ -9730,36 +9738,36 @@
         <v>2</v>
       </c>
       <c r="AM47" s="3">
-        <f>+AJ47+AL47</f>
+        <f t="shared" si="26"/>
         <v>78</v>
       </c>
       <c r="AN47" s="3">
         <v>2</v>
       </c>
       <c r="AO47" s="3">
-        <f>+AM47+AN47</f>
+        <f t="shared" si="27"/>
         <v>80</v>
       </c>
       <c r="AP47" s="3">
         <v>6</v>
       </c>
       <c r="AQ47" s="3">
-        <f>+AO47+AP47</f>
+        <f t="shared" si="30"/>
         <v>86</v>
       </c>
       <c r="AR47" s="3">
-        <f>+AQ47+7</f>
+        <f t="shared" ref="AR47:AR54" si="35">+AQ47+7</f>
         <v>93</v>
       </c>
       <c r="AS47" s="3">
-        <f>+AR47+7+AT47</f>
+        <f t="shared" si="28"/>
         <v>100</v>
       </c>
       <c r="AT47" s="3">
         <v>0</v>
       </c>
       <c r="AU47" s="3">
-        <f>+AA47-R47</f>
+        <f t="shared" si="29"/>
         <v>11</v>
       </c>
       <c r="AV47" s="3" t="s">
@@ -9813,44 +9821,44 @@
         <v>7</v>
       </c>
       <c r="M48" s="3">
-        <f>+IF(I48="SFK Freight Forwarder",L48,9)</f>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="N48" s="3">
         <v>14</v>
       </c>
       <c r="O48" s="3">
-        <f>IF(I48="SFK Freight Forwarder",M48,M48+N48-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P48" s="3">
-        <f>+IF(I48="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="32"/>
         <v>5</v>
       </c>
       <c r="Q48" s="3">
-        <f>+IF(I48="SFK Freight Forwarder",O48,O48+P48-1)</f>
+        <f t="shared" si="20"/>
         <v>26</v>
       </c>
       <c r="R48" s="3">
-        <f>9+N48</f>
+        <f t="shared" si="33"/>
         <v>23</v>
       </c>
       <c r="S48" s="3">
         <v>7</v>
       </c>
       <c r="T48" s="3">
-        <f>+R48+S48-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U48" s="3">
-        <f>+T48+1</f>
+        <f t="shared" si="34"/>
         <v>30</v>
       </c>
       <c r="V48" s="3">
         <v>2</v>
       </c>
       <c r="W48" s="3">
-        <f>+U48+V48-1</f>
+        <f t="shared" si="22"/>
         <v>31</v>
       </c>
       <c r="X48" s="3">
@@ -9878,21 +9886,21 @@
         <v>68</v>
       </c>
       <c r="AF48" s="3">
-        <f>+AE48+AA48-1</f>
+        <f t="shared" si="23"/>
         <v>103</v>
       </c>
       <c r="AG48" s="6">
         <v>3</v>
       </c>
       <c r="AH48" s="6">
-        <f>+AF48+AG48</f>
+        <f t="shared" si="24"/>
         <v>106</v>
       </c>
       <c r="AI48" s="3">
         <v>0</v>
       </c>
       <c r="AJ48" s="3">
-        <f>+AI48+AH48</f>
+        <f t="shared" si="25"/>
         <v>106</v>
       </c>
       <c r="AK48" s="3" t="s">
@@ -9902,36 +9910,36 @@
         <v>2</v>
       </c>
       <c r="AM48" s="3">
-        <f>+AJ48+AL48</f>
+        <f t="shared" si="26"/>
         <v>108</v>
       </c>
       <c r="AN48" s="3">
         <v>7</v>
       </c>
       <c r="AO48" s="3">
-        <f>+AM48+AN48</f>
+        <f t="shared" si="27"/>
         <v>115</v>
       </c>
       <c r="AP48" s="3">
         <v>5</v>
       </c>
       <c r="AQ48" s="3">
-        <f>+AO48+AP48</f>
+        <f t="shared" si="30"/>
         <v>120</v>
       </c>
       <c r="AR48" s="3">
-        <f>+AQ48+7</f>
+        <f t="shared" si="35"/>
         <v>127</v>
       </c>
       <c r="AS48" s="3">
-        <f>+AR48+7+AT48</f>
+        <f t="shared" si="28"/>
         <v>134</v>
       </c>
       <c r="AT48" s="3">
         <v>0</v>
       </c>
       <c r="AU48" s="3">
-        <f>+AA48-R48</f>
+        <f t="shared" si="29"/>
         <v>13</v>
       </c>
       <c r="AV48" s="3" t="s">
@@ -9985,44 +9993,44 @@
         <v>7</v>
       </c>
       <c r="M49" s="3">
-        <f>+IF(I49="SFK Freight Forwarder",L49,9)</f>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="N49" s="3">
         <v>14</v>
       </c>
       <c r="O49" s="3">
-        <f>IF(I49="SFK Freight Forwarder",M49,M49+N49-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P49" s="3">
-        <f>+IF(I49="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="32"/>
         <v>5</v>
       </c>
       <c r="Q49" s="3">
-        <f>+IF(I49="SFK Freight Forwarder",O49,O49+P49-1)</f>
+        <f t="shared" si="20"/>
         <v>26</v>
       </c>
       <c r="R49" s="3">
-        <f>9+N49</f>
+        <f t="shared" si="33"/>
         <v>23</v>
       </c>
       <c r="S49" s="3">
         <v>7</v>
       </c>
       <c r="T49" s="3">
-        <f>+R49+S49-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U49" s="3">
-        <f>+T49+1</f>
+        <f t="shared" si="34"/>
         <v>30</v>
       </c>
       <c r="V49" s="3">
         <v>2</v>
       </c>
       <c r="W49" s="3">
-        <f>+U49+V49-1</f>
+        <f t="shared" si="22"/>
         <v>31</v>
       </c>
       <c r="X49" s="3">
@@ -10035,7 +10043,7 @@
         <v>33</v>
       </c>
       <c r="AA49" s="6">
-        <f>+Z49+AB49-1</f>
+        <f t="shared" ref="AA49:AA54" si="36">+Z49+AB49-1</f>
         <v>38</v>
       </c>
       <c r="AB49" s="3">
@@ -10051,60 +10059,60 @@
         <v>42</v>
       </c>
       <c r="AF49" s="3">
-        <f>+AE49+AA49-1</f>
+        <f t="shared" si="23"/>
         <v>79</v>
       </c>
       <c r="AG49" s="6">
         <v>3</v>
       </c>
       <c r="AH49" s="6">
-        <f>+AF49+AG49</f>
+        <f t="shared" si="24"/>
         <v>82</v>
       </c>
       <c r="AI49" s="3">
         <v>0</v>
       </c>
       <c r="AJ49" s="3">
-        <f>+AI49+AH49</f>
+        <f t="shared" si="25"/>
         <v>82</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AL49" s="3">
-        <v>1</v>
+      <c r="AL49" s="46">
+        <v>2</v>
       </c>
       <c r="AM49" s="3">
-        <f>+AJ49+AL49</f>
-        <v>83</v>
+        <f t="shared" si="26"/>
+        <v>84</v>
       </c>
       <c r="AN49" s="3">
         <v>1</v>
       </c>
       <c r="AO49" s="3">
-        <f>+AM49+AN49</f>
-        <v>84</v>
+        <f t="shared" si="27"/>
+        <v>85</v>
       </c>
       <c r="AP49" s="3">
         <v>3</v>
       </c>
       <c r="AQ49" s="3">
-        <f>+AO49+AP49</f>
-        <v>87</v>
+        <f t="shared" si="30"/>
+        <v>88</v>
       </c>
       <c r="AR49" s="3">
-        <f>+AQ49+7</f>
-        <v>94</v>
+        <f t="shared" si="35"/>
+        <v>95</v>
       </c>
       <c r="AS49" s="3">
-        <f>+AR49+7+AT49</f>
-        <v>101</v>
+        <f t="shared" si="28"/>
+        <v>102</v>
       </c>
       <c r="AT49" s="3">
         <v>0</v>
       </c>
       <c r="AU49" s="3">
-        <f>+AA49-R49</f>
+        <f t="shared" si="29"/>
         <v>15</v>
       </c>
       <c r="AV49" s="3" t="s">
@@ -10158,44 +10166,44 @@
         <v>7</v>
       </c>
       <c r="M50" s="3">
-        <f>+IF(I50="SFK Freight Forwarder",L50,9)</f>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="N50" s="3">
         <v>14</v>
       </c>
       <c r="O50" s="3">
-        <f>IF(I50="SFK Freight Forwarder",M50,M50+N50-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P50" s="3">
-        <f>+IF(I50="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="32"/>
         <v>5</v>
       </c>
       <c r="Q50" s="3">
-        <f>+IF(I50="SFK Freight Forwarder",O50,O50+P50-1)</f>
+        <f t="shared" si="20"/>
         <v>26</v>
       </c>
       <c r="R50" s="3">
-        <f>9+N50</f>
+        <f t="shared" si="33"/>
         <v>23</v>
       </c>
       <c r="S50" s="3">
         <v>7</v>
       </c>
       <c r="T50" s="3">
-        <f>+R50+S50-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U50" s="3">
-        <f>+T50+1</f>
+        <f t="shared" si="34"/>
         <v>30</v>
       </c>
       <c r="V50" s="3">
         <v>2</v>
       </c>
       <c r="W50" s="3">
-        <f>+U50+V50-1</f>
+        <f t="shared" si="22"/>
         <v>31</v>
       </c>
       <c r="X50" s="3">
@@ -10210,7 +10218,7 @@
         <v>31</v>
       </c>
       <c r="AA50" s="6">
-        <f>+Z50+AB50-1</f>
+        <f t="shared" si="36"/>
         <v>34</v>
       </c>
       <c r="AB50" s="3">
@@ -10226,21 +10234,21 @@
         <v>48</v>
       </c>
       <c r="AF50" s="3">
-        <f>+AE50+AA50-1</f>
+        <f t="shared" si="23"/>
         <v>81</v>
       </c>
       <c r="AG50" s="6">
         <v>0</v>
       </c>
       <c r="AH50" s="6">
-        <f>+AF50+AG50</f>
+        <f t="shared" si="24"/>
         <v>81</v>
       </c>
       <c r="AI50" s="3">
         <v>0</v>
       </c>
       <c r="AJ50" s="3">
-        <f>+AI50+AH50</f>
+        <f t="shared" si="25"/>
         <v>81</v>
       </c>
       <c r="AK50" s="3" t="s">
@@ -10250,36 +10258,36 @@
         <v>3</v>
       </c>
       <c r="AM50" s="3">
-        <f>+AJ50+AL50</f>
+        <f t="shared" si="26"/>
         <v>84</v>
       </c>
       <c r="AN50" s="3">
         <v>8</v>
       </c>
       <c r="AO50" s="3">
-        <f>+AM50+AN50</f>
+        <f t="shared" si="27"/>
         <v>92</v>
       </c>
       <c r="AP50" s="3">
         <v>0</v>
       </c>
       <c r="AQ50" s="3">
-        <f>+AO50+AP50</f>
+        <f t="shared" si="30"/>
         <v>92</v>
       </c>
       <c r="AR50" s="3">
-        <f>+AQ50+7</f>
+        <f t="shared" si="35"/>
         <v>99</v>
       </c>
       <c r="AS50" s="3">
-        <f>+AR50+7+AT50</f>
+        <f t="shared" si="28"/>
         <v>106</v>
       </c>
       <c r="AT50" s="3">
         <v>0</v>
       </c>
       <c r="AU50" s="3">
-        <f>+AA50-R50</f>
+        <f t="shared" si="29"/>
         <v>11</v>
       </c>
       <c r="AV50" s="3" t="s">
@@ -10333,44 +10341,44 @@
         <v>2</v>
       </c>
       <c r="M51" s="3">
-        <f>+IF(I51="SFK Freight Forwarder",L51,9)</f>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="N51" s="3">
         <v>14</v>
       </c>
       <c r="O51" s="3">
-        <f>IF(I51="SFK Freight Forwarder",M51,M51+N51-1)</f>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="P51" s="3">
-        <f>+IF(I51="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="32"/>
         <v>5</v>
       </c>
       <c r="Q51" s="3">
-        <f>+IF(I51="SFK Freight Forwarder",O51,O51+P51-1)</f>
+        <f t="shared" si="20"/>
         <v>26</v>
       </c>
       <c r="R51" s="3">
-        <f>9+N51</f>
+        <f t="shared" si="33"/>
         <v>23</v>
       </c>
       <c r="S51" s="3">
         <v>7</v>
       </c>
       <c r="T51" s="3">
-        <f>+R51+S51-1</f>
+        <f t="shared" si="21"/>
         <v>29</v>
       </c>
       <c r="U51" s="3">
-        <f>+T51+1</f>
+        <f t="shared" si="34"/>
         <v>30</v>
       </c>
       <c r="V51" s="3">
         <v>2</v>
       </c>
       <c r="W51" s="3">
-        <f>+U51+V51-1</f>
+        <f t="shared" si="22"/>
         <v>31</v>
       </c>
       <c r="X51" s="3">
@@ -10385,7 +10393,7 @@
         <v>33</v>
       </c>
       <c r="AA51" s="6">
-        <f>+Z51+AB51-1</f>
+        <f t="shared" si="36"/>
         <v>34</v>
       </c>
       <c r="AB51" s="3">
@@ -10401,21 +10409,21 @@
         <v>50</v>
       </c>
       <c r="AF51" s="3">
-        <f>+AE51+AA51-1</f>
+        <f t="shared" si="23"/>
         <v>83</v>
       </c>
       <c r="AG51" s="6">
         <v>3</v>
       </c>
       <c r="AH51" s="6">
-        <f>+AF51+AG51</f>
+        <f t="shared" si="24"/>
         <v>86</v>
       </c>
       <c r="AI51" s="3">
         <v>0</v>
       </c>
       <c r="AJ51" s="3">
-        <f>+AI51+AH51</f>
+        <f t="shared" si="25"/>
         <v>86</v>
       </c>
       <c r="AK51" s="3" t="s">
@@ -10425,36 +10433,36 @@
         <v>4</v>
       </c>
       <c r="AM51" s="3">
-        <f>+AJ51+AL51</f>
+        <f t="shared" si="26"/>
         <v>90</v>
       </c>
       <c r="AN51" s="3">
         <v>2</v>
       </c>
       <c r="AO51" s="3">
-        <f>+AM51+AN51</f>
+        <f t="shared" si="27"/>
         <v>92</v>
       </c>
       <c r="AP51" s="3">
         <v>1</v>
       </c>
       <c r="AQ51" s="3">
-        <f>+AO51+AP51</f>
+        <f t="shared" si="30"/>
         <v>93</v>
       </c>
       <c r="AR51" s="3">
-        <f>+AQ51+7</f>
+        <f t="shared" si="35"/>
         <v>100</v>
       </c>
       <c r="AS51" s="3">
-        <f>+AR51+7+AT51</f>
+        <f t="shared" si="28"/>
         <v>107</v>
       </c>
       <c r="AT51" s="3">
         <v>0</v>
       </c>
       <c r="AU51" s="3">
-        <f>+AA51-R51</f>
+        <f t="shared" si="29"/>
         <v>11</v>
       </c>
       <c r="AV51" s="3" t="s">
@@ -10508,44 +10516,44 @@
         <v>7</v>
       </c>
       <c r="M52" s="3">
-        <f>+IF(I52="SFK Freight Forwarder",L52,9)</f>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="N52" s="3">
         <v>7</v>
       </c>
       <c r="O52" s="3">
-        <f>IF(I52="SFK Freight Forwarder",M52,M52+N52-1)</f>
+        <f t="shared" si="15"/>
         <v>15</v>
       </c>
       <c r="P52" s="3">
-        <f>+IF(I52="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="32"/>
         <v>5</v>
       </c>
       <c r="Q52" s="3">
-        <f>+IF(I52="SFK Freight Forwarder",O52,O52+P52-1)</f>
+        <f t="shared" si="20"/>
         <v>19</v>
       </c>
       <c r="R52" s="3">
-        <f>9+N52</f>
+        <f t="shared" si="33"/>
         <v>16</v>
       </c>
       <c r="S52" s="3">
         <v>3</v>
       </c>
       <c r="T52" s="3">
-        <f>+R52+S52-1</f>
+        <f t="shared" si="21"/>
         <v>18</v>
       </c>
       <c r="U52" s="3">
-        <f>+T52+1</f>
+        <f t="shared" si="34"/>
         <v>19</v>
       </c>
       <c r="V52" s="3">
         <v>5</v>
       </c>
       <c r="W52" s="3">
-        <f>+U52+V52-1</f>
+        <f t="shared" si="22"/>
         <v>23</v>
       </c>
       <c r="X52" s="3">
@@ -10559,7 +10567,7 @@
         <v>23</v>
       </c>
       <c r="AA52" s="6">
-        <f>+Z52+AB52-1</f>
+        <f t="shared" si="36"/>
         <v>25</v>
       </c>
       <c r="AB52" s="3">
@@ -10575,21 +10583,21 @@
         <v>40</v>
       </c>
       <c r="AF52" s="3">
-        <f>+AE52+AA52-1</f>
+        <f t="shared" si="23"/>
         <v>64</v>
       </c>
       <c r="AG52" s="6">
         <v>3</v>
       </c>
       <c r="AH52" s="6">
-        <f>+AF52+AG52</f>
+        <f t="shared" si="24"/>
         <v>67</v>
       </c>
       <c r="AI52" s="3">
         <v>7</v>
       </c>
       <c r="AJ52" s="3">
-        <f>+AI52+AH52</f>
+        <f t="shared" si="25"/>
         <v>74</v>
       </c>
       <c r="AK52" s="3">
@@ -10599,36 +10607,36 @@
         <v>6</v>
       </c>
       <c r="AM52" s="3">
-        <f>+AJ52+AL52</f>
+        <f t="shared" si="26"/>
         <v>80</v>
       </c>
       <c r="AN52" s="3">
         <v>2</v>
       </c>
       <c r="AO52" s="3">
-        <f>+AM52+AN52</f>
+        <f t="shared" si="27"/>
         <v>82</v>
       </c>
       <c r="AP52" s="3">
         <v>0</v>
       </c>
       <c r="AQ52" s="3">
-        <f>+AO52+AP52</f>
+        <f t="shared" si="30"/>
         <v>82</v>
       </c>
       <c r="AR52" s="3">
-        <f>+AQ52+7</f>
+        <f t="shared" si="35"/>
         <v>89</v>
       </c>
       <c r="AS52" s="3">
-        <f>+AR52+7+AT52</f>
+        <f t="shared" si="28"/>
         <v>96</v>
       </c>
       <c r="AT52" s="3">
         <v>0</v>
       </c>
       <c r="AU52" s="3">
-        <f>+AA52-R52</f>
+        <f t="shared" si="29"/>
         <v>9</v>
       </c>
       <c r="AV52" s="3" t="s">
@@ -10682,21 +10690,21 @@
         <v>5</v>
       </c>
       <c r="M53" s="3">
-        <f>+IF(I53="SFK Freight Forwarder",L53,9)</f>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="N53" s="23">
         <v>2</v>
       </c>
       <c r="O53" s="3">
-        <f>IF(I53="SFK Freight Forwarder",M53,M53+N53-1)</f>
+        <f t="shared" si="15"/>
         <v>10</v>
       </c>
       <c r="P53" s="3">
         <v>5</v>
       </c>
       <c r="Q53" s="3">
-        <f>+IF(I53="SFK Freight Forwarder",O53,O53+P53-1)</f>
+        <f t="shared" si="20"/>
         <v>14</v>
       </c>
       <c r="R53" s="23">
@@ -10715,7 +10723,7 @@
         <v>4</v>
       </c>
       <c r="W53" s="23">
-        <f>+U53+V53-1</f>
+        <f t="shared" si="22"/>
         <v>18</v>
       </c>
       <c r="X53" s="23">
@@ -10728,7 +10736,7 @@
         <v>19</v>
       </c>
       <c r="AA53" s="6">
-        <f>+Z53+AB53-1</f>
+        <f t="shared" si="36"/>
         <v>22</v>
       </c>
       <c r="AB53" s="23">
@@ -10740,21 +10748,21 @@
         <v>46</v>
       </c>
       <c r="AF53" s="23">
-        <f>+AE53+AA53-1</f>
+        <f t="shared" si="23"/>
         <v>67</v>
       </c>
       <c r="AG53" s="23">
         <v>3</v>
       </c>
       <c r="AH53" s="23">
-        <f>+AF53+AG53</f>
+        <f t="shared" si="24"/>
         <v>70</v>
       </c>
       <c r="AI53" s="23">
         <v>7</v>
       </c>
       <c r="AJ53" s="23">
-        <f>+AI53+AH53</f>
+        <f t="shared" si="25"/>
         <v>77</v>
       </c>
       <c r="AK53" s="23"/>
@@ -10762,36 +10770,36 @@
         <v>3</v>
       </c>
       <c r="AM53" s="23">
-        <f>+AJ53+AL53</f>
+        <f t="shared" si="26"/>
         <v>80</v>
       </c>
       <c r="AN53" s="23">
         <v>2</v>
       </c>
       <c r="AO53" s="23">
-        <f>+AM53+AN53</f>
+        <f t="shared" si="27"/>
         <v>82</v>
       </c>
       <c r="AP53" s="23">
         <v>2</v>
       </c>
       <c r="AQ53" s="23">
-        <f>+AO53+AP53</f>
+        <f t="shared" si="30"/>
         <v>84</v>
       </c>
       <c r="AR53" s="23">
-        <f>+AQ53+7</f>
+        <f t="shared" si="35"/>
         <v>91</v>
       </c>
       <c r="AS53" s="23">
-        <f>+AR53+7+AT53</f>
+        <f t="shared" si="28"/>
         <v>112</v>
       </c>
       <c r="AT53" s="23">
         <v>14</v>
       </c>
       <c r="AU53" s="3">
-        <f>+AA53-R53</f>
+        <f t="shared" si="29"/>
         <v>22</v>
       </c>
       <c r="AV53" s="23" t="s">
@@ -10845,21 +10853,21 @@
         <v>5</v>
       </c>
       <c r="M54" s="3">
-        <f>+IF(I54="SFK Freight Forwarder",L54,9)</f>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="N54" s="23">
         <v>2</v>
       </c>
       <c r="O54" s="3">
-        <f>IF(I54="SFK Freight Forwarder",M54,M54+N54-1)</f>
+        <f t="shared" si="15"/>
         <v>10</v>
       </c>
       <c r="P54" s="3">
         <v>5</v>
       </c>
       <c r="Q54" s="3">
-        <f>+IF(I54="SFK Freight Forwarder",O54,O54+P54-1)</f>
+        <f t="shared" si="20"/>
         <v>14</v>
       </c>
       <c r="R54" s="23">
@@ -10890,7 +10898,7 @@
         <v>22</v>
       </c>
       <c r="AA54" s="6">
-        <f>+Z54+AB54-1</f>
+        <f t="shared" si="36"/>
         <v>25</v>
       </c>
       <c r="AB54" s="23">
@@ -10902,58 +10910,58 @@
         <v>39</v>
       </c>
       <c r="AF54" s="23">
-        <f>+AE54+AA54-1</f>
+        <f t="shared" si="23"/>
         <v>63</v>
       </c>
       <c r="AG54" s="23">
         <v>3</v>
       </c>
       <c r="AH54" s="23">
-        <f>+AF54+AG54</f>
+        <f t="shared" si="24"/>
         <v>66</v>
       </c>
       <c r="AI54" s="23">
         <v>7</v>
       </c>
       <c r="AJ54" s="23">
-        <f>+AI54+AH54</f>
+        <f t="shared" si="25"/>
         <v>73</v>
       </c>
       <c r="AK54" s="23"/>
-      <c r="AL54" s="23">
-        <v>3</v>
+      <c r="AL54" s="47">
+        <v>2</v>
       </c>
       <c r="AM54" s="23">
-        <f>+AJ54+AL54</f>
-        <v>76</v>
+        <f t="shared" si="26"/>
+        <v>75</v>
       </c>
       <c r="AN54" s="23">
         <v>8</v>
       </c>
       <c r="AO54" s="23">
-        <f>+AM54+AN54</f>
-        <v>84</v>
+        <f t="shared" si="27"/>
+        <v>83</v>
       </c>
       <c r="AP54" s="23">
         <v>2</v>
       </c>
       <c r="AQ54" s="23">
-        <f>+AO54+AP54</f>
-        <v>86</v>
+        <f t="shared" si="30"/>
+        <v>85</v>
       </c>
       <c r="AR54" s="23">
-        <f>+AQ54+7</f>
-        <v>93</v>
+        <f t="shared" si="35"/>
+        <v>92</v>
       </c>
       <c r="AS54" s="23">
-        <f>+AR54+7+AT54</f>
-        <v>114</v>
+        <f t="shared" si="28"/>
+        <v>113</v>
       </c>
       <c r="AT54" s="23">
         <v>14</v>
       </c>
       <c r="AU54" s="3">
-        <f>+AA54-R54</f>
+        <f t="shared" si="29"/>
         <v>15</v>
       </c>
       <c r="AV54" s="23" t="s">
@@ -10965,8 +10973,8 @@
       <c r="AX54" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AY54" s="37">
-        <v>46143</v>
+      <c r="AY54" s="21">
+        <v>46507</v>
       </c>
     </row>
     <row r="61" spans="1:51" x14ac:dyDescent="0.25">
@@ -10997,6 +11005,12 @@
       <filters>
         <filter val="ESALG"/>
         <filter val="ESVLC"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="47">
+      <filters>
+        <filter val="Direct"/>
+        <filter val="Indirect"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -11093,174 +11107,174 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D8" s="45" t="s">
+    <row r="8" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8" s="45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D9" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H9" s="45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D10" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D9" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D10" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="45" t="s">
+      <c r="E10" s="43" t="s">
         <v>58</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>157</v>
       </c>
       <c r="G10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D11" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H11" s="45">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D11" s="46" t="s">
+    <row r="12" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D12" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D13" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13" s="45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D14" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D15" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="46" t="s">
+      <c r="E15" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F15" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="G11" s="44" t="s">
+      <c r="G15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H15" s="45">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D12" s="45" t="s">
+    <row r="16" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D16" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="45" t="s">
+      <c r="E16" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H16" s="45">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D13" s="45" t="s">
+    <row r="17" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D17" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="45" t="s">
+      <c r="E17" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H17" s="45">
         <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D14" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D15" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="G15" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="H15" s="23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D16" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H16" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D17" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="H17" s="23">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD0B8B9-3AC4-4CDC-B54E-88F8E53200E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC07925-F144-47AB-AB15-F42C57458940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="190" yWindow="260" windowWidth="19010" windowHeight="11370" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja2!$D$7:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="180">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -952,6 +952,21 @@
   </si>
   <si>
     <t>Customs (days)</t>
+  </si>
+  <si>
+    <t>NITCO</t>
+  </si>
+  <si>
+    <t>O011</t>
+  </si>
+  <si>
+    <t>S001</t>
+  </si>
+  <si>
+    <t>HUIWANG</t>
+  </si>
+  <si>
+    <t>S002</t>
   </si>
 </sst>
 </file>
@@ -1183,7 +1198,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1325,6 +1340,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1671,18 +1689,16 @@
     <col min="2" max="2" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.85546875" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" customWidth="1"/>
-    <col min="15" max="28" width="10.42578125" customWidth="1"/>
-    <col min="29" max="30" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="31" max="34" width="10.42578125" customWidth="1"/>
+    <col min="15" max="34" width="10.42578125" customWidth="1"/>
     <col min="35" max="36" width="15.140625" customWidth="1"/>
     <col min="37" max="37" width="15.85546875" customWidth="1"/>
     <col min="38" max="39" width="9.5703125" customWidth="1"/>
@@ -1909,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="P2" s="3">
-        <f t="shared" ref="P2:P40" si="0">+IF(I2="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P2:P26" si="0">+IF(I2="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q2" s="3">
@@ -4622,7 +4638,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>916</v>
       </c>
@@ -4968,7 +4984,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>918</v>
       </c>
@@ -5141,39 +5157,39 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>1039</v>
+        <v>920</v>
       </c>
       <c r="B21" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="C21" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="33" t="s">
         <v>81</v>
       </c>
       <c r="F21" s="19">
-        <v>91017700</v>
-      </c>
-      <c r="G21" s="5" t="s">
+        <v>91017500</v>
+      </c>
+      <c r="G21" s="35" t="s">
         <v>157</v>
       </c>
       <c r="H21" s="2">
-        <v>222222</v>
+        <v>2533780535</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J21" s="2">
-        <v>222222</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>46</v>
+        <v>2533780535</v>
+      </c>
+      <c r="K21" s="44" t="s">
+        <v>22</v>
       </c>
       <c r="L21" s="3">
         <v>7</v>
@@ -5183,11 +5199,11 @@
         <v>9</v>
       </c>
       <c r="N21" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O21" s="3">
         <f t="shared" si="15"/>
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="P21" s="3">
         <f t="shared" si="0"/>
@@ -5195,111 +5211,111 @@
       </c>
       <c r="Q21" s="3">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="R21" s="3">
         <f t="shared" si="16"/>
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="S21" s="3">
         <v>7</v>
       </c>
       <c r="T21" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="U21" s="3">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="V21" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W21" s="3">
         <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+      <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>33</v>
+      </c>
+      <c r="Z21" s="6">
         <v>37</v>
-      </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>37</v>
-      </c>
-      <c r="Z21" s="6">
-        <v>42</v>
       </c>
       <c r="AA21" s="6">
         <f t="shared" si="19"/>
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="AB21" s="3">
         <v>3</v>
       </c>
       <c r="AC21" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD21" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AE21" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF21" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AG21" s="6">
         <v>3</v>
       </c>
       <c r="AH21" s="6">
         <f t="shared" si="7"/>
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI21" s="3">
         <v>0</v>
       </c>
       <c r="AJ21" s="3">
         <f t="shared" si="8"/>
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AK21" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AL21" s="46">
         <v>2</v>
       </c>
       <c r="AM21" s="3">
         <f t="shared" si="9"/>
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="AN21" s="3">
         <v>8</v>
       </c>
       <c r="AO21" s="3">
         <f t="shared" si="10"/>
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="AP21" s="3">
         <v>2</v>
       </c>
       <c r="AQ21" s="3">
         <f t="shared" si="11"/>
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="AR21" s="3">
         <f t="shared" si="12"/>
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="13"/>
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="AT21" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU21" s="3">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV21" s="3" t="s">
         <v>130</v>
@@ -5308,7 +5324,7 @@
         <v>131</v>
       </c>
       <c r="AX21" s="20" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="AY21" s="21">
         <v>46507</v>
@@ -6181,13 +6197,13 @@
     </row>
     <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>920</v>
+        <v>930</v>
       </c>
       <c r="B27" s="33" t="s">
         <v>80</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D27" s="33" t="s">
         <v>58</v>
@@ -6196,22 +6212,22 @@
         <v>81</v>
       </c>
       <c r="F27" s="19">
-        <v>91017500</v>
-      </c>
-      <c r="G27" s="35" t="s">
+        <v>91017700</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>157</v>
       </c>
       <c r="H27" s="2">
-        <v>2533780535</v>
+        <v>26037000</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J27" s="2">
-        <v>2533780535</v>
-      </c>
-      <c r="K27" s="44" t="s">
-        <v>22</v>
+        <v>26037000</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="L27" s="3">
         <v>7</v>
@@ -6228,7 +6244,6 @@
         <v>22</v>
       </c>
       <c r="P27" s="3">
-        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q27" s="3">
@@ -6251,54 +6266,54 @@
         <v>30</v>
       </c>
       <c r="V27" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W27" s="3">
         <f t="shared" si="4"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="X27" s="3">
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Z27" s="6">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AA27" s="6">
         <f t="shared" si="19"/>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AB27" s="3">
         <v>3</v>
       </c>
       <c r="AC27" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD27" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AE27" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AF27" s="3">
         <f t="shared" si="6"/>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AG27" s="6">
         <v>3</v>
       </c>
       <c r="AH27" s="6">
         <f t="shared" si="7"/>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI27" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ27" s="3">
         <f t="shared" si="8"/>
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AK27" s="3" t="s">
         <v>55</v>
@@ -6308,36 +6323,36 @@
       </c>
       <c r="AM27" s="3">
         <f t="shared" si="9"/>
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="AN27" s="3">
         <v>8</v>
       </c>
       <c r="AO27" s="3">
         <f t="shared" si="10"/>
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AP27" s="3">
         <v>2</v>
       </c>
       <c r="AQ27" s="3">
         <f t="shared" si="11"/>
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AR27" s="3">
         <f t="shared" si="12"/>
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="13"/>
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="AT27" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AU27" s="3">
         <f t="shared" si="14"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV27" s="3" t="s">
         <v>130</v>
@@ -6401,7 +6416,7 @@
         <v>22</v>
       </c>
       <c r="P28" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="P28:P44" si="20">+IF(I28="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q28" s="3">
@@ -6574,7 +6589,7 @@
         <v>22</v>
       </c>
       <c r="P29" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="Q29" s="3">
@@ -6746,7 +6761,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q30" s="3">
@@ -6918,7 +6933,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q31" s="3">
@@ -7090,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q32" s="3">
@@ -7264,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q33" s="3">
@@ -7436,11 +7451,11 @@
         <v>0</v>
       </c>
       <c r="P34" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q34" s="3">
-        <f t="shared" ref="Q34:Q65" si="20">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
+        <f t="shared" ref="Q34:Q65" si="21">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
         <v>0</v>
       </c>
       <c r="R34" s="3">
@@ -7451,7 +7466,7 @@
         <v>7</v>
       </c>
       <c r="T34" s="3">
-        <f t="shared" ref="T34:T65" si="21">+R34+S34-1</f>
+        <f t="shared" ref="T34:T65" si="22">+R34+S34-1</f>
         <v>29</v>
       </c>
       <c r="U34" s="3">
@@ -7462,7 +7477,7 @@
         <v>1</v>
       </c>
       <c r="W34" s="3">
-        <f t="shared" ref="W34:W65" si="22">+U34+V34-1</f>
+        <f t="shared" ref="W34:W65" si="23">+U34+V34-1</f>
         <v>30</v>
       </c>
       <c r="X34" s="3">
@@ -7491,21 +7506,21 @@
         <v>63</v>
       </c>
       <c r="AF34" s="3">
-        <f t="shared" ref="AF34:AF65" si="23">+AE34+AA34-1</f>
+        <f t="shared" ref="AF34:AF65" si="24">+AE34+AA34-1</f>
         <v>98</v>
       </c>
       <c r="AG34" s="6">
         <v>3</v>
       </c>
       <c r="AH34" s="6">
-        <f t="shared" ref="AH34:AH65" si="24">+AF34+AG34</f>
+        <f t="shared" ref="AH34:AH65" si="25">+AF34+AG34</f>
         <v>101</v>
       </c>
       <c r="AI34" s="3">
         <v>0</v>
       </c>
       <c r="AJ34" s="3">
-        <f t="shared" ref="AJ34:AJ65" si="25">+AI34+AH34</f>
+        <f t="shared" ref="AJ34:AJ65" si="26">+AI34+AH34</f>
         <v>101</v>
       </c>
       <c r="AK34" s="3" t="s">
@@ -7515,14 +7530,14 @@
         <v>4</v>
       </c>
       <c r="AM34" s="3">
-        <f t="shared" ref="AM34:AM65" si="26">+AJ34+AL34</f>
+        <f t="shared" ref="AM34:AM65" si="27">+AJ34+AL34</f>
         <v>105</v>
       </c>
       <c r="AN34" s="3">
         <v>3</v>
       </c>
       <c r="AO34" s="3">
-        <f t="shared" ref="AO34:AO65" si="27">+AM34+AN34</f>
+        <f t="shared" ref="AO34:AO65" si="28">+AM34+AN34</f>
         <v>108</v>
       </c>
       <c r="AP34" s="3">
@@ -7537,14 +7552,14 @@
         <v>119</v>
       </c>
       <c r="AS34" s="3">
-        <f t="shared" ref="AS34:AS65" si="28">+AR34+7+AT34</f>
+        <f t="shared" ref="AS34:AS65" si="29">+AR34+7+AT34</f>
         <v>126</v>
       </c>
       <c r="AT34" s="3">
         <v>0</v>
       </c>
       <c r="AU34" s="3">
-        <f t="shared" ref="AU34:AU54" si="29">+AA34-R34</f>
+        <f t="shared" ref="AU34:AU55" si="30">+AA34-R34</f>
         <v>13</v>
       </c>
       <c r="AV34" s="3" t="s">
@@ -7608,11 +7623,11 @@
         <v>0</v>
       </c>
       <c r="P35" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R35" s="3">
@@ -7623,7 +7638,7 @@
         <v>7</v>
       </c>
       <c r="T35" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U35" s="3">
@@ -7634,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="W35" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>30</v>
       </c>
       <c r="X35" s="3">
@@ -7664,21 +7679,21 @@
         <v>48</v>
       </c>
       <c r="AF35" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>84</v>
       </c>
       <c r="AG35" s="6">
         <v>3</v>
       </c>
       <c r="AH35" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>87</v>
       </c>
       <c r="AI35" s="3">
         <v>14</v>
       </c>
       <c r="AJ35" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>101</v>
       </c>
       <c r="AK35" s="3" t="s">
@@ -7688,14 +7703,14 @@
         <v>2</v>
       </c>
       <c r="AM35" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>103</v>
       </c>
       <c r="AN35" s="3">
         <v>2</v>
       </c>
       <c r="AO35" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>105</v>
       </c>
       <c r="AP35" s="3">
@@ -7710,14 +7725,14 @@
         <v>112</v>
       </c>
       <c r="AS35" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>119</v>
       </c>
       <c r="AT35" s="3">
         <v>0</v>
       </c>
       <c r="AU35" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14</v>
       </c>
       <c r="AV35" s="3" t="s">
@@ -7781,11 +7796,11 @@
         <v>0</v>
       </c>
       <c r="P36" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q36" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R36" s="3">
@@ -7796,7 +7811,7 @@
         <v>7</v>
       </c>
       <c r="T36" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U36" s="3">
@@ -7807,7 +7822,7 @@
         <v>2</v>
       </c>
       <c r="W36" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>31</v>
       </c>
       <c r="X36" s="3">
@@ -7836,23 +7851,23 @@
         <v>17</v>
       </c>
       <c r="AF36" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>60</v>
       </c>
       <c r="AG36" s="6">
         <v>3</v>
       </c>
       <c r="AH36" s="6">
-        <f t="shared" si="24"/>
-        <v>63</v>
-      </c>
-      <c r="AI36" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="3">
         <f t="shared" si="25"/>
         <v>63</v>
       </c>
+      <c r="AI36" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="3">
+        <f t="shared" si="26"/>
+        <v>63</v>
+      </c>
       <c r="AK36" s="3" t="s">
         <v>60</v>
       </c>
@@ -7860,14 +7875,14 @@
         <v>0</v>
       </c>
       <c r="AM36" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>63</v>
       </c>
       <c r="AN36" s="3">
         <v>0</v>
       </c>
       <c r="AO36" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>63</v>
       </c>
       <c r="AP36" s="3">
@@ -7882,14 +7897,14 @@
         <v>70</v>
       </c>
       <c r="AS36" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>77</v>
       </c>
       <c r="AT36" s="3">
         <v>0</v>
       </c>
       <c r="AU36" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>21</v>
       </c>
       <c r="AV36" s="3" t="s">
@@ -7953,11 +7968,11 @@
         <v>0</v>
       </c>
       <c r="P37" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q37" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R37" s="3">
@@ -7968,7 +7983,7 @@
         <v>7</v>
       </c>
       <c r="T37" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U37" s="3">
@@ -7979,7 +7994,7 @@
         <v>2</v>
       </c>
       <c r="W37" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>31</v>
       </c>
       <c r="X37" s="3">
@@ -8008,23 +8023,23 @@
         <v>34</v>
       </c>
       <c r="AF37" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>77</v>
       </c>
       <c r="AG37" s="6">
         <v>3</v>
       </c>
       <c r="AH37" s="6">
-        <f t="shared" si="24"/>
-        <v>80</v>
-      </c>
-      <c r="AI37" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="3">
         <f t="shared" si="25"/>
         <v>80</v>
       </c>
+      <c r="AI37" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="3">
+        <f t="shared" si="26"/>
+        <v>80</v>
+      </c>
       <c r="AK37" s="3" t="s">
         <v>60</v>
       </c>
@@ -8032,14 +8047,14 @@
         <v>2</v>
       </c>
       <c r="AM37" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>82</v>
       </c>
       <c r="AN37" s="3">
         <v>2</v>
       </c>
       <c r="AO37" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>84</v>
       </c>
       <c r="AP37" s="3">
@@ -8054,14 +8069,14 @@
         <v>91</v>
       </c>
       <c r="AS37" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>98</v>
       </c>
       <c r="AT37" s="3">
         <v>0</v>
       </c>
       <c r="AU37" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>21</v>
       </c>
       <c r="AV37" s="3" t="s">
@@ -8125,11 +8140,11 @@
         <v>0</v>
       </c>
       <c r="P38" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q38" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R38" s="3">
@@ -8140,7 +8155,7 @@
         <v>7</v>
       </c>
       <c r="T38" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U38" s="3">
@@ -8151,7 +8166,7 @@
         <v>1</v>
       </c>
       <c r="W38" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>30</v>
       </c>
       <c r="X38" s="3">
@@ -8180,23 +8195,23 @@
         <v>53</v>
       </c>
       <c r="AF38" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>87</v>
       </c>
       <c r="AG38" s="6">
         <v>3</v>
       </c>
       <c r="AH38" s="6">
-        <f t="shared" si="24"/>
-        <v>90</v>
-      </c>
-      <c r="AI38" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="3">
         <f t="shared" si="25"/>
         <v>90</v>
       </c>
+      <c r="AI38" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="3">
+        <f t="shared" si="26"/>
+        <v>90</v>
+      </c>
       <c r="AK38" s="3" t="s">
         <v>60</v>
       </c>
@@ -8204,14 +8219,14 @@
         <v>2</v>
       </c>
       <c r="AM38" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>92</v>
       </c>
       <c r="AN38" s="3">
         <v>6</v>
       </c>
       <c r="AO38" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>98</v>
       </c>
       <c r="AP38" s="3">
@@ -8226,14 +8241,14 @@
         <v>105</v>
       </c>
       <c r="AS38" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>112</v>
       </c>
       <c r="AT38" s="3">
         <v>0</v>
       </c>
       <c r="AU38" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>12</v>
       </c>
       <c r="AV38" s="3" t="s">
@@ -8297,11 +8312,11 @@
         <v>0</v>
       </c>
       <c r="P39" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q39" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R39" s="3">
@@ -8312,7 +8327,7 @@
         <v>7</v>
       </c>
       <c r="T39" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U39" s="3">
@@ -8323,7 +8338,7 @@
         <v>2</v>
       </c>
       <c r="W39" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>31</v>
       </c>
       <c r="X39" s="3">
@@ -8352,23 +8367,23 @@
         <v>31</v>
       </c>
       <c r="AF39" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>66</v>
       </c>
       <c r="AG39" s="6">
         <v>3</v>
       </c>
       <c r="AH39" s="6">
-        <f t="shared" si="24"/>
-        <v>69</v>
-      </c>
-      <c r="AI39" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="3">
         <f t="shared" si="25"/>
         <v>69</v>
       </c>
+      <c r="AI39" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="3">
+        <f t="shared" si="26"/>
+        <v>69</v>
+      </c>
       <c r="AK39" s="3" t="s">
         <v>60</v>
       </c>
@@ -8376,14 +8391,14 @@
         <v>2</v>
       </c>
       <c r="AM39" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>71</v>
       </c>
       <c r="AN39" s="3">
         <v>5</v>
       </c>
       <c r="AO39" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>76</v>
       </c>
       <c r="AP39" s="3">
@@ -8398,14 +8413,14 @@
         <v>84</v>
       </c>
       <c r="AS39" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>91</v>
       </c>
       <c r="AT39" s="3">
         <v>0</v>
       </c>
       <c r="AU39" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>13</v>
       </c>
       <c r="AV39" s="3" t="s">
@@ -8469,11 +8484,11 @@
         <v>0</v>
       </c>
       <c r="P40" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q40" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R40" s="3">
@@ -8484,7 +8499,7 @@
         <v>7</v>
       </c>
       <c r="T40" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U40" s="3">
@@ -8495,7 +8510,7 @@
         <v>1</v>
       </c>
       <c r="W40" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>30</v>
       </c>
       <c r="X40" s="3">
@@ -8524,21 +8539,21 @@
         <v>67</v>
       </c>
       <c r="AF40" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>102</v>
       </c>
       <c r="AG40" s="6">
         <v>3</v>
       </c>
       <c r="AH40" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>105</v>
       </c>
       <c r="AI40" s="3">
         <v>7</v>
       </c>
       <c r="AJ40" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>112</v>
       </c>
       <c r="AK40" s="3" t="s">
@@ -8548,14 +8563,14 @@
         <v>3</v>
       </c>
       <c r="AM40" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>115</v>
       </c>
       <c r="AN40" s="3">
         <v>3</v>
       </c>
       <c r="AO40" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>118</v>
       </c>
       <c r="AP40" s="3">
@@ -8570,14 +8585,14 @@
         <v>126</v>
       </c>
       <c r="AS40" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>133</v>
       </c>
       <c r="AT40" s="3">
         <v>0</v>
       </c>
       <c r="AU40" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>13</v>
       </c>
       <c r="AV40" s="3" t="s">
@@ -8593,141 +8608,142 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>930</v>
+        <v>1039</v>
       </c>
       <c r="B41" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="33" t="s">
+      <c r="C41" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="33" t="s">
+      <c r="D41" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E41" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F41" s="19">
         <v>91017700</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="5" t="s">
         <v>157</v>
       </c>
       <c r="H41" s="2">
-        <v>26037000</v>
+        <v>222222</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J41" s="2">
-        <v>26037000</v>
+        <v>222222</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L41" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M41" s="3">
         <f>+IF(I41="SFK Freight Forwarder",L41,9)</f>
         <v>9</v>
       </c>
       <c r="N41" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O41" s="3">
         <f t="shared" si="15"/>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="P41" s="3">
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="Q41" s="3">
-        <f t="shared" si="20"/>
-        <v>26</v>
+        <f t="shared" si="21"/>
+        <v>33</v>
       </c>
       <c r="R41" s="3">
         <f t="shared" si="16"/>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="S41" s="3">
         <v>7</v>
       </c>
       <c r="T41" s="3">
-        <f t="shared" si="21"/>
-        <v>29</v>
+        <f t="shared" si="22"/>
+        <v>36</v>
       </c>
       <c r="U41" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="V41" s="3">
         <v>1</v>
       </c>
       <c r="W41" s="3">
-        <f t="shared" si="22"/>
-        <v>30</v>
+        <f t="shared" si="23"/>
+        <v>37</v>
       </c>
       <c r="X41" s="3">
         <v>0</v>
       </c>
       <c r="Y41" s="3">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Z41" s="6">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AA41" s="6">
         <f t="shared" si="19"/>
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AB41" s="3">
         <v>3</v>
       </c>
       <c r="AC41" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AD41" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE41" s="3">
         <v>40</v>
       </c>
       <c r="AF41" s="3">
-        <f t="shared" si="23"/>
-        <v>76</v>
+        <f t="shared" si="24"/>
+        <v>83</v>
       </c>
       <c r="AG41" s="6">
         <v>3</v>
       </c>
       <c r="AH41" s="6">
-        <f t="shared" si="24"/>
-        <v>79</v>
-      </c>
-      <c r="AI41" s="3">
-        <v>7</v>
-      </c>
-      <c r="AJ41" s="3">
         <f t="shared" si="25"/>
         <v>86</v>
       </c>
+      <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="3">
+        <f t="shared" si="26"/>
+        <v>86</v>
+      </c>
       <c r="AK41" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AL41" s="46">
+      <c r="AL41" s="3">
         <v>2</v>
       </c>
       <c r="AM41" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>88</v>
       </c>
       <c r="AN41" s="3">
         <v>8</v>
       </c>
       <c r="AO41" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>96</v>
       </c>
       <c r="AP41" s="3">
@@ -8742,14 +8758,14 @@
         <v>105</v>
       </c>
       <c r="AS41" s="3">
-        <f t="shared" si="28"/>
-        <v>129</v>
+        <f t="shared" si="29"/>
+        <v>112</v>
       </c>
       <c r="AT41" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AU41" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14</v>
       </c>
       <c r="AV41" s="3" t="s">
@@ -8759,7 +8775,7 @@
         <v>131</v>
       </c>
       <c r="AX41" s="20" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="AY41" s="21">
         <v>46507</v>
@@ -8813,11 +8829,11 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
-        <f>+IF(I42="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q42" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R42" s="3">
@@ -8828,7 +8844,7 @@
         <v>7</v>
       </c>
       <c r="T42" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U42" s="3">
@@ -8839,7 +8855,7 @@
         <v>1</v>
       </c>
       <c r="W42" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>30</v>
       </c>
       <c r="X42" s="3">
@@ -8868,23 +8884,23 @@
         <v>32</v>
       </c>
       <c r="AF42" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>67</v>
       </c>
       <c r="AG42" s="6">
         <v>3</v>
       </c>
       <c r="AH42" s="6">
-        <f t="shared" si="24"/>
-        <v>70</v>
-      </c>
-      <c r="AI42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ42" s="3">
         <f t="shared" si="25"/>
         <v>70</v>
       </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3">
+        <f t="shared" si="26"/>
+        <v>70</v>
+      </c>
       <c r="AK42" s="3" t="s">
         <v>60</v>
       </c>
@@ -8892,14 +8908,14 @@
         <v>4</v>
       </c>
       <c r="AM42" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>74</v>
       </c>
       <c r="AN42" s="3">
         <v>3</v>
       </c>
       <c r="AO42" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>77</v>
       </c>
       <c r="AP42" s="3">
@@ -8914,14 +8930,14 @@
         <v>84</v>
       </c>
       <c r="AS42" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>91</v>
       </c>
       <c r="AT42" s="3">
         <v>0</v>
       </c>
       <c r="AU42" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>13</v>
       </c>
       <c r="AV42" s="3" t="s">
@@ -8986,11 +9002,11 @@
         <v>29</v>
       </c>
       <c r="P43" s="3">
-        <f>+IF(I43="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="Q43" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="R43" s="3">
@@ -9001,7 +9017,7 @@
         <v>7</v>
       </c>
       <c r="T43" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>36</v>
       </c>
       <c r="U43" s="3">
@@ -9012,7 +9028,7 @@
         <v>1</v>
       </c>
       <c r="W43" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>37</v>
       </c>
       <c r="X43" s="3">
@@ -9041,21 +9057,21 @@
         <v>46</v>
       </c>
       <c r="AF43" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>84</v>
       </c>
       <c r="AG43" s="6">
         <v>3</v>
       </c>
       <c r="AH43" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>87</v>
       </c>
       <c r="AI43" s="3">
         <v>7</v>
       </c>
       <c r="AJ43" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>94</v>
       </c>
       <c r="AK43" s="3" t="s">
@@ -9065,14 +9081,14 @@
         <v>4</v>
       </c>
       <c r="AM43" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>98</v>
       </c>
       <c r="AN43" s="3">
         <v>3</v>
       </c>
       <c r="AO43" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>101</v>
       </c>
       <c r="AP43" s="3">
@@ -9087,14 +9103,14 @@
         <v>112</v>
       </c>
       <c r="AS43" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>119</v>
       </c>
       <c r="AT43" s="3">
         <v>0</v>
       </c>
       <c r="AU43" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>9</v>
       </c>
       <c r="AV43" s="3" t="s">
@@ -9159,11 +9175,11 @@
         <v>22</v>
       </c>
       <c r="P44" s="3">
-        <f>+IF(I44="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="Q44" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>26</v>
       </c>
       <c r="R44" s="3">
@@ -9174,7 +9190,7 @@
         <v>7</v>
       </c>
       <c r="T44" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U44" s="3">
@@ -9185,7 +9201,7 @@
         <v>2</v>
       </c>
       <c r="W44" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>31</v>
       </c>
       <c r="X44" s="3">
@@ -9214,23 +9230,23 @@
         <v>35</v>
       </c>
       <c r="AF44" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>75</v>
       </c>
       <c r="AG44" s="6">
         <v>3</v>
       </c>
       <c r="AH44" s="6">
-        <f t="shared" si="24"/>
-        <v>78</v>
-      </c>
-      <c r="AI44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ44" s="3">
         <f t="shared" si="25"/>
         <v>78</v>
       </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="3">
+        <f t="shared" si="26"/>
+        <v>78</v>
+      </c>
       <c r="AK44" s="3" t="s">
         <v>65</v>
       </c>
@@ -9238,14 +9254,14 @@
         <v>2</v>
       </c>
       <c r="AM44" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>80</v>
       </c>
       <c r="AN44" s="3">
         <v>2</v>
       </c>
       <c r="AO44" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>82</v>
       </c>
       <c r="AP44" s="3">
@@ -9260,14 +9276,14 @@
         <v>91</v>
       </c>
       <c r="AS44" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>98</v>
       </c>
       <c r="AT44" s="3">
         <v>0</v>
       </c>
       <c r="AU44" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>18</v>
       </c>
       <c r="AV44" s="3" t="s">
@@ -9334,7 +9350,7 @@
         <v>6</v>
       </c>
       <c r="Q45" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13</v>
       </c>
       <c r="R45" s="23">
@@ -9344,7 +9360,7 @@
         <v>12</v>
       </c>
       <c r="T45" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="U45" s="23">
@@ -9355,7 +9371,7 @@
         <v>5</v>
       </c>
       <c r="W45" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>26</v>
       </c>
       <c r="X45" s="23">
@@ -9379,21 +9395,21 @@
         <v>41</v>
       </c>
       <c r="AF45" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>71</v>
       </c>
       <c r="AG45" s="23">
         <v>3</v>
       </c>
       <c r="AH45" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>74</v>
       </c>
       <c r="AI45" s="23">
         <v>7</v>
       </c>
       <c r="AJ45" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>81</v>
       </c>
       <c r="AK45" s="23"/>
@@ -9401,14 +9417,14 @@
         <v>3</v>
       </c>
       <c r="AM45" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>84</v>
       </c>
       <c r="AN45" s="23">
         <v>5</v>
       </c>
       <c r="AO45" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>89</v>
       </c>
       <c r="AP45" s="23">
@@ -9422,14 +9438,14 @@
         <v>96</v>
       </c>
       <c r="AS45" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>117</v>
       </c>
       <c r="AT45" s="23">
         <v>14</v>
       </c>
       <c r="AU45" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>22</v>
       </c>
       <c r="AV45" s="23" t="s">
@@ -9445,7 +9461,7 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>172</v>
       </c>
@@ -9496,7 +9512,7 @@
         <v>6</v>
       </c>
       <c r="Q46" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13</v>
       </c>
       <c r="R46" s="23">
@@ -9506,7 +9522,7 @@
         <v>12</v>
       </c>
       <c r="T46" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="U46" s="23">
@@ -9517,7 +9533,7 @@
         <v>5</v>
       </c>
       <c r="W46" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>26</v>
       </c>
       <c r="X46" s="23">
@@ -9541,21 +9557,21 @@
         <v>34</v>
       </c>
       <c r="AF46" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>69</v>
       </c>
       <c r="AG46" s="23">
         <v>3</v>
       </c>
       <c r="AH46" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>72</v>
       </c>
       <c r="AI46" s="23">
         <v>0</v>
       </c>
       <c r="AJ46" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>72</v>
       </c>
       <c r="AK46" s="23"/>
@@ -9563,21 +9579,21 @@
         <v>2</v>
       </c>
       <c r="AM46" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>74</v>
       </c>
       <c r="AN46" s="23">
         <v>1</v>
       </c>
       <c r="AO46" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>75</v>
       </c>
       <c r="AP46" s="23">
         <v>3</v>
       </c>
       <c r="AQ46" s="3">
-        <f t="shared" ref="AQ46:AQ54" si="30">+AO46+AP46</f>
+        <f t="shared" ref="AQ46:AQ57" si="31">+AO46+AP46</f>
         <v>78</v>
       </c>
       <c r="AR46" s="23">
@@ -9585,14 +9601,14 @@
         <v>82</v>
       </c>
       <c r="AS46" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>103</v>
       </c>
       <c r="AT46" s="23">
         <v>14</v>
       </c>
       <c r="AU46" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>27</v>
       </c>
       <c r="AV46" s="23" t="s">
@@ -9646,7 +9662,7 @@
         <v>7</v>
       </c>
       <c r="M47" s="3">
-        <f t="shared" ref="M47:M54" si="31">+IF(I47="SFK Freight Forwarder",L47,9)</f>
+        <f t="shared" ref="M47:M54" si="32">+IF(I47="SFK Freight Forwarder",L47,9)</f>
         <v>9</v>
       </c>
       <c r="N47" s="3">
@@ -9657,33 +9673,33 @@
         <v>22</v>
       </c>
       <c r="P47" s="3">
-        <f t="shared" ref="P47:P52" si="32">+IF(I47="SFK Freight Forwarder",0,5)</f>
+        <f t="shared" ref="P47:P52" si="33">+IF(I47="SFK Freight Forwarder",0,5)</f>
         <v>5</v>
       </c>
       <c r="Q47" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>26</v>
       </c>
       <c r="R47" s="3">
-        <f t="shared" ref="R47:R52" si="33">9+N47</f>
+        <f t="shared" ref="R47:R52" si="34">9+N47</f>
         <v>23</v>
       </c>
       <c r="S47" s="3">
         <v>7</v>
       </c>
       <c r="T47" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U47" s="3">
-        <f t="shared" ref="U47:U52" si="34">+T47+1</f>
+        <f t="shared" ref="U47:U52" si="35">+T47+1</f>
         <v>30</v>
       </c>
       <c r="V47" s="3">
         <v>2</v>
       </c>
       <c r="W47" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>31</v>
       </c>
       <c r="X47" s="3">
@@ -9714,23 +9730,23 @@
         <v>40</v>
       </c>
       <c r="AF47" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>73</v>
       </c>
       <c r="AG47" s="6">
         <v>3</v>
       </c>
       <c r="AH47" s="6">
-        <f t="shared" si="24"/>
-        <v>76</v>
-      </c>
-      <c r="AI47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ47" s="3">
         <f t="shared" si="25"/>
         <v>76</v>
       </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3">
+        <f t="shared" si="26"/>
+        <v>76</v>
+      </c>
       <c r="AK47" s="3" t="s">
         <v>60</v>
       </c>
@@ -9738,36 +9754,36 @@
         <v>2</v>
       </c>
       <c r="AM47" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>78</v>
       </c>
       <c r="AN47" s="3">
         <v>2</v>
       </c>
       <c r="AO47" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>80</v>
       </c>
       <c r="AP47" s="3">
         <v>6</v>
       </c>
       <c r="AQ47" s="3">
+        <f t="shared" si="31"/>
+        <v>86</v>
+      </c>
+      <c r="AR47" s="3">
+        <f t="shared" ref="AR47:AR57" si="36">+AQ47+7</f>
+        <v>93</v>
+      </c>
+      <c r="AS47" s="3">
+        <f t="shared" si="29"/>
+        <v>100</v>
+      </c>
+      <c r="AT47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU47" s="3">
         <f t="shared" si="30"/>
-        <v>86</v>
-      </c>
-      <c r="AR47" s="3">
-        <f t="shared" ref="AR47:AR54" si="35">+AQ47+7</f>
-        <v>93</v>
-      </c>
-      <c r="AS47" s="3">
-        <f t="shared" si="28"/>
-        <v>100</v>
-      </c>
-      <c r="AT47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU47" s="3">
-        <f t="shared" si="29"/>
         <v>11</v>
       </c>
       <c r="AV47" s="3" t="s">
@@ -9821,7 +9837,7 @@
         <v>7</v>
       </c>
       <c r="M48" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9</v>
       </c>
       <c r="N48" s="3">
@@ -9832,33 +9848,33 @@
         <v>22</v>
       </c>
       <c r="P48" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5</v>
       </c>
       <c r="Q48" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>26</v>
       </c>
       <c r="R48" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>23</v>
       </c>
       <c r="S48" s="3">
         <v>7</v>
       </c>
       <c r="T48" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U48" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="V48" s="3">
         <v>2</v>
       </c>
       <c r="W48" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>31</v>
       </c>
       <c r="X48" s="3">
@@ -9886,23 +9902,23 @@
         <v>68</v>
       </c>
       <c r="AF48" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>103</v>
       </c>
       <c r="AG48" s="6">
         <v>3</v>
       </c>
       <c r="AH48" s="6">
-        <f t="shared" si="24"/>
-        <v>106</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ48" s="3">
         <f t="shared" si="25"/>
         <v>106</v>
       </c>
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="3">
+        <f t="shared" si="26"/>
+        <v>106</v>
+      </c>
       <c r="AK48" s="3" t="s">
         <v>60</v>
       </c>
@@ -9910,36 +9926,36 @@
         <v>2</v>
       </c>
       <c r="AM48" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>108</v>
       </c>
       <c r="AN48" s="3">
         <v>7</v>
       </c>
       <c r="AO48" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>115</v>
       </c>
       <c r="AP48" s="3">
         <v>5</v>
       </c>
       <c r="AQ48" s="3">
+        <f t="shared" si="31"/>
+        <v>120</v>
+      </c>
+      <c r="AR48" s="3">
+        <f t="shared" si="36"/>
+        <v>127</v>
+      </c>
+      <c r="AS48" s="3">
+        <f t="shared" si="29"/>
+        <v>134</v>
+      </c>
+      <c r="AT48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU48" s="3">
         <f t="shared" si="30"/>
-        <v>120</v>
-      </c>
-      <c r="AR48" s="3">
-        <f t="shared" si="35"/>
-        <v>127</v>
-      </c>
-      <c r="AS48" s="3">
-        <f t="shared" si="28"/>
-        <v>134</v>
-      </c>
-      <c r="AT48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU48" s="3">
-        <f t="shared" si="29"/>
         <v>13</v>
       </c>
       <c r="AV48" s="3" t="s">
@@ -9955,7 +9971,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>145</v>
       </c>
@@ -9993,7 +10009,7 @@
         <v>7</v>
       </c>
       <c r="M49" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9</v>
       </c>
       <c r="N49" s="3">
@@ -10004,33 +10020,33 @@
         <v>22</v>
       </c>
       <c r="P49" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5</v>
       </c>
       <c r="Q49" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>26</v>
       </c>
       <c r="R49" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>23</v>
       </c>
       <c r="S49" s="3">
         <v>7</v>
       </c>
       <c r="T49" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U49" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="V49" s="3">
         <v>2</v>
       </c>
       <c r="W49" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>31</v>
       </c>
       <c r="X49" s="3">
@@ -10043,7 +10059,7 @@
         <v>33</v>
       </c>
       <c r="AA49" s="6">
-        <f t="shared" ref="AA49:AA54" si="36">+Z49+AB49-1</f>
+        <f t="shared" ref="AA49:AA54" si="37">+Z49+AB49-1</f>
         <v>38</v>
       </c>
       <c r="AB49" s="3">
@@ -10059,23 +10075,23 @@
         <v>42</v>
       </c>
       <c r="AF49" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>79</v>
       </c>
       <c r="AG49" s="6">
         <v>3</v>
       </c>
       <c r="AH49" s="6">
-        <f t="shared" si="24"/>
-        <v>82</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ49" s="3">
         <f t="shared" si="25"/>
         <v>82</v>
       </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="3">
+        <f t="shared" si="26"/>
+        <v>82</v>
+      </c>
       <c r="AK49" s="3" t="s">
         <v>60</v>
       </c>
@@ -10083,36 +10099,36 @@
         <v>2</v>
       </c>
       <c r="AM49" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>84</v>
       </c>
       <c r="AN49" s="3">
         <v>1</v>
       </c>
       <c r="AO49" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>85</v>
       </c>
       <c r="AP49" s="3">
         <v>3</v>
       </c>
       <c r="AQ49" s="3">
+        <f t="shared" si="31"/>
+        <v>88</v>
+      </c>
+      <c r="AR49" s="3">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="AS49" s="3">
+        <f t="shared" si="29"/>
+        <v>102</v>
+      </c>
+      <c r="AT49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU49" s="3">
         <f t="shared" si="30"/>
-        <v>88</v>
-      </c>
-      <c r="AR49" s="3">
-        <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="AS49" s="3">
-        <f t="shared" si="28"/>
-        <v>102</v>
-      </c>
-      <c r="AT49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU49" s="3">
-        <f t="shared" si="29"/>
         <v>15</v>
       </c>
       <c r="AV49" s="3" t="s">
@@ -10166,7 +10182,7 @@
         <v>7</v>
       </c>
       <c r="M50" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9</v>
       </c>
       <c r="N50" s="3">
@@ -10177,33 +10193,33 @@
         <v>22</v>
       </c>
       <c r="P50" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5</v>
       </c>
       <c r="Q50" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>26</v>
       </c>
       <c r="R50" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>23</v>
       </c>
       <c r="S50" s="3">
         <v>7</v>
       </c>
       <c r="T50" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U50" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="V50" s="3">
         <v>2</v>
       </c>
       <c r="W50" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>31</v>
       </c>
       <c r="X50" s="3">
@@ -10218,7 +10234,7 @@
         <v>31</v>
       </c>
       <c r="AA50" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>34</v>
       </c>
       <c r="AB50" s="3">
@@ -10234,23 +10250,23 @@
         <v>48</v>
       </c>
       <c r="AF50" s="3">
-        <f t="shared" si="23"/>
-        <v>81</v>
-      </c>
-      <c r="AG50" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="6">
         <f t="shared" si="24"/>
         <v>81</v>
       </c>
-      <c r="AI50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ50" s="3">
+      <c r="AG50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="6">
         <f t="shared" si="25"/>
         <v>81</v>
       </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="3">
+        <f t="shared" si="26"/>
+        <v>81</v>
+      </c>
       <c r="AK50" s="3" t="s">
         <v>60</v>
       </c>
@@ -10258,36 +10274,36 @@
         <v>3</v>
       </c>
       <c r="AM50" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>84</v>
       </c>
       <c r="AN50" s="3">
         <v>8</v>
       </c>
       <c r="AO50" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>92</v>
       </c>
       <c r="AP50" s="3">
         <v>0</v>
       </c>
       <c r="AQ50" s="3">
+        <f t="shared" si="31"/>
+        <v>92</v>
+      </c>
+      <c r="AR50" s="3">
+        <f t="shared" si="36"/>
+        <v>99</v>
+      </c>
+      <c r="AS50" s="3">
+        <f t="shared" si="29"/>
+        <v>106</v>
+      </c>
+      <c r="AT50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU50" s="3">
         <f t="shared" si="30"/>
-        <v>92</v>
-      </c>
-      <c r="AR50" s="3">
-        <f t="shared" si="35"/>
-        <v>99</v>
-      </c>
-      <c r="AS50" s="3">
-        <f t="shared" si="28"/>
-        <v>106</v>
-      </c>
-      <c r="AT50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU50" s="3">
-        <f t="shared" si="29"/>
         <v>11</v>
       </c>
       <c r="AV50" s="3" t="s">
@@ -10341,7 +10357,7 @@
         <v>2</v>
       </c>
       <c r="M51" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9</v>
       </c>
       <c r="N51" s="3">
@@ -10352,33 +10368,33 @@
         <v>22</v>
       </c>
       <c r="P51" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5</v>
       </c>
       <c r="Q51" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>26</v>
       </c>
       <c r="R51" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>23</v>
       </c>
       <c r="S51" s="3">
         <v>7</v>
       </c>
       <c r="T51" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="U51" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="V51" s="3">
         <v>2</v>
       </c>
       <c r="W51" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>31</v>
       </c>
       <c r="X51" s="3">
@@ -10393,7 +10409,7 @@
         <v>33</v>
       </c>
       <c r="AA51" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>34</v>
       </c>
       <c r="AB51" s="3">
@@ -10409,23 +10425,23 @@
         <v>50</v>
       </c>
       <c r="AF51" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>83</v>
       </c>
       <c r="AG51" s="6">
         <v>3</v>
       </c>
       <c r="AH51" s="6">
-        <f t="shared" si="24"/>
-        <v>86</v>
-      </c>
-      <c r="AI51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ51" s="3">
         <f t="shared" si="25"/>
         <v>86</v>
       </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3">
+        <f t="shared" si="26"/>
+        <v>86</v>
+      </c>
       <c r="AK51" s="3" t="s">
         <v>60</v>
       </c>
@@ -10433,36 +10449,36 @@
         <v>4</v>
       </c>
       <c r="AM51" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>90</v>
       </c>
       <c r="AN51" s="3">
         <v>2</v>
       </c>
       <c r="AO51" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>92</v>
       </c>
       <c r="AP51" s="3">
         <v>1</v>
       </c>
       <c r="AQ51" s="3">
+        <f t="shared" si="31"/>
+        <v>93</v>
+      </c>
+      <c r="AR51" s="3">
+        <f t="shared" si="36"/>
+        <v>100</v>
+      </c>
+      <c r="AS51" s="3">
+        <f t="shared" si="29"/>
+        <v>107</v>
+      </c>
+      <c r="AT51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU51" s="3">
         <f t="shared" si="30"/>
-        <v>93</v>
-      </c>
-      <c r="AR51" s="3">
-        <f t="shared" si="35"/>
-        <v>100</v>
-      </c>
-      <c r="AS51" s="3">
-        <f t="shared" si="28"/>
-        <v>107</v>
-      </c>
-      <c r="AT51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU51" s="3">
-        <f t="shared" si="29"/>
         <v>11</v>
       </c>
       <c r="AV51" s="3" t="s">
@@ -10516,7 +10532,7 @@
         <v>7</v>
       </c>
       <c r="M52" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9</v>
       </c>
       <c r="N52" s="3">
@@ -10527,33 +10543,33 @@
         <v>15</v>
       </c>
       <c r="P52" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5</v>
       </c>
       <c r="Q52" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>19</v>
       </c>
       <c r="R52" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>16</v>
       </c>
       <c r="S52" s="3">
         <v>3</v>
       </c>
       <c r="T52" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>18</v>
       </c>
       <c r="U52" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>19</v>
       </c>
       <c r="V52" s="3">
         <v>5</v>
       </c>
       <c r="W52" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>23</v>
       </c>
       <c r="X52" s="3">
@@ -10567,7 +10583,7 @@
         <v>23</v>
       </c>
       <c r="AA52" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>25</v>
       </c>
       <c r="AB52" s="3">
@@ -10583,21 +10599,21 @@
         <v>40</v>
       </c>
       <c r="AF52" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>64</v>
       </c>
       <c r="AG52" s="6">
         <v>3</v>
       </c>
       <c r="AH52" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>67</v>
       </c>
       <c r="AI52" s="3">
         <v>7</v>
       </c>
       <c r="AJ52" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>74</v>
       </c>
       <c r="AK52" s="3">
@@ -10607,36 +10623,36 @@
         <v>6</v>
       </c>
       <c r="AM52" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>80</v>
       </c>
       <c r="AN52" s="3">
         <v>2</v>
       </c>
       <c r="AO52" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>82</v>
       </c>
       <c r="AP52" s="3">
         <v>0</v>
       </c>
       <c r="AQ52" s="3">
+        <f t="shared" si="31"/>
+        <v>82</v>
+      </c>
+      <c r="AR52" s="3">
+        <f t="shared" si="36"/>
+        <v>89</v>
+      </c>
+      <c r="AS52" s="3">
+        <f t="shared" si="29"/>
+        <v>96</v>
+      </c>
+      <c r="AT52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU52" s="3">
         <f t="shared" si="30"/>
-        <v>82</v>
-      </c>
-      <c r="AR52" s="3">
-        <f t="shared" si="35"/>
-        <v>89</v>
-      </c>
-      <c r="AS52" s="3">
-        <f t="shared" si="28"/>
-        <v>96</v>
-      </c>
-      <c r="AT52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU52" s="3">
-        <f t="shared" si="29"/>
         <v>9</v>
       </c>
       <c r="AV52" s="3" t="s">
@@ -10654,25 +10670,25 @@
     </row>
     <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C53" s="39" t="s">
         <v>68</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E53" s="38" t="s">
         <v>81</v>
       </c>
       <c r="F53" s="19">
-        <v>90014400</v>
+        <v>91017700</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -10690,7 +10706,7 @@
         <v>5</v>
       </c>
       <c r="M53" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9</v>
       </c>
       <c r="N53" s="23">
@@ -10704,40 +10720,39 @@
         <v>5</v>
       </c>
       <c r="Q53" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>14</v>
       </c>
       <c r="R53" s="23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S53" s="23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T53" s="25">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U53" s="23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V53" s="23">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W53" s="23">
-        <f t="shared" si="22"/>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="X53" s="23">
         <v>1</v>
       </c>
       <c r="Y53" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Z53" s="6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AA53" s="6">
-        <f t="shared" si="36"/>
-        <v>22</v>
+        <f t="shared" si="37"/>
+        <v>25</v>
       </c>
       <c r="AB53" s="23">
         <v>4</v>
@@ -10745,62 +10760,62 @@
       <c r="AC53" s="23"/>
       <c r="AD53" s="23"/>
       <c r="AE53" s="23">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AF53" s="23">
-        <f t="shared" si="23"/>
-        <v>67</v>
+        <f t="shared" si="24"/>
+        <v>63</v>
       </c>
       <c r="AG53" s="23">
         <v>3</v>
       </c>
       <c r="AH53" s="23">
-        <f t="shared" si="24"/>
-        <v>70</v>
+        <f t="shared" si="25"/>
+        <v>66</v>
       </c>
       <c r="AI53" s="23">
         <v>7</v>
       </c>
       <c r="AJ53" s="23">
-        <f t="shared" si="25"/>
-        <v>77</v>
+        <f t="shared" si="26"/>
+        <v>73</v>
       </c>
       <c r="AK53" s="23"/>
-      <c r="AL53" s="23">
-        <v>3</v>
+      <c r="AL53" s="47">
+        <v>2</v>
       </c>
       <c r="AM53" s="23">
-        <f t="shared" si="26"/>
-        <v>80</v>
+        <f t="shared" si="27"/>
+        <v>75</v>
       </c>
       <c r="AN53" s="23">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AO53" s="23">
-        <f t="shared" si="27"/>
-        <v>82</v>
+        <f t="shared" si="28"/>
+        <v>83</v>
       </c>
       <c r="AP53" s="23">
         <v>2</v>
       </c>
       <c r="AQ53" s="23">
-        <f t="shared" si="30"/>
-        <v>84</v>
+        <f t="shared" si="31"/>
+        <v>85</v>
       </c>
       <c r="AR53" s="23">
-        <f t="shared" si="35"/>
-        <v>91</v>
+        <f t="shared" si="36"/>
+        <v>92</v>
       </c>
       <c r="AS53" s="23">
-        <f t="shared" si="28"/>
-        <v>112</v>
+        <f t="shared" si="29"/>
+        <v>113</v>
       </c>
       <c r="AT53" s="23">
         <v>14</v>
       </c>
       <c r="AU53" s="3">
-        <f t="shared" si="29"/>
-        <v>22</v>
+        <f t="shared" si="30"/>
+        <v>15</v>
       </c>
       <c r="AV53" s="23" t="s">
         <v>133</v>
@@ -10811,31 +10826,31 @@
       <c r="AX53" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AY53" s="37">
-        <v>46143</v>
+      <c r="AY53" s="21">
+        <v>46507</v>
       </c>
     </row>
-    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C54" s="39" t="s">
         <v>68</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E54" s="38" t="s">
         <v>81</v>
       </c>
       <c r="F54" s="19">
-        <v>91017700</v>
+        <v>90014400</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -10853,7 +10868,7 @@
         <v>5</v>
       </c>
       <c r="M54" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9</v>
       </c>
       <c r="N54" s="23">
@@ -10867,39 +10882,40 @@
         <v>5</v>
       </c>
       <c r="Q54" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>14</v>
       </c>
       <c r="R54" s="23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S54" s="23">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T54" s="25">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="U54" s="23">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V54" s="23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W54" s="23">
-        <v>22</v>
+        <f>+U54+V54-1</f>
+        <v>18</v>
       </c>
       <c r="X54" s="23">
         <v>1</v>
       </c>
       <c r="Y54" s="3">
+        <v>18</v>
+      </c>
+      <c r="Z54" s="6">
+        <v>19</v>
+      </c>
+      <c r="AA54" s="6">
+        <f t="shared" si="37"/>
         <v>22</v>
-      </c>
-      <c r="Z54" s="6">
-        <v>22</v>
-      </c>
-      <c r="AA54" s="6">
-        <f t="shared" si="36"/>
-        <v>25</v>
       </c>
       <c r="AB54" s="23">
         <v>4</v>
@@ -10907,62 +10923,62 @@
       <c r="AC54" s="23"/>
       <c r="AD54" s="23"/>
       <c r="AE54" s="23">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AF54" s="23">
-        <f t="shared" si="23"/>
-        <v>63</v>
+        <f t="shared" si="24"/>
+        <v>67</v>
       </c>
       <c r="AG54" s="23">
         <v>3</v>
       </c>
       <c r="AH54" s="23">
-        <f t="shared" si="24"/>
-        <v>66</v>
+        <f t="shared" si="25"/>
+        <v>70</v>
       </c>
       <c r="AI54" s="23">
         <v>7</v>
       </c>
       <c r="AJ54" s="23">
-        <f t="shared" si="25"/>
-        <v>73</v>
+        <f t="shared" si="26"/>
+        <v>77</v>
       </c>
       <c r="AK54" s="23"/>
-      <c r="AL54" s="47">
+      <c r="AL54" s="23">
+        <v>3</v>
+      </c>
+      <c r="AM54" s="23">
+        <f t="shared" si="27"/>
+        <v>80</v>
+      </c>
+      <c r="AN54" s="23">
         <v>2</v>
       </c>
-      <c r="AM54" s="23">
-        <f t="shared" si="26"/>
-        <v>75</v>
-      </c>
-      <c r="AN54" s="23">
-        <v>8</v>
-      </c>
       <c r="AO54" s="23">
-        <f t="shared" si="27"/>
-        <v>83</v>
+        <f t="shared" si="28"/>
+        <v>82</v>
       </c>
       <c r="AP54" s="23">
         <v>2</v>
       </c>
       <c r="AQ54" s="23">
-        <f t="shared" si="30"/>
-        <v>85</v>
+        <f t="shared" si="31"/>
+        <v>84</v>
       </c>
       <c r="AR54" s="23">
-        <f t="shared" si="35"/>
-        <v>92</v>
+        <f t="shared" si="36"/>
+        <v>91</v>
       </c>
       <c r="AS54" s="23">
-        <f t="shared" si="28"/>
-        <v>113</v>
+        <f t="shared" si="29"/>
+        <v>112</v>
       </c>
       <c r="AT54" s="23">
         <v>14</v>
       </c>
       <c r="AU54" s="3">
-        <f t="shared" si="29"/>
-        <v>15</v>
+        <f t="shared" si="30"/>
+        <v>22</v>
       </c>
       <c r="AV54" s="23" t="s">
         <v>133</v>
@@ -10973,7 +10989,486 @@
       <c r="AX54" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AY54" s="21">
+      <c r="AY54" s="37">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C55" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="E55" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="F55" s="19">
+        <v>90016500</v>
+      </c>
+      <c r="G55" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="H55" s="2">
+        <v>0</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J55" s="2">
+        <v>29159</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L55" s="3">
+        <v>8</v>
+      </c>
+      <c r="M55" s="3">
+        <v>0</v>
+      </c>
+      <c r="N55" s="3">
+        <v>14</v>
+      </c>
+      <c r="O55" s="3">
+        <v>8</v>
+      </c>
+      <c r="P55" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q55" s="3">
+        <f t="shared" si="21"/>
+        <v>14</v>
+      </c>
+      <c r="R55" s="3">
+        <v>15</v>
+      </c>
+      <c r="S55" s="3">
+        <v>7</v>
+      </c>
+      <c r="T55" s="3">
+        <v>21</v>
+      </c>
+      <c r="U55" s="3">
+        <f>+T55+1</f>
+        <v>22</v>
+      </c>
+      <c r="V55" s="3">
+        <v>7</v>
+      </c>
+      <c r="W55" s="3">
+        <f>+U55+V55-1</f>
+        <v>28</v>
+      </c>
+      <c r="X55" s="3">
+        <v>2</v>
+      </c>
+      <c r="Y55" s="3">
+        <v>28</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>28</v>
+      </c>
+      <c r="AA55" s="6">
+        <v>29</v>
+      </c>
+      <c r="AB55" s="3">
+        <v>6</v>
+      </c>
+      <c r="AC55" s="3">
+        <v>7</v>
+      </c>
+      <c r="AD55" s="3">
+        <v>7</v>
+      </c>
+      <c r="AE55" s="3">
+        <v>50</v>
+      </c>
+      <c r="AF55" s="3">
+        <f t="shared" si="24"/>
+        <v>78</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH55" s="6">
+        <f t="shared" si="25"/>
+        <v>81</v>
+      </c>
+      <c r="AI55" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="3">
+        <f t="shared" si="26"/>
+        <v>81</v>
+      </c>
+      <c r="AK55" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL55" s="46">
+        <v>10</v>
+      </c>
+      <c r="AM55" s="3">
+        <f t="shared" si="27"/>
+        <v>91</v>
+      </c>
+      <c r="AN55" s="3">
+        <v>5</v>
+      </c>
+      <c r="AO55" s="3">
+        <f t="shared" si="28"/>
+        <v>96</v>
+      </c>
+      <c r="AP55" s="3">
+        <v>3</v>
+      </c>
+      <c r="AQ55" s="3">
+        <f t="shared" si="31"/>
+        <v>99</v>
+      </c>
+      <c r="AR55" s="3">
+        <f t="shared" si="36"/>
+        <v>106</v>
+      </c>
+      <c r="AS55" s="3">
+        <f t="shared" si="29"/>
+        <v>113</v>
+      </c>
+      <c r="AT55" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU55" s="3">
+        <f t="shared" si="30"/>
+        <v>14</v>
+      </c>
+      <c r="AV55" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW55" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AX55" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="AY55" s="40">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="56" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E56" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" s="19">
+        <v>91017700</v>
+      </c>
+      <c r="G56" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="H56" s="2">
+        <v>222222</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J56" s="2">
+        <v>222222</v>
+      </c>
+      <c r="K56" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="L56" s="3">
+        <v>7</v>
+      </c>
+      <c r="M56" s="3">
+        <v>9</v>
+      </c>
+      <c r="N56" s="23">
+        <v>21</v>
+      </c>
+      <c r="O56" s="3">
+        <v>29</v>
+      </c>
+      <c r="P56" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>33</v>
+      </c>
+      <c r="R56" s="23">
+        <v>30</v>
+      </c>
+      <c r="S56" s="23">
+        <v>7</v>
+      </c>
+      <c r="T56" s="23">
+        <v>36</v>
+      </c>
+      <c r="U56" s="23">
+        <v>37</v>
+      </c>
+      <c r="V56" s="23">
+        <v>1</v>
+      </c>
+      <c r="W56" s="23">
+        <v>37</v>
+      </c>
+      <c r="X56" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="3">
+        <v>37</v>
+      </c>
+      <c r="Z56" s="6">
+        <v>42</v>
+      </c>
+      <c r="AA56" s="6">
+        <v>44</v>
+      </c>
+      <c r="AB56" s="23">
+        <v>3</v>
+      </c>
+      <c r="AC56" s="33">
+        <v>4</v>
+      </c>
+      <c r="AD56" s="23">
+        <v>4</v>
+      </c>
+      <c r="AE56" s="23">
+        <v>40</v>
+      </c>
+      <c r="AF56" s="23">
+        <v>83</v>
+      </c>
+      <c r="AG56" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH56" s="23">
+        <v>86</v>
+      </c>
+      <c r="AI56" s="23">
+        <v>0</v>
+      </c>
+      <c r="AJ56" s="23">
+        <v>86</v>
+      </c>
+      <c r="AK56" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL56" s="23">
+        <v>2</v>
+      </c>
+      <c r="AM56" s="23">
+        <f t="shared" si="27"/>
+        <v>88</v>
+      </c>
+      <c r="AN56" s="23">
+        <v>1</v>
+      </c>
+      <c r="AO56" s="23">
+        <f t="shared" si="28"/>
+        <v>89</v>
+      </c>
+      <c r="AP56" s="23">
+        <v>3</v>
+      </c>
+      <c r="AQ56" s="23">
+        <f t="shared" si="31"/>
+        <v>92</v>
+      </c>
+      <c r="AR56" s="23">
+        <f t="shared" si="36"/>
+        <v>99</v>
+      </c>
+      <c r="AS56" s="23">
+        <f t="shared" ref="AS56:AS57" si="38">+AR56+7+AT56</f>
+        <v>106</v>
+      </c>
+      <c r="AT56" s="23">
+        <v>0</v>
+      </c>
+      <c r="AU56" s="23">
+        <v>14</v>
+      </c>
+      <c r="AV56" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW56" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="AX56" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY56">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="57" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B57" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F57" s="19">
+        <v>90016500</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H57" s="2">
+        <v>0</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J57" s="2">
+        <v>29159</v>
+      </c>
+      <c r="K57" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="L57" s="3">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3">
+        <v>8</v>
+      </c>
+      <c r="N57" s="3">
+        <v>1</v>
+      </c>
+      <c r="O57" s="3">
+        <v>8</v>
+      </c>
+      <c r="P57" s="3">
+        <v>6</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>13</v>
+      </c>
+      <c r="R57" s="3">
+        <v>9</v>
+      </c>
+      <c r="S57" s="3">
+        <v>12</v>
+      </c>
+      <c r="T57" s="3">
+        <v>20</v>
+      </c>
+      <c r="U57" s="3">
+        <v>22</v>
+      </c>
+      <c r="V57" s="3">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3">
+        <v>26</v>
+      </c>
+      <c r="X57" s="3">
+        <v>4</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>29</v>
+      </c>
+      <c r="Z57" s="6">
+        <v>34</v>
+      </c>
+      <c r="AA57" s="6">
+        <v>36</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>4</v>
+      </c>
+      <c r="AC57" s="3"/>
+      <c r="AD57" s="3"/>
+      <c r="AE57" s="6">
+        <v>34</v>
+      </c>
+      <c r="AF57" s="6">
+        <v>69</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>3</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>72</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="3">
+        <v>72</v>
+      </c>
+      <c r="AK57" s="3"/>
+      <c r="AL57" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM57" s="3">
+        <v>74</v>
+      </c>
+      <c r="AN57" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO57" s="3">
+        <v>75</v>
+      </c>
+      <c r="AP57" s="3">
+        <v>3</v>
+      </c>
+      <c r="AQ57" s="23">
+        <f t="shared" si="31"/>
+        <v>78</v>
+      </c>
+      <c r="AR57" s="23">
+        <f t="shared" si="36"/>
+        <v>85</v>
+      </c>
+      <c r="AS57" s="23">
+        <f t="shared" si="38"/>
+        <v>106</v>
+      </c>
+      <c r="AT57" s="3">
+        <v>14</v>
+      </c>
+      <c r="AU57" s="3">
+        <v>27</v>
+      </c>
+      <c r="AV57" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW57" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="AX57" t="s">
+        <v>56</v>
+      </c>
+      <c r="AY57">
         <v>46507</v>
       </c>
     </row>
@@ -11000,26 +11495,19 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY54" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="3">
+  <autoFilter ref="A1:AY57" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
+    <filterColumn colId="0">
       <filters>
-        <filter val="ESALG"/>
-        <filter val="ESVLC"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="47">
-      <filters>
-        <filter val="Direct"/>
-        <filter val="Indirect"/>
+        <filter val="930"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 C53:C1048195 E53:E1048195 D53:D60 D72:D1048195 C16:E52 K16:K1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
+  <dataValidations disablePrompts="1" count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 C58:C1048195 D72:D1048195 C16:E57 E58:E1048195 D58:D60 K16:K1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
       <formula1>shippername</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 H55:K1048195 C53:C1048195 E53:E1048195 D53:D60 D72:D1048195 C2:E52 J12:J54 I2:I54 K2:K54" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 D58:D60 H58:K1048195 C58:C1048195 E58:E1048195 D72:D1048195 J12:J57 I2:I57 C2:E57 K2:K57" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
       <formula1>AILNname</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048195" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC07925-F144-47AB-AB15-F42C57458940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8888B838-B456-427F-9FA2-28139610D62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja2" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja3" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja2!$D$7:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VTT actif'!$A$1:$AY$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -426,8 +427,334 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>ZHAO Tengda</author>
+    <author>KERHOAS Delphine</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{0DA5B882-74A5-4F2F-90D1-838EE848C665}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+jaune flux double</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{2877F806-0082-4CFE-BD62-9AC138F54BA5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{E23F635B-20D6-4A42-A2BB-4D99BD95E619}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Donc Si AILN SI2C =  Day ILN Order = Mardi = 9</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{204E7EC7-C672-40B6-B6FF-E26567733C28}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>KERHOAS Delphine:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+supplier period
+Delivery time to ILN = nbre de jour  soit 7 ou 14 =&gt; semaine complet </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{B09BABFD-7254-4794-8727-CAAF844B4ECE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+c'est jour</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{FDF987CC-CEE5-4C32-A68B-7358A63AB9B8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Time of recept est Durée 5 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{DB05CCCC-0B0D-46D3-A562-0A8B0D490FBC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+c'est jour</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{7FB46653-659E-4A49-B666-B709C56CE96A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Packaging est toujour 7</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{EE33B89B-21AA-4EC0-B350-1E237CE10548}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+c'est une durée</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{8F19CFE3-193F-47A8-A454-45865FF10FFA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+c'est une durée</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{8AEBFA37-B3C3-4E72-AADE-120FFC106A9C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+c'est une durée</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AL1" authorId="0" shapeId="0" xr:uid="{5DB733ED-228E-414A-95A7-5C12BDC0610D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+clé POD?
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AM1" authorId="0" shapeId="0" xr:uid="{E8903A01-4354-4042-9B39-98EEB412033C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ZHAO Tengda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+clé POD?
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="180">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -1341,7 +1668,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1682,20 +2009,20 @@
   <sheetPr codeName="Feuil4" filterMode="1">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:BF71"/>
+  <dimension ref="A1:BF69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.85546875" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="34" width="10.42578125" customWidth="1"/>
@@ -6195,7 +6522,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>930</v>
       </c>
@@ -7455,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="Q34" s="3">
-        <f t="shared" ref="Q34:Q65" si="21">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
+        <f t="shared" ref="Q34:Q55" si="21">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
         <v>0</v>
       </c>
       <c r="R34" s="3">
@@ -7466,7 +7793,7 @@
         <v>7</v>
       </c>
       <c r="T34" s="3">
-        <f t="shared" ref="T34:T65" si="22">+R34+S34-1</f>
+        <f t="shared" ref="T34:T52" si="22">+R34+S34-1</f>
         <v>29</v>
       </c>
       <c r="U34" s="3">
@@ -7477,7 +7804,7 @@
         <v>1</v>
       </c>
       <c r="W34" s="3">
-        <f t="shared" ref="W34:W65" si="23">+U34+V34-1</f>
+        <f t="shared" ref="W34:W52" si="23">+U34+V34-1</f>
         <v>30</v>
       </c>
       <c r="X34" s="3">
@@ -7506,21 +7833,21 @@
         <v>63</v>
       </c>
       <c r="AF34" s="3">
-        <f t="shared" ref="AF34:AF65" si="24">+AE34+AA34-1</f>
+        <f t="shared" ref="AF34:AF55" si="24">+AE34+AA34-1</f>
         <v>98</v>
       </c>
       <c r="AG34" s="6">
         <v>3</v>
       </c>
       <c r="AH34" s="6">
-        <f t="shared" ref="AH34:AH65" si="25">+AF34+AG34</f>
+        <f t="shared" ref="AH34:AH55" si="25">+AF34+AG34</f>
         <v>101</v>
       </c>
       <c r="AI34" s="3">
         <v>0</v>
       </c>
       <c r="AJ34" s="3">
-        <f t="shared" ref="AJ34:AJ65" si="26">+AI34+AH34</f>
+        <f t="shared" ref="AJ34:AJ55" si="26">+AI34+AH34</f>
         <v>101</v>
       </c>
       <c r="AK34" s="3" t="s">
@@ -7530,14 +7857,14 @@
         <v>4</v>
       </c>
       <c r="AM34" s="3">
-        <f t="shared" ref="AM34:AM65" si="27">+AJ34+AL34</f>
+        <f t="shared" ref="AM34:AM55" si="27">+AJ34+AL34</f>
         <v>105</v>
       </c>
       <c r="AN34" s="3">
         <v>3</v>
       </c>
       <c r="AO34" s="3">
-        <f t="shared" ref="AO34:AO65" si="28">+AM34+AN34</f>
+        <f t="shared" ref="AO34:AO55" si="28">+AM34+AN34</f>
         <v>108</v>
       </c>
       <c r="AP34" s="3">
@@ -7552,7 +7879,7 @@
         <v>119</v>
       </c>
       <c r="AS34" s="3">
-        <f t="shared" ref="AS34:AS65" si="29">+AR34+7+AT34</f>
+        <f t="shared" ref="AS34:AS55" si="29">+AR34+7+AT34</f>
         <v>126</v>
       </c>
       <c r="AT34" s="3">
@@ -9593,7 +9920,7 @@
         <v>3</v>
       </c>
       <c r="AQ46" s="3">
-        <f t="shared" ref="AQ46:AQ57" si="31">+AO46+AP46</f>
+        <f t="shared" ref="AQ46:AQ55" si="31">+AO46+AP46</f>
         <v>78</v>
       </c>
       <c r="AR46" s="23">
@@ -9772,7 +10099,7 @@
         <v>86</v>
       </c>
       <c r="AR47" s="3">
-        <f t="shared" ref="AR47:AR57" si="36">+AQ47+7</f>
+        <f t="shared" ref="AR47:AR55" si="36">+AQ47+7</f>
         <v>93</v>
       </c>
       <c r="AS47" s="3">
@@ -10993,7 +11320,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="55" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>176</v>
       </c>
@@ -11007,7 +11334,7 @@
         <v>136</v>
       </c>
       <c r="E55" s="48" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="F55" s="19">
         <v>90016500</v>
@@ -11037,14 +11364,14 @@
         <v>14</v>
       </c>
       <c r="O55" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P55" s="3">
         <v>7</v>
       </c>
       <c r="Q55" s="3">
         <f t="shared" si="21"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R55" s="3">
         <v>15</v>
@@ -11060,20 +11387,20 @@
         <v>22</v>
       </c>
       <c r="V55" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W55" s="3">
         <f>+U55+V55-1</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="X55" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y55" s="3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Z55" s="6">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA55" s="6">
         <v>29</v>
@@ -11160,357 +11487,45 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="56" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E56" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="F56" s="19">
-        <v>91017700</v>
-      </c>
-      <c r="G56" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="H56" s="2">
-        <v>222222</v>
-      </c>
-      <c r="I56" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J56" s="2">
-        <v>222222</v>
-      </c>
-      <c r="K56" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="L56" s="3">
-        <v>7</v>
-      </c>
-      <c r="M56" s="3">
-        <v>9</v>
-      </c>
-      <c r="N56" s="23">
-        <v>21</v>
-      </c>
-      <c r="O56" s="3">
-        <v>29</v>
-      </c>
-      <c r="P56" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q56" s="3">
-        <v>33</v>
-      </c>
-      <c r="R56" s="23">
-        <v>30</v>
-      </c>
-      <c r="S56" s="23">
-        <v>7</v>
-      </c>
-      <c r="T56" s="23">
-        <v>36</v>
-      </c>
-      <c r="U56" s="23">
-        <v>37</v>
-      </c>
-      <c r="V56" s="23">
-        <v>1</v>
-      </c>
-      <c r="W56" s="23">
-        <v>37</v>
-      </c>
-      <c r="X56" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y56" s="3">
-        <v>37</v>
-      </c>
-      <c r="Z56" s="6">
-        <v>42</v>
-      </c>
-      <c r="AA56" s="6">
-        <v>44</v>
-      </c>
-      <c r="AB56" s="23">
-        <v>3</v>
-      </c>
-      <c r="AC56" s="33">
-        <v>4</v>
-      </c>
-      <c r="AD56" s="23">
-        <v>4</v>
-      </c>
-      <c r="AE56" s="23">
-        <v>40</v>
-      </c>
-      <c r="AF56" s="23">
-        <v>83</v>
-      </c>
-      <c r="AG56" s="23">
-        <v>3</v>
-      </c>
-      <c r="AH56" s="23">
-        <v>86</v>
-      </c>
-      <c r="AI56" s="23">
-        <v>0</v>
-      </c>
-      <c r="AJ56" s="23">
-        <v>86</v>
-      </c>
-      <c r="AK56" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL56" s="23">
-        <v>2</v>
-      </c>
-      <c r="AM56" s="23">
-        <f t="shared" si="27"/>
-        <v>88</v>
-      </c>
-      <c r="AN56" s="23">
-        <v>1</v>
-      </c>
-      <c r="AO56" s="23">
-        <f t="shared" si="28"/>
-        <v>89</v>
-      </c>
-      <c r="AP56" s="23">
-        <v>3</v>
-      </c>
-      <c r="AQ56" s="23">
-        <f t="shared" si="31"/>
-        <v>92</v>
-      </c>
-      <c r="AR56" s="23">
-        <f t="shared" si="36"/>
-        <v>99</v>
-      </c>
-      <c r="AS56" s="23">
-        <f t="shared" ref="AS56:AS57" si="38">+AR56+7+AT56</f>
-        <v>106</v>
-      </c>
-      <c r="AT56" s="23">
-        <v>0</v>
-      </c>
-      <c r="AU56" s="23">
-        <v>14</v>
-      </c>
-      <c r="AV56" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="AW56" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="AX56" t="s">
-        <v>75</v>
-      </c>
-      <c r="AY56">
-        <v>46507</v>
-      </c>
-    </row>
-    <row r="57" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B57" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F57" s="19">
-        <v>90016500</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H57" s="2">
-        <v>0</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="J57" s="2">
-        <v>29159</v>
-      </c>
-      <c r="K57" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="L57" s="3">
-        <v>5</v>
-      </c>
-      <c r="M57" s="3">
-        <v>8</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1</v>
-      </c>
-      <c r="O57" s="3">
-        <v>8</v>
-      </c>
-      <c r="P57" s="3">
-        <v>6</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>13</v>
-      </c>
-      <c r="R57" s="3">
-        <v>9</v>
-      </c>
-      <c r="S57" s="3">
-        <v>12</v>
-      </c>
-      <c r="T57" s="3">
-        <v>20</v>
-      </c>
-      <c r="U57" s="3">
-        <v>22</v>
-      </c>
-      <c r="V57" s="3">
-        <v>5</v>
-      </c>
-      <c r="W57" s="3">
-        <v>26</v>
-      </c>
-      <c r="X57" s="3">
-        <v>4</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>29</v>
-      </c>
-      <c r="Z57" s="6">
-        <v>34</v>
-      </c>
-      <c r="AA57" s="6">
-        <v>36</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>4</v>
-      </c>
-      <c r="AC57" s="3"/>
-      <c r="AD57" s="3"/>
-      <c r="AE57" s="6">
-        <v>34</v>
-      </c>
-      <c r="AF57" s="6">
-        <v>69</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>3</v>
-      </c>
-      <c r="AH57" s="3">
-        <v>72</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ57" s="3">
-        <v>72</v>
-      </c>
-      <c r="AK57" s="3"/>
-      <c r="AL57" s="3">
-        <v>2</v>
-      </c>
-      <c r="AM57" s="3">
-        <v>74</v>
-      </c>
-      <c r="AN57" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO57" s="3">
-        <v>75</v>
-      </c>
-      <c r="AP57" s="3">
-        <v>3</v>
-      </c>
-      <c r="AQ57" s="23">
-        <f t="shared" si="31"/>
-        <v>78</v>
-      </c>
-      <c r="AR57" s="23">
-        <f t="shared" si="36"/>
-        <v>85</v>
-      </c>
-      <c r="AS57" s="23">
-        <f t="shared" si="38"/>
-        <v>106</v>
-      </c>
-      <c r="AT57" s="3">
-        <v>14</v>
-      </c>
-      <c r="AU57" s="3">
-        <v>27</v>
-      </c>
-      <c r="AV57" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="AW57" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="AX57" t="s">
-        <v>56</v>
-      </c>
-      <c r="AY57">
-        <v>46507</v>
-      </c>
+    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="D59" s="41"/>
     </row>
     <row r="61" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="D61" s="41"/>
+      <c r="D61" s="42"/>
     </row>
     <row r="63" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="D63" s="42"/>
+      <c r="D63" s="41"/>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D65" s="41"/>
+      <c r="D65" s="42"/>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D67" s="42"/>
+      <c r="D67" s="41"/>
+    </row>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D68" s="42"/>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D69" s="41"/>
-    </row>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D70" s="42"/>
-    </row>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D71" s="42"/>
+      <c r="D69" s="42"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY57" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
+  <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
     <filterColumn colId="0">
       <filters>
-        <filter val="930"/>
+        <filter val="O011"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 C58:C1048195 D72:D1048195 C16:E57 E58:E1048195 D58:D60 K16:K1048195" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 C56:C1048193 D70:D1048193 C16:E55 E56:E1048193 D56:D58 K16:K1048193" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
       <formula1>shippername</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 D58:D60 H58:K1048195 C58:C1048195 E58:E1048195 D72:D1048195 J12:J57 I2:I57 C2:E57 K2:K57" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 D56:D58 H56:K1048193 C56:C1048193 E56:E1048193 D70:D1048193 J12:J55 I2:I55 C2:E55 K2:K55" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
       <formula1>AILNname</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048195" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048193" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">
       <formula1>plantname</formula1>
     </dataValidation>
   </dataValidations>
@@ -11782,6 +11797,507 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A526D049-164C-47D4-96CD-56CBAA0ABF56}">
+  <dimension ref="A1:BF3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="R1" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="T1" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="U1" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="W1" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="X1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y1" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z1" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA1" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB1" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE1" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF1" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH1" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="AI1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ1" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK1" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM1" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="AN1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO1" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="AP1" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ1" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="AR1" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="AS1" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="AT1" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="AU1" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV1" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AW1" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX1" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY1" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="BA1">
+        <v>911</v>
+      </c>
+      <c r="BB1">
+        <v>926</v>
+      </c>
+      <c r="BE1">
+        <v>63</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="19">
+        <v>91017700</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="H2" s="2">
+        <v>222222</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="2">
+        <v>222222</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="L2" s="3">
+        <v>7</v>
+      </c>
+      <c r="M2" s="3">
+        <v>9</v>
+      </c>
+      <c r="N2" s="23">
+        <v>21</v>
+      </c>
+      <c r="O2" s="3">
+        <v>29</v>
+      </c>
+      <c r="P2" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>33</v>
+      </c>
+      <c r="R2" s="23">
+        <v>30</v>
+      </c>
+      <c r="S2" s="23">
+        <v>7</v>
+      </c>
+      <c r="T2" s="23">
+        <v>36</v>
+      </c>
+      <c r="U2" s="23">
+        <v>37</v>
+      </c>
+      <c r="V2" s="23">
+        <v>1</v>
+      </c>
+      <c r="W2" s="23">
+        <v>37</v>
+      </c>
+      <c r="X2" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>37</v>
+      </c>
+      <c r="Z2" s="6">
+        <v>42</v>
+      </c>
+      <c r="AA2" s="6">
+        <v>44</v>
+      </c>
+      <c r="AB2" s="23">
+        <v>3</v>
+      </c>
+      <c r="AC2" s="33">
+        <v>4</v>
+      </c>
+      <c r="AD2" s="23">
+        <v>4</v>
+      </c>
+      <c r="AE2" s="23">
+        <v>40</v>
+      </c>
+      <c r="AF2" s="23">
+        <v>83</v>
+      </c>
+      <c r="AG2" s="23">
+        <v>3</v>
+      </c>
+      <c r="AH2" s="23">
+        <v>86</v>
+      </c>
+      <c r="AI2" s="23">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="23">
+        <v>86</v>
+      </c>
+      <c r="AK2" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL2" s="23">
+        <v>2</v>
+      </c>
+      <c r="AM2" s="23">
+        <f t="shared" ref="AM2" si="0">+AJ2+AL2</f>
+        <v>88</v>
+      </c>
+      <c r="AN2" s="23">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="23">
+        <f t="shared" ref="AO2" si="1">+AM2+AN2</f>
+        <v>89</v>
+      </c>
+      <c r="AP2" s="23">
+        <v>3</v>
+      </c>
+      <c r="AQ2" s="23">
+        <f t="shared" ref="AQ2:AQ3" si="2">+AO2+AP2</f>
+        <v>92</v>
+      </c>
+      <c r="AR2" s="23">
+        <f t="shared" ref="AR2:AR3" si="3">+AQ2+7</f>
+        <v>99</v>
+      </c>
+      <c r="AS2" s="23">
+        <f t="shared" ref="AS2:AS3" si="4">+AR2+7+AT2</f>
+        <v>106</v>
+      </c>
+      <c r="AT2" s="23">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="23">
+        <v>14</v>
+      </c>
+      <c r="AV2" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW2" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY2">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" s="19">
+        <v>90016500</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="2">
+        <v>29159</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="L3" s="3">
+        <v>5</v>
+      </c>
+      <c r="M3" s="3">
+        <v>8</v>
+      </c>
+      <c r="N3" s="3">
+        <v>1</v>
+      </c>
+      <c r="O3" s="3">
+        <v>8</v>
+      </c>
+      <c r="P3" s="3">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>13</v>
+      </c>
+      <c r="R3" s="3">
+        <v>9</v>
+      </c>
+      <c r="S3" s="3">
+        <v>12</v>
+      </c>
+      <c r="T3" s="3">
+        <v>20</v>
+      </c>
+      <c r="U3" s="3">
+        <v>22</v>
+      </c>
+      <c r="V3" s="3">
+        <v>5</v>
+      </c>
+      <c r="W3" s="3">
+        <v>26</v>
+      </c>
+      <c r="X3" s="3">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>29</v>
+      </c>
+      <c r="Z3" s="6">
+        <v>34</v>
+      </c>
+      <c r="AA3" s="6">
+        <v>36</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="6">
+        <v>34</v>
+      </c>
+      <c r="AF3" s="6">
+        <v>69</v>
+      </c>
+      <c r="AG3" s="3">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="3">
+        <v>72</v>
+      </c>
+      <c r="AI3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3">
+        <v>72</v>
+      </c>
+      <c r="AK3" s="3"/>
+      <c r="AL3" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM3" s="3">
+        <v>74</v>
+      </c>
+      <c r="AN3" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="3">
+        <v>75</v>
+      </c>
+      <c r="AP3" s="3">
+        <v>3</v>
+      </c>
+      <c r="AQ3" s="23">
+        <f t="shared" si="2"/>
+        <v>78</v>
+      </c>
+      <c r="AR3" s="23">
+        <f t="shared" si="3"/>
+        <v>85</v>
+      </c>
+      <c r="AS3" s="23">
+        <f t="shared" si="4"/>
+        <v>106</v>
+      </c>
+      <c r="AT3" s="3">
+        <v>14</v>
+      </c>
+      <c r="AU3" s="3">
+        <v>27</v>
+      </c>
+      <c r="AV3" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW3" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AY3">
+        <v>46507</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G3" xr:uid="{3194311D-BEB7-4DF2-9AB9-2FB94FFAA4EC}">
+      <formula1>plantname</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K3 C2:E3" xr:uid="{7303FB90-DF85-4FA7-AC0B-4DEADE2A5044}">
+      <formula1>AILNname</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E3 K2:K3" xr:uid="{F34A82AD-0EB3-443D-9059-E6567C6CDA8B}">
+      <formula1>shippername</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9999a5d2-caa4-4f63-bace-dd6824b086db}" enabled="1" method="Standard" siteId="{de415ce7-227e-480f-88c9-c7dab50e161a}" contentBits="2" removed="0"/>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8888B838-B456-427F-9FA2-28139610D62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD4CF68-554B-4478-BE00-AB8AABEF6189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -2006,23 +2006,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4" filterMode="1">
+  <sheetPr codeName="Feuil4">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:BF69"/>
+  <dimension ref="A1:BF67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.85546875" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="34" width="10.42578125" customWidth="1"/>
@@ -2203,7 +2203,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>60</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>120</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>121</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>233</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>416</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>752</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>761</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>888</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>901</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>904</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>906</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>907</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>908</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>910</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>912</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>916</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>917</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>918</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>920</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>924</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>925</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>928</v>
       </c>
@@ -6522,7 +6522,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>930</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>931</v>
       </c>
@@ -6867,7 +6867,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>932</v>
       </c>
@@ -7040,7 +7040,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>1005</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>1006</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>1007</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>1009</v>
       </c>
@@ -7730,7 +7730,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>1010</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>1012</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>1014</v>
       </c>
@@ -8247,7 +8247,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>1015</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>1034</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1036</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>1037</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>1039</v>
       </c>
@@ -9108,7 +9108,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>1040</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>1045</v>
       </c>
@@ -9453,7 +9453,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>1084</v>
       </c>
@@ -9626,7 +9626,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>138</v>
       </c>
@@ -9788,7 +9788,7 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>172</v>
       </c>
@@ -9951,7 +9951,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>143</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>144</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>145</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>146</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>147</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="52" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>152</v>
       </c>
@@ -10995,7 +10995,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>168</v>
       </c>
@@ -11157,7 +11157,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>173</v>
       </c>
@@ -11487,45 +11487,39 @@
         <v>46507</v>
       </c>
     </row>
+    <row r="57" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="D57" s="41"/>
+    </row>
     <row r="59" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="D59" s="41"/>
+      <c r="D59" s="42"/>
     </row>
     <row r="61" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="D61" s="42"/>
+      <c r="D61" s="41"/>
     </row>
     <row r="63" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="D63" s="41"/>
+      <c r="D63" s="42"/>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D65" s="42"/>
+      <c r="D65" s="41"/>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D66" s="42"/>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D67" s="41"/>
-    </row>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D68" s="42"/>
-    </row>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D69" s="42"/>
+      <c r="D67" s="42"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="O011"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 C56:C1048193 D70:D1048193 C16:E55 E56:E1048193 D56:D58 K16:K1048193" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 D68:D1048191 C16:E55 K16:K1048191 D56 E56:E1048191 C56:C1048191" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
       <formula1>shippername</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 D56:D58 H56:K1048193 C56:C1048193 E56:E1048193 D70:D1048193 J12:J55 I2:I55 C2:E55 K2:K55" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J10 D68:D1048191 J12:J55 I2:I55 C2:E55 K2:K55 E56:E1048191 C56:C1048191 H56:K1048191 D56" xr:uid="{DD2A48DC-7068-4BD6-8A6F-E802386CE572}">
       <formula1>AILNname</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048193" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Please check information" error="This is not a known plant, please check the spelling or enter the information in the sheet &quot;Plant_ALIN&quot;" sqref="G2:G1048191" xr:uid="{D2D52A73-EC4B-4324-8BC4-BD77EF4C5461}">
       <formula1>plantname</formula1>
     </dataValidation>
   </dataValidations>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD4CF68-554B-4478-BE00-AB8AABEF6189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE843C4-C1B6-4607-9E43-CBB9517BCB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -2006,37 +2006,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4">
+  <sheetPr codeName="Feuil4" filterMode="1">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.453125" defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.42578125" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="1" max="1" width="9.54296875" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.453125" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.453125" style="8" customWidth="1" outlineLevel="1"/>
     <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.85546875" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" customWidth="1"/>
-    <col min="15" max="34" width="10.42578125" customWidth="1"/>
-    <col min="35" max="36" width="15.140625" customWidth="1"/>
-    <col min="37" max="37" width="15.85546875" customWidth="1"/>
-    <col min="38" max="39" width="9.5703125" customWidth="1"/>
-    <col min="40" max="41" width="15.42578125" customWidth="1"/>
-    <col min="42" max="42" width="10.42578125" customWidth="1" collapsed="1"/>
-    <col min="43" max="49" width="10.42578125" customWidth="1"/>
-    <col min="50" max="50" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.26953125" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.54296875" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.81640625" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.453125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" customWidth="1"/>
+    <col min="14" max="14" width="14.54296875" customWidth="1"/>
+    <col min="15" max="34" width="10.453125" customWidth="1"/>
+    <col min="35" max="36" width="15.1796875" customWidth="1"/>
+    <col min="37" max="37" width="15.81640625" customWidth="1"/>
+    <col min="38" max="39" width="9.54296875" customWidth="1"/>
+    <col min="40" max="41" width="15.453125" customWidth="1"/>
+    <col min="42" max="42" width="10.453125" customWidth="1" collapsed="1"/>
+    <col min="43" max="49" width="10.453125" customWidth="1"/>
+    <col min="50" max="50" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.26953125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>60</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>120</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>121</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>233</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>416</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>752</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>761</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>888</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>901</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>904</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>906</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>907</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>908</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>910</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>912</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>916</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>917</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>918</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M20" s="3">
         <f t="shared" si="18"/>
@@ -5484,7 +5484,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>920</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>924</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>925</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>928</v>
       </c>
@@ -6522,7 +6522,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>930</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>931</v>
       </c>
@@ -6867,7 +6867,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>932</v>
       </c>
@@ -7040,7 +7040,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>1005</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>1006</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>1007</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>1009</v>
       </c>
@@ -7730,7 +7730,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>1010</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>1012</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>1014</v>
       </c>
@@ -8247,7 +8247,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>1015</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>1034</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>1036</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>1037</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>1039</v>
       </c>
@@ -9108,7 +9108,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>1040</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>1045</v>
       </c>
@@ -9453,7 +9453,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>1084</v>
       </c>
@@ -9626,7 +9626,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>138</v>
       </c>
@@ -9788,7 +9788,7 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>172</v>
       </c>
@@ -9951,7 +9951,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>143</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>144</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>145</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="50" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>146</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>147</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>152</v>
       </c>
@@ -10995,7 +10995,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>168</v>
       </c>
@@ -11157,7 +11157,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>173</v>
       </c>
@@ -11320,7 +11320,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>176</v>
       </c>
@@ -11487,30 +11487,36 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="57" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:51" x14ac:dyDescent="0.35">
       <c r="D57" s="41"/>
     </row>
-    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:51" x14ac:dyDescent="0.35">
       <c r="D59" s="42"/>
     </row>
-    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:51" x14ac:dyDescent="0.35">
       <c r="D61" s="41"/>
     </row>
-    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:51" x14ac:dyDescent="0.35">
       <c r="D63" s="42"/>
     </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D65" s="41"/>
     </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D66" s="42"/>
     </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D67" s="42"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
+  <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="918"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 D68:D1048191 C16:E55 K16:K1048191 D56 E56:E1048191 C56:C1048191" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">
@@ -11536,9 +11542,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7007F1-B98C-4FB4-AD1E-FC672D1A14BF}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="B2:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>161</v>
       </c>
@@ -11552,7 +11558,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>164</v>
       </c>
@@ -11566,7 +11572,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>167</v>
       </c>
@@ -11579,15 +11585,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20166134-0068-44E4-897C-A3439A6356AD}">
   <dimension ref="D7:H17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="4:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:8" ht="29" x14ac:dyDescent="0.35">
       <c r="D7" s="31" t="s">
         <v>6</v>
       </c>
@@ -11604,7 +11610,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:8" ht="16" x14ac:dyDescent="0.4">
       <c r="D8" s="5" t="s">
         <v>68</v>
       </c>
@@ -11621,7 +11627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:8" ht="16" x14ac:dyDescent="0.4">
       <c r="D9" s="43" t="s">
         <v>98</v>
       </c>
@@ -11638,7 +11644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:8" ht="16" x14ac:dyDescent="0.4">
       <c r="D10" s="43" t="s">
         <v>62</v>
       </c>
@@ -11655,7 +11661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:8" ht="16" x14ac:dyDescent="0.4">
       <c r="D11" s="43" t="s">
         <v>68</v>
       </c>
@@ -11672,7 +11678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:8" ht="16" x14ac:dyDescent="0.4">
       <c r="D12" s="23" t="s">
         <v>68</v>
       </c>
@@ -11689,7 +11695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:8" ht="16" x14ac:dyDescent="0.4">
       <c r="D13" s="23" t="s">
         <v>68</v>
       </c>
@@ -11706,7 +11712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:8" ht="16" x14ac:dyDescent="0.4">
       <c r="D14" s="43" t="s">
         <v>52</v>
       </c>
@@ -11723,7 +11729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:8" ht="16" x14ac:dyDescent="0.4">
       <c r="D15" s="23" t="s">
         <v>57</v>
       </c>
@@ -11740,7 +11746,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="4:8" ht="16" x14ac:dyDescent="0.4">
       <c r="D16" s="43" t="s">
         <v>90</v>
       </c>
@@ -11757,7 +11763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="4:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:8" ht="16" x14ac:dyDescent="0.4">
       <c r="D17" s="43" t="s">
         <v>96</v>
       </c>
@@ -11794,9 +11800,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A526D049-164C-47D4-96CD-56CBAA0ABF56}">
   <dimension ref="A1:BF3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
@@ -11963,7 +11969,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>177</v>
       </c>
@@ -12123,7 +12129,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>179</v>
       </c>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE843C4-C1B6-4607-9E43-CBB9517BCB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE10EFA5-F509-46E3-8EC5-FAC01165B58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE10EFA5-F509-46E3-8EC5-FAC01165B58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1214FC8-FC25-485B-8D86-8B3F6DC0483B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="19090" yWindow="-1340" windowWidth="19420" windowHeight="11500" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -2016,13 +2016,13 @@
     <col min="2" max="2" width="12.81640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.453125" customWidth="1"/>
     <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.453125" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.26953125" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.54296875" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.81640625" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.453125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.453125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.26953125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.54296875" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.81640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.453125" style="9" customWidth="1" collapsed="1"/>
     <col min="13" max="13" width="10.453125" customWidth="1"/>
     <col min="14" max="14" width="14.54296875" customWidth="1"/>
     <col min="15" max="34" width="10.453125" customWidth="1"/>
@@ -5311,7 +5311,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>918</v>
       </c>
@@ -10995,7 +10995,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>168</v>
       </c>
@@ -11009,7 +11009,7 @@
         <v>58</v>
       </c>
       <c r="E53" s="38" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="F53" s="19">
         <v>91017700</v>
@@ -11513,7 +11513,12 @@
   <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
     <filterColumn colId="0">
       <filters>
-        <filter val="918"/>
+        <filter val="O009"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="SPAIN"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1214FC8-FC25-485B-8D86-8B3F6DC0483B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681503C2-C62F-4D40-A51B-C3D698FDB877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-1340" windowWidth="19420" windowHeight="11500" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
@@ -2006,7 +2006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4" filterMode="1">
+  <sheetPr codeName="Feuil4">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF67"/>
@@ -2203,7 +2203,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>60</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>120</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>121</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>233</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>416</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>752</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>761</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>888</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>901</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>904</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>906</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>907</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>908</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>910</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>912</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>915</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>916</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>917</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>918</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>920</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>921</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>924</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>925</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>927</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>928</v>
       </c>
@@ -6522,7 +6522,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>930</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>931</v>
       </c>
@@ -6867,7 +6867,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>932</v>
       </c>
@@ -7040,7 +7040,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>1005</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>1006</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>1007</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>1009</v>
       </c>
@@ -7730,7 +7730,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>1010</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>1012</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>1014</v>
       </c>
@@ -8247,7 +8247,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>1015</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>1034</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>1036</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>1037</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>1039</v>
       </c>
@@ -9108,7 +9108,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>1040</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>1045</v>
       </c>
@@ -9453,7 +9453,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>1084</v>
       </c>
@@ -9626,7 +9626,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>138</v>
       </c>
@@ -9788,7 +9788,7 @@
         <v>46508</v>
       </c>
     </row>
-    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>172</v>
       </c>
@@ -9951,7 +9951,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>143</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>144</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>145</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>146</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>147</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="52" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>152</v>
       </c>
@@ -11157,7 +11157,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>173</v>
       </c>
@@ -11320,7 +11320,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="55" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>176</v>
       </c>
@@ -11510,18 +11510,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="O009"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="SPAIN"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E12 K2:K12 D68:D1048191 C16:E55 K16:K1048191 D56 E56:E1048191 C56:C1048191" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E325B49-F87D-4EF0-BEB7-B64FEB846CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEC7993-0F51-4CEE-8109-CFD028F7550B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
@@ -2018,7 +2018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4" filterMode="1">
+  <sheetPr codeName="Feuil4">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF67"/>
@@ -2029,13 +2029,13 @@
     <col min="3" max="3" width="9.28515625" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.85546875" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="34" width="10.42578125" customWidth="1"/>
@@ -2216,7 +2216,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>138</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>143</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>144</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>146</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>147</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>152</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>172</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>175</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>60</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>120</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>121</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>233</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>416</v>
       </c>
@@ -4939,7 +4939,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>901</v>
       </c>
@@ -5112,7 +5112,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>904</v>
       </c>
@@ -5285,7 +5285,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>906</v>
       </c>
@@ -5458,7 +5458,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>907</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>908</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>910</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>912</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>915</v>
       </c>
@@ -6496,7 +6496,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>917</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>921</v>
       </c>
@@ -7188,7 +7188,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>924</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>925</v>
       </c>
@@ -7534,7 +7534,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>927</v>
       </c>
@@ -7707,7 +7707,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>928</v>
       </c>
@@ -7760,7 +7760,7 @@
         <v>5</v>
       </c>
       <c r="Q34" s="3">
-        <f t="shared" ref="Q34:Q65" si="27">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
+        <f t="shared" ref="Q34:Q55" si="27">+IF(I34="SFK Freight Forwarder",O34,O34+P34-1)</f>
         <v>19</v>
       </c>
       <c r="R34" s="3">
@@ -7811,21 +7811,21 @@
         <v>21</v>
       </c>
       <c r="AF34" s="3">
-        <f t="shared" ref="AF34:AF65" si="28">+AE34+AA34-1</f>
+        <f t="shared" ref="AF34:AF55" si="28">+AE34+AA34-1</f>
         <v>53</v>
       </c>
       <c r="AG34" s="6">
         <v>3</v>
       </c>
       <c r="AH34" s="6">
-        <f t="shared" ref="AH34:AH65" si="29">+AF34+AG34</f>
+        <f t="shared" ref="AH34:AH55" si="29">+AF34+AG34</f>
         <v>56</v>
       </c>
       <c r="AI34" s="3">
         <v>7</v>
       </c>
       <c r="AJ34" s="3">
-        <f t="shared" ref="AJ34:AJ65" si="30">+AI34+AH34</f>
+        <f t="shared" ref="AJ34:AJ55" si="30">+AI34+AH34</f>
         <v>63</v>
       </c>
       <c r="AK34" s="3" t="s">
@@ -7835,14 +7835,14 @@
         <v>2</v>
       </c>
       <c r="AM34" s="3">
-        <f t="shared" ref="AM34:AM65" si="31">+AJ34+AL34</f>
+        <f t="shared" ref="AM34:AM55" si="31">+AJ34+AL34</f>
         <v>65</v>
       </c>
       <c r="AN34" s="3">
         <v>2</v>
       </c>
       <c r="AO34" s="3">
-        <f t="shared" ref="AO34:AO65" si="32">+AM34+AN34</f>
+        <f t="shared" ref="AO34:AO55" si="32">+AM34+AN34</f>
         <v>67</v>
       </c>
       <c r="AP34" s="3">
@@ -7857,7 +7857,7 @@
         <v>77</v>
       </c>
       <c r="AS34" s="3">
-        <f t="shared" ref="AS34:AS65" si="33">+AR34+7+AT34</f>
+        <f t="shared" ref="AS34:AS55" si="33">+AR34+7+AT34</f>
         <v>98</v>
       </c>
       <c r="AT34" s="3">
@@ -8021,7 +8021,7 @@
         <v>4</v>
       </c>
       <c r="AQ35" s="3">
-        <f t="shared" ref="AQ35:AQ66" si="35">+AO35+AP35</f>
+        <f t="shared" ref="AQ35:AQ55" si="35">+AO35+AP35</f>
         <v>91</v>
       </c>
       <c r="AR35" s="3">
@@ -8052,7 +8052,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>931</v>
       </c>
@@ -8198,7 +8198,7 @@
         <v>91</v>
       </c>
       <c r="AR36" s="3">
-        <f t="shared" ref="AR36:AR67" si="37">+AQ36+7</f>
+        <f t="shared" ref="AR36:AR55" si="37">+AQ36+7</f>
         <v>98</v>
       </c>
       <c r="AS36" s="3">
@@ -8225,7 +8225,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>932</v>
       </c>
@@ -8571,7 +8571,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1045</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>1084</v>
       </c>
@@ -8917,7 +8917,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>752</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>761</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>888</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>1005</v>
       </c>
@@ -9602,7 +9602,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>1006</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>1007</v>
       </c>
@@ -9948,7 +9948,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>1009</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>1010</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>1012</v>
       </c>
@@ -10465,7 +10465,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>1014</v>
       </c>
@@ -10637,7 +10637,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>1015</v>
       </c>
@@ -10809,7 +10809,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="52" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>1034</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>1036</v>
       </c>
@@ -11153,7 +11153,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>1037</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="55" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>1040</v>
       </c>
@@ -11520,19 +11520,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="SPAIN"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="47">
-      <filters>
-        <filter val="Direct"/>
-        <filter val="Indirect"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C56:C1048191 K2:K12 D68:D1048191 C16:E55 K16:K1048191 D56 E56:E1048191 C2:E12" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEC7993-0F51-4CEE-8109-CFD028F7550B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABBCA3F-9EFD-49DB-AEFF-0534492BD4FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
@@ -2018,7 +2018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-  <sheetPr codeName="Feuil4">
+  <sheetPr codeName="Feuil4" filterMode="1">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:BF67"/>
@@ -2216,7 +2216,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>138</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>171</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>143</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>144</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>145</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>146</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>147</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>152</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>168</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>172</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>175</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>60</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>120</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>121</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>233</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>416</v>
       </c>
@@ -4939,7 +4939,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>901</v>
       </c>
@@ -5112,7 +5112,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>904</v>
       </c>
@@ -5285,7 +5285,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>906</v>
       </c>
@@ -5458,7 +5458,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>907</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>908</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>910</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>912</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>915</v>
       </c>
@@ -6438,11 +6438,11 @@
         <v>62</v>
       </c>
       <c r="AI26" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ26" s="3">
         <f t="shared" si="6"/>
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="AK26" s="3" t="s">
         <v>65</v>
@@ -6452,29 +6452,29 @@
       </c>
       <c r="AM26" s="3">
         <f t="shared" si="7"/>
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="AN26" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO26" s="3">
         <f t="shared" si="8"/>
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP26" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AQ26" s="3">
         <f t="shared" si="11"/>
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="AR26" s="3">
         <f t="shared" si="16"/>
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="9"/>
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="AT26" s="3">
         <v>13</v>
@@ -6496,7 +6496,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>917</v>
       </c>
@@ -6784,11 +6784,11 @@
         <v>75</v>
       </c>
       <c r="AI28" s="50">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AJ28" s="3">
         <f t="shared" si="6"/>
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AK28" s="3" t="s">
         <v>55</v>
@@ -6798,29 +6798,29 @@
       </c>
       <c r="AM28" s="3">
         <f t="shared" si="7"/>
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AN28" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO28" s="3">
         <f t="shared" si="8"/>
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="AP28" s="3">
         <v>1</v>
       </c>
       <c r="AQ28" s="3">
         <f t="shared" si="11"/>
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="AR28" s="3">
         <f t="shared" si="16"/>
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="9"/>
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="AT28" s="3">
         <v>14</v>
@@ -6967,33 +6967,33 @@
         <v>55</v>
       </c>
       <c r="AL29" s="46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM29" s="3">
         <f t="shared" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN29" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO29" s="3">
         <f t="shared" si="8"/>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AP29" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AQ29" s="3">
         <f t="shared" si="11"/>
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AR29" s="3">
         <f t="shared" si="16"/>
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="9"/>
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="AT29" s="3">
         <v>14</v>
@@ -7015,7 +7015,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>921</v>
       </c>
@@ -7188,7 +7188,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>924</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>925</v>
       </c>
@@ -7534,7 +7534,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>927</v>
       </c>
@@ -7707,7 +7707,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>928</v>
       </c>
@@ -7994,11 +7994,11 @@
         <v>79</v>
       </c>
       <c r="AI35" s="50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ35" s="3">
         <f t="shared" si="30"/>
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK35" s="3" t="s">
         <v>55</v>
@@ -8008,29 +8008,29 @@
       </c>
       <c r="AM35" s="3">
         <f t="shared" si="31"/>
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AN35" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AO35" s="3">
         <f t="shared" si="32"/>
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AP35" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AQ35" s="3">
         <f t="shared" ref="AQ35:AQ55" si="35">+AO35+AP35</f>
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AR35" s="3">
         <f t="shared" si="16"/>
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="AS35" s="3">
         <f t="shared" si="33"/>
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="AT35" s="3">
         <v>17</v>
@@ -8052,7 +8052,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>931</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>932</v>
       </c>
@@ -8530,26 +8530,26 @@
         <v>88</v>
       </c>
       <c r="AN38" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AO38" s="3">
         <f t="shared" si="32"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AP38" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ38" s="3">
         <f t="shared" si="35"/>
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AR38" s="3">
         <f t="shared" si="37"/>
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="33"/>
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="AT38" s="3">
         <v>0</v>
@@ -8571,7 +8571,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1045</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>1084</v>
       </c>
@@ -8917,7 +8917,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>752</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>761</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>888</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>1005</v>
       </c>
@@ -9602,7 +9602,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>1006</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>1007</v>
       </c>
@@ -9948,7 +9948,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>1009</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>1010</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>1012</v>
       </c>
@@ -10465,7 +10465,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="50" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>1014</v>
       </c>
@@ -10637,7 +10637,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="51" spans="1:51" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>1015</v>
       </c>
@@ -11153,7 +11153,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>1037</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>1040</v>
       </c>
@@ -11520,7 +11520,24 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}"/>
+  <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="1034"/>
+        <filter val="1036"/>
+        <filter val="1039"/>
+        <filter val="916"/>
+        <filter val="918"/>
+        <filter val="920"/>
+        <filter val="930"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="SPAIN"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C56:C1048191 K2:K12 D68:D1048191 C16:E55 K16:K1048191 D56 E56:E1048191 C2:E12" xr:uid="{833F6030-824F-4AAE-BA3C-131D886541AF}">

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABBCA3F-9EFD-49DB-AEFF-0534492BD4FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC56805-B386-4952-A435-2BBF82DF784C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
@@ -6808,19 +6808,19 @@
         <v>98</v>
       </c>
       <c r="AP28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ28" s="3">
         <f t="shared" si="11"/>
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AR28" s="3">
         <f t="shared" si="16"/>
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="9"/>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AT28" s="3">
         <v>14</v>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC56805-B386-4952-A435-2BBF82DF784C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB5B335-3F5E-4561-BFF3-DC42722BF42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
@@ -2378,7 +2378,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>171</v>
       </c>
@@ -2507,19 +2507,19 @@
         <v>75</v>
       </c>
       <c r="AP3" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ3" s="3">
         <f t="shared" ref="AQ3:AQ34" si="11">+AO3+AP3</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AR3" s="23">
         <f>+AQ3+4</f>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AS3" s="23">
         <f t="shared" si="9"/>
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AT3" s="23">
         <v>14</v>
@@ -3688,11 +3688,11 @@
         <v>66</v>
       </c>
       <c r="AI10" s="23">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ10" s="23">
         <f t="shared" si="6"/>
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="AK10" s="23"/>
       <c r="AL10" s="47">
@@ -3700,29 +3700,29 @@
       </c>
       <c r="AM10" s="23">
         <f t="shared" si="7"/>
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AN10" s="23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO10" s="23">
         <f t="shared" si="8"/>
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AP10" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ10" s="23">
         <f t="shared" si="11"/>
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AR10" s="23">
         <f t="shared" si="16"/>
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AS10" s="23">
         <f t="shared" si="9"/>
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="AT10" s="23">
         <v>14</v>
@@ -6323,7 +6323,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>916</v>
       </c>
@@ -6669,7 +6669,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>918</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>920</v>
       </c>
@@ -7880,7 +7880,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>930</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>1039</v>
       </c>
@@ -10809,7 +10809,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>1034</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>1036</v>
       </c>
@@ -11523,18 +11523,7 @@
   <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
     <filterColumn colId="0">
       <filters>
-        <filter val="1034"/>
-        <filter val="1036"/>
-        <filter val="1039"/>
-        <filter val="916"/>
-        <filter val="918"/>
-        <filter val="920"/>
-        <filter val="930"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="SPAIN"/>
+        <filter val="O002"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/VTT Tool/VTT DATA.xlsx
+++ b/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOJorge\Documents\Python projects\Horse Luis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB5B335-3F5E-4561-BFF3-DC42722BF42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF5AAF0-6DCC-40F8-828E-9CE26E0EB6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="18780" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -2378,7 +2378,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>171</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>908</v>
       </c>
@@ -5719,8 +5719,7 @@
         <v>36</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="25"/>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AB22" s="3">
         <v>2</v>
@@ -5732,25 +5731,25 @@
         <v>7</v>
       </c>
       <c r="AE22" s="3">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AF22" s="3">
         <f t="shared" si="4"/>
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AG22" s="6">
         <v>3</v>
       </c>
       <c r="AH22" s="6">
         <f t="shared" si="5"/>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI22" s="3">
         <v>7</v>
       </c>
       <c r="AJ22" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK22" s="28" t="s">
         <v>79</v>
@@ -5760,17 +5759,17 @@
       </c>
       <c r="AM22" s="3">
         <f t="shared" si="7"/>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN22" s="3">
         <v>2</v>
       </c>
       <c r="AO22" s="3">
         <f t="shared" si="8"/>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AP22" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ22" s="3">
         <f t="shared" si="11"/>
@@ -5789,7 +5788,7 @@
       </c>
       <c r="AU22" s="3">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AV22" s="3" t="s">
         <v>130</v>
@@ -11523,7 +11522,7 @@
   <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
     <filterColumn colId="0">
       <filters>
-        <filter val="O002"/>
+        <filter val="908"/>
       </filters>
     </filterColumn>
   </autoFilter>
